--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -545,7 +545,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
         <v>17</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Metric</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Pass Rate</t>
   </si>
   <si>
-    <t>0.00%</t>
+    <t>0%</t>
   </si>
   <si>
     <t>Category</t>
@@ -51,9 +51,6 @@
     <t>Duration (ms)</t>
   </si>
   <si>
-    <t>Fatal</t>
-  </si>
-  <si>
     <t>Title</t>
   </si>
   <si>
@@ -61,15 +58,6 @@
   </si>
   <si>
     <t>Error</t>
-  </si>
-  <si>
-    <t>[Fatal-T1] Setup/Appium Crash</t>
-  </si>
-  <si>
-    <t>failed</t>
-  </si>
-  <si>
-    <t>WebDriver session failed to initialize or crashed.</t>
   </si>
 </sst>
 </file>
@@ -465,7 +453,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -481,7 +469,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -500,7 +488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -528,26 +516,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -556,7 +524,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -571,33 +539,16 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
         <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
       </c>
       <c r="D1" t="s">
         <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2">
         <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1342</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1338</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1305</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1295</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1407</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1302</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1356</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1344</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1345</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
   </sheetData>
@@ -4154,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -4188,7 +4188,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -4205,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -4222,7 +4222,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -4256,7 +4256,7 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -4273,7 +4273,7 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4307,7 +4307,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4341,7 +4341,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -4358,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4409,7 +4409,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -4426,7 +4426,7 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -4460,7 +4460,7 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -4494,7 +4494,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -4511,7 +4511,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -4528,7 +4528,7 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -4545,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E25" t="s">
         <v>28</v>
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -4579,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -4596,7 +4596,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -4613,7 +4613,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
         <v>28</v>
@@ -4647,7 +4647,7 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4681,7 +4681,7 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4698,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="D34">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -4715,7 +4715,7 @@
         <v>27</v>
       </c>
       <c r="D35">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
         <v>28</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -4749,7 +4749,7 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E37" t="s">
         <v>28</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="D38">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
         <v>28</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
@@ -4817,7 +4817,7 @@
         <v>27</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4834,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4851,7 +4851,7 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
@@ -4885,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E45" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
         <v>27</v>
       </c>
       <c r="D46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="D48">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4953,7 +4953,7 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
@@ -4970,7 +4970,7 @@
         <v>27</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -4987,7 +4987,7 @@
         <v>27</v>
       </c>
       <c r="D51">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
@@ -5004,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5038,7 +5038,7 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E54" t="s">
         <v>28</v>
@@ -5055,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="D55">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -5072,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E56" t="s">
         <v>28</v>
@@ -5089,7 +5089,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E57" t="s">
         <v>28</v>
@@ -5106,7 +5106,7 @@
         <v>27</v>
       </c>
       <c r="D58">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -5123,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E59" t="s">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         <v>27</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E60" t="s">
         <v>28</v>
@@ -5157,7 +5157,7 @@
         <v>27</v>
       </c>
       <c r="D61">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -5174,7 +5174,7 @@
         <v>27</v>
       </c>
       <c r="D62">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
@@ -5191,7 +5191,7 @@
         <v>27</v>
       </c>
       <c r="D63">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="D64">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
@@ -5225,7 +5225,7 @@
         <v>27</v>
       </c>
       <c r="D65">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -5242,7 +5242,7 @@
         <v>27</v>
       </c>
       <c r="D66">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="D67">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
@@ -5293,7 +5293,7 @@
         <v>27</v>
       </c>
       <c r="D69">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -5310,7 +5310,7 @@
         <v>27</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="D71">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -5344,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="D72">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
@@ -5361,7 +5361,7 @@
         <v>27</v>
       </c>
       <c r="D73">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -5395,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="D75">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="D76">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
@@ -5429,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="D77">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -5446,7 +5446,7 @@
         <v>27</v>
       </c>
       <c r="D78">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
@@ -5463,7 +5463,7 @@
         <v>27</v>
       </c>
       <c r="D79">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
@@ -5480,7 +5480,7 @@
         <v>27</v>
       </c>
       <c r="D80">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
@@ -5497,7 +5497,7 @@
         <v>27</v>
       </c>
       <c r="D81">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -5514,7 +5514,7 @@
         <v>27</v>
       </c>
       <c r="D82">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
@@ -5531,7 +5531,7 @@
         <v>27</v>
       </c>
       <c r="D83">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
@@ -5548,7 +5548,7 @@
         <v>27</v>
       </c>
       <c r="D84">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
@@ -5565,7 +5565,7 @@
         <v>27</v>
       </c>
       <c r="D85">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -5582,7 +5582,7 @@
         <v>27</v>
       </c>
       <c r="D86">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
@@ -5599,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="D87">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
@@ -5616,7 +5616,7 @@
         <v>27</v>
       </c>
       <c r="D88">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -5633,7 +5633,7 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="D90">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -5667,7 +5667,7 @@
         <v>27</v>
       </c>
       <c r="D91">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E91" t="s">
         <v>28</v>
@@ -5684,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="D92">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
@@ -5701,7 +5701,7 @@
         <v>27</v>
       </c>
       <c r="D93">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E93" t="s">
         <v>28</v>
@@ -5718,7 +5718,7 @@
         <v>27</v>
       </c>
       <c r="D94">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E94" t="s">
         <v>28</v>
@@ -5735,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D95">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -5752,7 +5752,7 @@
         <v>27</v>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E96" t="s">
         <v>28</v>
@@ -5769,7 +5769,7 @@
         <v>27</v>
       </c>
       <c r="D97">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E97" t="s">
         <v>28</v>
@@ -5786,7 +5786,7 @@
         <v>27</v>
       </c>
       <c r="D98">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="D99">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E99" t="s">
         <v>28</v>
@@ -5820,7 +5820,7 @@
         <v>27</v>
       </c>
       <c r="D100">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E100" t="s">
         <v>28</v>
@@ -5837,7 +5837,7 @@
         <v>27</v>
       </c>
       <c r="D101">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E101" t="s">
         <v>28</v>
@@ -5854,7 +5854,7 @@
         <v>27</v>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E102" t="s">
         <v>28</v>
@@ -5871,7 +5871,7 @@
         <v>27</v>
       </c>
       <c r="D103">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E103" t="s">
         <v>28</v>
@@ -5905,7 +5905,7 @@
         <v>27</v>
       </c>
       <c r="D105">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E105" t="s">
         <v>28</v>
@@ -5922,7 +5922,7 @@
         <v>27</v>
       </c>
       <c r="D106">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>27</v>
       </c>
       <c r="D107">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E107" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="D108">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5973,7 +5973,7 @@
         <v>27</v>
       </c>
       <c r="D109">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E109" t="s">
         <v>28</v>
@@ -5990,7 +5990,7 @@
         <v>27</v>
       </c>
       <c r="D110">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E110" t="s">
         <v>28</v>
@@ -6007,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="D111">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="D112">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="D113">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E113" t="s">
         <v>28</v>
@@ -6058,7 +6058,7 @@
         <v>27</v>
       </c>
       <c r="D114">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>27</v>
       </c>
       <c r="D115">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -6092,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="D116">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E116" t="s">
         <v>28</v>
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="D117">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E117" t="s">
         <v>28</v>
@@ -6126,7 +6126,7 @@
         <v>27</v>
       </c>
       <c r="D118">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E118" t="s">
         <v>28</v>
@@ -6143,7 +6143,7 @@
         <v>27</v>
       </c>
       <c r="D119">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E119" t="s">
         <v>28</v>
@@ -6160,7 +6160,7 @@
         <v>27</v>
       </c>
       <c r="D120">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E120" t="s">
         <v>28</v>
@@ -6177,7 +6177,7 @@
         <v>27</v>
       </c>
       <c r="D121">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E121" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="D122">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E122" t="s">
         <v>28</v>
@@ -6211,7 +6211,7 @@
         <v>27</v>
       </c>
       <c r="D123">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E123" t="s">
         <v>28</v>
@@ -6228,7 +6228,7 @@
         <v>27</v>
       </c>
       <c r="D124">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E124" t="s">
         <v>28</v>
@@ -6245,7 +6245,7 @@
         <v>27</v>
       </c>
       <c r="D125">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
@@ -6262,7 +6262,7 @@
         <v>27</v>
       </c>
       <c r="D126">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -6279,7 +6279,7 @@
         <v>27</v>
       </c>
       <c r="D127">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E127" t="s">
         <v>28</v>
@@ -6296,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="D128">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E128" t="s">
         <v>28</v>
@@ -6313,7 +6313,7 @@
         <v>27</v>
       </c>
       <c r="D129">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
@@ -6330,7 +6330,7 @@
         <v>27</v>
       </c>
       <c r="D130">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E130" t="s">
         <v>28</v>
@@ -6347,7 +6347,7 @@
         <v>27</v>
       </c>
       <c r="D131">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E131" t="s">
         <v>28</v>
@@ -6364,7 +6364,7 @@
         <v>27</v>
       </c>
       <c r="D132">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E132" t="s">
         <v>28</v>
@@ -6381,7 +6381,7 @@
         <v>27</v>
       </c>
       <c r="D133">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E133" t="s">
         <v>28</v>
@@ -6398,7 +6398,7 @@
         <v>27</v>
       </c>
       <c r="D134">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E134" t="s">
         <v>28</v>
@@ -6415,7 +6415,7 @@
         <v>27</v>
       </c>
       <c r="D135">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E135" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="D136">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E136" t="s">
         <v>28</v>
@@ -6449,7 +6449,7 @@
         <v>27</v>
       </c>
       <c r="D137">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E137" t="s">
         <v>28</v>
@@ -6466,7 +6466,7 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E138" t="s">
         <v>28</v>
@@ -6483,7 +6483,7 @@
         <v>27</v>
       </c>
       <c r="D139">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E139" t="s">
         <v>28</v>
@@ -6517,7 +6517,7 @@
         <v>27</v>
       </c>
       <c r="D141">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E141" t="s">
         <v>28</v>
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="D142">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E142" t="s">
         <v>28</v>
@@ -6551,7 +6551,7 @@
         <v>27</v>
       </c>
       <c r="D143">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E143" t="s">
         <v>28</v>
@@ -6568,7 +6568,7 @@
         <v>27</v>
       </c>
       <c r="D144">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E144" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="D145">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E145" t="s">
         <v>28</v>
@@ -6602,7 +6602,7 @@
         <v>27</v>
       </c>
       <c r="D146">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E146" t="s">
         <v>28</v>
@@ -6619,7 +6619,7 @@
         <v>27</v>
       </c>
       <c r="D147">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E147" t="s">
         <v>28</v>
@@ -6636,7 +6636,7 @@
         <v>27</v>
       </c>
       <c r="D148">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E148" t="s">
         <v>28</v>
@@ -6653,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="D149">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6670,7 +6670,7 @@
         <v>27</v>
       </c>
       <c r="D150">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E150" t="s">
         <v>28</v>
@@ -6687,7 +6687,7 @@
         <v>27</v>
       </c>
       <c r="D151">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>27</v>
       </c>
       <c r="D152">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E152" t="s">
         <v>28</v>
@@ -6721,7 +6721,7 @@
         <v>27</v>
       </c>
       <c r="D153">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E153" t="s">
         <v>28</v>
@@ -6738,7 +6738,7 @@
         <v>27</v>
       </c>
       <c r="D154">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E154" t="s">
         <v>28</v>
@@ -6755,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -6772,7 +6772,7 @@
         <v>27</v>
       </c>
       <c r="D156">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E156" t="s">
         <v>28</v>
@@ -6789,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="D157">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E157" t="s">
         <v>28</v>
@@ -6806,7 +6806,7 @@
         <v>27</v>
       </c>
       <c r="D158">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E158" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="D159">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E159" t="s">
         <v>28</v>
@@ -6857,7 +6857,7 @@
         <v>27</v>
       </c>
       <c r="D161">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
@@ -6891,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="D163">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E163" t="s">
         <v>28</v>
@@ -6908,7 +6908,7 @@
         <v>27</v>
       </c>
       <c r="D164">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E164" t="s">
         <v>28</v>
@@ -6942,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="D166">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E166" t="s">
         <v>28</v>
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="D167">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E167" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="D168">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E168" t="s">
         <v>28</v>
@@ -6993,7 +6993,7 @@
         <v>27</v>
       </c>
       <c r="D169">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E169" t="s">
         <v>28</v>
@@ -7010,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="D170">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E170" t="s">
         <v>28</v>
@@ -7027,7 +7027,7 @@
         <v>27</v>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E171" t="s">
         <v>28</v>
@@ -7044,7 +7044,7 @@
         <v>27</v>
       </c>
       <c r="D172">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E172" t="s">
         <v>28</v>
@@ -7061,7 +7061,7 @@
         <v>27</v>
       </c>
       <c r="D173">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E173" t="s">
         <v>28</v>
@@ -7078,7 +7078,7 @@
         <v>27</v>
       </c>
       <c r="D174">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E174" t="s">
         <v>28</v>
@@ -7112,7 +7112,7 @@
         <v>27</v>
       </c>
       <c r="D176">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E176" t="s">
         <v>28</v>
@@ -7129,7 +7129,7 @@
         <v>27</v>
       </c>
       <c r="D177">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E177" t="s">
         <v>28</v>
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="D178">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E178" t="s">
         <v>28</v>
@@ -7163,7 +7163,7 @@
         <v>27</v>
       </c>
       <c r="D179">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E179" t="s">
         <v>28</v>
@@ -7180,7 +7180,7 @@
         <v>27</v>
       </c>
       <c r="D180">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="D182">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E182" t="s">
         <v>28</v>
@@ -7231,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="D183">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
@@ -7248,7 +7248,7 @@
         <v>27</v>
       </c>
       <c r="D184">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E184" t="s">
         <v>28</v>
@@ -7265,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="D185">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E185" t="s">
         <v>28</v>
@@ -7299,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="D187">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E187" t="s">
         <v>28</v>
@@ -7316,7 +7316,7 @@
         <v>27</v>
       </c>
       <c r="D188">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -7333,7 +7333,7 @@
         <v>27</v>
       </c>
       <c r="D189">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E189" t="s">
         <v>28</v>
@@ -7350,7 +7350,7 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E190" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="D191">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
@@ -7384,7 +7384,7 @@
         <v>27</v>
       </c>
       <c r="D192">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E192" t="s">
         <v>28</v>
@@ -7401,7 +7401,7 @@
         <v>27</v>
       </c>
       <c r="D193">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E193" t="s">
         <v>28</v>
@@ -7418,7 +7418,7 @@
         <v>27</v>
       </c>
       <c r="D194">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E194" t="s">
         <v>28</v>
@@ -7435,7 +7435,7 @@
         <v>27</v>
       </c>
       <c r="D195">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E195" t="s">
         <v>28</v>
@@ -7452,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="D196">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E196" t="s">
         <v>28</v>
@@ -7469,7 +7469,7 @@
         <v>27</v>
       </c>
       <c r="D197">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E197" t="s">
         <v>28</v>
@@ -7486,7 +7486,7 @@
         <v>27</v>
       </c>
       <c r="D198">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E198" t="s">
         <v>28</v>
@@ -7503,7 +7503,7 @@
         <v>27</v>
       </c>
       <c r="D199">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E199" t="s">
         <v>28</v>
@@ -7520,7 +7520,7 @@
         <v>27</v>
       </c>
       <c r="D200">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E200" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>27</v>
       </c>
       <c r="D201">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E201" t="s">
         <v>28</v>
@@ -7554,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="D202">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E202" t="s">
         <v>28</v>
@@ -7571,7 +7571,7 @@
         <v>27</v>
       </c>
       <c r="D203">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
@@ -7588,7 +7588,7 @@
         <v>27</v>
       </c>
       <c r="D204">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E204" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="D205">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -7639,7 +7639,7 @@
         <v>27</v>
       </c>
       <c r="D207">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E207" t="s">
         <v>28</v>
@@ -7656,7 +7656,7 @@
         <v>27</v>
       </c>
       <c r="D208">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E208" t="s">
         <v>28</v>
@@ -7673,7 +7673,7 @@
         <v>27</v>
       </c>
       <c r="D209">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E209" t="s">
         <v>28</v>
@@ -7690,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="D210">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E210" t="s">
         <v>28</v>
@@ -7707,7 +7707,7 @@
         <v>27</v>
       </c>
       <c r="D211">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E211" t="s">
         <v>28</v>
@@ -7724,7 +7724,7 @@
         <v>27</v>
       </c>
       <c r="D212">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E212" t="s">
         <v>28</v>
@@ -7741,7 +7741,7 @@
         <v>27</v>
       </c>
       <c r="D213">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E213" t="s">
         <v>28</v>
@@ -7775,7 +7775,7 @@
         <v>27</v>
       </c>
       <c r="D215">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E215" t="s">
         <v>28</v>
@@ -7792,7 +7792,7 @@
         <v>27</v>
       </c>
       <c r="D216">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E216" t="s">
         <v>28</v>
@@ -7809,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="D217">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E217" t="s">
         <v>28</v>
@@ -7826,7 +7826,7 @@
         <v>27</v>
       </c>
       <c r="D218">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E218" t="s">
         <v>28</v>
@@ -7843,7 +7843,7 @@
         <v>27</v>
       </c>
       <c r="D219">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E219" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="D220">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E220" t="s">
         <v>28</v>
@@ -7877,7 +7877,7 @@
         <v>27</v>
       </c>
       <c r="D221">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E221" t="s">
         <v>28</v>
@@ -7894,7 +7894,7 @@
         <v>27</v>
       </c>
       <c r="D222">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E222" t="s">
         <v>28</v>
@@ -7911,7 +7911,7 @@
         <v>27</v>
       </c>
       <c r="D223">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E223" t="s">
         <v>28</v>
@@ -7979,7 +7979,7 @@
         <v>27</v>
       </c>
       <c r="D227">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E227" t="s">
         <v>28</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="D228">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E228" t="s">
         <v>28</v>
@@ -8013,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="D229">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E229" t="s">
         <v>28</v>
@@ -8030,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="D230">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E230" t="s">
         <v>28</v>
@@ -8047,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="D231">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E231" t="s">
         <v>28</v>
@@ -8064,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="D232">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E232" t="s">
         <v>28</v>
@@ -8081,7 +8081,7 @@
         <v>27</v>
       </c>
       <c r="D233">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E233" t="s">
         <v>28</v>
@@ -8098,7 +8098,7 @@
         <v>27</v>
       </c>
       <c r="D234">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E234" t="s">
         <v>28</v>
@@ -8115,7 +8115,7 @@
         <v>27</v>
       </c>
       <c r="D235">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E235" t="s">
         <v>28</v>
@@ -8132,7 +8132,7 @@
         <v>27</v>
       </c>
       <c r="D236">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E236" t="s">
         <v>28</v>
@@ -8166,7 +8166,7 @@
         <v>27</v>
       </c>
       <c r="D238">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E238" t="s">
         <v>28</v>
@@ -8183,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="D239">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E239" t="s">
         <v>28</v>
@@ -8200,7 +8200,7 @@
         <v>27</v>
       </c>
       <c r="D240">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E240" t="s">
         <v>28</v>
@@ -8217,7 +8217,7 @@
         <v>27</v>
       </c>
       <c r="D241">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E241" t="s">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>27</v>
       </c>
       <c r="D242">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E242" t="s">
         <v>28</v>
@@ -8251,7 +8251,7 @@
         <v>27</v>
       </c>
       <c r="D243">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E243" t="s">
         <v>28</v>
@@ -8268,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="D244">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E244" t="s">
         <v>28</v>
@@ -8285,7 +8285,7 @@
         <v>27</v>
       </c>
       <c r="D245">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E245" t="s">
         <v>28</v>
@@ -8302,7 +8302,7 @@
         <v>27</v>
       </c>
       <c r="D246">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E246" t="s">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="D247">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E247" t="s">
         <v>28</v>
@@ -8353,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="D249">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E249" t="s">
         <v>28</v>
@@ -8370,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="D250">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E250" t="s">
         <v>28</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="D251">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E251" t="s">
         <v>28</v>
@@ -8404,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="D252">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E252" t="s">
         <v>28</v>
@@ -8421,7 +8421,7 @@
         <v>27</v>
       </c>
       <c r="D253">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E253" t="s">
         <v>28</v>
@@ -8438,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D254">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E254" t="s">
         <v>28</v>
@@ -8455,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="D255">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E255" t="s">
         <v>28</v>
@@ -8472,7 +8472,7 @@
         <v>27</v>
       </c>
       <c r="D256">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E256" t="s">
         <v>28</v>
@@ -8489,7 +8489,7 @@
         <v>27</v>
       </c>
       <c r="D257">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E257" t="s">
         <v>28</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="D258">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E258" t="s">
         <v>28</v>
@@ -8523,7 +8523,7 @@
         <v>27</v>
       </c>
       <c r="D259">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E259" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="D260">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E260" t="s">
         <v>28</v>
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="D261">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E261" t="s">
         <v>28</v>
@@ -8574,7 +8574,7 @@
         <v>27</v>
       </c>
       <c r="D262">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E262" t="s">
         <v>28</v>
@@ -8591,7 +8591,7 @@
         <v>27</v>
       </c>
       <c r="D263">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E263" t="s">
         <v>28</v>
@@ -8608,7 +8608,7 @@
         <v>27</v>
       </c>
       <c r="D264">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E264" t="s">
         <v>28</v>
@@ -8625,7 +8625,7 @@
         <v>27</v>
       </c>
       <c r="D265">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E265" t="s">
         <v>28</v>
@@ -8642,7 +8642,7 @@
         <v>27</v>
       </c>
       <c r="D266">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E266" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="D267">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E267" t="s">
         <v>28</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="D268">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E268" t="s">
         <v>28</v>
@@ -8693,7 +8693,7 @@
         <v>27</v>
       </c>
       <c r="D269">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E269" t="s">
         <v>28</v>
@@ -8727,7 +8727,7 @@
         <v>27</v>
       </c>
       <c r="D271">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E271" t="s">
         <v>28</v>
@@ -8744,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="D272">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E272" t="s">
         <v>28</v>
@@ -8761,7 +8761,7 @@
         <v>27</v>
       </c>
       <c r="D273">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E273" t="s">
         <v>28</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="D274">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E274" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>27</v>
       </c>
       <c r="D275">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E275" t="s">
         <v>28</v>
@@ -8812,7 +8812,7 @@
         <v>27</v>
       </c>
       <c r="D276">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E276" t="s">
         <v>28</v>
@@ -8846,7 +8846,7 @@
         <v>27</v>
       </c>
       <c r="D278">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E278" t="s">
         <v>28</v>
@@ -8863,7 +8863,7 @@
         <v>27</v>
       </c>
       <c r="D279">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E279" t="s">
         <v>28</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E280" t="s">
         <v>28</v>
@@ -8897,7 +8897,7 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E281" t="s">
         <v>28</v>
@@ -8914,7 +8914,7 @@
         <v>27</v>
       </c>
       <c r="D282">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E282" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="D283">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E283" t="s">
         <v>28</v>
@@ -8965,7 +8965,7 @@
         <v>27</v>
       </c>
       <c r="D285">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E285" t="s">
         <v>28</v>
@@ -8982,7 +8982,7 @@
         <v>27</v>
       </c>
       <c r="D286">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E286" t="s">
         <v>28</v>
@@ -8999,7 +8999,7 @@
         <v>27</v>
       </c>
       <c r="D287">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E287" t="s">
         <v>28</v>
@@ -9016,7 +9016,7 @@
         <v>27</v>
       </c>
       <c r="D288">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E288" t="s">
         <v>28</v>
@@ -9033,7 +9033,7 @@
         <v>27</v>
       </c>
       <c r="D289">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E289" t="s">
         <v>28</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="D290">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E290" t="s">
         <v>28</v>
@@ -9084,7 +9084,7 @@
         <v>27</v>
       </c>
       <c r="D292">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E292" t="s">
         <v>28</v>
@@ -9101,7 +9101,7 @@
         <v>27</v>
       </c>
       <c r="D293">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E293" t="s">
         <v>28</v>
@@ -9118,7 +9118,7 @@
         <v>27</v>
       </c>
       <c r="D294">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E294" t="s">
         <v>28</v>
@@ -9135,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="D295">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E295" t="s">
         <v>28</v>
@@ -9152,7 +9152,7 @@
         <v>27</v>
       </c>
       <c r="D296">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E296" t="s">
         <v>28</v>
@@ -9169,7 +9169,7 @@
         <v>27</v>
       </c>
       <c r="D297">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E297" t="s">
         <v>28</v>
@@ -9203,7 +9203,7 @@
         <v>27</v>
       </c>
       <c r="D299">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E299" t="s">
         <v>28</v>
@@ -9220,7 +9220,7 @@
         <v>27</v>
       </c>
       <c r="D300">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E300" t="s">
         <v>28</v>
@@ -9237,7 +9237,7 @@
         <v>27</v>
       </c>
       <c r="D301">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E301" t="s">
         <v>28</v>
@@ -9254,7 +9254,7 @@
         <v>27</v>
       </c>
       <c r="D302">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E302" t="s">
         <v>28</v>
@@ -9271,7 +9271,7 @@
         <v>27</v>
       </c>
       <c r="D303">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E303" t="s">
         <v>28</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="D304">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E304" t="s">
         <v>28</v>
@@ -9305,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="D305">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E305" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="D306">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E306" t="s">
         <v>28</v>
@@ -9339,7 +9339,7 @@
         <v>27</v>
       </c>
       <c r="D307">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E307" t="s">
         <v>28</v>
@@ -9356,7 +9356,7 @@
         <v>27</v>
       </c>
       <c r="D308">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E308" t="s">
         <v>28</v>
@@ -9373,7 +9373,7 @@
         <v>27</v>
       </c>
       <c r="D309">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E309" t="s">
         <v>28</v>
@@ -9390,7 +9390,7 @@
         <v>27</v>
       </c>
       <c r="D310">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E310" t="s">
         <v>28</v>
@@ -9407,7 +9407,7 @@
         <v>27</v>
       </c>
       <c r="D311">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E311" t="s">
         <v>28</v>
@@ -9424,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="D312">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E312" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="D313">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E313" t="s">
         <v>28</v>
@@ -9458,7 +9458,7 @@
         <v>27</v>
       </c>
       <c r="D314">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E314" t="s">
         <v>28</v>
@@ -9475,7 +9475,7 @@
         <v>27</v>
       </c>
       <c r="D315">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E315" t="s">
         <v>28</v>
@@ -9492,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="D316">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E316" t="s">
         <v>28</v>
@@ -9509,7 +9509,7 @@
         <v>27</v>
       </c>
       <c r="D317">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E317" t="s">
         <v>28</v>
@@ -9526,7 +9526,7 @@
         <v>27</v>
       </c>
       <c r="D318">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E318" t="s">
         <v>28</v>
@@ -9543,7 +9543,7 @@
         <v>27</v>
       </c>
       <c r="D319">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E319" t="s">
         <v>28</v>
@@ -9560,7 +9560,7 @@
         <v>27</v>
       </c>
       <c r="D320">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E320" t="s">
         <v>28</v>
@@ -9577,7 +9577,7 @@
         <v>27</v>
       </c>
       <c r="D321">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E321" t="s">
         <v>28</v>
@@ -9594,7 +9594,7 @@
         <v>27</v>
       </c>
       <c r="D322">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E322" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
         <v>27</v>
       </c>
       <c r="D323">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E323" t="s">
         <v>28</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="D324">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E324" t="s">
         <v>28</v>
@@ -9662,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="D326">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E326" t="s">
         <v>28</v>
@@ -9679,7 +9679,7 @@
         <v>27</v>
       </c>
       <c r="D327">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E327" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="D329">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E329" t="s">
         <v>28</v>
@@ -9730,7 +9730,7 @@
         <v>27</v>
       </c>
       <c r="D330">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E330" t="s">
         <v>28</v>
@@ -9747,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="D331">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E331" t="s">
         <v>28</v>
@@ -9764,7 +9764,7 @@
         <v>27</v>
       </c>
       <c r="D332">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E332" t="s">
         <v>28</v>
@@ -9781,7 +9781,7 @@
         <v>27</v>
       </c>
       <c r="D333">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E333" t="s">
         <v>28</v>
@@ -9798,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="D334">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E334" t="s">
         <v>28</v>
@@ -9815,7 +9815,7 @@
         <v>27</v>
       </c>
       <c r="D335">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E335" t="s">
         <v>28</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="D336">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E336" t="s">
         <v>28</v>
@@ -9849,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="D337">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E337" t="s">
         <v>28</v>
@@ -9866,7 +9866,7 @@
         <v>27</v>
       </c>
       <c r="D338">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E338" t="s">
         <v>28</v>
@@ -9883,7 +9883,7 @@
         <v>27</v>
       </c>
       <c r="D339">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E339" t="s">
         <v>28</v>
@@ -9900,7 +9900,7 @@
         <v>27</v>
       </c>
       <c r="D340">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E340" t="s">
         <v>28</v>
@@ -9917,7 +9917,7 @@
         <v>27</v>
       </c>
       <c r="D341">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E341" t="s">
         <v>28</v>
@@ -9934,7 +9934,7 @@
         <v>27</v>
       </c>
       <c r="D342">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E342" t="s">
         <v>28</v>
@@ -9951,7 +9951,7 @@
         <v>27</v>
       </c>
       <c r="D343">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E343" t="s">
         <v>28</v>
@@ -9968,7 +9968,7 @@
         <v>27</v>
       </c>
       <c r="D344">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E344" t="s">
         <v>28</v>
@@ -9985,7 +9985,7 @@
         <v>27</v>
       </c>
       <c r="D345">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E345" t="s">
         <v>28</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D346">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E346" t="s">
         <v>28</v>
@@ -10019,7 +10019,7 @@
         <v>27</v>
       </c>
       <c r="D347">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E347" t="s">
         <v>28</v>
@@ -10036,7 +10036,7 @@
         <v>27</v>
       </c>
       <c r="D348">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E348" t="s">
         <v>28</v>
@@ -10053,7 +10053,7 @@
         <v>27</v>
       </c>
       <c r="D349">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E349" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="D350">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E350" t="s">
         <v>28</v>
@@ -10087,7 +10087,7 @@
         <v>27</v>
       </c>
       <c r="D351">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E351" t="s">
         <v>28</v>
@@ -10104,7 +10104,7 @@
         <v>27</v>
       </c>
       <c r="D352">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E352" t="s">
         <v>28</v>
@@ -10121,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D353">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E353" t="s">
         <v>28</v>
@@ -10138,7 +10138,7 @@
         <v>27</v>
       </c>
       <c r="D354">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E354" t="s">
         <v>28</v>
@@ -10155,7 +10155,7 @@
         <v>27</v>
       </c>
       <c r="D355">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E355" t="s">
         <v>28</v>
@@ -10189,7 +10189,7 @@
         <v>27</v>
       </c>
       <c r="D357">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E357" t="s">
         <v>28</v>
@@ -10206,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="D358">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E358" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="D359">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E359" t="s">
         <v>28</v>
@@ -10240,7 +10240,7 @@
         <v>27</v>
       </c>
       <c r="D360">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E360" t="s">
         <v>28</v>
@@ -10257,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="D361">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E361" t="s">
         <v>28</v>
@@ -10274,7 +10274,7 @@
         <v>27</v>
       </c>
       <c r="D362">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E362" t="s">
         <v>28</v>
@@ -10291,7 +10291,7 @@
         <v>27</v>
       </c>
       <c r="D363">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E363" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="D364">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E364" t="s">
         <v>28</v>
@@ -10325,7 +10325,7 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E365" t="s">
         <v>28</v>
@@ -10342,7 +10342,7 @@
         <v>27</v>
       </c>
       <c r="D366">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E366" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
         <v>27</v>
       </c>
       <c r="D367">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E367" t="s">
         <v>28</v>
@@ -10376,7 +10376,7 @@
         <v>27</v>
       </c>
       <c r="D368">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E368" t="s">
         <v>28</v>
@@ -10393,7 +10393,7 @@
         <v>27</v>
       </c>
       <c r="D369">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E369" t="s">
         <v>28</v>
@@ -10410,7 +10410,7 @@
         <v>27</v>
       </c>
       <c r="D370">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E370" t="s">
         <v>28</v>
@@ -10427,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="D371">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E371" t="s">
         <v>28</v>
@@ -10444,7 +10444,7 @@
         <v>27</v>
       </c>
       <c r="D372">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E372" t="s">
         <v>28</v>
@@ -10461,7 +10461,7 @@
         <v>27</v>
       </c>
       <c r="D373">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E373" t="s">
         <v>28</v>
@@ -10478,7 +10478,7 @@
         <v>27</v>
       </c>
       <c r="D374">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E374" t="s">
         <v>28</v>
@@ -10495,7 +10495,7 @@
         <v>27</v>
       </c>
       <c r="D375">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E375" t="s">
         <v>28</v>
@@ -10512,7 +10512,7 @@
         <v>27</v>
       </c>
       <c r="D376">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E376" t="s">
         <v>28</v>
@@ -10529,7 +10529,7 @@
         <v>27</v>
       </c>
       <c r="D377">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E377" t="s">
         <v>28</v>
@@ -10546,7 +10546,7 @@
         <v>27</v>
       </c>
       <c r="D378">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E378" t="s">
         <v>28</v>
@@ -10563,7 +10563,7 @@
         <v>27</v>
       </c>
       <c r="D379">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E379" t="s">
         <v>28</v>
@@ -10597,7 +10597,7 @@
         <v>27</v>
       </c>
       <c r="D381">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E381" t="s">
         <v>28</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="D382">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E382" t="s">
         <v>28</v>
@@ -10631,7 +10631,7 @@
         <v>27</v>
       </c>
       <c r="D383">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E383" t="s">
         <v>28</v>
@@ -10648,7 +10648,7 @@
         <v>27</v>
       </c>
       <c r="D384">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E384" t="s">
         <v>28</v>
@@ -10665,7 +10665,7 @@
         <v>27</v>
       </c>
       <c r="D385">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E385" t="s">
         <v>28</v>
@@ -10682,7 +10682,7 @@
         <v>27</v>
       </c>
       <c r="D386">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E386" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="D387">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E387" t="s">
         <v>28</v>
@@ -10716,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="D388">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E388" t="s">
         <v>28</v>
@@ -10733,7 +10733,7 @@
         <v>27</v>
       </c>
       <c r="D389">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E389" t="s">
         <v>28</v>
@@ -10750,7 +10750,7 @@
         <v>27</v>
       </c>
       <c r="D390">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E390" t="s">
         <v>28</v>
@@ -10767,7 +10767,7 @@
         <v>27</v>
       </c>
       <c r="D391">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E391" t="s">
         <v>28</v>
@@ -10784,7 +10784,7 @@
         <v>27</v>
       </c>
       <c r="D392">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E392" t="s">
         <v>28</v>
@@ -10801,7 +10801,7 @@
         <v>27</v>
       </c>
       <c r="D393">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E393" t="s">
         <v>28</v>
@@ -10818,7 +10818,7 @@
         <v>27</v>
       </c>
       <c r="D394">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E394" t="s">
         <v>28</v>
@@ -10835,7 +10835,7 @@
         <v>27</v>
       </c>
       <c r="D395">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E395" t="s">
         <v>28</v>
@@ -10852,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="D396">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E396" t="s">
         <v>28</v>
@@ -10869,7 +10869,7 @@
         <v>27</v>
       </c>
       <c r="D397">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E397" t="s">
         <v>28</v>
@@ -10886,7 +10886,7 @@
         <v>27</v>
       </c>
       <c r="D398">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E398" t="s">
         <v>28</v>
@@ -10903,7 +10903,7 @@
         <v>27</v>
       </c>
       <c r="D399">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E399" t="s">
         <v>28</v>
@@ -10920,7 +10920,7 @@
         <v>27</v>
       </c>
       <c r="D400">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E400" t="s">
         <v>28</v>
@@ -10937,7 +10937,7 @@
         <v>27</v>
       </c>
       <c r="D401">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E401" t="s">
         <v>28</v>
@@ -10954,7 +10954,7 @@
         <v>27</v>
       </c>
       <c r="D402">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E402" t="s">
         <v>28</v>
@@ -10971,7 +10971,7 @@
         <v>27</v>
       </c>
       <c r="D403">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E403" t="s">
         <v>28</v>
@@ -10988,7 +10988,7 @@
         <v>27</v>
       </c>
       <c r="D404">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E404" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="D405">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E405" t="s">
         <v>28</v>
@@ -11022,7 +11022,7 @@
         <v>27</v>
       </c>
       <c r="D406">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E406" t="s">
         <v>28</v>
@@ -11039,7 +11039,7 @@
         <v>27</v>
       </c>
       <c r="D407">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E407" t="s">
         <v>28</v>
@@ -11056,7 +11056,7 @@
         <v>27</v>
       </c>
       <c r="D408">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E408" t="s">
         <v>28</v>
@@ -11073,7 +11073,7 @@
         <v>27</v>
       </c>
       <c r="D409">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E409" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="D410">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E410" t="s">
         <v>28</v>
@@ -11107,7 +11107,7 @@
         <v>27</v>
       </c>
       <c r="D411">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E411" t="s">
         <v>28</v>
@@ -11124,7 +11124,7 @@
         <v>27</v>
       </c>
       <c r="D412">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E412" t="s">
         <v>28</v>
@@ -11141,7 +11141,7 @@
         <v>27</v>
       </c>
       <c r="D413">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E413" t="s">
         <v>28</v>
@@ -11158,7 +11158,7 @@
         <v>27</v>
       </c>
       <c r="D414">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E414" t="s">
         <v>28</v>
@@ -11175,7 +11175,7 @@
         <v>27</v>
       </c>
       <c r="D415">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E415" t="s">
         <v>28</v>
@@ -11192,7 +11192,7 @@
         <v>27</v>
       </c>
       <c r="D416">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E416" t="s">
         <v>28</v>
@@ -11209,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="D417">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E417" t="s">
         <v>28</v>
@@ -11226,7 +11226,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E418" t="s">
         <v>28</v>
@@ -11243,7 +11243,7 @@
         <v>27</v>
       </c>
       <c r="D419">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E419" t="s">
         <v>28</v>
@@ -11260,7 +11260,7 @@
         <v>27</v>
       </c>
       <c r="D420">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E420" t="s">
         <v>28</v>
@@ -11277,7 +11277,7 @@
         <v>27</v>
       </c>
       <c r="D421">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E421" t="s">
         <v>28</v>
@@ -11294,7 +11294,7 @@
         <v>27</v>
       </c>
       <c r="D422">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E422" t="s">
         <v>28</v>
@@ -11311,7 +11311,7 @@
         <v>27</v>
       </c>
       <c r="D423">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E423" t="s">
         <v>28</v>
@@ -11328,7 +11328,7 @@
         <v>27</v>
       </c>
       <c r="D424">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E424" t="s">
         <v>28</v>
@@ -11345,7 +11345,7 @@
         <v>27</v>
       </c>
       <c r="D425">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E425" t="s">
         <v>28</v>
@@ -11362,7 +11362,7 @@
         <v>27</v>
       </c>
       <c r="D426">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E426" t="s">
         <v>28</v>
@@ -11379,7 +11379,7 @@
         <v>27</v>
       </c>
       <c r="D427">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E427" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="D428">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E428" t="s">
         <v>28</v>
@@ -11413,7 +11413,7 @@
         <v>27</v>
       </c>
       <c r="D429">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E429" t="s">
         <v>28</v>
@@ -11430,7 +11430,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E430" t="s">
         <v>28</v>
@@ -11447,7 +11447,7 @@
         <v>27</v>
       </c>
       <c r="D431">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E431" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="D433">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E433" t="s">
         <v>28</v>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="D435">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E435" t="s">
         <v>28</v>
@@ -11532,7 +11532,7 @@
         <v>27</v>
       </c>
       <c r="D436">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E436" t="s">
         <v>28</v>
@@ -11549,7 +11549,7 @@
         <v>27</v>
       </c>
       <c r="D437">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E437" t="s">
         <v>28</v>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
       <c r="D438">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E438" t="s">
         <v>28</v>
@@ -11583,7 +11583,7 @@
         <v>27</v>
       </c>
       <c r="D439">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E439" t="s">
         <v>28</v>
@@ -11617,7 +11617,7 @@
         <v>27</v>
       </c>
       <c r="D441">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E441" t="s">
         <v>28</v>
@@ -11634,7 +11634,7 @@
         <v>27</v>
       </c>
       <c r="D442">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E442" t="s">
         <v>28</v>
@@ -11651,7 +11651,7 @@
         <v>27</v>
       </c>
       <c r="D443">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E443" t="s">
         <v>28</v>
@@ -11668,7 +11668,7 @@
         <v>27</v>
       </c>
       <c r="D444">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E444" t="s">
         <v>28</v>
@@ -11685,7 +11685,7 @@
         <v>27</v>
       </c>
       <c r="D445">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E445" t="s">
         <v>28</v>
@@ -11702,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D446">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E446" t="s">
         <v>28</v>
@@ -11719,7 +11719,7 @@
         <v>27</v>
       </c>
       <c r="D447">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E447" t="s">
         <v>28</v>
@@ -11736,7 +11736,7 @@
         <v>27</v>
       </c>
       <c r="D448">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E448" t="s">
         <v>28</v>
@@ -11753,7 +11753,7 @@
         <v>27</v>
       </c>
       <c r="D449">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E449" t="s">
         <v>28</v>
@@ -11770,7 +11770,7 @@
         <v>27</v>
       </c>
       <c r="D450">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E450" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="D451">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E451" t="s">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>27</v>
       </c>
       <c r="D453">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E453" t="s">
         <v>28</v>
@@ -11838,7 +11838,7 @@
         <v>27</v>
       </c>
       <c r="D454">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E454" t="s">
         <v>28</v>
@@ -11855,7 +11855,7 @@
         <v>27</v>
       </c>
       <c r="D455">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E455" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="D456">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E456" t="s">
         <v>28</v>
@@ -11889,7 +11889,7 @@
         <v>27</v>
       </c>
       <c r="D457">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E457" t="s">
         <v>28</v>
@@ -11906,7 +11906,7 @@
         <v>27</v>
       </c>
       <c r="D458">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E458" t="s">
         <v>28</v>
@@ -11923,7 +11923,7 @@
         <v>27</v>
       </c>
       <c r="D459">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E459" t="s">
         <v>28</v>
@@ -11940,7 +11940,7 @@
         <v>27</v>
       </c>
       <c r="D460">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E460" t="s">
         <v>28</v>
@@ -11957,7 +11957,7 @@
         <v>27</v>
       </c>
       <c r="D461">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E461" t="s">
         <v>28</v>
@@ -11974,7 +11974,7 @@
         <v>27</v>
       </c>
       <c r="D462">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E462" t="s">
         <v>28</v>
@@ -11991,7 +11991,7 @@
         <v>27</v>
       </c>
       <c r="D463">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E463" t="s">
         <v>28</v>
@@ -12008,7 +12008,7 @@
         <v>27</v>
       </c>
       <c r="D464">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E464" t="s">
         <v>28</v>
@@ -12025,7 +12025,7 @@
         <v>27</v>
       </c>
       <c r="D465">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E465" t="s">
         <v>28</v>
@@ -12042,7 +12042,7 @@
         <v>27</v>
       </c>
       <c r="D466">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E466" t="s">
         <v>28</v>
@@ -12059,7 +12059,7 @@
         <v>27</v>
       </c>
       <c r="D467">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E467" t="s">
         <v>28</v>
@@ -12076,7 +12076,7 @@
         <v>27</v>
       </c>
       <c r="D468">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E468" t="s">
         <v>28</v>
@@ -12093,7 +12093,7 @@
         <v>27</v>
       </c>
       <c r="D469">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E469" t="s">
         <v>28</v>
@@ -12110,7 +12110,7 @@
         <v>27</v>
       </c>
       <c r="D470">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E470" t="s">
         <v>28</v>
@@ -12127,7 +12127,7 @@
         <v>27</v>
       </c>
       <c r="D471">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E471" t="s">
         <v>28</v>
@@ -12144,7 +12144,7 @@
         <v>27</v>
       </c>
       <c r="D472">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E472" t="s">
         <v>28</v>
@@ -12161,7 +12161,7 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E473" t="s">
         <v>28</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="D474">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E474" t="s">
         <v>28</v>
@@ -12195,7 +12195,7 @@
         <v>27</v>
       </c>
       <c r="D475">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E475" t="s">
         <v>28</v>
@@ -12212,7 +12212,7 @@
         <v>27</v>
       </c>
       <c r="D476">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E476" t="s">
         <v>28</v>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
       <c r="D477">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E477" t="s">
         <v>28</v>
@@ -12246,7 +12246,7 @@
         <v>27</v>
       </c>
       <c r="D478">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E478" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="D479">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E479" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="D480">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E480" t="s">
         <v>28</v>
@@ -12297,7 +12297,7 @@
         <v>27</v>
       </c>
       <c r="D481">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E481" t="s">
         <v>28</v>
@@ -12314,7 +12314,7 @@
         <v>27</v>
       </c>
       <c r="D482">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E482" t="s">
         <v>28</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="D483">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E483" t="s">
         <v>28</v>
@@ -12348,7 +12348,7 @@
         <v>27</v>
       </c>
       <c r="D484">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E484" t="s">
         <v>28</v>
@@ -12365,7 +12365,7 @@
         <v>27</v>
       </c>
       <c r="D485">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E485" t="s">
         <v>28</v>
@@ -12399,7 +12399,7 @@
         <v>27</v>
       </c>
       <c r="D487">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E487" t="s">
         <v>28</v>
@@ -12416,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="D488">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E488" t="s">
         <v>28</v>
@@ -12433,7 +12433,7 @@
         <v>27</v>
       </c>
       <c r="D489">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E489" t="s">
         <v>28</v>
@@ -12450,7 +12450,7 @@
         <v>27</v>
       </c>
       <c r="D490">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E490" t="s">
         <v>28</v>
@@ -12467,7 +12467,7 @@
         <v>27</v>
       </c>
       <c r="D491">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E491" t="s">
         <v>28</v>
@@ -12484,7 +12484,7 @@
         <v>27</v>
       </c>
       <c r="D492">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E492" t="s">
         <v>28</v>
@@ -12501,7 +12501,7 @@
         <v>27</v>
       </c>
       <c r="D493">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E493" t="s">
         <v>28</v>
@@ -12518,7 +12518,7 @@
         <v>27</v>
       </c>
       <c r="D494">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E494" t="s">
         <v>28</v>
@@ -12535,7 +12535,7 @@
         <v>27</v>
       </c>
       <c r="D495">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E495" t="s">
         <v>28</v>
@@ -12552,7 +12552,7 @@
         <v>27</v>
       </c>
       <c r="D496">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E496" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="D497">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E497" t="s">
         <v>28</v>
@@ -12586,7 +12586,7 @@
         <v>27</v>
       </c>
       <c r="D498">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E498" t="s">
         <v>28</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D499">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E499" t="s">
         <v>28</v>
@@ -12620,7 +12620,7 @@
         <v>27</v>
       </c>
       <c r="D500">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E500" t="s">
         <v>28</v>
@@ -12637,7 +12637,7 @@
         <v>27</v>
       </c>
       <c r="D501">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E501" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="D502">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E502" t="s">
         <v>28</v>
@@ -12671,7 +12671,7 @@
         <v>27</v>
       </c>
       <c r="D503">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E503" t="s">
         <v>28</v>
@@ -12688,7 +12688,7 @@
         <v>27</v>
       </c>
       <c r="D504">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E504" t="s">
         <v>28</v>
@@ -12705,7 +12705,7 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E505" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="D506">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E506" t="s">
         <v>28</v>
@@ -12739,7 +12739,7 @@
         <v>27</v>
       </c>
       <c r="D507">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E507" t="s">
         <v>28</v>
@@ -12756,7 +12756,7 @@
         <v>27</v>
       </c>
       <c r="D508">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E508" t="s">
         <v>28</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="D509">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E509" t="s">
         <v>28</v>
@@ -12790,7 +12790,7 @@
         <v>27</v>
       </c>
       <c r="D510">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E510" t="s">
         <v>28</v>
@@ -12807,7 +12807,7 @@
         <v>27</v>
       </c>
       <c r="D511">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E511" t="s">
         <v>28</v>
@@ -12824,7 +12824,7 @@
         <v>27</v>
       </c>
       <c r="D512">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E512" t="s">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27</v>
       </c>
       <c r="D513">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E513" t="s">
         <v>28</v>
@@ -12858,7 +12858,7 @@
         <v>27</v>
       </c>
       <c r="D514">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E514" t="s">
         <v>28</v>
@@ -12875,7 +12875,7 @@
         <v>27</v>
       </c>
       <c r="D515">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E515" t="s">
         <v>28</v>
@@ -12892,7 +12892,7 @@
         <v>27</v>
       </c>
       <c r="D516">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E516" t="s">
         <v>28</v>
@@ -12909,7 +12909,7 @@
         <v>27</v>
       </c>
       <c r="D517">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E517" t="s">
         <v>28</v>
@@ -12926,7 +12926,7 @@
         <v>27</v>
       </c>
       <c r="D518">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E518" t="s">
         <v>28</v>
@@ -12943,7 +12943,7 @@
         <v>27</v>
       </c>
       <c r="D519">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E519" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="D520">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E520" t="s">
         <v>28</v>
@@ -12977,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="D521">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E521" t="s">
         <v>28</v>
@@ -12994,7 +12994,7 @@
         <v>27</v>
       </c>
       <c r="D522">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E522" t="s">
         <v>28</v>
@@ -13011,7 +13011,7 @@
         <v>27</v>
       </c>
       <c r="D523">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E523" t="s">
         <v>28</v>
@@ -13028,7 +13028,7 @@
         <v>27</v>
       </c>
       <c r="D524">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E524" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="D525">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E525" t="s">
         <v>28</v>
@@ -13062,7 +13062,7 @@
         <v>27</v>
       </c>
       <c r="D526">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E526" t="s">
         <v>28</v>
@@ -13096,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="D528">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E528" t="s">
         <v>28</v>
@@ -13113,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="D529">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
@@ -13130,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -13147,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="D531">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
@@ -13181,7 +13181,7 @@
         <v>27</v>
       </c>
       <c r="D533">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E533" t="s">
         <v>28</v>
@@ -13215,7 +13215,7 @@
         <v>27</v>
       </c>
       <c r="D535">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E535" t="s">
         <v>28</v>
@@ -13232,7 +13232,7 @@
         <v>27</v>
       </c>
       <c r="D536">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E536" t="s">
         <v>28</v>
@@ -13249,7 +13249,7 @@
         <v>27</v>
       </c>
       <c r="D537">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E537" t="s">
         <v>28</v>
@@ -13266,7 +13266,7 @@
         <v>27</v>
       </c>
       <c r="D538">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E538" t="s">
         <v>28</v>
@@ -13283,7 +13283,7 @@
         <v>27</v>
       </c>
       <c r="D539">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E539" t="s">
         <v>28</v>
@@ -13300,7 +13300,7 @@
         <v>27</v>
       </c>
       <c r="D540">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E540" t="s">
         <v>28</v>
@@ -13334,7 +13334,7 @@
         <v>27</v>
       </c>
       <c r="D542">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E542" t="s">
         <v>28</v>
@@ -13368,7 +13368,7 @@
         <v>27</v>
       </c>
       <c r="D544">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E544" t="s">
         <v>28</v>
@@ -13385,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="D545">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
@@ -13402,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="D546">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
@@ -13419,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="D547">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E547" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="D548">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E548" t="s">
         <v>28</v>
@@ -13453,7 +13453,7 @@
         <v>27</v>
       </c>
       <c r="D549">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E549" t="s">
         <v>28</v>
@@ -13470,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="D550">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E550" t="s">
         <v>28</v>
@@ -13487,7 +13487,7 @@
         <v>27</v>
       </c>
       <c r="D551">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E551" t="s">
         <v>28</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="D552">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -13521,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="D553">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E553" t="s">
         <v>28</v>
@@ -13538,7 +13538,7 @@
         <v>27</v>
       </c>
       <c r="D554">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E554" t="s">
         <v>28</v>
@@ -13555,7 +13555,7 @@
         <v>27</v>
       </c>
       <c r="D555">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E555" t="s">
         <v>28</v>
@@ -13572,7 +13572,7 @@
         <v>27</v>
       </c>
       <c r="D556">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E556" t="s">
         <v>28</v>
@@ -13589,7 +13589,7 @@
         <v>27</v>
       </c>
       <c r="D557">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E557" t="s">
         <v>28</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="D558">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E558" t="s">
         <v>28</v>
@@ -13623,7 +13623,7 @@
         <v>27</v>
       </c>
       <c r="D559">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -13640,7 +13640,7 @@
         <v>27</v>
       </c>
       <c r="D560">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
@@ -13657,7 +13657,7 @@
         <v>27</v>
       </c>
       <c r="D561">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E561" t="s">
         <v>28</v>
@@ -13674,7 +13674,7 @@
         <v>27</v>
       </c>
       <c r="D562">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E562" t="s">
         <v>28</v>
@@ -13691,7 +13691,7 @@
         <v>27</v>
       </c>
       <c r="D563">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E563" t="s">
         <v>28</v>
@@ -13708,7 +13708,7 @@
         <v>27</v>
       </c>
       <c r="D564">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E564" t="s">
         <v>28</v>
@@ -13725,7 +13725,7 @@
         <v>27</v>
       </c>
       <c r="D565">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E565" t="s">
         <v>28</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="D566">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E566" t="s">
         <v>28</v>
@@ -13759,7 +13759,7 @@
         <v>27</v>
       </c>
       <c r="D567">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E567" t="s">
         <v>28</v>
@@ -13776,7 +13776,7 @@
         <v>27</v>
       </c>
       <c r="D568">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E568" t="s">
         <v>28</v>
@@ -13793,7 +13793,7 @@
         <v>27</v>
       </c>
       <c r="D569">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="D571">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E571" t="s">
         <v>28</v>
@@ -13844,7 +13844,7 @@
         <v>27</v>
       </c>
       <c r="D572">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E572" t="s">
         <v>28</v>
@@ -13861,7 +13861,7 @@
         <v>27</v>
       </c>
       <c r="D573">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E573" t="s">
         <v>28</v>
@@ -13878,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="D574">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E574" t="s">
         <v>28</v>
@@ -13895,7 +13895,7 @@
         <v>27</v>
       </c>
       <c r="D575">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E575" t="s">
         <v>28</v>
@@ -13912,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="D576">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E576" t="s">
         <v>28</v>
@@ -13929,7 +13929,7 @@
         <v>27</v>
       </c>
       <c r="D577">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E577" t="s">
         <v>28</v>
@@ -13946,7 +13946,7 @@
         <v>27</v>
       </c>
       <c r="D578">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E578" t="s">
         <v>28</v>
@@ -13963,7 +13963,7 @@
         <v>27</v>
       </c>
       <c r="D579">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E579" t="s">
         <v>28</v>
@@ -13980,7 +13980,7 @@
         <v>27</v>
       </c>
       <c r="D580">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E580" t="s">
         <v>28</v>
@@ -13997,7 +13997,7 @@
         <v>27</v>
       </c>
       <c r="D581">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E581" t="s">
         <v>28</v>
@@ -14014,7 +14014,7 @@
         <v>27</v>
       </c>
       <c r="D582">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E582" t="s">
         <v>28</v>
@@ -14031,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="D583">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E583" t="s">
         <v>28</v>
@@ -14048,7 +14048,7 @@
         <v>27</v>
       </c>
       <c r="D584">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E584" t="s">
         <v>28</v>
@@ -14065,7 +14065,7 @@
         <v>27</v>
       </c>
       <c r="D585">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E585" t="s">
         <v>28</v>
@@ -14082,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="D586">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E586" t="s">
         <v>28</v>
@@ -14099,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="D587">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E587" t="s">
         <v>28</v>
@@ -14116,7 +14116,7 @@
         <v>27</v>
       </c>
       <c r="D588">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E588" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="D589">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
@@ -14150,7 +14150,7 @@
         <v>27</v>
       </c>
       <c r="D590">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
@@ -14167,7 +14167,7 @@
         <v>27</v>
       </c>
       <c r="D591">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E591" t="s">
         <v>28</v>
@@ -14184,7 +14184,7 @@
         <v>27</v>
       </c>
       <c r="D592">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E592" t="s">
         <v>28</v>
@@ -14201,7 +14201,7 @@
         <v>27</v>
       </c>
       <c r="D593">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E593" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="D594">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E594" t="s">
         <v>28</v>
@@ -14235,7 +14235,7 @@
         <v>27</v>
       </c>
       <c r="D595">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E595" t="s">
         <v>28</v>
@@ -14252,7 +14252,7 @@
         <v>27</v>
       </c>
       <c r="D596">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
@@ -14269,7 +14269,7 @@
         <v>27</v>
       </c>
       <c r="D597">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
@@ -14286,7 +14286,7 @@
         <v>27</v>
       </c>
       <c r="D598">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
@@ -14303,7 +14303,7 @@
         <v>27</v>
       </c>
       <c r="D599">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="D600">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
@@ -14337,7 +14337,7 @@
         <v>27</v>
       </c>
       <c r="D601">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
@@ -14354,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="D602">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
@@ -14371,7 +14371,7 @@
         <v>27</v>
       </c>
       <c r="D603">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
@@ -14388,7 +14388,7 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
@@ -14405,7 +14405,7 @@
         <v>27</v>
       </c>
       <c r="D605">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E605" t="s">
         <v>28</v>
@@ -14422,7 +14422,7 @@
         <v>27</v>
       </c>
       <c r="D606">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E606" t="s">
         <v>28</v>
@@ -14456,7 +14456,7 @@
         <v>27</v>
       </c>
       <c r="D608">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
@@ -14473,7 +14473,7 @@
         <v>27</v>
       </c>
       <c r="D609">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E609" t="s">
         <v>28</v>
@@ -14490,7 +14490,7 @@
         <v>27</v>
       </c>
       <c r="D610">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E610" t="s">
         <v>28</v>
@@ -14507,7 +14507,7 @@
         <v>27</v>
       </c>
       <c r="D611">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E611" t="s">
         <v>28</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="D612">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E612" t="s">
         <v>28</v>
@@ -14541,7 +14541,7 @@
         <v>27</v>
       </c>
       <c r="D613">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E613" t="s">
         <v>28</v>
@@ -14558,7 +14558,7 @@
         <v>27</v>
       </c>
       <c r="D614">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E614" t="s">
         <v>28</v>
@@ -14575,7 +14575,7 @@
         <v>27</v>
       </c>
       <c r="D615">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E615" t="s">
         <v>28</v>
@@ -14592,7 +14592,7 @@
         <v>27</v>
       </c>
       <c r="D616">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E616" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="D617">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E617" t="s">
         <v>28</v>
@@ -14626,7 +14626,7 @@
         <v>27</v>
       </c>
       <c r="D618">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E618" t="s">
         <v>28</v>
@@ -14643,7 +14643,7 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E619" t="s">
         <v>28</v>
@@ -14677,7 +14677,7 @@
         <v>27</v>
       </c>
       <c r="D621">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E621" t="s">
         <v>28</v>
@@ -14711,7 +14711,7 @@
         <v>27</v>
       </c>
       <c r="D623">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E623" t="s">
         <v>28</v>
@@ -14728,7 +14728,7 @@
         <v>27</v>
       </c>
       <c r="D624">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E624" t="s">
         <v>28</v>
@@ -14745,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="D625">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E625" t="s">
         <v>28</v>
@@ -14762,7 +14762,7 @@
         <v>27</v>
       </c>
       <c r="D626">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E626" t="s">
         <v>28</v>
@@ -14779,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="D627">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E627" t="s">
         <v>28</v>
@@ -14796,7 +14796,7 @@
         <v>27</v>
       </c>
       <c r="D628">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E628" t="s">
         <v>28</v>
@@ -14830,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="D630">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E630" t="s">
         <v>28</v>
@@ -14847,7 +14847,7 @@
         <v>27</v>
       </c>
       <c r="D631">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E631" t="s">
         <v>28</v>
@@ -14864,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D632">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E632" t="s">
         <v>28</v>
@@ -14898,7 +14898,7 @@
         <v>27</v>
       </c>
       <c r="D634">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E634" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="D635">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E635" t="s">
         <v>28</v>
@@ -14932,7 +14932,7 @@
         <v>27</v>
       </c>
       <c r="D636">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E636" t="s">
         <v>28</v>
@@ -14949,7 +14949,7 @@
         <v>27</v>
       </c>
       <c r="D637">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E637" t="s">
         <v>28</v>
@@ -14966,7 +14966,7 @@
         <v>27</v>
       </c>
       <c r="D638">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E638" t="s">
         <v>28</v>
@@ -14983,7 +14983,7 @@
         <v>27</v>
       </c>
       <c r="D639">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E639" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E640" t="s">
         <v>28</v>
@@ -15017,7 +15017,7 @@
         <v>27</v>
       </c>
       <c r="D641">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E641" t="s">
         <v>28</v>
@@ -15034,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="D642">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E642" t="s">
         <v>28</v>
@@ -15051,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="D643">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E643" t="s">
         <v>28</v>
@@ -15068,7 +15068,7 @@
         <v>27</v>
       </c>
       <c r="D644">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E644" t="s">
         <v>28</v>
@@ -15085,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="D645">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E645" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>27</v>
       </c>
       <c r="D647">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E647" t="s">
         <v>28</v>
@@ -15153,7 +15153,7 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E649" t="s">
         <v>28</v>
@@ -15170,7 +15170,7 @@
         <v>27</v>
       </c>
       <c r="D650">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E650" t="s">
         <v>28</v>
@@ -15187,7 +15187,7 @@
         <v>27</v>
       </c>
       <c r="D651">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E651" t="s">
         <v>28</v>
@@ -15204,7 +15204,7 @@
         <v>27</v>
       </c>
       <c r="D652">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E652" t="s">
         <v>28</v>
@@ -15238,7 +15238,7 @@
         <v>27</v>
       </c>
       <c r="D654">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E654" t="s">
         <v>28</v>
@@ -15255,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="D655">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E655" t="s">
         <v>28</v>
@@ -15272,7 +15272,7 @@
         <v>27</v>
       </c>
       <c r="D656">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
@@ -15323,7 +15323,7 @@
         <v>27</v>
       </c>
       <c r="D659">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E659" t="s">
         <v>28</v>
@@ -15340,7 +15340,7 @@
         <v>27</v>
       </c>
       <c r="D660">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E660" t="s">
         <v>28</v>
@@ -15357,7 +15357,7 @@
         <v>27</v>
       </c>
       <c r="D661">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E661" t="s">
         <v>28</v>
@@ -15374,7 +15374,7 @@
         <v>27</v>
       </c>
       <c r="D662">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E662" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="D663">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E663" t="s">
         <v>28</v>
@@ -15408,7 +15408,7 @@
         <v>27</v>
       </c>
       <c r="D664">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E664" t="s">
         <v>28</v>
@@ -15425,7 +15425,7 @@
         <v>27</v>
       </c>
       <c r="D665">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E665" t="s">
         <v>28</v>
@@ -15442,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="D666">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E666" t="s">
         <v>28</v>
@@ -15459,7 +15459,7 @@
         <v>27</v>
       </c>
       <c r="D667">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E667" t="s">
         <v>28</v>
@@ -15476,7 +15476,7 @@
         <v>27</v>
       </c>
       <c r="D668">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E668" t="s">
         <v>28</v>
@@ -15493,7 +15493,7 @@
         <v>27</v>
       </c>
       <c r="D669">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E669" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>27</v>
       </c>
       <c r="D670">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E670" t="s">
         <v>28</v>
@@ -15527,7 +15527,7 @@
         <v>27</v>
       </c>
       <c r="D671">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E671" t="s">
         <v>28</v>
@@ -15544,7 +15544,7 @@
         <v>27</v>
       </c>
       <c r="D672">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E672" t="s">
         <v>28</v>
@@ -15561,7 +15561,7 @@
         <v>27</v>
       </c>
       <c r="D673">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E673" t="s">
         <v>28</v>
@@ -15578,7 +15578,7 @@
         <v>27</v>
       </c>
       <c r="D674">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E674" t="s">
         <v>28</v>
@@ -15595,7 +15595,7 @@
         <v>27</v>
       </c>
       <c r="D675">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E675" t="s">
         <v>28</v>
@@ -15629,7 +15629,7 @@
         <v>27</v>
       </c>
       <c r="D677">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E677" t="s">
         <v>28</v>
@@ -15646,7 +15646,7 @@
         <v>27</v>
       </c>
       <c r="D678">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E678" t="s">
         <v>28</v>
@@ -15663,7 +15663,7 @@
         <v>27</v>
       </c>
       <c r="D679">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E679" t="s">
         <v>28</v>
@@ -15680,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="D680">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E680" t="s">
         <v>28</v>
@@ -15697,7 +15697,7 @@
         <v>27</v>
       </c>
       <c r="D681">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E681" t="s">
         <v>28</v>
@@ -15714,7 +15714,7 @@
         <v>27</v>
       </c>
       <c r="D682">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E682" t="s">
         <v>28</v>
@@ -15731,7 +15731,7 @@
         <v>27</v>
       </c>
       <c r="D683">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E683" t="s">
         <v>28</v>
@@ -15748,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="D684">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E684" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="D686">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E686" t="s">
         <v>28</v>
@@ -15799,7 +15799,7 @@
         <v>27</v>
       </c>
       <c r="D687">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E687" t="s">
         <v>28</v>
@@ -15816,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="D688">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E688" t="s">
         <v>28</v>
@@ -15850,7 +15850,7 @@
         <v>27</v>
       </c>
       <c r="D690">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E690" t="s">
         <v>28</v>
@@ -15867,7 +15867,7 @@
         <v>27</v>
       </c>
       <c r="D691">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E691" t="s">
         <v>28</v>
@@ -15884,7 +15884,7 @@
         <v>27</v>
       </c>
       <c r="D692">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E692" t="s">
         <v>28</v>
@@ -15901,7 +15901,7 @@
         <v>27</v>
       </c>
       <c r="D693">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E693" t="s">
         <v>28</v>
@@ -15918,7 +15918,7 @@
         <v>27</v>
       </c>
       <c r="D694">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E694" t="s">
         <v>28</v>
@@ -15935,7 +15935,7 @@
         <v>27</v>
       </c>
       <c r="D695">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E695" t="s">
         <v>28</v>
@@ -15952,7 +15952,7 @@
         <v>27</v>
       </c>
       <c r="D696">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E696" t="s">
         <v>28</v>
@@ -15969,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="D697">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E697" t="s">
         <v>28</v>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
       <c r="D698">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E698" t="s">
         <v>28</v>
@@ -16003,7 +16003,7 @@
         <v>27</v>
       </c>
       <c r="D699">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E699" t="s">
         <v>28</v>
@@ -16020,7 +16020,7 @@
         <v>27</v>
       </c>
       <c r="D700">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E700" t="s">
         <v>28</v>
@@ -16037,7 +16037,7 @@
         <v>27</v>
       </c>
       <c r="D701">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E701" t="s">
         <v>28</v>
@@ -16054,7 +16054,7 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E702" t="s">
         <v>28</v>
@@ -16071,7 +16071,7 @@
         <v>27</v>
       </c>
       <c r="D703">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E703" t="s">
         <v>28</v>
@@ -16088,7 +16088,7 @@
         <v>27</v>
       </c>
       <c r="D704">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E704" t="s">
         <v>28</v>
@@ -16105,7 +16105,7 @@
         <v>27</v>
       </c>
       <c r="D705">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E705" t="s">
         <v>28</v>
@@ -16139,7 +16139,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E707" t="s">
         <v>28</v>
@@ -16156,7 +16156,7 @@
         <v>27</v>
       </c>
       <c r="D708">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E708" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="D709">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E709" t="s">
         <v>28</v>
@@ -16190,7 +16190,7 @@
         <v>27</v>
       </c>
       <c r="D710">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E710" t="s">
         <v>28</v>
@@ -16207,7 +16207,7 @@
         <v>27</v>
       </c>
       <c r="D711">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E711" t="s">
         <v>28</v>
@@ -16224,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="D712">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E712" t="s">
         <v>28</v>
@@ -16241,7 +16241,7 @@
         <v>27</v>
       </c>
       <c r="D713">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E713" t="s">
         <v>28</v>
@@ -16258,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="D714">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E714" t="s">
         <v>28</v>
@@ -16275,7 +16275,7 @@
         <v>27</v>
       </c>
       <c r="D715">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E715" t="s">
         <v>28</v>
@@ -16292,7 +16292,7 @@
         <v>27</v>
       </c>
       <c r="D716">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E716" t="s">
         <v>28</v>
@@ -16309,7 +16309,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E717" t="s">
         <v>28</v>
@@ -16326,7 +16326,7 @@
         <v>27</v>
       </c>
       <c r="D718">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E718" t="s">
         <v>28</v>
@@ -16343,7 +16343,7 @@
         <v>27</v>
       </c>
       <c r="D719">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E719" t="s">
         <v>28</v>
@@ -16360,7 +16360,7 @@
         <v>27</v>
       </c>
       <c r="D720">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E720" t="s">
         <v>28</v>
@@ -16377,7 +16377,7 @@
         <v>27</v>
       </c>
       <c r="D721">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E721" t="s">
         <v>28</v>
@@ -16394,7 +16394,7 @@
         <v>27</v>
       </c>
       <c r="D722">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E722" t="s">
         <v>28</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="D723">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E723" t="s">
         <v>28</v>
@@ -16428,7 +16428,7 @@
         <v>27</v>
       </c>
       <c r="D724">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E724" t="s">
         <v>28</v>
@@ -16445,7 +16445,7 @@
         <v>27</v>
       </c>
       <c r="D725">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E725" t="s">
         <v>28</v>
@@ -16462,7 +16462,7 @@
         <v>27</v>
       </c>
       <c r="D726">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E726" t="s">
         <v>28</v>
@@ -16479,7 +16479,7 @@
         <v>27</v>
       </c>
       <c r="D727">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E727" t="s">
         <v>28</v>
@@ -16496,7 +16496,7 @@
         <v>27</v>
       </c>
       <c r="D728">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E728" t="s">
         <v>28</v>
@@ -16513,7 +16513,7 @@
         <v>27</v>
       </c>
       <c r="D729">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E729" t="s">
         <v>28</v>
@@ -16530,7 +16530,7 @@
         <v>27</v>
       </c>
       <c r="D730">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E730" t="s">
         <v>28</v>
@@ -16547,7 +16547,7 @@
         <v>27</v>
       </c>
       <c r="D731">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E731" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="D732">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E732" t="s">
         <v>28</v>
@@ -16581,7 +16581,7 @@
         <v>27</v>
       </c>
       <c r="D733">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E733" t="s">
         <v>28</v>
@@ -16598,7 +16598,7 @@
         <v>27</v>
       </c>
       <c r="D734">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E734" t="s">
         <v>28</v>
@@ -16615,7 +16615,7 @@
         <v>27</v>
       </c>
       <c r="D735">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E735" t="s">
         <v>28</v>
@@ -16632,7 +16632,7 @@
         <v>27</v>
       </c>
       <c r="D736">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E736" t="s">
         <v>28</v>
@@ -16649,7 +16649,7 @@
         <v>27</v>
       </c>
       <c r="D737">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E737" t="s">
         <v>28</v>
@@ -16666,7 +16666,7 @@
         <v>27</v>
       </c>
       <c r="D738">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E738" t="s">
         <v>28</v>
@@ -16683,7 +16683,7 @@
         <v>27</v>
       </c>
       <c r="D739">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E739" t="s">
         <v>28</v>
@@ -16700,7 +16700,7 @@
         <v>27</v>
       </c>
       <c r="D740">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E740" t="s">
         <v>28</v>
@@ -16717,7 +16717,7 @@
         <v>27</v>
       </c>
       <c r="D741">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E741" t="s">
         <v>28</v>
@@ -16734,7 +16734,7 @@
         <v>27</v>
       </c>
       <c r="D742">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E742" t="s">
         <v>28</v>
@@ -16751,7 +16751,7 @@
         <v>27</v>
       </c>
       <c r="D743">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E743" t="s">
         <v>28</v>
@@ -16768,7 +16768,7 @@
         <v>27</v>
       </c>
       <c r="D744">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E744" t="s">
         <v>28</v>
@@ -16785,7 +16785,7 @@
         <v>27</v>
       </c>
       <c r="D745">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E745" t="s">
         <v>28</v>
@@ -16802,7 +16802,7 @@
         <v>27</v>
       </c>
       <c r="D746">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E746" t="s">
         <v>28</v>
@@ -16836,7 +16836,7 @@
         <v>27</v>
       </c>
       <c r="D748">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E748" t="s">
         <v>28</v>
@@ -16853,7 +16853,7 @@
         <v>27</v>
       </c>
       <c r="D749">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E749" t="s">
         <v>28</v>
@@ -16870,7 +16870,7 @@
         <v>27</v>
       </c>
       <c r="D750">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E750" t="s">
         <v>28</v>
@@ -16887,7 +16887,7 @@
         <v>27</v>
       </c>
       <c r="D751">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E751" t="s">
         <v>28</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="D752">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E752" t="s">
         <v>28</v>
@@ -16921,7 +16921,7 @@
         <v>27</v>
       </c>
       <c r="D753">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E753" t="s">
         <v>28</v>
@@ -16938,7 +16938,7 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E754" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="D755">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E755" t="s">
         <v>28</v>
@@ -16972,7 +16972,7 @@
         <v>27</v>
       </c>
       <c r="D756">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E756" t="s">
         <v>28</v>
@@ -16989,7 +16989,7 @@
         <v>27</v>
       </c>
       <c r="D757">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E757" t="s">
         <v>28</v>
@@ -17006,7 +17006,7 @@
         <v>27</v>
       </c>
       <c r="D758">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E758" t="s">
         <v>28</v>
@@ -17023,7 +17023,7 @@
         <v>27</v>
       </c>
       <c r="D759">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E759" t="s">
         <v>28</v>
@@ -17040,7 +17040,7 @@
         <v>27</v>
       </c>
       <c r="D760">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E760" t="s">
         <v>28</v>
@@ -17057,7 +17057,7 @@
         <v>27</v>
       </c>
       <c r="D761">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E761" t="s">
         <v>28</v>
@@ -17074,7 +17074,7 @@
         <v>27</v>
       </c>
       <c r="D762">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E762" t="s">
         <v>28</v>
@@ -17091,7 +17091,7 @@
         <v>27</v>
       </c>
       <c r="D763">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E763" t="s">
         <v>28</v>
@@ -17108,7 +17108,7 @@
         <v>27</v>
       </c>
       <c r="D764">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E764" t="s">
         <v>28</v>
@@ -17125,7 +17125,7 @@
         <v>27</v>
       </c>
       <c r="D765">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E765" t="s">
         <v>28</v>
@@ -17142,7 +17142,7 @@
         <v>27</v>
       </c>
       <c r="D766">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E766" t="s">
         <v>28</v>
@@ -17159,7 +17159,7 @@
         <v>27</v>
       </c>
       <c r="D767">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E767" t="s">
         <v>28</v>
@@ -17176,7 +17176,7 @@
         <v>27</v>
       </c>
       <c r="D768">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E768" t="s">
         <v>28</v>
@@ -17193,7 +17193,7 @@
         <v>27</v>
       </c>
       <c r="D769">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E769" t="s">
         <v>28</v>
@@ -17210,7 +17210,7 @@
         <v>27</v>
       </c>
       <c r="D770">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E770" t="s">
         <v>28</v>
@@ -17227,7 +17227,7 @@
         <v>27</v>
       </c>
       <c r="D771">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E771" t="s">
         <v>28</v>
@@ -17244,7 +17244,7 @@
         <v>27</v>
       </c>
       <c r="D772">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E772" t="s">
         <v>28</v>
@@ -17261,7 +17261,7 @@
         <v>27</v>
       </c>
       <c r="D773">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E773" t="s">
         <v>28</v>
@@ -17278,7 +17278,7 @@
         <v>27</v>
       </c>
       <c r="D774">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E774" t="s">
         <v>28</v>
@@ -17295,7 +17295,7 @@
         <v>27</v>
       </c>
       <c r="D775">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E775" t="s">
         <v>28</v>
@@ -17329,7 +17329,7 @@
         <v>27</v>
       </c>
       <c r="D777">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E777" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="D778">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E778" t="s">
         <v>28</v>
@@ -17363,7 +17363,7 @@
         <v>27</v>
       </c>
       <c r="D779">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E779" t="s">
         <v>28</v>
@@ -17380,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="D780">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E780" t="s">
         <v>28</v>
@@ -17397,7 +17397,7 @@
         <v>27</v>
       </c>
       <c r="D781">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E781" t="s">
         <v>28</v>
@@ -17414,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="D782">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E782" t="s">
         <v>28</v>
@@ -17431,7 +17431,7 @@
         <v>27</v>
       </c>
       <c r="D783">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E783" t="s">
         <v>28</v>
@@ -17448,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D784">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E784" t="s">
         <v>28</v>
@@ -17465,7 +17465,7 @@
         <v>27</v>
       </c>
       <c r="D785">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E785" t="s">
         <v>28</v>
@@ -17482,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="D786">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E786" t="s">
         <v>28</v>
@@ -17499,7 +17499,7 @@
         <v>27</v>
       </c>
       <c r="D787">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E787" t="s">
         <v>28</v>
@@ -17516,7 +17516,7 @@
         <v>27</v>
       </c>
       <c r="D788">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E788" t="s">
         <v>28</v>
@@ -17533,7 +17533,7 @@
         <v>27</v>
       </c>
       <c r="D789">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E789" t="s">
         <v>28</v>
@@ -17550,7 +17550,7 @@
         <v>27</v>
       </c>
       <c r="D790">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E790" t="s">
         <v>28</v>
@@ -17567,7 +17567,7 @@
         <v>27</v>
       </c>
       <c r="D791">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E791" t="s">
         <v>28</v>
@@ -17584,7 +17584,7 @@
         <v>27</v>
       </c>
       <c r="D792">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E792" t="s">
         <v>28</v>
@@ -17601,7 +17601,7 @@
         <v>27</v>
       </c>
       <c r="D793">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E793" t="s">
         <v>28</v>
@@ -17618,7 +17618,7 @@
         <v>27</v>
       </c>
       <c r="D794">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E794" t="s">
         <v>28</v>
@@ -17635,7 +17635,7 @@
         <v>27</v>
       </c>
       <c r="D795">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E795" t="s">
         <v>28</v>
@@ -17652,7 +17652,7 @@
         <v>27</v>
       </c>
       <c r="D796">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E796" t="s">
         <v>28</v>
@@ -17669,7 +17669,7 @@
         <v>27</v>
       </c>
       <c r="D797">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E797" t="s">
         <v>28</v>
@@ -17686,7 +17686,7 @@
         <v>27</v>
       </c>
       <c r="D798">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E798" t="s">
         <v>28</v>
@@ -17703,7 +17703,7 @@
         <v>27</v>
       </c>
       <c r="D799">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E799" t="s">
         <v>28</v>
@@ -17720,7 +17720,7 @@
         <v>27</v>
       </c>
       <c r="D800">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E800" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="D801">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E801" t="s">
         <v>28</v>
@@ -17771,7 +17771,7 @@
         <v>27</v>
       </c>
       <c r="D803">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E803" t="s">
         <v>28</v>
@@ -17805,7 +17805,7 @@
         <v>27</v>
       </c>
       <c r="D805">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E805" t="s">
         <v>28</v>
@@ -17822,7 +17822,7 @@
         <v>27</v>
       </c>
       <c r="D806">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E806" t="s">
         <v>28</v>
@@ -17839,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="D807">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E807" t="s">
         <v>28</v>
@@ -17856,7 +17856,7 @@
         <v>27</v>
       </c>
       <c r="D808">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E808" t="s">
         <v>28</v>
@@ -17873,7 +17873,7 @@
         <v>27</v>
       </c>
       <c r="D809">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E809" t="s">
         <v>28</v>
@@ -17890,7 +17890,7 @@
         <v>27</v>
       </c>
       <c r="D810">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E810" t="s">
         <v>28</v>
@@ -17907,7 +17907,7 @@
         <v>27</v>
       </c>
       <c r="D811">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E811" t="s">
         <v>28</v>
@@ -17924,7 +17924,7 @@
         <v>27</v>
       </c>
       <c r="D812">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E812" t="s">
         <v>28</v>
@@ -17941,7 +17941,7 @@
         <v>27</v>
       </c>
       <c r="D813">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E813" t="s">
         <v>28</v>
@@ -17958,7 +17958,7 @@
         <v>27</v>
       </c>
       <c r="D814">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E814" t="s">
         <v>28</v>
@@ -17975,7 +17975,7 @@
         <v>27</v>
       </c>
       <c r="D815">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E815" t="s">
         <v>28</v>
@@ -17992,7 +17992,7 @@
         <v>27</v>
       </c>
       <c r="D816">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E816" t="s">
         <v>28</v>
@@ -18009,7 +18009,7 @@
         <v>27</v>
       </c>
       <c r="D817">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E817" t="s">
         <v>28</v>
@@ -18026,7 +18026,7 @@
         <v>27</v>
       </c>
       <c r="D818">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E818" t="s">
         <v>28</v>
@@ -18060,7 +18060,7 @@
         <v>27</v>
       </c>
       <c r="D820">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E820" t="s">
         <v>28</v>
@@ -18077,7 +18077,7 @@
         <v>27</v>
       </c>
       <c r="D821">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E821" t="s">
         <v>28</v>
@@ -18094,7 +18094,7 @@
         <v>27</v>
       </c>
       <c r="D822">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E822" t="s">
         <v>28</v>
@@ -18111,7 +18111,7 @@
         <v>27</v>
       </c>
       <c r="D823">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E823" t="s">
         <v>28</v>
@@ -18128,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="D824">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E824" t="s">
         <v>28</v>
@@ -18145,7 +18145,7 @@
         <v>27</v>
       </c>
       <c r="D825">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E825" t="s">
         <v>28</v>
@@ -18179,7 +18179,7 @@
         <v>27</v>
       </c>
       <c r="D827">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E827" t="s">
         <v>28</v>
@@ -18196,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="D828">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E828" t="s">
         <v>28</v>
@@ -18230,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="D830">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E830" t="s">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E831" t="s">
         <v>28</v>
@@ -18264,7 +18264,7 @@
         <v>27</v>
       </c>
       <c r="D832">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E832" t="s">
         <v>28</v>
@@ -18281,7 +18281,7 @@
         <v>27</v>
       </c>
       <c r="D833">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E833" t="s">
         <v>28</v>
@@ -18298,7 +18298,7 @@
         <v>27</v>
       </c>
       <c r="D834">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E834" t="s">
         <v>28</v>
@@ -18315,7 +18315,7 @@
         <v>27</v>
       </c>
       <c r="D835">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E835" t="s">
         <v>28</v>
@@ -18332,7 +18332,7 @@
         <v>27</v>
       </c>
       <c r="D836">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E836" t="s">
         <v>28</v>
@@ -18349,7 +18349,7 @@
         <v>27</v>
       </c>
       <c r="D837">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E837" t="s">
         <v>28</v>
@@ -18366,7 +18366,7 @@
         <v>27</v>
       </c>
       <c r="D838">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E838" t="s">
         <v>28</v>
@@ -18383,7 +18383,7 @@
         <v>27</v>
       </c>
       <c r="D839">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E839" t="s">
         <v>28</v>
@@ -18400,7 +18400,7 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E840" t="s">
         <v>28</v>
@@ -18434,7 +18434,7 @@
         <v>27</v>
       </c>
       <c r="D842">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E842" t="s">
         <v>28</v>
@@ -18451,7 +18451,7 @@
         <v>27</v>
       </c>
       <c r="D843">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E843" t="s">
         <v>28</v>
@@ -18468,7 +18468,7 @@
         <v>27</v>
       </c>
       <c r="D844">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E844" t="s">
         <v>28</v>
@@ -18485,7 +18485,7 @@
         <v>27</v>
       </c>
       <c r="D845">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E845" t="s">
         <v>28</v>
@@ -18502,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="D846">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E846" t="s">
         <v>28</v>
@@ -18536,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="D848">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E848" t="s">
         <v>28</v>
@@ -18553,7 +18553,7 @@
         <v>27</v>
       </c>
       <c r="D849">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E849" t="s">
         <v>28</v>
@@ -18570,7 +18570,7 @@
         <v>27</v>
       </c>
       <c r="D850">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E850" t="s">
         <v>28</v>
@@ -18587,7 +18587,7 @@
         <v>27</v>
       </c>
       <c r="D851">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E851" t="s">
         <v>28</v>
@@ -18604,7 +18604,7 @@
         <v>27</v>
       </c>
       <c r="D852">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E852" t="s">
         <v>28</v>
@@ -18621,7 +18621,7 @@
         <v>27</v>
       </c>
       <c r="D853">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E853" t="s">
         <v>28</v>
@@ -18638,7 +18638,7 @@
         <v>27</v>
       </c>
       <c r="D854">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E854" t="s">
         <v>28</v>
@@ -18655,7 +18655,7 @@
         <v>27</v>
       </c>
       <c r="D855">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E855" t="s">
         <v>28</v>
@@ -18672,7 +18672,7 @@
         <v>27</v>
       </c>
       <c r="D856">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E856" t="s">
         <v>28</v>
@@ -18689,7 +18689,7 @@
         <v>27</v>
       </c>
       <c r="D857">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E857" t="s">
         <v>28</v>
@@ -18706,7 +18706,7 @@
         <v>27</v>
       </c>
       <c r="D858">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E858" t="s">
         <v>28</v>
@@ -18723,7 +18723,7 @@
         <v>27</v>
       </c>
       <c r="D859">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E859" t="s">
         <v>28</v>
@@ -18740,7 +18740,7 @@
         <v>27</v>
       </c>
       <c r="D860">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E860" t="s">
         <v>28</v>
@@ -18757,7 +18757,7 @@
         <v>27</v>
       </c>
       <c r="D861">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E861" t="s">
         <v>28</v>
@@ -18774,7 +18774,7 @@
         <v>27</v>
       </c>
       <c r="D862">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E862" t="s">
         <v>28</v>
@@ -18791,7 +18791,7 @@
         <v>27</v>
       </c>
       <c r="D863">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E863" t="s">
         <v>28</v>
@@ -18808,7 +18808,7 @@
         <v>27</v>
       </c>
       <c r="D864">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E864" t="s">
         <v>28</v>
@@ -18825,7 +18825,7 @@
         <v>27</v>
       </c>
       <c r="D865">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E865" t="s">
         <v>28</v>
@@ -18842,7 +18842,7 @@
         <v>27</v>
       </c>
       <c r="D866">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E866" t="s">
         <v>28</v>
@@ -18859,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="D867">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E867" t="s">
         <v>28</v>
@@ -18876,7 +18876,7 @@
         <v>27</v>
       </c>
       <c r="D868">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E868" t="s">
         <v>28</v>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
       <c r="D869">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E869" t="s">
         <v>28</v>
@@ -18910,7 +18910,7 @@
         <v>27</v>
       </c>
       <c r="D870">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E870" t="s">
         <v>28</v>
@@ -18927,7 +18927,7 @@
         <v>27</v>
       </c>
       <c r="D871">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E871" t="s">
         <v>28</v>
@@ -18944,7 +18944,7 @@
         <v>27</v>
       </c>
       <c r="D872">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E872" t="s">
         <v>28</v>
@@ -18961,7 +18961,7 @@
         <v>27</v>
       </c>
       <c r="D873">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E873" t="s">
         <v>28</v>
@@ -18978,7 +18978,7 @@
         <v>27</v>
       </c>
       <c r="D874">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E874" t="s">
         <v>28</v>
@@ -18995,7 +18995,7 @@
         <v>27</v>
       </c>
       <c r="D875">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E875" t="s">
         <v>28</v>
@@ -19012,7 +19012,7 @@
         <v>27</v>
       </c>
       <c r="D876">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E876" t="s">
         <v>28</v>
@@ -19029,7 +19029,7 @@
         <v>27</v>
       </c>
       <c r="D877">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E877" t="s">
         <v>28</v>
@@ -19046,7 +19046,7 @@
         <v>27</v>
       </c>
       <c r="D878">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E878" t="s">
         <v>28</v>
@@ -19063,7 +19063,7 @@
         <v>27</v>
       </c>
       <c r="D879">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E879" t="s">
         <v>28</v>
@@ -19080,7 +19080,7 @@
         <v>27</v>
       </c>
       <c r="D880">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E880" t="s">
         <v>28</v>
@@ -19097,7 +19097,7 @@
         <v>27</v>
       </c>
       <c r="D881">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E881" t="s">
         <v>28</v>
@@ -19114,7 +19114,7 @@
         <v>27</v>
       </c>
       <c r="D882">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E882" t="s">
         <v>28</v>
@@ -19131,7 +19131,7 @@
         <v>27</v>
       </c>
       <c r="D883">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E883" t="s">
         <v>28</v>
@@ -19148,7 +19148,7 @@
         <v>27</v>
       </c>
       <c r="D884">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E884" t="s">
         <v>28</v>
@@ -19165,7 +19165,7 @@
         <v>27</v>
       </c>
       <c r="D885">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E885" t="s">
         <v>28</v>
@@ -19182,7 +19182,7 @@
         <v>27</v>
       </c>
       <c r="D886">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E886" t="s">
         <v>28</v>
@@ -19199,7 +19199,7 @@
         <v>27</v>
       </c>
       <c r="D887">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E887" t="s">
         <v>28</v>
@@ -19216,7 +19216,7 @@
         <v>27</v>
       </c>
       <c r="D888">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E888" t="s">
         <v>28</v>
@@ -19233,7 +19233,7 @@
         <v>27</v>
       </c>
       <c r="D889">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E889" t="s">
         <v>28</v>
@@ -19250,7 +19250,7 @@
         <v>27</v>
       </c>
       <c r="D890">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E890" t="s">
         <v>28</v>
@@ -19267,7 +19267,7 @@
         <v>27</v>
       </c>
       <c r="D891">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E891" t="s">
         <v>28</v>
@@ -19284,7 +19284,7 @@
         <v>27</v>
       </c>
       <c r="D892">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E892" t="s">
         <v>28</v>
@@ -19301,7 +19301,7 @@
         <v>27</v>
       </c>
       <c r="D893">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E893" t="s">
         <v>28</v>
@@ -19318,7 +19318,7 @@
         <v>27</v>
       </c>
       <c r="D894">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E894" t="s">
         <v>28</v>
@@ -19335,7 +19335,7 @@
         <v>27</v>
       </c>
       <c r="D895">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E895" t="s">
         <v>28</v>
@@ -19352,7 +19352,7 @@
         <v>27</v>
       </c>
       <c r="D896">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E896" t="s">
         <v>28</v>
@@ -19369,7 +19369,7 @@
         <v>27</v>
       </c>
       <c r="D897">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E897" t="s">
         <v>28</v>
@@ -19386,7 +19386,7 @@
         <v>27</v>
       </c>
       <c r="D898">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E898" t="s">
         <v>28</v>
@@ -19403,7 +19403,7 @@
         <v>27</v>
       </c>
       <c r="D899">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E899" t="s">
         <v>28</v>
@@ -19420,7 +19420,7 @@
         <v>27</v>
       </c>
       <c r="D900">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E900" t="s">
         <v>28</v>
@@ -19437,7 +19437,7 @@
         <v>27</v>
       </c>
       <c r="D901">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E901" t="s">
         <v>28</v>
@@ -19454,7 +19454,7 @@
         <v>27</v>
       </c>
       <c r="D902">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E902" t="s">
         <v>28</v>
@@ -19471,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D903">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E903" t="s">
         <v>28</v>
@@ -19488,7 +19488,7 @@
         <v>27</v>
       </c>
       <c r="D904">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E904" t="s">
         <v>28</v>
@@ -19505,7 +19505,7 @@
         <v>27</v>
       </c>
       <c r="D905">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E905" t="s">
         <v>28</v>
@@ -19522,7 +19522,7 @@
         <v>27</v>
       </c>
       <c r="D906">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E906" t="s">
         <v>28</v>
@@ -19539,7 +19539,7 @@
         <v>27</v>
       </c>
       <c r="D907">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E907" t="s">
         <v>28</v>
@@ -19556,7 +19556,7 @@
         <v>27</v>
       </c>
       <c r="D908">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E908" t="s">
         <v>28</v>
@@ -19573,7 +19573,7 @@
         <v>27</v>
       </c>
       <c r="D909">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E909" t="s">
         <v>28</v>
@@ -19590,7 +19590,7 @@
         <v>27</v>
       </c>
       <c r="D910">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E910" t="s">
         <v>28</v>
@@ -19607,7 +19607,7 @@
         <v>27</v>
       </c>
       <c r="D911">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E911" t="s">
         <v>28</v>
@@ -19624,7 +19624,7 @@
         <v>27</v>
       </c>
       <c r="D912">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E912" t="s">
         <v>28</v>
@@ -19641,7 +19641,7 @@
         <v>27</v>
       </c>
       <c r="D913">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E913" t="s">
         <v>28</v>
@@ -19675,7 +19675,7 @@
         <v>27</v>
       </c>
       <c r="D915">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E915" t="s">
         <v>28</v>
@@ -19692,7 +19692,7 @@
         <v>27</v>
       </c>
       <c r="D916">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E916" t="s">
         <v>28</v>
@@ -19709,7 +19709,7 @@
         <v>27</v>
       </c>
       <c r="D917">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E917" t="s">
         <v>28</v>
@@ -19726,7 +19726,7 @@
         <v>27</v>
       </c>
       <c r="D918">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E918" t="s">
         <v>28</v>
@@ -19743,7 +19743,7 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E919" t="s">
         <v>28</v>
@@ -19760,7 +19760,7 @@
         <v>27</v>
       </c>
       <c r="D920">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E920" t="s">
         <v>28</v>
@@ -19777,7 +19777,7 @@
         <v>27</v>
       </c>
       <c r="D921">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E921" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>27</v>
       </c>
       <c r="D922">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E922" t="s">
         <v>28</v>
@@ -19811,7 +19811,7 @@
         <v>27</v>
       </c>
       <c r="D923">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E923" t="s">
         <v>28</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="D924">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E924" t="s">
         <v>28</v>
@@ -19845,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="D925">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E925" t="s">
         <v>28</v>
@@ -19862,7 +19862,7 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E926" t="s">
         <v>28</v>
@@ -19879,7 +19879,7 @@
         <v>27</v>
       </c>
       <c r="D927">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E927" t="s">
         <v>28</v>
@@ -19896,7 +19896,7 @@
         <v>27</v>
       </c>
       <c r="D928">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E928" t="s">
         <v>28</v>
@@ -19913,7 +19913,7 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E929" t="s">
         <v>28</v>
@@ -19930,7 +19930,7 @@
         <v>27</v>
       </c>
       <c r="D930">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E930" t="s">
         <v>28</v>
@@ -19947,7 +19947,7 @@
         <v>27</v>
       </c>
       <c r="D931">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E931" t="s">
         <v>28</v>
@@ -19964,7 +19964,7 @@
         <v>27</v>
       </c>
       <c r="D932">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E932" t="s">
         <v>28</v>
@@ -19998,7 +19998,7 @@
         <v>27</v>
       </c>
       <c r="D934">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E934" t="s">
         <v>28</v>
@@ -20015,7 +20015,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E935" t="s">
         <v>28</v>
@@ -20032,7 +20032,7 @@
         <v>27</v>
       </c>
       <c r="D936">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E936" t="s">
         <v>28</v>
@@ -20049,7 +20049,7 @@
         <v>27</v>
       </c>
       <c r="D937">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E937" t="s">
         <v>28</v>
@@ -20066,7 +20066,7 @@
         <v>27</v>
       </c>
       <c r="D938">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E938" t="s">
         <v>28</v>
@@ -20083,7 +20083,7 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E939" t="s">
         <v>28</v>
@@ -20100,7 +20100,7 @@
         <v>27</v>
       </c>
       <c r="D940">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E940" t="s">
         <v>28</v>
@@ -20117,7 +20117,7 @@
         <v>27</v>
       </c>
       <c r="D941">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E941" t="s">
         <v>28</v>
@@ -20134,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D942">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E942" t="s">
         <v>28</v>
@@ -20151,7 +20151,7 @@
         <v>27</v>
       </c>
       <c r="D943">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E943" t="s">
         <v>28</v>
@@ -20168,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="D944">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E944" t="s">
         <v>28</v>
@@ -20185,7 +20185,7 @@
         <v>27</v>
       </c>
       <c r="D945">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E945" t="s">
         <v>28</v>
@@ -20202,7 +20202,7 @@
         <v>27</v>
       </c>
       <c r="D946">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E946" t="s">
         <v>28</v>
@@ -20219,7 +20219,7 @@
         <v>27</v>
       </c>
       <c r="D947">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E947" t="s">
         <v>28</v>
@@ -20236,7 +20236,7 @@
         <v>27</v>
       </c>
       <c r="D948">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E948" t="s">
         <v>28</v>
@@ -20253,7 +20253,7 @@
         <v>27</v>
       </c>
       <c r="D949">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E949" t="s">
         <v>28</v>
@@ -20270,7 +20270,7 @@
         <v>27</v>
       </c>
       <c r="D950">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E950" t="s">
         <v>28</v>
@@ -20287,7 +20287,7 @@
         <v>27</v>
       </c>
       <c r="D951">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E951" t="s">
         <v>28</v>
@@ -20304,7 +20304,7 @@
         <v>27</v>
       </c>
       <c r="D952">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E952" t="s">
         <v>28</v>
@@ -20321,7 +20321,7 @@
         <v>27</v>
       </c>
       <c r="D953">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E953" t="s">
         <v>28</v>
@@ -20338,7 +20338,7 @@
         <v>27</v>
       </c>
       <c r="D954">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E954" t="s">
         <v>28</v>
@@ -20355,7 +20355,7 @@
         <v>27</v>
       </c>
       <c r="D955">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E955" t="s">
         <v>28</v>
@@ -20372,7 +20372,7 @@
         <v>27</v>
       </c>
       <c r="D956">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E956" t="s">
         <v>28</v>
@@ -20389,7 +20389,7 @@
         <v>27</v>
       </c>
       <c r="D957">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E957" t="s">
         <v>28</v>
@@ -20406,7 +20406,7 @@
         <v>27</v>
       </c>
       <c r="D958">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E958" t="s">
         <v>28</v>
@@ -20423,7 +20423,7 @@
         <v>27</v>
       </c>
       <c r="D959">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E959" t="s">
         <v>28</v>
@@ -20440,7 +20440,7 @@
         <v>27</v>
       </c>
       <c r="D960">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E960" t="s">
         <v>28</v>
@@ -20457,7 +20457,7 @@
         <v>27</v>
       </c>
       <c r="D961">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E961" t="s">
         <v>28</v>
@@ -20474,7 +20474,7 @@
         <v>27</v>
       </c>
       <c r="D962">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E962" t="s">
         <v>28</v>
@@ -20491,7 +20491,7 @@
         <v>27</v>
       </c>
       <c r="D963">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E963" t="s">
         <v>28</v>
@@ -20508,7 +20508,7 @@
         <v>27</v>
       </c>
       <c r="D964">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E964" t="s">
         <v>28</v>
@@ -20525,7 +20525,7 @@
         <v>27</v>
       </c>
       <c r="D965">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E965" t="s">
         <v>28</v>
@@ -20542,7 +20542,7 @@
         <v>27</v>
       </c>
       <c r="D966">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E966" t="s">
         <v>28</v>
@@ -20559,7 +20559,7 @@
         <v>27</v>
       </c>
       <c r="D967">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E967" t="s">
         <v>28</v>
@@ -20576,7 +20576,7 @@
         <v>27</v>
       </c>
       <c r="D968">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E968" t="s">
         <v>28</v>
@@ -20593,7 +20593,7 @@
         <v>27</v>
       </c>
       <c r="D969">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E969" t="s">
         <v>28</v>
@@ -20610,7 +20610,7 @@
         <v>27</v>
       </c>
       <c r="D970">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E970" t="s">
         <v>28</v>
@@ -20627,7 +20627,7 @@
         <v>27</v>
       </c>
       <c r="D971">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E971" t="s">
         <v>28</v>
@@ -20644,7 +20644,7 @@
         <v>27</v>
       </c>
       <c r="D972">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E972" t="s">
         <v>28</v>
@@ -20661,7 +20661,7 @@
         <v>27</v>
       </c>
       <c r="D973">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E973" t="s">
         <v>28</v>
@@ -20678,7 +20678,7 @@
         <v>27</v>
       </c>
       <c r="D974">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E974" t="s">
         <v>28</v>
@@ -20712,7 +20712,7 @@
         <v>27</v>
       </c>
       <c r="D976">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E976" t="s">
         <v>28</v>
@@ -20729,7 +20729,7 @@
         <v>27</v>
       </c>
       <c r="D977">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E977" t="s">
         <v>28</v>
@@ -20746,7 +20746,7 @@
         <v>27</v>
       </c>
       <c r="D978">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E978" t="s">
         <v>28</v>
@@ -20763,7 +20763,7 @@
         <v>27</v>
       </c>
       <c r="D979">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E979" t="s">
         <v>28</v>
@@ -20780,7 +20780,7 @@
         <v>27</v>
       </c>
       <c r="D980">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E980" t="s">
         <v>28</v>
@@ -20797,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="D981">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E981" t="s">
         <v>28</v>
@@ -20814,7 +20814,7 @@
         <v>27</v>
       </c>
       <c r="D982">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E982" t="s">
         <v>28</v>
@@ -20831,7 +20831,7 @@
         <v>27</v>
       </c>
       <c r="D983">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E983" t="s">
         <v>28</v>
@@ -20848,7 +20848,7 @@
         <v>27</v>
       </c>
       <c r="D984">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E984" t="s">
         <v>28</v>
@@ -20865,7 +20865,7 @@
         <v>27</v>
       </c>
       <c r="D985">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E985" t="s">
         <v>28</v>
@@ -20899,7 +20899,7 @@
         <v>27</v>
       </c>
       <c r="D987">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E987" t="s">
         <v>28</v>
@@ -20916,7 +20916,7 @@
         <v>27</v>
       </c>
       <c r="D988">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E988" t="s">
         <v>28</v>
@@ -20933,7 +20933,7 @@
         <v>27</v>
       </c>
       <c r="D989">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E989" t="s">
         <v>28</v>
@@ -20950,7 +20950,7 @@
         <v>27</v>
       </c>
       <c r="D990">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E990" t="s">
         <v>28</v>
@@ -20967,7 +20967,7 @@
         <v>27</v>
       </c>
       <c r="D991">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E991" t="s">
         <v>28</v>
@@ -20984,7 +20984,7 @@
         <v>27</v>
       </c>
       <c r="D992">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E992" t="s">
         <v>28</v>
@@ -21001,7 +21001,7 @@
         <v>27</v>
       </c>
       <c r="D993">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E993" t="s">
         <v>28</v>
@@ -21018,7 +21018,7 @@
         <v>27</v>
       </c>
       <c r="D994">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E994" t="s">
         <v>28</v>
@@ -21035,7 +21035,7 @@
         <v>27</v>
       </c>
       <c r="D995">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E995" t="s">
         <v>28</v>
@@ -21052,7 +21052,7 @@
         <v>27</v>
       </c>
       <c r="D996">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E996" t="s">
         <v>28</v>
@@ -21069,7 +21069,7 @@
         <v>27</v>
       </c>
       <c r="D997">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E997" t="s">
         <v>28</v>
@@ -21086,7 +21086,7 @@
         <v>27</v>
       </c>
       <c r="D998">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E998" t="s">
         <v>28</v>
@@ -21103,7 +21103,7 @@
         <v>27</v>
       </c>
       <c r="D999">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E999" t="s">
         <v>28</v>
@@ -21120,7 +21120,7 @@
         <v>27</v>
       </c>
       <c r="D1000">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E1000" t="s">
         <v>28</v>
@@ -21137,7 +21137,7 @@
         <v>27</v>
       </c>
       <c r="D1001">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E1001" t="s">
         <v>28</v>
@@ -21154,7 +21154,7 @@
         <v>27</v>
       </c>
       <c r="D1002">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E1002" t="s">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>27</v>
       </c>
       <c r="D1003">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E1003" t="s">
         <v>28</v>
@@ -21188,7 +21188,7 @@
         <v>27</v>
       </c>
       <c r="D1004">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1004" t="s">
         <v>28</v>
@@ -21205,7 +21205,7 @@
         <v>27</v>
       </c>
       <c r="D1005">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1005" t="s">
         <v>28</v>
@@ -21222,7 +21222,7 @@
         <v>27</v>
       </c>
       <c r="D1006">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1006" t="s">
         <v>28</v>
@@ -21256,7 +21256,7 @@
         <v>27</v>
       </c>
       <c r="D1008">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E1008" t="s">
         <v>28</v>
@@ -21273,7 +21273,7 @@
         <v>27</v>
       </c>
       <c r="D1009">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E1009" t="s">
         <v>28</v>
@@ -21290,7 +21290,7 @@
         <v>27</v>
       </c>
       <c r="D1010">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1010" t="s">
         <v>28</v>
@@ -21307,7 +21307,7 @@
         <v>27</v>
       </c>
       <c r="D1011">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E1011" t="s">
         <v>28</v>
@@ -21324,7 +21324,7 @@
         <v>27</v>
       </c>
       <c r="D1012">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1012" t="s">
         <v>28</v>
@@ -21341,7 +21341,7 @@
         <v>27</v>
       </c>
       <c r="D1013">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E1013" t="s">
         <v>28</v>
@@ -21358,7 +21358,7 @@
         <v>27</v>
       </c>
       <c r="D1014">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1014" t="s">
         <v>28</v>
@@ -21375,7 +21375,7 @@
         <v>27</v>
       </c>
       <c r="D1015">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1015" t="s">
         <v>28</v>
@@ -21392,7 +21392,7 @@
         <v>27</v>
       </c>
       <c r="D1016">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E1016" t="s">
         <v>28</v>
@@ -21409,7 +21409,7 @@
         <v>27</v>
       </c>
       <c r="D1017">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E1017" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>27</v>
       </c>
       <c r="D1018">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1018" t="s">
         <v>28</v>
@@ -21443,7 +21443,7 @@
         <v>27</v>
       </c>
       <c r="D1019">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1019" t="s">
         <v>28</v>
@@ -21460,7 +21460,7 @@
         <v>27</v>
       </c>
       <c r="D1020">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E1020" t="s">
         <v>28</v>
@@ -21477,7 +21477,7 @@
         <v>27</v>
       </c>
       <c r="D1021">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1021" t="s">
         <v>28</v>
@@ -21494,7 +21494,7 @@
         <v>27</v>
       </c>
       <c r="D1022">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1022" t="s">
         <v>28</v>
@@ -21511,7 +21511,7 @@
         <v>27</v>
       </c>
       <c r="D1023">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E1023" t="s">
         <v>28</v>
@@ -21528,7 +21528,7 @@
         <v>27</v>
       </c>
       <c r="D1024">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E1024" t="s">
         <v>28</v>
@@ -21545,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E1025" t="s">
         <v>28</v>
@@ -21562,7 +21562,7 @@
         <v>27</v>
       </c>
       <c r="D1026">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1026" t="s">
         <v>28</v>
@@ -21579,7 +21579,7 @@
         <v>27</v>
       </c>
       <c r="D1027">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E1027" t="s">
         <v>28</v>
@@ -21596,7 +21596,7 @@
         <v>27</v>
       </c>
       <c r="D1028">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E1028" t="s">
         <v>28</v>
@@ -21613,7 +21613,7 @@
         <v>27</v>
       </c>
       <c r="D1029">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E1029" t="s">
         <v>28</v>
@@ -21630,7 +21630,7 @@
         <v>27</v>
       </c>
       <c r="D1030">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E1030" t="s">
         <v>28</v>
@@ -21647,7 +21647,7 @@
         <v>27</v>
       </c>
       <c r="D1031">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1031" t="s">
         <v>28</v>
@@ -21664,7 +21664,7 @@
         <v>27</v>
       </c>
       <c r="D1032">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E1032" t="s">
         <v>28</v>
@@ -21681,7 +21681,7 @@
         <v>27</v>
       </c>
       <c r="D1033">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E1033" t="s">
         <v>28</v>
@@ -21698,7 +21698,7 @@
         <v>27</v>
       </c>
       <c r="D1034">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1034" t="s">
         <v>28</v>
@@ -21715,7 +21715,7 @@
         <v>27</v>
       </c>
       <c r="D1035">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1035" t="s">
         <v>28</v>
@@ -21732,7 +21732,7 @@
         <v>27</v>
       </c>
       <c r="D1036">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E1036" t="s">
         <v>28</v>
@@ -21749,7 +21749,7 @@
         <v>27</v>
       </c>
       <c r="D1037">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E1037" t="s">
         <v>28</v>
@@ -21766,7 +21766,7 @@
         <v>27</v>
       </c>
       <c r="D1038">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1038" t="s">
         <v>28</v>
@@ -21783,7 +21783,7 @@
         <v>27</v>
       </c>
       <c r="D1039">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E1039" t="s">
         <v>28</v>
@@ -21800,7 +21800,7 @@
         <v>27</v>
       </c>
       <c r="D1040">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E1040" t="s">
         <v>28</v>
@@ -21817,7 +21817,7 @@
         <v>27</v>
       </c>
       <c r="D1041">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1041" t="s">
         <v>28</v>
@@ -21834,7 +21834,7 @@
         <v>27</v>
       </c>
       <c r="D1042">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1042" t="s">
         <v>28</v>
@@ -21851,7 +21851,7 @@
         <v>27</v>
       </c>
       <c r="D1043">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1043" t="s">
         <v>28</v>
@@ -21868,7 +21868,7 @@
         <v>27</v>
       </c>
       <c r="D1044">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E1044" t="s">
         <v>28</v>
@@ -21885,7 +21885,7 @@
         <v>27</v>
       </c>
       <c r="D1045">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1045" t="s">
         <v>28</v>
@@ -21902,7 +21902,7 @@
         <v>27</v>
       </c>
       <c r="D1046">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1046" t="s">
         <v>28</v>
@@ -21919,7 +21919,7 @@
         <v>27</v>
       </c>
       <c r="D1047">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E1047" t="s">
         <v>28</v>
@@ -21936,7 +21936,7 @@
         <v>27</v>
       </c>
       <c r="D1048">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1048" t="s">
         <v>28</v>
@@ -21953,7 +21953,7 @@
         <v>27</v>
       </c>
       <c r="D1049">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E1049" t="s">
         <v>28</v>
@@ -21970,7 +21970,7 @@
         <v>27</v>
       </c>
       <c r="D1050">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E1050" t="s">
         <v>28</v>
@@ -21987,7 +21987,7 @@
         <v>27</v>
       </c>
       <c r="D1051">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1051" t="s">
         <v>28</v>
@@ -22004,7 +22004,7 @@
         <v>27</v>
       </c>
       <c r="D1052">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E1052" t="s">
         <v>28</v>
@@ -22021,7 +22021,7 @@
         <v>27</v>
       </c>
       <c r="D1053">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1053" t="s">
         <v>28</v>
@@ -22038,7 +22038,7 @@
         <v>27</v>
       </c>
       <c r="D1054">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E1054" t="s">
         <v>28</v>
@@ -22055,7 +22055,7 @@
         <v>27</v>
       </c>
       <c r="D1055">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1055" t="s">
         <v>28</v>
@@ -22072,7 +22072,7 @@
         <v>27</v>
       </c>
       <c r="D1056">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E1056" t="s">
         <v>28</v>
@@ -22089,7 +22089,7 @@
         <v>27</v>
       </c>
       <c r="D1057">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E1057" t="s">
         <v>28</v>
@@ -22106,7 +22106,7 @@
         <v>27</v>
       </c>
       <c r="D1058">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1058" t="s">
         <v>28</v>
@@ -22140,7 +22140,7 @@
         <v>27</v>
       </c>
       <c r="D1060">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1060" t="s">
         <v>28</v>
@@ -22157,7 +22157,7 @@
         <v>27</v>
       </c>
       <c r="D1061">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1061" t="s">
         <v>28</v>
@@ -22174,7 +22174,7 @@
         <v>27</v>
       </c>
       <c r="D1062">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E1062" t="s">
         <v>28</v>
@@ -22191,7 +22191,7 @@
         <v>27</v>
       </c>
       <c r="D1063">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E1063" t="s">
         <v>28</v>
@@ -22208,7 +22208,7 @@
         <v>27</v>
       </c>
       <c r="D1064">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1064" t="s">
         <v>28</v>
@@ -22225,7 +22225,7 @@
         <v>27</v>
       </c>
       <c r="D1065">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1065" t="s">
         <v>28</v>
@@ -22242,7 +22242,7 @@
         <v>27</v>
       </c>
       <c r="D1066">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1066" t="s">
         <v>28</v>
@@ -22259,7 +22259,7 @@
         <v>27</v>
       </c>
       <c r="D1067">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1067" t="s">
         <v>28</v>
@@ -22276,7 +22276,7 @@
         <v>27</v>
       </c>
       <c r="D1068">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E1068" t="s">
         <v>28</v>
@@ -22293,7 +22293,7 @@
         <v>27</v>
       </c>
       <c r="D1069">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1069" t="s">
         <v>28</v>
@@ -22310,7 +22310,7 @@
         <v>27</v>
       </c>
       <c r="D1070">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1070" t="s">
         <v>28</v>
@@ -22327,7 +22327,7 @@
         <v>27</v>
       </c>
       <c r="D1071">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E1071" t="s">
         <v>28</v>
@@ -22344,7 +22344,7 @@
         <v>27</v>
       </c>
       <c r="D1072">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1072" t="s">
         <v>28</v>
@@ -22361,7 +22361,7 @@
         <v>27</v>
       </c>
       <c r="D1073">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E1073" t="s">
         <v>28</v>
@@ -22378,7 +22378,7 @@
         <v>27</v>
       </c>
       <c r="D1074">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1074" t="s">
         <v>28</v>
@@ -22395,7 +22395,7 @@
         <v>27</v>
       </c>
       <c r="D1075">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1075" t="s">
         <v>28</v>
@@ -22412,7 +22412,7 @@
         <v>27</v>
       </c>
       <c r="D1076">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E1076" t="s">
         <v>28</v>
@@ -22429,7 +22429,7 @@
         <v>27</v>
       </c>
       <c r="D1077">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E1077" t="s">
         <v>28</v>
@@ -22446,7 +22446,7 @@
         <v>27</v>
       </c>
       <c r="D1078">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E1078" t="s">
         <v>28</v>
@@ -22463,7 +22463,7 @@
         <v>27</v>
       </c>
       <c r="D1079">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1079" t="s">
         <v>28</v>
@@ -22480,7 +22480,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E1080" t="s">
         <v>28</v>
@@ -22497,7 +22497,7 @@
         <v>27</v>
       </c>
       <c r="D1081">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1081" t="s">
         <v>28</v>
@@ -22514,7 +22514,7 @@
         <v>27</v>
       </c>
       <c r="D1082">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E1082" t="s">
         <v>28</v>
@@ -22531,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="D1083">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E1083" t="s">
         <v>28</v>
@@ -22548,7 +22548,7 @@
         <v>27</v>
       </c>
       <c r="D1084">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1084" t="s">
         <v>28</v>
@@ -22565,7 +22565,7 @@
         <v>27</v>
       </c>
       <c r="D1085">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E1085" t="s">
         <v>28</v>
@@ -22582,7 +22582,7 @@
         <v>27</v>
       </c>
       <c r="D1086">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1086" t="s">
         <v>28</v>
@@ -22599,7 +22599,7 @@
         <v>27</v>
       </c>
       <c r="D1087">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1087" t="s">
         <v>28</v>
@@ -22616,7 +22616,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1088" t="s">
         <v>28</v>
@@ -22633,7 +22633,7 @@
         <v>27</v>
       </c>
       <c r="D1089">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1089" t="s">
         <v>28</v>
@@ -22650,7 +22650,7 @@
         <v>27</v>
       </c>
       <c r="D1090">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1090" t="s">
         <v>28</v>
@@ -22667,7 +22667,7 @@
         <v>27</v>
       </c>
       <c r="D1091">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E1091" t="s">
         <v>28</v>
@@ -22684,7 +22684,7 @@
         <v>27</v>
       </c>
       <c r="D1092">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1092" t="s">
         <v>28</v>
@@ -22701,7 +22701,7 @@
         <v>27</v>
       </c>
       <c r="D1093">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E1093" t="s">
         <v>28</v>
@@ -22718,7 +22718,7 @@
         <v>27</v>
       </c>
       <c r="D1094">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E1094" t="s">
         <v>28</v>
@@ -22735,7 +22735,7 @@
         <v>27</v>
       </c>
       <c r="D1095">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E1095" t="s">
         <v>28</v>
@@ -22752,7 +22752,7 @@
         <v>27</v>
       </c>
       <c r="D1096">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E1096" t="s">
         <v>28</v>
@@ -22769,7 +22769,7 @@
         <v>27</v>
       </c>
       <c r="D1097">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1097" t="s">
         <v>28</v>
@@ -22786,7 +22786,7 @@
         <v>27</v>
       </c>
       <c r="D1098">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E1098" t="s">
         <v>28</v>
@@ -22803,7 +22803,7 @@
         <v>27</v>
       </c>
       <c r="D1099">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E1099" t="s">
         <v>28</v>
@@ -22820,7 +22820,7 @@
         <v>27</v>
       </c>
       <c r="D1100">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E1100" t="s">
         <v>28</v>
@@ -22837,7 +22837,7 @@
         <v>27</v>
       </c>
       <c r="D1101">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1101" t="s">
         <v>28</v>
@@ -22871,7 +22871,7 @@
         <v>27</v>
       </c>
       <c r="D1103">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1103" t="s">
         <v>28</v>
@@ -22888,7 +22888,7 @@
         <v>27</v>
       </c>
       <c r="D1104">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1104" t="s">
         <v>28</v>
@@ -22905,7 +22905,7 @@
         <v>27</v>
       </c>
       <c r="D1105">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1105" t="s">
         <v>28</v>
@@ -22922,7 +22922,7 @@
         <v>27</v>
       </c>
       <c r="D1106">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1106" t="s">
         <v>28</v>
@@ -22939,7 +22939,7 @@
         <v>27</v>
       </c>
       <c r="D1107">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1107" t="s">
         <v>28</v>
@@ -22956,7 +22956,7 @@
         <v>27</v>
       </c>
       <c r="D1108">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E1108" t="s">
         <v>28</v>
@@ -22990,7 +22990,7 @@
         <v>27</v>
       </c>
       <c r="D1110">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E1110" t="s">
         <v>28</v>
@@ -23007,7 +23007,7 @@
         <v>27</v>
       </c>
       <c r="D1111">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1111" t="s">
         <v>28</v>
@@ -23024,7 +23024,7 @@
         <v>27</v>
       </c>
       <c r="D1112">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1112" t="s">
         <v>28</v>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1323</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1248</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1408</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1278</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1280</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1281</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1395</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1333</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1269</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1324</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1263</v>
+        <v>1256</v>
       </c>
     </row>
   </sheetData>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -4188,7 +4188,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -4222,7 +4222,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -4273,7 +4273,7 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4307,7 +4307,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4341,7 +4341,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -4358,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4409,7 +4409,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -4426,7 +4426,7 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -4443,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -4460,7 +4460,7 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
@@ -4494,7 +4494,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -4511,7 +4511,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -4528,7 +4528,7 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -4545,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
         <v>28</v>
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -4579,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -4596,7 +4596,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -4613,7 +4613,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E30" t="s">
         <v>28</v>
@@ -4647,7 +4647,7 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4681,7 +4681,7 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4698,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -4749,7 +4749,7 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
         <v>28</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="D38">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E38" t="s">
         <v>28</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
@@ -4817,7 +4817,7 @@
         <v>27</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4834,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4851,7 +4851,7 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
@@ -4885,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="D45">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E45" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
         <v>27</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -4919,7 +4919,7 @@
         <v>27</v>
       </c>
       <c r="D47">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="D48">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4953,7 +4953,7 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
@@ -4970,7 +4970,7 @@
         <v>27</v>
       </c>
       <c r="D50">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -4987,7 +4987,7 @@
         <v>27</v>
       </c>
       <c r="D51">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
@@ -5004,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5038,7 +5038,7 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E54" t="s">
         <v>28</v>
@@ -5055,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -5072,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E56" t="s">
         <v>28</v>
@@ -5089,7 +5089,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E57" t="s">
         <v>28</v>
@@ -5106,7 +5106,7 @@
         <v>27</v>
       </c>
       <c r="D58">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         <v>27</v>
       </c>
       <c r="D60">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E60" t="s">
         <v>28</v>
@@ -5157,7 +5157,7 @@
         <v>27</v>
       </c>
       <c r="D61">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -5174,7 +5174,7 @@
         <v>27</v>
       </c>
       <c r="D62">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
@@ -5191,7 +5191,7 @@
         <v>27</v>
       </c>
       <c r="D63">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
@@ -5225,7 +5225,7 @@
         <v>27</v>
       </c>
       <c r="D65">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -5242,7 +5242,7 @@
         <v>27</v>
       </c>
       <c r="D66">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="D67">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
@@ -5293,7 +5293,7 @@
         <v>27</v>
       </c>
       <c r="D69">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -5310,7 +5310,7 @@
         <v>27</v>
       </c>
       <c r="D70">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="D71">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -5344,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="D72">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
@@ -5361,7 +5361,7 @@
         <v>27</v>
       </c>
       <c r="D73">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -5378,7 +5378,7 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
@@ -5395,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="D75">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="D76">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
@@ -5429,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -5446,7 +5446,7 @@
         <v>27</v>
       </c>
       <c r="D78">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
@@ -5463,7 +5463,7 @@
         <v>27</v>
       </c>
       <c r="D79">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
@@ -5480,7 +5480,7 @@
         <v>27</v>
       </c>
       <c r="D80">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
@@ -5497,7 +5497,7 @@
         <v>27</v>
       </c>
       <c r="D81">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -5514,7 +5514,7 @@
         <v>27</v>
       </c>
       <c r="D82">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
@@ -5531,7 +5531,7 @@
         <v>27</v>
       </c>
       <c r="D83">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
@@ -5548,7 +5548,7 @@
         <v>27</v>
       </c>
       <c r="D84">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
@@ -5599,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
@@ -5616,7 +5616,7 @@
         <v>27</v>
       </c>
       <c r="D88">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -5633,7 +5633,7 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="D90">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -5667,7 +5667,7 @@
         <v>27</v>
       </c>
       <c r="D91">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E91" t="s">
         <v>28</v>
@@ -5684,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="D92">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
@@ -5701,7 +5701,7 @@
         <v>27</v>
       </c>
       <c r="D93">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E93" t="s">
         <v>28</v>
@@ -5718,7 +5718,7 @@
         <v>27</v>
       </c>
       <c r="D94">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E94" t="s">
         <v>28</v>
@@ -5735,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D95">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -5752,7 +5752,7 @@
         <v>27</v>
       </c>
       <c r="D96">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
         <v>28</v>
@@ -5769,7 +5769,7 @@
         <v>27</v>
       </c>
       <c r="D97">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E97" t="s">
         <v>28</v>
@@ -5786,7 +5786,7 @@
         <v>27</v>
       </c>
       <c r="D98">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="D99">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E99" t="s">
         <v>28</v>
@@ -5820,7 +5820,7 @@
         <v>27</v>
       </c>
       <c r="D100">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E100" t="s">
         <v>28</v>
@@ -5837,7 +5837,7 @@
         <v>27</v>
       </c>
       <c r="D101">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E101" t="s">
         <v>28</v>
@@ -5854,7 +5854,7 @@
         <v>27</v>
       </c>
       <c r="D102">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E102" t="s">
         <v>28</v>
@@ -5871,7 +5871,7 @@
         <v>27</v>
       </c>
       <c r="D103">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E103" t="s">
         <v>28</v>
@@ -5888,7 +5888,7 @@
         <v>27</v>
       </c>
       <c r="D104">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E104" t="s">
         <v>28</v>
@@ -5905,7 +5905,7 @@
         <v>27</v>
       </c>
       <c r="D105">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E105" t="s">
         <v>28</v>
@@ -5922,7 +5922,7 @@
         <v>27</v>
       </c>
       <c r="D106">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>27</v>
       </c>
       <c r="D107">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E107" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="D108">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5973,7 +5973,7 @@
         <v>27</v>
       </c>
       <c r="D109">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E109" t="s">
         <v>28</v>
@@ -5990,7 +5990,7 @@
         <v>27</v>
       </c>
       <c r="D110">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E110" t="s">
         <v>28</v>
@@ -6007,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="D111">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="D112">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="D113">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E113" t="s">
         <v>28</v>
@@ -6058,7 +6058,7 @@
         <v>27</v>
       </c>
       <c r="D114">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>27</v>
       </c>
       <c r="D115">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -6092,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="D116">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E116" t="s">
         <v>28</v>
@@ -6126,7 +6126,7 @@
         <v>27</v>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E118" t="s">
         <v>28</v>
@@ -6143,7 +6143,7 @@
         <v>27</v>
       </c>
       <c r="D119">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E119" t="s">
         <v>28</v>
@@ -6177,7 +6177,7 @@
         <v>27</v>
       </c>
       <c r="D121">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E121" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="D122">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E122" t="s">
         <v>28</v>
@@ -6211,7 +6211,7 @@
         <v>27</v>
       </c>
       <c r="D123">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E123" t="s">
         <v>28</v>
@@ -6245,7 +6245,7 @@
         <v>27</v>
       </c>
       <c r="D125">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
@@ -6262,7 +6262,7 @@
         <v>27</v>
       </c>
       <c r="D126">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -6279,7 +6279,7 @@
         <v>27</v>
       </c>
       <c r="D127">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E127" t="s">
         <v>28</v>
@@ -6296,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="D128">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E128" t="s">
         <v>28</v>
@@ -6330,7 +6330,7 @@
         <v>27</v>
       </c>
       <c r="D130">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E130" t="s">
         <v>28</v>
@@ -6347,7 +6347,7 @@
         <v>27</v>
       </c>
       <c r="D131">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E131" t="s">
         <v>28</v>
@@ -6364,7 +6364,7 @@
         <v>27</v>
       </c>
       <c r="D132">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E132" t="s">
         <v>28</v>
@@ -6381,7 +6381,7 @@
         <v>27</v>
       </c>
       <c r="D133">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E133" t="s">
         <v>28</v>
@@ -6398,7 +6398,7 @@
         <v>27</v>
       </c>
       <c r="D134">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E134" t="s">
         <v>28</v>
@@ -6415,7 +6415,7 @@
         <v>27</v>
       </c>
       <c r="D135">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E135" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E136" t="s">
         <v>28</v>
@@ -6449,7 +6449,7 @@
         <v>27</v>
       </c>
       <c r="D137">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E137" t="s">
         <v>28</v>
@@ -6466,7 +6466,7 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E138" t="s">
         <v>28</v>
@@ -6483,7 +6483,7 @@
         <v>27</v>
       </c>
       <c r="D139">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E139" t="s">
         <v>28</v>
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="D142">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E142" t="s">
         <v>28</v>
@@ -6551,7 +6551,7 @@
         <v>27</v>
       </c>
       <c r="D143">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E143" t="s">
         <v>28</v>
@@ -6568,7 +6568,7 @@
         <v>27</v>
       </c>
       <c r="D144">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E144" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="D145">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E145" t="s">
         <v>28</v>
@@ -6602,7 +6602,7 @@
         <v>27</v>
       </c>
       <c r="D146">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E146" t="s">
         <v>28</v>
@@ -6619,7 +6619,7 @@
         <v>27</v>
       </c>
       <c r="D147">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E147" t="s">
         <v>28</v>
@@ -6636,7 +6636,7 @@
         <v>27</v>
       </c>
       <c r="D148">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E148" t="s">
         <v>28</v>
@@ -6653,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="D149">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6687,7 +6687,7 @@
         <v>27</v>
       </c>
       <c r="D151">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>27</v>
       </c>
       <c r="D152">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E152" t="s">
         <v>28</v>
@@ -6738,7 +6738,7 @@
         <v>27</v>
       </c>
       <c r="D154">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E154" t="s">
         <v>28</v>
@@ -6755,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -6772,7 +6772,7 @@
         <v>27</v>
       </c>
       <c r="D156">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E156" t="s">
         <v>28</v>
@@ -6789,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="D157">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E157" t="s">
         <v>28</v>
@@ -6806,7 +6806,7 @@
         <v>27</v>
       </c>
       <c r="D158">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E158" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="D159">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E159" t="s">
         <v>28</v>
@@ -6840,7 +6840,7 @@
         <v>27</v>
       </c>
       <c r="D160">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E160" t="s">
         <v>28</v>
@@ -6857,7 +6857,7 @@
         <v>27</v>
       </c>
       <c r="D161">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
@@ -6891,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="D163">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E163" t="s">
         <v>28</v>
@@ -6908,7 +6908,7 @@
         <v>27</v>
       </c>
       <c r="D164">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E164" t="s">
         <v>28</v>
@@ -6925,7 +6925,7 @@
         <v>27</v>
       </c>
       <c r="D165">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E165" t="s">
         <v>28</v>
@@ -6942,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="D166">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E166" t="s">
         <v>28</v>
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="D167">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E167" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="D168">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E168" t="s">
         <v>28</v>
@@ -7010,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="D170">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E170" t="s">
         <v>28</v>
@@ -7027,7 +7027,7 @@
         <v>27</v>
       </c>
       <c r="D171">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E171" t="s">
         <v>28</v>
@@ -7044,7 +7044,7 @@
         <v>27</v>
       </c>
       <c r="D172">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E172" t="s">
         <v>28</v>
@@ -7078,7 +7078,7 @@
         <v>27</v>
       </c>
       <c r="D174">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E174" t="s">
         <v>28</v>
@@ -7095,7 +7095,7 @@
         <v>27</v>
       </c>
       <c r="D175">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E175" t="s">
         <v>28</v>
@@ -7112,7 +7112,7 @@
         <v>27</v>
       </c>
       <c r="D176">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E176" t="s">
         <v>28</v>
@@ -7129,7 +7129,7 @@
         <v>27</v>
       </c>
       <c r="D177">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E177" t="s">
         <v>28</v>
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="D178">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E178" t="s">
         <v>28</v>
@@ -7163,7 +7163,7 @@
         <v>27</v>
       </c>
       <c r="D179">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E179" t="s">
         <v>28</v>
@@ -7180,7 +7180,7 @@
         <v>27</v>
       </c>
       <c r="D180">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -7197,7 +7197,7 @@
         <v>27</v>
       </c>
       <c r="D181">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E181" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="D182">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E182" t="s">
         <v>28</v>
@@ -7231,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="D183">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
@@ -7248,7 +7248,7 @@
         <v>27</v>
       </c>
       <c r="D184">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E184" t="s">
         <v>28</v>
@@ -7265,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="D185">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E185" t="s">
         <v>28</v>
@@ -7282,7 +7282,7 @@
         <v>27</v>
       </c>
       <c r="D186">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E186" t="s">
         <v>28</v>
@@ -7299,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="D187">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E187" t="s">
         <v>28</v>
@@ -7316,7 +7316,7 @@
         <v>27</v>
       </c>
       <c r="D188">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -7333,7 +7333,7 @@
         <v>27</v>
       </c>
       <c r="D189">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E189" t="s">
         <v>28</v>
@@ -7350,7 +7350,7 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E190" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="D191">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
@@ -7401,7 +7401,7 @@
         <v>27</v>
       </c>
       <c r="D193">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E193" t="s">
         <v>28</v>
@@ -7418,7 +7418,7 @@
         <v>27</v>
       </c>
       <c r="D194">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E194" t="s">
         <v>28</v>
@@ -7435,7 +7435,7 @@
         <v>27</v>
       </c>
       <c r="D195">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E195" t="s">
         <v>28</v>
@@ -7452,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="D196">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E196" t="s">
         <v>28</v>
@@ -7469,7 +7469,7 @@
         <v>27</v>
       </c>
       <c r="D197">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E197" t="s">
         <v>28</v>
@@ -7486,7 +7486,7 @@
         <v>27</v>
       </c>
       <c r="D198">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E198" t="s">
         <v>28</v>
@@ -7503,7 +7503,7 @@
         <v>27</v>
       </c>
       <c r="D199">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E199" t="s">
         <v>28</v>
@@ -7520,7 +7520,7 @@
         <v>27</v>
       </c>
       <c r="D200">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E200" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>27</v>
       </c>
       <c r="D201">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E201" t="s">
         <v>28</v>
@@ -7554,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="D202">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E202" t="s">
         <v>28</v>
@@ -7571,7 +7571,7 @@
         <v>27</v>
       </c>
       <c r="D203">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
@@ -7588,7 +7588,7 @@
         <v>27</v>
       </c>
       <c r="D204">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E204" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="D205">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -7622,7 +7622,7 @@
         <v>27</v>
       </c>
       <c r="D206">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E206" t="s">
         <v>28</v>
@@ -7639,7 +7639,7 @@
         <v>27</v>
       </c>
       <c r="D207">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E207" t="s">
         <v>28</v>
@@ -7656,7 +7656,7 @@
         <v>27</v>
       </c>
       <c r="D208">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E208" t="s">
         <v>28</v>
@@ -7673,7 +7673,7 @@
         <v>27</v>
       </c>
       <c r="D209">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E209" t="s">
         <v>28</v>
@@ -7690,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="D210">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E210" t="s">
         <v>28</v>
@@ -7707,7 +7707,7 @@
         <v>27</v>
       </c>
       <c r="D211">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E211" t="s">
         <v>28</v>
@@ -7724,7 +7724,7 @@
         <v>27</v>
       </c>
       <c r="D212">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E212" t="s">
         <v>28</v>
@@ -7741,7 +7741,7 @@
         <v>27</v>
       </c>
       <c r="D213">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E213" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="D214">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E214" t="s">
         <v>28</v>
@@ -7775,7 +7775,7 @@
         <v>27</v>
       </c>
       <c r="D215">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E215" t="s">
         <v>28</v>
@@ -7792,7 +7792,7 @@
         <v>27</v>
       </c>
       <c r="D216">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E216" t="s">
         <v>28</v>
@@ -7809,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="D217">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E217" t="s">
         <v>28</v>
@@ -7826,7 +7826,7 @@
         <v>27</v>
       </c>
       <c r="D218">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E218" t="s">
         <v>28</v>
@@ -7843,7 +7843,7 @@
         <v>27</v>
       </c>
       <c r="D219">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E219" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="D220">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E220" t="s">
         <v>28</v>
@@ -7877,7 +7877,7 @@
         <v>27</v>
       </c>
       <c r="D221">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E221" t="s">
         <v>28</v>
@@ -7894,7 +7894,7 @@
         <v>27</v>
       </c>
       <c r="D222">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E222" t="s">
         <v>28</v>
@@ -7911,7 +7911,7 @@
         <v>27</v>
       </c>
       <c r="D223">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E223" t="s">
         <v>28</v>
@@ -7928,7 +7928,7 @@
         <v>27</v>
       </c>
       <c r="D224">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E224" t="s">
         <v>28</v>
@@ -7945,7 +7945,7 @@
         <v>27</v>
       </c>
       <c r="D225">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E225" t="s">
         <v>28</v>
@@ -7962,7 +7962,7 @@
         <v>27</v>
       </c>
       <c r="D226">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E226" t="s">
         <v>28</v>
@@ -7979,7 +7979,7 @@
         <v>27</v>
       </c>
       <c r="D227">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E227" t="s">
         <v>28</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="D228">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E228" t="s">
         <v>28</v>
@@ -8013,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="D229">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E229" t="s">
         <v>28</v>
@@ -8030,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="D230">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E230" t="s">
         <v>28</v>
@@ -8047,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="D231">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E231" t="s">
         <v>28</v>
@@ -8064,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="D232">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E232" t="s">
         <v>28</v>
@@ -8081,7 +8081,7 @@
         <v>27</v>
       </c>
       <c r="D233">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E233" t="s">
         <v>28</v>
@@ -8098,7 +8098,7 @@
         <v>27</v>
       </c>
       <c r="D234">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E234" t="s">
         <v>28</v>
@@ -8115,7 +8115,7 @@
         <v>27</v>
       </c>
       <c r="D235">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E235" t="s">
         <v>28</v>
@@ -8132,7 +8132,7 @@
         <v>27</v>
       </c>
       <c r="D236">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E236" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="D237">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E237" t="s">
         <v>28</v>
@@ -8166,7 +8166,7 @@
         <v>27</v>
       </c>
       <c r="D238">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E238" t="s">
         <v>28</v>
@@ -8183,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="D239">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E239" t="s">
         <v>28</v>
@@ -8200,7 +8200,7 @@
         <v>27</v>
       </c>
       <c r="D240">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E240" t="s">
         <v>28</v>
@@ -8217,7 +8217,7 @@
         <v>27</v>
       </c>
       <c r="D241">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E241" t="s">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>27</v>
       </c>
       <c r="D242">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E242" t="s">
         <v>28</v>
@@ -8251,7 +8251,7 @@
         <v>27</v>
       </c>
       <c r="D243">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E243" t="s">
         <v>28</v>
@@ -8268,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="D244">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E244" t="s">
         <v>28</v>
@@ -8302,7 +8302,7 @@
         <v>27</v>
       </c>
       <c r="D246">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E246" t="s">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="D247">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E247" t="s">
         <v>28</v>
@@ -8336,7 +8336,7 @@
         <v>27</v>
       </c>
       <c r="D248">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E248" t="s">
         <v>28</v>
@@ -8353,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="D249">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E249" t="s">
         <v>28</v>
@@ -8370,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="D250">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E250" t="s">
         <v>28</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="D251">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E251" t="s">
         <v>28</v>
@@ -8404,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="D252">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E252" t="s">
         <v>28</v>
@@ -8421,7 +8421,7 @@
         <v>27</v>
       </c>
       <c r="D253">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E253" t="s">
         <v>28</v>
@@ -8438,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D254">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E254" t="s">
         <v>28</v>
@@ -8455,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="D255">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E255" t="s">
         <v>28</v>
@@ -8472,7 +8472,7 @@
         <v>27</v>
       </c>
       <c r="D256">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E256" t="s">
         <v>28</v>
@@ -8489,7 +8489,7 @@
         <v>27</v>
       </c>
       <c r="D257">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E257" t="s">
         <v>28</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="D258">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E258" t="s">
         <v>28</v>
@@ -8523,7 +8523,7 @@
         <v>27</v>
       </c>
       <c r="D259">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E259" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="D260">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E260" t="s">
         <v>28</v>
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="D261">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E261" t="s">
         <v>28</v>
@@ -8574,7 +8574,7 @@
         <v>27</v>
       </c>
       <c r="D262">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E262" t="s">
         <v>28</v>
@@ -8591,7 +8591,7 @@
         <v>27</v>
       </c>
       <c r="D263">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E263" t="s">
         <v>28</v>
@@ -8608,7 +8608,7 @@
         <v>27</v>
       </c>
       <c r="D264">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E264" t="s">
         <v>28</v>
@@ -8625,7 +8625,7 @@
         <v>27</v>
       </c>
       <c r="D265">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E265" t="s">
         <v>28</v>
@@ -8642,7 +8642,7 @@
         <v>27</v>
       </c>
       <c r="D266">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E266" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="D267">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E267" t="s">
         <v>28</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="D268">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E268" t="s">
         <v>28</v>
@@ -8693,7 +8693,7 @@
         <v>27</v>
       </c>
       <c r="D269">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E269" t="s">
         <v>28</v>
@@ -8710,7 +8710,7 @@
         <v>27</v>
       </c>
       <c r="D270">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E270" t="s">
         <v>28</v>
@@ -8727,7 +8727,7 @@
         <v>27</v>
       </c>
       <c r="D271">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E271" t="s">
         <v>28</v>
@@ -8744,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="D272">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E272" t="s">
         <v>28</v>
@@ -8761,7 +8761,7 @@
         <v>27</v>
       </c>
       <c r="D273">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E273" t="s">
         <v>28</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="D274">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E274" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>27</v>
       </c>
       <c r="D275">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E275" t="s">
         <v>28</v>
@@ -8812,7 +8812,7 @@
         <v>27</v>
       </c>
       <c r="D276">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E276" t="s">
         <v>28</v>
@@ -8829,7 +8829,7 @@
         <v>27</v>
       </c>
       <c r="D277">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E277" t="s">
         <v>28</v>
@@ -8846,7 +8846,7 @@
         <v>27</v>
       </c>
       <c r="D278">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E278" t="s">
         <v>28</v>
@@ -8863,7 +8863,7 @@
         <v>27</v>
       </c>
       <c r="D279">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E279" t="s">
         <v>28</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E280" t="s">
         <v>28</v>
@@ -8897,7 +8897,7 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E281" t="s">
         <v>28</v>
@@ -8914,7 +8914,7 @@
         <v>27</v>
       </c>
       <c r="D282">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E282" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="D283">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E283" t="s">
         <v>28</v>
@@ -8948,7 +8948,7 @@
         <v>27</v>
       </c>
       <c r="D284">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E284" t="s">
         <v>28</v>
@@ -8965,7 +8965,7 @@
         <v>27</v>
       </c>
       <c r="D285">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E285" t="s">
         <v>28</v>
@@ -8982,7 +8982,7 @@
         <v>27</v>
       </c>
       <c r="D286">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E286" t="s">
         <v>28</v>
@@ -8999,7 +8999,7 @@
         <v>27</v>
       </c>
       <c r="D287">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E287" t="s">
         <v>28</v>
@@ -9016,7 +9016,7 @@
         <v>27</v>
       </c>
       <c r="D288">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E288" t="s">
         <v>28</v>
@@ -9033,7 +9033,7 @@
         <v>27</v>
       </c>
       <c r="D289">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E289" t="s">
         <v>28</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="D290">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E290" t="s">
         <v>28</v>
@@ -9067,7 +9067,7 @@
         <v>27</v>
       </c>
       <c r="D291">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E291" t="s">
         <v>28</v>
@@ -9084,7 +9084,7 @@
         <v>27</v>
       </c>
       <c r="D292">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E292" t="s">
         <v>28</v>
@@ -9101,7 +9101,7 @@
         <v>27</v>
       </c>
       <c r="D293">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E293" t="s">
         <v>28</v>
@@ -9135,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="D295">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E295" t="s">
         <v>28</v>
@@ -9152,7 +9152,7 @@
         <v>27</v>
       </c>
       <c r="D296">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E296" t="s">
         <v>28</v>
@@ -9169,7 +9169,7 @@
         <v>27</v>
       </c>
       <c r="D297">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E297" t="s">
         <v>28</v>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="D298">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E298" t="s">
         <v>28</v>
@@ -9203,7 +9203,7 @@
         <v>27</v>
       </c>
       <c r="D299">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E299" t="s">
         <v>28</v>
@@ -9220,7 +9220,7 @@
         <v>27</v>
       </c>
       <c r="D300">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E300" t="s">
         <v>28</v>
@@ -9237,7 +9237,7 @@
         <v>27</v>
       </c>
       <c r="D301">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E301" t="s">
         <v>28</v>
@@ -9254,7 +9254,7 @@
         <v>27</v>
       </c>
       <c r="D302">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E302" t="s">
         <v>28</v>
@@ -9271,7 +9271,7 @@
         <v>27</v>
       </c>
       <c r="D303">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E303" t="s">
         <v>28</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="D304">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E304" t="s">
         <v>28</v>
@@ -9305,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="D305">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E305" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="D306">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E306" t="s">
         <v>28</v>
@@ -9339,7 +9339,7 @@
         <v>27</v>
       </c>
       <c r="D307">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E307" t="s">
         <v>28</v>
@@ -9356,7 +9356,7 @@
         <v>27</v>
       </c>
       <c r="D308">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E308" t="s">
         <v>28</v>
@@ -9373,7 +9373,7 @@
         <v>27</v>
       </c>
       <c r="D309">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E309" t="s">
         <v>28</v>
@@ -9390,7 +9390,7 @@
         <v>27</v>
       </c>
       <c r="D310">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E310" t="s">
         <v>28</v>
@@ -9407,7 +9407,7 @@
         <v>27</v>
       </c>
       <c r="D311">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E311" t="s">
         <v>28</v>
@@ -9424,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="D312">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E312" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="D313">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E313" t="s">
         <v>28</v>
@@ -9458,7 +9458,7 @@
         <v>27</v>
       </c>
       <c r="D314">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E314" t="s">
         <v>28</v>
@@ -9475,7 +9475,7 @@
         <v>27</v>
       </c>
       <c r="D315">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E315" t="s">
         <v>28</v>
@@ -9492,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="D316">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E316" t="s">
         <v>28</v>
@@ -9509,7 +9509,7 @@
         <v>27</v>
       </c>
       <c r="D317">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E317" t="s">
         <v>28</v>
@@ -9526,7 +9526,7 @@
         <v>27</v>
       </c>
       <c r="D318">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E318" t="s">
         <v>28</v>
@@ -9543,7 +9543,7 @@
         <v>27</v>
       </c>
       <c r="D319">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E319" t="s">
         <v>28</v>
@@ -9577,7 +9577,7 @@
         <v>27</v>
       </c>
       <c r="D321">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E321" t="s">
         <v>28</v>
@@ -9594,7 +9594,7 @@
         <v>27</v>
       </c>
       <c r="D322">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E322" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
         <v>27</v>
       </c>
       <c r="D323">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E323" t="s">
         <v>28</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="D324">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E324" t="s">
         <v>28</v>
@@ -9645,7 +9645,7 @@
         <v>27</v>
       </c>
       <c r="D325">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E325" t="s">
         <v>28</v>
@@ -9662,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="D326">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E326" t="s">
         <v>28</v>
@@ -9679,7 +9679,7 @@
         <v>27</v>
       </c>
       <c r="D327">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E327" t="s">
         <v>28</v>
@@ -9696,7 +9696,7 @@
         <v>27</v>
       </c>
       <c r="D328">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E328" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="D329">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E329" t="s">
         <v>28</v>
@@ -9730,7 +9730,7 @@
         <v>27</v>
       </c>
       <c r="D330">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E330" t="s">
         <v>28</v>
@@ -9747,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="D331">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E331" t="s">
         <v>28</v>
@@ -9764,7 +9764,7 @@
         <v>27</v>
       </c>
       <c r="D332">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E332" t="s">
         <v>28</v>
@@ -9781,7 +9781,7 @@
         <v>27</v>
       </c>
       <c r="D333">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E333" t="s">
         <v>28</v>
@@ -9798,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="D334">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E334" t="s">
         <v>28</v>
@@ -9815,7 +9815,7 @@
         <v>27</v>
       </c>
       <c r="D335">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E335" t="s">
         <v>28</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="D336">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E336" t="s">
         <v>28</v>
@@ -9849,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="D337">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E337" t="s">
         <v>28</v>
@@ -9866,7 +9866,7 @@
         <v>27</v>
       </c>
       <c r="D338">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E338" t="s">
         <v>28</v>
@@ -9883,7 +9883,7 @@
         <v>27</v>
       </c>
       <c r="D339">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E339" t="s">
         <v>28</v>
@@ -9900,7 +9900,7 @@
         <v>27</v>
       </c>
       <c r="D340">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E340" t="s">
         <v>28</v>
@@ -9917,7 +9917,7 @@
         <v>27</v>
       </c>
       <c r="D341">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E341" t="s">
         <v>28</v>
@@ -9934,7 +9934,7 @@
         <v>27</v>
       </c>
       <c r="D342">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E342" t="s">
         <v>28</v>
@@ -9951,7 +9951,7 @@
         <v>27</v>
       </c>
       <c r="D343">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E343" t="s">
         <v>28</v>
@@ -9968,7 +9968,7 @@
         <v>27</v>
       </c>
       <c r="D344">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E344" t="s">
         <v>28</v>
@@ -9985,7 +9985,7 @@
         <v>27</v>
       </c>
       <c r="D345">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E345" t="s">
         <v>28</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D346">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E346" t="s">
         <v>28</v>
@@ -10019,7 +10019,7 @@
         <v>27</v>
       </c>
       <c r="D347">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E347" t="s">
         <v>28</v>
@@ -10036,7 +10036,7 @@
         <v>27</v>
       </c>
       <c r="D348">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E348" t="s">
         <v>28</v>
@@ -10053,7 +10053,7 @@
         <v>27</v>
       </c>
       <c r="D349">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E349" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="D350">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E350" t="s">
         <v>28</v>
@@ -10104,7 +10104,7 @@
         <v>27</v>
       </c>
       <c r="D352">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E352" t="s">
         <v>28</v>
@@ -10121,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D353">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E353" t="s">
         <v>28</v>
@@ -10138,7 +10138,7 @@
         <v>27</v>
       </c>
       <c r="D354">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E354" t="s">
         <v>28</v>
@@ -10155,7 +10155,7 @@
         <v>27</v>
       </c>
       <c r="D355">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E355" t="s">
         <v>28</v>
@@ -10172,7 +10172,7 @@
         <v>27</v>
       </c>
       <c r="D356">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E356" t="s">
         <v>28</v>
@@ -10189,7 +10189,7 @@
         <v>27</v>
       </c>
       <c r="D357">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E357" t="s">
         <v>28</v>
@@ -10206,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="D358">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E358" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="D359">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E359" t="s">
         <v>28</v>
@@ -10240,7 +10240,7 @@
         <v>27</v>
       </c>
       <c r="D360">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E360" t="s">
         <v>28</v>
@@ -10257,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="D361">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E361" t="s">
         <v>28</v>
@@ -10274,7 +10274,7 @@
         <v>27</v>
       </c>
       <c r="D362">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E362" t="s">
         <v>28</v>
@@ -10291,7 +10291,7 @@
         <v>27</v>
       </c>
       <c r="D363">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E363" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="D364">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E364" t="s">
         <v>28</v>
@@ -10325,7 +10325,7 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E365" t="s">
         <v>28</v>
@@ -10342,7 +10342,7 @@
         <v>27</v>
       </c>
       <c r="D366">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E366" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
         <v>27</v>
       </c>
       <c r="D367">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E367" t="s">
         <v>28</v>
@@ -10376,7 +10376,7 @@
         <v>27</v>
       </c>
       <c r="D368">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E368" t="s">
         <v>28</v>
@@ -10393,7 +10393,7 @@
         <v>27</v>
       </c>
       <c r="D369">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E369" t="s">
         <v>28</v>
@@ -10410,7 +10410,7 @@
         <v>27</v>
       </c>
       <c r="D370">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E370" t="s">
         <v>28</v>
@@ -10427,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="D371">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E371" t="s">
         <v>28</v>
@@ -10444,7 +10444,7 @@
         <v>27</v>
       </c>
       <c r="D372">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E372" t="s">
         <v>28</v>
@@ -10461,7 +10461,7 @@
         <v>27</v>
       </c>
       <c r="D373">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E373" t="s">
         <v>28</v>
@@ -10495,7 +10495,7 @@
         <v>27</v>
       </c>
       <c r="D375">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E375" t="s">
         <v>28</v>
@@ -10512,7 +10512,7 @@
         <v>27</v>
       </c>
       <c r="D376">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E376" t="s">
         <v>28</v>
@@ -10529,7 +10529,7 @@
         <v>27</v>
       </c>
       <c r="D377">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E377" t="s">
         <v>28</v>
@@ -10546,7 +10546,7 @@
         <v>27</v>
       </c>
       <c r="D378">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E378" t="s">
         <v>28</v>
@@ -10563,7 +10563,7 @@
         <v>27</v>
       </c>
       <c r="D379">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E379" t="s">
         <v>28</v>
@@ -10580,7 +10580,7 @@
         <v>27</v>
       </c>
       <c r="D380">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E380" t="s">
         <v>28</v>
@@ -10597,7 +10597,7 @@
         <v>27</v>
       </c>
       <c r="D381">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E381" t="s">
         <v>28</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="D382">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E382" t="s">
         <v>28</v>
@@ -10631,7 +10631,7 @@
         <v>27</v>
       </c>
       <c r="D383">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E383" t="s">
         <v>28</v>
@@ -10648,7 +10648,7 @@
         <v>27</v>
       </c>
       <c r="D384">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E384" t="s">
         <v>28</v>
@@ -10682,7 +10682,7 @@
         <v>27</v>
       </c>
       <c r="D386">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E386" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="D387">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E387" t="s">
         <v>28</v>
@@ -10716,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="D388">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E388" t="s">
         <v>28</v>
@@ -10733,7 +10733,7 @@
         <v>27</v>
       </c>
       <c r="D389">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E389" t="s">
         <v>28</v>
@@ -10750,7 +10750,7 @@
         <v>27</v>
       </c>
       <c r="D390">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E390" t="s">
         <v>28</v>
@@ -10767,7 +10767,7 @@
         <v>27</v>
       </c>
       <c r="D391">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E391" t="s">
         <v>28</v>
@@ -10784,7 +10784,7 @@
         <v>27</v>
       </c>
       <c r="D392">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E392" t="s">
         <v>28</v>
@@ -10801,7 +10801,7 @@
         <v>27</v>
       </c>
       <c r="D393">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E393" t="s">
         <v>28</v>
@@ -10818,7 +10818,7 @@
         <v>27</v>
       </c>
       <c r="D394">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E394" t="s">
         <v>28</v>
@@ -10835,7 +10835,7 @@
         <v>27</v>
       </c>
       <c r="D395">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E395" t="s">
         <v>28</v>
@@ -10852,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="D396">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E396" t="s">
         <v>28</v>
@@ -10869,7 +10869,7 @@
         <v>27</v>
       </c>
       <c r="D397">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E397" t="s">
         <v>28</v>
@@ -10886,7 +10886,7 @@
         <v>27</v>
       </c>
       <c r="D398">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E398" t="s">
         <v>28</v>
@@ -10920,7 +10920,7 @@
         <v>27</v>
       </c>
       <c r="D400">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E400" t="s">
         <v>28</v>
@@ -10937,7 +10937,7 @@
         <v>27</v>
       </c>
       <c r="D401">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E401" t="s">
         <v>28</v>
@@ -10954,7 +10954,7 @@
         <v>27</v>
       </c>
       <c r="D402">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E402" t="s">
         <v>28</v>
@@ -10971,7 +10971,7 @@
         <v>27</v>
       </c>
       <c r="D403">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E403" t="s">
         <v>28</v>
@@ -10988,7 +10988,7 @@
         <v>27</v>
       </c>
       <c r="D404">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E404" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="D405">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E405" t="s">
         <v>28</v>
@@ -11022,7 +11022,7 @@
         <v>27</v>
       </c>
       <c r="D406">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E406" t="s">
         <v>28</v>
@@ -11039,7 +11039,7 @@
         <v>27</v>
       </c>
       <c r="D407">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E407" t="s">
         <v>28</v>
@@ -11073,7 +11073,7 @@
         <v>27</v>
       </c>
       <c r="D409">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E409" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="D410">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E410" t="s">
         <v>28</v>
@@ -11107,7 +11107,7 @@
         <v>27</v>
       </c>
       <c r="D411">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E411" t="s">
         <v>28</v>
@@ -11124,7 +11124,7 @@
         <v>27</v>
       </c>
       <c r="D412">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E412" t="s">
         <v>28</v>
@@ -11141,7 +11141,7 @@
         <v>27</v>
       </c>
       <c r="D413">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E413" t="s">
         <v>28</v>
@@ -11158,7 +11158,7 @@
         <v>27</v>
       </c>
       <c r="D414">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E414" t="s">
         <v>28</v>
@@ -11175,7 +11175,7 @@
         <v>27</v>
       </c>
       <c r="D415">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E415" t="s">
         <v>28</v>
@@ -11192,7 +11192,7 @@
         <v>27</v>
       </c>
       <c r="D416">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E416" t="s">
         <v>28</v>
@@ -11209,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="D417">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E417" t="s">
         <v>28</v>
@@ -11226,7 +11226,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E418" t="s">
         <v>28</v>
@@ -11243,7 +11243,7 @@
         <v>27</v>
       </c>
       <c r="D419">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E419" t="s">
         <v>28</v>
@@ -11260,7 +11260,7 @@
         <v>27</v>
       </c>
       <c r="D420">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E420" t="s">
         <v>28</v>
@@ -11294,7 +11294,7 @@
         <v>27</v>
       </c>
       <c r="D422">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E422" t="s">
         <v>28</v>
@@ -11311,7 +11311,7 @@
         <v>27</v>
       </c>
       <c r="D423">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E423" t="s">
         <v>28</v>
@@ -11328,7 +11328,7 @@
         <v>27</v>
       </c>
       <c r="D424">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E424" t="s">
         <v>28</v>
@@ -11345,7 +11345,7 @@
         <v>27</v>
       </c>
       <c r="D425">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E425" t="s">
         <v>28</v>
@@ -11362,7 +11362,7 @@
         <v>27</v>
       </c>
       <c r="D426">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E426" t="s">
         <v>28</v>
@@ -11379,7 +11379,7 @@
         <v>27</v>
       </c>
       <c r="D427">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E427" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="D428">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E428" t="s">
         <v>28</v>
@@ -11413,7 +11413,7 @@
         <v>27</v>
       </c>
       <c r="D429">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E429" t="s">
         <v>28</v>
@@ -11430,7 +11430,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E430" t="s">
         <v>28</v>
@@ -11447,7 +11447,7 @@
         <v>27</v>
       </c>
       <c r="D431">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E431" t="s">
         <v>28</v>
@@ -11464,7 +11464,7 @@
         <v>27</v>
       </c>
       <c r="D432">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E432" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="D433">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E433" t="s">
         <v>28</v>
@@ -11498,7 +11498,7 @@
         <v>27</v>
       </c>
       <c r="D434">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E434" t="s">
         <v>28</v>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="D435">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E435" t="s">
         <v>28</v>
@@ -11532,7 +11532,7 @@
         <v>27</v>
       </c>
       <c r="D436">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E436" t="s">
         <v>28</v>
@@ -11549,7 +11549,7 @@
         <v>27</v>
       </c>
       <c r="D437">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E437" t="s">
         <v>28</v>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
       <c r="D438">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E438" t="s">
         <v>28</v>
@@ -11583,7 +11583,7 @@
         <v>27</v>
       </c>
       <c r="D439">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E439" t="s">
         <v>28</v>
@@ -11600,7 +11600,7 @@
         <v>27</v>
       </c>
       <c r="D440">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E440" t="s">
         <v>28</v>
@@ -11617,7 +11617,7 @@
         <v>27</v>
       </c>
       <c r="D441">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E441" t="s">
         <v>28</v>
@@ -11634,7 +11634,7 @@
         <v>27</v>
       </c>
       <c r="D442">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E442" t="s">
         <v>28</v>
@@ -11651,7 +11651,7 @@
         <v>27</v>
       </c>
       <c r="D443">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E443" t="s">
         <v>28</v>
@@ -11668,7 +11668,7 @@
         <v>27</v>
       </c>
       <c r="D444">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E444" t="s">
         <v>28</v>
@@ -11685,7 +11685,7 @@
         <v>27</v>
       </c>
       <c r="D445">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E445" t="s">
         <v>28</v>
@@ -11702,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D446">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E446" t="s">
         <v>28</v>
@@ -11719,7 +11719,7 @@
         <v>27</v>
       </c>
       <c r="D447">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E447" t="s">
         <v>28</v>
@@ -11753,7 +11753,7 @@
         <v>27</v>
       </c>
       <c r="D449">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E449" t="s">
         <v>28</v>
@@ -11770,7 +11770,7 @@
         <v>27</v>
       </c>
       <c r="D450">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E450" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="D451">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E451" t="s">
         <v>28</v>
@@ -11804,7 +11804,7 @@
         <v>27</v>
       </c>
       <c r="D452">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E452" t="s">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>27</v>
       </c>
       <c r="D453">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E453" t="s">
         <v>28</v>
@@ -11838,7 +11838,7 @@
         <v>27</v>
       </c>
       <c r="D454">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E454" t="s">
         <v>28</v>
@@ -11855,7 +11855,7 @@
         <v>27</v>
       </c>
       <c r="D455">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E455" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="D456">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E456" t="s">
         <v>28</v>
@@ -11889,7 +11889,7 @@
         <v>27</v>
       </c>
       <c r="D457">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E457" t="s">
         <v>28</v>
@@ -11906,7 +11906,7 @@
         <v>27</v>
       </c>
       <c r="D458">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E458" t="s">
         <v>28</v>
@@ -11923,7 +11923,7 @@
         <v>27</v>
       </c>
       <c r="D459">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E459" t="s">
         <v>28</v>
@@ -11940,7 +11940,7 @@
         <v>27</v>
       </c>
       <c r="D460">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E460" t="s">
         <v>28</v>
@@ -11957,7 +11957,7 @@
         <v>27</v>
       </c>
       <c r="D461">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E461" t="s">
         <v>28</v>
@@ -11974,7 +11974,7 @@
         <v>27</v>
       </c>
       <c r="D462">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E462" t="s">
         <v>28</v>
@@ -11991,7 +11991,7 @@
         <v>27</v>
       </c>
       <c r="D463">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E463" t="s">
         <v>28</v>
@@ -12008,7 +12008,7 @@
         <v>27</v>
       </c>
       <c r="D464">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E464" t="s">
         <v>28</v>
@@ -12025,7 +12025,7 @@
         <v>27</v>
       </c>
       <c r="D465">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E465" t="s">
         <v>28</v>
@@ -12042,7 +12042,7 @@
         <v>27</v>
       </c>
       <c r="D466">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E466" t="s">
         <v>28</v>
@@ -12059,7 +12059,7 @@
         <v>27</v>
       </c>
       <c r="D467">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E467" t="s">
         <v>28</v>
@@ -12093,7 +12093,7 @@
         <v>27</v>
       </c>
       <c r="D469">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E469" t="s">
         <v>28</v>
@@ -12110,7 +12110,7 @@
         <v>27</v>
       </c>
       <c r="D470">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E470" t="s">
         <v>28</v>
@@ -12127,7 +12127,7 @@
         <v>27</v>
       </c>
       <c r="D471">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E471" t="s">
         <v>28</v>
@@ -12144,7 +12144,7 @@
         <v>27</v>
       </c>
       <c r="D472">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E472" t="s">
         <v>28</v>
@@ -12161,7 +12161,7 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E473" t="s">
         <v>28</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="D474">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E474" t="s">
         <v>28</v>
@@ -12195,7 +12195,7 @@
         <v>27</v>
       </c>
       <c r="D475">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E475" t="s">
         <v>28</v>
@@ -12212,7 +12212,7 @@
         <v>27</v>
       </c>
       <c r="D476">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E476" t="s">
         <v>28</v>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
       <c r="D477">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E477" t="s">
         <v>28</v>
@@ -12246,7 +12246,7 @@
         <v>27</v>
       </c>
       <c r="D478">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E478" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="D479">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E479" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="D480">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E480" t="s">
         <v>28</v>
@@ -12297,7 +12297,7 @@
         <v>27</v>
       </c>
       <c r="D481">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E481" t="s">
         <v>28</v>
@@ -12314,7 +12314,7 @@
         <v>27</v>
       </c>
       <c r="D482">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E482" t="s">
         <v>28</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="D483">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E483" t="s">
         <v>28</v>
@@ -12348,7 +12348,7 @@
         <v>27</v>
       </c>
       <c r="D484">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E484" t="s">
         <v>28</v>
@@ -12365,7 +12365,7 @@
         <v>27</v>
       </c>
       <c r="D485">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E485" t="s">
         <v>28</v>
@@ -12382,7 +12382,7 @@
         <v>27</v>
       </c>
       <c r="D486">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E486" t="s">
         <v>28</v>
@@ -12399,7 +12399,7 @@
         <v>27</v>
       </c>
       <c r="D487">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E487" t="s">
         <v>28</v>
@@ -12416,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="D488">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E488" t="s">
         <v>28</v>
@@ -12433,7 +12433,7 @@
         <v>27</v>
       </c>
       <c r="D489">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E489" t="s">
         <v>28</v>
@@ -12450,7 +12450,7 @@
         <v>27</v>
       </c>
       <c r="D490">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E490" t="s">
         <v>28</v>
@@ -12467,7 +12467,7 @@
         <v>27</v>
       </c>
       <c r="D491">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E491" t="s">
         <v>28</v>
@@ -12484,7 +12484,7 @@
         <v>27</v>
       </c>
       <c r="D492">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E492" t="s">
         <v>28</v>
@@ -12501,7 +12501,7 @@
         <v>27</v>
       </c>
       <c r="D493">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E493" t="s">
         <v>28</v>
@@ -12518,7 +12518,7 @@
         <v>27</v>
       </c>
       <c r="D494">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E494" t="s">
         <v>28</v>
@@ -12535,7 +12535,7 @@
         <v>27</v>
       </c>
       <c r="D495">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E495" t="s">
         <v>28</v>
@@ -12552,7 +12552,7 @@
         <v>27</v>
       </c>
       <c r="D496">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E496" t="s">
         <v>28</v>
@@ -12586,7 +12586,7 @@
         <v>27</v>
       </c>
       <c r="D498">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E498" t="s">
         <v>28</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D499">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E499" t="s">
         <v>28</v>
@@ -12620,7 +12620,7 @@
         <v>27</v>
       </c>
       <c r="D500">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E500" t="s">
         <v>28</v>
@@ -12637,7 +12637,7 @@
         <v>27</v>
       </c>
       <c r="D501">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E501" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="D502">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E502" t="s">
         <v>28</v>
@@ -12671,7 +12671,7 @@
         <v>27</v>
       </c>
       <c r="D503">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E503" t="s">
         <v>28</v>
@@ -12688,7 +12688,7 @@
         <v>27</v>
       </c>
       <c r="D504">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E504" t="s">
         <v>28</v>
@@ -12705,7 +12705,7 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E505" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="D506">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E506" t="s">
         <v>28</v>
@@ -12739,7 +12739,7 @@
         <v>27</v>
       </c>
       <c r="D507">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E507" t="s">
         <v>28</v>
@@ -12756,7 +12756,7 @@
         <v>27</v>
       </c>
       <c r="D508">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E508" t="s">
         <v>28</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="D509">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E509" t="s">
         <v>28</v>
@@ -12790,7 +12790,7 @@
         <v>27</v>
       </c>
       <c r="D510">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E510" t="s">
         <v>28</v>
@@ -12807,7 +12807,7 @@
         <v>27</v>
       </c>
       <c r="D511">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E511" t="s">
         <v>28</v>
@@ -12824,7 +12824,7 @@
         <v>27</v>
       </c>
       <c r="D512">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E512" t="s">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27</v>
       </c>
       <c r="D513">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E513" t="s">
         <v>28</v>
@@ -12858,7 +12858,7 @@
         <v>27</v>
       </c>
       <c r="D514">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E514" t="s">
         <v>28</v>
@@ -12875,7 +12875,7 @@
         <v>27</v>
       </c>
       <c r="D515">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E515" t="s">
         <v>28</v>
@@ -12892,7 +12892,7 @@
         <v>27</v>
       </c>
       <c r="D516">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E516" t="s">
         <v>28</v>
@@ -12909,7 +12909,7 @@
         <v>27</v>
       </c>
       <c r="D517">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E517" t="s">
         <v>28</v>
@@ -12926,7 +12926,7 @@
         <v>27</v>
       </c>
       <c r="D518">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E518" t="s">
         <v>28</v>
@@ -12943,7 +12943,7 @@
         <v>27</v>
       </c>
       <c r="D519">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E519" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="D520">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E520" t="s">
         <v>28</v>
@@ -12977,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="D521">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E521" t="s">
         <v>28</v>
@@ -13011,7 +13011,7 @@
         <v>27</v>
       </c>
       <c r="D523">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E523" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="D525">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E525" t="s">
         <v>28</v>
@@ -13062,7 +13062,7 @@
         <v>27</v>
       </c>
       <c r="D526">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E526" t="s">
         <v>28</v>
@@ -13096,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="D528">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E528" t="s">
         <v>28</v>
@@ -13113,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="D529">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
@@ -13130,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -13147,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="D531">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
@@ -13164,7 +13164,7 @@
         <v>27</v>
       </c>
       <c r="D532">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E532" t="s">
         <v>28</v>
@@ -13181,7 +13181,7 @@
         <v>27</v>
       </c>
       <c r="D533">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E533" t="s">
         <v>28</v>
@@ -13198,7 +13198,7 @@
         <v>27</v>
       </c>
       <c r="D534">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E534" t="s">
         <v>28</v>
@@ -13215,7 +13215,7 @@
         <v>27</v>
       </c>
       <c r="D535">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E535" t="s">
         <v>28</v>
@@ -13232,7 +13232,7 @@
         <v>27</v>
       </c>
       <c r="D536">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E536" t="s">
         <v>28</v>
@@ -13249,7 +13249,7 @@
         <v>27</v>
       </c>
       <c r="D537">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E537" t="s">
         <v>28</v>
@@ -13266,7 +13266,7 @@
         <v>27</v>
       </c>
       <c r="D538">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E538" t="s">
         <v>28</v>
@@ -13283,7 +13283,7 @@
         <v>27</v>
       </c>
       <c r="D539">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E539" t="s">
         <v>28</v>
@@ -13300,7 +13300,7 @@
         <v>27</v>
       </c>
       <c r="D540">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E540" t="s">
         <v>28</v>
@@ -13317,7 +13317,7 @@
         <v>27</v>
       </c>
       <c r="D541">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E541" t="s">
         <v>28</v>
@@ -13334,7 +13334,7 @@
         <v>27</v>
       </c>
       <c r="D542">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E542" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="D543">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E543" t="s">
         <v>28</v>
@@ -13368,7 +13368,7 @@
         <v>27</v>
       </c>
       <c r="D544">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E544" t="s">
         <v>28</v>
@@ -13385,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="D545">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
@@ -13402,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="D546">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
@@ -13419,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="D547">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E547" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="D548">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E548" t="s">
         <v>28</v>
@@ -13453,7 +13453,7 @@
         <v>27</v>
       </c>
       <c r="D549">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E549" t="s">
         <v>28</v>
@@ -13470,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="D550">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E550" t="s">
         <v>28</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="D552">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -13521,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="D553">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E553" t="s">
         <v>28</v>
@@ -13538,7 +13538,7 @@
         <v>27</v>
       </c>
       <c r="D554">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E554" t="s">
         <v>28</v>
@@ -13555,7 +13555,7 @@
         <v>27</v>
       </c>
       <c r="D555">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E555" t="s">
         <v>28</v>
@@ -13572,7 +13572,7 @@
         <v>27</v>
       </c>
       <c r="D556">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E556" t="s">
         <v>28</v>
@@ -13589,7 +13589,7 @@
         <v>27</v>
       </c>
       <c r="D557">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E557" t="s">
         <v>28</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="D558">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E558" t="s">
         <v>28</v>
@@ -13623,7 +13623,7 @@
         <v>27</v>
       </c>
       <c r="D559">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -13640,7 +13640,7 @@
         <v>27</v>
       </c>
       <c r="D560">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
@@ -13657,7 +13657,7 @@
         <v>27</v>
       </c>
       <c r="D561">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E561" t="s">
         <v>28</v>
@@ -13691,7 +13691,7 @@
         <v>27</v>
       </c>
       <c r="D563">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E563" t="s">
         <v>28</v>
@@ -13708,7 +13708,7 @@
         <v>27</v>
       </c>
       <c r="D564">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E564" t="s">
         <v>28</v>
@@ -13725,7 +13725,7 @@
         <v>27</v>
       </c>
       <c r="D565">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E565" t="s">
         <v>28</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="D566">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E566" t="s">
         <v>28</v>
@@ -13759,7 +13759,7 @@
         <v>27</v>
       </c>
       <c r="D567">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E567" t="s">
         <v>28</v>
@@ -13776,7 +13776,7 @@
         <v>27</v>
       </c>
       <c r="D568">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E568" t="s">
         <v>28</v>
@@ -13793,7 +13793,7 @@
         <v>27</v>
       </c>
       <c r="D569">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
@@ -13810,7 +13810,7 @@
         <v>27</v>
       </c>
       <c r="D570">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E570" t="s">
         <v>28</v>
@@ -13844,7 +13844,7 @@
         <v>27</v>
       </c>
       <c r="D572">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E572" t="s">
         <v>28</v>
@@ -13861,7 +13861,7 @@
         <v>27</v>
       </c>
       <c r="D573">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E573" t="s">
         <v>28</v>
@@ -13878,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="D574">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E574" t="s">
         <v>28</v>
@@ -13895,7 +13895,7 @@
         <v>27</v>
       </c>
       <c r="D575">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E575" t="s">
         <v>28</v>
@@ -13912,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="D576">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E576" t="s">
         <v>28</v>
@@ -13946,7 +13946,7 @@
         <v>27</v>
       </c>
       <c r="D578">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E578" t="s">
         <v>28</v>
@@ -13980,7 +13980,7 @@
         <v>27</v>
       </c>
       <c r="D580">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E580" t="s">
         <v>28</v>
@@ -13997,7 +13997,7 @@
         <v>27</v>
       </c>
       <c r="D581">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E581" t="s">
         <v>28</v>
@@ -14014,7 +14014,7 @@
         <v>27</v>
       </c>
       <c r="D582">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E582" t="s">
         <v>28</v>
@@ -14031,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="D583">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E583" t="s">
         <v>28</v>
@@ -14048,7 +14048,7 @@
         <v>27</v>
       </c>
       <c r="D584">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E584" t="s">
         <v>28</v>
@@ -14065,7 +14065,7 @@
         <v>27</v>
       </c>
       <c r="D585">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E585" t="s">
         <v>28</v>
@@ -14082,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="D586">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E586" t="s">
         <v>28</v>
@@ -14099,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="D587">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E587" t="s">
         <v>28</v>
@@ -14116,7 +14116,7 @@
         <v>27</v>
       </c>
       <c r="D588">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E588" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="D589">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
@@ -14150,7 +14150,7 @@
         <v>27</v>
       </c>
       <c r="D590">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
@@ -14167,7 +14167,7 @@
         <v>27</v>
       </c>
       <c r="D591">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E591" t="s">
         <v>28</v>
@@ -14184,7 +14184,7 @@
         <v>27</v>
       </c>
       <c r="D592">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E592" t="s">
         <v>28</v>
@@ -14201,7 +14201,7 @@
         <v>27</v>
       </c>
       <c r="D593">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E593" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="D594">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E594" t="s">
         <v>28</v>
@@ -14235,7 +14235,7 @@
         <v>27</v>
       </c>
       <c r="D595">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E595" t="s">
         <v>28</v>
@@ -14252,7 +14252,7 @@
         <v>27</v>
       </c>
       <c r="D596">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
@@ -14269,7 +14269,7 @@
         <v>27</v>
       </c>
       <c r="D597">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
@@ -14286,7 +14286,7 @@
         <v>27</v>
       </c>
       <c r="D598">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
@@ -14303,7 +14303,7 @@
         <v>27</v>
       </c>
       <c r="D599">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="D600">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
@@ -14337,7 +14337,7 @@
         <v>27</v>
       </c>
       <c r="D601">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
@@ -14354,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="D602">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
@@ -14371,7 +14371,7 @@
         <v>27</v>
       </c>
       <c r="D603">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
@@ -14388,7 +14388,7 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
@@ -14405,7 +14405,7 @@
         <v>27</v>
       </c>
       <c r="D605">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E605" t="s">
         <v>28</v>
@@ -14422,7 +14422,7 @@
         <v>27</v>
       </c>
       <c r="D606">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E606" t="s">
         <v>28</v>
@@ -14439,7 +14439,7 @@
         <v>27</v>
       </c>
       <c r="D607">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E607" t="s">
         <v>28</v>
@@ -14456,7 +14456,7 @@
         <v>27</v>
       </c>
       <c r="D608">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
@@ -14473,7 +14473,7 @@
         <v>27</v>
       </c>
       <c r="D609">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E609" t="s">
         <v>28</v>
@@ -14490,7 +14490,7 @@
         <v>27</v>
       </c>
       <c r="D610">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E610" t="s">
         <v>28</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="D612">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E612" t="s">
         <v>28</v>
@@ -14558,7 +14558,7 @@
         <v>27</v>
       </c>
       <c r="D614">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E614" t="s">
         <v>28</v>
@@ -14575,7 +14575,7 @@
         <v>27</v>
       </c>
       <c r="D615">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E615" t="s">
         <v>28</v>
@@ -14592,7 +14592,7 @@
         <v>27</v>
       </c>
       <c r="D616">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E616" t="s">
         <v>28</v>
@@ -14626,7 +14626,7 @@
         <v>27</v>
       </c>
       <c r="D618">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E618" t="s">
         <v>28</v>
@@ -14643,7 +14643,7 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E619" t="s">
         <v>28</v>
@@ -14677,7 +14677,7 @@
         <v>27</v>
       </c>
       <c r="D621">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E621" t="s">
         <v>28</v>
@@ -14711,7 +14711,7 @@
         <v>27</v>
       </c>
       <c r="D623">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E623" t="s">
         <v>28</v>
@@ -14728,7 +14728,7 @@
         <v>27</v>
       </c>
       <c r="D624">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E624" t="s">
         <v>28</v>
@@ -14745,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="D625">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E625" t="s">
         <v>28</v>
@@ -14762,7 +14762,7 @@
         <v>27</v>
       </c>
       <c r="D626">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E626" t="s">
         <v>28</v>
@@ -14779,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="D627">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E627" t="s">
         <v>28</v>
@@ -14796,7 +14796,7 @@
         <v>27</v>
       </c>
       <c r="D628">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E628" t="s">
         <v>28</v>
@@ -14813,7 +14813,7 @@
         <v>27</v>
       </c>
       <c r="D629">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E629" t="s">
         <v>28</v>
@@ -14830,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="D630">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E630" t="s">
         <v>28</v>
@@ -14847,7 +14847,7 @@
         <v>27</v>
       </c>
       <c r="D631">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E631" t="s">
         <v>28</v>
@@ -14864,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D632">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E632" t="s">
         <v>28</v>
@@ -14881,7 +14881,7 @@
         <v>27</v>
       </c>
       <c r="D633">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E633" t="s">
         <v>28</v>
@@ -14898,7 +14898,7 @@
         <v>27</v>
       </c>
       <c r="D634">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E634" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="D635">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E635" t="s">
         <v>28</v>
@@ -14932,7 +14932,7 @@
         <v>27</v>
       </c>
       <c r="D636">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E636" t="s">
         <v>28</v>
@@ -14949,7 +14949,7 @@
         <v>27</v>
       </c>
       <c r="D637">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E637" t="s">
         <v>28</v>
@@ -14966,7 +14966,7 @@
         <v>27</v>
       </c>
       <c r="D638">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E638" t="s">
         <v>28</v>
@@ -14983,7 +14983,7 @@
         <v>27</v>
       </c>
       <c r="D639">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E639" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E640" t="s">
         <v>28</v>
@@ -15017,7 +15017,7 @@
         <v>27</v>
       </c>
       <c r="D641">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E641" t="s">
         <v>28</v>
@@ -15034,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="D642">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E642" t="s">
         <v>28</v>
@@ -15051,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="D643">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E643" t="s">
         <v>28</v>
@@ -15068,7 +15068,7 @@
         <v>27</v>
       </c>
       <c r="D644">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E644" t="s">
         <v>28</v>
@@ -15085,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="D645">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E645" t="s">
         <v>28</v>
@@ -15102,7 +15102,7 @@
         <v>27</v>
       </c>
       <c r="D646">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E646" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>27</v>
       </c>
       <c r="D647">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E647" t="s">
         <v>28</v>
@@ -15136,7 +15136,7 @@
         <v>27</v>
       </c>
       <c r="D648">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E648" t="s">
         <v>28</v>
@@ -15153,7 +15153,7 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E649" t="s">
         <v>28</v>
@@ -15170,7 +15170,7 @@
         <v>27</v>
       </c>
       <c r="D650">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E650" t="s">
         <v>28</v>
@@ -15187,7 +15187,7 @@
         <v>27</v>
       </c>
       <c r="D651">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E651" t="s">
         <v>28</v>
@@ -15204,7 +15204,7 @@
         <v>27</v>
       </c>
       <c r="D652">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E652" t="s">
         <v>28</v>
@@ -15221,7 +15221,7 @@
         <v>27</v>
       </c>
       <c r="D653">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E653" t="s">
         <v>28</v>
@@ -15238,7 +15238,7 @@
         <v>27</v>
       </c>
       <c r="D654">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E654" t="s">
         <v>28</v>
@@ -15255,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="D655">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E655" t="s">
         <v>28</v>
@@ -15272,7 +15272,7 @@
         <v>27</v>
       </c>
       <c r="D656">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
@@ -15289,7 +15289,7 @@
         <v>27</v>
       </c>
       <c r="D657">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E657" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
@@ -15323,7 +15323,7 @@
         <v>27</v>
       </c>
       <c r="D659">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E659" t="s">
         <v>28</v>
@@ -15340,7 +15340,7 @@
         <v>27</v>
       </c>
       <c r="D660">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E660" t="s">
         <v>28</v>
@@ -15357,7 +15357,7 @@
         <v>27</v>
       </c>
       <c r="D661">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E661" t="s">
         <v>28</v>
@@ -15374,7 +15374,7 @@
         <v>27</v>
       </c>
       <c r="D662">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E662" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="D663">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E663" t="s">
         <v>28</v>
@@ -15408,7 +15408,7 @@
         <v>27</v>
       </c>
       <c r="D664">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E664" t="s">
         <v>28</v>
@@ -15425,7 +15425,7 @@
         <v>27</v>
       </c>
       <c r="D665">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E665" t="s">
         <v>28</v>
@@ -15442,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="D666">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E666" t="s">
         <v>28</v>
@@ -15459,7 +15459,7 @@
         <v>27</v>
       </c>
       <c r="D667">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E667" t="s">
         <v>28</v>
@@ -15493,7 +15493,7 @@
         <v>27</v>
       </c>
       <c r="D669">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E669" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>27</v>
       </c>
       <c r="D670">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E670" t="s">
         <v>28</v>
@@ -15527,7 +15527,7 @@
         <v>27</v>
       </c>
       <c r="D671">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E671" t="s">
         <v>28</v>
@@ -15561,7 +15561,7 @@
         <v>27</v>
       </c>
       <c r="D673">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E673" t="s">
         <v>28</v>
@@ -15578,7 +15578,7 @@
         <v>27</v>
       </c>
       <c r="D674">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E674" t="s">
         <v>28</v>
@@ -15612,7 +15612,7 @@
         <v>27</v>
       </c>
       <c r="D676">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E676" t="s">
         <v>28</v>
@@ -15629,7 +15629,7 @@
         <v>27</v>
       </c>
       <c r="D677">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E677" t="s">
         <v>28</v>
@@ -15646,7 +15646,7 @@
         <v>27</v>
       </c>
       <c r="D678">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E678" t="s">
         <v>28</v>
@@ -15663,7 +15663,7 @@
         <v>27</v>
       </c>
       <c r="D679">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E679" t="s">
         <v>28</v>
@@ -15680,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="D680">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E680" t="s">
         <v>28</v>
@@ -15697,7 +15697,7 @@
         <v>27</v>
       </c>
       <c r="D681">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E681" t="s">
         <v>28</v>
@@ -15714,7 +15714,7 @@
         <v>27</v>
       </c>
       <c r="D682">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E682" t="s">
         <v>28</v>
@@ -15731,7 +15731,7 @@
         <v>27</v>
       </c>
       <c r="D683">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E683" t="s">
         <v>28</v>
@@ -15748,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="D684">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E684" t="s">
         <v>28</v>
@@ -15765,7 +15765,7 @@
         <v>27</v>
       </c>
       <c r="D685">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E685" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="D686">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E686" t="s">
         <v>28</v>
@@ -15799,7 +15799,7 @@
         <v>27</v>
       </c>
       <c r="D687">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E687" t="s">
         <v>28</v>
@@ -15816,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="D688">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E688" t="s">
         <v>28</v>
@@ -15833,7 +15833,7 @@
         <v>27</v>
       </c>
       <c r="D689">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E689" t="s">
         <v>28</v>
@@ -15850,7 +15850,7 @@
         <v>27</v>
       </c>
       <c r="D690">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E690" t="s">
         <v>28</v>
@@ -15867,7 +15867,7 @@
         <v>27</v>
       </c>
       <c r="D691">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E691" t="s">
         <v>28</v>
@@ -15884,7 +15884,7 @@
         <v>27</v>
       </c>
       <c r="D692">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E692" t="s">
         <v>28</v>
@@ -15901,7 +15901,7 @@
         <v>27</v>
       </c>
       <c r="D693">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E693" t="s">
         <v>28</v>
@@ -15918,7 +15918,7 @@
         <v>27</v>
       </c>
       <c r="D694">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E694" t="s">
         <v>28</v>
@@ -15935,7 +15935,7 @@
         <v>27</v>
       </c>
       <c r="D695">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E695" t="s">
         <v>28</v>
@@ -15952,7 +15952,7 @@
         <v>27</v>
       </c>
       <c r="D696">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E696" t="s">
         <v>28</v>
@@ -15969,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="D697">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E697" t="s">
         <v>28</v>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
       <c r="D698">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E698" t="s">
         <v>28</v>
@@ -16003,7 +16003,7 @@
         <v>27</v>
       </c>
       <c r="D699">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E699" t="s">
         <v>28</v>
@@ -16020,7 +16020,7 @@
         <v>27</v>
       </c>
       <c r="D700">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E700" t="s">
         <v>28</v>
@@ -16054,7 +16054,7 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E702" t="s">
         <v>28</v>
@@ -16071,7 +16071,7 @@
         <v>27</v>
       </c>
       <c r="D703">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E703" t="s">
         <v>28</v>
@@ -16088,7 +16088,7 @@
         <v>27</v>
       </c>
       <c r="D704">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E704" t="s">
         <v>28</v>
@@ -16105,7 +16105,7 @@
         <v>27</v>
       </c>
       <c r="D705">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E705" t="s">
         <v>28</v>
@@ -16122,7 +16122,7 @@
         <v>27</v>
       </c>
       <c r="D706">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E706" t="s">
         <v>28</v>
@@ -16139,7 +16139,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E707" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="D709">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E709" t="s">
         <v>28</v>
@@ -16190,7 +16190,7 @@
         <v>27</v>
       </c>
       <c r="D710">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E710" t="s">
         <v>28</v>
@@ -16207,7 +16207,7 @@
         <v>27</v>
       </c>
       <c r="D711">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E711" t="s">
         <v>28</v>
@@ -16224,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="D712">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E712" t="s">
         <v>28</v>
@@ -16241,7 +16241,7 @@
         <v>27</v>
       </c>
       <c r="D713">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E713" t="s">
         <v>28</v>
@@ -16258,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="D714">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E714" t="s">
         <v>28</v>
@@ -16275,7 +16275,7 @@
         <v>27</v>
       </c>
       <c r="D715">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E715" t="s">
         <v>28</v>
@@ -16292,7 +16292,7 @@
         <v>27</v>
       </c>
       <c r="D716">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E716" t="s">
         <v>28</v>
@@ -16309,7 +16309,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E717" t="s">
         <v>28</v>
@@ -16326,7 +16326,7 @@
         <v>27</v>
       </c>
       <c r="D718">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E718" t="s">
         <v>28</v>
@@ -16343,7 +16343,7 @@
         <v>27</v>
       </c>
       <c r="D719">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E719" t="s">
         <v>28</v>
@@ -16360,7 +16360,7 @@
         <v>27</v>
       </c>
       <c r="D720">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E720" t="s">
         <v>28</v>
@@ -16377,7 +16377,7 @@
         <v>27</v>
       </c>
       <c r="D721">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E721" t="s">
         <v>28</v>
@@ -16394,7 +16394,7 @@
         <v>27</v>
       </c>
       <c r="D722">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E722" t="s">
         <v>28</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="D723">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E723" t="s">
         <v>28</v>
@@ -16428,7 +16428,7 @@
         <v>27</v>
       </c>
       <c r="D724">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E724" t="s">
         <v>28</v>
@@ -16445,7 +16445,7 @@
         <v>27</v>
       </c>
       <c r="D725">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E725" t="s">
         <v>28</v>
@@ -16462,7 +16462,7 @@
         <v>27</v>
       </c>
       <c r="D726">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E726" t="s">
         <v>28</v>
@@ -16479,7 +16479,7 @@
         <v>27</v>
       </c>
       <c r="D727">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E727" t="s">
         <v>28</v>
@@ -16496,7 +16496,7 @@
         <v>27</v>
       </c>
       <c r="D728">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E728" t="s">
         <v>28</v>
@@ -16513,7 +16513,7 @@
         <v>27</v>
       </c>
       <c r="D729">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E729" t="s">
         <v>28</v>
@@ -16530,7 +16530,7 @@
         <v>27</v>
       </c>
       <c r="D730">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E730" t="s">
         <v>28</v>
@@ -16547,7 +16547,7 @@
         <v>27</v>
       </c>
       <c r="D731">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E731" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="D732">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E732" t="s">
         <v>28</v>
@@ -16581,7 +16581,7 @@
         <v>27</v>
       </c>
       <c r="D733">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E733" t="s">
         <v>28</v>
@@ -16598,7 +16598,7 @@
         <v>27</v>
       </c>
       <c r="D734">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E734" t="s">
         <v>28</v>
@@ -16632,7 +16632,7 @@
         <v>27</v>
       </c>
       <c r="D736">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E736" t="s">
         <v>28</v>
@@ -16649,7 +16649,7 @@
         <v>27</v>
       </c>
       <c r="D737">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E737" t="s">
         <v>28</v>
@@ -16666,7 +16666,7 @@
         <v>27</v>
       </c>
       <c r="D738">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E738" t="s">
         <v>28</v>
@@ -16683,7 +16683,7 @@
         <v>27</v>
       </c>
       <c r="D739">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E739" t="s">
         <v>28</v>
@@ -16717,7 +16717,7 @@
         <v>27</v>
       </c>
       <c r="D741">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E741" t="s">
         <v>28</v>
@@ -16734,7 +16734,7 @@
         <v>27</v>
       </c>
       <c r="D742">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E742" t="s">
         <v>28</v>
@@ -16751,7 +16751,7 @@
         <v>27</v>
       </c>
       <c r="D743">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E743" t="s">
         <v>28</v>
@@ -16768,7 +16768,7 @@
         <v>27</v>
       </c>
       <c r="D744">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E744" t="s">
         <v>28</v>
@@ -16785,7 +16785,7 @@
         <v>27</v>
       </c>
       <c r="D745">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E745" t="s">
         <v>28</v>
@@ -16802,7 +16802,7 @@
         <v>27</v>
       </c>
       <c r="D746">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E746" t="s">
         <v>28</v>
@@ -16836,7 +16836,7 @@
         <v>27</v>
       </c>
       <c r="D748">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E748" t="s">
         <v>28</v>
@@ -16853,7 +16853,7 @@
         <v>27</v>
       </c>
       <c r="D749">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E749" t="s">
         <v>28</v>
@@ -16870,7 +16870,7 @@
         <v>27</v>
       </c>
       <c r="D750">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E750" t="s">
         <v>28</v>
@@ -16887,7 +16887,7 @@
         <v>27</v>
       </c>
       <c r="D751">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E751" t="s">
         <v>28</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="D752">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E752" t="s">
         <v>28</v>
@@ -16921,7 +16921,7 @@
         <v>27</v>
       </c>
       <c r="D753">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E753" t="s">
         <v>28</v>
@@ -16938,7 +16938,7 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E754" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="D755">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E755" t="s">
         <v>28</v>
@@ -16972,7 +16972,7 @@
         <v>27</v>
       </c>
       <c r="D756">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E756" t="s">
         <v>28</v>
@@ -16989,7 +16989,7 @@
         <v>27</v>
       </c>
       <c r="D757">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E757" t="s">
         <v>28</v>
@@ -17006,7 +17006,7 @@
         <v>27</v>
       </c>
       <c r="D758">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E758" t="s">
         <v>28</v>
@@ -17023,7 +17023,7 @@
         <v>27</v>
       </c>
       <c r="D759">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E759" t="s">
         <v>28</v>
@@ -17057,7 +17057,7 @@
         <v>27</v>
       </c>
       <c r="D761">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E761" t="s">
         <v>28</v>
@@ -17074,7 +17074,7 @@
         <v>27</v>
       </c>
       <c r="D762">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E762" t="s">
         <v>28</v>
@@ -17091,7 +17091,7 @@
         <v>27</v>
       </c>
       <c r="D763">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E763" t="s">
         <v>28</v>
@@ -17108,7 +17108,7 @@
         <v>27</v>
       </c>
       <c r="D764">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E764" t="s">
         <v>28</v>
@@ -17125,7 +17125,7 @@
         <v>27</v>
       </c>
       <c r="D765">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E765" t="s">
         <v>28</v>
@@ -17142,7 +17142,7 @@
         <v>27</v>
       </c>
       <c r="D766">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E766" t="s">
         <v>28</v>
@@ -17159,7 +17159,7 @@
         <v>27</v>
       </c>
       <c r="D767">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E767" t="s">
         <v>28</v>
@@ -17176,7 +17176,7 @@
         <v>27</v>
       </c>
       <c r="D768">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E768" t="s">
         <v>28</v>
@@ -17193,7 +17193,7 @@
         <v>27</v>
       </c>
       <c r="D769">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E769" t="s">
         <v>28</v>
@@ -17210,7 +17210,7 @@
         <v>27</v>
       </c>
       <c r="D770">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E770" t="s">
         <v>28</v>
@@ -17227,7 +17227,7 @@
         <v>27</v>
       </c>
       <c r="D771">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E771" t="s">
         <v>28</v>
@@ -17244,7 +17244,7 @@
         <v>27</v>
       </c>
       <c r="D772">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E772" t="s">
         <v>28</v>
@@ -17261,7 +17261,7 @@
         <v>27</v>
       </c>
       <c r="D773">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E773" t="s">
         <v>28</v>
@@ -17278,7 +17278,7 @@
         <v>27</v>
       </c>
       <c r="D774">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E774" t="s">
         <v>28</v>
@@ -17295,7 +17295,7 @@
         <v>27</v>
       </c>
       <c r="D775">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E775" t="s">
         <v>28</v>
@@ -17312,7 +17312,7 @@
         <v>27</v>
       </c>
       <c r="D776">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E776" t="s">
         <v>28</v>
@@ -17329,7 +17329,7 @@
         <v>27</v>
       </c>
       <c r="D777">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E777" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="D778">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E778" t="s">
         <v>28</v>
@@ -17363,7 +17363,7 @@
         <v>27</v>
       </c>
       <c r="D779">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E779" t="s">
         <v>28</v>
@@ -17380,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="D780">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E780" t="s">
         <v>28</v>
@@ -17397,7 +17397,7 @@
         <v>27</v>
       </c>
       <c r="D781">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E781" t="s">
         <v>28</v>
@@ -17414,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="D782">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E782" t="s">
         <v>28</v>
@@ -17431,7 +17431,7 @@
         <v>27</v>
       </c>
       <c r="D783">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E783" t="s">
         <v>28</v>
@@ -17448,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D784">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E784" t="s">
         <v>28</v>
@@ -17465,7 +17465,7 @@
         <v>27</v>
       </c>
       <c r="D785">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E785" t="s">
         <v>28</v>
@@ -17482,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="D786">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E786" t="s">
         <v>28</v>
@@ -17499,7 +17499,7 @@
         <v>27</v>
       </c>
       <c r="D787">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E787" t="s">
         <v>28</v>
@@ -17516,7 +17516,7 @@
         <v>27</v>
       </c>
       <c r="D788">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E788" t="s">
         <v>28</v>
@@ -17533,7 +17533,7 @@
         <v>27</v>
       </c>
       <c r="D789">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E789" t="s">
         <v>28</v>
@@ -17550,7 +17550,7 @@
         <v>27</v>
       </c>
       <c r="D790">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E790" t="s">
         <v>28</v>
@@ -17584,7 +17584,7 @@
         <v>27</v>
       </c>
       <c r="D792">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E792" t="s">
         <v>28</v>
@@ -17601,7 +17601,7 @@
         <v>27</v>
       </c>
       <c r="D793">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E793" t="s">
         <v>28</v>
@@ -17618,7 +17618,7 @@
         <v>27</v>
       </c>
       <c r="D794">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E794" t="s">
         <v>28</v>
@@ -17635,7 +17635,7 @@
         <v>27</v>
       </c>
       <c r="D795">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E795" t="s">
         <v>28</v>
@@ -17652,7 +17652,7 @@
         <v>27</v>
       </c>
       <c r="D796">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E796" t="s">
         <v>28</v>
@@ -17669,7 +17669,7 @@
         <v>27</v>
       </c>
       <c r="D797">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E797" t="s">
         <v>28</v>
@@ -17686,7 +17686,7 @@
         <v>27</v>
       </c>
       <c r="D798">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E798" t="s">
         <v>28</v>
@@ -17703,7 +17703,7 @@
         <v>27</v>
       </c>
       <c r="D799">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E799" t="s">
         <v>28</v>
@@ -17720,7 +17720,7 @@
         <v>27</v>
       </c>
       <c r="D800">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E800" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="D801">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E801" t="s">
         <v>28</v>
@@ -17754,7 +17754,7 @@
         <v>27</v>
       </c>
       <c r="D802">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E802" t="s">
         <v>28</v>
@@ -17771,7 +17771,7 @@
         <v>27</v>
       </c>
       <c r="D803">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E803" t="s">
         <v>28</v>
@@ -17805,7 +17805,7 @@
         <v>27</v>
       </c>
       <c r="D805">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E805" t="s">
         <v>28</v>
@@ -17822,7 +17822,7 @@
         <v>27</v>
       </c>
       <c r="D806">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E806" t="s">
         <v>28</v>
@@ -17839,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="D807">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E807" t="s">
         <v>28</v>
@@ -17856,7 +17856,7 @@
         <v>27</v>
       </c>
       <c r="D808">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E808" t="s">
         <v>28</v>
@@ -17873,7 +17873,7 @@
         <v>27</v>
       </c>
       <c r="D809">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E809" t="s">
         <v>28</v>
@@ -17890,7 +17890,7 @@
         <v>27</v>
       </c>
       <c r="D810">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E810" t="s">
         <v>28</v>
@@ -17907,7 +17907,7 @@
         <v>27</v>
       </c>
       <c r="D811">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E811" t="s">
         <v>28</v>
@@ -17941,7 +17941,7 @@
         <v>27</v>
       </c>
       <c r="D813">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E813" t="s">
         <v>28</v>
@@ -17958,7 +17958,7 @@
         <v>27</v>
       </c>
       <c r="D814">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E814" t="s">
         <v>28</v>
@@ -17975,7 +17975,7 @@
         <v>27</v>
       </c>
       <c r="D815">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E815" t="s">
         <v>28</v>
@@ -17992,7 +17992,7 @@
         <v>27</v>
       </c>
       <c r="D816">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E816" t="s">
         <v>28</v>
@@ -18009,7 +18009,7 @@
         <v>27</v>
       </c>
       <c r="D817">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E817" t="s">
         <v>28</v>
@@ -18026,7 +18026,7 @@
         <v>27</v>
       </c>
       <c r="D818">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E818" t="s">
         <v>28</v>
@@ -18043,7 +18043,7 @@
         <v>27</v>
       </c>
       <c r="D819">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E819" t="s">
         <v>28</v>
@@ -18060,7 +18060,7 @@
         <v>27</v>
       </c>
       <c r="D820">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E820" t="s">
         <v>28</v>
@@ -18077,7 +18077,7 @@
         <v>27</v>
       </c>
       <c r="D821">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E821" t="s">
         <v>28</v>
@@ -18094,7 +18094,7 @@
         <v>27</v>
       </c>
       <c r="D822">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E822" t="s">
         <v>28</v>
@@ -18111,7 +18111,7 @@
         <v>27</v>
       </c>
       <c r="D823">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E823" t="s">
         <v>28</v>
@@ -18128,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="D824">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E824" t="s">
         <v>28</v>
@@ -18162,7 +18162,7 @@
         <v>27</v>
       </c>
       <c r="D826">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E826" t="s">
         <v>28</v>
@@ -18179,7 +18179,7 @@
         <v>27</v>
       </c>
       <c r="D827">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E827" t="s">
         <v>28</v>
@@ -18196,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="D828">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E828" t="s">
         <v>28</v>
@@ -18230,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="D830">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E830" t="s">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E831" t="s">
         <v>28</v>
@@ -18264,7 +18264,7 @@
         <v>27</v>
       </c>
       <c r="D832">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E832" t="s">
         <v>28</v>
@@ -18281,7 +18281,7 @@
         <v>27</v>
       </c>
       <c r="D833">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E833" t="s">
         <v>28</v>
@@ -18298,7 +18298,7 @@
         <v>27</v>
       </c>
       <c r="D834">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E834" t="s">
         <v>28</v>
@@ -18315,7 +18315,7 @@
         <v>27</v>
       </c>
       <c r="D835">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E835" t="s">
         <v>28</v>
@@ -18332,7 +18332,7 @@
         <v>27</v>
       </c>
       <c r="D836">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E836" t="s">
         <v>28</v>
@@ -18349,7 +18349,7 @@
         <v>27</v>
       </c>
       <c r="D837">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E837" t="s">
         <v>28</v>
@@ -18366,7 +18366,7 @@
         <v>27</v>
       </c>
       <c r="D838">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E838" t="s">
         <v>28</v>
@@ -18383,7 +18383,7 @@
         <v>27</v>
       </c>
       <c r="D839">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E839" t="s">
         <v>28</v>
@@ -18400,7 +18400,7 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E840" t="s">
         <v>28</v>
@@ -18417,7 +18417,7 @@
         <v>27</v>
       </c>
       <c r="D841">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E841" t="s">
         <v>28</v>
@@ -18434,7 +18434,7 @@
         <v>27</v>
       </c>
       <c r="D842">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E842" t="s">
         <v>28</v>
@@ -18451,7 +18451,7 @@
         <v>27</v>
       </c>
       <c r="D843">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E843" t="s">
         <v>28</v>
@@ -18468,7 +18468,7 @@
         <v>27</v>
       </c>
       <c r="D844">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E844" t="s">
         <v>28</v>
@@ -18485,7 +18485,7 @@
         <v>27</v>
       </c>
       <c r="D845">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E845" t="s">
         <v>28</v>
@@ -18502,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="D846">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E846" t="s">
         <v>28</v>
@@ -18519,7 +18519,7 @@
         <v>27</v>
       </c>
       <c r="D847">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E847" t="s">
         <v>28</v>
@@ -18536,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="D848">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E848" t="s">
         <v>28</v>
@@ -18553,7 +18553,7 @@
         <v>27</v>
       </c>
       <c r="D849">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E849" t="s">
         <v>28</v>
@@ -18570,7 +18570,7 @@
         <v>27</v>
       </c>
       <c r="D850">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E850" t="s">
         <v>28</v>
@@ -18587,7 +18587,7 @@
         <v>27</v>
       </c>
       <c r="D851">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E851" t="s">
         <v>28</v>
@@ -18604,7 +18604,7 @@
         <v>27</v>
       </c>
       <c r="D852">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E852" t="s">
         <v>28</v>
@@ -18621,7 +18621,7 @@
         <v>27</v>
       </c>
       <c r="D853">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E853" t="s">
         <v>28</v>
@@ -18638,7 +18638,7 @@
         <v>27</v>
       </c>
       <c r="D854">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E854" t="s">
         <v>28</v>
@@ -18655,7 +18655,7 @@
         <v>27</v>
       </c>
       <c r="D855">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E855" t="s">
         <v>28</v>
@@ -18672,7 +18672,7 @@
         <v>27</v>
       </c>
       <c r="D856">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E856" t="s">
         <v>28</v>
@@ -18689,7 +18689,7 @@
         <v>27</v>
       </c>
       <c r="D857">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E857" t="s">
         <v>28</v>
@@ -18706,7 +18706,7 @@
         <v>27</v>
       </c>
       <c r="D858">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E858" t="s">
         <v>28</v>
@@ -18723,7 +18723,7 @@
         <v>27</v>
       </c>
       <c r="D859">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E859" t="s">
         <v>28</v>
@@ -18774,7 +18774,7 @@
         <v>27</v>
       </c>
       <c r="D862">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E862" t="s">
         <v>28</v>
@@ -18791,7 +18791,7 @@
         <v>27</v>
       </c>
       <c r="D863">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E863" t="s">
         <v>28</v>
@@ -18825,7 +18825,7 @@
         <v>27</v>
       </c>
       <c r="D865">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E865" t="s">
         <v>28</v>
@@ -18842,7 +18842,7 @@
         <v>27</v>
       </c>
       <c r="D866">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E866" t="s">
         <v>28</v>
@@ -18859,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="D867">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E867" t="s">
         <v>28</v>
@@ -18876,7 +18876,7 @@
         <v>27</v>
       </c>
       <c r="D868">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E868" t="s">
         <v>28</v>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
       <c r="D869">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E869" t="s">
         <v>28</v>
@@ -18910,7 +18910,7 @@
         <v>27</v>
       </c>
       <c r="D870">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E870" t="s">
         <v>28</v>
@@ -18927,7 +18927,7 @@
         <v>27</v>
       </c>
       <c r="D871">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E871" t="s">
         <v>28</v>
@@ -18944,7 +18944,7 @@
         <v>27</v>
       </c>
       <c r="D872">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E872" t="s">
         <v>28</v>
@@ -18961,7 +18961,7 @@
         <v>27</v>
       </c>
       <c r="D873">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E873" t="s">
         <v>28</v>
@@ -18978,7 +18978,7 @@
         <v>27</v>
       </c>
       <c r="D874">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E874" t="s">
         <v>28</v>
@@ -18995,7 +18995,7 @@
         <v>27</v>
       </c>
       <c r="D875">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E875" t="s">
         <v>28</v>
@@ -19012,7 +19012,7 @@
         <v>27</v>
       </c>
       <c r="D876">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E876" t="s">
         <v>28</v>
@@ -19029,7 +19029,7 @@
         <v>27</v>
       </c>
       <c r="D877">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E877" t="s">
         <v>28</v>
@@ -19046,7 +19046,7 @@
         <v>27</v>
       </c>
       <c r="D878">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E878" t="s">
         <v>28</v>
@@ -19063,7 +19063,7 @@
         <v>27</v>
       </c>
       <c r="D879">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E879" t="s">
         <v>28</v>
@@ -19080,7 +19080,7 @@
         <v>27</v>
       </c>
       <c r="D880">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E880" t="s">
         <v>28</v>
@@ -19097,7 +19097,7 @@
         <v>27</v>
       </c>
       <c r="D881">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E881" t="s">
         <v>28</v>
@@ -19114,7 +19114,7 @@
         <v>27</v>
       </c>
       <c r="D882">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E882" t="s">
         <v>28</v>
@@ -19131,7 +19131,7 @@
         <v>27</v>
       </c>
       <c r="D883">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E883" t="s">
         <v>28</v>
@@ -19148,7 +19148,7 @@
         <v>27</v>
       </c>
       <c r="D884">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E884" t="s">
         <v>28</v>
@@ -19165,7 +19165,7 @@
         <v>27</v>
       </c>
       <c r="D885">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E885" t="s">
         <v>28</v>
@@ -19182,7 +19182,7 @@
         <v>27</v>
       </c>
       <c r="D886">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E886" t="s">
         <v>28</v>
@@ -19199,7 +19199,7 @@
         <v>27</v>
       </c>
       <c r="D887">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E887" t="s">
         <v>28</v>
@@ -19233,7 +19233,7 @@
         <v>27</v>
       </c>
       <c r="D889">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E889" t="s">
         <v>28</v>
@@ -19250,7 +19250,7 @@
         <v>27</v>
       </c>
       <c r="D890">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E890" t="s">
         <v>28</v>
@@ -19267,7 +19267,7 @@
         <v>27</v>
       </c>
       <c r="D891">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E891" t="s">
         <v>28</v>
@@ -19284,7 +19284,7 @@
         <v>27</v>
       </c>
       <c r="D892">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E892" t="s">
         <v>28</v>
@@ -19301,7 +19301,7 @@
         <v>27</v>
       </c>
       <c r="D893">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E893" t="s">
         <v>28</v>
@@ -19318,7 +19318,7 @@
         <v>27</v>
       </c>
       <c r="D894">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E894" t="s">
         <v>28</v>
@@ -19335,7 +19335,7 @@
         <v>27</v>
       </c>
       <c r="D895">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E895" t="s">
         <v>28</v>
@@ -19352,7 +19352,7 @@
         <v>27</v>
       </c>
       <c r="D896">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E896" t="s">
         <v>28</v>
@@ -19369,7 +19369,7 @@
         <v>27</v>
       </c>
       <c r="D897">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E897" t="s">
         <v>28</v>
@@ -19386,7 +19386,7 @@
         <v>27</v>
       </c>
       <c r="D898">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E898" t="s">
         <v>28</v>
@@ -19403,7 +19403,7 @@
         <v>27</v>
       </c>
       <c r="D899">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E899" t="s">
         <v>28</v>
@@ -19420,7 +19420,7 @@
         <v>27</v>
       </c>
       <c r="D900">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E900" t="s">
         <v>28</v>
@@ -19437,7 +19437,7 @@
         <v>27</v>
       </c>
       <c r="D901">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E901" t="s">
         <v>28</v>
@@ -19454,7 +19454,7 @@
         <v>27</v>
       </c>
       <c r="D902">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E902" t="s">
         <v>28</v>
@@ -19471,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D903">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E903" t="s">
         <v>28</v>
@@ -19488,7 +19488,7 @@
         <v>27</v>
       </c>
       <c r="D904">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E904" t="s">
         <v>28</v>
@@ -19505,7 +19505,7 @@
         <v>27</v>
       </c>
       <c r="D905">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E905" t="s">
         <v>28</v>
@@ -19522,7 +19522,7 @@
         <v>27</v>
       </c>
       <c r="D906">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E906" t="s">
         <v>28</v>
@@ -19539,7 +19539,7 @@
         <v>27</v>
       </c>
       <c r="D907">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E907" t="s">
         <v>28</v>
@@ -19556,7 +19556,7 @@
         <v>27</v>
       </c>
       <c r="D908">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E908" t="s">
         <v>28</v>
@@ -19573,7 +19573,7 @@
         <v>27</v>
       </c>
       <c r="D909">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E909" t="s">
         <v>28</v>
@@ -19590,7 +19590,7 @@
         <v>27</v>
       </c>
       <c r="D910">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E910" t="s">
         <v>28</v>
@@ -19624,7 +19624,7 @@
         <v>27</v>
       </c>
       <c r="D912">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E912" t="s">
         <v>28</v>
@@ -19641,7 +19641,7 @@
         <v>27</v>
       </c>
       <c r="D913">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E913" t="s">
         <v>28</v>
@@ -19658,7 +19658,7 @@
         <v>27</v>
       </c>
       <c r="D914">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E914" t="s">
         <v>28</v>
@@ -19675,7 +19675,7 @@
         <v>27</v>
       </c>
       <c r="D915">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E915" t="s">
         <v>28</v>
@@ -19692,7 +19692,7 @@
         <v>27</v>
       </c>
       <c r="D916">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E916" t="s">
         <v>28</v>
@@ -19709,7 +19709,7 @@
         <v>27</v>
       </c>
       <c r="D917">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E917" t="s">
         <v>28</v>
@@ -19726,7 +19726,7 @@
         <v>27</v>
       </c>
       <c r="D918">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E918" t="s">
         <v>28</v>
@@ -19743,7 +19743,7 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E919" t="s">
         <v>28</v>
@@ -19760,7 +19760,7 @@
         <v>27</v>
       </c>
       <c r="D920">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E920" t="s">
         <v>28</v>
@@ -19777,7 +19777,7 @@
         <v>27</v>
       </c>
       <c r="D921">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E921" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>27</v>
       </c>
       <c r="D922">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E922" t="s">
         <v>28</v>
@@ -19811,7 +19811,7 @@
         <v>27</v>
       </c>
       <c r="D923">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E923" t="s">
         <v>28</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="D924">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E924" t="s">
         <v>28</v>
@@ -19845,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="D925">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E925" t="s">
         <v>28</v>
@@ -19862,7 +19862,7 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E926" t="s">
         <v>28</v>
@@ -19879,7 +19879,7 @@
         <v>27</v>
       </c>
       <c r="D927">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E927" t="s">
         <v>28</v>
@@ -19896,7 +19896,7 @@
         <v>27</v>
       </c>
       <c r="D928">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E928" t="s">
         <v>28</v>
@@ -19913,7 +19913,7 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E929" t="s">
         <v>28</v>
@@ -19930,7 +19930,7 @@
         <v>27</v>
       </c>
       <c r="D930">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E930" t="s">
         <v>28</v>
@@ -19947,7 +19947,7 @@
         <v>27</v>
       </c>
       <c r="D931">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E931" t="s">
         <v>28</v>
@@ -19964,7 +19964,7 @@
         <v>27</v>
       </c>
       <c r="D932">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E932" t="s">
         <v>28</v>
@@ -19981,7 +19981,7 @@
         <v>27</v>
       </c>
       <c r="D933">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E933" t="s">
         <v>28</v>
@@ -19998,7 +19998,7 @@
         <v>27</v>
       </c>
       <c r="D934">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E934" t="s">
         <v>28</v>
@@ -20015,7 +20015,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E935" t="s">
         <v>28</v>
@@ -20032,7 +20032,7 @@
         <v>27</v>
       </c>
       <c r="D936">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E936" t="s">
         <v>28</v>
@@ -20049,7 +20049,7 @@
         <v>27</v>
       </c>
       <c r="D937">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E937" t="s">
         <v>28</v>
@@ -20066,7 +20066,7 @@
         <v>27</v>
       </c>
       <c r="D938">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E938" t="s">
         <v>28</v>
@@ -20083,7 +20083,7 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E939" t="s">
         <v>28</v>
@@ -20100,7 +20100,7 @@
         <v>27</v>
       </c>
       <c r="D940">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E940" t="s">
         <v>28</v>
@@ -20117,7 +20117,7 @@
         <v>27</v>
       </c>
       <c r="D941">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E941" t="s">
         <v>28</v>
@@ -20134,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D942">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E942" t="s">
         <v>28</v>
@@ -20151,7 +20151,7 @@
         <v>27</v>
       </c>
       <c r="D943">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E943" t="s">
         <v>28</v>
@@ -20168,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="D944">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E944" t="s">
         <v>28</v>
@@ -20185,7 +20185,7 @@
         <v>27</v>
       </c>
       <c r="D945">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E945" t="s">
         <v>28</v>
@@ -20202,7 +20202,7 @@
         <v>27</v>
       </c>
       <c r="D946">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E946" t="s">
         <v>28</v>
@@ -20219,7 +20219,7 @@
         <v>27</v>
       </c>
       <c r="D947">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E947" t="s">
         <v>28</v>
@@ -20236,7 +20236,7 @@
         <v>27</v>
       </c>
       <c r="D948">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E948" t="s">
         <v>28</v>
@@ -20253,7 +20253,7 @@
         <v>27</v>
       </c>
       <c r="D949">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E949" t="s">
         <v>28</v>
@@ -20270,7 +20270,7 @@
         <v>27</v>
       </c>
       <c r="D950">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E950" t="s">
         <v>28</v>
@@ -20287,7 +20287,7 @@
         <v>27</v>
       </c>
       <c r="D951">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E951" t="s">
         <v>28</v>
@@ -20304,7 +20304,7 @@
         <v>27</v>
       </c>
       <c r="D952">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E952" t="s">
         <v>28</v>
@@ -20321,7 +20321,7 @@
         <v>27</v>
       </c>
       <c r="D953">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E953" t="s">
         <v>28</v>
@@ -20338,7 +20338,7 @@
         <v>27</v>
       </c>
       <c r="D954">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E954" t="s">
         <v>28</v>
@@ -20355,7 +20355,7 @@
         <v>27</v>
       </c>
       <c r="D955">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E955" t="s">
         <v>28</v>
@@ -20372,7 +20372,7 @@
         <v>27</v>
       </c>
       <c r="D956">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E956" t="s">
         <v>28</v>
@@ -20389,7 +20389,7 @@
         <v>27</v>
       </c>
       <c r="D957">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E957" t="s">
         <v>28</v>
@@ -20406,7 +20406,7 @@
         <v>27</v>
       </c>
       <c r="D958">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E958" t="s">
         <v>28</v>
@@ -20423,7 +20423,7 @@
         <v>27</v>
       </c>
       <c r="D959">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E959" t="s">
         <v>28</v>
@@ -20440,7 +20440,7 @@
         <v>27</v>
       </c>
       <c r="D960">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E960" t="s">
         <v>28</v>
@@ -20457,7 +20457,7 @@
         <v>27</v>
       </c>
       <c r="D961">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E961" t="s">
         <v>28</v>
@@ -20474,7 +20474,7 @@
         <v>27</v>
       </c>
       <c r="D962">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E962" t="s">
         <v>28</v>
@@ -20491,7 +20491,7 @@
         <v>27</v>
       </c>
       <c r="D963">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E963" t="s">
         <v>28</v>
@@ -20508,7 +20508,7 @@
         <v>27</v>
       </c>
       <c r="D964">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E964" t="s">
         <v>28</v>
@@ -20525,7 +20525,7 @@
         <v>27</v>
       </c>
       <c r="D965">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E965" t="s">
         <v>28</v>
@@ -20559,7 +20559,7 @@
         <v>27</v>
       </c>
       <c r="D967">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E967" t="s">
         <v>28</v>
@@ -20576,7 +20576,7 @@
         <v>27</v>
       </c>
       <c r="D968">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E968" t="s">
         <v>28</v>
@@ -20593,7 +20593,7 @@
         <v>27</v>
       </c>
       <c r="D969">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E969" t="s">
         <v>28</v>
@@ -20610,7 +20610,7 @@
         <v>27</v>
       </c>
       <c r="D970">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E970" t="s">
         <v>28</v>
@@ -20627,7 +20627,7 @@
         <v>27</v>
       </c>
       <c r="D971">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E971" t="s">
         <v>28</v>
@@ -20644,7 +20644,7 @@
         <v>27</v>
       </c>
       <c r="D972">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E972" t="s">
         <v>28</v>
@@ -20661,7 +20661,7 @@
         <v>27</v>
       </c>
       <c r="D973">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E973" t="s">
         <v>28</v>
@@ -20678,7 +20678,7 @@
         <v>27</v>
       </c>
       <c r="D974">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E974" t="s">
         <v>28</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="D975">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E975" t="s">
         <v>28</v>
@@ -20712,7 +20712,7 @@
         <v>27</v>
       </c>
       <c r="D976">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E976" t="s">
         <v>28</v>
@@ -20729,7 +20729,7 @@
         <v>27</v>
       </c>
       <c r="D977">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E977" t="s">
         <v>28</v>
@@ -20746,7 +20746,7 @@
         <v>27</v>
       </c>
       <c r="D978">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E978" t="s">
         <v>28</v>
@@ -20763,7 +20763,7 @@
         <v>27</v>
       </c>
       <c r="D979">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E979" t="s">
         <v>28</v>
@@ -20780,7 +20780,7 @@
         <v>27</v>
       </c>
       <c r="D980">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E980" t="s">
         <v>28</v>
@@ -20797,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="D981">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E981" t="s">
         <v>28</v>
@@ -20814,7 +20814,7 @@
         <v>27</v>
       </c>
       <c r="D982">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E982" t="s">
         <v>28</v>
@@ -20831,7 +20831,7 @@
         <v>27</v>
       </c>
       <c r="D983">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E983" t="s">
         <v>28</v>
@@ -20882,7 +20882,7 @@
         <v>27</v>
       </c>
       <c r="D986">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E986" t="s">
         <v>28</v>
@@ -20899,7 +20899,7 @@
         <v>27</v>
       </c>
       <c r="D987">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E987" t="s">
         <v>28</v>
@@ -20916,7 +20916,7 @@
         <v>27</v>
       </c>
       <c r="D988">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E988" t="s">
         <v>28</v>
@@ -20933,7 +20933,7 @@
         <v>27</v>
       </c>
       <c r="D989">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E989" t="s">
         <v>28</v>
@@ -20950,7 +20950,7 @@
         <v>27</v>
       </c>
       <c r="D990">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E990" t="s">
         <v>28</v>
@@ -20967,7 +20967,7 @@
         <v>27</v>
       </c>
       <c r="D991">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E991" t="s">
         <v>28</v>
@@ -20984,7 +20984,7 @@
         <v>27</v>
       </c>
       <c r="D992">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E992" t="s">
         <v>28</v>
@@ -21001,7 +21001,7 @@
         <v>27</v>
       </c>
       <c r="D993">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E993" t="s">
         <v>28</v>
@@ -21018,7 +21018,7 @@
         <v>27</v>
       </c>
       <c r="D994">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E994" t="s">
         <v>28</v>
@@ -21035,7 +21035,7 @@
         <v>27</v>
       </c>
       <c r="D995">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E995" t="s">
         <v>28</v>
@@ -21052,7 +21052,7 @@
         <v>27</v>
       </c>
       <c r="D996">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E996" t="s">
         <v>28</v>
@@ -21069,7 +21069,7 @@
         <v>27</v>
       </c>
       <c r="D997">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E997" t="s">
         <v>28</v>
@@ -21086,7 +21086,7 @@
         <v>27</v>
       </c>
       <c r="D998">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E998" t="s">
         <v>28</v>
@@ -21103,7 +21103,7 @@
         <v>27</v>
       </c>
       <c r="D999">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E999" t="s">
         <v>28</v>
@@ -21120,7 +21120,7 @@
         <v>27</v>
       </c>
       <c r="D1000">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1000" t="s">
         <v>28</v>
@@ -21137,7 +21137,7 @@
         <v>27</v>
       </c>
       <c r="D1001">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1001" t="s">
         <v>28</v>
@@ -21154,7 +21154,7 @@
         <v>27</v>
       </c>
       <c r="D1002">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1002" t="s">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>27</v>
       </c>
       <c r="D1003">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1003" t="s">
         <v>28</v>
@@ -21188,7 +21188,7 @@
         <v>27</v>
       </c>
       <c r="D1004">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E1004" t="s">
         <v>28</v>
@@ -21205,7 +21205,7 @@
         <v>27</v>
       </c>
       <c r="D1005">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E1005" t="s">
         <v>28</v>
@@ -21222,7 +21222,7 @@
         <v>27</v>
       </c>
       <c r="D1006">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1006" t="s">
         <v>28</v>
@@ -21239,7 +21239,7 @@
         <v>27</v>
       </c>
       <c r="D1007">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1007" t="s">
         <v>28</v>
@@ -21256,7 +21256,7 @@
         <v>27</v>
       </c>
       <c r="D1008">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E1008" t="s">
         <v>28</v>
@@ -21273,7 +21273,7 @@
         <v>27</v>
       </c>
       <c r="D1009">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1009" t="s">
         <v>28</v>
@@ -21290,7 +21290,7 @@
         <v>27</v>
       </c>
       <c r="D1010">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E1010" t="s">
         <v>28</v>
@@ -21307,7 +21307,7 @@
         <v>27</v>
       </c>
       <c r="D1011">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E1011" t="s">
         <v>28</v>
@@ -21324,7 +21324,7 @@
         <v>27</v>
       </c>
       <c r="D1012">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E1012" t="s">
         <v>28</v>
@@ -21341,7 +21341,7 @@
         <v>27</v>
       </c>
       <c r="D1013">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E1013" t="s">
         <v>28</v>
@@ -21375,7 +21375,7 @@
         <v>27</v>
       </c>
       <c r="D1015">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1015" t="s">
         <v>28</v>
@@ -21392,7 +21392,7 @@
         <v>27</v>
       </c>
       <c r="D1016">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1016" t="s">
         <v>28</v>
@@ -21409,7 +21409,7 @@
         <v>27</v>
       </c>
       <c r="D1017">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E1017" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>27</v>
       </c>
       <c r="D1018">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1018" t="s">
         <v>28</v>
@@ -21443,7 +21443,7 @@
         <v>27</v>
       </c>
       <c r="D1019">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1019" t="s">
         <v>28</v>
@@ -21460,7 +21460,7 @@
         <v>27</v>
       </c>
       <c r="D1020">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E1020" t="s">
         <v>28</v>
@@ -21494,7 +21494,7 @@
         <v>27</v>
       </c>
       <c r="D1022">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E1022" t="s">
         <v>28</v>
@@ -21511,7 +21511,7 @@
         <v>27</v>
       </c>
       <c r="D1023">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1023" t="s">
         <v>28</v>
@@ -21528,7 +21528,7 @@
         <v>27</v>
       </c>
       <c r="D1024">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E1024" t="s">
         <v>28</v>
@@ -21545,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1025" t="s">
         <v>28</v>
@@ -21562,7 +21562,7 @@
         <v>27</v>
       </c>
       <c r="D1026">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1026" t="s">
         <v>28</v>
@@ -21579,7 +21579,7 @@
         <v>27</v>
       </c>
       <c r="D1027">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E1027" t="s">
         <v>28</v>
@@ -21596,7 +21596,7 @@
         <v>27</v>
       </c>
       <c r="D1028">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1028" t="s">
         <v>28</v>
@@ -21613,7 +21613,7 @@
         <v>27</v>
       </c>
       <c r="D1029">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1029" t="s">
         <v>28</v>
@@ -21630,7 +21630,7 @@
         <v>27</v>
       </c>
       <c r="D1030">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1030" t="s">
         <v>28</v>
@@ -21647,7 +21647,7 @@
         <v>27</v>
       </c>
       <c r="D1031">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1031" t="s">
         <v>28</v>
@@ -21664,7 +21664,7 @@
         <v>27</v>
       </c>
       <c r="D1032">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1032" t="s">
         <v>28</v>
@@ -21681,7 +21681,7 @@
         <v>27</v>
       </c>
       <c r="D1033">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1033" t="s">
         <v>28</v>
@@ -21698,7 +21698,7 @@
         <v>27</v>
       </c>
       <c r="D1034">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E1034" t="s">
         <v>28</v>
@@ -21715,7 +21715,7 @@
         <v>27</v>
       </c>
       <c r="D1035">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E1035" t="s">
         <v>28</v>
@@ -21732,7 +21732,7 @@
         <v>27</v>
       </c>
       <c r="D1036">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E1036" t="s">
         <v>28</v>
@@ -21749,7 +21749,7 @@
         <v>27</v>
       </c>
       <c r="D1037">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1037" t="s">
         <v>28</v>
@@ -21766,7 +21766,7 @@
         <v>27</v>
       </c>
       <c r="D1038">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1038" t="s">
         <v>28</v>
@@ -21800,7 +21800,7 @@
         <v>27</v>
       </c>
       <c r="D1040">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1040" t="s">
         <v>28</v>
@@ -21817,7 +21817,7 @@
         <v>27</v>
       </c>
       <c r="D1041">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1041" t="s">
         <v>28</v>
@@ -21834,7 +21834,7 @@
         <v>27</v>
       </c>
       <c r="D1042">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1042" t="s">
         <v>28</v>
@@ -21851,7 +21851,7 @@
         <v>27</v>
       </c>
       <c r="D1043">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1043" t="s">
         <v>28</v>
@@ -21868,7 +21868,7 @@
         <v>27</v>
       </c>
       <c r="D1044">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E1044" t="s">
         <v>28</v>
@@ -21885,7 +21885,7 @@
         <v>27</v>
       </c>
       <c r="D1045">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E1045" t="s">
         <v>28</v>
@@ -21902,7 +21902,7 @@
         <v>27</v>
       </c>
       <c r="D1046">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E1046" t="s">
         <v>28</v>
@@ -21919,7 +21919,7 @@
         <v>27</v>
       </c>
       <c r="D1047">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1047" t="s">
         <v>28</v>
@@ -21936,7 +21936,7 @@
         <v>27</v>
       </c>
       <c r="D1048">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E1048" t="s">
         <v>28</v>
@@ -21953,7 +21953,7 @@
         <v>27</v>
       </c>
       <c r="D1049">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E1049" t="s">
         <v>28</v>
@@ -21970,7 +21970,7 @@
         <v>27</v>
       </c>
       <c r="D1050">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E1050" t="s">
         <v>28</v>
@@ -21987,7 +21987,7 @@
         <v>27</v>
       </c>
       <c r="D1051">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1051" t="s">
         <v>28</v>
@@ -22004,7 +22004,7 @@
         <v>27</v>
       </c>
       <c r="D1052">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E1052" t="s">
         <v>28</v>
@@ -22021,7 +22021,7 @@
         <v>27</v>
       </c>
       <c r="D1053">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1053" t="s">
         <v>28</v>
@@ -22055,7 +22055,7 @@
         <v>27</v>
       </c>
       <c r="D1055">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E1055" t="s">
         <v>28</v>
@@ -22072,7 +22072,7 @@
         <v>27</v>
       </c>
       <c r="D1056">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E1056" t="s">
         <v>28</v>
@@ -22089,7 +22089,7 @@
         <v>27</v>
       </c>
       <c r="D1057">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1057" t="s">
         <v>28</v>
@@ -22106,7 +22106,7 @@
         <v>27</v>
       </c>
       <c r="D1058">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1058" t="s">
         <v>28</v>
@@ -22123,7 +22123,7 @@
         <v>27</v>
       </c>
       <c r="D1059">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1059" t="s">
         <v>28</v>
@@ -22140,7 +22140,7 @@
         <v>27</v>
       </c>
       <c r="D1060">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1060" t="s">
         <v>28</v>
@@ -22157,7 +22157,7 @@
         <v>27</v>
       </c>
       <c r="D1061">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E1061" t="s">
         <v>28</v>
@@ -22174,7 +22174,7 @@
         <v>27</v>
       </c>
       <c r="D1062">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E1062" t="s">
         <v>28</v>
@@ -22191,7 +22191,7 @@
         <v>27</v>
       </c>
       <c r="D1063">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1063" t="s">
         <v>28</v>
@@ -22208,7 +22208,7 @@
         <v>27</v>
       </c>
       <c r="D1064">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E1064" t="s">
         <v>28</v>
@@ -22225,7 +22225,7 @@
         <v>27</v>
       </c>
       <c r="D1065">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1065" t="s">
         <v>28</v>
@@ -22242,7 +22242,7 @@
         <v>27</v>
       </c>
       <c r="D1066">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1066" t="s">
         <v>28</v>
@@ -22259,7 +22259,7 @@
         <v>27</v>
       </c>
       <c r="D1067">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E1067" t="s">
         <v>28</v>
@@ -22276,7 +22276,7 @@
         <v>27</v>
       </c>
       <c r="D1068">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E1068" t="s">
         <v>28</v>
@@ -22293,7 +22293,7 @@
         <v>27</v>
       </c>
       <c r="D1069">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1069" t="s">
         <v>28</v>
@@ -22310,7 +22310,7 @@
         <v>27</v>
       </c>
       <c r="D1070">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1070" t="s">
         <v>28</v>
@@ -22327,7 +22327,7 @@
         <v>27</v>
       </c>
       <c r="D1071">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1071" t="s">
         <v>28</v>
@@ -22344,7 +22344,7 @@
         <v>27</v>
       </c>
       <c r="D1072">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E1072" t="s">
         <v>28</v>
@@ -22361,7 +22361,7 @@
         <v>27</v>
       </c>
       <c r="D1073">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1073" t="s">
         <v>28</v>
@@ -22378,7 +22378,7 @@
         <v>27</v>
       </c>
       <c r="D1074">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1074" t="s">
         <v>28</v>
@@ -22395,7 +22395,7 @@
         <v>27</v>
       </c>
       <c r="D1075">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1075" t="s">
         <v>28</v>
@@ -22412,7 +22412,7 @@
         <v>27</v>
       </c>
       <c r="D1076">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1076" t="s">
         <v>28</v>
@@ -22429,7 +22429,7 @@
         <v>27</v>
       </c>
       <c r="D1077">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E1077" t="s">
         <v>28</v>
@@ -22446,7 +22446,7 @@
         <v>27</v>
       </c>
       <c r="D1078">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E1078" t="s">
         <v>28</v>
@@ -22463,7 +22463,7 @@
         <v>27</v>
       </c>
       <c r="D1079">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E1079" t="s">
         <v>28</v>
@@ -22480,7 +22480,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1080" t="s">
         <v>28</v>
@@ -22497,7 +22497,7 @@
         <v>27</v>
       </c>
       <c r="D1081">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1081" t="s">
         <v>28</v>
@@ -22514,7 +22514,7 @@
         <v>27</v>
       </c>
       <c r="D1082">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1082" t="s">
         <v>28</v>
@@ -22531,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="D1083">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1083" t="s">
         <v>28</v>
@@ -22548,7 +22548,7 @@
         <v>27</v>
       </c>
       <c r="D1084">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E1084" t="s">
         <v>28</v>
@@ -22565,7 +22565,7 @@
         <v>27</v>
       </c>
       <c r="D1085">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E1085" t="s">
         <v>28</v>
@@ -22582,7 +22582,7 @@
         <v>27</v>
       </c>
       <c r="D1086">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1086" t="s">
         <v>28</v>
@@ -22599,7 +22599,7 @@
         <v>27</v>
       </c>
       <c r="D1087">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E1087" t="s">
         <v>28</v>
@@ -22616,7 +22616,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E1088" t="s">
         <v>28</v>
@@ -22633,7 +22633,7 @@
         <v>27</v>
       </c>
       <c r="D1089">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E1089" t="s">
         <v>28</v>
@@ -22650,7 +22650,7 @@
         <v>27</v>
       </c>
       <c r="D1090">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1090" t="s">
         <v>28</v>
@@ -22667,7 +22667,7 @@
         <v>27</v>
       </c>
       <c r="D1091">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E1091" t="s">
         <v>28</v>
@@ -22684,7 +22684,7 @@
         <v>27</v>
       </c>
       <c r="D1092">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E1092" t="s">
         <v>28</v>
@@ -22701,7 +22701,7 @@
         <v>27</v>
       </c>
       <c r="D1093">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1093" t="s">
         <v>28</v>
@@ -22718,7 +22718,7 @@
         <v>27</v>
       </c>
       <c r="D1094">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1094" t="s">
         <v>28</v>
@@ -22735,7 +22735,7 @@
         <v>27</v>
       </c>
       <c r="D1095">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1095" t="s">
         <v>28</v>
@@ -22752,7 +22752,7 @@
         <v>27</v>
       </c>
       <c r="D1096">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E1096" t="s">
         <v>28</v>
@@ -22769,7 +22769,7 @@
         <v>27</v>
       </c>
       <c r="D1097">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1097" t="s">
         <v>28</v>
@@ -22786,7 +22786,7 @@
         <v>27</v>
       </c>
       <c r="D1098">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1098" t="s">
         <v>28</v>
@@ -22803,7 +22803,7 @@
         <v>27</v>
       </c>
       <c r="D1099">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1099" t="s">
         <v>28</v>
@@ -22820,7 +22820,7 @@
         <v>27</v>
       </c>
       <c r="D1100">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1100" t="s">
         <v>28</v>
@@ -22837,7 +22837,7 @@
         <v>27</v>
       </c>
       <c r="D1101">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1101" t="s">
         <v>28</v>
@@ -22854,7 +22854,7 @@
         <v>27</v>
       </c>
       <c r="D1102">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E1102" t="s">
         <v>28</v>
@@ -22888,7 +22888,7 @@
         <v>27</v>
       </c>
       <c r="D1104">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1104" t="s">
         <v>28</v>
@@ -22905,7 +22905,7 @@
         <v>27</v>
       </c>
       <c r="D1105">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1105" t="s">
         <v>28</v>
@@ -22922,7 +22922,7 @@
         <v>27</v>
       </c>
       <c r="D1106">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1106" t="s">
         <v>28</v>
@@ -22939,7 +22939,7 @@
         <v>27</v>
       </c>
       <c r="D1107">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1107" t="s">
         <v>28</v>
@@ -22956,7 +22956,7 @@
         <v>27</v>
       </c>
       <c r="D1108">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E1108" t="s">
         <v>28</v>
@@ -22973,7 +22973,7 @@
         <v>27</v>
       </c>
       <c r="D1109">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E1109" t="s">
         <v>28</v>
@@ -23007,7 +23007,7 @@
         <v>27</v>
       </c>
       <c r="D1111">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1111" t="s">
         <v>28</v>
@@ -23024,7 +23024,7 @@
         <v>27</v>
       </c>
       <c r="D1112">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1112" t="s">
         <v>28</v>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1313</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1293</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1277</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1326</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1244</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1261</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1242</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1276</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1332</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1318</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1256</v>
+        <v>1310</v>
       </c>
     </row>
   </sheetData>
@@ -4154,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -4188,7 +4188,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -4205,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -4222,7 +4222,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4256,7 +4256,7 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -4273,7 +4273,7 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4307,7 +4307,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4341,7 +4341,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -4358,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4409,7 +4409,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -4426,7 +4426,7 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -4443,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -4460,7 +4460,7 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
@@ -4494,7 +4494,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -4511,7 +4511,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -4528,7 +4528,7 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -4545,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" t="s">
         <v>28</v>
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -4579,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -4596,7 +4596,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -4613,7 +4613,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E30" t="s">
         <v>28</v>
@@ -4647,7 +4647,7 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4681,7 +4681,7 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4698,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="D34">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -4715,7 +4715,7 @@
         <v>27</v>
       </c>
       <c r="D35">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E35" t="s">
         <v>28</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -4749,7 +4749,7 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E37" t="s">
         <v>28</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
         <v>28</v>
@@ -4783,7 +4783,7 @@
         <v>27</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E39" t="s">
         <v>28</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
@@ -4817,7 +4817,7 @@
         <v>27</v>
       </c>
       <c r="D41">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4834,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4851,7 +4851,7 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
         <v>27</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -4919,7 +4919,7 @@
         <v>27</v>
       </c>
       <c r="D47">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="D48">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4953,7 +4953,7 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
@@ -4970,7 +4970,7 @@
         <v>27</v>
       </c>
       <c r="D50">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -4987,7 +4987,7 @@
         <v>27</v>
       </c>
       <c r="D51">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
@@ -5004,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5038,7 +5038,7 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
         <v>28</v>
@@ -5055,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="D55">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -5072,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E56" t="s">
         <v>28</v>
@@ -5089,7 +5089,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E57" t="s">
         <v>28</v>
@@ -5106,7 +5106,7 @@
         <v>27</v>
       </c>
       <c r="D58">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -5123,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E59" t="s">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         <v>27</v>
       </c>
       <c r="D60">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E60" t="s">
         <v>28</v>
@@ -5157,7 +5157,7 @@
         <v>27</v>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -5174,7 +5174,7 @@
         <v>27</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
@@ -5191,7 +5191,7 @@
         <v>27</v>
       </c>
       <c r="D63">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="D64">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
@@ -5225,7 +5225,7 @@
         <v>27</v>
       </c>
       <c r="D65">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="D67">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
@@ -5293,7 +5293,7 @@
         <v>27</v>
       </c>
       <c r="D69">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -5310,7 +5310,7 @@
         <v>27</v>
       </c>
       <c r="D70">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="D71">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -5344,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="D72">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
@@ -5361,7 +5361,7 @@
         <v>27</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -5378,7 +5378,7 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
@@ -5395,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="D75">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="D76">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
@@ -5429,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="D77">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -5446,7 +5446,7 @@
         <v>27</v>
       </c>
       <c r="D78">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
@@ -5480,7 +5480,7 @@
         <v>27</v>
       </c>
       <c r="D80">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
@@ -5497,7 +5497,7 @@
         <v>27</v>
       </c>
       <c r="D81">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -5514,7 +5514,7 @@
         <v>27</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
@@ -5548,7 +5548,7 @@
         <v>27</v>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
@@ -5565,7 +5565,7 @@
         <v>27</v>
       </c>
       <c r="D85">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -5582,7 +5582,7 @@
         <v>27</v>
       </c>
       <c r="D86">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
@@ -5599,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="D87">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
@@ -5616,7 +5616,7 @@
         <v>27</v>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -5633,7 +5633,7 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="D90">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -5684,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="D92">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
@@ -5701,7 +5701,7 @@
         <v>27</v>
       </c>
       <c r="D93">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E93" t="s">
         <v>28</v>
@@ -5718,7 +5718,7 @@
         <v>27</v>
       </c>
       <c r="D94">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E94" t="s">
         <v>28</v>
@@ -5735,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D95">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -5752,7 +5752,7 @@
         <v>27</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E96" t="s">
         <v>28</v>
@@ -5769,7 +5769,7 @@
         <v>27</v>
       </c>
       <c r="D97">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E97" t="s">
         <v>28</v>
@@ -5786,7 +5786,7 @@
         <v>27</v>
       </c>
       <c r="D98">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="D99">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E99" t="s">
         <v>28</v>
@@ -5820,7 +5820,7 @@
         <v>27</v>
       </c>
       <c r="D100">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E100" t="s">
         <v>28</v>
@@ -5837,7 +5837,7 @@
         <v>27</v>
       </c>
       <c r="D101">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E101" t="s">
         <v>28</v>
@@ -5854,7 +5854,7 @@
         <v>27</v>
       </c>
       <c r="D102">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E102" t="s">
         <v>28</v>
@@ -5871,7 +5871,7 @@
         <v>27</v>
       </c>
       <c r="D103">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E103" t="s">
         <v>28</v>
@@ -5888,7 +5888,7 @@
         <v>27</v>
       </c>
       <c r="D104">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E104" t="s">
         <v>28</v>
@@ -5905,7 +5905,7 @@
         <v>27</v>
       </c>
       <c r="D105">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E105" t="s">
         <v>28</v>
@@ -5922,7 +5922,7 @@
         <v>27</v>
       </c>
       <c r="D106">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>27</v>
       </c>
       <c r="D107">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E107" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="D108">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5973,7 +5973,7 @@
         <v>27</v>
       </c>
       <c r="D109">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E109" t="s">
         <v>28</v>
@@ -5990,7 +5990,7 @@
         <v>27</v>
       </c>
       <c r="D110">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E110" t="s">
         <v>28</v>
@@ -6007,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="D111">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="D112">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="D113">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E113" t="s">
         <v>28</v>
@@ -6058,7 +6058,7 @@
         <v>27</v>
       </c>
       <c r="D114">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>27</v>
       </c>
       <c r="D115">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -6092,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="D116">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E116" t="s">
         <v>28</v>
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="D117">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E117" t="s">
         <v>28</v>
@@ -6126,7 +6126,7 @@
         <v>27</v>
       </c>
       <c r="D118">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E118" t="s">
         <v>28</v>
@@ -6143,7 +6143,7 @@
         <v>27</v>
       </c>
       <c r="D119">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E119" t="s">
         <v>28</v>
@@ -6177,7 +6177,7 @@
         <v>27</v>
       </c>
       <c r="D121">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E121" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="D122">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E122" t="s">
         <v>28</v>
@@ -6211,7 +6211,7 @@
         <v>27</v>
       </c>
       <c r="D123">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E123" t="s">
         <v>28</v>
@@ -6228,7 +6228,7 @@
         <v>27</v>
       </c>
       <c r="D124">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E124" t="s">
         <v>28</v>
@@ -6245,7 +6245,7 @@
         <v>27</v>
       </c>
       <c r="D125">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
@@ -6262,7 +6262,7 @@
         <v>27</v>
       </c>
       <c r="D126">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -6279,7 +6279,7 @@
         <v>27</v>
       </c>
       <c r="D127">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E127" t="s">
         <v>28</v>
@@ -6296,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="D128">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E128" t="s">
         <v>28</v>
@@ -6313,7 +6313,7 @@
         <v>27</v>
       </c>
       <c r="D129">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
@@ -6330,7 +6330,7 @@
         <v>27</v>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E130" t="s">
         <v>28</v>
@@ -6347,7 +6347,7 @@
         <v>27</v>
       </c>
       <c r="D131">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E131" t="s">
         <v>28</v>
@@ -6364,7 +6364,7 @@
         <v>27</v>
       </c>
       <c r="D132">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E132" t="s">
         <v>28</v>
@@ -6381,7 +6381,7 @@
         <v>27</v>
       </c>
       <c r="D133">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E133" t="s">
         <v>28</v>
@@ -6398,7 +6398,7 @@
         <v>27</v>
       </c>
       <c r="D134">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E134" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="D136">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E136" t="s">
         <v>28</v>
@@ -6449,7 +6449,7 @@
         <v>27</v>
       </c>
       <c r="D137">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E137" t="s">
         <v>28</v>
@@ -6466,7 +6466,7 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E138" t="s">
         <v>28</v>
@@ -6500,7 +6500,7 @@
         <v>27</v>
       </c>
       <c r="D140">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E140" t="s">
         <v>28</v>
@@ -6517,7 +6517,7 @@
         <v>27</v>
       </c>
       <c r="D141">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E141" t="s">
         <v>28</v>
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="D142">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E142" t="s">
         <v>28</v>
@@ -6551,7 +6551,7 @@
         <v>27</v>
       </c>
       <c r="D143">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E143" t="s">
         <v>28</v>
@@ -6568,7 +6568,7 @@
         <v>27</v>
       </c>
       <c r="D144">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E144" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="D145">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E145" t="s">
         <v>28</v>
@@ -6619,7 +6619,7 @@
         <v>27</v>
       </c>
       <c r="D147">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E147" t="s">
         <v>28</v>
@@ -6636,7 +6636,7 @@
         <v>27</v>
       </c>
       <c r="D148">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E148" t="s">
         <v>28</v>
@@ -6653,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="D149">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6670,7 +6670,7 @@
         <v>27</v>
       </c>
       <c r="D150">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E150" t="s">
         <v>28</v>
@@ -6687,7 +6687,7 @@
         <v>27</v>
       </c>
       <c r="D151">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>27</v>
       </c>
       <c r="D152">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E152" t="s">
         <v>28</v>
@@ -6721,7 +6721,7 @@
         <v>27</v>
       </c>
       <c r="D153">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E153" t="s">
         <v>28</v>
@@ -6738,7 +6738,7 @@
         <v>27</v>
       </c>
       <c r="D154">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E154" t="s">
         <v>28</v>
@@ -6755,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -6772,7 +6772,7 @@
         <v>27</v>
       </c>
       <c r="D156">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E156" t="s">
         <v>28</v>
@@ -6789,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="D157">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E157" t="s">
         <v>28</v>
@@ -6806,7 +6806,7 @@
         <v>27</v>
       </c>
       <c r="D158">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E158" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="D159">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E159" t="s">
         <v>28</v>
@@ -6840,7 +6840,7 @@
         <v>27</v>
       </c>
       <c r="D160">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E160" t="s">
         <v>28</v>
@@ -6857,7 +6857,7 @@
         <v>27</v>
       </c>
       <c r="D161">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
@@ -6925,7 +6925,7 @@
         <v>27</v>
       </c>
       <c r="D165">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E165" t="s">
         <v>28</v>
@@ -6942,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="D166">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E166" t="s">
         <v>28</v>
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="D167">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E167" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="D168">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E168" t="s">
         <v>28</v>
@@ -6993,7 +6993,7 @@
         <v>27</v>
       </c>
       <c r="D169">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E169" t="s">
         <v>28</v>
@@ -7010,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="D170">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E170" t="s">
         <v>28</v>
@@ -7027,7 +7027,7 @@
         <v>27</v>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E171" t="s">
         <v>28</v>
@@ -7044,7 +7044,7 @@
         <v>27</v>
       </c>
       <c r="D172">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E172" t="s">
         <v>28</v>
@@ -7061,7 +7061,7 @@
         <v>27</v>
       </c>
       <c r="D173">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E173" t="s">
         <v>28</v>
@@ -7078,7 +7078,7 @@
         <v>27</v>
       </c>
       <c r="D174">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E174" t="s">
         <v>28</v>
@@ -7095,7 +7095,7 @@
         <v>27</v>
       </c>
       <c r="D175">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E175" t="s">
         <v>28</v>
@@ -7112,7 +7112,7 @@
         <v>27</v>
       </c>
       <c r="D176">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E176" t="s">
         <v>28</v>
@@ -7129,7 +7129,7 @@
         <v>27</v>
       </c>
       <c r="D177">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E177" t="s">
         <v>28</v>
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="D178">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E178" t="s">
         <v>28</v>
@@ -7163,7 +7163,7 @@
         <v>27</v>
       </c>
       <c r="D179">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E179" t="s">
         <v>28</v>
@@ -7180,7 +7180,7 @@
         <v>27</v>
       </c>
       <c r="D180">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -7197,7 +7197,7 @@
         <v>27</v>
       </c>
       <c r="D181">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E181" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="D182">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E182" t="s">
         <v>28</v>
@@ -7231,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="D183">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
@@ -7248,7 +7248,7 @@
         <v>27</v>
       </c>
       <c r="D184">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E184" t="s">
         <v>28</v>
@@ -7265,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="D185">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E185" t="s">
         <v>28</v>
@@ -7282,7 +7282,7 @@
         <v>27</v>
       </c>
       <c r="D186">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E186" t="s">
         <v>28</v>
@@ -7299,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="D187">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E187" t="s">
         <v>28</v>
@@ -7316,7 +7316,7 @@
         <v>27</v>
       </c>
       <c r="D188">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -7333,7 +7333,7 @@
         <v>27</v>
       </c>
       <c r="D189">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E189" t="s">
         <v>28</v>
@@ -7350,7 +7350,7 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E190" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="D191">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
@@ -7384,7 +7384,7 @@
         <v>27</v>
       </c>
       <c r="D192">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E192" t="s">
         <v>28</v>
@@ -7401,7 +7401,7 @@
         <v>27</v>
       </c>
       <c r="D193">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E193" t="s">
         <v>28</v>
@@ -7435,7 +7435,7 @@
         <v>27</v>
       </c>
       <c r="D195">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E195" t="s">
         <v>28</v>
@@ -7452,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="D196">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E196" t="s">
         <v>28</v>
@@ -7486,7 +7486,7 @@
         <v>27</v>
       </c>
       <c r="D198">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E198" t="s">
         <v>28</v>
@@ -7503,7 +7503,7 @@
         <v>27</v>
       </c>
       <c r="D199">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E199" t="s">
         <v>28</v>
@@ -7520,7 +7520,7 @@
         <v>27</v>
       </c>
       <c r="D200">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E200" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>27</v>
       </c>
       <c r="D201">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E201" t="s">
         <v>28</v>
@@ -7554,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="D202">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E202" t="s">
         <v>28</v>
@@ -7571,7 +7571,7 @@
         <v>27</v>
       </c>
       <c r="D203">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
@@ -7588,7 +7588,7 @@
         <v>27</v>
       </c>
       <c r="D204">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E204" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="D205">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -7622,7 +7622,7 @@
         <v>27</v>
       </c>
       <c r="D206">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E206" t="s">
         <v>28</v>
@@ -7639,7 +7639,7 @@
         <v>27</v>
       </c>
       <c r="D207">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E207" t="s">
         <v>28</v>
@@ -7656,7 +7656,7 @@
         <v>27</v>
       </c>
       <c r="D208">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E208" t="s">
         <v>28</v>
@@ -7673,7 +7673,7 @@
         <v>27</v>
       </c>
       <c r="D209">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E209" t="s">
         <v>28</v>
@@ -7690,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="D210">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E210" t="s">
         <v>28</v>
@@ -7707,7 +7707,7 @@
         <v>27</v>
       </c>
       <c r="D211">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E211" t="s">
         <v>28</v>
@@ -7724,7 +7724,7 @@
         <v>27</v>
       </c>
       <c r="D212">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E212" t="s">
         <v>28</v>
@@ -7741,7 +7741,7 @@
         <v>27</v>
       </c>
       <c r="D213">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E213" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="D214">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E214" t="s">
         <v>28</v>
@@ -7775,7 +7775,7 @@
         <v>27</v>
       </c>
       <c r="D215">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E215" t="s">
         <v>28</v>
@@ -7792,7 +7792,7 @@
         <v>27</v>
       </c>
       <c r="D216">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E216" t="s">
         <v>28</v>
@@ -7809,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="D217">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E217" t="s">
         <v>28</v>
@@ -7826,7 +7826,7 @@
         <v>27</v>
       </c>
       <c r="D218">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E218" t="s">
         <v>28</v>
@@ -7843,7 +7843,7 @@
         <v>27</v>
       </c>
       <c r="D219">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E219" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="D220">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E220" t="s">
         <v>28</v>
@@ -7877,7 +7877,7 @@
         <v>27</v>
       </c>
       <c r="D221">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E221" t="s">
         <v>28</v>
@@ -7894,7 +7894,7 @@
         <v>27</v>
       </c>
       <c r="D222">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E222" t="s">
         <v>28</v>
@@ -7911,7 +7911,7 @@
         <v>27</v>
       </c>
       <c r="D223">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E223" t="s">
         <v>28</v>
@@ -7928,7 +7928,7 @@
         <v>27</v>
       </c>
       <c r="D224">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E224" t="s">
         <v>28</v>
@@ -7945,7 +7945,7 @@
         <v>27</v>
       </c>
       <c r="D225">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E225" t="s">
         <v>28</v>
@@ -7962,7 +7962,7 @@
         <v>27</v>
       </c>
       <c r="D226">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E226" t="s">
         <v>28</v>
@@ -7979,7 +7979,7 @@
         <v>27</v>
       </c>
       <c r="D227">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E227" t="s">
         <v>28</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="D228">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E228" t="s">
         <v>28</v>
@@ -8013,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="D229">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E229" t="s">
         <v>28</v>
@@ -8030,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="D230">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E230" t="s">
         <v>28</v>
@@ -8047,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="D231">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E231" t="s">
         <v>28</v>
@@ -8064,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="D232">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E232" t="s">
         <v>28</v>
@@ -8081,7 +8081,7 @@
         <v>27</v>
       </c>
       <c r="D233">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E233" t="s">
         <v>28</v>
@@ -8098,7 +8098,7 @@
         <v>27</v>
       </c>
       <c r="D234">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E234" t="s">
         <v>28</v>
@@ -8115,7 +8115,7 @@
         <v>27</v>
       </c>
       <c r="D235">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E235" t="s">
         <v>28</v>
@@ -8132,7 +8132,7 @@
         <v>27</v>
       </c>
       <c r="D236">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E236" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="D237">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E237" t="s">
         <v>28</v>
@@ -8166,7 +8166,7 @@
         <v>27</v>
       </c>
       <c r="D238">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E238" t="s">
         <v>28</v>
@@ -8183,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="D239">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E239" t="s">
         <v>28</v>
@@ -8200,7 +8200,7 @@
         <v>27</v>
       </c>
       <c r="D240">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E240" t="s">
         <v>28</v>
@@ -8217,7 +8217,7 @@
         <v>27</v>
       </c>
       <c r="D241">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E241" t="s">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>27</v>
       </c>
       <c r="D242">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E242" t="s">
         <v>28</v>
@@ -8251,7 +8251,7 @@
         <v>27</v>
       </c>
       <c r="D243">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E243" t="s">
         <v>28</v>
@@ -8268,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="D244">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E244" t="s">
         <v>28</v>
@@ -8285,7 +8285,7 @@
         <v>27</v>
       </c>
       <c r="D245">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E245" t="s">
         <v>28</v>
@@ -8302,7 +8302,7 @@
         <v>27</v>
       </c>
       <c r="D246">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E246" t="s">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="D247">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E247" t="s">
         <v>28</v>
@@ -8336,7 +8336,7 @@
         <v>27</v>
       </c>
       <c r="D248">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E248" t="s">
         <v>28</v>
@@ -8353,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="D249">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E249" t="s">
         <v>28</v>
@@ -8370,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="D250">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E250" t="s">
         <v>28</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="D251">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E251" t="s">
         <v>28</v>
@@ -8404,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="D252">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E252" t="s">
         <v>28</v>
@@ -8421,7 +8421,7 @@
         <v>27</v>
       </c>
       <c r="D253">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E253" t="s">
         <v>28</v>
@@ -8438,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D254">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E254" t="s">
         <v>28</v>
@@ -8455,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="D255">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E255" t="s">
         <v>28</v>
@@ -8472,7 +8472,7 @@
         <v>27</v>
       </c>
       <c r="D256">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E256" t="s">
         <v>28</v>
@@ -8489,7 +8489,7 @@
         <v>27</v>
       </c>
       <c r="D257">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E257" t="s">
         <v>28</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="D258">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E258" t="s">
         <v>28</v>
@@ -8523,7 +8523,7 @@
         <v>27</v>
       </c>
       <c r="D259">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E259" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="D260">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E260" t="s">
         <v>28</v>
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="D261">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E261" t="s">
         <v>28</v>
@@ -8574,7 +8574,7 @@
         <v>27</v>
       </c>
       <c r="D262">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E262" t="s">
         <v>28</v>
@@ -8591,7 +8591,7 @@
         <v>27</v>
       </c>
       <c r="D263">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E263" t="s">
         <v>28</v>
@@ -8608,7 +8608,7 @@
         <v>27</v>
       </c>
       <c r="D264">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E264" t="s">
         <v>28</v>
@@ -8625,7 +8625,7 @@
         <v>27</v>
       </c>
       <c r="D265">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E265" t="s">
         <v>28</v>
@@ -8642,7 +8642,7 @@
         <v>27</v>
       </c>
       <c r="D266">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E266" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="D267">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E267" t="s">
         <v>28</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="D268">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E268" t="s">
         <v>28</v>
@@ -8693,7 +8693,7 @@
         <v>27</v>
       </c>
       <c r="D269">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E269" t="s">
         <v>28</v>
@@ -8710,7 +8710,7 @@
         <v>27</v>
       </c>
       <c r="D270">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E270" t="s">
         <v>28</v>
@@ -8727,7 +8727,7 @@
         <v>27</v>
       </c>
       <c r="D271">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E271" t="s">
         <v>28</v>
@@ -8744,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="D272">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E272" t="s">
         <v>28</v>
@@ -8761,7 +8761,7 @@
         <v>27</v>
       </c>
       <c r="D273">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E273" t="s">
         <v>28</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="D274">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E274" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>27</v>
       </c>
       <c r="D275">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E275" t="s">
         <v>28</v>
@@ -8812,7 +8812,7 @@
         <v>27</v>
       </c>
       <c r="D276">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E276" t="s">
         <v>28</v>
@@ -8829,7 +8829,7 @@
         <v>27</v>
       </c>
       <c r="D277">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E277" t="s">
         <v>28</v>
@@ -8846,7 +8846,7 @@
         <v>27</v>
       </c>
       <c r="D278">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E278" t="s">
         <v>28</v>
@@ -8863,7 +8863,7 @@
         <v>27</v>
       </c>
       <c r="D279">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E279" t="s">
         <v>28</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E280" t="s">
         <v>28</v>
@@ -8897,7 +8897,7 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E281" t="s">
         <v>28</v>
@@ -8914,7 +8914,7 @@
         <v>27</v>
       </c>
       <c r="D282">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E282" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="D283">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E283" t="s">
         <v>28</v>
@@ -8948,7 +8948,7 @@
         <v>27</v>
       </c>
       <c r="D284">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E284" t="s">
         <v>28</v>
@@ -8965,7 +8965,7 @@
         <v>27</v>
       </c>
       <c r="D285">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E285" t="s">
         <v>28</v>
@@ -8982,7 +8982,7 @@
         <v>27</v>
       </c>
       <c r="D286">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E286" t="s">
         <v>28</v>
@@ -8999,7 +8999,7 @@
         <v>27</v>
       </c>
       <c r="D287">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E287" t="s">
         <v>28</v>
@@ -9016,7 +9016,7 @@
         <v>27</v>
       </c>
       <c r="D288">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E288" t="s">
         <v>28</v>
@@ -9033,7 +9033,7 @@
         <v>27</v>
       </c>
       <c r="D289">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E289" t="s">
         <v>28</v>
@@ -9067,7 +9067,7 @@
         <v>27</v>
       </c>
       <c r="D291">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E291" t="s">
         <v>28</v>
@@ -9084,7 +9084,7 @@
         <v>27</v>
       </c>
       <c r="D292">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E292" t="s">
         <v>28</v>
@@ -9101,7 +9101,7 @@
         <v>27</v>
       </c>
       <c r="D293">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E293" t="s">
         <v>28</v>
@@ -9118,7 +9118,7 @@
         <v>27</v>
       </c>
       <c r="D294">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E294" t="s">
         <v>28</v>
@@ -9135,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="D295">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E295" t="s">
         <v>28</v>
@@ -9152,7 +9152,7 @@
         <v>27</v>
       </c>
       <c r="D296">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E296" t="s">
         <v>28</v>
@@ -9169,7 +9169,7 @@
         <v>27</v>
       </c>
       <c r="D297">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E297" t="s">
         <v>28</v>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="D298">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E298" t="s">
         <v>28</v>
@@ -9203,7 +9203,7 @@
         <v>27</v>
       </c>
       <c r="D299">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E299" t="s">
         <v>28</v>
@@ -9220,7 +9220,7 @@
         <v>27</v>
       </c>
       <c r="D300">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E300" t="s">
         <v>28</v>
@@ -9237,7 +9237,7 @@
         <v>27</v>
       </c>
       <c r="D301">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E301" t="s">
         <v>28</v>
@@ -9254,7 +9254,7 @@
         <v>27</v>
       </c>
       <c r="D302">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E302" t="s">
         <v>28</v>
@@ -9271,7 +9271,7 @@
         <v>27</v>
       </c>
       <c r="D303">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E303" t="s">
         <v>28</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="D304">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E304" t="s">
         <v>28</v>
@@ -9305,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="D305">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E305" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="D306">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E306" t="s">
         <v>28</v>
@@ -9339,7 +9339,7 @@
         <v>27</v>
       </c>
       <c r="D307">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E307" t="s">
         <v>28</v>
@@ -9356,7 +9356,7 @@
         <v>27</v>
       </c>
       <c r="D308">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E308" t="s">
         <v>28</v>
@@ -9373,7 +9373,7 @@
         <v>27</v>
       </c>
       <c r="D309">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E309" t="s">
         <v>28</v>
@@ -9390,7 +9390,7 @@
         <v>27</v>
       </c>
       <c r="D310">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E310" t="s">
         <v>28</v>
@@ -9407,7 +9407,7 @@
         <v>27</v>
       </c>
       <c r="D311">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E311" t="s">
         <v>28</v>
@@ -9424,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="D312">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E312" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="D313">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E313" t="s">
         <v>28</v>
@@ -9458,7 +9458,7 @@
         <v>27</v>
       </c>
       <c r="D314">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E314" t="s">
         <v>28</v>
@@ -9475,7 +9475,7 @@
         <v>27</v>
       </c>
       <c r="D315">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E315" t="s">
         <v>28</v>
@@ -9492,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="D316">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E316" t="s">
         <v>28</v>
@@ -9509,7 +9509,7 @@
         <v>27</v>
       </c>
       <c r="D317">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E317" t="s">
         <v>28</v>
@@ -9526,7 +9526,7 @@
         <v>27</v>
       </c>
       <c r="D318">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E318" t="s">
         <v>28</v>
@@ -9543,7 +9543,7 @@
         <v>27</v>
       </c>
       <c r="D319">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E319" t="s">
         <v>28</v>
@@ -9560,7 +9560,7 @@
         <v>27</v>
       </c>
       <c r="D320">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E320" t="s">
         <v>28</v>
@@ -9577,7 +9577,7 @@
         <v>27</v>
       </c>
       <c r="D321">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E321" t="s">
         <v>28</v>
@@ -9594,7 +9594,7 @@
         <v>27</v>
       </c>
       <c r="D322">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E322" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
         <v>27</v>
       </c>
       <c r="D323">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E323" t="s">
         <v>28</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="D324">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E324" t="s">
         <v>28</v>
@@ -9645,7 +9645,7 @@
         <v>27</v>
       </c>
       <c r="D325">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E325" t="s">
         <v>28</v>
@@ -9662,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="D326">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E326" t="s">
         <v>28</v>
@@ -9679,7 +9679,7 @@
         <v>27</v>
       </c>
       <c r="D327">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E327" t="s">
         <v>28</v>
@@ -9696,7 +9696,7 @@
         <v>27</v>
       </c>
       <c r="D328">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E328" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="D329">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E329" t="s">
         <v>28</v>
@@ -9730,7 +9730,7 @@
         <v>27</v>
       </c>
       <c r="D330">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E330" t="s">
         <v>28</v>
@@ -9747,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="D331">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E331" t="s">
         <v>28</v>
@@ -9764,7 +9764,7 @@
         <v>27</v>
       </c>
       <c r="D332">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E332" t="s">
         <v>28</v>
@@ -9781,7 +9781,7 @@
         <v>27</v>
       </c>
       <c r="D333">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E333" t="s">
         <v>28</v>
@@ -9798,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="D334">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E334" t="s">
         <v>28</v>
@@ -9815,7 +9815,7 @@
         <v>27</v>
       </c>
       <c r="D335">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E335" t="s">
         <v>28</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="D336">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E336" t="s">
         <v>28</v>
@@ -9849,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="D337">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E337" t="s">
         <v>28</v>
@@ -9866,7 +9866,7 @@
         <v>27</v>
       </c>
       <c r="D338">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E338" t="s">
         <v>28</v>
@@ -9900,7 +9900,7 @@
         <v>27</v>
       </c>
       <c r="D340">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E340" t="s">
         <v>28</v>
@@ -9917,7 +9917,7 @@
         <v>27</v>
       </c>
       <c r="D341">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E341" t="s">
         <v>28</v>
@@ -9934,7 +9934,7 @@
         <v>27</v>
       </c>
       <c r="D342">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E342" t="s">
         <v>28</v>
@@ -9951,7 +9951,7 @@
         <v>27</v>
       </c>
       <c r="D343">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E343" t="s">
         <v>28</v>
@@ -9968,7 +9968,7 @@
         <v>27</v>
       </c>
       <c r="D344">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E344" t="s">
         <v>28</v>
@@ -9985,7 +9985,7 @@
         <v>27</v>
       </c>
       <c r="D345">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E345" t="s">
         <v>28</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D346">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E346" t="s">
         <v>28</v>
@@ -10019,7 +10019,7 @@
         <v>27</v>
       </c>
       <c r="D347">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E347" t="s">
         <v>28</v>
@@ -10036,7 +10036,7 @@
         <v>27</v>
       </c>
       <c r="D348">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E348" t="s">
         <v>28</v>
@@ -10053,7 +10053,7 @@
         <v>27</v>
       </c>
       <c r="D349">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E349" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="D350">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E350" t="s">
         <v>28</v>
@@ -10087,7 +10087,7 @@
         <v>27</v>
       </c>
       <c r="D351">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E351" t="s">
         <v>28</v>
@@ -10104,7 +10104,7 @@
         <v>27</v>
       </c>
       <c r="D352">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E352" t="s">
         <v>28</v>
@@ -10121,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D353">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E353" t="s">
         <v>28</v>
@@ -10138,7 +10138,7 @@
         <v>27</v>
       </c>
       <c r="D354">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E354" t="s">
         <v>28</v>
@@ -10155,7 +10155,7 @@
         <v>27</v>
       </c>
       <c r="D355">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E355" t="s">
         <v>28</v>
@@ -10172,7 +10172,7 @@
         <v>27</v>
       </c>
       <c r="D356">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E356" t="s">
         <v>28</v>
@@ -10189,7 +10189,7 @@
         <v>27</v>
       </c>
       <c r="D357">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E357" t="s">
         <v>28</v>
@@ -10206,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="D358">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E358" t="s">
         <v>28</v>
@@ -10240,7 +10240,7 @@
         <v>27</v>
       </c>
       <c r="D360">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E360" t="s">
         <v>28</v>
@@ -10257,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="D361">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E361" t="s">
         <v>28</v>
@@ -10274,7 +10274,7 @@
         <v>27</v>
       </c>
       <c r="D362">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E362" t="s">
         <v>28</v>
@@ -10291,7 +10291,7 @@
         <v>27</v>
       </c>
       <c r="D363">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E363" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="D364">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E364" t="s">
         <v>28</v>
@@ -10325,7 +10325,7 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E365" t="s">
         <v>28</v>
@@ -10342,7 +10342,7 @@
         <v>27</v>
       </c>
       <c r="D366">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E366" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
         <v>27</v>
       </c>
       <c r="D367">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E367" t="s">
         <v>28</v>
@@ -10376,7 +10376,7 @@
         <v>27</v>
       </c>
       <c r="D368">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E368" t="s">
         <v>28</v>
@@ -10393,7 +10393,7 @@
         <v>27</v>
       </c>
       <c r="D369">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E369" t="s">
         <v>28</v>
@@ -10410,7 +10410,7 @@
         <v>27</v>
       </c>
       <c r="D370">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E370" t="s">
         <v>28</v>
@@ -10427,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="D371">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E371" t="s">
         <v>28</v>
@@ -10444,7 +10444,7 @@
         <v>27</v>
       </c>
       <c r="D372">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E372" t="s">
         <v>28</v>
@@ -10461,7 +10461,7 @@
         <v>27</v>
       </c>
       <c r="D373">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E373" t="s">
         <v>28</v>
@@ -10478,7 +10478,7 @@
         <v>27</v>
       </c>
       <c r="D374">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E374" t="s">
         <v>28</v>
@@ -10495,7 +10495,7 @@
         <v>27</v>
       </c>
       <c r="D375">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E375" t="s">
         <v>28</v>
@@ -10512,7 +10512,7 @@
         <v>27</v>
       </c>
       <c r="D376">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E376" t="s">
         <v>28</v>
@@ -10529,7 +10529,7 @@
         <v>27</v>
       </c>
       <c r="D377">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E377" t="s">
         <v>28</v>
@@ -10546,7 +10546,7 @@
         <v>27</v>
       </c>
       <c r="D378">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E378" t="s">
         <v>28</v>
@@ -10563,7 +10563,7 @@
         <v>27</v>
       </c>
       <c r="D379">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E379" t="s">
         <v>28</v>
@@ -10580,7 +10580,7 @@
         <v>27</v>
       </c>
       <c r="D380">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E380" t="s">
         <v>28</v>
@@ -10597,7 +10597,7 @@
         <v>27</v>
       </c>
       <c r="D381">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E381" t="s">
         <v>28</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="D382">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E382" t="s">
         <v>28</v>
@@ -10631,7 +10631,7 @@
         <v>27</v>
       </c>
       <c r="D383">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E383" t="s">
         <v>28</v>
@@ -10648,7 +10648,7 @@
         <v>27</v>
       </c>
       <c r="D384">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E384" t="s">
         <v>28</v>
@@ -10665,7 +10665,7 @@
         <v>27</v>
       </c>
       <c r="D385">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E385" t="s">
         <v>28</v>
@@ -10682,7 +10682,7 @@
         <v>27</v>
       </c>
       <c r="D386">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E386" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="D387">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E387" t="s">
         <v>28</v>
@@ -10716,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="D388">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E388" t="s">
         <v>28</v>
@@ -10733,7 +10733,7 @@
         <v>27</v>
       </c>
       <c r="D389">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E389" t="s">
         <v>28</v>
@@ -10750,7 +10750,7 @@
         <v>27</v>
       </c>
       <c r="D390">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E390" t="s">
         <v>28</v>
@@ -10767,7 +10767,7 @@
         <v>27</v>
       </c>
       <c r="D391">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E391" t="s">
         <v>28</v>
@@ -10784,7 +10784,7 @@
         <v>27</v>
       </c>
       <c r="D392">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E392" t="s">
         <v>28</v>
@@ -10801,7 +10801,7 @@
         <v>27</v>
       </c>
       <c r="D393">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E393" t="s">
         <v>28</v>
@@ -10818,7 +10818,7 @@
         <v>27</v>
       </c>
       <c r="D394">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E394" t="s">
         <v>28</v>
@@ -10835,7 +10835,7 @@
         <v>27</v>
       </c>
       <c r="D395">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E395" t="s">
         <v>28</v>
@@ -10852,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="D396">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E396" t="s">
         <v>28</v>
@@ -10869,7 +10869,7 @@
         <v>27</v>
       </c>
       <c r="D397">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E397" t="s">
         <v>28</v>
@@ -10886,7 +10886,7 @@
         <v>27</v>
       </c>
       <c r="D398">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E398" t="s">
         <v>28</v>
@@ -10903,7 +10903,7 @@
         <v>27</v>
       </c>
       <c r="D399">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E399" t="s">
         <v>28</v>
@@ -10920,7 +10920,7 @@
         <v>27</v>
       </c>
       <c r="D400">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E400" t="s">
         <v>28</v>
@@ -10937,7 +10937,7 @@
         <v>27</v>
       </c>
       <c r="D401">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E401" t="s">
         <v>28</v>
@@ -10954,7 +10954,7 @@
         <v>27</v>
       </c>
       <c r="D402">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E402" t="s">
         <v>28</v>
@@ -10971,7 +10971,7 @@
         <v>27</v>
       </c>
       <c r="D403">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E403" t="s">
         <v>28</v>
@@ -10988,7 +10988,7 @@
         <v>27</v>
       </c>
       <c r="D404">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E404" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="D405">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E405" t="s">
         <v>28</v>
@@ -11022,7 +11022,7 @@
         <v>27</v>
       </c>
       <c r="D406">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E406" t="s">
         <v>28</v>
@@ -11039,7 +11039,7 @@
         <v>27</v>
       </c>
       <c r="D407">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E407" t="s">
         <v>28</v>
@@ -11056,7 +11056,7 @@
         <v>27</v>
       </c>
       <c r="D408">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E408" t="s">
         <v>28</v>
@@ -11073,7 +11073,7 @@
         <v>27</v>
       </c>
       <c r="D409">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E409" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="D410">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E410" t="s">
         <v>28</v>
@@ -11107,7 +11107,7 @@
         <v>27</v>
       </c>
       <c r="D411">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E411" t="s">
         <v>28</v>
@@ -11141,7 +11141,7 @@
         <v>27</v>
       </c>
       <c r="D413">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E413" t="s">
         <v>28</v>
@@ -11158,7 +11158,7 @@
         <v>27</v>
       </c>
       <c r="D414">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E414" t="s">
         <v>28</v>
@@ -11175,7 +11175,7 @@
         <v>27</v>
       </c>
       <c r="D415">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E415" t="s">
         <v>28</v>
@@ -11192,7 +11192,7 @@
         <v>27</v>
       </c>
       <c r="D416">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E416" t="s">
         <v>28</v>
@@ -11209,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="D417">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E417" t="s">
         <v>28</v>
@@ -11226,7 +11226,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E418" t="s">
         <v>28</v>
@@ -11243,7 +11243,7 @@
         <v>27</v>
       </c>
       <c r="D419">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E419" t="s">
         <v>28</v>
@@ -11260,7 +11260,7 @@
         <v>27</v>
       </c>
       <c r="D420">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E420" t="s">
         <v>28</v>
@@ -11294,7 +11294,7 @@
         <v>27</v>
       </c>
       <c r="D422">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E422" t="s">
         <v>28</v>
@@ -11311,7 +11311,7 @@
         <v>27</v>
       </c>
       <c r="D423">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E423" t="s">
         <v>28</v>
@@ -11328,7 +11328,7 @@
         <v>27</v>
       </c>
       <c r="D424">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E424" t="s">
         <v>28</v>
@@ -11345,7 +11345,7 @@
         <v>27</v>
       </c>
       <c r="D425">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E425" t="s">
         <v>28</v>
@@ -11362,7 +11362,7 @@
         <v>27</v>
       </c>
       <c r="D426">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E426" t="s">
         <v>28</v>
@@ -11379,7 +11379,7 @@
         <v>27</v>
       </c>
       <c r="D427">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E427" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="D428">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E428" t="s">
         <v>28</v>
@@ -11413,7 +11413,7 @@
         <v>27</v>
       </c>
       <c r="D429">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E429" t="s">
         <v>28</v>
@@ -11430,7 +11430,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E430" t="s">
         <v>28</v>
@@ -11447,7 +11447,7 @@
         <v>27</v>
       </c>
       <c r="D431">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E431" t="s">
         <v>28</v>
@@ -11464,7 +11464,7 @@
         <v>27</v>
       </c>
       <c r="D432">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E432" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="D433">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E433" t="s">
         <v>28</v>
@@ -11498,7 +11498,7 @@
         <v>27</v>
       </c>
       <c r="D434">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E434" t="s">
         <v>28</v>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="D435">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E435" t="s">
         <v>28</v>
@@ -11532,7 +11532,7 @@
         <v>27</v>
       </c>
       <c r="D436">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E436" t="s">
         <v>28</v>
@@ -11549,7 +11549,7 @@
         <v>27</v>
       </c>
       <c r="D437">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E437" t="s">
         <v>28</v>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
       <c r="D438">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E438" t="s">
         <v>28</v>
@@ -11583,7 +11583,7 @@
         <v>27</v>
       </c>
       <c r="D439">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E439" t="s">
         <v>28</v>
@@ -11617,7 +11617,7 @@
         <v>27</v>
       </c>
       <c r="D441">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E441" t="s">
         <v>28</v>
@@ -11634,7 +11634,7 @@
         <v>27</v>
       </c>
       <c r="D442">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E442" t="s">
         <v>28</v>
@@ -11651,7 +11651,7 @@
         <v>27</v>
       </c>
       <c r="D443">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E443" t="s">
         <v>28</v>
@@ -11668,7 +11668,7 @@
         <v>27</v>
       </c>
       <c r="D444">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E444" t="s">
         <v>28</v>
@@ -11685,7 +11685,7 @@
         <v>27</v>
       </c>
       <c r="D445">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E445" t="s">
         <v>28</v>
@@ -11702,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D446">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E446" t="s">
         <v>28</v>
@@ -11719,7 +11719,7 @@
         <v>27</v>
       </c>
       <c r="D447">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E447" t="s">
         <v>28</v>
@@ -11736,7 +11736,7 @@
         <v>27</v>
       </c>
       <c r="D448">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E448" t="s">
         <v>28</v>
@@ -11753,7 +11753,7 @@
         <v>27</v>
       </c>
       <c r="D449">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E449" t="s">
         <v>28</v>
@@ -11770,7 +11770,7 @@
         <v>27</v>
       </c>
       <c r="D450">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E450" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="D451">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E451" t="s">
         <v>28</v>
@@ -11804,7 +11804,7 @@
         <v>27</v>
       </c>
       <c r="D452">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E452" t="s">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>27</v>
       </c>
       <c r="D453">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E453" t="s">
         <v>28</v>
@@ -11855,7 +11855,7 @@
         <v>27</v>
       </c>
       <c r="D455">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E455" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="D456">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E456" t="s">
         <v>28</v>
@@ -11889,7 +11889,7 @@
         <v>27</v>
       </c>
       <c r="D457">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E457" t="s">
         <v>28</v>
@@ -11906,7 +11906,7 @@
         <v>27</v>
       </c>
       <c r="D458">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E458" t="s">
         <v>28</v>
@@ -11940,7 +11940,7 @@
         <v>27</v>
       </c>
       <c r="D460">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E460" t="s">
         <v>28</v>
@@ -11974,7 +11974,7 @@
         <v>27</v>
       </c>
       <c r="D462">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E462" t="s">
         <v>28</v>
@@ -11991,7 +11991,7 @@
         <v>27</v>
       </c>
       <c r="D463">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E463" t="s">
         <v>28</v>
@@ -12008,7 +12008,7 @@
         <v>27</v>
       </c>
       <c r="D464">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E464" t="s">
         <v>28</v>
@@ -12025,7 +12025,7 @@
         <v>27</v>
       </c>
       <c r="D465">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E465" t="s">
         <v>28</v>
@@ -12042,7 +12042,7 @@
         <v>27</v>
       </c>
       <c r="D466">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E466" t="s">
         <v>28</v>
@@ -12059,7 +12059,7 @@
         <v>27</v>
       </c>
       <c r="D467">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E467" t="s">
         <v>28</v>
@@ -12093,7 +12093,7 @@
         <v>27</v>
       </c>
       <c r="D469">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E469" t="s">
         <v>28</v>
@@ -12110,7 +12110,7 @@
         <v>27</v>
       </c>
       <c r="D470">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E470" t="s">
         <v>28</v>
@@ -12127,7 +12127,7 @@
         <v>27</v>
       </c>
       <c r="D471">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E471" t="s">
         <v>28</v>
@@ -12144,7 +12144,7 @@
         <v>27</v>
       </c>
       <c r="D472">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E472" t="s">
         <v>28</v>
@@ -12161,7 +12161,7 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E473" t="s">
         <v>28</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="D474">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E474" t="s">
         <v>28</v>
@@ -12195,7 +12195,7 @@
         <v>27</v>
       </c>
       <c r="D475">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E475" t="s">
         <v>28</v>
@@ -12212,7 +12212,7 @@
         <v>27</v>
       </c>
       <c r="D476">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E476" t="s">
         <v>28</v>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
       <c r="D477">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E477" t="s">
         <v>28</v>
@@ -12246,7 +12246,7 @@
         <v>27</v>
       </c>
       <c r="D478">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E478" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="D479">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E479" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="D480">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E480" t="s">
         <v>28</v>
@@ -12297,7 +12297,7 @@
         <v>27</v>
       </c>
       <c r="D481">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E481" t="s">
         <v>28</v>
@@ -12314,7 +12314,7 @@
         <v>27</v>
       </c>
       <c r="D482">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E482" t="s">
         <v>28</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="D483">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E483" t="s">
         <v>28</v>
@@ -12348,7 +12348,7 @@
         <v>27</v>
       </c>
       <c r="D484">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E484" t="s">
         <v>28</v>
@@ -12365,7 +12365,7 @@
         <v>27</v>
       </c>
       <c r="D485">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E485" t="s">
         <v>28</v>
@@ -12382,7 +12382,7 @@
         <v>27</v>
       </c>
       <c r="D486">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E486" t="s">
         <v>28</v>
@@ -12399,7 +12399,7 @@
         <v>27</v>
       </c>
       <c r="D487">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E487" t="s">
         <v>28</v>
@@ -12416,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="D488">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E488" t="s">
         <v>28</v>
@@ -12433,7 +12433,7 @@
         <v>27</v>
       </c>
       <c r="D489">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E489" t="s">
         <v>28</v>
@@ -12450,7 +12450,7 @@
         <v>27</v>
       </c>
       <c r="D490">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E490" t="s">
         <v>28</v>
@@ -12467,7 +12467,7 @@
         <v>27</v>
       </c>
       <c r="D491">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E491" t="s">
         <v>28</v>
@@ -12484,7 +12484,7 @@
         <v>27</v>
       </c>
       <c r="D492">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E492" t="s">
         <v>28</v>
@@ -12501,7 +12501,7 @@
         <v>27</v>
       </c>
       <c r="D493">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E493" t="s">
         <v>28</v>
@@ -12518,7 +12518,7 @@
         <v>27</v>
       </c>
       <c r="D494">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E494" t="s">
         <v>28</v>
@@ -12535,7 +12535,7 @@
         <v>27</v>
       </c>
       <c r="D495">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E495" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="D497">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E497" t="s">
         <v>28</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D499">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E499" t="s">
         <v>28</v>
@@ -12620,7 +12620,7 @@
         <v>27</v>
       </c>
       <c r="D500">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E500" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="D502">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E502" t="s">
         <v>28</v>
@@ -12671,7 +12671,7 @@
         <v>27</v>
       </c>
       <c r="D503">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E503" t="s">
         <v>28</v>
@@ -12688,7 +12688,7 @@
         <v>27</v>
       </c>
       <c r="D504">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E504" t="s">
         <v>28</v>
@@ -12705,7 +12705,7 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E505" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="D506">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E506" t="s">
         <v>28</v>
@@ -12739,7 +12739,7 @@
         <v>27</v>
       </c>
       <c r="D507">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E507" t="s">
         <v>28</v>
@@ -12756,7 +12756,7 @@
         <v>27</v>
       </c>
       <c r="D508">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E508" t="s">
         <v>28</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="D509">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E509" t="s">
         <v>28</v>
@@ -12807,7 +12807,7 @@
         <v>27</v>
       </c>
       <c r="D511">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E511" t="s">
         <v>28</v>
@@ -12824,7 +12824,7 @@
         <v>27</v>
       </c>
       <c r="D512">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E512" t="s">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27</v>
       </c>
       <c r="D513">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E513" t="s">
         <v>28</v>
@@ -12858,7 +12858,7 @@
         <v>27</v>
       </c>
       <c r="D514">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E514" t="s">
         <v>28</v>
@@ -12892,7 +12892,7 @@
         <v>27</v>
       </c>
       <c r="D516">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E516" t="s">
         <v>28</v>
@@ -12926,7 +12926,7 @@
         <v>27</v>
       </c>
       <c r="D518">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E518" t="s">
         <v>28</v>
@@ -12943,7 +12943,7 @@
         <v>27</v>
       </c>
       <c r="D519">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E519" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="D520">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E520" t="s">
         <v>28</v>
@@ -12977,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="D521">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E521" t="s">
         <v>28</v>
@@ -12994,7 +12994,7 @@
         <v>27</v>
       </c>
       <c r="D522">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E522" t="s">
         <v>28</v>
@@ -13011,7 +13011,7 @@
         <v>27</v>
       </c>
       <c r="D523">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E523" t="s">
         <v>28</v>
@@ -13028,7 +13028,7 @@
         <v>27</v>
       </c>
       <c r="D524">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E524" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="D525">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E525" t="s">
         <v>28</v>
@@ -13062,7 +13062,7 @@
         <v>27</v>
       </c>
       <c r="D526">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E526" t="s">
         <v>28</v>
@@ -13079,7 +13079,7 @@
         <v>27</v>
       </c>
       <c r="D527">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E527" t="s">
         <v>28</v>
@@ -13096,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="D528">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E528" t="s">
         <v>28</v>
@@ -13113,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="D529">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
@@ -13130,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -13147,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="D531">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
@@ -13164,7 +13164,7 @@
         <v>27</v>
       </c>
       <c r="D532">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E532" t="s">
         <v>28</v>
@@ -13181,7 +13181,7 @@
         <v>27</v>
       </c>
       <c r="D533">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E533" t="s">
         <v>28</v>
@@ -13198,7 +13198,7 @@
         <v>27</v>
       </c>
       <c r="D534">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E534" t="s">
         <v>28</v>
@@ -13232,7 +13232,7 @@
         <v>27</v>
       </c>
       <c r="D536">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E536" t="s">
         <v>28</v>
@@ -13249,7 +13249,7 @@
         <v>27</v>
       </c>
       <c r="D537">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E537" t="s">
         <v>28</v>
@@ -13283,7 +13283,7 @@
         <v>27</v>
       </c>
       <c r="D539">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E539" t="s">
         <v>28</v>
@@ -13300,7 +13300,7 @@
         <v>27</v>
       </c>
       <c r="D540">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E540" t="s">
         <v>28</v>
@@ -13317,7 +13317,7 @@
         <v>27</v>
       </c>
       <c r="D541">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E541" t="s">
         <v>28</v>
@@ -13334,7 +13334,7 @@
         <v>27</v>
       </c>
       <c r="D542">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E542" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="D543">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E543" t="s">
         <v>28</v>
@@ -13368,7 +13368,7 @@
         <v>27</v>
       </c>
       <c r="D544">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E544" t="s">
         <v>28</v>
@@ -13385,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="D545">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
@@ -13402,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="D546">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
@@ -13419,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="D547">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E547" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="D548">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E548" t="s">
         <v>28</v>
@@ -13453,7 +13453,7 @@
         <v>27</v>
       </c>
       <c r="D549">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E549" t="s">
         <v>28</v>
@@ -13470,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="D550">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E550" t="s">
         <v>28</v>
@@ -13487,7 +13487,7 @@
         <v>27</v>
       </c>
       <c r="D551">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E551" t="s">
         <v>28</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="D552">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -13521,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="D553">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E553" t="s">
         <v>28</v>
@@ -13538,7 +13538,7 @@
         <v>27</v>
       </c>
       <c r="D554">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E554" t="s">
         <v>28</v>
@@ -13555,7 +13555,7 @@
         <v>27</v>
       </c>
       <c r="D555">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E555" t="s">
         <v>28</v>
@@ -13572,7 +13572,7 @@
         <v>27</v>
       </c>
       <c r="D556">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E556" t="s">
         <v>28</v>
@@ -13589,7 +13589,7 @@
         <v>27</v>
       </c>
       <c r="D557">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E557" t="s">
         <v>28</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="D558">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E558" t="s">
         <v>28</v>
@@ -13623,7 +13623,7 @@
         <v>27</v>
       </c>
       <c r="D559">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -13640,7 +13640,7 @@
         <v>27</v>
       </c>
       <c r="D560">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
@@ -13657,7 +13657,7 @@
         <v>27</v>
       </c>
       <c r="D561">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E561" t="s">
         <v>28</v>
@@ -13674,7 +13674,7 @@
         <v>27</v>
       </c>
       <c r="D562">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E562" t="s">
         <v>28</v>
@@ -13691,7 +13691,7 @@
         <v>27</v>
       </c>
       <c r="D563">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E563" t="s">
         <v>28</v>
@@ -13708,7 +13708,7 @@
         <v>27</v>
       </c>
       <c r="D564">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E564" t="s">
         <v>28</v>
@@ -13725,7 +13725,7 @@
         <v>27</v>
       </c>
       <c r="D565">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E565" t="s">
         <v>28</v>
@@ -13759,7 +13759,7 @@
         <v>27</v>
       </c>
       <c r="D567">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E567" t="s">
         <v>28</v>
@@ -13776,7 +13776,7 @@
         <v>27</v>
       </c>
       <c r="D568">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E568" t="s">
         <v>28</v>
@@ -13793,7 +13793,7 @@
         <v>27</v>
       </c>
       <c r="D569">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
@@ -13810,7 +13810,7 @@
         <v>27</v>
       </c>
       <c r="D570">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E570" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="D571">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E571" t="s">
         <v>28</v>
@@ -13844,7 +13844,7 @@
         <v>27</v>
       </c>
       <c r="D572">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E572" t="s">
         <v>28</v>
@@ -13861,7 +13861,7 @@
         <v>27</v>
       </c>
       <c r="D573">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E573" t="s">
         <v>28</v>
@@ -13878,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="D574">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E574" t="s">
         <v>28</v>
@@ -13895,7 +13895,7 @@
         <v>27</v>
       </c>
       <c r="D575">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E575" t="s">
         <v>28</v>
@@ -13912,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="D576">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E576" t="s">
         <v>28</v>
@@ -13929,7 +13929,7 @@
         <v>27</v>
       </c>
       <c r="D577">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E577" t="s">
         <v>28</v>
@@ -13946,7 +13946,7 @@
         <v>27</v>
       </c>
       <c r="D578">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E578" t="s">
         <v>28</v>
@@ -13963,7 +13963,7 @@
         <v>27</v>
       </c>
       <c r="D579">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E579" t="s">
         <v>28</v>
@@ -13980,7 +13980,7 @@
         <v>27</v>
       </c>
       <c r="D580">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E580" t="s">
         <v>28</v>
@@ -13997,7 +13997,7 @@
         <v>27</v>
       </c>
       <c r="D581">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E581" t="s">
         <v>28</v>
@@ -14014,7 +14014,7 @@
         <v>27</v>
       </c>
       <c r="D582">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E582" t="s">
         <v>28</v>
@@ -14031,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="D583">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E583" t="s">
         <v>28</v>
@@ -14048,7 +14048,7 @@
         <v>27</v>
       </c>
       <c r="D584">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E584" t="s">
         <v>28</v>
@@ -14065,7 +14065,7 @@
         <v>27</v>
       </c>
       <c r="D585">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E585" t="s">
         <v>28</v>
@@ -14082,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="D586">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E586" t="s">
         <v>28</v>
@@ -14099,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="D587">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E587" t="s">
         <v>28</v>
@@ -14116,7 +14116,7 @@
         <v>27</v>
       </c>
       <c r="D588">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E588" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="D589">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
@@ -14150,7 +14150,7 @@
         <v>27</v>
       </c>
       <c r="D590">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
@@ -14167,7 +14167,7 @@
         <v>27</v>
       </c>
       <c r="D591">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E591" t="s">
         <v>28</v>
@@ -14184,7 +14184,7 @@
         <v>27</v>
       </c>
       <c r="D592">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E592" t="s">
         <v>28</v>
@@ -14201,7 +14201,7 @@
         <v>27</v>
       </c>
       <c r="D593">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E593" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="D594">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E594" t="s">
         <v>28</v>
@@ -14252,7 +14252,7 @@
         <v>27</v>
       </c>
       <c r="D596">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
@@ -14269,7 +14269,7 @@
         <v>27</v>
       </c>
       <c r="D597">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
@@ -14286,7 +14286,7 @@
         <v>27</v>
       </c>
       <c r="D598">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
@@ -14303,7 +14303,7 @@
         <v>27</v>
       </c>
       <c r="D599">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="D600">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
@@ -14354,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="D602">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
@@ -14371,7 +14371,7 @@
         <v>27</v>
       </c>
       <c r="D603">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
@@ -14388,7 +14388,7 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
@@ -14405,7 +14405,7 @@
         <v>27</v>
       </c>
       <c r="D605">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E605" t="s">
         <v>28</v>
@@ -14422,7 +14422,7 @@
         <v>27</v>
       </c>
       <c r="D606">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E606" t="s">
         <v>28</v>
@@ -14439,7 +14439,7 @@
         <v>27</v>
       </c>
       <c r="D607">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E607" t="s">
         <v>28</v>
@@ -14456,7 +14456,7 @@
         <v>27</v>
       </c>
       <c r="D608">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
@@ -14490,7 +14490,7 @@
         <v>27</v>
       </c>
       <c r="D610">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E610" t="s">
         <v>28</v>
@@ -14507,7 +14507,7 @@
         <v>27</v>
       </c>
       <c r="D611">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E611" t="s">
         <v>28</v>
@@ -14541,7 +14541,7 @@
         <v>27</v>
       </c>
       <c r="D613">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E613" t="s">
         <v>28</v>
@@ -14558,7 +14558,7 @@
         <v>27</v>
       </c>
       <c r="D614">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E614" t="s">
         <v>28</v>
@@ -14575,7 +14575,7 @@
         <v>27</v>
       </c>
       <c r="D615">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E615" t="s">
         <v>28</v>
@@ -14592,7 +14592,7 @@
         <v>27</v>
       </c>
       <c r="D616">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E616" t="s">
         <v>28</v>
@@ -14626,7 +14626,7 @@
         <v>27</v>
       </c>
       <c r="D618">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E618" t="s">
         <v>28</v>
@@ -14643,7 +14643,7 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E619" t="s">
         <v>28</v>
@@ -14660,7 +14660,7 @@
         <v>27</v>
       </c>
       <c r="D620">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E620" t="s">
         <v>28</v>
@@ -14677,7 +14677,7 @@
         <v>27</v>
       </c>
       <c r="D621">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E621" t="s">
         <v>28</v>
@@ -14694,7 +14694,7 @@
         <v>27</v>
       </c>
       <c r="D622">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E622" t="s">
         <v>28</v>
@@ -14711,7 +14711,7 @@
         <v>27</v>
       </c>
       <c r="D623">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E623" t="s">
         <v>28</v>
@@ -14728,7 +14728,7 @@
         <v>27</v>
       </c>
       <c r="D624">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E624" t="s">
         <v>28</v>
@@ -14745,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="D625">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E625" t="s">
         <v>28</v>
@@ -14779,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="D627">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E627" t="s">
         <v>28</v>
@@ -14796,7 +14796,7 @@
         <v>27</v>
       </c>
       <c r="D628">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E628" t="s">
         <v>28</v>
@@ -14813,7 +14813,7 @@
         <v>27</v>
       </c>
       <c r="D629">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E629" t="s">
         <v>28</v>
@@ -14830,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="D630">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E630" t="s">
         <v>28</v>
@@ -14847,7 +14847,7 @@
         <v>27</v>
       </c>
       <c r="D631">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E631" t="s">
         <v>28</v>
@@ -14864,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D632">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E632" t="s">
         <v>28</v>
@@ -14881,7 +14881,7 @@
         <v>27</v>
       </c>
       <c r="D633">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E633" t="s">
         <v>28</v>
@@ -14898,7 +14898,7 @@
         <v>27</v>
       </c>
       <c r="D634">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E634" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="D635">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E635" t="s">
         <v>28</v>
@@ -14932,7 +14932,7 @@
         <v>27</v>
       </c>
       <c r="D636">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E636" t="s">
         <v>28</v>
@@ -14949,7 +14949,7 @@
         <v>27</v>
       </c>
       <c r="D637">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E637" t="s">
         <v>28</v>
@@ -14966,7 +14966,7 @@
         <v>27</v>
       </c>
       <c r="D638">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E638" t="s">
         <v>28</v>
@@ -14983,7 +14983,7 @@
         <v>27</v>
       </c>
       <c r="D639">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E639" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E640" t="s">
         <v>28</v>
@@ -15017,7 +15017,7 @@
         <v>27</v>
       </c>
       <c r="D641">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E641" t="s">
         <v>28</v>
@@ -15034,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="D642">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E642" t="s">
         <v>28</v>
@@ -15051,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="D643">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E643" t="s">
         <v>28</v>
@@ -15068,7 +15068,7 @@
         <v>27</v>
       </c>
       <c r="D644">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E644" t="s">
         <v>28</v>
@@ -15085,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="D645">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E645" t="s">
         <v>28</v>
@@ -15102,7 +15102,7 @@
         <v>27</v>
       </c>
       <c r="D646">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E646" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>27</v>
       </c>
       <c r="D647">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E647" t="s">
         <v>28</v>
@@ -15136,7 +15136,7 @@
         <v>27</v>
       </c>
       <c r="D648">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E648" t="s">
         <v>28</v>
@@ -15153,7 +15153,7 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E649" t="s">
         <v>28</v>
@@ -15170,7 +15170,7 @@
         <v>27</v>
       </c>
       <c r="D650">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E650" t="s">
         <v>28</v>
@@ -15187,7 +15187,7 @@
         <v>27</v>
       </c>
       <c r="D651">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E651" t="s">
         <v>28</v>
@@ -15204,7 +15204,7 @@
         <v>27</v>
       </c>
       <c r="D652">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E652" t="s">
         <v>28</v>
@@ -15221,7 +15221,7 @@
         <v>27</v>
       </c>
       <c r="D653">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E653" t="s">
         <v>28</v>
@@ -15255,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="D655">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E655" t="s">
         <v>28</v>
@@ -15272,7 +15272,7 @@
         <v>27</v>
       </c>
       <c r="D656">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
@@ -15289,7 +15289,7 @@
         <v>27</v>
       </c>
       <c r="D657">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E657" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
@@ -15323,7 +15323,7 @@
         <v>27</v>
       </c>
       <c r="D659">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E659" t="s">
         <v>28</v>
@@ -15340,7 +15340,7 @@
         <v>27</v>
       </c>
       <c r="D660">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E660" t="s">
         <v>28</v>
@@ -15357,7 +15357,7 @@
         <v>27</v>
       </c>
       <c r="D661">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E661" t="s">
         <v>28</v>
@@ -15374,7 +15374,7 @@
         <v>27</v>
       </c>
       <c r="D662">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E662" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="D663">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E663" t="s">
         <v>28</v>
@@ -15408,7 +15408,7 @@
         <v>27</v>
       </c>
       <c r="D664">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E664" t="s">
         <v>28</v>
@@ -15425,7 +15425,7 @@
         <v>27</v>
       </c>
       <c r="D665">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E665" t="s">
         <v>28</v>
@@ -15442,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="D666">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E666" t="s">
         <v>28</v>
@@ -15459,7 +15459,7 @@
         <v>27</v>
       </c>
       <c r="D667">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E667" t="s">
         <v>28</v>
@@ -15476,7 +15476,7 @@
         <v>27</v>
       </c>
       <c r="D668">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E668" t="s">
         <v>28</v>
@@ -15493,7 +15493,7 @@
         <v>27</v>
       </c>
       <c r="D669">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E669" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>27</v>
       </c>
       <c r="D670">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E670" t="s">
         <v>28</v>
@@ -15527,7 +15527,7 @@
         <v>27</v>
       </c>
       <c r="D671">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E671" t="s">
         <v>28</v>
@@ -15544,7 +15544,7 @@
         <v>27</v>
       </c>
       <c r="D672">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E672" t="s">
         <v>28</v>
@@ -15578,7 +15578,7 @@
         <v>27</v>
       </c>
       <c r="D674">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E674" t="s">
         <v>28</v>
@@ -15595,7 +15595,7 @@
         <v>27</v>
       </c>
       <c r="D675">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E675" t="s">
         <v>28</v>
@@ -15612,7 +15612,7 @@
         <v>27</v>
       </c>
       <c r="D676">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E676" t="s">
         <v>28</v>
@@ -15629,7 +15629,7 @@
         <v>27</v>
       </c>
       <c r="D677">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E677" t="s">
         <v>28</v>
@@ -15646,7 +15646,7 @@
         <v>27</v>
       </c>
       <c r="D678">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E678" t="s">
         <v>28</v>
@@ -15663,7 +15663,7 @@
         <v>27</v>
       </c>
       <c r="D679">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E679" t="s">
         <v>28</v>
@@ -15680,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="D680">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E680" t="s">
         <v>28</v>
@@ -15697,7 +15697,7 @@
         <v>27</v>
       </c>
       <c r="D681">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E681" t="s">
         <v>28</v>
@@ -15731,7 +15731,7 @@
         <v>27</v>
       </c>
       <c r="D683">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E683" t="s">
         <v>28</v>
@@ -15748,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="D684">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E684" t="s">
         <v>28</v>
@@ -15765,7 +15765,7 @@
         <v>27</v>
       </c>
       <c r="D685">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E685" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="D686">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E686" t="s">
         <v>28</v>
@@ -15799,7 +15799,7 @@
         <v>27</v>
       </c>
       <c r="D687">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E687" t="s">
         <v>28</v>
@@ -15816,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="D688">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E688" t="s">
         <v>28</v>
@@ -15833,7 +15833,7 @@
         <v>27</v>
       </c>
       <c r="D689">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E689" t="s">
         <v>28</v>
@@ -15850,7 +15850,7 @@
         <v>27</v>
       </c>
       <c r="D690">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E690" t="s">
         <v>28</v>
@@ -15867,7 +15867,7 @@
         <v>27</v>
       </c>
       <c r="D691">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E691" t="s">
         <v>28</v>
@@ -15884,7 +15884,7 @@
         <v>27</v>
       </c>
       <c r="D692">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E692" t="s">
         <v>28</v>
@@ -15901,7 +15901,7 @@
         <v>27</v>
       </c>
       <c r="D693">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E693" t="s">
         <v>28</v>
@@ -15918,7 +15918,7 @@
         <v>27</v>
       </c>
       <c r="D694">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E694" t="s">
         <v>28</v>
@@ -15969,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="D697">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E697" t="s">
         <v>28</v>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
       <c r="D698">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E698" t="s">
         <v>28</v>
@@ -16003,7 +16003,7 @@
         <v>27</v>
       </c>
       <c r="D699">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E699" t="s">
         <v>28</v>
@@ -16020,7 +16020,7 @@
         <v>27</v>
       </c>
       <c r="D700">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E700" t="s">
         <v>28</v>
@@ -16037,7 +16037,7 @@
         <v>27</v>
       </c>
       <c r="D701">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E701" t="s">
         <v>28</v>
@@ -16054,7 +16054,7 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E702" t="s">
         <v>28</v>
@@ -16071,7 +16071,7 @@
         <v>27</v>
       </c>
       <c r="D703">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E703" t="s">
         <v>28</v>
@@ -16088,7 +16088,7 @@
         <v>27</v>
       </c>
       <c r="D704">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E704" t="s">
         <v>28</v>
@@ -16105,7 +16105,7 @@
         <v>27</v>
       </c>
       <c r="D705">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E705" t="s">
         <v>28</v>
@@ -16122,7 +16122,7 @@
         <v>27</v>
       </c>
       <c r="D706">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E706" t="s">
         <v>28</v>
@@ -16139,7 +16139,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E707" t="s">
         <v>28</v>
@@ -16156,7 +16156,7 @@
         <v>27</v>
       </c>
       <c r="D708">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E708" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="D709">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E709" t="s">
         <v>28</v>
@@ -16190,7 +16190,7 @@
         <v>27</v>
       </c>
       <c r="D710">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E710" t="s">
         <v>28</v>
@@ -16207,7 +16207,7 @@
         <v>27</v>
       </c>
       <c r="D711">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E711" t="s">
         <v>28</v>
@@ -16224,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="D712">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E712" t="s">
         <v>28</v>
@@ -16241,7 +16241,7 @@
         <v>27</v>
       </c>
       <c r="D713">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E713" t="s">
         <v>28</v>
@@ -16258,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="D714">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E714" t="s">
         <v>28</v>
@@ -16275,7 +16275,7 @@
         <v>27</v>
       </c>
       <c r="D715">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E715" t="s">
         <v>28</v>
@@ -16292,7 +16292,7 @@
         <v>27</v>
       </c>
       <c r="D716">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E716" t="s">
         <v>28</v>
@@ -16309,7 +16309,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E717" t="s">
         <v>28</v>
@@ -16326,7 +16326,7 @@
         <v>27</v>
       </c>
       <c r="D718">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E718" t="s">
         <v>28</v>
@@ -16343,7 +16343,7 @@
         <v>27</v>
       </c>
       <c r="D719">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E719" t="s">
         <v>28</v>
@@ -16360,7 +16360,7 @@
         <v>27</v>
       </c>
       <c r="D720">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E720" t="s">
         <v>28</v>
@@ -16377,7 +16377,7 @@
         <v>27</v>
       </c>
       <c r="D721">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E721" t="s">
         <v>28</v>
@@ -16394,7 +16394,7 @@
         <v>27</v>
       </c>
       <c r="D722">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E722" t="s">
         <v>28</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="D723">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E723" t="s">
         <v>28</v>
@@ -16428,7 +16428,7 @@
         <v>27</v>
       </c>
       <c r="D724">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E724" t="s">
         <v>28</v>
@@ -16462,7 +16462,7 @@
         <v>27</v>
       </c>
       <c r="D726">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E726" t="s">
         <v>28</v>
@@ -16479,7 +16479,7 @@
         <v>27</v>
       </c>
       <c r="D727">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E727" t="s">
         <v>28</v>
@@ -16496,7 +16496,7 @@
         <v>27</v>
       </c>
       <c r="D728">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E728" t="s">
         <v>28</v>
@@ -16513,7 +16513,7 @@
         <v>27</v>
       </c>
       <c r="D729">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E729" t="s">
         <v>28</v>
@@ -16530,7 +16530,7 @@
         <v>27</v>
       </c>
       <c r="D730">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E730" t="s">
         <v>28</v>
@@ -16547,7 +16547,7 @@
         <v>27</v>
       </c>
       <c r="D731">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E731" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="D732">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E732" t="s">
         <v>28</v>
@@ -16581,7 +16581,7 @@
         <v>27</v>
       </c>
       <c r="D733">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E733" t="s">
         <v>28</v>
@@ -16615,7 +16615,7 @@
         <v>27</v>
       </c>
       <c r="D735">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E735" t="s">
         <v>28</v>
@@ -16632,7 +16632,7 @@
         <v>27</v>
       </c>
       <c r="D736">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E736" t="s">
         <v>28</v>
@@ -16649,7 +16649,7 @@
         <v>27</v>
       </c>
       <c r="D737">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E737" t="s">
         <v>28</v>
@@ -16666,7 +16666,7 @@
         <v>27</v>
       </c>
       <c r="D738">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E738" t="s">
         <v>28</v>
@@ -16683,7 +16683,7 @@
         <v>27</v>
       </c>
       <c r="D739">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E739" t="s">
         <v>28</v>
@@ -16700,7 +16700,7 @@
         <v>27</v>
       </c>
       <c r="D740">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E740" t="s">
         <v>28</v>
@@ -16717,7 +16717,7 @@
         <v>27</v>
       </c>
       <c r="D741">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E741" t="s">
         <v>28</v>
@@ -16734,7 +16734,7 @@
         <v>27</v>
       </c>
       <c r="D742">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E742" t="s">
         <v>28</v>
@@ -16751,7 +16751,7 @@
         <v>27</v>
       </c>
       <c r="D743">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E743" t="s">
         <v>28</v>
@@ -16768,7 +16768,7 @@
         <v>27</v>
       </c>
       <c r="D744">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E744" t="s">
         <v>28</v>
@@ -16785,7 +16785,7 @@
         <v>27</v>
       </c>
       <c r="D745">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E745" t="s">
         <v>28</v>
@@ -16802,7 +16802,7 @@
         <v>27</v>
       </c>
       <c r="D746">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E746" t="s">
         <v>28</v>
@@ -16819,7 +16819,7 @@
         <v>27</v>
       </c>
       <c r="D747">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E747" t="s">
         <v>28</v>
@@ -16836,7 +16836,7 @@
         <v>27</v>
       </c>
       <c r="D748">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E748" t="s">
         <v>28</v>
@@ -16853,7 +16853,7 @@
         <v>27</v>
       </c>
       <c r="D749">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E749" t="s">
         <v>28</v>
@@ -16870,7 +16870,7 @@
         <v>27</v>
       </c>
       <c r="D750">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E750" t="s">
         <v>28</v>
@@ -16887,7 +16887,7 @@
         <v>27</v>
       </c>
       <c r="D751">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E751" t="s">
         <v>28</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="D752">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E752" t="s">
         <v>28</v>
@@ -16921,7 +16921,7 @@
         <v>27</v>
       </c>
       <c r="D753">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E753" t="s">
         <v>28</v>
@@ -16938,7 +16938,7 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E754" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="D755">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E755" t="s">
         <v>28</v>
@@ -16972,7 +16972,7 @@
         <v>27</v>
       </c>
       <c r="D756">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E756" t="s">
         <v>28</v>
@@ -16989,7 +16989,7 @@
         <v>27</v>
       </c>
       <c r="D757">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E757" t="s">
         <v>28</v>
@@ -17023,7 +17023,7 @@
         <v>27</v>
       </c>
       <c r="D759">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E759" t="s">
         <v>28</v>
@@ -17040,7 +17040,7 @@
         <v>27</v>
       </c>
       <c r="D760">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E760" t="s">
         <v>28</v>
@@ -17057,7 +17057,7 @@
         <v>27</v>
       </c>
       <c r="D761">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E761" t="s">
         <v>28</v>
@@ -17074,7 +17074,7 @@
         <v>27</v>
       </c>
       <c r="D762">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E762" t="s">
         <v>28</v>
@@ -17091,7 +17091,7 @@
         <v>27</v>
       </c>
       <c r="D763">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E763" t="s">
         <v>28</v>
@@ -17108,7 +17108,7 @@
         <v>27</v>
       </c>
       <c r="D764">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E764" t="s">
         <v>28</v>
@@ -17125,7 +17125,7 @@
         <v>27</v>
       </c>
       <c r="D765">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E765" t="s">
         <v>28</v>
@@ -17142,7 +17142,7 @@
         <v>27</v>
       </c>
       <c r="D766">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E766" t="s">
         <v>28</v>
@@ -17159,7 +17159,7 @@
         <v>27</v>
       </c>
       <c r="D767">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E767" t="s">
         <v>28</v>
@@ -17176,7 +17176,7 @@
         <v>27</v>
       </c>
       <c r="D768">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E768" t="s">
         <v>28</v>
@@ -17193,7 +17193,7 @@
         <v>27</v>
       </c>
       <c r="D769">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E769" t="s">
         <v>28</v>
@@ -17210,7 +17210,7 @@
         <v>27</v>
       </c>
       <c r="D770">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E770" t="s">
         <v>28</v>
@@ -17227,7 +17227,7 @@
         <v>27</v>
       </c>
       <c r="D771">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E771" t="s">
         <v>28</v>
@@ -17244,7 +17244,7 @@
         <v>27</v>
       </c>
       <c r="D772">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E772" t="s">
         <v>28</v>
@@ -17261,7 +17261,7 @@
         <v>27</v>
       </c>
       <c r="D773">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E773" t="s">
         <v>28</v>
@@ -17278,7 +17278,7 @@
         <v>27</v>
       </c>
       <c r="D774">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E774" t="s">
         <v>28</v>
@@ -17295,7 +17295,7 @@
         <v>27</v>
       </c>
       <c r="D775">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E775" t="s">
         <v>28</v>
@@ -17312,7 +17312,7 @@
         <v>27</v>
       </c>
       <c r="D776">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E776" t="s">
         <v>28</v>
@@ -17329,7 +17329,7 @@
         <v>27</v>
       </c>
       <c r="D777">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E777" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="D778">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E778" t="s">
         <v>28</v>
@@ -17363,7 +17363,7 @@
         <v>27</v>
       </c>
       <c r="D779">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E779" t="s">
         <v>28</v>
@@ -17380,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="D780">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E780" t="s">
         <v>28</v>
@@ -17397,7 +17397,7 @@
         <v>27</v>
       </c>
       <c r="D781">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E781" t="s">
         <v>28</v>
@@ -17414,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="D782">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E782" t="s">
         <v>28</v>
@@ -17431,7 +17431,7 @@
         <v>27</v>
       </c>
       <c r="D783">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E783" t="s">
         <v>28</v>
@@ -17448,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D784">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E784" t="s">
         <v>28</v>
@@ -17465,7 +17465,7 @@
         <v>27</v>
       </c>
       <c r="D785">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E785" t="s">
         <v>28</v>
@@ -17482,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="D786">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E786" t="s">
         <v>28</v>
@@ -17499,7 +17499,7 @@
         <v>27</v>
       </c>
       <c r="D787">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E787" t="s">
         <v>28</v>
@@ -17516,7 +17516,7 @@
         <v>27</v>
       </c>
       <c r="D788">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E788" t="s">
         <v>28</v>
@@ -17533,7 +17533,7 @@
         <v>27</v>
       </c>
       <c r="D789">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E789" t="s">
         <v>28</v>
@@ -17550,7 +17550,7 @@
         <v>27</v>
       </c>
       <c r="D790">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E790" t="s">
         <v>28</v>
@@ -17567,7 +17567,7 @@
         <v>27</v>
       </c>
       <c r="D791">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E791" t="s">
         <v>28</v>
@@ -17584,7 +17584,7 @@
         <v>27</v>
       </c>
       <c r="D792">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E792" t="s">
         <v>28</v>
@@ -17601,7 +17601,7 @@
         <v>27</v>
       </c>
       <c r="D793">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E793" t="s">
         <v>28</v>
@@ -17618,7 +17618,7 @@
         <v>27</v>
       </c>
       <c r="D794">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E794" t="s">
         <v>28</v>
@@ -17652,7 +17652,7 @@
         <v>27</v>
       </c>
       <c r="D796">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E796" t="s">
         <v>28</v>
@@ -17669,7 +17669,7 @@
         <v>27</v>
       </c>
       <c r="D797">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E797" t="s">
         <v>28</v>
@@ -17686,7 +17686,7 @@
         <v>27</v>
       </c>
       <c r="D798">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E798" t="s">
         <v>28</v>
@@ -17703,7 +17703,7 @@
         <v>27</v>
       </c>
       <c r="D799">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E799" t="s">
         <v>28</v>
@@ -17720,7 +17720,7 @@
         <v>27</v>
       </c>
       <c r="D800">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E800" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="D801">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E801" t="s">
         <v>28</v>
@@ -17754,7 +17754,7 @@
         <v>27</v>
       </c>
       <c r="D802">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E802" t="s">
         <v>28</v>
@@ -17771,7 +17771,7 @@
         <v>27</v>
       </c>
       <c r="D803">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E803" t="s">
         <v>28</v>
@@ -17788,7 +17788,7 @@
         <v>27</v>
       </c>
       <c r="D804">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E804" t="s">
         <v>28</v>
@@ -17805,7 +17805,7 @@
         <v>27</v>
       </c>
       <c r="D805">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E805" t="s">
         <v>28</v>
@@ -17822,7 +17822,7 @@
         <v>27</v>
       </c>
       <c r="D806">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E806" t="s">
         <v>28</v>
@@ -17839,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="D807">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E807" t="s">
         <v>28</v>
@@ -17856,7 +17856,7 @@
         <v>27</v>
       </c>
       <c r="D808">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E808" t="s">
         <v>28</v>
@@ -17873,7 +17873,7 @@
         <v>27</v>
       </c>
       <c r="D809">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E809" t="s">
         <v>28</v>
@@ -17890,7 +17890,7 @@
         <v>27</v>
       </c>
       <c r="D810">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E810" t="s">
         <v>28</v>
@@ -17907,7 +17907,7 @@
         <v>27</v>
       </c>
       <c r="D811">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E811" t="s">
         <v>28</v>
@@ -17924,7 +17924,7 @@
         <v>27</v>
       </c>
       <c r="D812">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E812" t="s">
         <v>28</v>
@@ -17941,7 +17941,7 @@
         <v>27</v>
       </c>
       <c r="D813">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E813" t="s">
         <v>28</v>
@@ -17958,7 +17958,7 @@
         <v>27</v>
       </c>
       <c r="D814">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E814" t="s">
         <v>28</v>
@@ -17975,7 +17975,7 @@
         <v>27</v>
       </c>
       <c r="D815">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E815" t="s">
         <v>28</v>
@@ -17992,7 +17992,7 @@
         <v>27</v>
       </c>
       <c r="D816">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E816" t="s">
         <v>28</v>
@@ -18009,7 +18009,7 @@
         <v>27</v>
       </c>
       <c r="D817">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E817" t="s">
         <v>28</v>
@@ -18026,7 +18026,7 @@
         <v>27</v>
       </c>
       <c r="D818">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E818" t="s">
         <v>28</v>
@@ -18043,7 +18043,7 @@
         <v>27</v>
       </c>
       <c r="D819">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E819" t="s">
         <v>28</v>
@@ -18060,7 +18060,7 @@
         <v>27</v>
       </c>
       <c r="D820">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E820" t="s">
         <v>28</v>
@@ -18077,7 +18077,7 @@
         <v>27</v>
       </c>
       <c r="D821">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E821" t="s">
         <v>28</v>
@@ -18094,7 +18094,7 @@
         <v>27</v>
       </c>
       <c r="D822">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E822" t="s">
         <v>28</v>
@@ -18111,7 +18111,7 @@
         <v>27</v>
       </c>
       <c r="D823">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E823" t="s">
         <v>28</v>
@@ -18128,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="D824">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E824" t="s">
         <v>28</v>
@@ -18145,7 +18145,7 @@
         <v>27</v>
       </c>
       <c r="D825">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E825" t="s">
         <v>28</v>
@@ -18162,7 +18162,7 @@
         <v>27</v>
       </c>
       <c r="D826">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E826" t="s">
         <v>28</v>
@@ -18179,7 +18179,7 @@
         <v>27</v>
       </c>
       <c r="D827">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E827" t="s">
         <v>28</v>
@@ -18196,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="D828">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E828" t="s">
         <v>28</v>
@@ -18213,7 +18213,7 @@
         <v>27</v>
       </c>
       <c r="D829">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E829" t="s">
         <v>28</v>
@@ -18230,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="D830">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E830" t="s">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E831" t="s">
         <v>28</v>
@@ -18264,7 +18264,7 @@
         <v>27</v>
       </c>
       <c r="D832">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E832" t="s">
         <v>28</v>
@@ -18281,7 +18281,7 @@
         <v>27</v>
       </c>
       <c r="D833">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E833" t="s">
         <v>28</v>
@@ -18298,7 +18298,7 @@
         <v>27</v>
       </c>
       <c r="D834">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E834" t="s">
         <v>28</v>
@@ -18315,7 +18315,7 @@
         <v>27</v>
       </c>
       <c r="D835">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E835" t="s">
         <v>28</v>
@@ -18332,7 +18332,7 @@
         <v>27</v>
       </c>
       <c r="D836">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E836" t="s">
         <v>28</v>
@@ -18349,7 +18349,7 @@
         <v>27</v>
       </c>
       <c r="D837">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E837" t="s">
         <v>28</v>
@@ -18366,7 +18366,7 @@
         <v>27</v>
       </c>
       <c r="D838">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E838" t="s">
         <v>28</v>
@@ -18383,7 +18383,7 @@
         <v>27</v>
       </c>
       <c r="D839">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E839" t="s">
         <v>28</v>
@@ -18400,7 +18400,7 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E840" t="s">
         <v>28</v>
@@ -18417,7 +18417,7 @@
         <v>27</v>
       </c>
       <c r="D841">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E841" t="s">
         <v>28</v>
@@ -18434,7 +18434,7 @@
         <v>27</v>
       </c>
       <c r="D842">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E842" t="s">
         <v>28</v>
@@ -18468,7 +18468,7 @@
         <v>27</v>
       </c>
       <c r="D844">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E844" t="s">
         <v>28</v>
@@ -18485,7 +18485,7 @@
         <v>27</v>
       </c>
       <c r="D845">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E845" t="s">
         <v>28</v>
@@ -18502,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="D846">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E846" t="s">
         <v>28</v>
@@ -18536,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="D848">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E848" t="s">
         <v>28</v>
@@ -18553,7 +18553,7 @@
         <v>27</v>
       </c>
       <c r="D849">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E849" t="s">
         <v>28</v>
@@ -18570,7 +18570,7 @@
         <v>27</v>
       </c>
       <c r="D850">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E850" t="s">
         <v>28</v>
@@ -18587,7 +18587,7 @@
         <v>27</v>
       </c>
       <c r="D851">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E851" t="s">
         <v>28</v>
@@ -18604,7 +18604,7 @@
         <v>27</v>
       </c>
       <c r="D852">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E852" t="s">
         <v>28</v>
@@ -18621,7 +18621,7 @@
         <v>27</v>
       </c>
       <c r="D853">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E853" t="s">
         <v>28</v>
@@ -18638,7 +18638,7 @@
         <v>27</v>
       </c>
       <c r="D854">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E854" t="s">
         <v>28</v>
@@ -18655,7 +18655,7 @@
         <v>27</v>
       </c>
       <c r="D855">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E855" t="s">
         <v>28</v>
@@ -18689,7 +18689,7 @@
         <v>27</v>
       </c>
       <c r="D857">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E857" t="s">
         <v>28</v>
@@ -18706,7 +18706,7 @@
         <v>27</v>
       </c>
       <c r="D858">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E858" t="s">
         <v>28</v>
@@ -18723,7 +18723,7 @@
         <v>27</v>
       </c>
       <c r="D859">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E859" t="s">
         <v>28</v>
@@ -18740,7 +18740,7 @@
         <v>27</v>
       </c>
       <c r="D860">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E860" t="s">
         <v>28</v>
@@ -18791,7 +18791,7 @@
         <v>27</v>
       </c>
       <c r="D863">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E863" t="s">
         <v>28</v>
@@ -18808,7 +18808,7 @@
         <v>27</v>
       </c>
       <c r="D864">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E864" t="s">
         <v>28</v>
@@ -18825,7 +18825,7 @@
         <v>27</v>
       </c>
       <c r="D865">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E865" t="s">
         <v>28</v>
@@ -18842,7 +18842,7 @@
         <v>27</v>
       </c>
       <c r="D866">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E866" t="s">
         <v>28</v>
@@ -18859,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="D867">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E867" t="s">
         <v>28</v>
@@ -18876,7 +18876,7 @@
         <v>27</v>
       </c>
       <c r="D868">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E868" t="s">
         <v>28</v>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
       <c r="D869">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E869" t="s">
         <v>28</v>
@@ -18910,7 +18910,7 @@
         <v>27</v>
       </c>
       <c r="D870">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E870" t="s">
         <v>28</v>
@@ -18927,7 +18927,7 @@
         <v>27</v>
       </c>
       <c r="D871">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E871" t="s">
         <v>28</v>
@@ -18944,7 +18944,7 @@
         <v>27</v>
       </c>
       <c r="D872">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E872" t="s">
         <v>28</v>
@@ -18961,7 +18961,7 @@
         <v>27</v>
       </c>
       <c r="D873">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E873" t="s">
         <v>28</v>
@@ -18978,7 +18978,7 @@
         <v>27</v>
       </c>
       <c r="D874">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E874" t="s">
         <v>28</v>
@@ -18995,7 +18995,7 @@
         <v>27</v>
       </c>
       <c r="D875">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E875" t="s">
         <v>28</v>
@@ -19012,7 +19012,7 @@
         <v>27</v>
       </c>
       <c r="D876">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E876" t="s">
         <v>28</v>
@@ -19029,7 +19029,7 @@
         <v>27</v>
       </c>
       <c r="D877">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E877" t="s">
         <v>28</v>
@@ -19046,7 +19046,7 @@
         <v>27</v>
       </c>
       <c r="D878">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E878" t="s">
         <v>28</v>
@@ -19080,7 +19080,7 @@
         <v>27</v>
       </c>
       <c r="D880">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E880" t="s">
         <v>28</v>
@@ -19097,7 +19097,7 @@
         <v>27</v>
       </c>
       <c r="D881">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E881" t="s">
         <v>28</v>
@@ -19114,7 +19114,7 @@
         <v>27</v>
       </c>
       <c r="D882">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E882" t="s">
         <v>28</v>
@@ -19131,7 +19131,7 @@
         <v>27</v>
       </c>
       <c r="D883">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E883" t="s">
         <v>28</v>
@@ -19148,7 +19148,7 @@
         <v>27</v>
       </c>
       <c r="D884">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E884" t="s">
         <v>28</v>
@@ -19165,7 +19165,7 @@
         <v>27</v>
       </c>
       <c r="D885">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E885" t="s">
         <v>28</v>
@@ -19182,7 +19182,7 @@
         <v>27</v>
       </c>
       <c r="D886">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E886" t="s">
         <v>28</v>
@@ -19199,7 +19199,7 @@
         <v>27</v>
       </c>
       <c r="D887">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E887" t="s">
         <v>28</v>
@@ -19216,7 +19216,7 @@
         <v>27</v>
       </c>
       <c r="D888">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E888" t="s">
         <v>28</v>
@@ -19233,7 +19233,7 @@
         <v>27</v>
       </c>
       <c r="D889">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E889" t="s">
         <v>28</v>
@@ -19250,7 +19250,7 @@
         <v>27</v>
       </c>
       <c r="D890">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E890" t="s">
         <v>28</v>
@@ -19267,7 +19267,7 @@
         <v>27</v>
       </c>
       <c r="D891">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E891" t="s">
         <v>28</v>
@@ -19284,7 +19284,7 @@
         <v>27</v>
       </c>
       <c r="D892">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E892" t="s">
         <v>28</v>
@@ -19301,7 +19301,7 @@
         <v>27</v>
       </c>
       <c r="D893">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E893" t="s">
         <v>28</v>
@@ -19318,7 +19318,7 @@
         <v>27</v>
       </c>
       <c r="D894">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E894" t="s">
         <v>28</v>
@@ -19335,7 +19335,7 @@
         <v>27</v>
       </c>
       <c r="D895">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E895" t="s">
         <v>28</v>
@@ -19352,7 +19352,7 @@
         <v>27</v>
       </c>
       <c r="D896">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E896" t="s">
         <v>28</v>
@@ -19369,7 +19369,7 @@
         <v>27</v>
       </c>
       <c r="D897">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E897" t="s">
         <v>28</v>
@@ -19386,7 +19386,7 @@
         <v>27</v>
       </c>
       <c r="D898">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E898" t="s">
         <v>28</v>
@@ -19403,7 +19403,7 @@
         <v>27</v>
       </c>
       <c r="D899">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E899" t="s">
         <v>28</v>
@@ -19420,7 +19420,7 @@
         <v>27</v>
       </c>
       <c r="D900">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E900" t="s">
         <v>28</v>
@@ -19437,7 +19437,7 @@
         <v>27</v>
       </c>
       <c r="D901">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E901" t="s">
         <v>28</v>
@@ -19454,7 +19454,7 @@
         <v>27</v>
       </c>
       <c r="D902">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E902" t="s">
         <v>28</v>
@@ -19471,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D903">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E903" t="s">
         <v>28</v>
@@ -19488,7 +19488,7 @@
         <v>27</v>
       </c>
       <c r="D904">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E904" t="s">
         <v>28</v>
@@ -19505,7 +19505,7 @@
         <v>27</v>
       </c>
       <c r="D905">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E905" t="s">
         <v>28</v>
@@ -19522,7 +19522,7 @@
         <v>27</v>
       </c>
       <c r="D906">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E906" t="s">
         <v>28</v>
@@ -19539,7 +19539,7 @@
         <v>27</v>
       </c>
       <c r="D907">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E907" t="s">
         <v>28</v>
@@ -19556,7 +19556,7 @@
         <v>27</v>
       </c>
       <c r="D908">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E908" t="s">
         <v>28</v>
@@ -19573,7 +19573,7 @@
         <v>27</v>
       </c>
       <c r="D909">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E909" t="s">
         <v>28</v>
@@ -19590,7 +19590,7 @@
         <v>27</v>
       </c>
       <c r="D910">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E910" t="s">
         <v>28</v>
@@ -19607,7 +19607,7 @@
         <v>27</v>
       </c>
       <c r="D911">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E911" t="s">
         <v>28</v>
@@ -19624,7 +19624,7 @@
         <v>27</v>
       </c>
       <c r="D912">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E912" t="s">
         <v>28</v>
@@ -19641,7 +19641,7 @@
         <v>27</v>
       </c>
       <c r="D913">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E913" t="s">
         <v>28</v>
@@ -19658,7 +19658,7 @@
         <v>27</v>
       </c>
       <c r="D914">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E914" t="s">
         <v>28</v>
@@ -19675,7 +19675,7 @@
         <v>27</v>
       </c>
       <c r="D915">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E915" t="s">
         <v>28</v>
@@ -19692,7 +19692,7 @@
         <v>27</v>
       </c>
       <c r="D916">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E916" t="s">
         <v>28</v>
@@ -19709,7 +19709,7 @@
         <v>27</v>
       </c>
       <c r="D917">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E917" t="s">
         <v>28</v>
@@ -19726,7 +19726,7 @@
         <v>27</v>
       </c>
       <c r="D918">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E918" t="s">
         <v>28</v>
@@ -19743,7 +19743,7 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E919" t="s">
         <v>28</v>
@@ -19760,7 +19760,7 @@
         <v>27</v>
       </c>
       <c r="D920">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E920" t="s">
         <v>28</v>
@@ -19777,7 +19777,7 @@
         <v>27</v>
       </c>
       <c r="D921">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E921" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>27</v>
       </c>
       <c r="D922">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E922" t="s">
         <v>28</v>
@@ -19811,7 +19811,7 @@
         <v>27</v>
       </c>
       <c r="D923">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E923" t="s">
         <v>28</v>
@@ -19845,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="D925">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E925" t="s">
         <v>28</v>
@@ -19862,7 +19862,7 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E926" t="s">
         <v>28</v>
@@ -19879,7 +19879,7 @@
         <v>27</v>
       </c>
       <c r="D927">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E927" t="s">
         <v>28</v>
@@ -19896,7 +19896,7 @@
         <v>27</v>
       </c>
       <c r="D928">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E928" t="s">
         <v>28</v>
@@ -19913,7 +19913,7 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E929" t="s">
         <v>28</v>
@@ -19930,7 +19930,7 @@
         <v>27</v>
       </c>
       <c r="D930">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E930" t="s">
         <v>28</v>
@@ -19947,7 +19947,7 @@
         <v>27</v>
       </c>
       <c r="D931">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E931" t="s">
         <v>28</v>
@@ -19981,7 +19981,7 @@
         <v>27</v>
       </c>
       <c r="D933">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E933" t="s">
         <v>28</v>
@@ -19998,7 +19998,7 @@
         <v>27</v>
       </c>
       <c r="D934">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E934" t="s">
         <v>28</v>
@@ -20015,7 +20015,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E935" t="s">
         <v>28</v>
@@ -20032,7 +20032,7 @@
         <v>27</v>
       </c>
       <c r="D936">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E936" t="s">
         <v>28</v>
@@ -20049,7 +20049,7 @@
         <v>27</v>
       </c>
       <c r="D937">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E937" t="s">
         <v>28</v>
@@ -20066,7 +20066,7 @@
         <v>27</v>
       </c>
       <c r="D938">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E938" t="s">
         <v>28</v>
@@ -20083,7 +20083,7 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E939" t="s">
         <v>28</v>
@@ -20100,7 +20100,7 @@
         <v>27</v>
       </c>
       <c r="D940">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E940" t="s">
         <v>28</v>
@@ -20117,7 +20117,7 @@
         <v>27</v>
       </c>
       <c r="D941">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E941" t="s">
         <v>28</v>
@@ -20134,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D942">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E942" t="s">
         <v>28</v>
@@ -20151,7 +20151,7 @@
         <v>27</v>
       </c>
       <c r="D943">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E943" t="s">
         <v>28</v>
@@ -20168,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="D944">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E944" t="s">
         <v>28</v>
@@ -20185,7 +20185,7 @@
         <v>27</v>
       </c>
       <c r="D945">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E945" t="s">
         <v>28</v>
@@ -20202,7 +20202,7 @@
         <v>27</v>
       </c>
       <c r="D946">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E946" t="s">
         <v>28</v>
@@ -20219,7 +20219,7 @@
         <v>27</v>
       </c>
       <c r="D947">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E947" t="s">
         <v>28</v>
@@ -20236,7 +20236,7 @@
         <v>27</v>
       </c>
       <c r="D948">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E948" t="s">
         <v>28</v>
@@ -20253,7 +20253,7 @@
         <v>27</v>
       </c>
       <c r="D949">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E949" t="s">
         <v>28</v>
@@ -20270,7 +20270,7 @@
         <v>27</v>
       </c>
       <c r="D950">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E950" t="s">
         <v>28</v>
@@ -20304,7 +20304,7 @@
         <v>27</v>
       </c>
       <c r="D952">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E952" t="s">
         <v>28</v>
@@ -20321,7 +20321,7 @@
         <v>27</v>
       </c>
       <c r="D953">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E953" t="s">
         <v>28</v>
@@ -20338,7 +20338,7 @@
         <v>27</v>
       </c>
       <c r="D954">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E954" t="s">
         <v>28</v>
@@ -20355,7 +20355,7 @@
         <v>27</v>
       </c>
       <c r="D955">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E955" t="s">
         <v>28</v>
@@ -20372,7 +20372,7 @@
         <v>27</v>
       </c>
       <c r="D956">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E956" t="s">
         <v>28</v>
@@ -20389,7 +20389,7 @@
         <v>27</v>
       </c>
       <c r="D957">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E957" t="s">
         <v>28</v>
@@ -20406,7 +20406,7 @@
         <v>27</v>
       </c>
       <c r="D958">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E958" t="s">
         <v>28</v>
@@ -20423,7 +20423,7 @@
         <v>27</v>
       </c>
       <c r="D959">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E959" t="s">
         <v>28</v>
@@ -20440,7 +20440,7 @@
         <v>27</v>
       </c>
       <c r="D960">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E960" t="s">
         <v>28</v>
@@ -20457,7 +20457,7 @@
         <v>27</v>
       </c>
       <c r="D961">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E961" t="s">
         <v>28</v>
@@ -20491,7 +20491,7 @@
         <v>27</v>
       </c>
       <c r="D963">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E963" t="s">
         <v>28</v>
@@ -20508,7 +20508,7 @@
         <v>27</v>
       </c>
       <c r="D964">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E964" t="s">
         <v>28</v>
@@ -20525,7 +20525,7 @@
         <v>27</v>
       </c>
       <c r="D965">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E965" t="s">
         <v>28</v>
@@ -20542,7 +20542,7 @@
         <v>27</v>
       </c>
       <c r="D966">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E966" t="s">
         <v>28</v>
@@ -20559,7 +20559,7 @@
         <v>27</v>
       </c>
       <c r="D967">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E967" t="s">
         <v>28</v>
@@ -20576,7 +20576,7 @@
         <v>27</v>
       </c>
       <c r="D968">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E968" t="s">
         <v>28</v>
@@ -20593,7 +20593,7 @@
         <v>27</v>
       </c>
       <c r="D969">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E969" t="s">
         <v>28</v>
@@ -20610,7 +20610,7 @@
         <v>27</v>
       </c>
       <c r="D970">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E970" t="s">
         <v>28</v>
@@ -20627,7 +20627,7 @@
         <v>27</v>
       </c>
       <c r="D971">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E971" t="s">
         <v>28</v>
@@ -20644,7 +20644,7 @@
         <v>27</v>
       </c>
       <c r="D972">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E972" t="s">
         <v>28</v>
@@ -20661,7 +20661,7 @@
         <v>27</v>
       </c>
       <c r="D973">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E973" t="s">
         <v>28</v>
@@ -20678,7 +20678,7 @@
         <v>27</v>
       </c>
       <c r="D974">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E974" t="s">
         <v>28</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="D975">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E975" t="s">
         <v>28</v>
@@ -20712,7 +20712,7 @@
         <v>27</v>
       </c>
       <c r="D976">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E976" t="s">
         <v>28</v>
@@ -20729,7 +20729,7 @@
         <v>27</v>
       </c>
       <c r="D977">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E977" t="s">
         <v>28</v>
@@ -20746,7 +20746,7 @@
         <v>27</v>
       </c>
       <c r="D978">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E978" t="s">
         <v>28</v>
@@ -20763,7 +20763,7 @@
         <v>27</v>
       </c>
       <c r="D979">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E979" t="s">
         <v>28</v>
@@ -20780,7 +20780,7 @@
         <v>27</v>
       </c>
       <c r="D980">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E980" t="s">
         <v>28</v>
@@ -20797,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="D981">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E981" t="s">
         <v>28</v>
@@ -20814,7 +20814,7 @@
         <v>27</v>
       </c>
       <c r="D982">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E982" t="s">
         <v>28</v>
@@ -20831,7 +20831,7 @@
         <v>27</v>
       </c>
       <c r="D983">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E983" t="s">
         <v>28</v>
@@ -20848,7 +20848,7 @@
         <v>27</v>
       </c>
       <c r="D984">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E984" t="s">
         <v>28</v>
@@ -20865,7 +20865,7 @@
         <v>27</v>
       </c>
       <c r="D985">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E985" t="s">
         <v>28</v>
@@ -20882,7 +20882,7 @@
         <v>27</v>
       </c>
       <c r="D986">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E986" t="s">
         <v>28</v>
@@ -20899,7 +20899,7 @@
         <v>27</v>
       </c>
       <c r="D987">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E987" t="s">
         <v>28</v>
@@ -20933,7 +20933,7 @@
         <v>27</v>
       </c>
       <c r="D989">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E989" t="s">
         <v>28</v>
@@ -20950,7 +20950,7 @@
         <v>27</v>
       </c>
       <c r="D990">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E990" t="s">
         <v>28</v>
@@ -20967,7 +20967,7 @@
         <v>27</v>
       </c>
       <c r="D991">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E991" t="s">
         <v>28</v>
@@ -20984,7 +20984,7 @@
         <v>27</v>
       </c>
       <c r="D992">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E992" t="s">
         <v>28</v>
@@ -21001,7 +21001,7 @@
         <v>27</v>
       </c>
       <c r="D993">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E993" t="s">
         <v>28</v>
@@ -21018,7 +21018,7 @@
         <v>27</v>
       </c>
       <c r="D994">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E994" t="s">
         <v>28</v>
@@ -21035,7 +21035,7 @@
         <v>27</v>
       </c>
       <c r="D995">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E995" t="s">
         <v>28</v>
@@ -21052,7 +21052,7 @@
         <v>27</v>
       </c>
       <c r="D996">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E996" t="s">
         <v>28</v>
@@ -21069,7 +21069,7 @@
         <v>27</v>
       </c>
       <c r="D997">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E997" t="s">
         <v>28</v>
@@ -21086,7 +21086,7 @@
         <v>27</v>
       </c>
       <c r="D998">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E998" t="s">
         <v>28</v>
@@ -21120,7 +21120,7 @@
         <v>27</v>
       </c>
       <c r="D1000">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E1000" t="s">
         <v>28</v>
@@ -21137,7 +21137,7 @@
         <v>27</v>
       </c>
       <c r="D1001">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E1001" t="s">
         <v>28</v>
@@ -21154,7 +21154,7 @@
         <v>27</v>
       </c>
       <c r="D1002">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1002" t="s">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>27</v>
       </c>
       <c r="D1003">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E1003" t="s">
         <v>28</v>
@@ -21188,7 +21188,7 @@
         <v>27</v>
       </c>
       <c r="D1004">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1004" t="s">
         <v>28</v>
@@ -21205,7 +21205,7 @@
         <v>27</v>
       </c>
       <c r="D1005">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1005" t="s">
         <v>28</v>
@@ -21222,7 +21222,7 @@
         <v>27</v>
       </c>
       <c r="D1006">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E1006" t="s">
         <v>28</v>
@@ -21239,7 +21239,7 @@
         <v>27</v>
       </c>
       <c r="D1007">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1007" t="s">
         <v>28</v>
@@ -21256,7 +21256,7 @@
         <v>27</v>
       </c>
       <c r="D1008">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E1008" t="s">
         <v>28</v>
@@ -21273,7 +21273,7 @@
         <v>27</v>
       </c>
       <c r="D1009">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1009" t="s">
         <v>28</v>
@@ -21290,7 +21290,7 @@
         <v>27</v>
       </c>
       <c r="D1010">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1010" t="s">
         <v>28</v>
@@ -21307,7 +21307,7 @@
         <v>27</v>
       </c>
       <c r="D1011">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E1011" t="s">
         <v>28</v>
@@ -21324,7 +21324,7 @@
         <v>27</v>
       </c>
       <c r="D1012">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E1012" t="s">
         <v>28</v>
@@ -21341,7 +21341,7 @@
         <v>27</v>
       </c>
       <c r="D1013">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1013" t="s">
         <v>28</v>
@@ -21358,7 +21358,7 @@
         <v>27</v>
       </c>
       <c r="D1014">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1014" t="s">
         <v>28</v>
@@ -21375,7 +21375,7 @@
         <v>27</v>
       </c>
       <c r="D1015">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1015" t="s">
         <v>28</v>
@@ -21409,7 +21409,7 @@
         <v>27</v>
       </c>
       <c r="D1017">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1017" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>27</v>
       </c>
       <c r="D1018">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1018" t="s">
         <v>28</v>
@@ -21443,7 +21443,7 @@
         <v>27</v>
       </c>
       <c r="D1019">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E1019" t="s">
         <v>28</v>
@@ -21460,7 +21460,7 @@
         <v>27</v>
       </c>
       <c r="D1020">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1020" t="s">
         <v>28</v>
@@ -21477,7 +21477,7 @@
         <v>27</v>
       </c>
       <c r="D1021">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E1021" t="s">
         <v>28</v>
@@ -21494,7 +21494,7 @@
         <v>27</v>
       </c>
       <c r="D1022">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1022" t="s">
         <v>28</v>
@@ -21528,7 +21528,7 @@
         <v>27</v>
       </c>
       <c r="D1024">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1024" t="s">
         <v>28</v>
@@ -21545,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E1025" t="s">
         <v>28</v>
@@ -21562,7 +21562,7 @@
         <v>27</v>
       </c>
       <c r="D1026">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1026" t="s">
         <v>28</v>
@@ -21579,7 +21579,7 @@
         <v>27</v>
       </c>
       <c r="D1027">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E1027" t="s">
         <v>28</v>
@@ -21613,7 +21613,7 @@
         <v>27</v>
       </c>
       <c r="D1029">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E1029" t="s">
         <v>28</v>
@@ -21630,7 +21630,7 @@
         <v>27</v>
       </c>
       <c r="D1030">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1030" t="s">
         <v>28</v>
@@ -21647,7 +21647,7 @@
         <v>27</v>
       </c>
       <c r="D1031">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E1031" t="s">
         <v>28</v>
@@ -21664,7 +21664,7 @@
         <v>27</v>
       </c>
       <c r="D1032">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1032" t="s">
         <v>28</v>
@@ -21681,7 +21681,7 @@
         <v>27</v>
       </c>
       <c r="D1033">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1033" t="s">
         <v>28</v>
@@ -21698,7 +21698,7 @@
         <v>27</v>
       </c>
       <c r="D1034">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1034" t="s">
         <v>28</v>
@@ -21715,7 +21715,7 @@
         <v>27</v>
       </c>
       <c r="D1035">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1035" t="s">
         <v>28</v>
@@ -21732,7 +21732,7 @@
         <v>27</v>
       </c>
       <c r="D1036">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E1036" t="s">
         <v>28</v>
@@ -21749,7 +21749,7 @@
         <v>27</v>
       </c>
       <c r="D1037">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E1037" t="s">
         <v>28</v>
@@ -21783,7 +21783,7 @@
         <v>27</v>
       </c>
       <c r="D1039">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E1039" t="s">
         <v>28</v>
@@ -21800,7 +21800,7 @@
         <v>27</v>
       </c>
       <c r="D1040">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1040" t="s">
         <v>28</v>
@@ -21817,7 +21817,7 @@
         <v>27</v>
       </c>
       <c r="D1041">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E1041" t="s">
         <v>28</v>
@@ -21834,7 +21834,7 @@
         <v>27</v>
       </c>
       <c r="D1042">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1042" t="s">
         <v>28</v>
@@ -21868,7 +21868,7 @@
         <v>27</v>
       </c>
       <c r="D1044">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1044" t="s">
         <v>28</v>
@@ -21885,7 +21885,7 @@
         <v>27</v>
       </c>
       <c r="D1045">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E1045" t="s">
         <v>28</v>
@@ -21902,7 +21902,7 @@
         <v>27</v>
       </c>
       <c r="D1046">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1046" t="s">
         <v>28</v>
@@ -21919,7 +21919,7 @@
         <v>27</v>
       </c>
       <c r="D1047">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1047" t="s">
         <v>28</v>
@@ -21936,7 +21936,7 @@
         <v>27</v>
       </c>
       <c r="D1048">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E1048" t="s">
         <v>28</v>
@@ -21953,7 +21953,7 @@
         <v>27</v>
       </c>
       <c r="D1049">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E1049" t="s">
         <v>28</v>
@@ -21970,7 +21970,7 @@
         <v>27</v>
       </c>
       <c r="D1050">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E1050" t="s">
         <v>28</v>
@@ -21987,7 +21987,7 @@
         <v>27</v>
       </c>
       <c r="D1051">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E1051" t="s">
         <v>28</v>
@@ -22004,7 +22004,7 @@
         <v>27</v>
       </c>
       <c r="D1052">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1052" t="s">
         <v>28</v>
@@ -22021,7 +22021,7 @@
         <v>27</v>
       </c>
       <c r="D1053">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1053" t="s">
         <v>28</v>
@@ -22038,7 +22038,7 @@
         <v>27</v>
       </c>
       <c r="D1054">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1054" t="s">
         <v>28</v>
@@ -22055,7 +22055,7 @@
         <v>27</v>
       </c>
       <c r="D1055">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1055" t="s">
         <v>28</v>
@@ -22072,7 +22072,7 @@
         <v>27</v>
       </c>
       <c r="D1056">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1056" t="s">
         <v>28</v>
@@ -22089,7 +22089,7 @@
         <v>27</v>
       </c>
       <c r="D1057">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1057" t="s">
         <v>28</v>
@@ -22106,7 +22106,7 @@
         <v>27</v>
       </c>
       <c r="D1058">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E1058" t="s">
         <v>28</v>
@@ -22123,7 +22123,7 @@
         <v>27</v>
       </c>
       <c r="D1059">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E1059" t="s">
         <v>28</v>
@@ -22140,7 +22140,7 @@
         <v>27</v>
       </c>
       <c r="D1060">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1060" t="s">
         <v>28</v>
@@ -22157,7 +22157,7 @@
         <v>27</v>
       </c>
       <c r="D1061">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1061" t="s">
         <v>28</v>
@@ -22174,7 +22174,7 @@
         <v>27</v>
       </c>
       <c r="D1062">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1062" t="s">
         <v>28</v>
@@ -22191,7 +22191,7 @@
         <v>27</v>
       </c>
       <c r="D1063">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E1063" t="s">
         <v>28</v>
@@ -22208,7 +22208,7 @@
         <v>27</v>
       </c>
       <c r="D1064">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1064" t="s">
         <v>28</v>
@@ -22225,7 +22225,7 @@
         <v>27</v>
       </c>
       <c r="D1065">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1065" t="s">
         <v>28</v>
@@ -22242,7 +22242,7 @@
         <v>27</v>
       </c>
       <c r="D1066">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1066" t="s">
         <v>28</v>
@@ -22259,7 +22259,7 @@
         <v>27</v>
       </c>
       <c r="D1067">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1067" t="s">
         <v>28</v>
@@ -22276,7 +22276,7 @@
         <v>27</v>
       </c>
       <c r="D1068">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1068" t="s">
         <v>28</v>
@@ -22310,7 +22310,7 @@
         <v>27</v>
       </c>
       <c r="D1070">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E1070" t="s">
         <v>28</v>
@@ -22344,7 +22344,7 @@
         <v>27</v>
       </c>
       <c r="D1072">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E1072" t="s">
         <v>28</v>
@@ -22361,7 +22361,7 @@
         <v>27</v>
       </c>
       <c r="D1073">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E1073" t="s">
         <v>28</v>
@@ -22378,7 +22378,7 @@
         <v>27</v>
       </c>
       <c r="D1074">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1074" t="s">
         <v>28</v>
@@ -22395,7 +22395,7 @@
         <v>27</v>
       </c>
       <c r="D1075">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E1075" t="s">
         <v>28</v>
@@ -22412,7 +22412,7 @@
         <v>27</v>
       </c>
       <c r="D1076">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E1076" t="s">
         <v>28</v>
@@ -22429,7 +22429,7 @@
         <v>27</v>
       </c>
       <c r="D1077">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1077" t="s">
         <v>28</v>
@@ -22446,7 +22446,7 @@
         <v>27</v>
       </c>
       <c r="D1078">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1078" t="s">
         <v>28</v>
@@ -22463,7 +22463,7 @@
         <v>27</v>
       </c>
       <c r="D1079">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E1079" t="s">
         <v>28</v>
@@ -22480,7 +22480,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1080" t="s">
         <v>28</v>
@@ -22497,7 +22497,7 @@
         <v>27</v>
       </c>
       <c r="D1081">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E1081" t="s">
         <v>28</v>
@@ -22514,7 +22514,7 @@
         <v>27</v>
       </c>
       <c r="D1082">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1082" t="s">
         <v>28</v>
@@ -22531,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="D1083">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1083" t="s">
         <v>28</v>
@@ -22548,7 +22548,7 @@
         <v>27</v>
       </c>
       <c r="D1084">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1084" t="s">
         <v>28</v>
@@ -22565,7 +22565,7 @@
         <v>27</v>
       </c>
       <c r="D1085">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1085" t="s">
         <v>28</v>
@@ -22582,7 +22582,7 @@
         <v>27</v>
       </c>
       <c r="D1086">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1086" t="s">
         <v>28</v>
@@ -22599,7 +22599,7 @@
         <v>27</v>
       </c>
       <c r="D1087">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1087" t="s">
         <v>28</v>
@@ -22616,7 +22616,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1088" t="s">
         <v>28</v>
@@ -22633,7 +22633,7 @@
         <v>27</v>
       </c>
       <c r="D1089">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1089" t="s">
         <v>28</v>
@@ -22650,7 +22650,7 @@
         <v>27</v>
       </c>
       <c r="D1090">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1090" t="s">
         <v>28</v>
@@ -22667,7 +22667,7 @@
         <v>27</v>
       </c>
       <c r="D1091">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1091" t="s">
         <v>28</v>
@@ -22684,7 +22684,7 @@
         <v>27</v>
       </c>
       <c r="D1092">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E1092" t="s">
         <v>28</v>
@@ -22701,7 +22701,7 @@
         <v>27</v>
       </c>
       <c r="D1093">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1093" t="s">
         <v>28</v>
@@ -22718,7 +22718,7 @@
         <v>27</v>
       </c>
       <c r="D1094">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1094" t="s">
         <v>28</v>
@@ -22735,7 +22735,7 @@
         <v>27</v>
       </c>
       <c r="D1095">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1095" t="s">
         <v>28</v>
@@ -22752,7 +22752,7 @@
         <v>27</v>
       </c>
       <c r="D1096">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E1096" t="s">
         <v>28</v>
@@ -22769,7 +22769,7 @@
         <v>27</v>
       </c>
       <c r="D1097">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1097" t="s">
         <v>28</v>
@@ -22786,7 +22786,7 @@
         <v>27</v>
       </c>
       <c r="D1098">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1098" t="s">
         <v>28</v>
@@ -22803,7 +22803,7 @@
         <v>27</v>
       </c>
       <c r="D1099">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E1099" t="s">
         <v>28</v>
@@ -22820,7 +22820,7 @@
         <v>27</v>
       </c>
       <c r="D1100">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E1100" t="s">
         <v>28</v>
@@ -22837,7 +22837,7 @@
         <v>27</v>
       </c>
       <c r="D1101">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E1101" t="s">
         <v>28</v>
@@ -22854,7 +22854,7 @@
         <v>27</v>
       </c>
       <c r="D1102">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E1102" t="s">
         <v>28</v>
@@ -22871,7 +22871,7 @@
         <v>27</v>
       </c>
       <c r="D1103">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1103" t="s">
         <v>28</v>
@@ -22888,7 +22888,7 @@
         <v>27</v>
       </c>
       <c r="D1104">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1104" t="s">
         <v>28</v>
@@ -22905,7 +22905,7 @@
         <v>27</v>
       </c>
       <c r="D1105">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1105" t="s">
         <v>28</v>
@@ -22922,7 +22922,7 @@
         <v>27</v>
       </c>
       <c r="D1106">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1106" t="s">
         <v>28</v>
@@ -22939,7 +22939,7 @@
         <v>27</v>
       </c>
       <c r="D1107">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E1107" t="s">
         <v>28</v>
@@ -22956,7 +22956,7 @@
         <v>27</v>
       </c>
       <c r="D1108">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1108" t="s">
         <v>28</v>
@@ -22973,7 +22973,7 @@
         <v>27</v>
       </c>
       <c r="D1109">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1109" t="s">
         <v>28</v>
@@ -22990,7 +22990,7 @@
         <v>27</v>
       </c>
       <c r="D1110">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E1110" t="s">
         <v>28</v>
@@ -23007,7 +23007,7 @@
         <v>27</v>
       </c>
       <c r="D1111">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1111" t="s">
         <v>28</v>
@@ -23024,7 +23024,7 @@
         <v>27</v>
       </c>
       <c r="D1112">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1112" t="s">
         <v>28</v>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1298</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1315</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1344</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1213</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1308</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1159</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1270</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1321</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1279</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1310</v>
+        <v>1252</v>
       </c>
     </row>
   </sheetData>
@@ -4154,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -4188,7 +4188,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -4205,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -4222,7 +4222,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -4256,7 +4256,7 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -4273,7 +4273,7 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4307,7 +4307,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4341,7 +4341,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -4358,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4409,7 +4409,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -4426,7 +4426,7 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -4443,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -4460,7 +4460,7 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
@@ -4494,7 +4494,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -4511,7 +4511,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -4528,7 +4528,7 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -4545,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
         <v>28</v>
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -4579,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -4596,7 +4596,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s">
         <v>28</v>
@@ -4647,7 +4647,7 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4681,7 +4681,7 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4698,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -4749,7 +4749,7 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E37" t="s">
         <v>28</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="D38">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E38" t="s">
         <v>28</v>
@@ -4783,7 +4783,7 @@
         <v>27</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E39" t="s">
         <v>28</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
@@ -4817,7 +4817,7 @@
         <v>27</v>
       </c>
       <c r="D41">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4834,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4851,7 +4851,7 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
@@ -4885,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
         <v>27</v>
       </c>
       <c r="D46">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -4919,7 +4919,7 @@
         <v>27</v>
       </c>
       <c r="D47">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="D48">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4953,7 +4953,7 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
@@ -4970,7 +4970,7 @@
         <v>27</v>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -4987,7 +4987,7 @@
         <v>27</v>
       </c>
       <c r="D51">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
@@ -5004,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5038,7 +5038,7 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E54" t="s">
         <v>28</v>
@@ -5055,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="D55">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -5072,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E56" t="s">
         <v>28</v>
@@ -5089,7 +5089,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E57" t="s">
         <v>28</v>
@@ -5106,7 +5106,7 @@
         <v>27</v>
       </c>
       <c r="D58">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -5123,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E59" t="s">
         <v>28</v>
@@ -5157,7 +5157,7 @@
         <v>27</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -5174,7 +5174,7 @@
         <v>27</v>
       </c>
       <c r="D62">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
@@ -5191,7 +5191,7 @@
         <v>27</v>
       </c>
       <c r="D63">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
@@ -5225,7 +5225,7 @@
         <v>27</v>
       </c>
       <c r="D65">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -5242,7 +5242,7 @@
         <v>27</v>
       </c>
       <c r="D66">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="D67">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
@@ -5293,7 +5293,7 @@
         <v>27</v>
       </c>
       <c r="D69">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -5310,7 +5310,7 @@
         <v>27</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="D71">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -5344,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="D72">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
@@ -5361,7 +5361,7 @@
         <v>27</v>
       </c>
       <c r="D73">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -5378,7 +5378,7 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
@@ -5395,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="D75">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="D76">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
@@ -5429,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="D77">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -5446,7 +5446,7 @@
         <v>27</v>
       </c>
       <c r="D78">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
@@ -5463,7 +5463,7 @@
         <v>27</v>
       </c>
       <c r="D79">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
@@ -5480,7 +5480,7 @@
         <v>27</v>
       </c>
       <c r="D80">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
@@ -5497,7 +5497,7 @@
         <v>27</v>
       </c>
       <c r="D81">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -5514,7 +5514,7 @@
         <v>27</v>
       </c>
       <c r="D82">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
@@ -5531,7 +5531,7 @@
         <v>27</v>
       </c>
       <c r="D83">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
@@ -5548,7 +5548,7 @@
         <v>27</v>
       </c>
       <c r="D84">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
@@ -5565,7 +5565,7 @@
         <v>27</v>
       </c>
       <c r="D85">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -5582,7 +5582,7 @@
         <v>27</v>
       </c>
       <c r="D86">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
@@ -5599,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="D87">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
@@ -5616,7 +5616,7 @@
         <v>27</v>
       </c>
       <c r="D88">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -5633,7 +5633,7 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="D90">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -5667,7 +5667,7 @@
         <v>27</v>
       </c>
       <c r="D91">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E91" t="s">
         <v>28</v>
@@ -5684,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="D92">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
@@ -5701,7 +5701,7 @@
         <v>27</v>
       </c>
       <c r="D93">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E93" t="s">
         <v>28</v>
@@ -5718,7 +5718,7 @@
         <v>27</v>
       </c>
       <c r="D94">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E94" t="s">
         <v>28</v>
@@ -5735,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D95">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -5752,7 +5752,7 @@
         <v>27</v>
       </c>
       <c r="D96">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E96" t="s">
         <v>28</v>
@@ -5769,7 +5769,7 @@
         <v>27</v>
       </c>
       <c r="D97">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E97" t="s">
         <v>28</v>
@@ -5786,7 +5786,7 @@
         <v>27</v>
       </c>
       <c r="D98">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="D99">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
         <v>28</v>
@@ -5820,7 +5820,7 @@
         <v>27</v>
       </c>
       <c r="D100">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E100" t="s">
         <v>28</v>
@@ -5837,7 +5837,7 @@
         <v>27</v>
       </c>
       <c r="D101">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E101" t="s">
         <v>28</v>
@@ -5854,7 +5854,7 @@
         <v>27</v>
       </c>
       <c r="D102">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E102" t="s">
         <v>28</v>
@@ -5871,7 +5871,7 @@
         <v>27</v>
       </c>
       <c r="D103">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E103" t="s">
         <v>28</v>
@@ -5888,7 +5888,7 @@
         <v>27</v>
       </c>
       <c r="D104">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E104" t="s">
         <v>28</v>
@@ -5905,7 +5905,7 @@
         <v>27</v>
       </c>
       <c r="D105">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E105" t="s">
         <v>28</v>
@@ -5922,7 +5922,7 @@
         <v>27</v>
       </c>
       <c r="D106">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>27</v>
       </c>
       <c r="D107">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E107" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="D108">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5973,7 +5973,7 @@
         <v>27</v>
       </c>
       <c r="D109">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E109" t="s">
         <v>28</v>
@@ -5990,7 +5990,7 @@
         <v>27</v>
       </c>
       <c r="D110">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E110" t="s">
         <v>28</v>
@@ -6007,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="D111">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="D112">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="D113">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E113" t="s">
         <v>28</v>
@@ -6058,7 +6058,7 @@
         <v>27</v>
       </c>
       <c r="D114">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>27</v>
       </c>
       <c r="D115">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -6092,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="D116">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E116" t="s">
         <v>28</v>
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="D117">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E117" t="s">
         <v>28</v>
@@ -6126,7 +6126,7 @@
         <v>27</v>
       </c>
       <c r="D118">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E118" t="s">
         <v>28</v>
@@ -6143,7 +6143,7 @@
         <v>27</v>
       </c>
       <c r="D119">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E119" t="s">
         <v>28</v>
@@ -6160,7 +6160,7 @@
         <v>27</v>
       </c>
       <c r="D120">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E120" t="s">
         <v>28</v>
@@ -6177,7 +6177,7 @@
         <v>27</v>
       </c>
       <c r="D121">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E121" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="D122">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E122" t="s">
         <v>28</v>
@@ -6211,7 +6211,7 @@
         <v>27</v>
       </c>
       <c r="D123">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E123" t="s">
         <v>28</v>
@@ -6228,7 +6228,7 @@
         <v>27</v>
       </c>
       <c r="D124">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E124" t="s">
         <v>28</v>
@@ -6245,7 +6245,7 @@
         <v>27</v>
       </c>
       <c r="D125">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
@@ -6262,7 +6262,7 @@
         <v>27</v>
       </c>
       <c r="D126">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -6279,7 +6279,7 @@
         <v>27</v>
       </c>
       <c r="D127">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E127" t="s">
         <v>28</v>
@@ -6296,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="D128">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E128" t="s">
         <v>28</v>
@@ -6313,7 +6313,7 @@
         <v>27</v>
       </c>
       <c r="D129">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
@@ -6330,7 +6330,7 @@
         <v>27</v>
       </c>
       <c r="D130">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E130" t="s">
         <v>28</v>
@@ -6347,7 +6347,7 @@
         <v>27</v>
       </c>
       <c r="D131">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E131" t="s">
         <v>28</v>
@@ -6364,7 +6364,7 @@
         <v>27</v>
       </c>
       <c r="D132">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E132" t="s">
         <v>28</v>
@@ -6381,7 +6381,7 @@
         <v>27</v>
       </c>
       <c r="D133">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E133" t="s">
         <v>28</v>
@@ -6398,7 +6398,7 @@
         <v>27</v>
       </c>
       <c r="D134">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E134" t="s">
         <v>28</v>
@@ -6415,7 +6415,7 @@
         <v>27</v>
       </c>
       <c r="D135">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E135" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="D136">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E136" t="s">
         <v>28</v>
@@ -6449,7 +6449,7 @@
         <v>27</v>
       </c>
       <c r="D137">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E137" t="s">
         <v>28</v>
@@ -6466,7 +6466,7 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E138" t="s">
         <v>28</v>
@@ -6483,7 +6483,7 @@
         <v>27</v>
       </c>
       <c r="D139">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E139" t="s">
         <v>28</v>
@@ -6500,7 +6500,7 @@
         <v>27</v>
       </c>
       <c r="D140">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E140" t="s">
         <v>28</v>
@@ -6517,7 +6517,7 @@
         <v>27</v>
       </c>
       <c r="D141">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E141" t="s">
         <v>28</v>
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="D142">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E142" t="s">
         <v>28</v>
@@ -6551,7 +6551,7 @@
         <v>27</v>
       </c>
       <c r="D143">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E143" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="D145">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E145" t="s">
         <v>28</v>
@@ -6602,7 +6602,7 @@
         <v>27</v>
       </c>
       <c r="D146">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E146" t="s">
         <v>28</v>
@@ -6636,7 +6636,7 @@
         <v>27</v>
       </c>
       <c r="D148">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E148" t="s">
         <v>28</v>
@@ -6653,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="D149">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6670,7 +6670,7 @@
         <v>27</v>
       </c>
       <c r="D150">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E150" t="s">
         <v>28</v>
@@ -6687,7 +6687,7 @@
         <v>27</v>
       </c>
       <c r="D151">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>27</v>
       </c>
       <c r="D152">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E152" t="s">
         <v>28</v>
@@ -6721,7 +6721,7 @@
         <v>27</v>
       </c>
       <c r="D153">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E153" t="s">
         <v>28</v>
@@ -6755,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -6772,7 +6772,7 @@
         <v>27</v>
       </c>
       <c r="D156">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E156" t="s">
         <v>28</v>
@@ -6789,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="D157">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E157" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="D159">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E159" t="s">
         <v>28</v>
@@ -6840,7 +6840,7 @@
         <v>27</v>
       </c>
       <c r="D160">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E160" t="s">
         <v>28</v>
@@ -6857,7 +6857,7 @@
         <v>27</v>
       </c>
       <c r="D161">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
@@ -6891,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="D163">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E163" t="s">
         <v>28</v>
@@ -6908,7 +6908,7 @@
         <v>27</v>
       </c>
       <c r="D164">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E164" t="s">
         <v>28</v>
@@ -6925,7 +6925,7 @@
         <v>27</v>
       </c>
       <c r="D165">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E165" t="s">
         <v>28</v>
@@ -6942,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="D166">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E166" t="s">
         <v>28</v>
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="D167">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E167" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="D168">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E168" t="s">
         <v>28</v>
@@ -6993,7 +6993,7 @@
         <v>27</v>
       </c>
       <c r="D169">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E169" t="s">
         <v>28</v>
@@ -7010,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="D170">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E170" t="s">
         <v>28</v>
@@ -7027,7 +7027,7 @@
         <v>27</v>
       </c>
       <c r="D171">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E171" t="s">
         <v>28</v>
@@ -7044,7 +7044,7 @@
         <v>27</v>
       </c>
       <c r="D172">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E172" t="s">
         <v>28</v>
@@ -7061,7 +7061,7 @@
         <v>27</v>
       </c>
       <c r="D173">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E173" t="s">
         <v>28</v>
@@ -7078,7 +7078,7 @@
         <v>27</v>
       </c>
       <c r="D174">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E174" t="s">
         <v>28</v>
@@ -7095,7 +7095,7 @@
         <v>27</v>
       </c>
       <c r="D175">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E175" t="s">
         <v>28</v>
@@ -7129,7 +7129,7 @@
         <v>27</v>
       </c>
       <c r="D177">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E177" t="s">
         <v>28</v>
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="D178">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E178" t="s">
         <v>28</v>
@@ -7163,7 +7163,7 @@
         <v>27</v>
       </c>
       <c r="D179">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E179" t="s">
         <v>28</v>
@@ -7180,7 +7180,7 @@
         <v>27</v>
       </c>
       <c r="D180">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -7197,7 +7197,7 @@
         <v>27</v>
       </c>
       <c r="D181">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E181" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="D182">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E182" t="s">
         <v>28</v>
@@ -7231,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="D183">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
@@ -7248,7 +7248,7 @@
         <v>27</v>
       </c>
       <c r="D184">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E184" t="s">
         <v>28</v>
@@ -7265,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="D185">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E185" t="s">
         <v>28</v>
@@ -7282,7 +7282,7 @@
         <v>27</v>
       </c>
       <c r="D186">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E186" t="s">
         <v>28</v>
@@ -7299,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="D187">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E187" t="s">
         <v>28</v>
@@ -7316,7 +7316,7 @@
         <v>27</v>
       </c>
       <c r="D188">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -7333,7 +7333,7 @@
         <v>27</v>
       </c>
       <c r="D189">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E189" t="s">
         <v>28</v>
@@ -7350,7 +7350,7 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E190" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="D191">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
@@ -7384,7 +7384,7 @@
         <v>27</v>
       </c>
       <c r="D192">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E192" t="s">
         <v>28</v>
@@ -7401,7 +7401,7 @@
         <v>27</v>
       </c>
       <c r="D193">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E193" t="s">
         <v>28</v>
@@ -7418,7 +7418,7 @@
         <v>27</v>
       </c>
       <c r="D194">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E194" t="s">
         <v>28</v>
@@ -7435,7 +7435,7 @@
         <v>27</v>
       </c>
       <c r="D195">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E195" t="s">
         <v>28</v>
@@ -7452,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="D196">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E196" t="s">
         <v>28</v>
@@ -7469,7 +7469,7 @@
         <v>27</v>
       </c>
       <c r="D197">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E197" t="s">
         <v>28</v>
@@ -7486,7 +7486,7 @@
         <v>27</v>
       </c>
       <c r="D198">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E198" t="s">
         <v>28</v>
@@ -7503,7 +7503,7 @@
         <v>27</v>
       </c>
       <c r="D199">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E199" t="s">
         <v>28</v>
@@ -7520,7 +7520,7 @@
         <v>27</v>
       </c>
       <c r="D200">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E200" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>27</v>
       </c>
       <c r="D201">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E201" t="s">
         <v>28</v>
@@ -7554,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="D202">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E202" t="s">
         <v>28</v>
@@ -7571,7 +7571,7 @@
         <v>27</v>
       </c>
       <c r="D203">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
@@ -7588,7 +7588,7 @@
         <v>27</v>
       </c>
       <c r="D204">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E204" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="D205">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -7622,7 +7622,7 @@
         <v>27</v>
       </c>
       <c r="D206">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E206" t="s">
         <v>28</v>
@@ -7639,7 +7639,7 @@
         <v>27</v>
       </c>
       <c r="D207">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E207" t="s">
         <v>28</v>
@@ -7656,7 +7656,7 @@
         <v>27</v>
       </c>
       <c r="D208">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E208" t="s">
         <v>28</v>
@@ -7673,7 +7673,7 @@
         <v>27</v>
       </c>
       <c r="D209">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E209" t="s">
         <v>28</v>
@@ -7690,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="D210">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E210" t="s">
         <v>28</v>
@@ -7707,7 +7707,7 @@
         <v>27</v>
       </c>
       <c r="D211">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E211" t="s">
         <v>28</v>
@@ -7724,7 +7724,7 @@
         <v>27</v>
       </c>
       <c r="D212">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E212" t="s">
         <v>28</v>
@@ -7741,7 +7741,7 @@
         <v>27</v>
       </c>
       <c r="D213">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E213" t="s">
         <v>28</v>
@@ -7775,7 +7775,7 @@
         <v>27</v>
       </c>
       <c r="D215">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E215" t="s">
         <v>28</v>
@@ -7792,7 +7792,7 @@
         <v>27</v>
       </c>
       <c r="D216">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E216" t="s">
         <v>28</v>
@@ -7809,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="D217">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E217" t="s">
         <v>28</v>
@@ -7826,7 +7826,7 @@
         <v>27</v>
       </c>
       <c r="D218">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E218" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="D220">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E220" t="s">
         <v>28</v>
@@ -7877,7 +7877,7 @@
         <v>27</v>
       </c>
       <c r="D221">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E221" t="s">
         <v>28</v>
@@ -7894,7 +7894,7 @@
         <v>27</v>
       </c>
       <c r="D222">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E222" t="s">
         <v>28</v>
@@ -7911,7 +7911,7 @@
         <v>27</v>
       </c>
       <c r="D223">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E223" t="s">
         <v>28</v>
@@ -7928,7 +7928,7 @@
         <v>27</v>
       </c>
       <c r="D224">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E224" t="s">
         <v>28</v>
@@ -7945,7 +7945,7 @@
         <v>27</v>
       </c>
       <c r="D225">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E225" t="s">
         <v>28</v>
@@ -7962,7 +7962,7 @@
         <v>27</v>
       </c>
       <c r="D226">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E226" t="s">
         <v>28</v>
@@ -7979,7 +7979,7 @@
         <v>27</v>
       </c>
       <c r="D227">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E227" t="s">
         <v>28</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="D228">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E228" t="s">
         <v>28</v>
@@ -8013,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="D229">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E229" t="s">
         <v>28</v>
@@ -8030,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="D230">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E230" t="s">
         <v>28</v>
@@ -8047,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="D231">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E231" t="s">
         <v>28</v>
@@ -8064,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="D232">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E232" t="s">
         <v>28</v>
@@ -8115,7 +8115,7 @@
         <v>27</v>
       </c>
       <c r="D235">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E235" t="s">
         <v>28</v>
@@ -8132,7 +8132,7 @@
         <v>27</v>
       </c>
       <c r="D236">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E236" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="D237">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E237" t="s">
         <v>28</v>
@@ -8166,7 +8166,7 @@
         <v>27</v>
       </c>
       <c r="D238">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E238" t="s">
         <v>28</v>
@@ -8183,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="D239">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E239" t="s">
         <v>28</v>
@@ -8200,7 +8200,7 @@
         <v>27</v>
       </c>
       <c r="D240">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E240" t="s">
         <v>28</v>
@@ -8217,7 +8217,7 @@
         <v>27</v>
       </c>
       <c r="D241">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E241" t="s">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>27</v>
       </c>
       <c r="D242">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E242" t="s">
         <v>28</v>
@@ -8251,7 +8251,7 @@
         <v>27</v>
       </c>
       <c r="D243">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E243" t="s">
         <v>28</v>
@@ -8268,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="D244">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E244" t="s">
         <v>28</v>
@@ -8285,7 +8285,7 @@
         <v>27</v>
       </c>
       <c r="D245">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E245" t="s">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="D247">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E247" t="s">
         <v>28</v>
@@ -8336,7 +8336,7 @@
         <v>27</v>
       </c>
       <c r="D248">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E248" t="s">
         <v>28</v>
@@ -8353,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="D249">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E249" t="s">
         <v>28</v>
@@ -8370,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="D250">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E250" t="s">
         <v>28</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="D251">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E251" t="s">
         <v>28</v>
@@ -8404,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="D252">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E252" t="s">
         <v>28</v>
@@ -8421,7 +8421,7 @@
         <v>27</v>
       </c>
       <c r="D253">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E253" t="s">
         <v>28</v>
@@ -8438,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D254">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E254" t="s">
         <v>28</v>
@@ -8455,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="D255">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E255" t="s">
         <v>28</v>
@@ -8472,7 +8472,7 @@
         <v>27</v>
       </c>
       <c r="D256">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E256" t="s">
         <v>28</v>
@@ -8489,7 +8489,7 @@
         <v>27</v>
       </c>
       <c r="D257">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E257" t="s">
         <v>28</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="D258">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E258" t="s">
         <v>28</v>
@@ -8523,7 +8523,7 @@
         <v>27</v>
       </c>
       <c r="D259">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E259" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="D260">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E260" t="s">
         <v>28</v>
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="D261">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E261" t="s">
         <v>28</v>
@@ -8574,7 +8574,7 @@
         <v>27</v>
       </c>
       <c r="D262">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E262" t="s">
         <v>28</v>
@@ -8591,7 +8591,7 @@
         <v>27</v>
       </c>
       <c r="D263">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E263" t="s">
         <v>28</v>
@@ -8608,7 +8608,7 @@
         <v>27</v>
       </c>
       <c r="D264">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E264" t="s">
         <v>28</v>
@@ -8625,7 +8625,7 @@
         <v>27</v>
       </c>
       <c r="D265">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E265" t="s">
         <v>28</v>
@@ -8642,7 +8642,7 @@
         <v>27</v>
       </c>
       <c r="D266">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E266" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="D267">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E267" t="s">
         <v>28</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="D268">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E268" t="s">
         <v>28</v>
@@ -8693,7 +8693,7 @@
         <v>27</v>
       </c>
       <c r="D269">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E269" t="s">
         <v>28</v>
@@ -8710,7 +8710,7 @@
         <v>27</v>
       </c>
       <c r="D270">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E270" t="s">
         <v>28</v>
@@ -8727,7 +8727,7 @@
         <v>27</v>
       </c>
       <c r="D271">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E271" t="s">
         <v>28</v>
@@ -8744,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="D272">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E272" t="s">
         <v>28</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="D274">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E274" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>27</v>
       </c>
       <c r="D275">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E275" t="s">
         <v>28</v>
@@ -8812,7 +8812,7 @@
         <v>27</v>
       </c>
       <c r="D276">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E276" t="s">
         <v>28</v>
@@ -8829,7 +8829,7 @@
         <v>27</v>
       </c>
       <c r="D277">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E277" t="s">
         <v>28</v>
@@ -8846,7 +8846,7 @@
         <v>27</v>
       </c>
       <c r="D278">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E278" t="s">
         <v>28</v>
@@ -8863,7 +8863,7 @@
         <v>27</v>
       </c>
       <c r="D279">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E279" t="s">
         <v>28</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E280" t="s">
         <v>28</v>
@@ -8897,7 +8897,7 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E281" t="s">
         <v>28</v>
@@ -8914,7 +8914,7 @@
         <v>27</v>
       </c>
       <c r="D282">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E282" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="D283">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E283" t="s">
         <v>28</v>
@@ -8965,7 +8965,7 @@
         <v>27</v>
       </c>
       <c r="D285">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E285" t="s">
         <v>28</v>
@@ -8982,7 +8982,7 @@
         <v>27</v>
       </c>
       <c r="D286">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E286" t="s">
         <v>28</v>
@@ -8999,7 +8999,7 @@
         <v>27</v>
       </c>
       <c r="D287">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E287" t="s">
         <v>28</v>
@@ -9016,7 +9016,7 @@
         <v>27</v>
       </c>
       <c r="D288">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E288" t="s">
         <v>28</v>
@@ -9033,7 +9033,7 @@
         <v>27</v>
       </c>
       <c r="D289">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E289" t="s">
         <v>28</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="D290">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E290" t="s">
         <v>28</v>
@@ -9067,7 +9067,7 @@
         <v>27</v>
       </c>
       <c r="D291">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E291" t="s">
         <v>28</v>
@@ -9084,7 +9084,7 @@
         <v>27</v>
       </c>
       <c r="D292">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E292" t="s">
         <v>28</v>
@@ -9118,7 +9118,7 @@
         <v>27</v>
       </c>
       <c r="D294">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E294" t="s">
         <v>28</v>
@@ -9135,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="D295">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E295" t="s">
         <v>28</v>
@@ -9152,7 +9152,7 @@
         <v>27</v>
       </c>
       <c r="D296">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E296" t="s">
         <v>28</v>
@@ -9169,7 +9169,7 @@
         <v>27</v>
       </c>
       <c r="D297">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E297" t="s">
         <v>28</v>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="D298">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E298" t="s">
         <v>28</v>
@@ -9203,7 +9203,7 @@
         <v>27</v>
       </c>
       <c r="D299">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E299" t="s">
         <v>28</v>
@@ -9220,7 +9220,7 @@
         <v>27</v>
       </c>
       <c r="D300">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E300" t="s">
         <v>28</v>
@@ -9237,7 +9237,7 @@
         <v>27</v>
       </c>
       <c r="D301">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E301" t="s">
         <v>28</v>
@@ -9254,7 +9254,7 @@
         <v>27</v>
       </c>
       <c r="D302">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E302" t="s">
         <v>28</v>
@@ -9271,7 +9271,7 @@
         <v>27</v>
       </c>
       <c r="D303">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E303" t="s">
         <v>28</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="D304">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E304" t="s">
         <v>28</v>
@@ -9305,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="D305">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E305" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="D306">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E306" t="s">
         <v>28</v>
@@ -9339,7 +9339,7 @@
         <v>27</v>
       </c>
       <c r="D307">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E307" t="s">
         <v>28</v>
@@ -9356,7 +9356,7 @@
         <v>27</v>
       </c>
       <c r="D308">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E308" t="s">
         <v>28</v>
@@ -9373,7 +9373,7 @@
         <v>27</v>
       </c>
       <c r="D309">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E309" t="s">
         <v>28</v>
@@ -9390,7 +9390,7 @@
         <v>27</v>
       </c>
       <c r="D310">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E310" t="s">
         <v>28</v>
@@ -9407,7 +9407,7 @@
         <v>27</v>
       </c>
       <c r="D311">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E311" t="s">
         <v>28</v>
@@ -9424,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="D312">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E312" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="D313">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E313" t="s">
         <v>28</v>
@@ -9458,7 +9458,7 @@
         <v>27</v>
       </c>
       <c r="D314">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E314" t="s">
         <v>28</v>
@@ -9492,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="D316">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E316" t="s">
         <v>28</v>
@@ -9509,7 +9509,7 @@
         <v>27</v>
       </c>
       <c r="D317">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E317" t="s">
         <v>28</v>
@@ -9526,7 +9526,7 @@
         <v>27</v>
       </c>
       <c r="D318">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E318" t="s">
         <v>28</v>
@@ -9543,7 +9543,7 @@
         <v>27</v>
       </c>
       <c r="D319">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E319" t="s">
         <v>28</v>
@@ -9560,7 +9560,7 @@
         <v>27</v>
       </c>
       <c r="D320">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E320" t="s">
         <v>28</v>
@@ -9577,7 +9577,7 @@
         <v>27</v>
       </c>
       <c r="D321">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E321" t="s">
         <v>28</v>
@@ -9594,7 +9594,7 @@
         <v>27</v>
       </c>
       <c r="D322">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E322" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
         <v>27</v>
       </c>
       <c r="D323">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E323" t="s">
         <v>28</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="D324">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E324" t="s">
         <v>28</v>
@@ -9645,7 +9645,7 @@
         <v>27</v>
       </c>
       <c r="D325">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E325" t="s">
         <v>28</v>
@@ -9662,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="D326">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E326" t="s">
         <v>28</v>
@@ -9679,7 +9679,7 @@
         <v>27</v>
       </c>
       <c r="D327">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E327" t="s">
         <v>28</v>
@@ -9696,7 +9696,7 @@
         <v>27</v>
       </c>
       <c r="D328">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E328" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="D329">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E329" t="s">
         <v>28</v>
@@ -9730,7 +9730,7 @@
         <v>27</v>
       </c>
       <c r="D330">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E330" t="s">
         <v>28</v>
@@ -9747,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="D331">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E331" t="s">
         <v>28</v>
@@ -9764,7 +9764,7 @@
         <v>27</v>
       </c>
       <c r="D332">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E332" t="s">
         <v>28</v>
@@ -9781,7 +9781,7 @@
         <v>27</v>
       </c>
       <c r="D333">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E333" t="s">
         <v>28</v>
@@ -9798,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="D334">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E334" t="s">
         <v>28</v>
@@ -9815,7 +9815,7 @@
         <v>27</v>
       </c>
       <c r="D335">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E335" t="s">
         <v>28</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="D336">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E336" t="s">
         <v>28</v>
@@ -9849,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="D337">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E337" t="s">
         <v>28</v>
@@ -9866,7 +9866,7 @@
         <v>27</v>
       </c>
       <c r="D338">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E338" t="s">
         <v>28</v>
@@ -9883,7 +9883,7 @@
         <v>27</v>
       </c>
       <c r="D339">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E339" t="s">
         <v>28</v>
@@ -9900,7 +9900,7 @@
         <v>27</v>
       </c>
       <c r="D340">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E340" t="s">
         <v>28</v>
@@ -9917,7 +9917,7 @@
         <v>27</v>
       </c>
       <c r="D341">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E341" t="s">
         <v>28</v>
@@ -9934,7 +9934,7 @@
         <v>27</v>
       </c>
       <c r="D342">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E342" t="s">
         <v>28</v>
@@ -9951,7 +9951,7 @@
         <v>27</v>
       </c>
       <c r="D343">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E343" t="s">
         <v>28</v>
@@ -9968,7 +9968,7 @@
         <v>27</v>
       </c>
       <c r="D344">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E344" t="s">
         <v>28</v>
@@ -9985,7 +9985,7 @@
         <v>27</v>
       </c>
       <c r="D345">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E345" t="s">
         <v>28</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D346">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E346" t="s">
         <v>28</v>
@@ -10019,7 +10019,7 @@
         <v>27</v>
       </c>
       <c r="D347">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E347" t="s">
         <v>28</v>
@@ -10036,7 +10036,7 @@
         <v>27</v>
       </c>
       <c r="D348">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E348" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="D350">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E350" t="s">
         <v>28</v>
@@ -10087,7 +10087,7 @@
         <v>27</v>
       </c>
       <c r="D351">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E351" t="s">
         <v>28</v>
@@ -10104,7 +10104,7 @@
         <v>27</v>
       </c>
       <c r="D352">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E352" t="s">
         <v>28</v>
@@ -10121,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D353">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E353" t="s">
         <v>28</v>
@@ -10138,7 +10138,7 @@
         <v>27</v>
       </c>
       <c r="D354">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E354" t="s">
         <v>28</v>
@@ -10155,7 +10155,7 @@
         <v>27</v>
       </c>
       <c r="D355">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E355" t="s">
         <v>28</v>
@@ -10172,7 +10172,7 @@
         <v>27</v>
       </c>
       <c r="D356">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E356" t="s">
         <v>28</v>
@@ -10189,7 +10189,7 @@
         <v>27</v>
       </c>
       <c r="D357">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E357" t="s">
         <v>28</v>
@@ -10206,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="D358">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E358" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="D359">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E359" t="s">
         <v>28</v>
@@ -10240,7 +10240,7 @@
         <v>27</v>
       </c>
       <c r="D360">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E360" t="s">
         <v>28</v>
@@ -10257,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="D361">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E361" t="s">
         <v>28</v>
@@ -10291,7 +10291,7 @@
         <v>27</v>
       </c>
       <c r="D363">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E363" t="s">
         <v>28</v>
@@ -10325,7 +10325,7 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E365" t="s">
         <v>28</v>
@@ -10342,7 +10342,7 @@
         <v>27</v>
       </c>
       <c r="D366">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E366" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
         <v>27</v>
       </c>
       <c r="D367">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E367" t="s">
         <v>28</v>
@@ -10376,7 +10376,7 @@
         <v>27</v>
       </c>
       <c r="D368">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E368" t="s">
         <v>28</v>
@@ -10393,7 +10393,7 @@
         <v>27</v>
       </c>
       <c r="D369">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E369" t="s">
         <v>28</v>
@@ -10410,7 +10410,7 @@
         <v>27</v>
       </c>
       <c r="D370">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E370" t="s">
         <v>28</v>
@@ -10427,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="D371">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E371" t="s">
         <v>28</v>
@@ -10444,7 +10444,7 @@
         <v>27</v>
       </c>
       <c r="D372">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E372" t="s">
         <v>28</v>
@@ -10461,7 +10461,7 @@
         <v>27</v>
       </c>
       <c r="D373">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E373" t="s">
         <v>28</v>
@@ -10478,7 +10478,7 @@
         <v>27</v>
       </c>
       <c r="D374">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E374" t="s">
         <v>28</v>
@@ -10495,7 +10495,7 @@
         <v>27</v>
       </c>
       <c r="D375">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E375" t="s">
         <v>28</v>
@@ -10512,7 +10512,7 @@
         <v>27</v>
       </c>
       <c r="D376">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E376" t="s">
         <v>28</v>
@@ -10529,7 +10529,7 @@
         <v>27</v>
       </c>
       <c r="D377">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E377" t="s">
         <v>28</v>
@@ -10546,7 +10546,7 @@
         <v>27</v>
       </c>
       <c r="D378">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E378" t="s">
         <v>28</v>
@@ -10563,7 +10563,7 @@
         <v>27</v>
       </c>
       <c r="D379">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E379" t="s">
         <v>28</v>
@@ -10580,7 +10580,7 @@
         <v>27</v>
       </c>
       <c r="D380">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E380" t="s">
         <v>28</v>
@@ -10597,7 +10597,7 @@
         <v>27</v>
       </c>
       <c r="D381">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E381" t="s">
         <v>28</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="D382">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E382" t="s">
         <v>28</v>
@@ -10631,7 +10631,7 @@
         <v>27</v>
       </c>
       <c r="D383">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E383" t="s">
         <v>28</v>
@@ -10665,7 +10665,7 @@
         <v>27</v>
       </c>
       <c r="D385">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E385" t="s">
         <v>28</v>
@@ -10682,7 +10682,7 @@
         <v>27</v>
       </c>
       <c r="D386">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E386" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="D387">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E387" t="s">
         <v>28</v>
@@ -10716,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="D388">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E388" t="s">
         <v>28</v>
@@ -10733,7 +10733,7 @@
         <v>27</v>
       </c>
       <c r="D389">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E389" t="s">
         <v>28</v>
@@ -10750,7 +10750,7 @@
         <v>27</v>
       </c>
       <c r="D390">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E390" t="s">
         <v>28</v>
@@ -10767,7 +10767,7 @@
         <v>27</v>
       </c>
       <c r="D391">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E391" t="s">
         <v>28</v>
@@ -10801,7 +10801,7 @@
         <v>27</v>
       </c>
       <c r="D393">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E393" t="s">
         <v>28</v>
@@ -10818,7 +10818,7 @@
         <v>27</v>
       </c>
       <c r="D394">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E394" t="s">
         <v>28</v>
@@ -10835,7 +10835,7 @@
         <v>27</v>
       </c>
       <c r="D395">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E395" t="s">
         <v>28</v>
@@ -10852,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="D396">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E396" t="s">
         <v>28</v>
@@ -10869,7 +10869,7 @@
         <v>27</v>
       </c>
       <c r="D397">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E397" t="s">
         <v>28</v>
@@ -10886,7 +10886,7 @@
         <v>27</v>
       </c>
       <c r="D398">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E398" t="s">
         <v>28</v>
@@ -10903,7 +10903,7 @@
         <v>27</v>
       </c>
       <c r="D399">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E399" t="s">
         <v>28</v>
@@ -10920,7 +10920,7 @@
         <v>27</v>
       </c>
       <c r="D400">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E400" t="s">
         <v>28</v>
@@ -10937,7 +10937,7 @@
         <v>27</v>
       </c>
       <c r="D401">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E401" t="s">
         <v>28</v>
@@ -10954,7 +10954,7 @@
         <v>27</v>
       </c>
       <c r="D402">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E402" t="s">
         <v>28</v>
@@ -10971,7 +10971,7 @@
         <v>27</v>
       </c>
       <c r="D403">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E403" t="s">
         <v>28</v>
@@ -10988,7 +10988,7 @@
         <v>27</v>
       </c>
       <c r="D404">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E404" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="D405">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E405" t="s">
         <v>28</v>
@@ -11022,7 +11022,7 @@
         <v>27</v>
       </c>
       <c r="D406">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E406" t="s">
         <v>28</v>
@@ -11039,7 +11039,7 @@
         <v>27</v>
       </c>
       <c r="D407">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E407" t="s">
         <v>28</v>
@@ -11056,7 +11056,7 @@
         <v>27</v>
       </c>
       <c r="D408">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E408" t="s">
         <v>28</v>
@@ -11073,7 +11073,7 @@
         <v>27</v>
       </c>
       <c r="D409">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E409" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="D410">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E410" t="s">
         <v>28</v>
@@ -11107,7 +11107,7 @@
         <v>27</v>
       </c>
       <c r="D411">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E411" t="s">
         <v>28</v>
@@ -11124,7 +11124,7 @@
         <v>27</v>
       </c>
       <c r="D412">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E412" t="s">
         <v>28</v>
@@ -11141,7 +11141,7 @@
         <v>27</v>
       </c>
       <c r="D413">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E413" t="s">
         <v>28</v>
@@ -11175,7 +11175,7 @@
         <v>27</v>
       </c>
       <c r="D415">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E415" t="s">
         <v>28</v>
@@ -11192,7 +11192,7 @@
         <v>27</v>
       </c>
       <c r="D416">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E416" t="s">
         <v>28</v>
@@ -11209,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="D417">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E417" t="s">
         <v>28</v>
@@ -11226,7 +11226,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E418" t="s">
         <v>28</v>
@@ -11243,7 +11243,7 @@
         <v>27</v>
       </c>
       <c r="D419">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E419" t="s">
         <v>28</v>
@@ -11260,7 +11260,7 @@
         <v>27</v>
       </c>
       <c r="D420">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E420" t="s">
         <v>28</v>
@@ -11277,7 +11277,7 @@
         <v>27</v>
       </c>
       <c r="D421">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E421" t="s">
         <v>28</v>
@@ -11294,7 +11294,7 @@
         <v>27</v>
       </c>
       <c r="D422">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E422" t="s">
         <v>28</v>
@@ -11328,7 +11328,7 @@
         <v>27</v>
       </c>
       <c r="D424">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E424" t="s">
         <v>28</v>
@@ -11345,7 +11345,7 @@
         <v>27</v>
       </c>
       <c r="D425">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E425" t="s">
         <v>28</v>
@@ -11379,7 +11379,7 @@
         <v>27</v>
       </c>
       <c r="D427">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E427" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="D428">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E428" t="s">
         <v>28</v>
@@ -11413,7 +11413,7 @@
         <v>27</v>
       </c>
       <c r="D429">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E429" t="s">
         <v>28</v>
@@ -11430,7 +11430,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E430" t="s">
         <v>28</v>
@@ -11464,7 +11464,7 @@
         <v>27</v>
       </c>
       <c r="D432">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E432" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="D433">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E433" t="s">
         <v>28</v>
@@ -11498,7 +11498,7 @@
         <v>27</v>
       </c>
       <c r="D434">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E434" t="s">
         <v>28</v>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="D435">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E435" t="s">
         <v>28</v>
@@ -11532,7 +11532,7 @@
         <v>27</v>
       </c>
       <c r="D436">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E436" t="s">
         <v>28</v>
@@ -11549,7 +11549,7 @@
         <v>27</v>
       </c>
       <c r="D437">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E437" t="s">
         <v>28</v>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
       <c r="D438">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E438" t="s">
         <v>28</v>
@@ -11583,7 +11583,7 @@
         <v>27</v>
       </c>
       <c r="D439">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E439" t="s">
         <v>28</v>
@@ -11600,7 +11600,7 @@
         <v>27</v>
       </c>
       <c r="D440">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E440" t="s">
         <v>28</v>
@@ -11617,7 +11617,7 @@
         <v>27</v>
       </c>
       <c r="D441">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E441" t="s">
         <v>28</v>
@@ -11634,7 +11634,7 @@
         <v>27</v>
       </c>
       <c r="D442">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E442" t="s">
         <v>28</v>
@@ -11651,7 +11651,7 @@
         <v>27</v>
       </c>
       <c r="D443">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E443" t="s">
         <v>28</v>
@@ -11668,7 +11668,7 @@
         <v>27</v>
       </c>
       <c r="D444">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E444" t="s">
         <v>28</v>
@@ -11685,7 +11685,7 @@
         <v>27</v>
       </c>
       <c r="D445">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E445" t="s">
         <v>28</v>
@@ -11702,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D446">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E446" t="s">
         <v>28</v>
@@ -11719,7 +11719,7 @@
         <v>27</v>
       </c>
       <c r="D447">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E447" t="s">
         <v>28</v>
@@ -11736,7 +11736,7 @@
         <v>27</v>
       </c>
       <c r="D448">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E448" t="s">
         <v>28</v>
@@ -11753,7 +11753,7 @@
         <v>27</v>
       </c>
       <c r="D449">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E449" t="s">
         <v>28</v>
@@ -11770,7 +11770,7 @@
         <v>27</v>
       </c>
       <c r="D450">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E450" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="D451">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E451" t="s">
         <v>28</v>
@@ -11804,7 +11804,7 @@
         <v>27</v>
       </c>
       <c r="D452">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E452" t="s">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>27</v>
       </c>
       <c r="D453">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E453" t="s">
         <v>28</v>
@@ -11838,7 +11838,7 @@
         <v>27</v>
       </c>
       <c r="D454">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E454" t="s">
         <v>28</v>
@@ -11855,7 +11855,7 @@
         <v>27</v>
       </c>
       <c r="D455">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E455" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="D456">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E456" t="s">
         <v>28</v>
@@ -11889,7 +11889,7 @@
         <v>27</v>
       </c>
       <c r="D457">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E457" t="s">
         <v>28</v>
@@ -11906,7 +11906,7 @@
         <v>27</v>
       </c>
       <c r="D458">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E458" t="s">
         <v>28</v>
@@ -11923,7 +11923,7 @@
         <v>27</v>
       </c>
       <c r="D459">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E459" t="s">
         <v>28</v>
@@ -11957,7 +11957,7 @@
         <v>27</v>
       </c>
       <c r="D461">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E461" t="s">
         <v>28</v>
@@ -11974,7 +11974,7 @@
         <v>27</v>
       </c>
       <c r="D462">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E462" t="s">
         <v>28</v>
@@ -11991,7 +11991,7 @@
         <v>27</v>
       </c>
       <c r="D463">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E463" t="s">
         <v>28</v>
@@ -12008,7 +12008,7 @@
         <v>27</v>
       </c>
       <c r="D464">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E464" t="s">
         <v>28</v>
@@ -12025,7 +12025,7 @@
         <v>27</v>
       </c>
       <c r="D465">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E465" t="s">
         <v>28</v>
@@ -12042,7 +12042,7 @@
         <v>27</v>
       </c>
       <c r="D466">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E466" t="s">
         <v>28</v>
@@ -12059,7 +12059,7 @@
         <v>27</v>
       </c>
       <c r="D467">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E467" t="s">
         <v>28</v>
@@ -12076,7 +12076,7 @@
         <v>27</v>
       </c>
       <c r="D468">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E468" t="s">
         <v>28</v>
@@ -12110,7 +12110,7 @@
         <v>27</v>
       </c>
       <c r="D470">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E470" t="s">
         <v>28</v>
@@ -12127,7 +12127,7 @@
         <v>27</v>
       </c>
       <c r="D471">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E471" t="s">
         <v>28</v>
@@ -12144,7 +12144,7 @@
         <v>27</v>
       </c>
       <c r="D472">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E472" t="s">
         <v>28</v>
@@ -12161,7 +12161,7 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E473" t="s">
         <v>28</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="D474">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E474" t="s">
         <v>28</v>
@@ -12195,7 +12195,7 @@
         <v>27</v>
       </c>
       <c r="D475">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E475" t="s">
         <v>28</v>
@@ -12212,7 +12212,7 @@
         <v>27</v>
       </c>
       <c r="D476">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E476" t="s">
         <v>28</v>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
       <c r="D477">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E477" t="s">
         <v>28</v>
@@ -12246,7 +12246,7 @@
         <v>27</v>
       </c>
       <c r="D478">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E478" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="D479">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E479" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="D480">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E480" t="s">
         <v>28</v>
@@ -12297,7 +12297,7 @@
         <v>27</v>
       </c>
       <c r="D481">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E481" t="s">
         <v>28</v>
@@ -12314,7 +12314,7 @@
         <v>27</v>
       </c>
       <c r="D482">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E482" t="s">
         <v>28</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="D483">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E483" t="s">
         <v>28</v>
@@ -12348,7 +12348,7 @@
         <v>27</v>
       </c>
       <c r="D484">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E484" t="s">
         <v>28</v>
@@ -12365,7 +12365,7 @@
         <v>27</v>
       </c>
       <c r="D485">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E485" t="s">
         <v>28</v>
@@ -12382,7 +12382,7 @@
         <v>27</v>
       </c>
       <c r="D486">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E486" t="s">
         <v>28</v>
@@ -12399,7 +12399,7 @@
         <v>27</v>
       </c>
       <c r="D487">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E487" t="s">
         <v>28</v>
@@ -12416,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="D488">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E488" t="s">
         <v>28</v>
@@ -12433,7 +12433,7 @@
         <v>27</v>
       </c>
       <c r="D489">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E489" t="s">
         <v>28</v>
@@ -12450,7 +12450,7 @@
         <v>27</v>
       </c>
       <c r="D490">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E490" t="s">
         <v>28</v>
@@ -12467,7 +12467,7 @@
         <v>27</v>
       </c>
       <c r="D491">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E491" t="s">
         <v>28</v>
@@ -12484,7 +12484,7 @@
         <v>27</v>
       </c>
       <c r="D492">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E492" t="s">
         <v>28</v>
@@ -12501,7 +12501,7 @@
         <v>27</v>
       </c>
       <c r="D493">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E493" t="s">
         <v>28</v>
@@ -12518,7 +12518,7 @@
         <v>27</v>
       </c>
       <c r="D494">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E494" t="s">
         <v>28</v>
@@ -12535,7 +12535,7 @@
         <v>27</v>
       </c>
       <c r="D495">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E495" t="s">
         <v>28</v>
@@ -12552,7 +12552,7 @@
         <v>27</v>
       </c>
       <c r="D496">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E496" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="D497">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E497" t="s">
         <v>28</v>
@@ -12586,7 +12586,7 @@
         <v>27</v>
       </c>
       <c r="D498">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E498" t="s">
         <v>28</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D499">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E499" t="s">
         <v>28</v>
@@ -12620,7 +12620,7 @@
         <v>27</v>
       </c>
       <c r="D500">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E500" t="s">
         <v>28</v>
@@ -12637,7 +12637,7 @@
         <v>27</v>
       </c>
       <c r="D501">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E501" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="D502">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E502" t="s">
         <v>28</v>
@@ -12671,7 +12671,7 @@
         <v>27</v>
       </c>
       <c r="D503">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E503" t="s">
         <v>28</v>
@@ -12705,7 +12705,7 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E505" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="D506">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E506" t="s">
         <v>28</v>
@@ -12739,7 +12739,7 @@
         <v>27</v>
       </c>
       <c r="D507">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E507" t="s">
         <v>28</v>
@@ -12756,7 +12756,7 @@
         <v>27</v>
       </c>
       <c r="D508">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E508" t="s">
         <v>28</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="D509">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E509" t="s">
         <v>28</v>
@@ -12790,7 +12790,7 @@
         <v>27</v>
       </c>
       <c r="D510">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E510" t="s">
         <v>28</v>
@@ -12807,7 +12807,7 @@
         <v>27</v>
       </c>
       <c r="D511">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E511" t="s">
         <v>28</v>
@@ -12824,7 +12824,7 @@
         <v>27</v>
       </c>
       <c r="D512">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E512" t="s">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27</v>
       </c>
       <c r="D513">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E513" t="s">
         <v>28</v>
@@ -12858,7 +12858,7 @@
         <v>27</v>
       </c>
       <c r="D514">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E514" t="s">
         <v>28</v>
@@ -12875,7 +12875,7 @@
         <v>27</v>
       </c>
       <c r="D515">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E515" t="s">
         <v>28</v>
@@ -12892,7 +12892,7 @@
         <v>27</v>
       </c>
       <c r="D516">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E516" t="s">
         <v>28</v>
@@ -12909,7 +12909,7 @@
         <v>27</v>
       </c>
       <c r="D517">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E517" t="s">
         <v>28</v>
@@ -12926,7 +12926,7 @@
         <v>27</v>
       </c>
       <c r="D518">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E518" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="D520">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E520" t="s">
         <v>28</v>
@@ -12977,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="D521">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E521" t="s">
         <v>28</v>
@@ -12994,7 +12994,7 @@
         <v>27</v>
       </c>
       <c r="D522">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E522" t="s">
         <v>28</v>
@@ -13011,7 +13011,7 @@
         <v>27</v>
       </c>
       <c r="D523">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E523" t="s">
         <v>28</v>
@@ -13028,7 +13028,7 @@
         <v>27</v>
       </c>
       <c r="D524">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E524" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="D525">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E525" t="s">
         <v>28</v>
@@ -13062,7 +13062,7 @@
         <v>27</v>
       </c>
       <c r="D526">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E526" t="s">
         <v>28</v>
@@ -13079,7 +13079,7 @@
         <v>27</v>
       </c>
       <c r="D527">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E527" t="s">
         <v>28</v>
@@ -13096,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="D528">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E528" t="s">
         <v>28</v>
@@ -13113,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="D529">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
@@ -13130,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -13147,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="D531">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
@@ -13164,7 +13164,7 @@
         <v>27</v>
       </c>
       <c r="D532">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E532" t="s">
         <v>28</v>
@@ -13181,7 +13181,7 @@
         <v>27</v>
       </c>
       <c r="D533">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E533" t="s">
         <v>28</v>
@@ -13198,7 +13198,7 @@
         <v>27</v>
       </c>
       <c r="D534">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E534" t="s">
         <v>28</v>
@@ -13215,7 +13215,7 @@
         <v>27</v>
       </c>
       <c r="D535">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E535" t="s">
         <v>28</v>
@@ -13232,7 +13232,7 @@
         <v>27</v>
       </c>
       <c r="D536">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E536" t="s">
         <v>28</v>
@@ -13249,7 +13249,7 @@
         <v>27</v>
       </c>
       <c r="D537">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E537" t="s">
         <v>28</v>
@@ -13266,7 +13266,7 @@
         <v>27</v>
       </c>
       <c r="D538">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E538" t="s">
         <v>28</v>
@@ -13283,7 +13283,7 @@
         <v>27</v>
       </c>
       <c r="D539">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E539" t="s">
         <v>28</v>
@@ -13300,7 +13300,7 @@
         <v>27</v>
       </c>
       <c r="D540">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E540" t="s">
         <v>28</v>
@@ -13317,7 +13317,7 @@
         <v>27</v>
       </c>
       <c r="D541">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E541" t="s">
         <v>28</v>
@@ -13334,7 +13334,7 @@
         <v>27</v>
       </c>
       <c r="D542">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E542" t="s">
         <v>28</v>
@@ -13368,7 +13368,7 @@
         <v>27</v>
       </c>
       <c r="D544">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E544" t="s">
         <v>28</v>
@@ -13385,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="D545">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
@@ -13402,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="D546">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
@@ -13419,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="D547">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E547" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="D548">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E548" t="s">
         <v>28</v>
@@ -13453,7 +13453,7 @@
         <v>27</v>
       </c>
       <c r="D549">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E549" t="s">
         <v>28</v>
@@ -13487,7 +13487,7 @@
         <v>27</v>
       </c>
       <c r="D551">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E551" t="s">
         <v>28</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="D552">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -13521,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="D553">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E553" t="s">
         <v>28</v>
@@ -13538,7 +13538,7 @@
         <v>27</v>
       </c>
       <c r="D554">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E554" t="s">
         <v>28</v>
@@ -13555,7 +13555,7 @@
         <v>27</v>
       </c>
       <c r="D555">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E555" t="s">
         <v>28</v>
@@ -13572,7 +13572,7 @@
         <v>27</v>
       </c>
       <c r="D556">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E556" t="s">
         <v>28</v>
@@ -13589,7 +13589,7 @@
         <v>27</v>
       </c>
       <c r="D557">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E557" t="s">
         <v>28</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="D558">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E558" t="s">
         <v>28</v>
@@ -13623,7 +13623,7 @@
         <v>27</v>
       </c>
       <c r="D559">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -13640,7 +13640,7 @@
         <v>27</v>
       </c>
       <c r="D560">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
@@ -13657,7 +13657,7 @@
         <v>27</v>
       </c>
       <c r="D561">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E561" t="s">
         <v>28</v>
@@ -13674,7 +13674,7 @@
         <v>27</v>
       </c>
       <c r="D562">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E562" t="s">
         <v>28</v>
@@ -13691,7 +13691,7 @@
         <v>27</v>
       </c>
       <c r="D563">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E563" t="s">
         <v>28</v>
@@ -13708,7 +13708,7 @@
         <v>27</v>
       </c>
       <c r="D564">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E564" t="s">
         <v>28</v>
@@ -13725,7 +13725,7 @@
         <v>27</v>
       </c>
       <c r="D565">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E565" t="s">
         <v>28</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="D566">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E566" t="s">
         <v>28</v>
@@ -13759,7 +13759,7 @@
         <v>27</v>
       </c>
       <c r="D567">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E567" t="s">
         <v>28</v>
@@ -13776,7 +13776,7 @@
         <v>27</v>
       </c>
       <c r="D568">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E568" t="s">
         <v>28</v>
@@ -13793,7 +13793,7 @@
         <v>27</v>
       </c>
       <c r="D569">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
@@ -13810,7 +13810,7 @@
         <v>27</v>
       </c>
       <c r="D570">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E570" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="D571">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E571" t="s">
         <v>28</v>
@@ -13844,7 +13844,7 @@
         <v>27</v>
       </c>
       <c r="D572">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E572" t="s">
         <v>28</v>
@@ -13878,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="D574">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E574" t="s">
         <v>28</v>
@@ -13895,7 +13895,7 @@
         <v>27</v>
       </c>
       <c r="D575">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E575" t="s">
         <v>28</v>
@@ -13912,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="D576">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E576" t="s">
         <v>28</v>
@@ -13929,7 +13929,7 @@
         <v>27</v>
       </c>
       <c r="D577">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E577" t="s">
         <v>28</v>
@@ -13963,7 +13963,7 @@
         <v>27</v>
       </c>
       <c r="D579">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E579" t="s">
         <v>28</v>
@@ -13980,7 +13980,7 @@
         <v>27</v>
       </c>
       <c r="D580">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E580" t="s">
         <v>28</v>
@@ -13997,7 +13997,7 @@
         <v>27</v>
       </c>
       <c r="D581">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E581" t="s">
         <v>28</v>
@@ -14014,7 +14014,7 @@
         <v>27</v>
       </c>
       <c r="D582">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E582" t="s">
         <v>28</v>
@@ -14031,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="D583">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E583" t="s">
         <v>28</v>
@@ -14048,7 +14048,7 @@
         <v>27</v>
       </c>
       <c r="D584">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E584" t="s">
         <v>28</v>
@@ -14065,7 +14065,7 @@
         <v>27</v>
       </c>
       <c r="D585">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E585" t="s">
         <v>28</v>
@@ -14082,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="D586">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E586" t="s">
         <v>28</v>
@@ -14099,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="D587">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E587" t="s">
         <v>28</v>
@@ -14116,7 +14116,7 @@
         <v>27</v>
       </c>
       <c r="D588">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E588" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="D589">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
@@ -14150,7 +14150,7 @@
         <v>27</v>
       </c>
       <c r="D590">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
@@ -14167,7 +14167,7 @@
         <v>27</v>
       </c>
       <c r="D591">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E591" t="s">
         <v>28</v>
@@ -14184,7 +14184,7 @@
         <v>27</v>
       </c>
       <c r="D592">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E592" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="D594">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E594" t="s">
         <v>28</v>
@@ -14235,7 +14235,7 @@
         <v>27</v>
       </c>
       <c r="D595">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E595" t="s">
         <v>28</v>
@@ -14252,7 +14252,7 @@
         <v>27</v>
       </c>
       <c r="D596">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
@@ -14269,7 +14269,7 @@
         <v>27</v>
       </c>
       <c r="D597">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
@@ -14286,7 +14286,7 @@
         <v>27</v>
       </c>
       <c r="D598">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
@@ -14303,7 +14303,7 @@
         <v>27</v>
       </c>
       <c r="D599">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="D600">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
@@ -14337,7 +14337,7 @@
         <v>27</v>
       </c>
       <c r="D601">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
@@ -14354,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="D602">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
@@ -14371,7 +14371,7 @@
         <v>27</v>
       </c>
       <c r="D603">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
@@ -14388,7 +14388,7 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
@@ -14405,7 +14405,7 @@
         <v>27</v>
       </c>
       <c r="D605">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E605" t="s">
         <v>28</v>
@@ -14422,7 +14422,7 @@
         <v>27</v>
       </c>
       <c r="D606">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E606" t="s">
         <v>28</v>
@@ -14439,7 +14439,7 @@
         <v>27</v>
       </c>
       <c r="D607">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E607" t="s">
         <v>28</v>
@@ -14456,7 +14456,7 @@
         <v>27</v>
       </c>
       <c r="D608">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
@@ -14473,7 +14473,7 @@
         <v>27</v>
       </c>
       <c r="D609">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E609" t="s">
         <v>28</v>
@@ -14490,7 +14490,7 @@
         <v>27</v>
       </c>
       <c r="D610">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E610" t="s">
         <v>28</v>
@@ -14507,7 +14507,7 @@
         <v>27</v>
       </c>
       <c r="D611">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E611" t="s">
         <v>28</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="D612">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E612" t="s">
         <v>28</v>
@@ -14541,7 +14541,7 @@
         <v>27</v>
       </c>
       <c r="D613">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E613" t="s">
         <v>28</v>
@@ -14558,7 +14558,7 @@
         <v>27</v>
       </c>
       <c r="D614">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E614" t="s">
         <v>28</v>
@@ -14575,7 +14575,7 @@
         <v>27</v>
       </c>
       <c r="D615">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E615" t="s">
         <v>28</v>
@@ -14592,7 +14592,7 @@
         <v>27</v>
       </c>
       <c r="D616">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E616" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="D617">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E617" t="s">
         <v>28</v>
@@ -14626,7 +14626,7 @@
         <v>27</v>
       </c>
       <c r="D618">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E618" t="s">
         <v>28</v>
@@ -14643,7 +14643,7 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E619" t="s">
         <v>28</v>
@@ -14660,7 +14660,7 @@
         <v>27</v>
       </c>
       <c r="D620">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E620" t="s">
         <v>28</v>
@@ -14677,7 +14677,7 @@
         <v>27</v>
       </c>
       <c r="D621">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E621" t="s">
         <v>28</v>
@@ -14694,7 +14694,7 @@
         <v>27</v>
       </c>
       <c r="D622">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E622" t="s">
         <v>28</v>
@@ -14711,7 +14711,7 @@
         <v>27</v>
       </c>
       <c r="D623">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E623" t="s">
         <v>28</v>
@@ -14728,7 +14728,7 @@
         <v>27</v>
       </c>
       <c r="D624">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E624" t="s">
         <v>28</v>
@@ -14745,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="D625">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E625" t="s">
         <v>28</v>
@@ -14762,7 +14762,7 @@
         <v>27</v>
       </c>
       <c r="D626">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E626" t="s">
         <v>28</v>
@@ -14779,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="D627">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E627" t="s">
         <v>28</v>
@@ -14813,7 +14813,7 @@
         <v>27</v>
       </c>
       <c r="D629">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E629" t="s">
         <v>28</v>
@@ -14830,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="D630">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E630" t="s">
         <v>28</v>
@@ -14847,7 +14847,7 @@
         <v>27</v>
       </c>
       <c r="D631">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E631" t="s">
         <v>28</v>
@@ -14864,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D632">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E632" t="s">
         <v>28</v>
@@ -14881,7 +14881,7 @@
         <v>27</v>
       </c>
       <c r="D633">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E633" t="s">
         <v>28</v>
@@ -14898,7 +14898,7 @@
         <v>27</v>
       </c>
       <c r="D634">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E634" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="D635">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E635" t="s">
         <v>28</v>
@@ -14932,7 +14932,7 @@
         <v>27</v>
       </c>
       <c r="D636">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E636" t="s">
         <v>28</v>
@@ -14949,7 +14949,7 @@
         <v>27</v>
       </c>
       <c r="D637">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E637" t="s">
         <v>28</v>
@@ -14983,7 +14983,7 @@
         <v>27</v>
       </c>
       <c r="D639">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E639" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E640" t="s">
         <v>28</v>
@@ -15017,7 +15017,7 @@
         <v>27</v>
       </c>
       <c r="D641">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E641" t="s">
         <v>28</v>
@@ -15034,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="D642">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E642" t="s">
         <v>28</v>
@@ -15051,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="D643">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E643" t="s">
         <v>28</v>
@@ -15068,7 +15068,7 @@
         <v>27</v>
       </c>
       <c r="D644">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E644" t="s">
         <v>28</v>
@@ -15085,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="D645">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E645" t="s">
         <v>28</v>
@@ -15102,7 +15102,7 @@
         <v>27</v>
       </c>
       <c r="D646">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E646" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>27</v>
       </c>
       <c r="D647">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E647" t="s">
         <v>28</v>
@@ -15136,7 +15136,7 @@
         <v>27</v>
       </c>
       <c r="D648">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E648" t="s">
         <v>28</v>
@@ -15153,7 +15153,7 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E649" t="s">
         <v>28</v>
@@ -15170,7 +15170,7 @@
         <v>27</v>
       </c>
       <c r="D650">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E650" t="s">
         <v>28</v>
@@ -15187,7 +15187,7 @@
         <v>27</v>
       </c>
       <c r="D651">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E651" t="s">
         <v>28</v>
@@ -15204,7 +15204,7 @@
         <v>27</v>
       </c>
       <c r="D652">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E652" t="s">
         <v>28</v>
@@ -15221,7 +15221,7 @@
         <v>27</v>
       </c>
       <c r="D653">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E653" t="s">
         <v>28</v>
@@ -15238,7 +15238,7 @@
         <v>27</v>
       </c>
       <c r="D654">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E654" t="s">
         <v>28</v>
@@ -15255,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="D655">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E655" t="s">
         <v>28</v>
@@ -15272,7 +15272,7 @@
         <v>27</v>
       </c>
       <c r="D656">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
@@ -15289,7 +15289,7 @@
         <v>27</v>
       </c>
       <c r="D657">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E657" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
@@ -15357,7 +15357,7 @@
         <v>27</v>
       </c>
       <c r="D661">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E661" t="s">
         <v>28</v>
@@ -15374,7 +15374,7 @@
         <v>27</v>
       </c>
       <c r="D662">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E662" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="D663">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E663" t="s">
         <v>28</v>
@@ -15408,7 +15408,7 @@
         <v>27</v>
       </c>
       <c r="D664">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E664" t="s">
         <v>28</v>
@@ -15425,7 +15425,7 @@
         <v>27</v>
       </c>
       <c r="D665">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E665" t="s">
         <v>28</v>
@@ -15442,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="D666">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E666" t="s">
         <v>28</v>
@@ -15459,7 +15459,7 @@
         <v>27</v>
       </c>
       <c r="D667">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E667" t="s">
         <v>28</v>
@@ -15476,7 +15476,7 @@
         <v>27</v>
       </c>
       <c r="D668">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E668" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>27</v>
       </c>
       <c r="D670">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E670" t="s">
         <v>28</v>
@@ -15527,7 +15527,7 @@
         <v>27</v>
       </c>
       <c r="D671">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E671" t="s">
         <v>28</v>
@@ -15544,7 +15544,7 @@
         <v>27</v>
       </c>
       <c r="D672">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E672" t="s">
         <v>28</v>
@@ -15561,7 +15561,7 @@
         <v>27</v>
       </c>
       <c r="D673">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E673" t="s">
         <v>28</v>
@@ -15578,7 +15578,7 @@
         <v>27</v>
       </c>
       <c r="D674">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E674" t="s">
         <v>28</v>
@@ -15595,7 +15595,7 @@
         <v>27</v>
       </c>
       <c r="D675">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E675" t="s">
         <v>28</v>
@@ -15612,7 +15612,7 @@
         <v>27</v>
       </c>
       <c r="D676">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E676" t="s">
         <v>28</v>
@@ -15629,7 +15629,7 @@
         <v>27</v>
       </c>
       <c r="D677">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E677" t="s">
         <v>28</v>
@@ -15646,7 +15646,7 @@
         <v>27</v>
       </c>
       <c r="D678">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E678" t="s">
         <v>28</v>
@@ -15663,7 +15663,7 @@
         <v>27</v>
       </c>
       <c r="D679">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E679" t="s">
         <v>28</v>
@@ -15680,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="D680">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E680" t="s">
         <v>28</v>
@@ -15697,7 +15697,7 @@
         <v>27</v>
       </c>
       <c r="D681">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E681" t="s">
         <v>28</v>
@@ -15714,7 +15714,7 @@
         <v>27</v>
       </c>
       <c r="D682">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E682" t="s">
         <v>28</v>
@@ -15731,7 +15731,7 @@
         <v>27</v>
       </c>
       <c r="D683">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E683" t="s">
         <v>28</v>
@@ -15748,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="D684">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E684" t="s">
         <v>28</v>
@@ -15765,7 +15765,7 @@
         <v>27</v>
       </c>
       <c r="D685">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E685" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="D686">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E686" t="s">
         <v>28</v>
@@ -15799,7 +15799,7 @@
         <v>27</v>
       </c>
       <c r="D687">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E687" t="s">
         <v>28</v>
@@ -15816,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="D688">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E688" t="s">
         <v>28</v>
@@ -15833,7 +15833,7 @@
         <v>27</v>
       </c>
       <c r="D689">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E689" t="s">
         <v>28</v>
@@ -15850,7 +15850,7 @@
         <v>27</v>
       </c>
       <c r="D690">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E690" t="s">
         <v>28</v>
@@ -15867,7 +15867,7 @@
         <v>27</v>
       </c>
       <c r="D691">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E691" t="s">
         <v>28</v>
@@ -15884,7 +15884,7 @@
         <v>27</v>
       </c>
       <c r="D692">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E692" t="s">
         <v>28</v>
@@ -15901,7 +15901,7 @@
         <v>27</v>
       </c>
       <c r="D693">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E693" t="s">
         <v>28</v>
@@ -15918,7 +15918,7 @@
         <v>27</v>
       </c>
       <c r="D694">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E694" t="s">
         <v>28</v>
@@ -15952,7 +15952,7 @@
         <v>27</v>
       </c>
       <c r="D696">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E696" t="s">
         <v>28</v>
@@ -15969,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="D697">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E697" t="s">
         <v>28</v>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
       <c r="D698">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E698" t="s">
         <v>28</v>
@@ -16003,7 +16003,7 @@
         <v>27</v>
       </c>
       <c r="D699">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E699" t="s">
         <v>28</v>
@@ -16020,7 +16020,7 @@
         <v>27</v>
       </c>
       <c r="D700">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E700" t="s">
         <v>28</v>
@@ -16037,7 +16037,7 @@
         <v>27</v>
       </c>
       <c r="D701">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E701" t="s">
         <v>28</v>
@@ -16054,7 +16054,7 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E702" t="s">
         <v>28</v>
@@ -16071,7 +16071,7 @@
         <v>27</v>
       </c>
       <c r="D703">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E703" t="s">
         <v>28</v>
@@ -16105,7 +16105,7 @@
         <v>27</v>
       </c>
       <c r="D705">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E705" t="s">
         <v>28</v>
@@ -16122,7 +16122,7 @@
         <v>27</v>
       </c>
       <c r="D706">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E706" t="s">
         <v>28</v>
@@ -16139,7 +16139,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E707" t="s">
         <v>28</v>
@@ -16156,7 +16156,7 @@
         <v>27</v>
       </c>
       <c r="D708">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E708" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="D709">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E709" t="s">
         <v>28</v>
@@ -16190,7 +16190,7 @@
         <v>27</v>
       </c>
       <c r="D710">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E710" t="s">
         <v>28</v>
@@ -16207,7 +16207,7 @@
         <v>27</v>
       </c>
       <c r="D711">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E711" t="s">
         <v>28</v>
@@ -16224,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="D712">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E712" t="s">
         <v>28</v>
@@ -16241,7 +16241,7 @@
         <v>27</v>
       </c>
       <c r="D713">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E713" t="s">
         <v>28</v>
@@ -16258,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="D714">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E714" t="s">
         <v>28</v>
@@ -16275,7 +16275,7 @@
         <v>27</v>
       </c>
       <c r="D715">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E715" t="s">
         <v>28</v>
@@ -16292,7 +16292,7 @@
         <v>27</v>
       </c>
       <c r="D716">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E716" t="s">
         <v>28</v>
@@ -16309,7 +16309,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E717" t="s">
         <v>28</v>
@@ -16326,7 +16326,7 @@
         <v>27</v>
       </c>
       <c r="D718">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E718" t="s">
         <v>28</v>
@@ -16343,7 +16343,7 @@
         <v>27</v>
       </c>
       <c r="D719">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E719" t="s">
         <v>28</v>
@@ -16360,7 +16360,7 @@
         <v>27</v>
       </c>
       <c r="D720">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E720" t="s">
         <v>28</v>
@@ -16377,7 +16377,7 @@
         <v>27</v>
       </c>
       <c r="D721">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E721" t="s">
         <v>28</v>
@@ -16394,7 +16394,7 @@
         <v>27</v>
       </c>
       <c r="D722">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E722" t="s">
         <v>28</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="D723">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E723" t="s">
         <v>28</v>
@@ -16428,7 +16428,7 @@
         <v>27</v>
       </c>
       <c r="D724">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E724" t="s">
         <v>28</v>
@@ -16462,7 +16462,7 @@
         <v>27</v>
       </c>
       <c r="D726">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E726" t="s">
         <v>28</v>
@@ -16479,7 +16479,7 @@
         <v>27</v>
       </c>
       <c r="D727">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E727" t="s">
         <v>28</v>
@@ -16496,7 +16496,7 @@
         <v>27</v>
       </c>
       <c r="D728">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E728" t="s">
         <v>28</v>
@@ -16513,7 +16513,7 @@
         <v>27</v>
       </c>
       <c r="D729">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E729" t="s">
         <v>28</v>
@@ -16530,7 +16530,7 @@
         <v>27</v>
       </c>
       <c r="D730">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E730" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="D732">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E732" t="s">
         <v>28</v>
@@ -16581,7 +16581,7 @@
         <v>27</v>
       </c>
       <c r="D733">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E733" t="s">
         <v>28</v>
@@ -16598,7 +16598,7 @@
         <v>27</v>
       </c>
       <c r="D734">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E734" t="s">
         <v>28</v>
@@ -16615,7 +16615,7 @@
         <v>27</v>
       </c>
       <c r="D735">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E735" t="s">
         <v>28</v>
@@ -16632,7 +16632,7 @@
         <v>27</v>
       </c>
       <c r="D736">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E736" t="s">
         <v>28</v>
@@ -16649,7 +16649,7 @@
         <v>27</v>
       </c>
       <c r="D737">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E737" t="s">
         <v>28</v>
@@ -16666,7 +16666,7 @@
         <v>27</v>
       </c>
       <c r="D738">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E738" t="s">
         <v>28</v>
@@ -16683,7 +16683,7 @@
         <v>27</v>
       </c>
       <c r="D739">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E739" t="s">
         <v>28</v>
@@ -16700,7 +16700,7 @@
         <v>27</v>
       </c>
       <c r="D740">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E740" t="s">
         <v>28</v>
@@ -16717,7 +16717,7 @@
         <v>27</v>
       </c>
       <c r="D741">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E741" t="s">
         <v>28</v>
@@ -16734,7 +16734,7 @@
         <v>27</v>
       </c>
       <c r="D742">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E742" t="s">
         <v>28</v>
@@ -16751,7 +16751,7 @@
         <v>27</v>
       </c>
       <c r="D743">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E743" t="s">
         <v>28</v>
@@ -16768,7 +16768,7 @@
         <v>27</v>
       </c>
       <c r="D744">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E744" t="s">
         <v>28</v>
@@ -16785,7 +16785,7 @@
         <v>27</v>
       </c>
       <c r="D745">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E745" t="s">
         <v>28</v>
@@ -16802,7 +16802,7 @@
         <v>27</v>
       </c>
       <c r="D746">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E746" t="s">
         <v>28</v>
@@ -16819,7 +16819,7 @@
         <v>27</v>
       </c>
       <c r="D747">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E747" t="s">
         <v>28</v>
@@ -16836,7 +16836,7 @@
         <v>27</v>
       </c>
       <c r="D748">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E748" t="s">
         <v>28</v>
@@ -16853,7 +16853,7 @@
         <v>27</v>
       </c>
       <c r="D749">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E749" t="s">
         <v>28</v>
@@ -16887,7 +16887,7 @@
         <v>27</v>
       </c>
       <c r="D751">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E751" t="s">
         <v>28</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="D752">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E752" t="s">
         <v>28</v>
@@ -16921,7 +16921,7 @@
         <v>27</v>
       </c>
       <c r="D753">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E753" t="s">
         <v>28</v>
@@ -16938,7 +16938,7 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E754" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="D755">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E755" t="s">
         <v>28</v>
@@ -16972,7 +16972,7 @@
         <v>27</v>
       </c>
       <c r="D756">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E756" t="s">
         <v>28</v>
@@ -16989,7 +16989,7 @@
         <v>27</v>
       </c>
       <c r="D757">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E757" t="s">
         <v>28</v>
@@ -17006,7 +17006,7 @@
         <v>27</v>
       </c>
       <c r="D758">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E758" t="s">
         <v>28</v>
@@ -17023,7 +17023,7 @@
         <v>27</v>
       </c>
       <c r="D759">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E759" t="s">
         <v>28</v>
@@ -17040,7 +17040,7 @@
         <v>27</v>
       </c>
       <c r="D760">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E760" t="s">
         <v>28</v>
@@ -17057,7 +17057,7 @@
         <v>27</v>
       </c>
       <c r="D761">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E761" t="s">
         <v>28</v>
@@ -17074,7 +17074,7 @@
         <v>27</v>
       </c>
       <c r="D762">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E762" t="s">
         <v>28</v>
@@ -17091,7 +17091,7 @@
         <v>27</v>
       </c>
       <c r="D763">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E763" t="s">
         <v>28</v>
@@ -17108,7 +17108,7 @@
         <v>27</v>
       </c>
       <c r="D764">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E764" t="s">
         <v>28</v>
@@ -17125,7 +17125,7 @@
         <v>27</v>
       </c>
       <c r="D765">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E765" t="s">
         <v>28</v>
@@ -17142,7 +17142,7 @@
         <v>27</v>
       </c>
       <c r="D766">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E766" t="s">
         <v>28</v>
@@ -17159,7 +17159,7 @@
         <v>27</v>
       </c>
       <c r="D767">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E767" t="s">
         <v>28</v>
@@ -17176,7 +17176,7 @@
         <v>27</v>
       </c>
       <c r="D768">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E768" t="s">
         <v>28</v>
@@ -17193,7 +17193,7 @@
         <v>27</v>
       </c>
       <c r="D769">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E769" t="s">
         <v>28</v>
@@ -17210,7 +17210,7 @@
         <v>27</v>
       </c>
       <c r="D770">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E770" t="s">
         <v>28</v>
@@ -17227,7 +17227,7 @@
         <v>27</v>
       </c>
       <c r="D771">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E771" t="s">
         <v>28</v>
@@ -17244,7 +17244,7 @@
         <v>27</v>
       </c>
       <c r="D772">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E772" t="s">
         <v>28</v>
@@ -17261,7 +17261,7 @@
         <v>27</v>
       </c>
       <c r="D773">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E773" t="s">
         <v>28</v>
@@ -17278,7 +17278,7 @@
         <v>27</v>
       </c>
       <c r="D774">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E774" t="s">
         <v>28</v>
@@ -17295,7 +17295,7 @@
         <v>27</v>
       </c>
       <c r="D775">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E775" t="s">
         <v>28</v>
@@ -17312,7 +17312,7 @@
         <v>27</v>
       </c>
       <c r="D776">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E776" t="s">
         <v>28</v>
@@ -17329,7 +17329,7 @@
         <v>27</v>
       </c>
       <c r="D777">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E777" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="D778">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E778" t="s">
         <v>28</v>
@@ -17363,7 +17363,7 @@
         <v>27</v>
       </c>
       <c r="D779">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E779" t="s">
         <v>28</v>
@@ -17380,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="D780">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E780" t="s">
         <v>28</v>
@@ -17414,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="D782">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E782" t="s">
         <v>28</v>
@@ -17431,7 +17431,7 @@
         <v>27</v>
       </c>
       <c r="D783">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E783" t="s">
         <v>28</v>
@@ -17448,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D784">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E784" t="s">
         <v>28</v>
@@ -17465,7 +17465,7 @@
         <v>27</v>
       </c>
       <c r="D785">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E785" t="s">
         <v>28</v>
@@ -17482,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="D786">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E786" t="s">
         <v>28</v>
@@ -17499,7 +17499,7 @@
         <v>27</v>
       </c>
       <c r="D787">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E787" t="s">
         <v>28</v>
@@ -17516,7 +17516,7 @@
         <v>27</v>
       </c>
       <c r="D788">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E788" t="s">
         <v>28</v>
@@ -17533,7 +17533,7 @@
         <v>27</v>
       </c>
       <c r="D789">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E789" t="s">
         <v>28</v>
@@ -17550,7 +17550,7 @@
         <v>27</v>
       </c>
       <c r="D790">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E790" t="s">
         <v>28</v>
@@ -17567,7 +17567,7 @@
         <v>27</v>
       </c>
       <c r="D791">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E791" t="s">
         <v>28</v>
@@ -17584,7 +17584,7 @@
         <v>27</v>
       </c>
       <c r="D792">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E792" t="s">
         <v>28</v>
@@ -17601,7 +17601,7 @@
         <v>27</v>
       </c>
       <c r="D793">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E793" t="s">
         <v>28</v>
@@ -17618,7 +17618,7 @@
         <v>27</v>
       </c>
       <c r="D794">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E794" t="s">
         <v>28</v>
@@ -17635,7 +17635,7 @@
         <v>27</v>
       </c>
       <c r="D795">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E795" t="s">
         <v>28</v>
@@ -17652,7 +17652,7 @@
         <v>27</v>
       </c>
       <c r="D796">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E796" t="s">
         <v>28</v>
@@ -17669,7 +17669,7 @@
         <v>27</v>
       </c>
       <c r="D797">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E797" t="s">
         <v>28</v>
@@ -17686,7 +17686,7 @@
         <v>27</v>
       </c>
       <c r="D798">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E798" t="s">
         <v>28</v>
@@ -17703,7 +17703,7 @@
         <v>27</v>
       </c>
       <c r="D799">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E799" t="s">
         <v>28</v>
@@ -17720,7 +17720,7 @@
         <v>27</v>
       </c>
       <c r="D800">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E800" t="s">
         <v>28</v>
@@ -17754,7 +17754,7 @@
         <v>27</v>
       </c>
       <c r="D802">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E802" t="s">
         <v>28</v>
@@ -17771,7 +17771,7 @@
         <v>27</v>
       </c>
       <c r="D803">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E803" t="s">
         <v>28</v>
@@ -17788,7 +17788,7 @@
         <v>27</v>
       </c>
       <c r="D804">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E804" t="s">
         <v>28</v>
@@ -17805,7 +17805,7 @@
         <v>27</v>
       </c>
       <c r="D805">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E805" t="s">
         <v>28</v>
@@ -17822,7 +17822,7 @@
         <v>27</v>
       </c>
       <c r="D806">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E806" t="s">
         <v>28</v>
@@ -17839,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="D807">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E807" t="s">
         <v>28</v>
@@ -17856,7 +17856,7 @@
         <v>27</v>
       </c>
       <c r="D808">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E808" t="s">
         <v>28</v>
@@ -17890,7 +17890,7 @@
         <v>27</v>
       </c>
       <c r="D810">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E810" t="s">
         <v>28</v>
@@ -17907,7 +17907,7 @@
         <v>27</v>
       </c>
       <c r="D811">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E811" t="s">
         <v>28</v>
@@ -17941,7 +17941,7 @@
         <v>27</v>
       </c>
       <c r="D813">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E813" t="s">
         <v>28</v>
@@ -17958,7 +17958,7 @@
         <v>27</v>
       </c>
       <c r="D814">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E814" t="s">
         <v>28</v>
@@ -17975,7 +17975,7 @@
         <v>27</v>
       </c>
       <c r="D815">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E815" t="s">
         <v>28</v>
@@ -17992,7 +17992,7 @@
         <v>27</v>
       </c>
       <c r="D816">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E816" t="s">
         <v>28</v>
@@ -18009,7 +18009,7 @@
         <v>27</v>
       </c>
       <c r="D817">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E817" t="s">
         <v>28</v>
@@ -18026,7 +18026,7 @@
         <v>27</v>
       </c>
       <c r="D818">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E818" t="s">
         <v>28</v>
@@ -18043,7 +18043,7 @@
         <v>27</v>
       </c>
       <c r="D819">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E819" t="s">
         <v>28</v>
@@ -18060,7 +18060,7 @@
         <v>27</v>
       </c>
       <c r="D820">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E820" t="s">
         <v>28</v>
@@ -18077,7 +18077,7 @@
         <v>27</v>
       </c>
       <c r="D821">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E821" t="s">
         <v>28</v>
@@ -18094,7 +18094,7 @@
         <v>27</v>
       </c>
       <c r="D822">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E822" t="s">
         <v>28</v>
@@ -18111,7 +18111,7 @@
         <v>27</v>
       </c>
       <c r="D823">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E823" t="s">
         <v>28</v>
@@ -18128,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="D824">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E824" t="s">
         <v>28</v>
@@ -18145,7 +18145,7 @@
         <v>27</v>
       </c>
       <c r="D825">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E825" t="s">
         <v>28</v>
@@ -18162,7 +18162,7 @@
         <v>27</v>
       </c>
       <c r="D826">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E826" t="s">
         <v>28</v>
@@ -18179,7 +18179,7 @@
         <v>27</v>
       </c>
       <c r="D827">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E827" t="s">
         <v>28</v>
@@ -18196,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="D828">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E828" t="s">
         <v>28</v>
@@ -18213,7 +18213,7 @@
         <v>27</v>
       </c>
       <c r="D829">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E829" t="s">
         <v>28</v>
@@ -18230,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="D830">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E830" t="s">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E831" t="s">
         <v>28</v>
@@ -18281,7 +18281,7 @@
         <v>27</v>
       </c>
       <c r="D833">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E833" t="s">
         <v>28</v>
@@ -18298,7 +18298,7 @@
         <v>27</v>
       </c>
       <c r="D834">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E834" t="s">
         <v>28</v>
@@ -18315,7 +18315,7 @@
         <v>27</v>
       </c>
       <c r="D835">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E835" t="s">
         <v>28</v>
@@ -18332,7 +18332,7 @@
         <v>27</v>
       </c>
       <c r="D836">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E836" t="s">
         <v>28</v>
@@ -18349,7 +18349,7 @@
         <v>27</v>
       </c>
       <c r="D837">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E837" t="s">
         <v>28</v>
@@ -18366,7 +18366,7 @@
         <v>27</v>
       </c>
       <c r="D838">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E838" t="s">
         <v>28</v>
@@ -18383,7 +18383,7 @@
         <v>27</v>
       </c>
       <c r="D839">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E839" t="s">
         <v>28</v>
@@ -18400,7 +18400,7 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E840" t="s">
         <v>28</v>
@@ -18417,7 +18417,7 @@
         <v>27</v>
       </c>
       <c r="D841">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E841" t="s">
         <v>28</v>
@@ -18434,7 +18434,7 @@
         <v>27</v>
       </c>
       <c r="D842">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E842" t="s">
         <v>28</v>
@@ -18451,7 +18451,7 @@
         <v>27</v>
       </c>
       <c r="D843">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E843" t="s">
         <v>28</v>
@@ -18468,7 +18468,7 @@
         <v>27</v>
       </c>
       <c r="D844">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E844" t="s">
         <v>28</v>
@@ -18485,7 +18485,7 @@
         <v>27</v>
       </c>
       <c r="D845">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E845" t="s">
         <v>28</v>
@@ -18502,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="D846">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E846" t="s">
         <v>28</v>
@@ -18519,7 +18519,7 @@
         <v>27</v>
       </c>
       <c r="D847">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E847" t="s">
         <v>28</v>
@@ -18536,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="D848">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E848" t="s">
         <v>28</v>
@@ -18553,7 +18553,7 @@
         <v>27</v>
       </c>
       <c r="D849">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E849" t="s">
         <v>28</v>
@@ -18570,7 +18570,7 @@
         <v>27</v>
       </c>
       <c r="D850">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E850" t="s">
         <v>28</v>
@@ -18587,7 +18587,7 @@
         <v>27</v>
       </c>
       <c r="D851">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E851" t="s">
         <v>28</v>
@@ -18604,7 +18604,7 @@
         <v>27</v>
       </c>
       <c r="D852">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E852" t="s">
         <v>28</v>
@@ -18621,7 +18621,7 @@
         <v>27</v>
       </c>
       <c r="D853">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E853" t="s">
         <v>28</v>
@@ -18638,7 +18638,7 @@
         <v>27</v>
       </c>
       <c r="D854">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E854" t="s">
         <v>28</v>
@@ -18655,7 +18655,7 @@
         <v>27</v>
       </c>
       <c r="D855">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E855" t="s">
         <v>28</v>
@@ -18672,7 +18672,7 @@
         <v>27</v>
       </c>
       <c r="D856">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E856" t="s">
         <v>28</v>
@@ -18689,7 +18689,7 @@
         <v>27</v>
       </c>
       <c r="D857">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E857" t="s">
         <v>28</v>
@@ -18706,7 +18706,7 @@
         <v>27</v>
       </c>
       <c r="D858">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E858" t="s">
         <v>28</v>
@@ -18723,7 +18723,7 @@
         <v>27</v>
       </c>
       <c r="D859">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E859" t="s">
         <v>28</v>
@@ -18740,7 +18740,7 @@
         <v>27</v>
       </c>
       <c r="D860">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E860" t="s">
         <v>28</v>
@@ -18757,7 +18757,7 @@
         <v>27</v>
       </c>
       <c r="D861">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E861" t="s">
         <v>28</v>
@@ -18774,7 +18774,7 @@
         <v>27</v>
       </c>
       <c r="D862">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E862" t="s">
         <v>28</v>
@@ -18791,7 +18791,7 @@
         <v>27</v>
       </c>
       <c r="D863">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E863" t="s">
         <v>28</v>
@@ -18808,7 +18808,7 @@
         <v>27</v>
       </c>
       <c r="D864">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E864" t="s">
         <v>28</v>
@@ -18825,7 +18825,7 @@
         <v>27</v>
       </c>
       <c r="D865">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E865" t="s">
         <v>28</v>
@@ -18859,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="D867">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E867" t="s">
         <v>28</v>
@@ -18876,7 +18876,7 @@
         <v>27</v>
       </c>
       <c r="D868">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E868" t="s">
         <v>28</v>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
       <c r="D869">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E869" t="s">
         <v>28</v>
@@ -18910,7 +18910,7 @@
         <v>27</v>
       </c>
       <c r="D870">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E870" t="s">
         <v>28</v>
@@ -18927,7 +18927,7 @@
         <v>27</v>
       </c>
       <c r="D871">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E871" t="s">
         <v>28</v>
@@ -18944,7 +18944,7 @@
         <v>27</v>
       </c>
       <c r="D872">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E872" t="s">
         <v>28</v>
@@ -18961,7 +18961,7 @@
         <v>27</v>
       </c>
       <c r="D873">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E873" t="s">
         <v>28</v>
@@ -18978,7 +18978,7 @@
         <v>27</v>
       </c>
       <c r="D874">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E874" t="s">
         <v>28</v>
@@ -18995,7 +18995,7 @@
         <v>27</v>
       </c>
       <c r="D875">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E875" t="s">
         <v>28</v>
@@ -19012,7 +19012,7 @@
         <v>27</v>
       </c>
       <c r="D876">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E876" t="s">
         <v>28</v>
@@ -19029,7 +19029,7 @@
         <v>27</v>
       </c>
       <c r="D877">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E877" t="s">
         <v>28</v>
@@ -19063,7 +19063,7 @@
         <v>27</v>
       </c>
       <c r="D879">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E879" t="s">
         <v>28</v>
@@ -19080,7 +19080,7 @@
         <v>27</v>
       </c>
       <c r="D880">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E880" t="s">
         <v>28</v>
@@ -19097,7 +19097,7 @@
         <v>27</v>
       </c>
       <c r="D881">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E881" t="s">
         <v>28</v>
@@ -19114,7 +19114,7 @@
         <v>27</v>
       </c>
       <c r="D882">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E882" t="s">
         <v>28</v>
@@ -19131,7 +19131,7 @@
         <v>27</v>
       </c>
       <c r="D883">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E883" t="s">
         <v>28</v>
@@ -19148,7 +19148,7 @@
         <v>27</v>
       </c>
       <c r="D884">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E884" t="s">
         <v>28</v>
@@ -19182,7 +19182,7 @@
         <v>27</v>
       </c>
       <c r="D886">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E886" t="s">
         <v>28</v>
@@ -19199,7 +19199,7 @@
         <v>27</v>
       </c>
       <c r="D887">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E887" t="s">
         <v>28</v>
@@ -19216,7 +19216,7 @@
         <v>27</v>
       </c>
       <c r="D888">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E888" t="s">
         <v>28</v>
@@ -19233,7 +19233,7 @@
         <v>27</v>
       </c>
       <c r="D889">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E889" t="s">
         <v>28</v>
@@ -19250,7 +19250,7 @@
         <v>27</v>
       </c>
       <c r="D890">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E890" t="s">
         <v>28</v>
@@ -19267,7 +19267,7 @@
         <v>27</v>
       </c>
       <c r="D891">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E891" t="s">
         <v>28</v>
@@ -19284,7 +19284,7 @@
         <v>27</v>
       </c>
       <c r="D892">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E892" t="s">
         <v>28</v>
@@ -19301,7 +19301,7 @@
         <v>27</v>
       </c>
       <c r="D893">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E893" t="s">
         <v>28</v>
@@ -19318,7 +19318,7 @@
         <v>27</v>
       </c>
       <c r="D894">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E894" t="s">
         <v>28</v>
@@ -19335,7 +19335,7 @@
         <v>27</v>
       </c>
       <c r="D895">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E895" t="s">
         <v>28</v>
@@ -19352,7 +19352,7 @@
         <v>27</v>
       </c>
       <c r="D896">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E896" t="s">
         <v>28</v>
@@ -19369,7 +19369,7 @@
         <v>27</v>
       </c>
       <c r="D897">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E897" t="s">
         <v>28</v>
@@ -19386,7 +19386,7 @@
         <v>27</v>
       </c>
       <c r="D898">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E898" t="s">
         <v>28</v>
@@ -19403,7 +19403,7 @@
         <v>27</v>
       </c>
       <c r="D899">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E899" t="s">
         <v>28</v>
@@ -19420,7 +19420,7 @@
         <v>27</v>
       </c>
       <c r="D900">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E900" t="s">
         <v>28</v>
@@ -19437,7 +19437,7 @@
         <v>27</v>
       </c>
       <c r="D901">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E901" t="s">
         <v>28</v>
@@ -19454,7 +19454,7 @@
         <v>27</v>
       </c>
       <c r="D902">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E902" t="s">
         <v>28</v>
@@ -19471,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D903">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E903" t="s">
         <v>28</v>
@@ -19488,7 +19488,7 @@
         <v>27</v>
       </c>
       <c r="D904">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E904" t="s">
         <v>28</v>
@@ -19505,7 +19505,7 @@
         <v>27</v>
       </c>
       <c r="D905">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E905" t="s">
         <v>28</v>
@@ -19539,7 +19539,7 @@
         <v>27</v>
       </c>
       <c r="D907">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E907" t="s">
         <v>28</v>
@@ -19556,7 +19556,7 @@
         <v>27</v>
       </c>
       <c r="D908">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E908" t="s">
         <v>28</v>
@@ -19573,7 +19573,7 @@
         <v>27</v>
       </c>
       <c r="D909">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E909" t="s">
         <v>28</v>
@@ -19590,7 +19590,7 @@
         <v>27</v>
       </c>
       <c r="D910">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E910" t="s">
         <v>28</v>
@@ -19624,7 +19624,7 @@
         <v>27</v>
       </c>
       <c r="D912">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E912" t="s">
         <v>28</v>
@@ -19641,7 +19641,7 @@
         <v>27</v>
       </c>
       <c r="D913">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E913" t="s">
         <v>28</v>
@@ -19658,7 +19658,7 @@
         <v>27</v>
       </c>
       <c r="D914">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E914" t="s">
         <v>28</v>
@@ -19675,7 +19675,7 @@
         <v>27</v>
       </c>
       <c r="D915">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E915" t="s">
         <v>28</v>
@@ -19692,7 +19692,7 @@
         <v>27</v>
       </c>
       <c r="D916">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E916" t="s">
         <v>28</v>
@@ -19709,7 +19709,7 @@
         <v>27</v>
       </c>
       <c r="D917">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E917" t="s">
         <v>28</v>
@@ -19726,7 +19726,7 @@
         <v>27</v>
       </c>
       <c r="D918">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E918" t="s">
         <v>28</v>
@@ -19743,7 +19743,7 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E919" t="s">
         <v>28</v>
@@ -19760,7 +19760,7 @@
         <v>27</v>
       </c>
       <c r="D920">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E920" t="s">
         <v>28</v>
@@ -19777,7 +19777,7 @@
         <v>27</v>
       </c>
       <c r="D921">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E921" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>27</v>
       </c>
       <c r="D922">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E922" t="s">
         <v>28</v>
@@ -19811,7 +19811,7 @@
         <v>27</v>
       </c>
       <c r="D923">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E923" t="s">
         <v>28</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="D924">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E924" t="s">
         <v>28</v>
@@ -19845,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="D925">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E925" t="s">
         <v>28</v>
@@ -19862,7 +19862,7 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E926" t="s">
         <v>28</v>
@@ -19879,7 +19879,7 @@
         <v>27</v>
       </c>
       <c r="D927">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E927" t="s">
         <v>28</v>
@@ -19896,7 +19896,7 @@
         <v>27</v>
       </c>
       <c r="D928">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E928" t="s">
         <v>28</v>
@@ -19913,7 +19913,7 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E929" t="s">
         <v>28</v>
@@ -19930,7 +19930,7 @@
         <v>27</v>
       </c>
       <c r="D930">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E930" t="s">
         <v>28</v>
@@ -19947,7 +19947,7 @@
         <v>27</v>
       </c>
       <c r="D931">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E931" t="s">
         <v>28</v>
@@ -19964,7 +19964,7 @@
         <v>27</v>
       </c>
       <c r="D932">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E932" t="s">
         <v>28</v>
@@ -19981,7 +19981,7 @@
         <v>27</v>
       </c>
       <c r="D933">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E933" t="s">
         <v>28</v>
@@ -19998,7 +19998,7 @@
         <v>27</v>
       </c>
       <c r="D934">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E934" t="s">
         <v>28</v>
@@ -20015,7 +20015,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E935" t="s">
         <v>28</v>
@@ -20032,7 +20032,7 @@
         <v>27</v>
       </c>
       <c r="D936">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E936" t="s">
         <v>28</v>
@@ -20066,7 +20066,7 @@
         <v>27</v>
       </c>
       <c r="D938">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E938" t="s">
         <v>28</v>
@@ -20083,7 +20083,7 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E939" t="s">
         <v>28</v>
@@ -20100,7 +20100,7 @@
         <v>27</v>
       </c>
       <c r="D940">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E940" t="s">
         <v>28</v>
@@ -20117,7 +20117,7 @@
         <v>27</v>
       </c>
       <c r="D941">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E941" t="s">
         <v>28</v>
@@ -20134,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D942">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E942" t="s">
         <v>28</v>
@@ -20151,7 +20151,7 @@
         <v>27</v>
       </c>
       <c r="D943">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E943" t="s">
         <v>28</v>
@@ -20168,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="D944">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E944" t="s">
         <v>28</v>
@@ -20185,7 +20185,7 @@
         <v>27</v>
       </c>
       <c r="D945">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E945" t="s">
         <v>28</v>
@@ -20202,7 +20202,7 @@
         <v>27</v>
       </c>
       <c r="D946">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E946" t="s">
         <v>28</v>
@@ -20219,7 +20219,7 @@
         <v>27</v>
       </c>
       <c r="D947">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E947" t="s">
         <v>28</v>
@@ -20236,7 +20236,7 @@
         <v>27</v>
       </c>
       <c r="D948">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E948" t="s">
         <v>28</v>
@@ -20253,7 +20253,7 @@
         <v>27</v>
       </c>
       <c r="D949">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E949" t="s">
         <v>28</v>
@@ -20270,7 +20270,7 @@
         <v>27</v>
       </c>
       <c r="D950">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E950" t="s">
         <v>28</v>
@@ -20304,7 +20304,7 @@
         <v>27</v>
       </c>
       <c r="D952">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E952" t="s">
         <v>28</v>
@@ -20321,7 +20321,7 @@
         <v>27</v>
       </c>
       <c r="D953">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E953" t="s">
         <v>28</v>
@@ -20355,7 +20355,7 @@
         <v>27</v>
       </c>
       <c r="D955">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E955" t="s">
         <v>28</v>
@@ -20372,7 +20372,7 @@
         <v>27</v>
       </c>
       <c r="D956">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E956" t="s">
         <v>28</v>
@@ -20389,7 +20389,7 @@
         <v>27</v>
       </c>
       <c r="D957">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E957" t="s">
         <v>28</v>
@@ -20406,7 +20406,7 @@
         <v>27</v>
       </c>
       <c r="D958">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E958" t="s">
         <v>28</v>
@@ -20423,7 +20423,7 @@
         <v>27</v>
       </c>
       <c r="D959">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E959" t="s">
         <v>28</v>
@@ -20440,7 +20440,7 @@
         <v>27</v>
       </c>
       <c r="D960">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E960" t="s">
         <v>28</v>
@@ -20457,7 +20457,7 @@
         <v>27</v>
       </c>
       <c r="D961">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E961" t="s">
         <v>28</v>
@@ -20474,7 +20474,7 @@
         <v>27</v>
       </c>
       <c r="D962">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E962" t="s">
         <v>28</v>
@@ -20491,7 +20491,7 @@
         <v>27</v>
       </c>
       <c r="D963">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E963" t="s">
         <v>28</v>
@@ -20508,7 +20508,7 @@
         <v>27</v>
       </c>
       <c r="D964">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E964" t="s">
         <v>28</v>
@@ -20542,7 +20542,7 @@
         <v>27</v>
       </c>
       <c r="D966">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E966" t="s">
         <v>28</v>
@@ -20559,7 +20559,7 @@
         <v>27</v>
       </c>
       <c r="D967">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E967" t="s">
         <v>28</v>
@@ -20576,7 +20576,7 @@
         <v>27</v>
       </c>
       <c r="D968">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E968" t="s">
         <v>28</v>
@@ -20593,7 +20593,7 @@
         <v>27</v>
       </c>
       <c r="D969">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E969" t="s">
         <v>28</v>
@@ -20610,7 +20610,7 @@
         <v>27</v>
       </c>
       <c r="D970">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E970" t="s">
         <v>28</v>
@@ -20627,7 +20627,7 @@
         <v>27</v>
       </c>
       <c r="D971">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E971" t="s">
         <v>28</v>
@@ -20644,7 +20644,7 @@
         <v>27</v>
       </c>
       <c r="D972">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E972" t="s">
         <v>28</v>
@@ -20661,7 +20661,7 @@
         <v>27</v>
       </c>
       <c r="D973">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E973" t="s">
         <v>28</v>
@@ -20678,7 +20678,7 @@
         <v>27</v>
       </c>
       <c r="D974">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E974" t="s">
         <v>28</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="D975">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E975" t="s">
         <v>28</v>
@@ -20712,7 +20712,7 @@
         <v>27</v>
       </c>
       <c r="D976">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E976" t="s">
         <v>28</v>
@@ -20729,7 +20729,7 @@
         <v>27</v>
       </c>
       <c r="D977">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E977" t="s">
         <v>28</v>
@@ -20746,7 +20746,7 @@
         <v>27</v>
       </c>
       <c r="D978">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E978" t="s">
         <v>28</v>
@@ -20763,7 +20763,7 @@
         <v>27</v>
       </c>
       <c r="D979">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E979" t="s">
         <v>28</v>
@@ -20780,7 +20780,7 @@
         <v>27</v>
       </c>
       <c r="D980">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E980" t="s">
         <v>28</v>
@@ -20797,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="D981">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E981" t="s">
         <v>28</v>
@@ -20814,7 +20814,7 @@
         <v>27</v>
       </c>
       <c r="D982">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E982" t="s">
         <v>28</v>
@@ -20831,7 +20831,7 @@
         <v>27</v>
       </c>
       <c r="D983">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E983" t="s">
         <v>28</v>
@@ -20848,7 +20848,7 @@
         <v>27</v>
       </c>
       <c r="D984">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E984" t="s">
         <v>28</v>
@@ -20865,7 +20865,7 @@
         <v>27</v>
       </c>
       <c r="D985">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E985" t="s">
         <v>28</v>
@@ -20882,7 +20882,7 @@
         <v>27</v>
       </c>
       <c r="D986">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E986" t="s">
         <v>28</v>
@@ -20899,7 +20899,7 @@
         <v>27</v>
       </c>
       <c r="D987">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E987" t="s">
         <v>28</v>
@@ -20916,7 +20916,7 @@
         <v>27</v>
       </c>
       <c r="D988">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E988" t="s">
         <v>28</v>
@@ -20933,7 +20933,7 @@
         <v>27</v>
       </c>
       <c r="D989">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E989" t="s">
         <v>28</v>
@@ -20967,7 +20967,7 @@
         <v>27</v>
       </c>
       <c r="D991">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E991" t="s">
         <v>28</v>
@@ -20984,7 +20984,7 @@
         <v>27</v>
       </c>
       <c r="D992">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E992" t="s">
         <v>28</v>
@@ -21001,7 +21001,7 @@
         <v>27</v>
       </c>
       <c r="D993">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E993" t="s">
         <v>28</v>
@@ -21018,7 +21018,7 @@
         <v>27</v>
       </c>
       <c r="D994">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E994" t="s">
         <v>28</v>
@@ -21052,7 +21052,7 @@
         <v>27</v>
       </c>
       <c r="D996">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E996" t="s">
         <v>28</v>
@@ -21069,7 +21069,7 @@
         <v>27</v>
       </c>
       <c r="D997">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E997" t="s">
         <v>28</v>
@@ -21086,7 +21086,7 @@
         <v>27</v>
       </c>
       <c r="D998">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E998" t="s">
         <v>28</v>
@@ -21103,7 +21103,7 @@
         <v>27</v>
       </c>
       <c r="D999">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E999" t="s">
         <v>28</v>
@@ -21120,7 +21120,7 @@
         <v>27</v>
       </c>
       <c r="D1000">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1000" t="s">
         <v>28</v>
@@ -21137,7 +21137,7 @@
         <v>27</v>
       </c>
       <c r="D1001">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1001" t="s">
         <v>28</v>
@@ -21154,7 +21154,7 @@
         <v>27</v>
       </c>
       <c r="D1002">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1002" t="s">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>27</v>
       </c>
       <c r="D1003">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1003" t="s">
         <v>28</v>
@@ -21188,7 +21188,7 @@
         <v>27</v>
       </c>
       <c r="D1004">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E1004" t="s">
         <v>28</v>
@@ -21205,7 +21205,7 @@
         <v>27</v>
       </c>
       <c r="D1005">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1005" t="s">
         <v>28</v>
@@ -21222,7 +21222,7 @@
         <v>27</v>
       </c>
       <c r="D1006">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E1006" t="s">
         <v>28</v>
@@ -21239,7 +21239,7 @@
         <v>27</v>
       </c>
       <c r="D1007">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E1007" t="s">
         <v>28</v>
@@ -21256,7 +21256,7 @@
         <v>27</v>
       </c>
       <c r="D1008">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E1008" t="s">
         <v>28</v>
@@ -21273,7 +21273,7 @@
         <v>27</v>
       </c>
       <c r="D1009">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1009" t="s">
         <v>28</v>
@@ -21290,7 +21290,7 @@
         <v>27</v>
       </c>
       <c r="D1010">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1010" t="s">
         <v>28</v>
@@ -21307,7 +21307,7 @@
         <v>27</v>
       </c>
       <c r="D1011">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1011" t="s">
         <v>28</v>
@@ -21324,7 +21324,7 @@
         <v>27</v>
       </c>
       <c r="D1012">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E1012" t="s">
         <v>28</v>
@@ -21341,7 +21341,7 @@
         <v>27</v>
       </c>
       <c r="D1013">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1013" t="s">
         <v>28</v>
@@ -21358,7 +21358,7 @@
         <v>27</v>
       </c>
       <c r="D1014">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E1014" t="s">
         <v>28</v>
@@ -21375,7 +21375,7 @@
         <v>27</v>
       </c>
       <c r="D1015">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E1015" t="s">
         <v>28</v>
@@ -21392,7 +21392,7 @@
         <v>27</v>
       </c>
       <c r="D1016">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1016" t="s">
         <v>28</v>
@@ -21409,7 +21409,7 @@
         <v>27</v>
       </c>
       <c r="D1017">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1017" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>27</v>
       </c>
       <c r="D1018">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1018" t="s">
         <v>28</v>
@@ -21460,7 +21460,7 @@
         <v>27</v>
       </c>
       <c r="D1020">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1020" t="s">
         <v>28</v>
@@ -21477,7 +21477,7 @@
         <v>27</v>
       </c>
       <c r="D1021">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E1021" t="s">
         <v>28</v>
@@ -21494,7 +21494,7 @@
         <v>27</v>
       </c>
       <c r="D1022">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1022" t="s">
         <v>28</v>
@@ -21511,7 +21511,7 @@
         <v>27</v>
       </c>
       <c r="D1023">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1023" t="s">
         <v>28</v>
@@ -21528,7 +21528,7 @@
         <v>27</v>
       </c>
       <c r="D1024">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1024" t="s">
         <v>28</v>
@@ -21545,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E1025" t="s">
         <v>28</v>
@@ -21562,7 +21562,7 @@
         <v>27</v>
       </c>
       <c r="D1026">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1026" t="s">
         <v>28</v>
@@ -21579,7 +21579,7 @@
         <v>27</v>
       </c>
       <c r="D1027">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1027" t="s">
         <v>28</v>
@@ -21596,7 +21596,7 @@
         <v>27</v>
       </c>
       <c r="D1028">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E1028" t="s">
         <v>28</v>
@@ -21613,7 +21613,7 @@
         <v>27</v>
       </c>
       <c r="D1029">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E1029" t="s">
         <v>28</v>
@@ -21630,7 +21630,7 @@
         <v>27</v>
       </c>
       <c r="D1030">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E1030" t="s">
         <v>28</v>
@@ -21664,7 +21664,7 @@
         <v>27</v>
       </c>
       <c r="D1032">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1032" t="s">
         <v>28</v>
@@ -21681,7 +21681,7 @@
         <v>27</v>
       </c>
       <c r="D1033">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E1033" t="s">
         <v>28</v>
@@ -21698,7 +21698,7 @@
         <v>27</v>
       </c>
       <c r="D1034">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E1034" t="s">
         <v>28</v>
@@ -21715,7 +21715,7 @@
         <v>27</v>
       </c>
       <c r="D1035">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1035" t="s">
         <v>28</v>
@@ -21732,7 +21732,7 @@
         <v>27</v>
       </c>
       <c r="D1036">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E1036" t="s">
         <v>28</v>
@@ -21749,7 +21749,7 @@
         <v>27</v>
       </c>
       <c r="D1037">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1037" t="s">
         <v>28</v>
@@ -21766,7 +21766,7 @@
         <v>27</v>
       </c>
       <c r="D1038">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1038" t="s">
         <v>28</v>
@@ -21783,7 +21783,7 @@
         <v>27</v>
       </c>
       <c r="D1039">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1039" t="s">
         <v>28</v>
@@ -21800,7 +21800,7 @@
         <v>27</v>
       </c>
       <c r="D1040">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E1040" t="s">
         <v>28</v>
@@ -21817,7 +21817,7 @@
         <v>27</v>
       </c>
       <c r="D1041">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1041" t="s">
         <v>28</v>
@@ -21834,7 +21834,7 @@
         <v>27</v>
       </c>
       <c r="D1042">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E1042" t="s">
         <v>28</v>
@@ -21851,7 +21851,7 @@
         <v>27</v>
       </c>
       <c r="D1043">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E1043" t="s">
         <v>28</v>
@@ -21868,7 +21868,7 @@
         <v>27</v>
       </c>
       <c r="D1044">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1044" t="s">
         <v>28</v>
@@ -21885,7 +21885,7 @@
         <v>27</v>
       </c>
       <c r="D1045">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1045" t="s">
         <v>28</v>
@@ -21902,7 +21902,7 @@
         <v>27</v>
       </c>
       <c r="D1046">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E1046" t="s">
         <v>28</v>
@@ -21919,7 +21919,7 @@
         <v>27</v>
       </c>
       <c r="D1047">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1047" t="s">
         <v>28</v>
@@ -21936,7 +21936,7 @@
         <v>27</v>
       </c>
       <c r="D1048">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1048" t="s">
         <v>28</v>
@@ -21953,7 +21953,7 @@
         <v>27</v>
       </c>
       <c r="D1049">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1049" t="s">
         <v>28</v>
@@ -21970,7 +21970,7 @@
         <v>27</v>
       </c>
       <c r="D1050">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E1050" t="s">
         <v>28</v>
@@ -22004,7 +22004,7 @@
         <v>27</v>
       </c>
       <c r="D1052">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1052" t="s">
         <v>28</v>
@@ -22021,7 +22021,7 @@
         <v>27</v>
       </c>
       <c r="D1053">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E1053" t="s">
         <v>28</v>
@@ -22038,7 +22038,7 @@
         <v>27</v>
       </c>
       <c r="D1054">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E1054" t="s">
         <v>28</v>
@@ -22055,7 +22055,7 @@
         <v>27</v>
       </c>
       <c r="D1055">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1055" t="s">
         <v>28</v>
@@ -22072,7 +22072,7 @@
         <v>27</v>
       </c>
       <c r="D1056">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1056" t="s">
         <v>28</v>
@@ -22089,7 +22089,7 @@
         <v>27</v>
       </c>
       <c r="D1057">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1057" t="s">
         <v>28</v>
@@ -22106,7 +22106,7 @@
         <v>27</v>
       </c>
       <c r="D1058">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E1058" t="s">
         <v>28</v>
@@ -22123,7 +22123,7 @@
         <v>27</v>
       </c>
       <c r="D1059">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1059" t="s">
         <v>28</v>
@@ -22140,7 +22140,7 @@
         <v>27</v>
       </c>
       <c r="D1060">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1060" t="s">
         <v>28</v>
@@ -22157,7 +22157,7 @@
         <v>27</v>
       </c>
       <c r="D1061">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E1061" t="s">
         <v>28</v>
@@ -22174,7 +22174,7 @@
         <v>27</v>
       </c>
       <c r="D1062">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1062" t="s">
         <v>28</v>
@@ -22191,7 +22191,7 @@
         <v>27</v>
       </c>
       <c r="D1063">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1063" t="s">
         <v>28</v>
@@ -22208,7 +22208,7 @@
         <v>27</v>
       </c>
       <c r="D1064">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1064" t="s">
         <v>28</v>
@@ -22225,7 +22225,7 @@
         <v>27</v>
       </c>
       <c r="D1065">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E1065" t="s">
         <v>28</v>
@@ -22242,7 +22242,7 @@
         <v>27</v>
       </c>
       <c r="D1066">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E1066" t="s">
         <v>28</v>
@@ -22259,7 +22259,7 @@
         <v>27</v>
       </c>
       <c r="D1067">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1067" t="s">
         <v>28</v>
@@ -22293,7 +22293,7 @@
         <v>27</v>
       </c>
       <c r="D1069">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E1069" t="s">
         <v>28</v>
@@ -22310,7 +22310,7 @@
         <v>27</v>
       </c>
       <c r="D1070">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E1070" t="s">
         <v>28</v>
@@ -22327,7 +22327,7 @@
         <v>27</v>
       </c>
       <c r="D1071">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E1071" t="s">
         <v>28</v>
@@ -22344,7 +22344,7 @@
         <v>27</v>
       </c>
       <c r="D1072">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1072" t="s">
         <v>28</v>
@@ -22361,7 +22361,7 @@
         <v>27</v>
       </c>
       <c r="D1073">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E1073" t="s">
         <v>28</v>
@@ -22378,7 +22378,7 @@
         <v>27</v>
       </c>
       <c r="D1074">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1074" t="s">
         <v>28</v>
@@ -22395,7 +22395,7 @@
         <v>27</v>
       </c>
       <c r="D1075">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1075" t="s">
         <v>28</v>
@@ -22412,7 +22412,7 @@
         <v>27</v>
       </c>
       <c r="D1076">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1076" t="s">
         <v>28</v>
@@ -22429,7 +22429,7 @@
         <v>27</v>
       </c>
       <c r="D1077">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E1077" t="s">
         <v>28</v>
@@ -22446,7 +22446,7 @@
         <v>27</v>
       </c>
       <c r="D1078">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E1078" t="s">
         <v>28</v>
@@ -22463,7 +22463,7 @@
         <v>27</v>
       </c>
       <c r="D1079">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E1079" t="s">
         <v>28</v>
@@ -22480,7 +22480,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E1080" t="s">
         <v>28</v>
@@ -22531,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="D1083">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1083" t="s">
         <v>28</v>
@@ -22548,7 +22548,7 @@
         <v>27</v>
       </c>
       <c r="D1084">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1084" t="s">
         <v>28</v>
@@ -22565,7 +22565,7 @@
         <v>27</v>
       </c>
       <c r="D1085">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1085" t="s">
         <v>28</v>
@@ -22582,7 +22582,7 @@
         <v>27</v>
       </c>
       <c r="D1086">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E1086" t="s">
         <v>28</v>
@@ -22616,7 +22616,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E1088" t="s">
         <v>28</v>
@@ -22633,7 +22633,7 @@
         <v>27</v>
       </c>
       <c r="D1089">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1089" t="s">
         <v>28</v>
@@ -22650,7 +22650,7 @@
         <v>27</v>
       </c>
       <c r="D1090">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E1090" t="s">
         <v>28</v>
@@ -22667,7 +22667,7 @@
         <v>27</v>
       </c>
       <c r="D1091">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1091" t="s">
         <v>28</v>
@@ -22684,7 +22684,7 @@
         <v>27</v>
       </c>
       <c r="D1092">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1092" t="s">
         <v>28</v>
@@ -22701,7 +22701,7 @@
         <v>27</v>
       </c>
       <c r="D1093">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1093" t="s">
         <v>28</v>
@@ -22718,7 +22718,7 @@
         <v>27</v>
       </c>
       <c r="D1094">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E1094" t="s">
         <v>28</v>
@@ -22735,7 +22735,7 @@
         <v>27</v>
       </c>
       <c r="D1095">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1095" t="s">
         <v>28</v>
@@ -22769,7 +22769,7 @@
         <v>27</v>
       </c>
       <c r="D1097">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E1097" t="s">
         <v>28</v>
@@ -22786,7 +22786,7 @@
         <v>27</v>
       </c>
       <c r="D1098">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E1098" t="s">
         <v>28</v>
@@ -22803,7 +22803,7 @@
         <v>27</v>
       </c>
       <c r="D1099">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1099" t="s">
         <v>28</v>
@@ -22820,7 +22820,7 @@
         <v>27</v>
       </c>
       <c r="D1100">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1100" t="s">
         <v>28</v>
@@ -22837,7 +22837,7 @@
         <v>27</v>
       </c>
       <c r="D1101">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1101" t="s">
         <v>28</v>
@@ -22854,7 +22854,7 @@
         <v>27</v>
       </c>
       <c r="D1102">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1102" t="s">
         <v>28</v>
@@ -22871,7 +22871,7 @@
         <v>27</v>
       </c>
       <c r="D1103">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E1103" t="s">
         <v>28</v>
@@ -22888,7 +22888,7 @@
         <v>27</v>
       </c>
       <c r="D1104">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E1104" t="s">
         <v>28</v>
@@ -22905,7 +22905,7 @@
         <v>27</v>
       </c>
       <c r="D1105">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1105" t="s">
         <v>28</v>
@@ -22922,7 +22922,7 @@
         <v>27</v>
       </c>
       <c r="D1106">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1106" t="s">
         <v>28</v>
@@ -22939,7 +22939,7 @@
         <v>27</v>
       </c>
       <c r="D1107">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1107" t="s">
         <v>28</v>
@@ -22956,7 +22956,7 @@
         <v>27</v>
       </c>
       <c r="D1108">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E1108" t="s">
         <v>28</v>
@@ -22973,7 +22973,7 @@
         <v>27</v>
       </c>
       <c r="D1109">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1109" t="s">
         <v>28</v>
@@ -22990,7 +22990,7 @@
         <v>27</v>
       </c>
       <c r="D1110">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E1110" t="s">
         <v>28</v>
@@ -23007,7 +23007,7 @@
         <v>27</v>
       </c>
       <c r="D1111">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1111" t="s">
         <v>28</v>
@@ -23024,7 +23024,7 @@
         <v>27</v>
       </c>
       <c r="D1112">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1112" t="s">
         <v>28</v>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1284</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1243</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1263</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1342</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1336</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1288</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1261</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1320</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1245</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1313</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1252</v>
+        <v>1262</v>
       </c>
     </row>
   </sheetData>
@@ -4154,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -4188,7 +4188,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -4205,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -4222,7 +4222,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -4256,7 +4256,7 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4307,7 +4307,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4341,7 +4341,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -4358,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4409,7 +4409,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -4426,7 +4426,7 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -4443,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
@@ -4494,7 +4494,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -4511,7 +4511,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -4528,7 +4528,7 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -4545,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E25" t="s">
         <v>28</v>
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -4579,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -4596,7 +4596,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -4613,7 +4613,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E29" t="s">
         <v>28</v>
@@ -4647,7 +4647,7 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4681,7 +4681,7 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4698,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="D34">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -4715,7 +4715,7 @@
         <v>27</v>
       </c>
       <c r="D35">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E35" t="s">
         <v>28</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="D38">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
         <v>28</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
@@ -4817,7 +4817,7 @@
         <v>27</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4834,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4851,7 +4851,7 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
         <v>27</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -4919,7 +4919,7 @@
         <v>27</v>
       </c>
       <c r="D47">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="D48">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4953,7 +4953,7 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
@@ -4970,7 +4970,7 @@
         <v>27</v>
       </c>
       <c r="D50">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -4987,7 +4987,7 @@
         <v>27</v>
       </c>
       <c r="D51">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
@@ -5004,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5038,7 +5038,7 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E54" t="s">
         <v>28</v>
@@ -5055,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="D55">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -5072,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
         <v>28</v>
@@ -5089,7 +5089,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E57" t="s">
         <v>28</v>
@@ -5106,7 +5106,7 @@
         <v>27</v>
       </c>
       <c r="D58">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -5123,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E59" t="s">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         <v>27</v>
       </c>
       <c r="D60">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E60" t="s">
         <v>28</v>
@@ -5157,7 +5157,7 @@
         <v>27</v>
       </c>
       <c r="D61">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -5174,7 +5174,7 @@
         <v>27</v>
       </c>
       <c r="D62">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
@@ -5191,7 +5191,7 @@
         <v>27</v>
       </c>
       <c r="D63">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="D64">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
@@ -5225,7 +5225,7 @@
         <v>27</v>
       </c>
       <c r="D65">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -5242,7 +5242,7 @@
         <v>27</v>
       </c>
       <c r="D66">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="D67">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
@@ -5293,7 +5293,7 @@
         <v>27</v>
       </c>
       <c r="D69">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -5310,7 +5310,7 @@
         <v>27</v>
       </c>
       <c r="D70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="D71">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -5344,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="D72">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
@@ -5378,7 +5378,7 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
@@ -5395,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="D76">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
@@ -5429,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -5446,7 +5446,7 @@
         <v>27</v>
       </c>
       <c r="D78">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
@@ -5463,7 +5463,7 @@
         <v>27</v>
       </c>
       <c r="D79">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
@@ -5480,7 +5480,7 @@
         <v>27</v>
       </c>
       <c r="D80">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
@@ -5497,7 +5497,7 @@
         <v>27</v>
       </c>
       <c r="D81">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -5514,7 +5514,7 @@
         <v>27</v>
       </c>
       <c r="D82">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
@@ -5531,7 +5531,7 @@
         <v>27</v>
       </c>
       <c r="D83">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
@@ -5548,7 +5548,7 @@
         <v>27</v>
       </c>
       <c r="D84">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
@@ -5565,7 +5565,7 @@
         <v>27</v>
       </c>
       <c r="D85">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -5582,7 +5582,7 @@
         <v>27</v>
       </c>
       <c r="D86">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
@@ -5599,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="D87">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
@@ -5616,7 +5616,7 @@
         <v>27</v>
       </c>
       <c r="D88">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -5633,7 +5633,7 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="D90">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -5667,7 +5667,7 @@
         <v>27</v>
       </c>
       <c r="D91">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E91" t="s">
         <v>28</v>
@@ -5684,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="D92">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
@@ -5701,7 +5701,7 @@
         <v>27</v>
       </c>
       <c r="D93">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E93" t="s">
         <v>28</v>
@@ -5735,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D95">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -5752,7 +5752,7 @@
         <v>27</v>
       </c>
       <c r="D96">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E96" t="s">
         <v>28</v>
@@ -5769,7 +5769,7 @@
         <v>27</v>
       </c>
       <c r="D97">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E97" t="s">
         <v>28</v>
@@ -5786,7 +5786,7 @@
         <v>27</v>
       </c>
       <c r="D98">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -5837,7 +5837,7 @@
         <v>27</v>
       </c>
       <c r="D101">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
         <v>28</v>
@@ -5854,7 +5854,7 @@
         <v>27</v>
       </c>
       <c r="D102">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E102" t="s">
         <v>28</v>
@@ -5871,7 +5871,7 @@
         <v>27</v>
       </c>
       <c r="D103">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E103" t="s">
         <v>28</v>
@@ -5888,7 +5888,7 @@
         <v>27</v>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E104" t="s">
         <v>28</v>
@@ -5905,7 +5905,7 @@
         <v>27</v>
       </c>
       <c r="D105">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E105" t="s">
         <v>28</v>
@@ -5922,7 +5922,7 @@
         <v>27</v>
       </c>
       <c r="D106">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>27</v>
       </c>
       <c r="D107">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E107" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="D108">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5973,7 +5973,7 @@
         <v>27</v>
       </c>
       <c r="D109">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E109" t="s">
         <v>28</v>
@@ -5990,7 +5990,7 @@
         <v>27</v>
       </c>
       <c r="D110">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E110" t="s">
         <v>28</v>
@@ -6007,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="D111">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="D112">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="D113">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E113" t="s">
         <v>28</v>
@@ -6058,7 +6058,7 @@
         <v>27</v>
       </c>
       <c r="D114">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>27</v>
       </c>
       <c r="D115">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -6092,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="D116">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E116" t="s">
         <v>28</v>
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="D117">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E117" t="s">
         <v>28</v>
@@ -6126,7 +6126,7 @@
         <v>27</v>
       </c>
       <c r="D118">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E118" t="s">
         <v>28</v>
@@ -6143,7 +6143,7 @@
         <v>27</v>
       </c>
       <c r="D119">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E119" t="s">
         <v>28</v>
@@ -6160,7 +6160,7 @@
         <v>27</v>
       </c>
       <c r="D120">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E120" t="s">
         <v>28</v>
@@ -6177,7 +6177,7 @@
         <v>27</v>
       </c>
       <c r="D121">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E121" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="D122">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E122" t="s">
         <v>28</v>
@@ -6211,7 +6211,7 @@
         <v>27</v>
       </c>
       <c r="D123">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E123" t="s">
         <v>28</v>
@@ -6228,7 +6228,7 @@
         <v>27</v>
       </c>
       <c r="D124">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E124" t="s">
         <v>28</v>
@@ -6245,7 +6245,7 @@
         <v>27</v>
       </c>
       <c r="D125">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
@@ -6262,7 +6262,7 @@
         <v>27</v>
       </c>
       <c r="D126">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -6279,7 +6279,7 @@
         <v>27</v>
       </c>
       <c r="D127">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E127" t="s">
         <v>28</v>
@@ -6296,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="D128">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E128" t="s">
         <v>28</v>
@@ -6313,7 +6313,7 @@
         <v>27</v>
       </c>
       <c r="D129">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
@@ -6330,7 +6330,7 @@
         <v>27</v>
       </c>
       <c r="D130">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E130" t="s">
         <v>28</v>
@@ -6347,7 +6347,7 @@
         <v>27</v>
       </c>
       <c r="D131">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E131" t="s">
         <v>28</v>
@@ -6364,7 +6364,7 @@
         <v>27</v>
       </c>
       <c r="D132">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E132" t="s">
         <v>28</v>
@@ -6381,7 +6381,7 @@
         <v>27</v>
       </c>
       <c r="D133">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E133" t="s">
         <v>28</v>
@@ -6398,7 +6398,7 @@
         <v>27</v>
       </c>
       <c r="D134">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E134" t="s">
         <v>28</v>
@@ -6415,7 +6415,7 @@
         <v>27</v>
       </c>
       <c r="D135">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E135" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="D136">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E136" t="s">
         <v>28</v>
@@ -6449,7 +6449,7 @@
         <v>27</v>
       </c>
       <c r="D137">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E137" t="s">
         <v>28</v>
@@ -6466,7 +6466,7 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E138" t="s">
         <v>28</v>
@@ -6483,7 +6483,7 @@
         <v>27</v>
       </c>
       <c r="D139">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E139" t="s">
         <v>28</v>
@@ -6500,7 +6500,7 @@
         <v>27</v>
       </c>
       <c r="D140">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E140" t="s">
         <v>28</v>
@@ -6517,7 +6517,7 @@
         <v>27</v>
       </c>
       <c r="D141">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E141" t="s">
         <v>28</v>
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="D142">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E142" t="s">
         <v>28</v>
@@ -6551,7 +6551,7 @@
         <v>27</v>
       </c>
       <c r="D143">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E143" t="s">
         <v>28</v>
@@ -6568,7 +6568,7 @@
         <v>27</v>
       </c>
       <c r="D144">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E144" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="D145">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E145" t="s">
         <v>28</v>
@@ -6602,7 +6602,7 @@
         <v>27</v>
       </c>
       <c r="D146">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E146" t="s">
         <v>28</v>
@@ -6619,7 +6619,7 @@
         <v>27</v>
       </c>
       <c r="D147">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E147" t="s">
         <v>28</v>
@@ -6636,7 +6636,7 @@
         <v>27</v>
       </c>
       <c r="D148">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E148" t="s">
         <v>28</v>
@@ -6653,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="D149">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6670,7 +6670,7 @@
         <v>27</v>
       </c>
       <c r="D150">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E150" t="s">
         <v>28</v>
@@ -6687,7 +6687,7 @@
         <v>27</v>
       </c>
       <c r="D151">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>27</v>
       </c>
       <c r="D152">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E152" t="s">
         <v>28</v>
@@ -6721,7 +6721,7 @@
         <v>27</v>
       </c>
       <c r="D153">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E153" t="s">
         <v>28</v>
@@ -6738,7 +6738,7 @@
         <v>27</v>
       </c>
       <c r="D154">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E154" t="s">
         <v>28</v>
@@ -6755,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -6772,7 +6772,7 @@
         <v>27</v>
       </c>
       <c r="D156">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E156" t="s">
         <v>28</v>
@@ -6789,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="D157">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E157" t="s">
         <v>28</v>
@@ -6806,7 +6806,7 @@
         <v>27</v>
       </c>
       <c r="D158">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E158" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="D159">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E159" t="s">
         <v>28</v>
@@ -6840,7 +6840,7 @@
         <v>27</v>
       </c>
       <c r="D160">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E160" t="s">
         <v>28</v>
@@ -6857,7 +6857,7 @@
         <v>27</v>
       </c>
       <c r="D161">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
@@ -6891,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="D163">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E163" t="s">
         <v>28</v>
@@ -6908,7 +6908,7 @@
         <v>27</v>
       </c>
       <c r="D164">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E164" t="s">
         <v>28</v>
@@ -6925,7 +6925,7 @@
         <v>27</v>
       </c>
       <c r="D165">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E165" t="s">
         <v>28</v>
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="D167">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E167" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="D168">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E168" t="s">
         <v>28</v>
@@ -6993,7 +6993,7 @@
         <v>27</v>
       </c>
       <c r="D169">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E169" t="s">
         <v>28</v>
@@ -7010,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="D170">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E170" t="s">
         <v>28</v>
@@ -7027,7 +7027,7 @@
         <v>27</v>
       </c>
       <c r="D171">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E171" t="s">
         <v>28</v>
@@ -7044,7 +7044,7 @@
         <v>27</v>
       </c>
       <c r="D172">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E172" t="s">
         <v>28</v>
@@ -7061,7 +7061,7 @@
         <v>27</v>
       </c>
       <c r="D173">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E173" t="s">
         <v>28</v>
@@ -7078,7 +7078,7 @@
         <v>27</v>
       </c>
       <c r="D174">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E174" t="s">
         <v>28</v>
@@ -7095,7 +7095,7 @@
         <v>27</v>
       </c>
       <c r="D175">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E175" t="s">
         <v>28</v>
@@ -7112,7 +7112,7 @@
         <v>27</v>
       </c>
       <c r="D176">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E176" t="s">
         <v>28</v>
@@ -7129,7 +7129,7 @@
         <v>27</v>
       </c>
       <c r="D177">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E177" t="s">
         <v>28</v>
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="D178">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E178" t="s">
         <v>28</v>
@@ -7163,7 +7163,7 @@
         <v>27</v>
       </c>
       <c r="D179">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E179" t="s">
         <v>28</v>
@@ -7180,7 +7180,7 @@
         <v>27</v>
       </c>
       <c r="D180">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -7197,7 +7197,7 @@
         <v>27</v>
       </c>
       <c r="D181">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E181" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="D182">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E182" t="s">
         <v>28</v>
@@ -7231,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="D183">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
@@ -7248,7 +7248,7 @@
         <v>27</v>
       </c>
       <c r="D184">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E184" t="s">
         <v>28</v>
@@ -7265,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="D185">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E185" t="s">
         <v>28</v>
@@ -7282,7 +7282,7 @@
         <v>27</v>
       </c>
       <c r="D186">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E186" t="s">
         <v>28</v>
@@ -7299,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="D187">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E187" t="s">
         <v>28</v>
@@ -7316,7 +7316,7 @@
         <v>27</v>
       </c>
       <c r="D188">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -7333,7 +7333,7 @@
         <v>27</v>
       </c>
       <c r="D189">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E189" t="s">
         <v>28</v>
@@ -7350,7 +7350,7 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E190" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="D191">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
@@ -7384,7 +7384,7 @@
         <v>27</v>
       </c>
       <c r="D192">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E192" t="s">
         <v>28</v>
@@ -7401,7 +7401,7 @@
         <v>27</v>
       </c>
       <c r="D193">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E193" t="s">
         <v>28</v>
@@ -7418,7 +7418,7 @@
         <v>27</v>
       </c>
       <c r="D194">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E194" t="s">
         <v>28</v>
@@ -7435,7 +7435,7 @@
         <v>27</v>
       </c>
       <c r="D195">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E195" t="s">
         <v>28</v>
@@ -7452,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="D196">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E196" t="s">
         <v>28</v>
@@ -7469,7 +7469,7 @@
         <v>27</v>
       </c>
       <c r="D197">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E197" t="s">
         <v>28</v>
@@ -7486,7 +7486,7 @@
         <v>27</v>
       </c>
       <c r="D198">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E198" t="s">
         <v>28</v>
@@ -7503,7 +7503,7 @@
         <v>27</v>
       </c>
       <c r="D199">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E199" t="s">
         <v>28</v>
@@ -7520,7 +7520,7 @@
         <v>27</v>
       </c>
       <c r="D200">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E200" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>27</v>
       </c>
       <c r="D201">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E201" t="s">
         <v>28</v>
@@ -7554,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="D202">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E202" t="s">
         <v>28</v>
@@ -7571,7 +7571,7 @@
         <v>27</v>
       </c>
       <c r="D203">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
@@ -7588,7 +7588,7 @@
         <v>27</v>
       </c>
       <c r="D204">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E204" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="D205">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -7622,7 +7622,7 @@
         <v>27</v>
       </c>
       <c r="D206">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E206" t="s">
         <v>28</v>
@@ -7639,7 +7639,7 @@
         <v>27</v>
       </c>
       <c r="D207">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E207" t="s">
         <v>28</v>
@@ -7656,7 +7656,7 @@
         <v>27</v>
       </c>
       <c r="D208">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E208" t="s">
         <v>28</v>
@@ -7673,7 +7673,7 @@
         <v>27</v>
       </c>
       <c r="D209">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E209" t="s">
         <v>28</v>
@@ -7690,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="D210">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E210" t="s">
         <v>28</v>
@@ -7707,7 +7707,7 @@
         <v>27</v>
       </c>
       <c r="D211">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E211" t="s">
         <v>28</v>
@@ -7724,7 +7724,7 @@
         <v>27</v>
       </c>
       <c r="D212">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E212" t="s">
         <v>28</v>
@@ -7741,7 +7741,7 @@
         <v>27</v>
       </c>
       <c r="D213">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E213" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="D214">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E214" t="s">
         <v>28</v>
@@ -7775,7 +7775,7 @@
         <v>27</v>
       </c>
       <c r="D215">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E215" t="s">
         <v>28</v>
@@ -7792,7 +7792,7 @@
         <v>27</v>
       </c>
       <c r="D216">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E216" t="s">
         <v>28</v>
@@ -7809,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="D217">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E217" t="s">
         <v>28</v>
@@ -7826,7 +7826,7 @@
         <v>27</v>
       </c>
       <c r="D218">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E218" t="s">
         <v>28</v>
@@ -7843,7 +7843,7 @@
         <v>27</v>
       </c>
       <c r="D219">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E219" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="D220">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E220" t="s">
         <v>28</v>
@@ -7877,7 +7877,7 @@
         <v>27</v>
       </c>
       <c r="D221">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E221" t="s">
         <v>28</v>
@@ -7894,7 +7894,7 @@
         <v>27</v>
       </c>
       <c r="D222">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E222" t="s">
         <v>28</v>
@@ -7911,7 +7911,7 @@
         <v>27</v>
       </c>
       <c r="D223">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E223" t="s">
         <v>28</v>
@@ -7928,7 +7928,7 @@
         <v>27</v>
       </c>
       <c r="D224">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E224" t="s">
         <v>28</v>
@@ -7945,7 +7945,7 @@
         <v>27</v>
       </c>
       <c r="D225">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E225" t="s">
         <v>28</v>
@@ -7962,7 +7962,7 @@
         <v>27</v>
       </c>
       <c r="D226">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E226" t="s">
         <v>28</v>
@@ -7979,7 +7979,7 @@
         <v>27</v>
       </c>
       <c r="D227">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E227" t="s">
         <v>28</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="D228">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E228" t="s">
         <v>28</v>
@@ -8013,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="D229">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E229" t="s">
         <v>28</v>
@@ -8030,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="D230">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E230" t="s">
         <v>28</v>
@@ -8047,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="D231">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E231" t="s">
         <v>28</v>
@@ -8064,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="D232">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E232" t="s">
         <v>28</v>
@@ -8081,7 +8081,7 @@
         <v>27</v>
       </c>
       <c r="D233">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E233" t="s">
         <v>28</v>
@@ -8098,7 +8098,7 @@
         <v>27</v>
       </c>
       <c r="D234">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E234" t="s">
         <v>28</v>
@@ -8115,7 +8115,7 @@
         <v>27</v>
       </c>
       <c r="D235">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E235" t="s">
         <v>28</v>
@@ -8132,7 +8132,7 @@
         <v>27</v>
       </c>
       <c r="D236">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E236" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="D237">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E237" t="s">
         <v>28</v>
@@ -8166,7 +8166,7 @@
         <v>27</v>
       </c>
       <c r="D238">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E238" t="s">
         <v>28</v>
@@ -8183,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="D239">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E239" t="s">
         <v>28</v>
@@ -8200,7 +8200,7 @@
         <v>27</v>
       </c>
       <c r="D240">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E240" t="s">
         <v>28</v>
@@ -8217,7 +8217,7 @@
         <v>27</v>
       </c>
       <c r="D241">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E241" t="s">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>27</v>
       </c>
       <c r="D242">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E242" t="s">
         <v>28</v>
@@ -8251,7 +8251,7 @@
         <v>27</v>
       </c>
       <c r="D243">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E243" t="s">
         <v>28</v>
@@ -8268,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="D244">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E244" t="s">
         <v>28</v>
@@ -8285,7 +8285,7 @@
         <v>27</v>
       </c>
       <c r="D245">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E245" t="s">
         <v>28</v>
@@ -8302,7 +8302,7 @@
         <v>27</v>
       </c>
       <c r="D246">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E246" t="s">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="D247">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E247" t="s">
         <v>28</v>
@@ -8336,7 +8336,7 @@
         <v>27</v>
       </c>
       <c r="D248">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E248" t="s">
         <v>28</v>
@@ -8353,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="D249">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E249" t="s">
         <v>28</v>
@@ -8370,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="D250">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E250" t="s">
         <v>28</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="D251">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E251" t="s">
         <v>28</v>
@@ -8404,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="D252">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E252" t="s">
         <v>28</v>
@@ -8421,7 +8421,7 @@
         <v>27</v>
       </c>
       <c r="D253">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E253" t="s">
         <v>28</v>
@@ -8438,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D254">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E254" t="s">
         <v>28</v>
@@ -8455,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="D255">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E255" t="s">
         <v>28</v>
@@ -8472,7 +8472,7 @@
         <v>27</v>
       </c>
       <c r="D256">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E256" t="s">
         <v>28</v>
@@ -8489,7 +8489,7 @@
         <v>27</v>
       </c>
       <c r="D257">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E257" t="s">
         <v>28</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="D258">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E258" t="s">
         <v>28</v>
@@ -8523,7 +8523,7 @@
         <v>27</v>
       </c>
       <c r="D259">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E259" t="s">
         <v>28</v>
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="D261">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E261" t="s">
         <v>28</v>
@@ -8574,7 +8574,7 @@
         <v>27</v>
       </c>
       <c r="D262">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E262" t="s">
         <v>28</v>
@@ -8591,7 +8591,7 @@
         <v>27</v>
       </c>
       <c r="D263">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E263" t="s">
         <v>28</v>
@@ -8608,7 +8608,7 @@
         <v>27</v>
       </c>
       <c r="D264">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E264" t="s">
         <v>28</v>
@@ -8625,7 +8625,7 @@
         <v>27</v>
       </c>
       <c r="D265">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E265" t="s">
         <v>28</v>
@@ -8642,7 +8642,7 @@
         <v>27</v>
       </c>
       <c r="D266">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E266" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="D267">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E267" t="s">
         <v>28</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="D268">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E268" t="s">
         <v>28</v>
@@ -8693,7 +8693,7 @@
         <v>27</v>
       </c>
       <c r="D269">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E269" t="s">
         <v>28</v>
@@ -8710,7 +8710,7 @@
         <v>27</v>
       </c>
       <c r="D270">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E270" t="s">
         <v>28</v>
@@ -8727,7 +8727,7 @@
         <v>27</v>
       </c>
       <c r="D271">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E271" t="s">
         <v>28</v>
@@ -8744,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="D272">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E272" t="s">
         <v>28</v>
@@ -8761,7 +8761,7 @@
         <v>27</v>
       </c>
       <c r="D273">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E273" t="s">
         <v>28</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="D274">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E274" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>27</v>
       </c>
       <c r="D275">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E275" t="s">
         <v>28</v>
@@ -8812,7 +8812,7 @@
         <v>27</v>
       </c>
       <c r="D276">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E276" t="s">
         <v>28</v>
@@ -8829,7 +8829,7 @@
         <v>27</v>
       </c>
       <c r="D277">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E277" t="s">
         <v>28</v>
@@ -8846,7 +8846,7 @@
         <v>27</v>
       </c>
       <c r="D278">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E278" t="s">
         <v>28</v>
@@ -8863,7 +8863,7 @@
         <v>27</v>
       </c>
       <c r="D279">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E279" t="s">
         <v>28</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E280" t="s">
         <v>28</v>
@@ -8897,7 +8897,7 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E281" t="s">
         <v>28</v>
@@ -8914,7 +8914,7 @@
         <v>27</v>
       </c>
       <c r="D282">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E282" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="D283">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E283" t="s">
         <v>28</v>
@@ -8948,7 +8948,7 @@
         <v>27</v>
       </c>
       <c r="D284">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E284" t="s">
         <v>28</v>
@@ -8965,7 +8965,7 @@
         <v>27</v>
       </c>
       <c r="D285">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E285" t="s">
         <v>28</v>
@@ -8982,7 +8982,7 @@
         <v>27</v>
       </c>
       <c r="D286">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E286" t="s">
         <v>28</v>
@@ -8999,7 +8999,7 @@
         <v>27</v>
       </c>
       <c r="D287">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E287" t="s">
         <v>28</v>
@@ -9016,7 +9016,7 @@
         <v>27</v>
       </c>
       <c r="D288">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E288" t="s">
         <v>28</v>
@@ -9033,7 +9033,7 @@
         <v>27</v>
       </c>
       <c r="D289">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E289" t="s">
         <v>28</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="D290">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E290" t="s">
         <v>28</v>
@@ -9067,7 +9067,7 @@
         <v>27</v>
       </c>
       <c r="D291">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E291" t="s">
         <v>28</v>
@@ -9084,7 +9084,7 @@
         <v>27</v>
       </c>
       <c r="D292">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E292" t="s">
         <v>28</v>
@@ -9101,7 +9101,7 @@
         <v>27</v>
       </c>
       <c r="D293">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E293" t="s">
         <v>28</v>
@@ -9118,7 +9118,7 @@
         <v>27</v>
       </c>
       <c r="D294">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E294" t="s">
         <v>28</v>
@@ -9135,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="D295">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E295" t="s">
         <v>28</v>
@@ -9152,7 +9152,7 @@
         <v>27</v>
       </c>
       <c r="D296">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E296" t="s">
         <v>28</v>
@@ -9169,7 +9169,7 @@
         <v>27</v>
       </c>
       <c r="D297">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E297" t="s">
         <v>28</v>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="D298">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E298" t="s">
         <v>28</v>
@@ -9203,7 +9203,7 @@
         <v>27</v>
       </c>
       <c r="D299">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E299" t="s">
         <v>28</v>
@@ -9220,7 +9220,7 @@
         <v>27</v>
       </c>
       <c r="D300">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E300" t="s">
         <v>28</v>
@@ -9237,7 +9237,7 @@
         <v>27</v>
       </c>
       <c r="D301">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E301" t="s">
         <v>28</v>
@@ -9254,7 +9254,7 @@
         <v>27</v>
       </c>
       <c r="D302">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E302" t="s">
         <v>28</v>
@@ -9271,7 +9271,7 @@
         <v>27</v>
       </c>
       <c r="D303">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E303" t="s">
         <v>28</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="D304">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E304" t="s">
         <v>28</v>
@@ -9305,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="D305">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E305" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="D306">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E306" t="s">
         <v>28</v>
@@ -9339,7 +9339,7 @@
         <v>27</v>
       </c>
       <c r="D307">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E307" t="s">
         <v>28</v>
@@ -9373,7 +9373,7 @@
         <v>27</v>
       </c>
       <c r="D309">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E309" t="s">
         <v>28</v>
@@ -9390,7 +9390,7 @@
         <v>27</v>
       </c>
       <c r="D310">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E310" t="s">
         <v>28</v>
@@ -9407,7 +9407,7 @@
         <v>27</v>
       </c>
       <c r="D311">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E311" t="s">
         <v>28</v>
@@ -9424,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="D312">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E312" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="D313">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E313" t="s">
         <v>28</v>
@@ -9458,7 +9458,7 @@
         <v>27</v>
       </c>
       <c r="D314">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E314" t="s">
         <v>28</v>
@@ -9492,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="D316">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E316" t="s">
         <v>28</v>
@@ -9509,7 +9509,7 @@
         <v>27</v>
       </c>
       <c r="D317">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E317" t="s">
         <v>28</v>
@@ -9526,7 +9526,7 @@
         <v>27</v>
       </c>
       <c r="D318">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E318" t="s">
         <v>28</v>
@@ -9543,7 +9543,7 @@
         <v>27</v>
       </c>
       <c r="D319">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E319" t="s">
         <v>28</v>
@@ -9560,7 +9560,7 @@
         <v>27</v>
       </c>
       <c r="D320">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E320" t="s">
         <v>28</v>
@@ -9577,7 +9577,7 @@
         <v>27</v>
       </c>
       <c r="D321">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E321" t="s">
         <v>28</v>
@@ -9594,7 +9594,7 @@
         <v>27</v>
       </c>
       <c r="D322">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E322" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
         <v>27</v>
       </c>
       <c r="D323">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E323" t="s">
         <v>28</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="D324">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E324" t="s">
         <v>28</v>
@@ -9645,7 +9645,7 @@
         <v>27</v>
       </c>
       <c r="D325">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E325" t="s">
         <v>28</v>
@@ -9662,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="D326">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E326" t="s">
         <v>28</v>
@@ -9679,7 +9679,7 @@
         <v>27</v>
       </c>
       <c r="D327">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E327" t="s">
         <v>28</v>
@@ -9696,7 +9696,7 @@
         <v>27</v>
       </c>
       <c r="D328">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E328" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="D329">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E329" t="s">
         <v>28</v>
@@ -9730,7 +9730,7 @@
         <v>27</v>
       </c>
       <c r="D330">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E330" t="s">
         <v>28</v>
@@ -9747,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="D331">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E331" t="s">
         <v>28</v>
@@ -9764,7 +9764,7 @@
         <v>27</v>
       </c>
       <c r="D332">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E332" t="s">
         <v>28</v>
@@ -9781,7 +9781,7 @@
         <v>27</v>
       </c>
       <c r="D333">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E333" t="s">
         <v>28</v>
@@ -9798,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="D334">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E334" t="s">
         <v>28</v>
@@ -9815,7 +9815,7 @@
         <v>27</v>
       </c>
       <c r="D335">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E335" t="s">
         <v>28</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="D336">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E336" t="s">
         <v>28</v>
@@ -9849,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="D337">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E337" t="s">
         <v>28</v>
@@ -9866,7 +9866,7 @@
         <v>27</v>
       </c>
       <c r="D338">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E338" t="s">
         <v>28</v>
@@ -9883,7 +9883,7 @@
         <v>27</v>
       </c>
       <c r="D339">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E339" t="s">
         <v>28</v>
@@ -9900,7 +9900,7 @@
         <v>27</v>
       </c>
       <c r="D340">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E340" t="s">
         <v>28</v>
@@ -9917,7 +9917,7 @@
         <v>27</v>
       </c>
       <c r="D341">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E341" t="s">
         <v>28</v>
@@ -9934,7 +9934,7 @@
         <v>27</v>
       </c>
       <c r="D342">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E342" t="s">
         <v>28</v>
@@ -9951,7 +9951,7 @@
         <v>27</v>
       </c>
       <c r="D343">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E343" t="s">
         <v>28</v>
@@ -9968,7 +9968,7 @@
         <v>27</v>
       </c>
       <c r="D344">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E344" t="s">
         <v>28</v>
@@ -9985,7 +9985,7 @@
         <v>27</v>
       </c>
       <c r="D345">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E345" t="s">
         <v>28</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D346">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E346" t="s">
         <v>28</v>
@@ -10019,7 +10019,7 @@
         <v>27</v>
       </c>
       <c r="D347">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E347" t="s">
         <v>28</v>
@@ -10036,7 +10036,7 @@
         <v>27</v>
       </c>
       <c r="D348">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E348" t="s">
         <v>28</v>
@@ -10053,7 +10053,7 @@
         <v>27</v>
       </c>
       <c r="D349">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E349" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="D350">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E350" t="s">
         <v>28</v>
@@ -10087,7 +10087,7 @@
         <v>27</v>
       </c>
       <c r="D351">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E351" t="s">
         <v>28</v>
@@ -10104,7 +10104,7 @@
         <v>27</v>
       </c>
       <c r="D352">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E352" t="s">
         <v>28</v>
@@ -10121,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D353">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E353" t="s">
         <v>28</v>
@@ -10138,7 +10138,7 @@
         <v>27</v>
       </c>
       <c r="D354">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E354" t="s">
         <v>28</v>
@@ -10155,7 +10155,7 @@
         <v>27</v>
       </c>
       <c r="D355">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E355" t="s">
         <v>28</v>
@@ -10172,7 +10172,7 @@
         <v>27</v>
       </c>
       <c r="D356">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E356" t="s">
         <v>28</v>
@@ -10189,7 +10189,7 @@
         <v>27</v>
       </c>
       <c r="D357">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E357" t="s">
         <v>28</v>
@@ -10206,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="D358">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E358" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="D359">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E359" t="s">
         <v>28</v>
@@ -10240,7 +10240,7 @@
         <v>27</v>
       </c>
       <c r="D360">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E360" t="s">
         <v>28</v>
@@ -10257,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="D361">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E361" t="s">
         <v>28</v>
@@ -10274,7 +10274,7 @@
         <v>27</v>
       </c>
       <c r="D362">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E362" t="s">
         <v>28</v>
@@ -10291,7 +10291,7 @@
         <v>27</v>
       </c>
       <c r="D363">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E363" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="D364">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E364" t="s">
         <v>28</v>
@@ -10325,7 +10325,7 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E365" t="s">
         <v>28</v>
@@ -10342,7 +10342,7 @@
         <v>27</v>
       </c>
       <c r="D366">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E366" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
         <v>27</v>
       </c>
       <c r="D367">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E367" t="s">
         <v>28</v>
@@ -10376,7 +10376,7 @@
         <v>27</v>
       </c>
       <c r="D368">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E368" t="s">
         <v>28</v>
@@ -10410,7 +10410,7 @@
         <v>27</v>
       </c>
       <c r="D370">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E370" t="s">
         <v>28</v>
@@ -10427,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="D371">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E371" t="s">
         <v>28</v>
@@ -10444,7 +10444,7 @@
         <v>27</v>
       </c>
       <c r="D372">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E372" t="s">
         <v>28</v>
@@ -10478,7 +10478,7 @@
         <v>27</v>
       </c>
       <c r="D374">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E374" t="s">
         <v>28</v>
@@ -10495,7 +10495,7 @@
         <v>27</v>
       </c>
       <c r="D375">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E375" t="s">
         <v>28</v>
@@ -10512,7 +10512,7 @@
         <v>27</v>
       </c>
       <c r="D376">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E376" t="s">
         <v>28</v>
@@ -10529,7 +10529,7 @@
         <v>27</v>
       </c>
       <c r="D377">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E377" t="s">
         <v>28</v>
@@ -10546,7 +10546,7 @@
         <v>27</v>
       </c>
       <c r="D378">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E378" t="s">
         <v>28</v>
@@ -10563,7 +10563,7 @@
         <v>27</v>
       </c>
       <c r="D379">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E379" t="s">
         <v>28</v>
@@ -10580,7 +10580,7 @@
         <v>27</v>
       </c>
       <c r="D380">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E380" t="s">
         <v>28</v>
@@ -10597,7 +10597,7 @@
         <v>27</v>
       </c>
       <c r="D381">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E381" t="s">
         <v>28</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="D382">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E382" t="s">
         <v>28</v>
@@ -10631,7 +10631,7 @@
         <v>27</v>
       </c>
       <c r="D383">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E383" t="s">
         <v>28</v>
@@ -10665,7 +10665,7 @@
         <v>27</v>
       </c>
       <c r="D385">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E385" t="s">
         <v>28</v>
@@ -10682,7 +10682,7 @@
         <v>27</v>
       </c>
       <c r="D386">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E386" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="D387">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E387" t="s">
         <v>28</v>
@@ -10716,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="D388">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E388" t="s">
         <v>28</v>
@@ -10733,7 +10733,7 @@
         <v>27</v>
       </c>
       <c r="D389">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E389" t="s">
         <v>28</v>
@@ -10750,7 +10750,7 @@
         <v>27</v>
       </c>
       <c r="D390">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E390" t="s">
         <v>28</v>
@@ -10784,7 +10784,7 @@
         <v>27</v>
       </c>
       <c r="D392">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E392" t="s">
         <v>28</v>
@@ -10801,7 +10801,7 @@
         <v>27</v>
       </c>
       <c r="D393">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E393" t="s">
         <v>28</v>
@@ -10818,7 +10818,7 @@
         <v>27</v>
       </c>
       <c r="D394">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E394" t="s">
         <v>28</v>
@@ -10835,7 +10835,7 @@
         <v>27</v>
       </c>
       <c r="D395">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E395" t="s">
         <v>28</v>
@@ -10852,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="D396">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E396" t="s">
         <v>28</v>
@@ -10869,7 +10869,7 @@
         <v>27</v>
       </c>
       <c r="D397">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E397" t="s">
         <v>28</v>
@@ -10886,7 +10886,7 @@
         <v>27</v>
       </c>
       <c r="D398">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E398" t="s">
         <v>28</v>
@@ -10903,7 +10903,7 @@
         <v>27</v>
       </c>
       <c r="D399">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E399" t="s">
         <v>28</v>
@@ -10920,7 +10920,7 @@
         <v>27</v>
       </c>
       <c r="D400">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E400" t="s">
         <v>28</v>
@@ -10937,7 +10937,7 @@
         <v>27</v>
       </c>
       <c r="D401">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E401" t="s">
         <v>28</v>
@@ -10954,7 +10954,7 @@
         <v>27</v>
       </c>
       <c r="D402">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E402" t="s">
         <v>28</v>
@@ -10971,7 +10971,7 @@
         <v>27</v>
       </c>
       <c r="D403">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E403" t="s">
         <v>28</v>
@@ -10988,7 +10988,7 @@
         <v>27</v>
       </c>
       <c r="D404">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E404" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="D405">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E405" t="s">
         <v>28</v>
@@ -11022,7 +11022,7 @@
         <v>27</v>
       </c>
       <c r="D406">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E406" t="s">
         <v>28</v>
@@ -11039,7 +11039,7 @@
         <v>27</v>
       </c>
       <c r="D407">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E407" t="s">
         <v>28</v>
@@ -11056,7 +11056,7 @@
         <v>27</v>
       </c>
       <c r="D408">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E408" t="s">
         <v>28</v>
@@ -11073,7 +11073,7 @@
         <v>27</v>
       </c>
       <c r="D409">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E409" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="D410">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E410" t="s">
         <v>28</v>
@@ -11107,7 +11107,7 @@
         <v>27</v>
       </c>
       <c r="D411">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E411" t="s">
         <v>28</v>
@@ -11124,7 +11124,7 @@
         <v>27</v>
       </c>
       <c r="D412">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E412" t="s">
         <v>28</v>
@@ -11158,7 +11158,7 @@
         <v>27</v>
       </c>
       <c r="D414">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E414" t="s">
         <v>28</v>
@@ -11175,7 +11175,7 @@
         <v>27</v>
       </c>
       <c r="D415">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E415" t="s">
         <v>28</v>
@@ -11192,7 +11192,7 @@
         <v>27</v>
       </c>
       <c r="D416">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E416" t="s">
         <v>28</v>
@@ -11209,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="D417">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E417" t="s">
         <v>28</v>
@@ -11226,7 +11226,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E418" t="s">
         <v>28</v>
@@ -11243,7 +11243,7 @@
         <v>27</v>
       </c>
       <c r="D419">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E419" t="s">
         <v>28</v>
@@ -11260,7 +11260,7 @@
         <v>27</v>
       </c>
       <c r="D420">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E420" t="s">
         <v>28</v>
@@ -11277,7 +11277,7 @@
         <v>27</v>
       </c>
       <c r="D421">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E421" t="s">
         <v>28</v>
@@ -11294,7 +11294,7 @@
         <v>27</v>
       </c>
       <c r="D422">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E422" t="s">
         <v>28</v>
@@ -11311,7 +11311,7 @@
         <v>27</v>
       </c>
       <c r="D423">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E423" t="s">
         <v>28</v>
@@ -11328,7 +11328,7 @@
         <v>27</v>
       </c>
       <c r="D424">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E424" t="s">
         <v>28</v>
@@ -11345,7 +11345,7 @@
         <v>27</v>
       </c>
       <c r="D425">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E425" t="s">
         <v>28</v>
@@ -11362,7 +11362,7 @@
         <v>27</v>
       </c>
       <c r="D426">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E426" t="s">
         <v>28</v>
@@ -11379,7 +11379,7 @@
         <v>27</v>
       </c>
       <c r="D427">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E427" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="D428">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E428" t="s">
         <v>28</v>
@@ -11413,7 +11413,7 @@
         <v>27</v>
       </c>
       <c r="D429">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E429" t="s">
         <v>28</v>
@@ -11430,7 +11430,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E430" t="s">
         <v>28</v>
@@ -11464,7 +11464,7 @@
         <v>27</v>
       </c>
       <c r="D432">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E432" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="D433">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E433" t="s">
         <v>28</v>
@@ -11498,7 +11498,7 @@
         <v>27</v>
       </c>
       <c r="D434">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E434" t="s">
         <v>28</v>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="D435">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E435" t="s">
         <v>28</v>
@@ -11532,7 +11532,7 @@
         <v>27</v>
       </c>
       <c r="D436">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E436" t="s">
         <v>28</v>
@@ -11549,7 +11549,7 @@
         <v>27</v>
       </c>
       <c r="D437">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E437" t="s">
         <v>28</v>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
       <c r="D438">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E438" t="s">
         <v>28</v>
@@ -11583,7 +11583,7 @@
         <v>27</v>
       </c>
       <c r="D439">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E439" t="s">
         <v>28</v>
@@ -11600,7 +11600,7 @@
         <v>27</v>
       </c>
       <c r="D440">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E440" t="s">
         <v>28</v>
@@ -11617,7 +11617,7 @@
         <v>27</v>
       </c>
       <c r="D441">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E441" t="s">
         <v>28</v>
@@ -11634,7 +11634,7 @@
         <v>27</v>
       </c>
       <c r="D442">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E442" t="s">
         <v>28</v>
@@ -11651,7 +11651,7 @@
         <v>27</v>
       </c>
       <c r="D443">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E443" t="s">
         <v>28</v>
@@ -11668,7 +11668,7 @@
         <v>27</v>
       </c>
       <c r="D444">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E444" t="s">
         <v>28</v>
@@ -11685,7 +11685,7 @@
         <v>27</v>
       </c>
       <c r="D445">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E445" t="s">
         <v>28</v>
@@ -11702,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D446">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E446" t="s">
         <v>28</v>
@@ -11719,7 +11719,7 @@
         <v>27</v>
       </c>
       <c r="D447">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E447" t="s">
         <v>28</v>
@@ -11736,7 +11736,7 @@
         <v>27</v>
       </c>
       <c r="D448">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E448" t="s">
         <v>28</v>
@@ -11753,7 +11753,7 @@
         <v>27</v>
       </c>
       <c r="D449">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E449" t="s">
         <v>28</v>
@@ -11770,7 +11770,7 @@
         <v>27</v>
       </c>
       <c r="D450">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E450" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="D451">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E451" t="s">
         <v>28</v>
@@ -11804,7 +11804,7 @@
         <v>27</v>
       </c>
       <c r="D452">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E452" t="s">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>27</v>
       </c>
       <c r="D453">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E453" t="s">
         <v>28</v>
@@ -11838,7 +11838,7 @@
         <v>27</v>
       </c>
       <c r="D454">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E454" t="s">
         <v>28</v>
@@ -11855,7 +11855,7 @@
         <v>27</v>
       </c>
       <c r="D455">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E455" t="s">
         <v>28</v>
@@ -11889,7 +11889,7 @@
         <v>27</v>
       </c>
       <c r="D457">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E457" t="s">
         <v>28</v>
@@ -11906,7 +11906,7 @@
         <v>27</v>
       </c>
       <c r="D458">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E458" t="s">
         <v>28</v>
@@ -11923,7 +11923,7 @@
         <v>27</v>
       </c>
       <c r="D459">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E459" t="s">
         <v>28</v>
@@ -11940,7 +11940,7 @@
         <v>27</v>
       </c>
       <c r="D460">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E460" t="s">
         <v>28</v>
@@ -11957,7 +11957,7 @@
         <v>27</v>
       </c>
       <c r="D461">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E461" t="s">
         <v>28</v>
@@ -11974,7 +11974,7 @@
         <v>27</v>
       </c>
       <c r="D462">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E462" t="s">
         <v>28</v>
@@ -11991,7 +11991,7 @@
         <v>27</v>
       </c>
       <c r="D463">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E463" t="s">
         <v>28</v>
@@ -12008,7 +12008,7 @@
         <v>27</v>
       </c>
       <c r="D464">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E464" t="s">
         <v>28</v>
@@ -12025,7 +12025,7 @@
         <v>27</v>
       </c>
       <c r="D465">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E465" t="s">
         <v>28</v>
@@ -12042,7 +12042,7 @@
         <v>27</v>
       </c>
       <c r="D466">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E466" t="s">
         <v>28</v>
@@ -12059,7 +12059,7 @@
         <v>27</v>
       </c>
       <c r="D467">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E467" t="s">
         <v>28</v>
@@ -12076,7 +12076,7 @@
         <v>27</v>
       </c>
       <c r="D468">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E468" t="s">
         <v>28</v>
@@ -12093,7 +12093,7 @@
         <v>27</v>
       </c>
       <c r="D469">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E469" t="s">
         <v>28</v>
@@ -12110,7 +12110,7 @@
         <v>27</v>
       </c>
       <c r="D470">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E470" t="s">
         <v>28</v>
@@ -12127,7 +12127,7 @@
         <v>27</v>
       </c>
       <c r="D471">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E471" t="s">
         <v>28</v>
@@ -12144,7 +12144,7 @@
         <v>27</v>
       </c>
       <c r="D472">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E472" t="s">
         <v>28</v>
@@ -12161,7 +12161,7 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E473" t="s">
         <v>28</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="D474">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E474" t="s">
         <v>28</v>
@@ -12195,7 +12195,7 @@
         <v>27</v>
       </c>
       <c r="D475">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E475" t="s">
         <v>28</v>
@@ -12212,7 +12212,7 @@
         <v>27</v>
       </c>
       <c r="D476">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E476" t="s">
         <v>28</v>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
       <c r="D477">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E477" t="s">
         <v>28</v>
@@ -12246,7 +12246,7 @@
         <v>27</v>
       </c>
       <c r="D478">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E478" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="D479">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E479" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="D480">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E480" t="s">
         <v>28</v>
@@ -12297,7 +12297,7 @@
         <v>27</v>
       </c>
       <c r="D481">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E481" t="s">
         <v>28</v>
@@ -12314,7 +12314,7 @@
         <v>27</v>
       </c>
       <c r="D482">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E482" t="s">
         <v>28</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="D483">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E483" t="s">
         <v>28</v>
@@ -12348,7 +12348,7 @@
         <v>27</v>
       </c>
       <c r="D484">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E484" t="s">
         <v>28</v>
@@ -12365,7 +12365,7 @@
         <v>27</v>
       </c>
       <c r="D485">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E485" t="s">
         <v>28</v>
@@ -12382,7 +12382,7 @@
         <v>27</v>
       </c>
       <c r="D486">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E486" t="s">
         <v>28</v>
@@ -12399,7 +12399,7 @@
         <v>27</v>
       </c>
       <c r="D487">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E487" t="s">
         <v>28</v>
@@ -12416,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="D488">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E488" t="s">
         <v>28</v>
@@ -12433,7 +12433,7 @@
         <v>27</v>
       </c>
       <c r="D489">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E489" t="s">
         <v>28</v>
@@ -12450,7 +12450,7 @@
         <v>27</v>
       </c>
       <c r="D490">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E490" t="s">
         <v>28</v>
@@ -12467,7 +12467,7 @@
         <v>27</v>
       </c>
       <c r="D491">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E491" t="s">
         <v>28</v>
@@ -12484,7 +12484,7 @@
         <v>27</v>
       </c>
       <c r="D492">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E492" t="s">
         <v>28</v>
@@ -12501,7 +12501,7 @@
         <v>27</v>
       </c>
       <c r="D493">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E493" t="s">
         <v>28</v>
@@ -12518,7 +12518,7 @@
         <v>27</v>
       </c>
       <c r="D494">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E494" t="s">
         <v>28</v>
@@ -12535,7 +12535,7 @@
         <v>27</v>
       </c>
       <c r="D495">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E495" t="s">
         <v>28</v>
@@ -12552,7 +12552,7 @@
         <v>27</v>
       </c>
       <c r="D496">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E496" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="D497">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E497" t="s">
         <v>28</v>
@@ -12586,7 +12586,7 @@
         <v>27</v>
       </c>
       <c r="D498">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E498" t="s">
         <v>28</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D499">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E499" t="s">
         <v>28</v>
@@ -12620,7 +12620,7 @@
         <v>27</v>
       </c>
       <c r="D500">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E500" t="s">
         <v>28</v>
@@ -12637,7 +12637,7 @@
         <v>27</v>
       </c>
       <c r="D501">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E501" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="D502">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E502" t="s">
         <v>28</v>
@@ -12671,7 +12671,7 @@
         <v>27</v>
       </c>
       <c r="D503">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E503" t="s">
         <v>28</v>
@@ -12688,7 +12688,7 @@
         <v>27</v>
       </c>
       <c r="D504">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E504" t="s">
         <v>28</v>
@@ -12705,7 +12705,7 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E505" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="D506">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E506" t="s">
         <v>28</v>
@@ -12739,7 +12739,7 @@
         <v>27</v>
       </c>
       <c r="D507">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E507" t="s">
         <v>28</v>
@@ -12756,7 +12756,7 @@
         <v>27</v>
       </c>
       <c r="D508">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E508" t="s">
         <v>28</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="D509">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E509" t="s">
         <v>28</v>
@@ -12790,7 +12790,7 @@
         <v>27</v>
       </c>
       <c r="D510">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E510" t="s">
         <v>28</v>
@@ -12824,7 +12824,7 @@
         <v>27</v>
       </c>
       <c r="D512">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E512" t="s">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27</v>
       </c>
       <c r="D513">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E513" t="s">
         <v>28</v>
@@ -12858,7 +12858,7 @@
         <v>27</v>
       </c>
       <c r="D514">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E514" t="s">
         <v>28</v>
@@ -12875,7 +12875,7 @@
         <v>27</v>
       </c>
       <c r="D515">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E515" t="s">
         <v>28</v>
@@ -12892,7 +12892,7 @@
         <v>27</v>
       </c>
       <c r="D516">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E516" t="s">
         <v>28</v>
@@ -12909,7 +12909,7 @@
         <v>27</v>
       </c>
       <c r="D517">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E517" t="s">
         <v>28</v>
@@ -12943,7 +12943,7 @@
         <v>27</v>
       </c>
       <c r="D519">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E519" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="D520">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E520" t="s">
         <v>28</v>
@@ -12977,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="D521">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E521" t="s">
         <v>28</v>
@@ -12994,7 +12994,7 @@
         <v>27</v>
       </c>
       <c r="D522">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E522" t="s">
         <v>28</v>
@@ -13011,7 +13011,7 @@
         <v>27</v>
       </c>
       <c r="D523">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E523" t="s">
         <v>28</v>
@@ -13028,7 +13028,7 @@
         <v>27</v>
       </c>
       <c r="D524">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E524" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="D525">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E525" t="s">
         <v>28</v>
@@ -13062,7 +13062,7 @@
         <v>27</v>
       </c>
       <c r="D526">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E526" t="s">
         <v>28</v>
@@ -13079,7 +13079,7 @@
         <v>27</v>
       </c>
       <c r="D527">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E527" t="s">
         <v>28</v>
@@ -13096,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="D528">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E528" t="s">
         <v>28</v>
@@ -13113,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="D529">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
@@ -13130,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -13147,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="D531">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
@@ -13164,7 +13164,7 @@
         <v>27</v>
       </c>
       <c r="D532">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E532" t="s">
         <v>28</v>
@@ -13181,7 +13181,7 @@
         <v>27</v>
       </c>
       <c r="D533">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E533" t="s">
         <v>28</v>
@@ -13198,7 +13198,7 @@
         <v>27</v>
       </c>
       <c r="D534">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E534" t="s">
         <v>28</v>
@@ -13215,7 +13215,7 @@
         <v>27</v>
       </c>
       <c r="D535">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E535" t="s">
         <v>28</v>
@@ -13232,7 +13232,7 @@
         <v>27</v>
       </c>
       <c r="D536">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E536" t="s">
         <v>28</v>
@@ -13249,7 +13249,7 @@
         <v>27</v>
       </c>
       <c r="D537">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E537" t="s">
         <v>28</v>
@@ -13266,7 +13266,7 @@
         <v>27</v>
       </c>
       <c r="D538">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E538" t="s">
         <v>28</v>
@@ -13283,7 +13283,7 @@
         <v>27</v>
       </c>
       <c r="D539">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E539" t="s">
         <v>28</v>
@@ -13300,7 +13300,7 @@
         <v>27</v>
       </c>
       <c r="D540">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E540" t="s">
         <v>28</v>
@@ -13317,7 +13317,7 @@
         <v>27</v>
       </c>
       <c r="D541">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E541" t="s">
         <v>28</v>
@@ -13334,7 +13334,7 @@
         <v>27</v>
       </c>
       <c r="D542">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E542" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="D543">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E543" t="s">
         <v>28</v>
@@ -13385,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="D545">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
@@ -13402,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="D546">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
@@ -13419,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="D547">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E547" t="s">
         <v>28</v>
@@ -13453,7 +13453,7 @@
         <v>27</v>
       </c>
       <c r="D549">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E549" t="s">
         <v>28</v>
@@ -13470,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="D550">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E550" t="s">
         <v>28</v>
@@ -13487,7 +13487,7 @@
         <v>27</v>
       </c>
       <c r="D551">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E551" t="s">
         <v>28</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="D552">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -13521,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="D553">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E553" t="s">
         <v>28</v>
@@ -13538,7 +13538,7 @@
         <v>27</v>
       </c>
       <c r="D554">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E554" t="s">
         <v>28</v>
@@ -13555,7 +13555,7 @@
         <v>27</v>
       </c>
       <c r="D555">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E555" t="s">
         <v>28</v>
@@ -13572,7 +13572,7 @@
         <v>27</v>
       </c>
       <c r="D556">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E556" t="s">
         <v>28</v>
@@ -13623,7 +13623,7 @@
         <v>27</v>
       </c>
       <c r="D559">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -13640,7 +13640,7 @@
         <v>27</v>
       </c>
       <c r="D560">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
@@ -13657,7 +13657,7 @@
         <v>27</v>
       </c>
       <c r="D561">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E561" t="s">
         <v>28</v>
@@ -13674,7 +13674,7 @@
         <v>27</v>
       </c>
       <c r="D562">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E562" t="s">
         <v>28</v>
@@ -13691,7 +13691,7 @@
         <v>27</v>
       </c>
       <c r="D563">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E563" t="s">
         <v>28</v>
@@ -13708,7 +13708,7 @@
         <v>27</v>
       </c>
       <c r="D564">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E564" t="s">
         <v>28</v>
@@ -13725,7 +13725,7 @@
         <v>27</v>
       </c>
       <c r="D565">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E565" t="s">
         <v>28</v>
@@ -13759,7 +13759,7 @@
         <v>27</v>
       </c>
       <c r="D567">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E567" t="s">
         <v>28</v>
@@ -13776,7 +13776,7 @@
         <v>27</v>
       </c>
       <c r="D568">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E568" t="s">
         <v>28</v>
@@ -13793,7 +13793,7 @@
         <v>27</v>
       </c>
       <c r="D569">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
@@ -13810,7 +13810,7 @@
         <v>27</v>
       </c>
       <c r="D570">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E570" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="D571">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E571" t="s">
         <v>28</v>
@@ -13844,7 +13844,7 @@
         <v>27</v>
       </c>
       <c r="D572">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E572" t="s">
         <v>28</v>
@@ -13861,7 +13861,7 @@
         <v>27</v>
       </c>
       <c r="D573">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E573" t="s">
         <v>28</v>
@@ -13878,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="D574">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E574" t="s">
         <v>28</v>
@@ -13895,7 +13895,7 @@
         <v>27</v>
       </c>
       <c r="D575">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E575" t="s">
         <v>28</v>
@@ -13912,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="D576">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E576" t="s">
         <v>28</v>
@@ -13929,7 +13929,7 @@
         <v>27</v>
       </c>
       <c r="D577">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E577" t="s">
         <v>28</v>
@@ -13946,7 +13946,7 @@
         <v>27</v>
       </c>
       <c r="D578">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E578" t="s">
         <v>28</v>
@@ -13963,7 +13963,7 @@
         <v>27</v>
       </c>
       <c r="D579">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E579" t="s">
         <v>28</v>
@@ -13980,7 +13980,7 @@
         <v>27</v>
       </c>
       <c r="D580">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E580" t="s">
         <v>28</v>
@@ -13997,7 +13997,7 @@
         <v>27</v>
       </c>
       <c r="D581">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E581" t="s">
         <v>28</v>
@@ -14014,7 +14014,7 @@
         <v>27</v>
       </c>
       <c r="D582">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E582" t="s">
         <v>28</v>
@@ -14031,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="D583">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E583" t="s">
         <v>28</v>
@@ -14048,7 +14048,7 @@
         <v>27</v>
       </c>
       <c r="D584">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E584" t="s">
         <v>28</v>
@@ -14065,7 +14065,7 @@
         <v>27</v>
       </c>
       <c r="D585">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E585" t="s">
         <v>28</v>
@@ -14082,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="D586">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E586" t="s">
         <v>28</v>
@@ -14099,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="D587">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E587" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="D589">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
@@ -14150,7 +14150,7 @@
         <v>27</v>
       </c>
       <c r="D590">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
@@ -14167,7 +14167,7 @@
         <v>27</v>
       </c>
       <c r="D591">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E591" t="s">
         <v>28</v>
@@ -14201,7 +14201,7 @@
         <v>27</v>
       </c>
       <c r="D593">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E593" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="D594">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E594" t="s">
         <v>28</v>
@@ -14235,7 +14235,7 @@
         <v>27</v>
       </c>
       <c r="D595">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E595" t="s">
         <v>28</v>
@@ -14252,7 +14252,7 @@
         <v>27</v>
       </c>
       <c r="D596">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
@@ -14269,7 +14269,7 @@
         <v>27</v>
       </c>
       <c r="D597">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
@@ -14286,7 +14286,7 @@
         <v>27</v>
       </c>
       <c r="D598">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
@@ -14303,7 +14303,7 @@
         <v>27</v>
       </c>
       <c r="D599">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="D600">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
@@ -14337,7 +14337,7 @@
         <v>27</v>
       </c>
       <c r="D601">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
@@ -14354,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="D602">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
@@ -14388,7 +14388,7 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
@@ -14405,7 +14405,7 @@
         <v>27</v>
       </c>
       <c r="D605">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E605" t="s">
         <v>28</v>
@@ -14422,7 +14422,7 @@
         <v>27</v>
       </c>
       <c r="D606">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E606" t="s">
         <v>28</v>
@@ -14439,7 +14439,7 @@
         <v>27</v>
       </c>
       <c r="D607">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E607" t="s">
         <v>28</v>
@@ -14456,7 +14456,7 @@
         <v>27</v>
       </c>
       <c r="D608">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
@@ -14473,7 +14473,7 @@
         <v>27</v>
       </c>
       <c r="D609">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E609" t="s">
         <v>28</v>
@@ -14490,7 +14490,7 @@
         <v>27</v>
       </c>
       <c r="D610">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E610" t="s">
         <v>28</v>
@@ -14507,7 +14507,7 @@
         <v>27</v>
       </c>
       <c r="D611">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E611" t="s">
         <v>28</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="D612">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E612" t="s">
         <v>28</v>
@@ -14541,7 +14541,7 @@
         <v>27</v>
       </c>
       <c r="D613">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E613" t="s">
         <v>28</v>
@@ -14558,7 +14558,7 @@
         <v>27</v>
       </c>
       <c r="D614">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E614" t="s">
         <v>28</v>
@@ -14575,7 +14575,7 @@
         <v>27</v>
       </c>
       <c r="D615">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E615" t="s">
         <v>28</v>
@@ -14592,7 +14592,7 @@
         <v>27</v>
       </c>
       <c r="D616">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E616" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="D617">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E617" t="s">
         <v>28</v>
@@ -14626,7 +14626,7 @@
         <v>27</v>
       </c>
       <c r="D618">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E618" t="s">
         <v>28</v>
@@ -14643,7 +14643,7 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E619" t="s">
         <v>28</v>
@@ -14660,7 +14660,7 @@
         <v>27</v>
       </c>
       <c r="D620">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E620" t="s">
         <v>28</v>
@@ -14677,7 +14677,7 @@
         <v>27</v>
       </c>
       <c r="D621">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E621" t="s">
         <v>28</v>
@@ -14694,7 +14694,7 @@
         <v>27</v>
       </c>
       <c r="D622">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E622" t="s">
         <v>28</v>
@@ -14711,7 +14711,7 @@
         <v>27</v>
       </c>
       <c r="D623">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E623" t="s">
         <v>28</v>
@@ -14728,7 +14728,7 @@
         <v>27</v>
       </c>
       <c r="D624">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E624" t="s">
         <v>28</v>
@@ -14745,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="D625">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E625" t="s">
         <v>28</v>
@@ -14762,7 +14762,7 @@
         <v>27</v>
       </c>
       <c r="D626">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E626" t="s">
         <v>28</v>
@@ -14779,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="D627">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E627" t="s">
         <v>28</v>
@@ -14796,7 +14796,7 @@
         <v>27</v>
       </c>
       <c r="D628">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E628" t="s">
         <v>28</v>
@@ -14813,7 +14813,7 @@
         <v>27</v>
       </c>
       <c r="D629">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E629" t="s">
         <v>28</v>
@@ -14830,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="D630">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E630" t="s">
         <v>28</v>
@@ -14847,7 +14847,7 @@
         <v>27</v>
       </c>
       <c r="D631">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E631" t="s">
         <v>28</v>
@@ -14864,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D632">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E632" t="s">
         <v>28</v>
@@ -14881,7 +14881,7 @@
         <v>27</v>
       </c>
       <c r="D633">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E633" t="s">
         <v>28</v>
@@ -14898,7 +14898,7 @@
         <v>27</v>
       </c>
       <c r="D634">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E634" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="D635">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E635" t="s">
         <v>28</v>
@@ -14932,7 +14932,7 @@
         <v>27</v>
       </c>
       <c r="D636">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E636" t="s">
         <v>28</v>
@@ -14949,7 +14949,7 @@
         <v>27</v>
       </c>
       <c r="D637">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E637" t="s">
         <v>28</v>
@@ -14966,7 +14966,7 @@
         <v>27</v>
       </c>
       <c r="D638">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E638" t="s">
         <v>28</v>
@@ -14983,7 +14983,7 @@
         <v>27</v>
       </c>
       <c r="D639">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E639" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E640" t="s">
         <v>28</v>
@@ -15017,7 +15017,7 @@
         <v>27</v>
       </c>
       <c r="D641">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E641" t="s">
         <v>28</v>
@@ -15034,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="D642">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E642" t="s">
         <v>28</v>
@@ -15051,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="D643">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E643" t="s">
         <v>28</v>
@@ -15068,7 +15068,7 @@
         <v>27</v>
       </c>
       <c r="D644">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E644" t="s">
         <v>28</v>
@@ -15085,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="D645">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E645" t="s">
         <v>28</v>
@@ -15102,7 +15102,7 @@
         <v>27</v>
       </c>
       <c r="D646">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E646" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>27</v>
       </c>
       <c r="D647">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E647" t="s">
         <v>28</v>
@@ -15136,7 +15136,7 @@
         <v>27</v>
       </c>
       <c r="D648">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E648" t="s">
         <v>28</v>
@@ -15153,7 +15153,7 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E649" t="s">
         <v>28</v>
@@ -15170,7 +15170,7 @@
         <v>27</v>
       </c>
       <c r="D650">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E650" t="s">
         <v>28</v>
@@ -15187,7 +15187,7 @@
         <v>27</v>
       </c>
       <c r="D651">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E651" t="s">
         <v>28</v>
@@ -15204,7 +15204,7 @@
         <v>27</v>
       </c>
       <c r="D652">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E652" t="s">
         <v>28</v>
@@ -15221,7 +15221,7 @@
         <v>27</v>
       </c>
       <c r="D653">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E653" t="s">
         <v>28</v>
@@ -15238,7 +15238,7 @@
         <v>27</v>
       </c>
       <c r="D654">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E654" t="s">
         <v>28</v>
@@ -15255,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="D655">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E655" t="s">
         <v>28</v>
@@ -15272,7 +15272,7 @@
         <v>27</v>
       </c>
       <c r="D656">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
@@ -15289,7 +15289,7 @@
         <v>27</v>
       </c>
       <c r="D657">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E657" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
@@ -15323,7 +15323,7 @@
         <v>27</v>
       </c>
       <c r="D659">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E659" t="s">
         <v>28</v>
@@ -15340,7 +15340,7 @@
         <v>27</v>
       </c>
       <c r="D660">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E660" t="s">
         <v>28</v>
@@ -15357,7 +15357,7 @@
         <v>27</v>
       </c>
       <c r="D661">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E661" t="s">
         <v>28</v>
@@ -15374,7 +15374,7 @@
         <v>27</v>
       </c>
       <c r="D662">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E662" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="D663">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E663" t="s">
         <v>28</v>
@@ -15408,7 +15408,7 @@
         <v>27</v>
       </c>
       <c r="D664">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E664" t="s">
         <v>28</v>
@@ -15425,7 +15425,7 @@
         <v>27</v>
       </c>
       <c r="D665">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E665" t="s">
         <v>28</v>
@@ -15442,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="D666">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E666" t="s">
         <v>28</v>
@@ -15459,7 +15459,7 @@
         <v>27</v>
       </c>
       <c r="D667">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E667" t="s">
         <v>28</v>
@@ -15476,7 +15476,7 @@
         <v>27</v>
       </c>
       <c r="D668">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E668" t="s">
         <v>28</v>
@@ -15493,7 +15493,7 @@
         <v>27</v>
       </c>
       <c r="D669">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E669" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>27</v>
       </c>
       <c r="D670">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E670" t="s">
         <v>28</v>
@@ -15527,7 +15527,7 @@
         <v>27</v>
       </c>
       <c r="D671">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E671" t="s">
         <v>28</v>
@@ -15544,7 +15544,7 @@
         <v>27</v>
       </c>
       <c r="D672">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E672" t="s">
         <v>28</v>
@@ -15561,7 +15561,7 @@
         <v>27</v>
       </c>
       <c r="D673">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E673" t="s">
         <v>28</v>
@@ -15578,7 +15578,7 @@
         <v>27</v>
       </c>
       <c r="D674">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E674" t="s">
         <v>28</v>
@@ -15595,7 +15595,7 @@
         <v>27</v>
       </c>
       <c r="D675">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E675" t="s">
         <v>28</v>
@@ -15612,7 +15612,7 @@
         <v>27</v>
       </c>
       <c r="D676">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E676" t="s">
         <v>28</v>
@@ -15629,7 +15629,7 @@
         <v>27</v>
       </c>
       <c r="D677">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E677" t="s">
         <v>28</v>
@@ -15646,7 +15646,7 @@
         <v>27</v>
       </c>
       <c r="D678">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E678" t="s">
         <v>28</v>
@@ -15663,7 +15663,7 @@
         <v>27</v>
       </c>
       <c r="D679">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E679" t="s">
         <v>28</v>
@@ -15680,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="D680">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E680" t="s">
         <v>28</v>
@@ -15697,7 +15697,7 @@
         <v>27</v>
       </c>
       <c r="D681">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E681" t="s">
         <v>28</v>
@@ -15714,7 +15714,7 @@
         <v>27</v>
       </c>
       <c r="D682">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E682" t="s">
         <v>28</v>
@@ -15731,7 +15731,7 @@
         <v>27</v>
       </c>
       <c r="D683">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E683" t="s">
         <v>28</v>
@@ -15748,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="D684">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E684" t="s">
         <v>28</v>
@@ -15765,7 +15765,7 @@
         <v>27</v>
       </c>
       <c r="D685">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E685" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="D686">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E686" t="s">
         <v>28</v>
@@ -15799,7 +15799,7 @@
         <v>27</v>
       </c>
       <c r="D687">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E687" t="s">
         <v>28</v>
@@ -15816,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="D688">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E688" t="s">
         <v>28</v>
@@ -15833,7 +15833,7 @@
         <v>27</v>
       </c>
       <c r="D689">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E689" t="s">
         <v>28</v>
@@ -15850,7 +15850,7 @@
         <v>27</v>
       </c>
       <c r="D690">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E690" t="s">
         <v>28</v>
@@ -15867,7 +15867,7 @@
         <v>27</v>
       </c>
       <c r="D691">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E691" t="s">
         <v>28</v>
@@ -15884,7 +15884,7 @@
         <v>27</v>
       </c>
       <c r="D692">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E692" t="s">
         <v>28</v>
@@ -15901,7 +15901,7 @@
         <v>27</v>
       </c>
       <c r="D693">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E693" t="s">
         <v>28</v>
@@ -15918,7 +15918,7 @@
         <v>27</v>
       </c>
       <c r="D694">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E694" t="s">
         <v>28</v>
@@ -15935,7 +15935,7 @@
         <v>27</v>
       </c>
       <c r="D695">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E695" t="s">
         <v>28</v>
@@ -15952,7 +15952,7 @@
         <v>27</v>
       </c>
       <c r="D696">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E696" t="s">
         <v>28</v>
@@ -15969,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="D697">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E697" t="s">
         <v>28</v>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
       <c r="D698">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E698" t="s">
         <v>28</v>
@@ -16003,7 +16003,7 @@
         <v>27</v>
       </c>
       <c r="D699">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E699" t="s">
         <v>28</v>
@@ -16020,7 +16020,7 @@
         <v>27</v>
       </c>
       <c r="D700">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E700" t="s">
         <v>28</v>
@@ -16037,7 +16037,7 @@
         <v>27</v>
       </c>
       <c r="D701">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E701" t="s">
         <v>28</v>
@@ -16054,7 +16054,7 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E702" t="s">
         <v>28</v>
@@ -16071,7 +16071,7 @@
         <v>27</v>
       </c>
       <c r="D703">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E703" t="s">
         <v>28</v>
@@ -16088,7 +16088,7 @@
         <v>27</v>
       </c>
       <c r="D704">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E704" t="s">
         <v>28</v>
@@ -16105,7 +16105,7 @@
         <v>27</v>
       </c>
       <c r="D705">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E705" t="s">
         <v>28</v>
@@ -16139,7 +16139,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E707" t="s">
         <v>28</v>
@@ -16156,7 +16156,7 @@
         <v>27</v>
       </c>
       <c r="D708">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E708" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="D709">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E709" t="s">
         <v>28</v>
@@ -16190,7 +16190,7 @@
         <v>27</v>
       </c>
       <c r="D710">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E710" t="s">
         <v>28</v>
@@ -16224,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="D712">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E712" t="s">
         <v>28</v>
@@ -16241,7 +16241,7 @@
         <v>27</v>
       </c>
       <c r="D713">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E713" t="s">
         <v>28</v>
@@ -16258,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="D714">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E714" t="s">
         <v>28</v>
@@ -16292,7 +16292,7 @@
         <v>27</v>
       </c>
       <c r="D716">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E716" t="s">
         <v>28</v>
@@ -16309,7 +16309,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E717" t="s">
         <v>28</v>
@@ -16326,7 +16326,7 @@
         <v>27</v>
       </c>
       <c r="D718">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E718" t="s">
         <v>28</v>
@@ -16343,7 +16343,7 @@
         <v>27</v>
       </c>
       <c r="D719">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E719" t="s">
         <v>28</v>
@@ -16360,7 +16360,7 @@
         <v>27</v>
       </c>
       <c r="D720">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E720" t="s">
         <v>28</v>
@@ -16377,7 +16377,7 @@
         <v>27</v>
       </c>
       <c r="D721">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E721" t="s">
         <v>28</v>
@@ -16394,7 +16394,7 @@
         <v>27</v>
       </c>
       <c r="D722">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E722" t="s">
         <v>28</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="D723">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E723" t="s">
         <v>28</v>
@@ -16428,7 +16428,7 @@
         <v>27</v>
       </c>
       <c r="D724">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E724" t="s">
         <v>28</v>
@@ -16445,7 +16445,7 @@
         <v>27</v>
       </c>
       <c r="D725">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E725" t="s">
         <v>28</v>
@@ -16462,7 +16462,7 @@
         <v>27</v>
       </c>
       <c r="D726">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E726" t="s">
         <v>28</v>
@@ -16479,7 +16479,7 @@
         <v>27</v>
       </c>
       <c r="D727">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E727" t="s">
         <v>28</v>
@@ -16496,7 +16496,7 @@
         <v>27</v>
       </c>
       <c r="D728">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E728" t="s">
         <v>28</v>
@@ -16513,7 +16513,7 @@
         <v>27</v>
       </c>
       <c r="D729">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E729" t="s">
         <v>28</v>
@@ -16530,7 +16530,7 @@
         <v>27</v>
       </c>
       <c r="D730">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E730" t="s">
         <v>28</v>
@@ -16547,7 +16547,7 @@
         <v>27</v>
       </c>
       <c r="D731">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E731" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="D732">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E732" t="s">
         <v>28</v>
@@ -16581,7 +16581,7 @@
         <v>27</v>
       </c>
       <c r="D733">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E733" t="s">
         <v>28</v>
@@ -16598,7 +16598,7 @@
         <v>27</v>
       </c>
       <c r="D734">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E734" t="s">
         <v>28</v>
@@ -16615,7 +16615,7 @@
         <v>27</v>
       </c>
       <c r="D735">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E735" t="s">
         <v>28</v>
@@ -16632,7 +16632,7 @@
         <v>27</v>
       </c>
       <c r="D736">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E736" t="s">
         <v>28</v>
@@ -16649,7 +16649,7 @@
         <v>27</v>
       </c>
       <c r="D737">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E737" t="s">
         <v>28</v>
@@ -16666,7 +16666,7 @@
         <v>27</v>
       </c>
       <c r="D738">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E738" t="s">
         <v>28</v>
@@ -16700,7 +16700,7 @@
         <v>27</v>
       </c>
       <c r="D740">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E740" t="s">
         <v>28</v>
@@ -16717,7 +16717,7 @@
         <v>27</v>
       </c>
       <c r="D741">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E741" t="s">
         <v>28</v>
@@ -16734,7 +16734,7 @@
         <v>27</v>
       </c>
       <c r="D742">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E742" t="s">
         <v>28</v>
@@ -16751,7 +16751,7 @@
         <v>27</v>
       </c>
       <c r="D743">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E743" t="s">
         <v>28</v>
@@ -16768,7 +16768,7 @@
         <v>27</v>
       </c>
       <c r="D744">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E744" t="s">
         <v>28</v>
@@ -16785,7 +16785,7 @@
         <v>27</v>
       </c>
       <c r="D745">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E745" t="s">
         <v>28</v>
@@ -16802,7 +16802,7 @@
         <v>27</v>
       </c>
       <c r="D746">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E746" t="s">
         <v>28</v>
@@ -16819,7 +16819,7 @@
         <v>27</v>
       </c>
       <c r="D747">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E747" t="s">
         <v>28</v>
@@ -16836,7 +16836,7 @@
         <v>27</v>
       </c>
       <c r="D748">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E748" t="s">
         <v>28</v>
@@ -16853,7 +16853,7 @@
         <v>27</v>
       </c>
       <c r="D749">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E749" t="s">
         <v>28</v>
@@ -16870,7 +16870,7 @@
         <v>27</v>
       </c>
       <c r="D750">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E750" t="s">
         <v>28</v>
@@ -16887,7 +16887,7 @@
         <v>27</v>
       </c>
       <c r="D751">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E751" t="s">
         <v>28</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="D752">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E752" t="s">
         <v>28</v>
@@ -16921,7 +16921,7 @@
         <v>27</v>
       </c>
       <c r="D753">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E753" t="s">
         <v>28</v>
@@ -16938,7 +16938,7 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E754" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="D755">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E755" t="s">
         <v>28</v>
@@ -16972,7 +16972,7 @@
         <v>27</v>
       </c>
       <c r="D756">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E756" t="s">
         <v>28</v>
@@ -16989,7 +16989,7 @@
         <v>27</v>
       </c>
       <c r="D757">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E757" t="s">
         <v>28</v>
@@ -17006,7 +17006,7 @@
         <v>27</v>
       </c>
       <c r="D758">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E758" t="s">
         <v>28</v>
@@ -17023,7 +17023,7 @@
         <v>27</v>
       </c>
       <c r="D759">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E759" t="s">
         <v>28</v>
@@ -17040,7 +17040,7 @@
         <v>27</v>
       </c>
       <c r="D760">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E760" t="s">
         <v>28</v>
@@ -17057,7 +17057,7 @@
         <v>27</v>
       </c>
       <c r="D761">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E761" t="s">
         <v>28</v>
@@ -17074,7 +17074,7 @@
         <v>27</v>
       </c>
       <c r="D762">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E762" t="s">
         <v>28</v>
@@ -17091,7 +17091,7 @@
         <v>27</v>
       </c>
       <c r="D763">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E763" t="s">
         <v>28</v>
@@ -17108,7 +17108,7 @@
         <v>27</v>
       </c>
       <c r="D764">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E764" t="s">
         <v>28</v>
@@ -17125,7 +17125,7 @@
         <v>27</v>
       </c>
       <c r="D765">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E765" t="s">
         <v>28</v>
@@ -17142,7 +17142,7 @@
         <v>27</v>
       </c>
       <c r="D766">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E766" t="s">
         <v>28</v>
@@ -17159,7 +17159,7 @@
         <v>27</v>
       </c>
       <c r="D767">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E767" t="s">
         <v>28</v>
@@ -17176,7 +17176,7 @@
         <v>27</v>
       </c>
       <c r="D768">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E768" t="s">
         <v>28</v>
@@ -17193,7 +17193,7 @@
         <v>27</v>
       </c>
       <c r="D769">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E769" t="s">
         <v>28</v>
@@ -17210,7 +17210,7 @@
         <v>27</v>
       </c>
       <c r="D770">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E770" t="s">
         <v>28</v>
@@ -17227,7 +17227,7 @@
         <v>27</v>
       </c>
       <c r="D771">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E771" t="s">
         <v>28</v>
@@ -17244,7 +17244,7 @@
         <v>27</v>
       </c>
       <c r="D772">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E772" t="s">
         <v>28</v>
@@ -17261,7 +17261,7 @@
         <v>27</v>
       </c>
       <c r="D773">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E773" t="s">
         <v>28</v>
@@ -17278,7 +17278,7 @@
         <v>27</v>
       </c>
       <c r="D774">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E774" t="s">
         <v>28</v>
@@ -17295,7 +17295,7 @@
         <v>27</v>
       </c>
       <c r="D775">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E775" t="s">
         <v>28</v>
@@ -17312,7 +17312,7 @@
         <v>27</v>
       </c>
       <c r="D776">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E776" t="s">
         <v>28</v>
@@ -17329,7 +17329,7 @@
         <v>27</v>
       </c>
       <c r="D777">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E777" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="D778">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E778" t="s">
         <v>28</v>
@@ -17363,7 +17363,7 @@
         <v>27</v>
       </c>
       <c r="D779">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E779" t="s">
         <v>28</v>
@@ -17380,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="D780">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E780" t="s">
         <v>28</v>
@@ -17397,7 +17397,7 @@
         <v>27</v>
       </c>
       <c r="D781">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E781" t="s">
         <v>28</v>
@@ -17414,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="D782">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E782" t="s">
         <v>28</v>
@@ -17431,7 +17431,7 @@
         <v>27</v>
       </c>
       <c r="D783">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E783" t="s">
         <v>28</v>
@@ -17448,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D784">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E784" t="s">
         <v>28</v>
@@ -17482,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="D786">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E786" t="s">
         <v>28</v>
@@ -17499,7 +17499,7 @@
         <v>27</v>
       </c>
       <c r="D787">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E787" t="s">
         <v>28</v>
@@ -17516,7 +17516,7 @@
         <v>27</v>
       </c>
       <c r="D788">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E788" t="s">
         <v>28</v>
@@ -17533,7 +17533,7 @@
         <v>27</v>
       </c>
       <c r="D789">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E789" t="s">
         <v>28</v>
@@ -17550,7 +17550,7 @@
         <v>27</v>
       </c>
       <c r="D790">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E790" t="s">
         <v>28</v>
@@ -17567,7 +17567,7 @@
         <v>27</v>
       </c>
       <c r="D791">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E791" t="s">
         <v>28</v>
@@ -17584,7 +17584,7 @@
         <v>27</v>
       </c>
       <c r="D792">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E792" t="s">
         <v>28</v>
@@ -17618,7 +17618,7 @@
         <v>27</v>
       </c>
       <c r="D794">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E794" t="s">
         <v>28</v>
@@ -17635,7 +17635,7 @@
         <v>27</v>
       </c>
       <c r="D795">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E795" t="s">
         <v>28</v>
@@ -17652,7 +17652,7 @@
         <v>27</v>
       </c>
       <c r="D796">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E796" t="s">
         <v>28</v>
@@ -17669,7 +17669,7 @@
         <v>27</v>
       </c>
       <c r="D797">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E797" t="s">
         <v>28</v>
@@ -17686,7 +17686,7 @@
         <v>27</v>
       </c>
       <c r="D798">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E798" t="s">
         <v>28</v>
@@ -17703,7 +17703,7 @@
         <v>27</v>
       </c>
       <c r="D799">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E799" t="s">
         <v>28</v>
@@ -17720,7 +17720,7 @@
         <v>27</v>
       </c>
       <c r="D800">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E800" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="D801">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E801" t="s">
         <v>28</v>
@@ -17754,7 +17754,7 @@
         <v>27</v>
       </c>
       <c r="D802">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E802" t="s">
         <v>28</v>
@@ -17771,7 +17771,7 @@
         <v>27</v>
       </c>
       <c r="D803">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E803" t="s">
         <v>28</v>
@@ -17788,7 +17788,7 @@
         <v>27</v>
       </c>
       <c r="D804">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E804" t="s">
         <v>28</v>
@@ -17805,7 +17805,7 @@
         <v>27</v>
       </c>
       <c r="D805">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E805" t="s">
         <v>28</v>
@@ -17822,7 +17822,7 @@
         <v>27</v>
       </c>
       <c r="D806">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E806" t="s">
         <v>28</v>
@@ -17839,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="D807">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E807" t="s">
         <v>28</v>
@@ -17856,7 +17856,7 @@
         <v>27</v>
       </c>
       <c r="D808">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E808" t="s">
         <v>28</v>
@@ -17873,7 +17873,7 @@
         <v>27</v>
       </c>
       <c r="D809">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E809" t="s">
         <v>28</v>
@@ -17890,7 +17890,7 @@
         <v>27</v>
       </c>
       <c r="D810">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E810" t="s">
         <v>28</v>
@@ -17907,7 +17907,7 @@
         <v>27</v>
       </c>
       <c r="D811">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E811" t="s">
         <v>28</v>
@@ -17924,7 +17924,7 @@
         <v>27</v>
       </c>
       <c r="D812">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E812" t="s">
         <v>28</v>
@@ -17941,7 +17941,7 @@
         <v>27</v>
       </c>
       <c r="D813">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E813" t="s">
         <v>28</v>
@@ -17958,7 +17958,7 @@
         <v>27</v>
       </c>
       <c r="D814">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E814" t="s">
         <v>28</v>
@@ -17975,7 +17975,7 @@
         <v>27</v>
       </c>
       <c r="D815">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E815" t="s">
         <v>28</v>
@@ -17992,7 +17992,7 @@
         <v>27</v>
       </c>
       <c r="D816">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E816" t="s">
         <v>28</v>
@@ -18009,7 +18009,7 @@
         <v>27</v>
       </c>
       <c r="D817">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E817" t="s">
         <v>28</v>
@@ -18043,7 +18043,7 @@
         <v>27</v>
       </c>
       <c r="D819">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E819" t="s">
         <v>28</v>
@@ -18060,7 +18060,7 @@
         <v>27</v>
       </c>
       <c r="D820">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E820" t="s">
         <v>28</v>
@@ -18077,7 +18077,7 @@
         <v>27</v>
       </c>
       <c r="D821">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E821" t="s">
         <v>28</v>
@@ -18094,7 +18094,7 @@
         <v>27</v>
       </c>
       <c r="D822">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E822" t="s">
         <v>28</v>
@@ -18111,7 +18111,7 @@
         <v>27</v>
       </c>
       <c r="D823">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E823" t="s">
         <v>28</v>
@@ -18128,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="D824">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E824" t="s">
         <v>28</v>
@@ -18145,7 +18145,7 @@
         <v>27</v>
       </c>
       <c r="D825">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E825" t="s">
         <v>28</v>
@@ -18162,7 +18162,7 @@
         <v>27</v>
       </c>
       <c r="D826">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E826" t="s">
         <v>28</v>
@@ -18179,7 +18179,7 @@
         <v>27</v>
       </c>
       <c r="D827">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E827" t="s">
         <v>28</v>
@@ -18196,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="D828">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E828" t="s">
         <v>28</v>
@@ -18213,7 +18213,7 @@
         <v>27</v>
       </c>
       <c r="D829">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E829" t="s">
         <v>28</v>
@@ -18230,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="D830">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E830" t="s">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E831" t="s">
         <v>28</v>
@@ -18264,7 +18264,7 @@
         <v>27</v>
       </c>
       <c r="D832">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E832" t="s">
         <v>28</v>
@@ -18281,7 +18281,7 @@
         <v>27</v>
       </c>
       <c r="D833">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E833" t="s">
         <v>28</v>
@@ -18298,7 +18298,7 @@
         <v>27</v>
       </c>
       <c r="D834">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E834" t="s">
         <v>28</v>
@@ -18315,7 +18315,7 @@
         <v>27</v>
       </c>
       <c r="D835">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E835" t="s">
         <v>28</v>
@@ -18332,7 +18332,7 @@
         <v>27</v>
       </c>
       <c r="D836">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E836" t="s">
         <v>28</v>
@@ -18349,7 +18349,7 @@
         <v>27</v>
       </c>
       <c r="D837">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E837" t="s">
         <v>28</v>
@@ -18366,7 +18366,7 @@
         <v>27</v>
       </c>
       <c r="D838">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E838" t="s">
         <v>28</v>
@@ -18383,7 +18383,7 @@
         <v>27</v>
       </c>
       <c r="D839">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E839" t="s">
         <v>28</v>
@@ -18400,7 +18400,7 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E840" t="s">
         <v>28</v>
@@ -18434,7 +18434,7 @@
         <v>27</v>
       </c>
       <c r="D842">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E842" t="s">
         <v>28</v>
@@ -18451,7 +18451,7 @@
         <v>27</v>
       </c>
       <c r="D843">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E843" t="s">
         <v>28</v>
@@ -18468,7 +18468,7 @@
         <v>27</v>
       </c>
       <c r="D844">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E844" t="s">
         <v>28</v>
@@ -18502,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="D846">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E846" t="s">
         <v>28</v>
@@ -18519,7 +18519,7 @@
         <v>27</v>
       </c>
       <c r="D847">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E847" t="s">
         <v>28</v>
@@ -18536,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="D848">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E848" t="s">
         <v>28</v>
@@ -18553,7 +18553,7 @@
         <v>27</v>
       </c>
       <c r="D849">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E849" t="s">
         <v>28</v>
@@ -18570,7 +18570,7 @@
         <v>27</v>
       </c>
       <c r="D850">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E850" t="s">
         <v>28</v>
@@ -18587,7 +18587,7 @@
         <v>27</v>
       </c>
       <c r="D851">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E851" t="s">
         <v>28</v>
@@ -18604,7 +18604,7 @@
         <v>27</v>
       </c>
       <c r="D852">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E852" t="s">
         <v>28</v>
@@ -18621,7 +18621,7 @@
         <v>27</v>
       </c>
       <c r="D853">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E853" t="s">
         <v>28</v>
@@ -18638,7 +18638,7 @@
         <v>27</v>
       </c>
       <c r="D854">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E854" t="s">
         <v>28</v>
@@ -18655,7 +18655,7 @@
         <v>27</v>
       </c>
       <c r="D855">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E855" t="s">
         <v>28</v>
@@ -18672,7 +18672,7 @@
         <v>27</v>
       </c>
       <c r="D856">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E856" t="s">
         <v>28</v>
@@ -18689,7 +18689,7 @@
         <v>27</v>
       </c>
       <c r="D857">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E857" t="s">
         <v>28</v>
@@ -18706,7 +18706,7 @@
         <v>27</v>
       </c>
       <c r="D858">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E858" t="s">
         <v>28</v>
@@ -18723,7 +18723,7 @@
         <v>27</v>
       </c>
       <c r="D859">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E859" t="s">
         <v>28</v>
@@ -18740,7 +18740,7 @@
         <v>27</v>
       </c>
       <c r="D860">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E860" t="s">
         <v>28</v>
@@ -18774,7 +18774,7 @@
         <v>27</v>
       </c>
       <c r="D862">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E862" t="s">
         <v>28</v>
@@ -18791,7 +18791,7 @@
         <v>27</v>
       </c>
       <c r="D863">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E863" t="s">
         <v>28</v>
@@ -18808,7 +18808,7 @@
         <v>27</v>
       </c>
       <c r="D864">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E864" t="s">
         <v>28</v>
@@ -18825,7 +18825,7 @@
         <v>27</v>
       </c>
       <c r="D865">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E865" t="s">
         <v>28</v>
@@ -18842,7 +18842,7 @@
         <v>27</v>
       </c>
       <c r="D866">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E866" t="s">
         <v>28</v>
@@ -18859,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="D867">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E867" t="s">
         <v>28</v>
@@ -18876,7 +18876,7 @@
         <v>27</v>
       </c>
       <c r="D868">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E868" t="s">
         <v>28</v>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
       <c r="D869">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E869" t="s">
         <v>28</v>
@@ -18910,7 +18910,7 @@
         <v>27</v>
       </c>
       <c r="D870">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E870" t="s">
         <v>28</v>
@@ -18944,7 +18944,7 @@
         <v>27</v>
       </c>
       <c r="D872">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E872" t="s">
         <v>28</v>
@@ -18961,7 +18961,7 @@
         <v>27</v>
       </c>
       <c r="D873">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E873" t="s">
         <v>28</v>
@@ -18978,7 +18978,7 @@
         <v>27</v>
       </c>
       <c r="D874">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E874" t="s">
         <v>28</v>
@@ -18995,7 +18995,7 @@
         <v>27</v>
       </c>
       <c r="D875">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E875" t="s">
         <v>28</v>
@@ -19012,7 +19012,7 @@
         <v>27</v>
       </c>
       <c r="D876">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E876" t="s">
         <v>28</v>
@@ -19029,7 +19029,7 @@
         <v>27</v>
       </c>
       <c r="D877">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E877" t="s">
         <v>28</v>
@@ -19046,7 +19046,7 @@
         <v>27</v>
       </c>
       <c r="D878">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E878" t="s">
         <v>28</v>
@@ -19063,7 +19063,7 @@
         <v>27</v>
       </c>
       <c r="D879">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E879" t="s">
         <v>28</v>
@@ -19080,7 +19080,7 @@
         <v>27</v>
       </c>
       <c r="D880">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E880" t="s">
         <v>28</v>
@@ -19097,7 +19097,7 @@
         <v>27</v>
       </c>
       <c r="D881">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E881" t="s">
         <v>28</v>
@@ -19114,7 +19114,7 @@
         <v>27</v>
       </c>
       <c r="D882">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E882" t="s">
         <v>28</v>
@@ -19131,7 +19131,7 @@
         <v>27</v>
       </c>
       <c r="D883">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E883" t="s">
         <v>28</v>
@@ -19148,7 +19148,7 @@
         <v>27</v>
       </c>
       <c r="D884">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E884" t="s">
         <v>28</v>
@@ -19165,7 +19165,7 @@
         <v>27</v>
       </c>
       <c r="D885">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E885" t="s">
         <v>28</v>
@@ -19182,7 +19182,7 @@
         <v>27</v>
       </c>
       <c r="D886">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E886" t="s">
         <v>28</v>
@@ -19216,7 +19216,7 @@
         <v>27</v>
       </c>
       <c r="D888">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E888" t="s">
         <v>28</v>
@@ -19250,7 +19250,7 @@
         <v>27</v>
       </c>
       <c r="D890">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E890" t="s">
         <v>28</v>
@@ -19267,7 +19267,7 @@
         <v>27</v>
       </c>
       <c r="D891">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E891" t="s">
         <v>28</v>
@@ -19284,7 +19284,7 @@
         <v>27</v>
       </c>
       <c r="D892">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E892" t="s">
         <v>28</v>
@@ -19301,7 +19301,7 @@
         <v>27</v>
       </c>
       <c r="D893">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E893" t="s">
         <v>28</v>
@@ -19318,7 +19318,7 @@
         <v>27</v>
       </c>
       <c r="D894">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E894" t="s">
         <v>28</v>
@@ -19335,7 +19335,7 @@
         <v>27</v>
       </c>
       <c r="D895">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E895" t="s">
         <v>28</v>
@@ -19352,7 +19352,7 @@
         <v>27</v>
       </c>
       <c r="D896">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E896" t="s">
         <v>28</v>
@@ -19369,7 +19369,7 @@
         <v>27</v>
       </c>
       <c r="D897">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E897" t="s">
         <v>28</v>
@@ -19386,7 +19386,7 @@
         <v>27</v>
       </c>
       <c r="D898">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E898" t="s">
         <v>28</v>
@@ -19403,7 +19403,7 @@
         <v>27</v>
       </c>
       <c r="D899">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E899" t="s">
         <v>28</v>
@@ -19420,7 +19420,7 @@
         <v>27</v>
       </c>
       <c r="D900">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E900" t="s">
         <v>28</v>
@@ -19437,7 +19437,7 @@
         <v>27</v>
       </c>
       <c r="D901">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E901" t="s">
         <v>28</v>
@@ -19454,7 +19454,7 @@
         <v>27</v>
       </c>
       <c r="D902">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E902" t="s">
         <v>28</v>
@@ -19471,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D903">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E903" t="s">
         <v>28</v>
@@ -19488,7 +19488,7 @@
         <v>27</v>
       </c>
       <c r="D904">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E904" t="s">
         <v>28</v>
@@ -19522,7 +19522,7 @@
         <v>27</v>
       </c>
       <c r="D906">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E906" t="s">
         <v>28</v>
@@ -19539,7 +19539,7 @@
         <v>27</v>
       </c>
       <c r="D907">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E907" t="s">
         <v>28</v>
@@ -19556,7 +19556,7 @@
         <v>27</v>
       </c>
       <c r="D908">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E908" t="s">
         <v>28</v>
@@ -19573,7 +19573,7 @@
         <v>27</v>
       </c>
       <c r="D909">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E909" t="s">
         <v>28</v>
@@ -19590,7 +19590,7 @@
         <v>27</v>
       </c>
       <c r="D910">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E910" t="s">
         <v>28</v>
@@ -19607,7 +19607,7 @@
         <v>27</v>
       </c>
       <c r="D911">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E911" t="s">
         <v>28</v>
@@ -19624,7 +19624,7 @@
         <v>27</v>
       </c>
       <c r="D912">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E912" t="s">
         <v>28</v>
@@ -19658,7 +19658,7 @@
         <v>27</v>
       </c>
       <c r="D914">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E914" t="s">
         <v>28</v>
@@ -19675,7 +19675,7 @@
         <v>27</v>
       </c>
       <c r="D915">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E915" t="s">
         <v>28</v>
@@ -19692,7 +19692,7 @@
         <v>27</v>
       </c>
       <c r="D916">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E916" t="s">
         <v>28</v>
@@ -19709,7 +19709,7 @@
         <v>27</v>
       </c>
       <c r="D917">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E917" t="s">
         <v>28</v>
@@ -19726,7 +19726,7 @@
         <v>27</v>
       </c>
       <c r="D918">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E918" t="s">
         <v>28</v>
@@ -19743,7 +19743,7 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E919" t="s">
         <v>28</v>
@@ -19760,7 +19760,7 @@
         <v>27</v>
       </c>
       <c r="D920">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E920" t="s">
         <v>28</v>
@@ -19777,7 +19777,7 @@
         <v>27</v>
       </c>
       <c r="D921">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E921" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>27</v>
       </c>
       <c r="D922">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E922" t="s">
         <v>28</v>
@@ -19811,7 +19811,7 @@
         <v>27</v>
       </c>
       <c r="D923">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E923" t="s">
         <v>28</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="D924">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E924" t="s">
         <v>28</v>
@@ -19845,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="D925">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E925" t="s">
         <v>28</v>
@@ -19862,7 +19862,7 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E926" t="s">
         <v>28</v>
@@ -19879,7 +19879,7 @@
         <v>27</v>
       </c>
       <c r="D927">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E927" t="s">
         <v>28</v>
@@ -19896,7 +19896,7 @@
         <v>27</v>
       </c>
       <c r="D928">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E928" t="s">
         <v>28</v>
@@ -19913,7 +19913,7 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E929" t="s">
         <v>28</v>
@@ -19930,7 +19930,7 @@
         <v>27</v>
       </c>
       <c r="D930">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E930" t="s">
         <v>28</v>
@@ -19947,7 +19947,7 @@
         <v>27</v>
       </c>
       <c r="D931">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E931" t="s">
         <v>28</v>
@@ -19964,7 +19964,7 @@
         <v>27</v>
       </c>
       <c r="D932">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E932" t="s">
         <v>28</v>
@@ -19981,7 +19981,7 @@
         <v>27</v>
       </c>
       <c r="D933">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E933" t="s">
         <v>28</v>
@@ -19998,7 +19998,7 @@
         <v>27</v>
       </c>
       <c r="D934">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E934" t="s">
         <v>28</v>
@@ -20015,7 +20015,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E935" t="s">
         <v>28</v>
@@ -20032,7 +20032,7 @@
         <v>27</v>
       </c>
       <c r="D936">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E936" t="s">
         <v>28</v>
@@ -20049,7 +20049,7 @@
         <v>27</v>
       </c>
       <c r="D937">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E937" t="s">
         <v>28</v>
@@ -20066,7 +20066,7 @@
         <v>27</v>
       </c>
       <c r="D938">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E938" t="s">
         <v>28</v>
@@ -20083,7 +20083,7 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E939" t="s">
         <v>28</v>
@@ -20100,7 +20100,7 @@
         <v>27</v>
       </c>
       <c r="D940">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E940" t="s">
         <v>28</v>
@@ -20117,7 +20117,7 @@
         <v>27</v>
       </c>
       <c r="D941">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E941" t="s">
         <v>28</v>
@@ -20134,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D942">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E942" t="s">
         <v>28</v>
@@ -20151,7 +20151,7 @@
         <v>27</v>
       </c>
       <c r="D943">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E943" t="s">
         <v>28</v>
@@ -20168,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="D944">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E944" t="s">
         <v>28</v>
@@ -20185,7 +20185,7 @@
         <v>27</v>
       </c>
       <c r="D945">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E945" t="s">
         <v>28</v>
@@ -20202,7 +20202,7 @@
         <v>27</v>
       </c>
       <c r="D946">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E946" t="s">
         <v>28</v>
@@ -20219,7 +20219,7 @@
         <v>27</v>
       </c>
       <c r="D947">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E947" t="s">
         <v>28</v>
@@ -20236,7 +20236,7 @@
         <v>27</v>
       </c>
       <c r="D948">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E948" t="s">
         <v>28</v>
@@ -20253,7 +20253,7 @@
         <v>27</v>
       </c>
       <c r="D949">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E949" t="s">
         <v>28</v>
@@ -20270,7 +20270,7 @@
         <v>27</v>
       </c>
       <c r="D950">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E950" t="s">
         <v>28</v>
@@ -20287,7 +20287,7 @@
         <v>27</v>
       </c>
       <c r="D951">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E951" t="s">
         <v>28</v>
@@ -20304,7 +20304,7 @@
         <v>27</v>
       </c>
       <c r="D952">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E952" t="s">
         <v>28</v>
@@ -20321,7 +20321,7 @@
         <v>27</v>
       </c>
       <c r="D953">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E953" t="s">
         <v>28</v>
@@ -20338,7 +20338,7 @@
         <v>27</v>
       </c>
       <c r="D954">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E954" t="s">
         <v>28</v>
@@ -20372,7 +20372,7 @@
         <v>27</v>
       </c>
       <c r="D956">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E956" t="s">
         <v>28</v>
@@ -20389,7 +20389,7 @@
         <v>27</v>
       </c>
       <c r="D957">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E957" t="s">
         <v>28</v>
@@ -20406,7 +20406,7 @@
         <v>27</v>
       </c>
       <c r="D958">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E958" t="s">
         <v>28</v>
@@ -20423,7 +20423,7 @@
         <v>27</v>
       </c>
       <c r="D959">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E959" t="s">
         <v>28</v>
@@ -20440,7 +20440,7 @@
         <v>27</v>
       </c>
       <c r="D960">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E960" t="s">
         <v>28</v>
@@ -20457,7 +20457,7 @@
         <v>27</v>
       </c>
       <c r="D961">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E961" t="s">
         <v>28</v>
@@ -20474,7 +20474,7 @@
         <v>27</v>
       </c>
       <c r="D962">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E962" t="s">
         <v>28</v>
@@ -20491,7 +20491,7 @@
         <v>27</v>
       </c>
       <c r="D963">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E963" t="s">
         <v>28</v>
@@ -20525,7 +20525,7 @@
         <v>27</v>
       </c>
       <c r="D965">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E965" t="s">
         <v>28</v>
@@ -20542,7 +20542,7 @@
         <v>27</v>
       </c>
       <c r="D966">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E966" t="s">
         <v>28</v>
@@ -20559,7 +20559,7 @@
         <v>27</v>
       </c>
       <c r="D967">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E967" t="s">
         <v>28</v>
@@ -20593,7 +20593,7 @@
         <v>27</v>
       </c>
       <c r="D969">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E969" t="s">
         <v>28</v>
@@ -20610,7 +20610,7 @@
         <v>27</v>
       </c>
       <c r="D970">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E970" t="s">
         <v>28</v>
@@ -20627,7 +20627,7 @@
         <v>27</v>
       </c>
       <c r="D971">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E971" t="s">
         <v>28</v>
@@ -20644,7 +20644,7 @@
         <v>27</v>
       </c>
       <c r="D972">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E972" t="s">
         <v>28</v>
@@ -20661,7 +20661,7 @@
         <v>27</v>
       </c>
       <c r="D973">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E973" t="s">
         <v>28</v>
@@ -20678,7 +20678,7 @@
         <v>27</v>
       </c>
       <c r="D974">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E974" t="s">
         <v>28</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="D975">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E975" t="s">
         <v>28</v>
@@ -20712,7 +20712,7 @@
         <v>27</v>
       </c>
       <c r="D976">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E976" t="s">
         <v>28</v>
@@ -20729,7 +20729,7 @@
         <v>27</v>
       </c>
       <c r="D977">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E977" t="s">
         <v>28</v>
@@ -20746,7 +20746,7 @@
         <v>27</v>
       </c>
       <c r="D978">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E978" t="s">
         <v>28</v>
@@ -20763,7 +20763,7 @@
         <v>27</v>
       </c>
       <c r="D979">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E979" t="s">
         <v>28</v>
@@ -20780,7 +20780,7 @@
         <v>27</v>
       </c>
       <c r="D980">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E980" t="s">
         <v>28</v>
@@ -20797,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="D981">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E981" t="s">
         <v>28</v>
@@ -20814,7 +20814,7 @@
         <v>27</v>
       </c>
       <c r="D982">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E982" t="s">
         <v>28</v>
@@ -20831,7 +20831,7 @@
         <v>27</v>
       </c>
       <c r="D983">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E983" t="s">
         <v>28</v>
@@ -20848,7 +20848,7 @@
         <v>27</v>
       </c>
       <c r="D984">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E984" t="s">
         <v>28</v>
@@ -20865,7 +20865,7 @@
         <v>27</v>
       </c>
       <c r="D985">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E985" t="s">
         <v>28</v>
@@ -20882,7 +20882,7 @@
         <v>27</v>
       </c>
       <c r="D986">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E986" t="s">
         <v>28</v>
@@ -20899,7 +20899,7 @@
         <v>27</v>
       </c>
       <c r="D987">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E987" t="s">
         <v>28</v>
@@ -20916,7 +20916,7 @@
         <v>27</v>
       </c>
       <c r="D988">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E988" t="s">
         <v>28</v>
@@ -20933,7 +20933,7 @@
         <v>27</v>
       </c>
       <c r="D989">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E989" t="s">
         <v>28</v>
@@ -20950,7 +20950,7 @@
         <v>27</v>
       </c>
       <c r="D990">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E990" t="s">
         <v>28</v>
@@ -20984,7 +20984,7 @@
         <v>27</v>
       </c>
       <c r="D992">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E992" t="s">
         <v>28</v>
@@ -21001,7 +21001,7 @@
         <v>27</v>
       </c>
       <c r="D993">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E993" t="s">
         <v>28</v>
@@ -21018,7 +21018,7 @@
         <v>27</v>
       </c>
       <c r="D994">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E994" t="s">
         <v>28</v>
@@ -21035,7 +21035,7 @@
         <v>27</v>
       </c>
       <c r="D995">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E995" t="s">
         <v>28</v>
@@ -21052,7 +21052,7 @@
         <v>27</v>
       </c>
       <c r="D996">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E996" t="s">
         <v>28</v>
@@ -21069,7 +21069,7 @@
         <v>27</v>
       </c>
       <c r="D997">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E997" t="s">
         <v>28</v>
@@ -21086,7 +21086,7 @@
         <v>27</v>
       </c>
       <c r="D998">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E998" t="s">
         <v>28</v>
@@ -21103,7 +21103,7 @@
         <v>27</v>
       </c>
       <c r="D999">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E999" t="s">
         <v>28</v>
@@ -21120,7 +21120,7 @@
         <v>27</v>
       </c>
       <c r="D1000">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1000" t="s">
         <v>28</v>
@@ -21137,7 +21137,7 @@
         <v>27</v>
       </c>
       <c r="D1001">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1001" t="s">
         <v>28</v>
@@ -21154,7 +21154,7 @@
         <v>27</v>
       </c>
       <c r="D1002">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E1002" t="s">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>27</v>
       </c>
       <c r="D1003">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E1003" t="s">
         <v>28</v>
@@ -21188,7 +21188,7 @@
         <v>27</v>
       </c>
       <c r="D1004">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1004" t="s">
         <v>28</v>
@@ -21205,7 +21205,7 @@
         <v>27</v>
       </c>
       <c r="D1005">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1005" t="s">
         <v>28</v>
@@ -21222,7 +21222,7 @@
         <v>27</v>
       </c>
       <c r="D1006">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E1006" t="s">
         <v>28</v>
@@ -21239,7 +21239,7 @@
         <v>27</v>
       </c>
       <c r="D1007">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1007" t="s">
         <v>28</v>
@@ -21256,7 +21256,7 @@
         <v>27</v>
       </c>
       <c r="D1008">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1008" t="s">
         <v>28</v>
@@ -21273,7 +21273,7 @@
         <v>27</v>
       </c>
       <c r="D1009">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E1009" t="s">
         <v>28</v>
@@ -21290,7 +21290,7 @@
         <v>27</v>
       </c>
       <c r="D1010">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E1010" t="s">
         <v>28</v>
@@ -21307,7 +21307,7 @@
         <v>27</v>
       </c>
       <c r="D1011">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E1011" t="s">
         <v>28</v>
@@ -21324,7 +21324,7 @@
         <v>27</v>
       </c>
       <c r="D1012">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1012" t="s">
         <v>28</v>
@@ -21341,7 +21341,7 @@
         <v>27</v>
       </c>
       <c r="D1013">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1013" t="s">
         <v>28</v>
@@ -21358,7 +21358,7 @@
         <v>27</v>
       </c>
       <c r="D1014">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1014" t="s">
         <v>28</v>
@@ -21375,7 +21375,7 @@
         <v>27</v>
       </c>
       <c r="D1015">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1015" t="s">
         <v>28</v>
@@ -21392,7 +21392,7 @@
         <v>27</v>
       </c>
       <c r="D1016">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1016" t="s">
         <v>28</v>
@@ -21409,7 +21409,7 @@
         <v>27</v>
       </c>
       <c r="D1017">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1017" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>27</v>
       </c>
       <c r="D1018">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1018" t="s">
         <v>28</v>
@@ -21443,7 +21443,7 @@
         <v>27</v>
       </c>
       <c r="D1019">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E1019" t="s">
         <v>28</v>
@@ -21460,7 +21460,7 @@
         <v>27</v>
       </c>
       <c r="D1020">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1020" t="s">
         <v>28</v>
@@ -21477,7 +21477,7 @@
         <v>27</v>
       </c>
       <c r="D1021">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1021" t="s">
         <v>28</v>
@@ -21494,7 +21494,7 @@
         <v>27</v>
       </c>
       <c r="D1022">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1022" t="s">
         <v>28</v>
@@ -21511,7 +21511,7 @@
         <v>27</v>
       </c>
       <c r="D1023">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1023" t="s">
         <v>28</v>
@@ -21528,7 +21528,7 @@
         <v>27</v>
       </c>
       <c r="D1024">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E1024" t="s">
         <v>28</v>
@@ -21545,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E1025" t="s">
         <v>28</v>
@@ -21562,7 +21562,7 @@
         <v>27</v>
       </c>
       <c r="D1026">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1026" t="s">
         <v>28</v>
@@ -21579,7 +21579,7 @@
         <v>27</v>
       </c>
       <c r="D1027">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E1027" t="s">
         <v>28</v>
@@ -21596,7 +21596,7 @@
         <v>27</v>
       </c>
       <c r="D1028">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E1028" t="s">
         <v>28</v>
@@ -21613,7 +21613,7 @@
         <v>27</v>
       </c>
       <c r="D1029">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1029" t="s">
         <v>28</v>
@@ -21630,7 +21630,7 @@
         <v>27</v>
       </c>
       <c r="D1030">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E1030" t="s">
         <v>28</v>
@@ -21647,7 +21647,7 @@
         <v>27</v>
       </c>
       <c r="D1031">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1031" t="s">
         <v>28</v>
@@ -21664,7 +21664,7 @@
         <v>27</v>
       </c>
       <c r="D1032">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1032" t="s">
         <v>28</v>
@@ -21698,7 +21698,7 @@
         <v>27</v>
       </c>
       <c r="D1034">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1034" t="s">
         <v>28</v>
@@ -21715,7 +21715,7 @@
         <v>27</v>
       </c>
       <c r="D1035">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1035" t="s">
         <v>28</v>
@@ -21732,7 +21732,7 @@
         <v>27</v>
       </c>
       <c r="D1036">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E1036" t="s">
         <v>28</v>
@@ -21749,7 +21749,7 @@
         <v>27</v>
       </c>
       <c r="D1037">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1037" t="s">
         <v>28</v>
@@ -21766,7 +21766,7 @@
         <v>27</v>
       </c>
       <c r="D1038">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1038" t="s">
         <v>28</v>
@@ -21783,7 +21783,7 @@
         <v>27</v>
       </c>
       <c r="D1039">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1039" t="s">
         <v>28</v>
@@ -21800,7 +21800,7 @@
         <v>27</v>
       </c>
       <c r="D1040">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1040" t="s">
         <v>28</v>
@@ -21817,7 +21817,7 @@
         <v>27</v>
       </c>
       <c r="D1041">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1041" t="s">
         <v>28</v>
@@ -21834,7 +21834,7 @@
         <v>27</v>
       </c>
       <c r="D1042">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1042" t="s">
         <v>28</v>
@@ -21851,7 +21851,7 @@
         <v>27</v>
       </c>
       <c r="D1043">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1043" t="s">
         <v>28</v>
@@ -21885,7 +21885,7 @@
         <v>27</v>
       </c>
       <c r="D1045">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1045" t="s">
         <v>28</v>
@@ -21902,7 +21902,7 @@
         <v>27</v>
       </c>
       <c r="D1046">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1046" t="s">
         <v>28</v>
@@ -21919,7 +21919,7 @@
         <v>27</v>
       </c>
       <c r="D1047">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1047" t="s">
         <v>28</v>
@@ -21936,7 +21936,7 @@
         <v>27</v>
       </c>
       <c r="D1048">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1048" t="s">
         <v>28</v>
@@ -21953,7 +21953,7 @@
         <v>27</v>
       </c>
       <c r="D1049">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1049" t="s">
         <v>28</v>
@@ -21970,7 +21970,7 @@
         <v>27</v>
       </c>
       <c r="D1050">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E1050" t="s">
         <v>28</v>
@@ -21987,7 +21987,7 @@
         <v>27</v>
       </c>
       <c r="D1051">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1051" t="s">
         <v>28</v>
@@ -22004,7 +22004,7 @@
         <v>27</v>
       </c>
       <c r="D1052">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1052" t="s">
         <v>28</v>
@@ -22021,7 +22021,7 @@
         <v>27</v>
       </c>
       <c r="D1053">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E1053" t="s">
         <v>28</v>
@@ -22038,7 +22038,7 @@
         <v>27</v>
       </c>
       <c r="D1054">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E1054" t="s">
         <v>28</v>
@@ -22055,7 +22055,7 @@
         <v>27</v>
       </c>
       <c r="D1055">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E1055" t="s">
         <v>28</v>
@@ -22072,7 +22072,7 @@
         <v>27</v>
       </c>
       <c r="D1056">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E1056" t="s">
         <v>28</v>
@@ -22089,7 +22089,7 @@
         <v>27</v>
       </c>
       <c r="D1057">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E1057" t="s">
         <v>28</v>
@@ -22106,7 +22106,7 @@
         <v>27</v>
       </c>
       <c r="D1058">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E1058" t="s">
         <v>28</v>
@@ -22123,7 +22123,7 @@
         <v>27</v>
       </c>
       <c r="D1059">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1059" t="s">
         <v>28</v>
@@ -22140,7 +22140,7 @@
         <v>27</v>
       </c>
       <c r="D1060">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E1060" t="s">
         <v>28</v>
@@ -22157,7 +22157,7 @@
         <v>27</v>
       </c>
       <c r="D1061">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1061" t="s">
         <v>28</v>
@@ -22174,7 +22174,7 @@
         <v>27</v>
       </c>
       <c r="D1062">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1062" t="s">
         <v>28</v>
@@ -22191,7 +22191,7 @@
         <v>27</v>
       </c>
       <c r="D1063">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1063" t="s">
         <v>28</v>
@@ -22208,7 +22208,7 @@
         <v>27</v>
       </c>
       <c r="D1064">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E1064" t="s">
         <v>28</v>
@@ -22225,7 +22225,7 @@
         <v>27</v>
       </c>
       <c r="D1065">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1065" t="s">
         <v>28</v>
@@ -22242,7 +22242,7 @@
         <v>27</v>
       </c>
       <c r="D1066">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E1066" t="s">
         <v>28</v>
@@ -22259,7 +22259,7 @@
         <v>27</v>
       </c>
       <c r="D1067">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E1067" t="s">
         <v>28</v>
@@ -22276,7 +22276,7 @@
         <v>27</v>
       </c>
       <c r="D1068">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1068" t="s">
         <v>28</v>
@@ -22293,7 +22293,7 @@
         <v>27</v>
       </c>
       <c r="D1069">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1069" t="s">
         <v>28</v>
@@ -22310,7 +22310,7 @@
         <v>27</v>
       </c>
       <c r="D1070">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1070" t="s">
         <v>28</v>
@@ -22327,7 +22327,7 @@
         <v>27</v>
       </c>
       <c r="D1071">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E1071" t="s">
         <v>28</v>
@@ -22344,7 +22344,7 @@
         <v>27</v>
       </c>
       <c r="D1072">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E1072" t="s">
         <v>28</v>
@@ -22361,7 +22361,7 @@
         <v>27</v>
       </c>
       <c r="D1073">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1073" t="s">
         <v>28</v>
@@ -22395,7 +22395,7 @@
         <v>27</v>
       </c>
       <c r="D1075">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E1075" t="s">
         <v>28</v>
@@ -22412,7 +22412,7 @@
         <v>27</v>
       </c>
       <c r="D1076">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E1076" t="s">
         <v>28</v>
@@ -22429,7 +22429,7 @@
         <v>27</v>
       </c>
       <c r="D1077">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1077" t="s">
         <v>28</v>
@@ -22463,7 +22463,7 @@
         <v>27</v>
       </c>
       <c r="D1079">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E1079" t="s">
         <v>28</v>
@@ -22480,7 +22480,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1080" t="s">
         <v>28</v>
@@ -22497,7 +22497,7 @@
         <v>27</v>
       </c>
       <c r="D1081">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1081" t="s">
         <v>28</v>
@@ -22514,7 +22514,7 @@
         <v>27</v>
       </c>
       <c r="D1082">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1082" t="s">
         <v>28</v>
@@ -22531,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="D1083">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E1083" t="s">
         <v>28</v>
@@ -22548,7 +22548,7 @@
         <v>27</v>
       </c>
       <c r="D1084">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E1084" t="s">
         <v>28</v>
@@ -22565,7 +22565,7 @@
         <v>27</v>
       </c>
       <c r="D1085">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E1085" t="s">
         <v>28</v>
@@ -22582,7 +22582,7 @@
         <v>27</v>
       </c>
       <c r="D1086">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E1086" t="s">
         <v>28</v>
@@ -22599,7 +22599,7 @@
         <v>27</v>
       </c>
       <c r="D1087">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1087" t="s">
         <v>28</v>
@@ -22616,7 +22616,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E1088" t="s">
         <v>28</v>
@@ -22633,7 +22633,7 @@
         <v>27</v>
       </c>
       <c r="D1089">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1089" t="s">
         <v>28</v>
@@ -22650,7 +22650,7 @@
         <v>27</v>
       </c>
       <c r="D1090">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E1090" t="s">
         <v>28</v>
@@ -22667,7 +22667,7 @@
         <v>27</v>
       </c>
       <c r="D1091">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1091" t="s">
         <v>28</v>
@@ -22684,7 +22684,7 @@
         <v>27</v>
       </c>
       <c r="D1092">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E1092" t="s">
         <v>28</v>
@@ -22701,7 +22701,7 @@
         <v>27</v>
       </c>
       <c r="D1093">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E1093" t="s">
         <v>28</v>
@@ -22718,7 +22718,7 @@
         <v>27</v>
       </c>
       <c r="D1094">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1094" t="s">
         <v>28</v>
@@ -22735,7 +22735,7 @@
         <v>27</v>
       </c>
       <c r="D1095">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E1095" t="s">
         <v>28</v>
@@ -22752,7 +22752,7 @@
         <v>27</v>
       </c>
       <c r="D1096">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E1096" t="s">
         <v>28</v>
@@ -22769,7 +22769,7 @@
         <v>27</v>
       </c>
       <c r="D1097">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1097" t="s">
         <v>28</v>
@@ -22786,7 +22786,7 @@
         <v>27</v>
       </c>
       <c r="D1098">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1098" t="s">
         <v>28</v>
@@ -22803,7 +22803,7 @@
         <v>27</v>
       </c>
       <c r="D1099">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E1099" t="s">
         <v>28</v>
@@ -22820,7 +22820,7 @@
         <v>27</v>
       </c>
       <c r="D1100">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1100" t="s">
         <v>28</v>
@@ -22837,7 +22837,7 @@
         <v>27</v>
       </c>
       <c r="D1101">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E1101" t="s">
         <v>28</v>
@@ -22871,7 +22871,7 @@
         <v>27</v>
       </c>
       <c r="D1103">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1103" t="s">
         <v>28</v>
@@ -22888,7 +22888,7 @@
         <v>27</v>
       </c>
       <c r="D1104">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1104" t="s">
         <v>28</v>
@@ -22973,7 +22973,7 @@
         <v>27</v>
       </c>
       <c r="D1109">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1109" t="s">
         <v>28</v>
@@ -22990,7 +22990,7 @@
         <v>27</v>
       </c>
       <c r="D1110">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E1110" t="s">
         <v>28</v>
@@ -23007,7 +23007,7 @@
         <v>27</v>
       </c>
       <c r="D1111">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E1111" t="s">
         <v>28</v>
@@ -23024,7 +23024,7 @@
         <v>27</v>
       </c>
       <c r="D1112">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E1112" t="s">
         <v>28</v>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1273</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1272</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1335</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1346</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1311</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1265</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1342</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1353</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1253</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1262</v>
+        <v>1293</v>
       </c>
     </row>
   </sheetData>
@@ -4154,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -4188,7 +4188,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -4205,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -4222,7 +4222,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -4256,7 +4256,7 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -4273,7 +4273,7 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4307,7 +4307,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4341,7 +4341,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -4358,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4409,7 +4409,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -4426,7 +4426,7 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -4443,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -4460,7 +4460,7 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
@@ -4494,7 +4494,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -4511,7 +4511,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -4528,7 +4528,7 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -4545,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s">
         <v>28</v>
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -4579,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -4596,7 +4596,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -4613,7 +4613,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E30" t="s">
         <v>28</v>
@@ -4647,7 +4647,7 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4698,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="D34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -4715,7 +4715,7 @@
         <v>27</v>
       </c>
       <c r="D35">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E35" t="s">
         <v>28</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -4749,7 +4749,7 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="s">
         <v>28</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
         <v>28</v>
@@ -4783,7 +4783,7 @@
         <v>27</v>
       </c>
       <c r="D39">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
         <v>28</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
@@ -4817,7 +4817,7 @@
         <v>27</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4834,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4851,7 +4851,7 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
@@ -4885,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
         <v>27</v>
       </c>
       <c r="D46">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -4919,7 +4919,7 @@
         <v>27</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4953,7 +4953,7 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
@@ -4970,7 +4970,7 @@
         <v>27</v>
       </c>
       <c r="D50">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -4987,7 +4987,7 @@
         <v>27</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
@@ -5004,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5055,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="D55">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -5072,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E56" t="s">
         <v>28</v>
@@ -5089,7 +5089,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E57" t="s">
         <v>28</v>
@@ -5106,7 +5106,7 @@
         <v>27</v>
       </c>
       <c r="D58">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -5123,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E59" t="s">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         <v>27</v>
       </c>
       <c r="D60">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E60" t="s">
         <v>28</v>
@@ -5174,7 +5174,7 @@
         <v>27</v>
       </c>
       <c r="D62">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
@@ -5191,7 +5191,7 @@
         <v>27</v>
       </c>
       <c r="D63">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="D64">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
@@ -5225,7 +5225,7 @@
         <v>27</v>
       </c>
       <c r="D65">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -5242,7 +5242,7 @@
         <v>27</v>
       </c>
       <c r="D66">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="D67">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
@@ -5310,7 +5310,7 @@
         <v>27</v>
       </c>
       <c r="D70">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="D71">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -5344,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="D72">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
@@ -5361,7 +5361,7 @@
         <v>27</v>
       </c>
       <c r="D73">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -5378,7 +5378,7 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
@@ -5395,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="D75">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="D76">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
@@ -5429,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="D77">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -5446,7 +5446,7 @@
         <v>27</v>
       </c>
       <c r="D78">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
@@ -5463,7 +5463,7 @@
         <v>27</v>
       </c>
       <c r="D79">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
@@ -5480,7 +5480,7 @@
         <v>27</v>
       </c>
       <c r="D80">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
@@ -5497,7 +5497,7 @@
         <v>27</v>
       </c>
       <c r="D81">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -5514,7 +5514,7 @@
         <v>27</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
@@ -5531,7 +5531,7 @@
         <v>27</v>
       </c>
       <c r="D83">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
@@ -5565,7 +5565,7 @@
         <v>27</v>
       </c>
       <c r="D85">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -5582,7 +5582,7 @@
         <v>27</v>
       </c>
       <c r="D86">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
@@ -5599,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="D87">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
@@ -5616,7 +5616,7 @@
         <v>27</v>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -5633,7 +5633,7 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="D90">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -5667,7 +5667,7 @@
         <v>27</v>
       </c>
       <c r="D91">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E91" t="s">
         <v>28</v>
@@ -5684,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="D92">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
@@ -5701,7 +5701,7 @@
         <v>27</v>
       </c>
       <c r="D93">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E93" t="s">
         <v>28</v>
@@ -5718,7 +5718,7 @@
         <v>27</v>
       </c>
       <c r="D94">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s">
         <v>28</v>
@@ -5735,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D95">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -5769,7 +5769,7 @@
         <v>27</v>
       </c>
       <c r="D97">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E97" t="s">
         <v>28</v>
@@ -5786,7 +5786,7 @@
         <v>27</v>
       </c>
       <c r="D98">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="D99">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E99" t="s">
         <v>28</v>
@@ -5820,7 +5820,7 @@
         <v>27</v>
       </c>
       <c r="D100">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E100" t="s">
         <v>28</v>
@@ -5837,7 +5837,7 @@
         <v>27</v>
       </c>
       <c r="D101">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E101" t="s">
         <v>28</v>
@@ -5854,7 +5854,7 @@
         <v>27</v>
       </c>
       <c r="D102">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E102" t="s">
         <v>28</v>
@@ -5871,7 +5871,7 @@
         <v>27</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E103" t="s">
         <v>28</v>
@@ -5888,7 +5888,7 @@
         <v>27</v>
       </c>
       <c r="D104">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E104" t="s">
         <v>28</v>
@@ -5905,7 +5905,7 @@
         <v>27</v>
       </c>
       <c r="D105">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E105" t="s">
         <v>28</v>
@@ -5922,7 +5922,7 @@
         <v>27</v>
       </c>
       <c r="D106">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>27</v>
       </c>
       <c r="D107">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E107" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="D108">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5973,7 +5973,7 @@
         <v>27</v>
       </c>
       <c r="D109">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E109" t="s">
         <v>28</v>
@@ -5990,7 +5990,7 @@
         <v>27</v>
       </c>
       <c r="D110">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E110" t="s">
         <v>28</v>
@@ -6007,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="D111">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="D112">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="D113">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E113" t="s">
         <v>28</v>
@@ -6058,7 +6058,7 @@
         <v>27</v>
       </c>
       <c r="D114">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>27</v>
       </c>
       <c r="D115">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -6092,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="D116">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E116" t="s">
         <v>28</v>
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="D117">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E117" t="s">
         <v>28</v>
@@ -6126,7 +6126,7 @@
         <v>27</v>
       </c>
       <c r="D118">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E118" t="s">
         <v>28</v>
@@ -6143,7 +6143,7 @@
         <v>27</v>
       </c>
       <c r="D119">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E119" t="s">
         <v>28</v>
@@ -6160,7 +6160,7 @@
         <v>27</v>
       </c>
       <c r="D120">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E120" t="s">
         <v>28</v>
@@ -6177,7 +6177,7 @@
         <v>27</v>
       </c>
       <c r="D121">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E121" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="D122">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
         <v>28</v>
@@ -6211,7 +6211,7 @@
         <v>27</v>
       </c>
       <c r="D123">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E123" t="s">
         <v>28</v>
@@ -6228,7 +6228,7 @@
         <v>27</v>
       </c>
       <c r="D124">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E124" t="s">
         <v>28</v>
@@ -6245,7 +6245,7 @@
         <v>27</v>
       </c>
       <c r="D125">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
@@ -6262,7 +6262,7 @@
         <v>27</v>
       </c>
       <c r="D126">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -6279,7 +6279,7 @@
         <v>27</v>
       </c>
       <c r="D127">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E127" t="s">
         <v>28</v>
@@ -6296,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="D128">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E128" t="s">
         <v>28</v>
@@ -6313,7 +6313,7 @@
         <v>27</v>
       </c>
       <c r="D129">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
@@ -6347,7 +6347,7 @@
         <v>27</v>
       </c>
       <c r="D131">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E131" t="s">
         <v>28</v>
@@ -6364,7 +6364,7 @@
         <v>27</v>
       </c>
       <c r="D132">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E132" t="s">
         <v>28</v>
@@ -6381,7 +6381,7 @@
         <v>27</v>
       </c>
       <c r="D133">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E133" t="s">
         <v>28</v>
@@ -6398,7 +6398,7 @@
         <v>27</v>
       </c>
       <c r="D134">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E134" t="s">
         <v>28</v>
@@ -6415,7 +6415,7 @@
         <v>27</v>
       </c>
       <c r="D135">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E135" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="D136">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E136" t="s">
         <v>28</v>
@@ -6449,7 +6449,7 @@
         <v>27</v>
       </c>
       <c r="D137">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E137" t="s">
         <v>28</v>
@@ -6466,7 +6466,7 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E138" t="s">
         <v>28</v>
@@ -6483,7 +6483,7 @@
         <v>27</v>
       </c>
       <c r="D139">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E139" t="s">
         <v>28</v>
@@ -6500,7 +6500,7 @@
         <v>27</v>
       </c>
       <c r="D140">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E140" t="s">
         <v>28</v>
@@ -6517,7 +6517,7 @@
         <v>27</v>
       </c>
       <c r="D141">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E141" t="s">
         <v>28</v>
@@ -6551,7 +6551,7 @@
         <v>27</v>
       </c>
       <c r="D143">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E143" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="D145">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E145" t="s">
         <v>28</v>
@@ -6602,7 +6602,7 @@
         <v>27</v>
       </c>
       <c r="D146">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E146" t="s">
         <v>28</v>
@@ -6619,7 +6619,7 @@
         <v>27</v>
       </c>
       <c r="D147">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E147" t="s">
         <v>28</v>
@@ -6636,7 +6636,7 @@
         <v>27</v>
       </c>
       <c r="D148">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E148" t="s">
         <v>28</v>
@@ -6653,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="D149">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6670,7 +6670,7 @@
         <v>27</v>
       </c>
       <c r="D150">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E150" t="s">
         <v>28</v>
@@ -6687,7 +6687,7 @@
         <v>27</v>
       </c>
       <c r="D151">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>27</v>
       </c>
       <c r="D152">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E152" t="s">
         <v>28</v>
@@ -6721,7 +6721,7 @@
         <v>27</v>
       </c>
       <c r="D153">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E153" t="s">
         <v>28</v>
@@ -6738,7 +6738,7 @@
         <v>27</v>
       </c>
       <c r="D154">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E154" t="s">
         <v>28</v>
@@ -6755,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -6772,7 +6772,7 @@
         <v>27</v>
       </c>
       <c r="D156">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E156" t="s">
         <v>28</v>
@@ -6789,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="D157">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E157" t="s">
         <v>28</v>
@@ -6840,7 +6840,7 @@
         <v>27</v>
       </c>
       <c r="D160">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E160" t="s">
         <v>28</v>
@@ -6857,7 +6857,7 @@
         <v>27</v>
       </c>
       <c r="D161">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
@@ -6891,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="D163">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E163" t="s">
         <v>28</v>
@@ -6908,7 +6908,7 @@
         <v>27</v>
       </c>
       <c r="D164">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E164" t="s">
         <v>28</v>
@@ -6925,7 +6925,7 @@
         <v>27</v>
       </c>
       <c r="D165">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E165" t="s">
         <v>28</v>
@@ -6942,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="D166">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E166" t="s">
         <v>28</v>
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="D167">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E167" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="D168">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E168" t="s">
         <v>28</v>
@@ -6993,7 +6993,7 @@
         <v>27</v>
       </c>
       <c r="D169">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E169" t="s">
         <v>28</v>
@@ -7010,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="D170">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E170" t="s">
         <v>28</v>
@@ -7027,7 +7027,7 @@
         <v>27</v>
       </c>
       <c r="D171">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E171" t="s">
         <v>28</v>
@@ -7044,7 +7044,7 @@
         <v>27</v>
       </c>
       <c r="D172">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E172" t="s">
         <v>28</v>
@@ -7061,7 +7061,7 @@
         <v>27</v>
       </c>
       <c r="D173">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E173" t="s">
         <v>28</v>
@@ -7078,7 +7078,7 @@
         <v>27</v>
       </c>
       <c r="D174">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E174" t="s">
         <v>28</v>
@@ -7095,7 +7095,7 @@
         <v>27</v>
       </c>
       <c r="D175">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E175" t="s">
         <v>28</v>
@@ -7112,7 +7112,7 @@
         <v>27</v>
       </c>
       <c r="D176">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E176" t="s">
         <v>28</v>
@@ -7129,7 +7129,7 @@
         <v>27</v>
       </c>
       <c r="D177">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E177" t="s">
         <v>28</v>
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="D178">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E178" t="s">
         <v>28</v>
@@ -7180,7 +7180,7 @@
         <v>27</v>
       </c>
       <c r="D180">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -7197,7 +7197,7 @@
         <v>27</v>
       </c>
       <c r="D181">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E181" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="D182">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E182" t="s">
         <v>28</v>
@@ -7231,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="D183">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
@@ -7248,7 +7248,7 @@
         <v>27</v>
       </c>
       <c r="D184">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E184" t="s">
         <v>28</v>
@@ -7265,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="D185">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E185" t="s">
         <v>28</v>
@@ -7282,7 +7282,7 @@
         <v>27</v>
       </c>
       <c r="D186">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E186" t="s">
         <v>28</v>
@@ -7299,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="D187">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E187" t="s">
         <v>28</v>
@@ -7316,7 +7316,7 @@
         <v>27</v>
       </c>
       <c r="D188">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -7333,7 +7333,7 @@
         <v>27</v>
       </c>
       <c r="D189">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E189" t="s">
         <v>28</v>
@@ -7350,7 +7350,7 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E190" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="D191">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
@@ -7384,7 +7384,7 @@
         <v>27</v>
       </c>
       <c r="D192">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E192" t="s">
         <v>28</v>
@@ -7401,7 +7401,7 @@
         <v>27</v>
       </c>
       <c r="D193">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E193" t="s">
         <v>28</v>
@@ -7418,7 +7418,7 @@
         <v>27</v>
       </c>
       <c r="D194">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E194" t="s">
         <v>28</v>
@@ -7435,7 +7435,7 @@
         <v>27</v>
       </c>
       <c r="D195">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E195" t="s">
         <v>28</v>
@@ -7452,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="D196">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E196" t="s">
         <v>28</v>
@@ -7469,7 +7469,7 @@
         <v>27</v>
       </c>
       <c r="D197">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E197" t="s">
         <v>28</v>
@@ -7486,7 +7486,7 @@
         <v>27</v>
       </c>
       <c r="D198">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E198" t="s">
         <v>28</v>
@@ -7503,7 +7503,7 @@
         <v>27</v>
       </c>
       <c r="D199">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E199" t="s">
         <v>28</v>
@@ -7520,7 +7520,7 @@
         <v>27</v>
       </c>
       <c r="D200">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E200" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>27</v>
       </c>
       <c r="D201">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E201" t="s">
         <v>28</v>
@@ -7554,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="D202">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E202" t="s">
         <v>28</v>
@@ -7571,7 +7571,7 @@
         <v>27</v>
       </c>
       <c r="D203">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="D205">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -7622,7 +7622,7 @@
         <v>27</v>
       </c>
       <c r="D206">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E206" t="s">
         <v>28</v>
@@ -7639,7 +7639,7 @@
         <v>27</v>
       </c>
       <c r="D207">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E207" t="s">
         <v>28</v>
@@ -7656,7 +7656,7 @@
         <v>27</v>
       </c>
       <c r="D208">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E208" t="s">
         <v>28</v>
@@ -7673,7 +7673,7 @@
         <v>27</v>
       </c>
       <c r="D209">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E209" t="s">
         <v>28</v>
@@ -7690,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="D210">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E210" t="s">
         <v>28</v>
@@ -7707,7 +7707,7 @@
         <v>27</v>
       </c>
       <c r="D211">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E211" t="s">
         <v>28</v>
@@ -7724,7 +7724,7 @@
         <v>27</v>
       </c>
       <c r="D212">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E212" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="D214">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E214" t="s">
         <v>28</v>
@@ -7775,7 +7775,7 @@
         <v>27</v>
       </c>
       <c r="D215">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E215" t="s">
         <v>28</v>
@@ -7792,7 +7792,7 @@
         <v>27</v>
       </c>
       <c r="D216">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E216" t="s">
         <v>28</v>
@@ -7809,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="D217">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E217" t="s">
         <v>28</v>
@@ -7826,7 +7826,7 @@
         <v>27</v>
       </c>
       <c r="D218">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E218" t="s">
         <v>28</v>
@@ -7843,7 +7843,7 @@
         <v>27</v>
       </c>
       <c r="D219">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E219" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="D220">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E220" t="s">
         <v>28</v>
@@ -7877,7 +7877,7 @@
         <v>27</v>
       </c>
       <c r="D221">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E221" t="s">
         <v>28</v>
@@ -7894,7 +7894,7 @@
         <v>27</v>
       </c>
       <c r="D222">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E222" t="s">
         <v>28</v>
@@ -7911,7 +7911,7 @@
         <v>27</v>
       </c>
       <c r="D223">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E223" t="s">
         <v>28</v>
@@ -7928,7 +7928,7 @@
         <v>27</v>
       </c>
       <c r="D224">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E224" t="s">
         <v>28</v>
@@ -7945,7 +7945,7 @@
         <v>27</v>
       </c>
       <c r="D225">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E225" t="s">
         <v>28</v>
@@ -7962,7 +7962,7 @@
         <v>27</v>
       </c>
       <c r="D226">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E226" t="s">
         <v>28</v>
@@ -7979,7 +7979,7 @@
         <v>27</v>
       </c>
       <c r="D227">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E227" t="s">
         <v>28</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="D228">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E228" t="s">
         <v>28</v>
@@ -8013,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="D229">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E229" t="s">
         <v>28</v>
@@ -8030,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="D230">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E230" t="s">
         <v>28</v>
@@ -8047,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="D231">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E231" t="s">
         <v>28</v>
@@ -8064,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="D232">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E232" t="s">
         <v>28</v>
@@ -8081,7 +8081,7 @@
         <v>27</v>
       </c>
       <c r="D233">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E233" t="s">
         <v>28</v>
@@ -8098,7 +8098,7 @@
         <v>27</v>
       </c>
       <c r="D234">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E234" t="s">
         <v>28</v>
@@ -8115,7 +8115,7 @@
         <v>27</v>
       </c>
       <c r="D235">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E235" t="s">
         <v>28</v>
@@ -8132,7 +8132,7 @@
         <v>27</v>
       </c>
       <c r="D236">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E236" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="D237">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E237" t="s">
         <v>28</v>
@@ -8183,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="D239">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E239" t="s">
         <v>28</v>
@@ -8200,7 +8200,7 @@
         <v>27</v>
       </c>
       <c r="D240">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E240" t="s">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>27</v>
       </c>
       <c r="D242">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E242" t="s">
         <v>28</v>
@@ -8251,7 +8251,7 @@
         <v>27</v>
       </c>
       <c r="D243">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E243" t="s">
         <v>28</v>
@@ -8268,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="D244">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E244" t="s">
         <v>28</v>
@@ -8285,7 +8285,7 @@
         <v>27</v>
       </c>
       <c r="D245">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E245" t="s">
         <v>28</v>
@@ -8302,7 +8302,7 @@
         <v>27</v>
       </c>
       <c r="D246">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E246" t="s">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="D247">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E247" t="s">
         <v>28</v>
@@ -8336,7 +8336,7 @@
         <v>27</v>
       </c>
       <c r="D248">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E248" t="s">
         <v>28</v>
@@ -8370,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="D250">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E250" t="s">
         <v>28</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="D251">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E251" t="s">
         <v>28</v>
@@ -8404,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="D252">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E252" t="s">
         <v>28</v>
@@ -8421,7 +8421,7 @@
         <v>27</v>
       </c>
       <c r="D253">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E253" t="s">
         <v>28</v>
@@ -8438,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D254">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E254" t="s">
         <v>28</v>
@@ -8455,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="D255">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E255" t="s">
         <v>28</v>
@@ -8472,7 +8472,7 @@
         <v>27</v>
       </c>
       <c r="D256">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E256" t="s">
         <v>28</v>
@@ -8489,7 +8489,7 @@
         <v>27</v>
       </c>
       <c r="D257">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E257" t="s">
         <v>28</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="D258">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E258" t="s">
         <v>28</v>
@@ -8523,7 +8523,7 @@
         <v>27</v>
       </c>
       <c r="D259">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E259" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="D260">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E260" t="s">
         <v>28</v>
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="D261">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E261" t="s">
         <v>28</v>
@@ -8574,7 +8574,7 @@
         <v>27</v>
       </c>
       <c r="D262">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E262" t="s">
         <v>28</v>
@@ -8591,7 +8591,7 @@
         <v>27</v>
       </c>
       <c r="D263">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E263" t="s">
         <v>28</v>
@@ -8608,7 +8608,7 @@
         <v>27</v>
       </c>
       <c r="D264">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E264" t="s">
         <v>28</v>
@@ -8625,7 +8625,7 @@
         <v>27</v>
       </c>
       <c r="D265">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E265" t="s">
         <v>28</v>
@@ -8642,7 +8642,7 @@
         <v>27</v>
       </c>
       <c r="D266">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E266" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="D267">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E267" t="s">
         <v>28</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="D268">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E268" t="s">
         <v>28</v>
@@ -8693,7 +8693,7 @@
         <v>27</v>
       </c>
       <c r="D269">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E269" t="s">
         <v>28</v>
@@ -8710,7 +8710,7 @@
         <v>27</v>
       </c>
       <c r="D270">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E270" t="s">
         <v>28</v>
@@ -8727,7 +8727,7 @@
         <v>27</v>
       </c>
       <c r="D271">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E271" t="s">
         <v>28</v>
@@ -8744,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="D272">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E272" t="s">
         <v>28</v>
@@ -8761,7 +8761,7 @@
         <v>27</v>
       </c>
       <c r="D273">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E273" t="s">
         <v>28</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="D274">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E274" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>27</v>
       </c>
       <c r="D275">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E275" t="s">
         <v>28</v>
@@ -8829,7 +8829,7 @@
         <v>27</v>
       </c>
       <c r="D277">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E277" t="s">
         <v>28</v>
@@ -8846,7 +8846,7 @@
         <v>27</v>
       </c>
       <c r="D278">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E278" t="s">
         <v>28</v>
@@ -8863,7 +8863,7 @@
         <v>27</v>
       </c>
       <c r="D279">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E279" t="s">
         <v>28</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E280" t="s">
         <v>28</v>
@@ -8897,7 +8897,7 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E281" t="s">
         <v>28</v>
@@ -8914,7 +8914,7 @@
         <v>27</v>
       </c>
       <c r="D282">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E282" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="D283">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E283" t="s">
         <v>28</v>
@@ -8948,7 +8948,7 @@
         <v>27</v>
       </c>
       <c r="D284">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E284" t="s">
         <v>28</v>
@@ -8965,7 +8965,7 @@
         <v>27</v>
       </c>
       <c r="D285">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E285" t="s">
         <v>28</v>
@@ -8982,7 +8982,7 @@
         <v>27</v>
       </c>
       <c r="D286">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E286" t="s">
         <v>28</v>
@@ -8999,7 +8999,7 @@
         <v>27</v>
       </c>
       <c r="D287">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E287" t="s">
         <v>28</v>
@@ -9016,7 +9016,7 @@
         <v>27</v>
       </c>
       <c r="D288">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E288" t="s">
         <v>28</v>
@@ -9033,7 +9033,7 @@
         <v>27</v>
       </c>
       <c r="D289">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E289" t="s">
         <v>28</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="D290">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E290" t="s">
         <v>28</v>
@@ -9067,7 +9067,7 @@
         <v>27</v>
       </c>
       <c r="D291">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E291" t="s">
         <v>28</v>
@@ -9084,7 +9084,7 @@
         <v>27</v>
       </c>
       <c r="D292">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E292" t="s">
         <v>28</v>
@@ -9101,7 +9101,7 @@
         <v>27</v>
       </c>
       <c r="D293">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E293" t="s">
         <v>28</v>
@@ -9118,7 +9118,7 @@
         <v>27</v>
       </c>
       <c r="D294">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E294" t="s">
         <v>28</v>
@@ -9135,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="D295">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E295" t="s">
         <v>28</v>
@@ -9152,7 +9152,7 @@
         <v>27</v>
       </c>
       <c r="D296">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E296" t="s">
         <v>28</v>
@@ -9169,7 +9169,7 @@
         <v>27</v>
       </c>
       <c r="D297">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E297" t="s">
         <v>28</v>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="D298">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E298" t="s">
         <v>28</v>
@@ -9203,7 +9203,7 @@
         <v>27</v>
       </c>
       <c r="D299">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E299" t="s">
         <v>28</v>
@@ -9220,7 +9220,7 @@
         <v>27</v>
       </c>
       <c r="D300">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E300" t="s">
         <v>28</v>
@@ -9237,7 +9237,7 @@
         <v>27</v>
       </c>
       <c r="D301">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E301" t="s">
         <v>28</v>
@@ -9254,7 +9254,7 @@
         <v>27</v>
       </c>
       <c r="D302">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E302" t="s">
         <v>28</v>
@@ -9271,7 +9271,7 @@
         <v>27</v>
       </c>
       <c r="D303">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E303" t="s">
         <v>28</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="D304">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E304" t="s">
         <v>28</v>
@@ -9305,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="D305">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E305" t="s">
         <v>28</v>
@@ -9339,7 +9339,7 @@
         <v>27</v>
       </c>
       <c r="D307">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E307" t="s">
         <v>28</v>
@@ -9356,7 +9356,7 @@
         <v>27</v>
       </c>
       <c r="D308">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E308" t="s">
         <v>28</v>
@@ -9373,7 +9373,7 @@
         <v>27</v>
       </c>
       <c r="D309">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E309" t="s">
         <v>28</v>
@@ -9390,7 +9390,7 @@
         <v>27</v>
       </c>
       <c r="D310">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E310" t="s">
         <v>28</v>
@@ -9407,7 +9407,7 @@
         <v>27</v>
       </c>
       <c r="D311">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E311" t="s">
         <v>28</v>
@@ -9424,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="D312">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E312" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="D313">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E313" t="s">
         <v>28</v>
@@ -9458,7 +9458,7 @@
         <v>27</v>
       </c>
       <c r="D314">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E314" t="s">
         <v>28</v>
@@ -9475,7 +9475,7 @@
         <v>27</v>
       </c>
       <c r="D315">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E315" t="s">
         <v>28</v>
@@ -9492,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="D316">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E316" t="s">
         <v>28</v>
@@ -9509,7 +9509,7 @@
         <v>27</v>
       </c>
       <c r="D317">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E317" t="s">
         <v>28</v>
@@ -9526,7 +9526,7 @@
         <v>27</v>
       </c>
       <c r="D318">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E318" t="s">
         <v>28</v>
@@ -9543,7 +9543,7 @@
         <v>27</v>
       </c>
       <c r="D319">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E319" t="s">
         <v>28</v>
@@ -9560,7 +9560,7 @@
         <v>27</v>
       </c>
       <c r="D320">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E320" t="s">
         <v>28</v>
@@ -9577,7 +9577,7 @@
         <v>27</v>
       </c>
       <c r="D321">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E321" t="s">
         <v>28</v>
@@ -9594,7 +9594,7 @@
         <v>27</v>
       </c>
       <c r="D322">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E322" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
         <v>27</v>
       </c>
       <c r="D323">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E323" t="s">
         <v>28</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="D324">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E324" t="s">
         <v>28</v>
@@ -9645,7 +9645,7 @@
         <v>27</v>
       </c>
       <c r="D325">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E325" t="s">
         <v>28</v>
@@ -9662,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="D326">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E326" t="s">
         <v>28</v>
@@ -9679,7 +9679,7 @@
         <v>27</v>
       </c>
       <c r="D327">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E327" t="s">
         <v>28</v>
@@ -9696,7 +9696,7 @@
         <v>27</v>
       </c>
       <c r="D328">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E328" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="D329">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E329" t="s">
         <v>28</v>
@@ -9730,7 +9730,7 @@
         <v>27</v>
       </c>
       <c r="D330">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E330" t="s">
         <v>28</v>
@@ -9747,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="D331">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E331" t="s">
         <v>28</v>
@@ -9764,7 +9764,7 @@
         <v>27</v>
       </c>
       <c r="D332">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E332" t="s">
         <v>28</v>
@@ -9781,7 +9781,7 @@
         <v>27</v>
       </c>
       <c r="D333">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E333" t="s">
         <v>28</v>
@@ -9798,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="D334">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E334" t="s">
         <v>28</v>
@@ -9815,7 +9815,7 @@
         <v>27</v>
       </c>
       <c r="D335">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E335" t="s">
         <v>28</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="D336">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E336" t="s">
         <v>28</v>
@@ -9849,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="D337">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E337" t="s">
         <v>28</v>
@@ -9866,7 +9866,7 @@
         <v>27</v>
       </c>
       <c r="D338">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E338" t="s">
         <v>28</v>
@@ -9883,7 +9883,7 @@
         <v>27</v>
       </c>
       <c r="D339">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E339" t="s">
         <v>28</v>
@@ -9900,7 +9900,7 @@
         <v>27</v>
       </c>
       <c r="D340">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E340" t="s">
         <v>28</v>
@@ -9917,7 +9917,7 @@
         <v>27</v>
       </c>
       <c r="D341">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E341" t="s">
         <v>28</v>
@@ -9934,7 +9934,7 @@
         <v>27</v>
       </c>
       <c r="D342">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E342" t="s">
         <v>28</v>
@@ -9951,7 +9951,7 @@
         <v>27</v>
       </c>
       <c r="D343">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E343" t="s">
         <v>28</v>
@@ -9968,7 +9968,7 @@
         <v>27</v>
       </c>
       <c r="D344">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E344" t="s">
         <v>28</v>
@@ -9985,7 +9985,7 @@
         <v>27</v>
       </c>
       <c r="D345">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E345" t="s">
         <v>28</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D346">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E346" t="s">
         <v>28</v>
@@ -10019,7 +10019,7 @@
         <v>27</v>
       </c>
       <c r="D347">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E347" t="s">
         <v>28</v>
@@ -10036,7 +10036,7 @@
         <v>27</v>
       </c>
       <c r="D348">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E348" t="s">
         <v>28</v>
@@ -10053,7 +10053,7 @@
         <v>27</v>
       </c>
       <c r="D349">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E349" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="D350">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E350" t="s">
         <v>28</v>
@@ -10087,7 +10087,7 @@
         <v>27</v>
       </c>
       <c r="D351">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E351" t="s">
         <v>28</v>
@@ -10104,7 +10104,7 @@
         <v>27</v>
       </c>
       <c r="D352">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E352" t="s">
         <v>28</v>
@@ -10121,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D353">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E353" t="s">
         <v>28</v>
@@ -10138,7 +10138,7 @@
         <v>27</v>
       </c>
       <c r="D354">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E354" t="s">
         <v>28</v>
@@ -10155,7 +10155,7 @@
         <v>27</v>
       </c>
       <c r="D355">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E355" t="s">
         <v>28</v>
@@ -10172,7 +10172,7 @@
         <v>27</v>
       </c>
       <c r="D356">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E356" t="s">
         <v>28</v>
@@ -10189,7 +10189,7 @@
         <v>27</v>
       </c>
       <c r="D357">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E357" t="s">
         <v>28</v>
@@ -10206,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="D358">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E358" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="D359">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E359" t="s">
         <v>28</v>
@@ -10240,7 +10240,7 @@
         <v>27</v>
       </c>
       <c r="D360">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E360" t="s">
         <v>28</v>
@@ -10257,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="D361">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E361" t="s">
         <v>28</v>
@@ -10274,7 +10274,7 @@
         <v>27</v>
       </c>
       <c r="D362">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E362" t="s">
         <v>28</v>
@@ -10291,7 +10291,7 @@
         <v>27</v>
       </c>
       <c r="D363">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E363" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="D364">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E364" t="s">
         <v>28</v>
@@ -10325,7 +10325,7 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E365" t="s">
         <v>28</v>
@@ -10342,7 +10342,7 @@
         <v>27</v>
       </c>
       <c r="D366">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E366" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
         <v>27</v>
       </c>
       <c r="D367">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E367" t="s">
         <v>28</v>
@@ -10376,7 +10376,7 @@
         <v>27</v>
       </c>
       <c r="D368">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E368" t="s">
         <v>28</v>
@@ -10393,7 +10393,7 @@
         <v>27</v>
       </c>
       <c r="D369">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E369" t="s">
         <v>28</v>
@@ -10410,7 +10410,7 @@
         <v>27</v>
       </c>
       <c r="D370">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E370" t="s">
         <v>28</v>
@@ -10427,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="D371">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E371" t="s">
         <v>28</v>
@@ -10461,7 +10461,7 @@
         <v>27</v>
       </c>
       <c r="D373">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E373" t="s">
         <v>28</v>
@@ -10478,7 +10478,7 @@
         <v>27</v>
       </c>
       <c r="D374">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E374" t="s">
         <v>28</v>
@@ -10495,7 +10495,7 @@
         <v>27</v>
       </c>
       <c r="D375">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E375" t="s">
         <v>28</v>
@@ -10512,7 +10512,7 @@
         <v>27</v>
       </c>
       <c r="D376">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E376" t="s">
         <v>28</v>
@@ -10529,7 +10529,7 @@
         <v>27</v>
       </c>
       <c r="D377">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E377" t="s">
         <v>28</v>
@@ -10546,7 +10546,7 @@
         <v>27</v>
       </c>
       <c r="D378">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E378" t="s">
         <v>28</v>
@@ -10563,7 +10563,7 @@
         <v>27</v>
       </c>
       <c r="D379">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E379" t="s">
         <v>28</v>
@@ -10580,7 +10580,7 @@
         <v>27</v>
       </c>
       <c r="D380">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E380" t="s">
         <v>28</v>
@@ -10597,7 +10597,7 @@
         <v>27</v>
       </c>
       <c r="D381">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E381" t="s">
         <v>28</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="D382">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E382" t="s">
         <v>28</v>
@@ -10648,7 +10648,7 @@
         <v>27</v>
       </c>
       <c r="D384">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E384" t="s">
         <v>28</v>
@@ -10665,7 +10665,7 @@
         <v>27</v>
       </c>
       <c r="D385">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E385" t="s">
         <v>28</v>
@@ -10682,7 +10682,7 @@
         <v>27</v>
       </c>
       <c r="D386">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E386" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="D387">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E387" t="s">
         <v>28</v>
@@ -10716,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="D388">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E388" t="s">
         <v>28</v>
@@ -10733,7 +10733,7 @@
         <v>27</v>
       </c>
       <c r="D389">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E389" t="s">
         <v>28</v>
@@ -10750,7 +10750,7 @@
         <v>27</v>
       </c>
       <c r="D390">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E390" t="s">
         <v>28</v>
@@ -10767,7 +10767,7 @@
         <v>27</v>
       </c>
       <c r="D391">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E391" t="s">
         <v>28</v>
@@ -10784,7 +10784,7 @@
         <v>27</v>
       </c>
       <c r="D392">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E392" t="s">
         <v>28</v>
@@ -10801,7 +10801,7 @@
         <v>27</v>
       </c>
       <c r="D393">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E393" t="s">
         <v>28</v>
@@ -10818,7 +10818,7 @@
         <v>27</v>
       </c>
       <c r="D394">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E394" t="s">
         <v>28</v>
@@ -10835,7 +10835,7 @@
         <v>27</v>
       </c>
       <c r="D395">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E395" t="s">
         <v>28</v>
@@ -10852,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="D396">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E396" t="s">
         <v>28</v>
@@ -10869,7 +10869,7 @@
         <v>27</v>
       </c>
       <c r="D397">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E397" t="s">
         <v>28</v>
@@ -10886,7 +10886,7 @@
         <v>27</v>
       </c>
       <c r="D398">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E398" t="s">
         <v>28</v>
@@ -10903,7 +10903,7 @@
         <v>27</v>
       </c>
       <c r="D399">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E399" t="s">
         <v>28</v>
@@ -10920,7 +10920,7 @@
         <v>27</v>
       </c>
       <c r="D400">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E400" t="s">
         <v>28</v>
@@ -10937,7 +10937,7 @@
         <v>27</v>
       </c>
       <c r="D401">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E401" t="s">
         <v>28</v>
@@ -10954,7 +10954,7 @@
         <v>27</v>
       </c>
       <c r="D402">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E402" t="s">
         <v>28</v>
@@ -10971,7 +10971,7 @@
         <v>27</v>
       </c>
       <c r="D403">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E403" t="s">
         <v>28</v>
@@ -10988,7 +10988,7 @@
         <v>27</v>
       </c>
       <c r="D404">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E404" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="D405">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E405" t="s">
         <v>28</v>
@@ -11022,7 +11022,7 @@
         <v>27</v>
       </c>
       <c r="D406">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E406" t="s">
         <v>28</v>
@@ -11039,7 +11039,7 @@
         <v>27</v>
       </c>
       <c r="D407">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E407" t="s">
         <v>28</v>
@@ -11056,7 +11056,7 @@
         <v>27</v>
       </c>
       <c r="D408">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E408" t="s">
         <v>28</v>
@@ -11073,7 +11073,7 @@
         <v>27</v>
       </c>
       <c r="D409">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E409" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="D410">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E410" t="s">
         <v>28</v>
@@ -11107,7 +11107,7 @@
         <v>27</v>
       </c>
       <c r="D411">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E411" t="s">
         <v>28</v>
@@ -11124,7 +11124,7 @@
         <v>27</v>
       </c>
       <c r="D412">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E412" t="s">
         <v>28</v>
@@ -11141,7 +11141,7 @@
         <v>27</v>
       </c>
       <c r="D413">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E413" t="s">
         <v>28</v>
@@ -11158,7 +11158,7 @@
         <v>27</v>
       </c>
       <c r="D414">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E414" t="s">
         <v>28</v>
@@ -11175,7 +11175,7 @@
         <v>27</v>
       </c>
       <c r="D415">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E415" t="s">
         <v>28</v>
@@ -11192,7 +11192,7 @@
         <v>27</v>
       </c>
       <c r="D416">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E416" t="s">
         <v>28</v>
@@ -11209,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="D417">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E417" t="s">
         <v>28</v>
@@ -11226,7 +11226,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E418" t="s">
         <v>28</v>
@@ -11243,7 +11243,7 @@
         <v>27</v>
       </c>
       <c r="D419">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E419" t="s">
         <v>28</v>
@@ -11260,7 +11260,7 @@
         <v>27</v>
       </c>
       <c r="D420">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E420" t="s">
         <v>28</v>
@@ -11311,7 +11311,7 @@
         <v>27</v>
       </c>
       <c r="D423">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E423" t="s">
         <v>28</v>
@@ -11328,7 +11328,7 @@
         <v>27</v>
       </c>
       <c r="D424">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E424" t="s">
         <v>28</v>
@@ -11345,7 +11345,7 @@
         <v>27</v>
       </c>
       <c r="D425">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E425" t="s">
         <v>28</v>
@@ -11362,7 +11362,7 @@
         <v>27</v>
       </c>
       <c r="D426">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E426" t="s">
         <v>28</v>
@@ -11379,7 +11379,7 @@
         <v>27</v>
       </c>
       <c r="D427">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E427" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="D428">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E428" t="s">
         <v>28</v>
@@ -11413,7 +11413,7 @@
         <v>27</v>
       </c>
       <c r="D429">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E429" t="s">
         <v>28</v>
@@ -11430,7 +11430,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E430" t="s">
         <v>28</v>
@@ -11447,7 +11447,7 @@
         <v>27</v>
       </c>
       <c r="D431">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E431" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="D433">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E433" t="s">
         <v>28</v>
@@ -11498,7 +11498,7 @@
         <v>27</v>
       </c>
       <c r="D434">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E434" t="s">
         <v>28</v>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="D435">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E435" t="s">
         <v>28</v>
@@ -11532,7 +11532,7 @@
         <v>27</v>
       </c>
       <c r="D436">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E436" t="s">
         <v>28</v>
@@ -11549,7 +11549,7 @@
         <v>27</v>
       </c>
       <c r="D437">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E437" t="s">
         <v>28</v>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
       <c r="D438">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E438" t="s">
         <v>28</v>
@@ -11583,7 +11583,7 @@
         <v>27</v>
       </c>
       <c r="D439">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E439" t="s">
         <v>28</v>
@@ -11600,7 +11600,7 @@
         <v>27</v>
       </c>
       <c r="D440">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E440" t="s">
         <v>28</v>
@@ -11617,7 +11617,7 @@
         <v>27</v>
       </c>
       <c r="D441">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E441" t="s">
         <v>28</v>
@@ -11634,7 +11634,7 @@
         <v>27</v>
       </c>
       <c r="D442">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E442" t="s">
         <v>28</v>
@@ -11651,7 +11651,7 @@
         <v>27</v>
       </c>
       <c r="D443">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E443" t="s">
         <v>28</v>
@@ -11668,7 +11668,7 @@
         <v>27</v>
       </c>
       <c r="D444">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E444" t="s">
         <v>28</v>
@@ -11685,7 +11685,7 @@
         <v>27</v>
       </c>
       <c r="D445">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E445" t="s">
         <v>28</v>
@@ -11702,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D446">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E446" t="s">
         <v>28</v>
@@ -11719,7 +11719,7 @@
         <v>27</v>
       </c>
       <c r="D447">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E447" t="s">
         <v>28</v>
@@ -11736,7 +11736,7 @@
         <v>27</v>
       </c>
       <c r="D448">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E448" t="s">
         <v>28</v>
@@ -11753,7 +11753,7 @@
         <v>27</v>
       </c>
       <c r="D449">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E449" t="s">
         <v>28</v>
@@ -11770,7 +11770,7 @@
         <v>27</v>
       </c>
       <c r="D450">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E450" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="D451">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E451" t="s">
         <v>28</v>
@@ -11804,7 +11804,7 @@
         <v>27</v>
       </c>
       <c r="D452">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E452" t="s">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>27</v>
       </c>
       <c r="D453">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E453" t="s">
         <v>28</v>
@@ -11838,7 +11838,7 @@
         <v>27</v>
       </c>
       <c r="D454">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E454" t="s">
         <v>28</v>
@@ -11855,7 +11855,7 @@
         <v>27</v>
       </c>
       <c r="D455">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E455" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="D456">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E456" t="s">
         <v>28</v>
@@ -11889,7 +11889,7 @@
         <v>27</v>
       </c>
       <c r="D457">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E457" t="s">
         <v>28</v>
@@ -11906,7 +11906,7 @@
         <v>27</v>
       </c>
       <c r="D458">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E458" t="s">
         <v>28</v>
@@ -11923,7 +11923,7 @@
         <v>27</v>
       </c>
       <c r="D459">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E459" t="s">
         <v>28</v>
@@ -11940,7 +11940,7 @@
         <v>27</v>
       </c>
       <c r="D460">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E460" t="s">
         <v>28</v>
@@ -11957,7 +11957,7 @@
         <v>27</v>
       </c>
       <c r="D461">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E461" t="s">
         <v>28</v>
@@ -11974,7 +11974,7 @@
         <v>27</v>
       </c>
       <c r="D462">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E462" t="s">
         <v>28</v>
@@ -11991,7 +11991,7 @@
         <v>27</v>
       </c>
       <c r="D463">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E463" t="s">
         <v>28</v>
@@ -12008,7 +12008,7 @@
         <v>27</v>
       </c>
       <c r="D464">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E464" t="s">
         <v>28</v>
@@ -12025,7 +12025,7 @@
         <v>27</v>
       </c>
       <c r="D465">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E465" t="s">
         <v>28</v>
@@ -12042,7 +12042,7 @@
         <v>27</v>
       </c>
       <c r="D466">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E466" t="s">
         <v>28</v>
@@ -12059,7 +12059,7 @@
         <v>27</v>
       </c>
       <c r="D467">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E467" t="s">
         <v>28</v>
@@ -12076,7 +12076,7 @@
         <v>27</v>
       </c>
       <c r="D468">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E468" t="s">
         <v>28</v>
@@ -12093,7 +12093,7 @@
         <v>27</v>
       </c>
       <c r="D469">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E469" t="s">
         <v>28</v>
@@ -12110,7 +12110,7 @@
         <v>27</v>
       </c>
       <c r="D470">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E470" t="s">
         <v>28</v>
@@ -12127,7 +12127,7 @@
         <v>27</v>
       </c>
       <c r="D471">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E471" t="s">
         <v>28</v>
@@ -12144,7 +12144,7 @@
         <v>27</v>
       </c>
       <c r="D472">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E472" t="s">
         <v>28</v>
@@ -12161,7 +12161,7 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E473" t="s">
         <v>28</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="D474">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E474" t="s">
         <v>28</v>
@@ -12195,7 +12195,7 @@
         <v>27</v>
       </c>
       <c r="D475">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E475" t="s">
         <v>28</v>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
       <c r="D477">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E477" t="s">
         <v>28</v>
@@ -12246,7 +12246,7 @@
         <v>27</v>
       </c>
       <c r="D478">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E478" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="D479">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E479" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="D480">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E480" t="s">
         <v>28</v>
@@ -12297,7 +12297,7 @@
         <v>27</v>
       </c>
       <c r="D481">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E481" t="s">
         <v>28</v>
@@ -12314,7 +12314,7 @@
         <v>27</v>
       </c>
       <c r="D482">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E482" t="s">
         <v>28</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="D483">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E483" t="s">
         <v>28</v>
@@ -12348,7 +12348,7 @@
         <v>27</v>
       </c>
       <c r="D484">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E484" t="s">
         <v>28</v>
@@ -12365,7 +12365,7 @@
         <v>27</v>
       </c>
       <c r="D485">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E485" t="s">
         <v>28</v>
@@ -12382,7 +12382,7 @@
         <v>27</v>
       </c>
       <c r="D486">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E486" t="s">
         <v>28</v>
@@ -12399,7 +12399,7 @@
         <v>27</v>
       </c>
       <c r="D487">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E487" t="s">
         <v>28</v>
@@ -12416,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="D488">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E488" t="s">
         <v>28</v>
@@ -12433,7 +12433,7 @@
         <v>27</v>
       </c>
       <c r="D489">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E489" t="s">
         <v>28</v>
@@ -12450,7 +12450,7 @@
         <v>27</v>
       </c>
       <c r="D490">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E490" t="s">
         <v>28</v>
@@ -12467,7 +12467,7 @@
         <v>27</v>
       </c>
       <c r="D491">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E491" t="s">
         <v>28</v>
@@ -12484,7 +12484,7 @@
         <v>27</v>
       </c>
       <c r="D492">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E492" t="s">
         <v>28</v>
@@ -12501,7 +12501,7 @@
         <v>27</v>
       </c>
       <c r="D493">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E493" t="s">
         <v>28</v>
@@ -12518,7 +12518,7 @@
         <v>27</v>
       </c>
       <c r="D494">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E494" t="s">
         <v>28</v>
@@ -12535,7 +12535,7 @@
         <v>27</v>
       </c>
       <c r="D495">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E495" t="s">
         <v>28</v>
@@ -12552,7 +12552,7 @@
         <v>27</v>
       </c>
       <c r="D496">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E496" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="D497">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E497" t="s">
         <v>28</v>
@@ -12586,7 +12586,7 @@
         <v>27</v>
       </c>
       <c r="D498">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E498" t="s">
         <v>28</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D499">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E499" t="s">
         <v>28</v>
@@ -12620,7 +12620,7 @@
         <v>27</v>
       </c>
       <c r="D500">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E500" t="s">
         <v>28</v>
@@ -12637,7 +12637,7 @@
         <v>27</v>
       </c>
       <c r="D501">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E501" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="D502">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E502" t="s">
         <v>28</v>
@@ -12671,7 +12671,7 @@
         <v>27</v>
       </c>
       <c r="D503">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E503" t="s">
         <v>28</v>
@@ -12688,7 +12688,7 @@
         <v>27</v>
       </c>
       <c r="D504">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E504" t="s">
         <v>28</v>
@@ -12705,7 +12705,7 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E505" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="D506">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E506" t="s">
         <v>28</v>
@@ -12739,7 +12739,7 @@
         <v>27</v>
       </c>
       <c r="D507">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E507" t="s">
         <v>28</v>
@@ -12756,7 +12756,7 @@
         <v>27</v>
       </c>
       <c r="D508">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E508" t="s">
         <v>28</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="D509">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E509" t="s">
         <v>28</v>
@@ -12790,7 +12790,7 @@
         <v>27</v>
       </c>
       <c r="D510">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E510" t="s">
         <v>28</v>
@@ -12807,7 +12807,7 @@
         <v>27</v>
       </c>
       <c r="D511">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E511" t="s">
         <v>28</v>
@@ -12824,7 +12824,7 @@
         <v>27</v>
       </c>
       <c r="D512">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E512" t="s">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27</v>
       </c>
       <c r="D513">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E513" t="s">
         <v>28</v>
@@ -12858,7 +12858,7 @@
         <v>27</v>
       </c>
       <c r="D514">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E514" t="s">
         <v>28</v>
@@ -12875,7 +12875,7 @@
         <v>27</v>
       </c>
       <c r="D515">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E515" t="s">
         <v>28</v>
@@ -12892,7 +12892,7 @@
         <v>27</v>
       </c>
       <c r="D516">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E516" t="s">
         <v>28</v>
@@ -12909,7 +12909,7 @@
         <v>27</v>
       </c>
       <c r="D517">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E517" t="s">
         <v>28</v>
@@ -12926,7 +12926,7 @@
         <v>27</v>
       </c>
       <c r="D518">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E518" t="s">
         <v>28</v>
@@ -12943,7 +12943,7 @@
         <v>27</v>
       </c>
       <c r="D519">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E519" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="D520">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E520" t="s">
         <v>28</v>
@@ -12977,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="D521">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E521" t="s">
         <v>28</v>
@@ -12994,7 +12994,7 @@
         <v>27</v>
       </c>
       <c r="D522">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E522" t="s">
         <v>28</v>
@@ -13011,7 +13011,7 @@
         <v>27</v>
       </c>
       <c r="D523">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E523" t="s">
         <v>28</v>
@@ -13028,7 +13028,7 @@
         <v>27</v>
       </c>
       <c r="D524">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E524" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="D525">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E525" t="s">
         <v>28</v>
@@ -13062,7 +13062,7 @@
         <v>27</v>
       </c>
       <c r="D526">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E526" t="s">
         <v>28</v>
@@ -13079,7 +13079,7 @@
         <v>27</v>
       </c>
       <c r="D527">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E527" t="s">
         <v>28</v>
@@ -13096,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="D528">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E528" t="s">
         <v>28</v>
@@ -13113,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="D529">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
@@ -13130,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -13147,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="D531">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
@@ -13164,7 +13164,7 @@
         <v>27</v>
       </c>
       <c r="D532">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E532" t="s">
         <v>28</v>
@@ -13181,7 +13181,7 @@
         <v>27</v>
       </c>
       <c r="D533">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E533" t="s">
         <v>28</v>
@@ -13198,7 +13198,7 @@
         <v>27</v>
       </c>
       <c r="D534">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E534" t="s">
         <v>28</v>
@@ -13215,7 +13215,7 @@
         <v>27</v>
       </c>
       <c r="D535">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E535" t="s">
         <v>28</v>
@@ -13232,7 +13232,7 @@
         <v>27</v>
       </c>
       <c r="D536">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E536" t="s">
         <v>28</v>
@@ -13249,7 +13249,7 @@
         <v>27</v>
       </c>
       <c r="D537">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E537" t="s">
         <v>28</v>
@@ -13283,7 +13283,7 @@
         <v>27</v>
       </c>
       <c r="D539">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E539" t="s">
         <v>28</v>
@@ -13300,7 +13300,7 @@
         <v>27</v>
       </c>
       <c r="D540">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E540" t="s">
         <v>28</v>
@@ -13317,7 +13317,7 @@
         <v>27</v>
       </c>
       <c r="D541">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E541" t="s">
         <v>28</v>
@@ -13334,7 +13334,7 @@
         <v>27</v>
       </c>
       <c r="D542">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E542" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="D543">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E543" t="s">
         <v>28</v>
@@ -13368,7 +13368,7 @@
         <v>27</v>
       </c>
       <c r="D544">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E544" t="s">
         <v>28</v>
@@ -13385,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="D545">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
@@ -13402,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="D546">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
@@ -13419,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="D547">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E547" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="D548">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E548" t="s">
         <v>28</v>
@@ -13453,7 +13453,7 @@
         <v>27</v>
       </c>
       <c r="D549">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E549" t="s">
         <v>28</v>
@@ -13470,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="D550">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E550" t="s">
         <v>28</v>
@@ -13487,7 +13487,7 @@
         <v>27</v>
       </c>
       <c r="D551">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E551" t="s">
         <v>28</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="D552">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -13521,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="D553">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E553" t="s">
         <v>28</v>
@@ -13538,7 +13538,7 @@
         <v>27</v>
       </c>
       <c r="D554">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E554" t="s">
         <v>28</v>
@@ -13555,7 +13555,7 @@
         <v>27</v>
       </c>
       <c r="D555">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E555" t="s">
         <v>28</v>
@@ -13572,7 +13572,7 @@
         <v>27</v>
       </c>
       <c r="D556">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E556" t="s">
         <v>28</v>
@@ -13589,7 +13589,7 @@
         <v>27</v>
       </c>
       <c r="D557">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E557" t="s">
         <v>28</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="D558">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E558" t="s">
         <v>28</v>
@@ -13623,7 +13623,7 @@
         <v>27</v>
       </c>
       <c r="D559">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -13640,7 +13640,7 @@
         <v>27</v>
       </c>
       <c r="D560">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
@@ -13657,7 +13657,7 @@
         <v>27</v>
       </c>
       <c r="D561">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E561" t="s">
         <v>28</v>
@@ -13674,7 +13674,7 @@
         <v>27</v>
       </c>
       <c r="D562">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E562" t="s">
         <v>28</v>
@@ -13691,7 +13691,7 @@
         <v>27</v>
       </c>
       <c r="D563">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E563" t="s">
         <v>28</v>
@@ -13708,7 +13708,7 @@
         <v>27</v>
       </c>
       <c r="D564">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E564" t="s">
         <v>28</v>
@@ -13725,7 +13725,7 @@
         <v>27</v>
       </c>
       <c r="D565">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E565" t="s">
         <v>28</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="D566">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E566" t="s">
         <v>28</v>
@@ -13759,7 +13759,7 @@
         <v>27</v>
       </c>
       <c r="D567">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E567" t="s">
         <v>28</v>
@@ -13776,7 +13776,7 @@
         <v>27</v>
       </c>
       <c r="D568">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E568" t="s">
         <v>28</v>
@@ -13793,7 +13793,7 @@
         <v>27</v>
       </c>
       <c r="D569">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="D571">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E571" t="s">
         <v>28</v>
@@ -13844,7 +13844,7 @@
         <v>27</v>
       </c>
       <c r="D572">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E572" t="s">
         <v>28</v>
@@ -13861,7 +13861,7 @@
         <v>27</v>
       </c>
       <c r="D573">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E573" t="s">
         <v>28</v>
@@ -13878,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="D574">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E574" t="s">
         <v>28</v>
@@ -13895,7 +13895,7 @@
         <v>27</v>
       </c>
       <c r="D575">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E575" t="s">
         <v>28</v>
@@ -13912,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="D576">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E576" t="s">
         <v>28</v>
@@ -13929,7 +13929,7 @@
         <v>27</v>
       </c>
       <c r="D577">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E577" t="s">
         <v>28</v>
@@ -13946,7 +13946,7 @@
         <v>27</v>
       </c>
       <c r="D578">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E578" t="s">
         <v>28</v>
@@ -13963,7 +13963,7 @@
         <v>27</v>
       </c>
       <c r="D579">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E579" t="s">
         <v>28</v>
@@ -13980,7 +13980,7 @@
         <v>27</v>
       </c>
       <c r="D580">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E580" t="s">
         <v>28</v>
@@ -13997,7 +13997,7 @@
         <v>27</v>
       </c>
       <c r="D581">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E581" t="s">
         <v>28</v>
@@ -14014,7 +14014,7 @@
         <v>27</v>
       </c>
       <c r="D582">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E582" t="s">
         <v>28</v>
@@ -14031,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="D583">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E583" t="s">
         <v>28</v>
@@ -14048,7 +14048,7 @@
         <v>27</v>
       </c>
       <c r="D584">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E584" t="s">
         <v>28</v>
@@ -14082,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="D586">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E586" t="s">
         <v>28</v>
@@ -14099,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="D587">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E587" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="D589">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
@@ -14150,7 +14150,7 @@
         <v>27</v>
       </c>
       <c r="D590">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
@@ -14167,7 +14167,7 @@
         <v>27</v>
       </c>
       <c r="D591">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E591" t="s">
         <v>28</v>
@@ -14201,7 +14201,7 @@
         <v>27</v>
       </c>
       <c r="D593">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E593" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="D594">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E594" t="s">
         <v>28</v>
@@ -14235,7 +14235,7 @@
         <v>27</v>
       </c>
       <c r="D595">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E595" t="s">
         <v>28</v>
@@ -14252,7 +14252,7 @@
         <v>27</v>
       </c>
       <c r="D596">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
@@ -14269,7 +14269,7 @@
         <v>27</v>
       </c>
       <c r="D597">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
@@ -14286,7 +14286,7 @@
         <v>27</v>
       </c>
       <c r="D598">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
@@ -14303,7 +14303,7 @@
         <v>27</v>
       </c>
       <c r="D599">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="D600">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
@@ -14337,7 +14337,7 @@
         <v>27</v>
       </c>
       <c r="D601">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
@@ -14354,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="D602">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
@@ -14371,7 +14371,7 @@
         <v>27</v>
       </c>
       <c r="D603">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
@@ -14388,7 +14388,7 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
@@ -14405,7 +14405,7 @@
         <v>27</v>
       </c>
       <c r="D605">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E605" t="s">
         <v>28</v>
@@ -14422,7 +14422,7 @@
         <v>27</v>
       </c>
       <c r="D606">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E606" t="s">
         <v>28</v>
@@ -14439,7 +14439,7 @@
         <v>27</v>
       </c>
       <c r="D607">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E607" t="s">
         <v>28</v>
@@ -14456,7 +14456,7 @@
         <v>27</v>
       </c>
       <c r="D608">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
@@ -14473,7 +14473,7 @@
         <v>27</v>
       </c>
       <c r="D609">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E609" t="s">
         <v>28</v>
@@ -14490,7 +14490,7 @@
         <v>27</v>
       </c>
       <c r="D610">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E610" t="s">
         <v>28</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="D612">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E612" t="s">
         <v>28</v>
@@ -14541,7 +14541,7 @@
         <v>27</v>
       </c>
       <c r="D613">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E613" t="s">
         <v>28</v>
@@ -14558,7 +14558,7 @@
         <v>27</v>
       </c>
       <c r="D614">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E614" t="s">
         <v>28</v>
@@ -14575,7 +14575,7 @@
         <v>27</v>
       </c>
       <c r="D615">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E615" t="s">
         <v>28</v>
@@ -14592,7 +14592,7 @@
         <v>27</v>
       </c>
       <c r="D616">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E616" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="D617">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E617" t="s">
         <v>28</v>
@@ -14626,7 +14626,7 @@
         <v>27</v>
       </c>
       <c r="D618">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E618" t="s">
         <v>28</v>
@@ -14643,7 +14643,7 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E619" t="s">
         <v>28</v>
@@ -14660,7 +14660,7 @@
         <v>27</v>
       </c>
       <c r="D620">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E620" t="s">
         <v>28</v>
@@ -14677,7 +14677,7 @@
         <v>27</v>
       </c>
       <c r="D621">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E621" t="s">
         <v>28</v>
@@ -14711,7 +14711,7 @@
         <v>27</v>
       </c>
       <c r="D623">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E623" t="s">
         <v>28</v>
@@ -14728,7 +14728,7 @@
         <v>27</v>
       </c>
       <c r="D624">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E624" t="s">
         <v>28</v>
@@ -14745,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="D625">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E625" t="s">
         <v>28</v>
@@ -14762,7 +14762,7 @@
         <v>27</v>
       </c>
       <c r="D626">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E626" t="s">
         <v>28</v>
@@ -14779,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="D627">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E627" t="s">
         <v>28</v>
@@ -14796,7 +14796,7 @@
         <v>27</v>
       </c>
       <c r="D628">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E628" t="s">
         <v>28</v>
@@ -14813,7 +14813,7 @@
         <v>27</v>
       </c>
       <c r="D629">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E629" t="s">
         <v>28</v>
@@ -14830,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="D630">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E630" t="s">
         <v>28</v>
@@ -14847,7 +14847,7 @@
         <v>27</v>
       </c>
       <c r="D631">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E631" t="s">
         <v>28</v>
@@ -14864,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D632">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E632" t="s">
         <v>28</v>
@@ -14898,7 +14898,7 @@
         <v>27</v>
       </c>
       <c r="D634">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E634" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="D635">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E635" t="s">
         <v>28</v>
@@ -14932,7 +14932,7 @@
         <v>27</v>
       </c>
       <c r="D636">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E636" t="s">
         <v>28</v>
@@ -14949,7 +14949,7 @@
         <v>27</v>
       </c>
       <c r="D637">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E637" t="s">
         <v>28</v>
@@ -14966,7 +14966,7 @@
         <v>27</v>
       </c>
       <c r="D638">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E638" t="s">
         <v>28</v>
@@ -14983,7 +14983,7 @@
         <v>27</v>
       </c>
       <c r="D639">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E639" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E640" t="s">
         <v>28</v>
@@ -15017,7 +15017,7 @@
         <v>27</v>
       </c>
       <c r="D641">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E641" t="s">
         <v>28</v>
@@ -15034,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="D642">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E642" t="s">
         <v>28</v>
@@ -15051,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="D643">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E643" t="s">
         <v>28</v>
@@ -15068,7 +15068,7 @@
         <v>27</v>
       </c>
       <c r="D644">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E644" t="s">
         <v>28</v>
@@ -15085,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="D645">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E645" t="s">
         <v>28</v>
@@ -15102,7 +15102,7 @@
         <v>27</v>
       </c>
       <c r="D646">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E646" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>27</v>
       </c>
       <c r="D647">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E647" t="s">
         <v>28</v>
@@ -15136,7 +15136,7 @@
         <v>27</v>
       </c>
       <c r="D648">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E648" t="s">
         <v>28</v>
@@ -15153,7 +15153,7 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E649" t="s">
         <v>28</v>
@@ -15170,7 +15170,7 @@
         <v>27</v>
       </c>
       <c r="D650">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E650" t="s">
         <v>28</v>
@@ -15187,7 +15187,7 @@
         <v>27</v>
       </c>
       <c r="D651">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E651" t="s">
         <v>28</v>
@@ -15204,7 +15204,7 @@
         <v>27</v>
       </c>
       <c r="D652">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E652" t="s">
         <v>28</v>
@@ -15221,7 +15221,7 @@
         <v>27</v>
       </c>
       <c r="D653">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E653" t="s">
         <v>28</v>
@@ -15238,7 +15238,7 @@
         <v>27</v>
       </c>
       <c r="D654">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E654" t="s">
         <v>28</v>
@@ -15255,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="D655">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E655" t="s">
         <v>28</v>
@@ -15272,7 +15272,7 @@
         <v>27</v>
       </c>
       <c r="D656">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
@@ -15323,7 +15323,7 @@
         <v>27</v>
       </c>
       <c r="D659">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E659" t="s">
         <v>28</v>
@@ -15340,7 +15340,7 @@
         <v>27</v>
       </c>
       <c r="D660">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E660" t="s">
         <v>28</v>
@@ -15357,7 +15357,7 @@
         <v>27</v>
       </c>
       <c r="D661">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E661" t="s">
         <v>28</v>
@@ -15374,7 +15374,7 @@
         <v>27</v>
       </c>
       <c r="D662">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E662" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="D663">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E663" t="s">
         <v>28</v>
@@ -15408,7 +15408,7 @@
         <v>27</v>
       </c>
       <c r="D664">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E664" t="s">
         <v>28</v>
@@ -15425,7 +15425,7 @@
         <v>27</v>
       </c>
       <c r="D665">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E665" t="s">
         <v>28</v>
@@ -15442,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="D666">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E666" t="s">
         <v>28</v>
@@ -15459,7 +15459,7 @@
         <v>27</v>
       </c>
       <c r="D667">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E667" t="s">
         <v>28</v>
@@ -15476,7 +15476,7 @@
         <v>27</v>
       </c>
       <c r="D668">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E668" t="s">
         <v>28</v>
@@ -15493,7 +15493,7 @@
         <v>27</v>
       </c>
       <c r="D669">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E669" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>27</v>
       </c>
       <c r="D670">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E670" t="s">
         <v>28</v>
@@ -15527,7 +15527,7 @@
         <v>27</v>
       </c>
       <c r="D671">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E671" t="s">
         <v>28</v>
@@ -15544,7 +15544,7 @@
         <v>27</v>
       </c>
       <c r="D672">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E672" t="s">
         <v>28</v>
@@ -15561,7 +15561,7 @@
         <v>27</v>
       </c>
       <c r="D673">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E673" t="s">
         <v>28</v>
@@ -15578,7 +15578,7 @@
         <v>27</v>
       </c>
       <c r="D674">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E674" t="s">
         <v>28</v>
@@ -15595,7 +15595,7 @@
         <v>27</v>
       </c>
       <c r="D675">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E675" t="s">
         <v>28</v>
@@ -15612,7 +15612,7 @@
         <v>27</v>
       </c>
       <c r="D676">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E676" t="s">
         <v>28</v>
@@ -15629,7 +15629,7 @@
         <v>27</v>
       </c>
       <c r="D677">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E677" t="s">
         <v>28</v>
@@ -15646,7 +15646,7 @@
         <v>27</v>
       </c>
       <c r="D678">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E678" t="s">
         <v>28</v>
@@ -15663,7 +15663,7 @@
         <v>27</v>
       </c>
       <c r="D679">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E679" t="s">
         <v>28</v>
@@ -15680,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="D680">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E680" t="s">
         <v>28</v>
@@ -15697,7 +15697,7 @@
         <v>27</v>
       </c>
       <c r="D681">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E681" t="s">
         <v>28</v>
@@ -15714,7 +15714,7 @@
         <v>27</v>
       </c>
       <c r="D682">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E682" t="s">
         <v>28</v>
@@ -15731,7 +15731,7 @@
         <v>27</v>
       </c>
       <c r="D683">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E683" t="s">
         <v>28</v>
@@ -15748,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="D684">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E684" t="s">
         <v>28</v>
@@ -15765,7 +15765,7 @@
         <v>27</v>
       </c>
       <c r="D685">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E685" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="D686">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E686" t="s">
         <v>28</v>
@@ -15799,7 +15799,7 @@
         <v>27</v>
       </c>
       <c r="D687">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E687" t="s">
         <v>28</v>
@@ -15816,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="D688">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E688" t="s">
         <v>28</v>
@@ -15850,7 +15850,7 @@
         <v>27</v>
       </c>
       <c r="D690">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E690" t="s">
         <v>28</v>
@@ -15867,7 +15867,7 @@
         <v>27</v>
       </c>
       <c r="D691">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E691" t="s">
         <v>28</v>
@@ -15884,7 +15884,7 @@
         <v>27</v>
       </c>
       <c r="D692">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E692" t="s">
         <v>28</v>
@@ -15901,7 +15901,7 @@
         <v>27</v>
       </c>
       <c r="D693">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E693" t="s">
         <v>28</v>
@@ -15918,7 +15918,7 @@
         <v>27</v>
       </c>
       <c r="D694">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E694" t="s">
         <v>28</v>
@@ -15935,7 +15935,7 @@
         <v>27</v>
       </c>
       <c r="D695">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E695" t="s">
         <v>28</v>
@@ -15952,7 +15952,7 @@
         <v>27</v>
       </c>
       <c r="D696">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E696" t="s">
         <v>28</v>
@@ -15969,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="D697">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E697" t="s">
         <v>28</v>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
       <c r="D698">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E698" t="s">
         <v>28</v>
@@ -16003,7 +16003,7 @@
         <v>27</v>
       </c>
       <c r="D699">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E699" t="s">
         <v>28</v>
@@ -16020,7 +16020,7 @@
         <v>27</v>
       </c>
       <c r="D700">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E700" t="s">
         <v>28</v>
@@ -16037,7 +16037,7 @@
         <v>27</v>
       </c>
       <c r="D701">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E701" t="s">
         <v>28</v>
@@ -16054,7 +16054,7 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E702" t="s">
         <v>28</v>
@@ -16071,7 +16071,7 @@
         <v>27</v>
       </c>
       <c r="D703">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E703" t="s">
         <v>28</v>
@@ -16088,7 +16088,7 @@
         <v>27</v>
       </c>
       <c r="D704">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E704" t="s">
         <v>28</v>
@@ -16105,7 +16105,7 @@
         <v>27</v>
       </c>
       <c r="D705">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E705" t="s">
         <v>28</v>
@@ -16122,7 +16122,7 @@
         <v>27</v>
       </c>
       <c r="D706">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E706" t="s">
         <v>28</v>
@@ -16139,7 +16139,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E707" t="s">
         <v>28</v>
@@ -16156,7 +16156,7 @@
         <v>27</v>
       </c>
       <c r="D708">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E708" t="s">
         <v>28</v>
@@ -16190,7 +16190,7 @@
         <v>27</v>
       </c>
       <c r="D710">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E710" t="s">
         <v>28</v>
@@ -16207,7 +16207,7 @@
         <v>27</v>
       </c>
       <c r="D711">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E711" t="s">
         <v>28</v>
@@ -16224,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="D712">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E712" t="s">
         <v>28</v>
@@ -16241,7 +16241,7 @@
         <v>27</v>
       </c>
       <c r="D713">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E713" t="s">
         <v>28</v>
@@ -16258,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="D714">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E714" t="s">
         <v>28</v>
@@ -16292,7 +16292,7 @@
         <v>27</v>
       </c>
       <c r="D716">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E716" t="s">
         <v>28</v>
@@ -16309,7 +16309,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E717" t="s">
         <v>28</v>
@@ -16326,7 +16326,7 @@
         <v>27</v>
       </c>
       <c r="D718">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E718" t="s">
         <v>28</v>
@@ -16343,7 +16343,7 @@
         <v>27</v>
       </c>
       <c r="D719">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E719" t="s">
         <v>28</v>
@@ -16377,7 +16377,7 @@
         <v>27</v>
       </c>
       <c r="D721">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E721" t="s">
         <v>28</v>
@@ -16394,7 +16394,7 @@
         <v>27</v>
       </c>
       <c r="D722">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E722" t="s">
         <v>28</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="D723">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E723" t="s">
         <v>28</v>
@@ -16428,7 +16428,7 @@
         <v>27</v>
       </c>
       <c r="D724">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E724" t="s">
         <v>28</v>
@@ -16445,7 +16445,7 @@
         <v>27</v>
       </c>
       <c r="D725">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E725" t="s">
         <v>28</v>
@@ -16462,7 +16462,7 @@
         <v>27</v>
       </c>
       <c r="D726">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E726" t="s">
         <v>28</v>
@@ -16479,7 +16479,7 @@
         <v>27</v>
       </c>
       <c r="D727">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E727" t="s">
         <v>28</v>
@@ -16496,7 +16496,7 @@
         <v>27</v>
       </c>
       <c r="D728">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E728" t="s">
         <v>28</v>
@@ -16513,7 +16513,7 @@
         <v>27</v>
       </c>
       <c r="D729">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E729" t="s">
         <v>28</v>
@@ -16530,7 +16530,7 @@
         <v>27</v>
       </c>
       <c r="D730">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E730" t="s">
         <v>28</v>
@@ -16547,7 +16547,7 @@
         <v>27</v>
       </c>
       <c r="D731">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E731" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="D732">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E732" t="s">
         <v>28</v>
@@ -16581,7 +16581,7 @@
         <v>27</v>
       </c>
       <c r="D733">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E733" t="s">
         <v>28</v>
@@ -16598,7 +16598,7 @@
         <v>27</v>
       </c>
       <c r="D734">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E734" t="s">
         <v>28</v>
@@ -16615,7 +16615,7 @@
         <v>27</v>
       </c>
       <c r="D735">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E735" t="s">
         <v>28</v>
@@ -16632,7 +16632,7 @@
         <v>27</v>
       </c>
       <c r="D736">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E736" t="s">
         <v>28</v>
@@ -16649,7 +16649,7 @@
         <v>27</v>
       </c>
       <c r="D737">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E737" t="s">
         <v>28</v>
@@ -16666,7 +16666,7 @@
         <v>27</v>
       </c>
       <c r="D738">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E738" t="s">
         <v>28</v>
@@ -16683,7 +16683,7 @@
         <v>27</v>
       </c>
       <c r="D739">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E739" t="s">
         <v>28</v>
@@ -16700,7 +16700,7 @@
         <v>27</v>
       </c>
       <c r="D740">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E740" t="s">
         <v>28</v>
@@ -16717,7 +16717,7 @@
         <v>27</v>
       </c>
       <c r="D741">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E741" t="s">
         <v>28</v>
@@ -16734,7 +16734,7 @@
         <v>27</v>
       </c>
       <c r="D742">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E742" t="s">
         <v>28</v>
@@ -16751,7 +16751,7 @@
         <v>27</v>
       </c>
       <c r="D743">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E743" t="s">
         <v>28</v>
@@ -16768,7 +16768,7 @@
         <v>27</v>
       </c>
       <c r="D744">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E744" t="s">
         <v>28</v>
@@ -16785,7 +16785,7 @@
         <v>27</v>
       </c>
       <c r="D745">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E745" t="s">
         <v>28</v>
@@ -16802,7 +16802,7 @@
         <v>27</v>
       </c>
       <c r="D746">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E746" t="s">
         <v>28</v>
@@ -16819,7 +16819,7 @@
         <v>27</v>
       </c>
       <c r="D747">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E747" t="s">
         <v>28</v>
@@ -16836,7 +16836,7 @@
         <v>27</v>
       </c>
       <c r="D748">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E748" t="s">
         <v>28</v>
@@ -16853,7 +16853,7 @@
         <v>27</v>
       </c>
       <c r="D749">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E749" t="s">
         <v>28</v>
@@ -16870,7 +16870,7 @@
         <v>27</v>
       </c>
       <c r="D750">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E750" t="s">
         <v>28</v>
@@ -16887,7 +16887,7 @@
         <v>27</v>
       </c>
       <c r="D751">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E751" t="s">
         <v>28</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="D752">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E752" t="s">
         <v>28</v>
@@ -16921,7 +16921,7 @@
         <v>27</v>
       </c>
       <c r="D753">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E753" t="s">
         <v>28</v>
@@ -16938,7 +16938,7 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E754" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="D755">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E755" t="s">
         <v>28</v>
@@ -16972,7 +16972,7 @@
         <v>27</v>
       </c>
       <c r="D756">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E756" t="s">
         <v>28</v>
@@ -16989,7 +16989,7 @@
         <v>27</v>
       </c>
       <c r="D757">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E757" t="s">
         <v>28</v>
@@ -17006,7 +17006,7 @@
         <v>27</v>
       </c>
       <c r="D758">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E758" t="s">
         <v>28</v>
@@ -17023,7 +17023,7 @@
         <v>27</v>
       </c>
       <c r="D759">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E759" t="s">
         <v>28</v>
@@ -17057,7 +17057,7 @@
         <v>27</v>
       </c>
       <c r="D761">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E761" t="s">
         <v>28</v>
@@ -17074,7 +17074,7 @@
         <v>27</v>
       </c>
       <c r="D762">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E762" t="s">
         <v>28</v>
@@ -17091,7 +17091,7 @@
         <v>27</v>
       </c>
       <c r="D763">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E763" t="s">
         <v>28</v>
@@ -17108,7 +17108,7 @@
         <v>27</v>
       </c>
       <c r="D764">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E764" t="s">
         <v>28</v>
@@ -17125,7 +17125,7 @@
         <v>27</v>
       </c>
       <c r="D765">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E765" t="s">
         <v>28</v>
@@ -17142,7 +17142,7 @@
         <v>27</v>
       </c>
       <c r="D766">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E766" t="s">
         <v>28</v>
@@ -17159,7 +17159,7 @@
         <v>27</v>
       </c>
       <c r="D767">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E767" t="s">
         <v>28</v>
@@ -17176,7 +17176,7 @@
         <v>27</v>
       </c>
       <c r="D768">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E768" t="s">
         <v>28</v>
@@ -17193,7 +17193,7 @@
         <v>27</v>
       </c>
       <c r="D769">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E769" t="s">
         <v>28</v>
@@ -17210,7 +17210,7 @@
         <v>27</v>
       </c>
       <c r="D770">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E770" t="s">
         <v>28</v>
@@ -17227,7 +17227,7 @@
         <v>27</v>
       </c>
       <c r="D771">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E771" t="s">
         <v>28</v>
@@ -17244,7 +17244,7 @@
         <v>27</v>
       </c>
       <c r="D772">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E772" t="s">
         <v>28</v>
@@ -17261,7 +17261,7 @@
         <v>27</v>
       </c>
       <c r="D773">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E773" t="s">
         <v>28</v>
@@ -17278,7 +17278,7 @@
         <v>27</v>
       </c>
       <c r="D774">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E774" t="s">
         <v>28</v>
@@ -17295,7 +17295,7 @@
         <v>27</v>
       </c>
       <c r="D775">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E775" t="s">
         <v>28</v>
@@ -17312,7 +17312,7 @@
         <v>27</v>
       </c>
       <c r="D776">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E776" t="s">
         <v>28</v>
@@ -17329,7 +17329,7 @@
         <v>27</v>
       </c>
       <c r="D777">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E777" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="D778">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E778" t="s">
         <v>28</v>
@@ -17363,7 +17363,7 @@
         <v>27</v>
       </c>
       <c r="D779">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E779" t="s">
         <v>28</v>
@@ -17380,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="D780">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E780" t="s">
         <v>28</v>
@@ -17397,7 +17397,7 @@
         <v>27</v>
       </c>
       <c r="D781">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E781" t="s">
         <v>28</v>
@@ -17414,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="D782">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E782" t="s">
         <v>28</v>
@@ -17431,7 +17431,7 @@
         <v>27</v>
       </c>
       <c r="D783">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E783" t="s">
         <v>28</v>
@@ -17448,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D784">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E784" t="s">
         <v>28</v>
@@ -17465,7 +17465,7 @@
         <v>27</v>
       </c>
       <c r="D785">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E785" t="s">
         <v>28</v>
@@ -17482,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="D786">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E786" t="s">
         <v>28</v>
@@ -17499,7 +17499,7 @@
         <v>27</v>
       </c>
       <c r="D787">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E787" t="s">
         <v>28</v>
@@ -17533,7 +17533,7 @@
         <v>27</v>
       </c>
       <c r="D789">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E789" t="s">
         <v>28</v>
@@ -17550,7 +17550,7 @@
         <v>27</v>
       </c>
       <c r="D790">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E790" t="s">
         <v>28</v>
@@ -17567,7 +17567,7 @@
         <v>27</v>
       </c>
       <c r="D791">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E791" t="s">
         <v>28</v>
@@ -17584,7 +17584,7 @@
         <v>27</v>
       </c>
       <c r="D792">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E792" t="s">
         <v>28</v>
@@ -17618,7 +17618,7 @@
         <v>27</v>
       </c>
       <c r="D794">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E794" t="s">
         <v>28</v>
@@ -17652,7 +17652,7 @@
         <v>27</v>
       </c>
       <c r="D796">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E796" t="s">
         <v>28</v>
@@ -17669,7 +17669,7 @@
         <v>27</v>
       </c>
       <c r="D797">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E797" t="s">
         <v>28</v>
@@ -17686,7 +17686,7 @@
         <v>27</v>
       </c>
       <c r="D798">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E798" t="s">
         <v>28</v>
@@ -17703,7 +17703,7 @@
         <v>27</v>
       </c>
       <c r="D799">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E799" t="s">
         <v>28</v>
@@ -17720,7 +17720,7 @@
         <v>27</v>
       </c>
       <c r="D800">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E800" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="D801">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E801" t="s">
         <v>28</v>
@@ -17754,7 +17754,7 @@
         <v>27</v>
       </c>
       <c r="D802">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E802" t="s">
         <v>28</v>
@@ -17771,7 +17771,7 @@
         <v>27</v>
       </c>
       <c r="D803">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E803" t="s">
         <v>28</v>
@@ -17788,7 +17788,7 @@
         <v>27</v>
       </c>
       <c r="D804">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E804" t="s">
         <v>28</v>
@@ -17805,7 +17805,7 @@
         <v>27</v>
       </c>
       <c r="D805">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E805" t="s">
         <v>28</v>
@@ -17822,7 +17822,7 @@
         <v>27</v>
       </c>
       <c r="D806">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E806" t="s">
         <v>28</v>
@@ -17839,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="D807">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E807" t="s">
         <v>28</v>
@@ -17856,7 +17856,7 @@
         <v>27</v>
       </c>
       <c r="D808">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E808" t="s">
         <v>28</v>
@@ -17890,7 +17890,7 @@
         <v>27</v>
       </c>
       <c r="D810">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E810" t="s">
         <v>28</v>
@@ -17907,7 +17907,7 @@
         <v>27</v>
       </c>
       <c r="D811">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E811" t="s">
         <v>28</v>
@@ -17924,7 +17924,7 @@
         <v>27</v>
       </c>
       <c r="D812">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E812" t="s">
         <v>28</v>
@@ -17941,7 +17941,7 @@
         <v>27</v>
       </c>
       <c r="D813">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E813" t="s">
         <v>28</v>
@@ -17958,7 +17958,7 @@
         <v>27</v>
       </c>
       <c r="D814">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E814" t="s">
         <v>28</v>
@@ -17975,7 +17975,7 @@
         <v>27</v>
       </c>
       <c r="D815">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E815" t="s">
         <v>28</v>
@@ -18009,7 +18009,7 @@
         <v>27</v>
       </c>
       <c r="D817">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E817" t="s">
         <v>28</v>
@@ -18043,7 +18043,7 @@
         <v>27</v>
       </c>
       <c r="D819">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E819" t="s">
         <v>28</v>
@@ -18060,7 +18060,7 @@
         <v>27</v>
       </c>
       <c r="D820">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E820" t="s">
         <v>28</v>
@@ -18077,7 +18077,7 @@
         <v>27</v>
       </c>
       <c r="D821">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E821" t="s">
         <v>28</v>
@@ -18094,7 +18094,7 @@
         <v>27</v>
       </c>
       <c r="D822">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E822" t="s">
         <v>28</v>
@@ -18111,7 +18111,7 @@
         <v>27</v>
       </c>
       <c r="D823">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E823" t="s">
         <v>28</v>
@@ -18128,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="D824">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E824" t="s">
         <v>28</v>
@@ -18145,7 +18145,7 @@
         <v>27</v>
       </c>
       <c r="D825">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E825" t="s">
         <v>28</v>
@@ -18162,7 +18162,7 @@
         <v>27</v>
       </c>
       <c r="D826">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E826" t="s">
         <v>28</v>
@@ -18179,7 +18179,7 @@
         <v>27</v>
       </c>
       <c r="D827">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E827" t="s">
         <v>28</v>
@@ -18196,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="D828">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E828" t="s">
         <v>28</v>
@@ -18213,7 +18213,7 @@
         <v>27</v>
       </c>
       <c r="D829">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E829" t="s">
         <v>28</v>
@@ -18230,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="D830">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E830" t="s">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E831" t="s">
         <v>28</v>
@@ -18264,7 +18264,7 @@
         <v>27</v>
       </c>
       <c r="D832">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E832" t="s">
         <v>28</v>
@@ -18281,7 +18281,7 @@
         <v>27</v>
       </c>
       <c r="D833">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E833" t="s">
         <v>28</v>
@@ -18298,7 +18298,7 @@
         <v>27</v>
       </c>
       <c r="D834">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E834" t="s">
         <v>28</v>
@@ -18315,7 +18315,7 @@
         <v>27</v>
       </c>
       <c r="D835">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E835" t="s">
         <v>28</v>
@@ -18332,7 +18332,7 @@
         <v>27</v>
       </c>
       <c r="D836">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E836" t="s">
         <v>28</v>
@@ -18349,7 +18349,7 @@
         <v>27</v>
       </c>
       <c r="D837">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E837" t="s">
         <v>28</v>
@@ -18366,7 +18366,7 @@
         <v>27</v>
       </c>
       <c r="D838">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E838" t="s">
         <v>28</v>
@@ -18383,7 +18383,7 @@
         <v>27</v>
       </c>
       <c r="D839">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E839" t="s">
         <v>28</v>
@@ -18400,7 +18400,7 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E840" t="s">
         <v>28</v>
@@ -18417,7 +18417,7 @@
         <v>27</v>
       </c>
       <c r="D841">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E841" t="s">
         <v>28</v>
@@ -18434,7 +18434,7 @@
         <v>27</v>
       </c>
       <c r="D842">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E842" t="s">
         <v>28</v>
@@ -18451,7 +18451,7 @@
         <v>27</v>
       </c>
       <c r="D843">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E843" t="s">
         <v>28</v>
@@ -18468,7 +18468,7 @@
         <v>27</v>
       </c>
       <c r="D844">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E844" t="s">
         <v>28</v>
@@ -18485,7 +18485,7 @@
         <v>27</v>
       </c>
       <c r="D845">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E845" t="s">
         <v>28</v>
@@ -18502,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="D846">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E846" t="s">
         <v>28</v>
@@ -18519,7 +18519,7 @@
         <v>27</v>
       </c>
       <c r="D847">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E847" t="s">
         <v>28</v>
@@ -18536,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="D848">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E848" t="s">
         <v>28</v>
@@ -18553,7 +18553,7 @@
         <v>27</v>
       </c>
       <c r="D849">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E849" t="s">
         <v>28</v>
@@ -18570,7 +18570,7 @@
         <v>27</v>
       </c>
       <c r="D850">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E850" t="s">
         <v>28</v>
@@ -18587,7 +18587,7 @@
         <v>27</v>
       </c>
       <c r="D851">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E851" t="s">
         <v>28</v>
@@ -18604,7 +18604,7 @@
         <v>27</v>
       </c>
       <c r="D852">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E852" t="s">
         <v>28</v>
@@ -18621,7 +18621,7 @@
         <v>27</v>
       </c>
       <c r="D853">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E853" t="s">
         <v>28</v>
@@ -18638,7 +18638,7 @@
         <v>27</v>
       </c>
       <c r="D854">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E854" t="s">
         <v>28</v>
@@ -18655,7 +18655,7 @@
         <v>27</v>
       </c>
       <c r="D855">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E855" t="s">
         <v>28</v>
@@ -18672,7 +18672,7 @@
         <v>27</v>
       </c>
       <c r="D856">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E856" t="s">
         <v>28</v>
@@ -18689,7 +18689,7 @@
         <v>27</v>
       </c>
       <c r="D857">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E857" t="s">
         <v>28</v>
@@ -18706,7 +18706,7 @@
         <v>27</v>
       </c>
       <c r="D858">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E858" t="s">
         <v>28</v>
@@ -18723,7 +18723,7 @@
         <v>27</v>
       </c>
       <c r="D859">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E859" t="s">
         <v>28</v>
@@ -18740,7 +18740,7 @@
         <v>27</v>
       </c>
       <c r="D860">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E860" t="s">
         <v>28</v>
@@ -18757,7 +18757,7 @@
         <v>27</v>
       </c>
       <c r="D861">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E861" t="s">
         <v>28</v>
@@ -18774,7 +18774,7 @@
         <v>27</v>
       </c>
       <c r="D862">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E862" t="s">
         <v>28</v>
@@ -18791,7 +18791,7 @@
         <v>27</v>
       </c>
       <c r="D863">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E863" t="s">
         <v>28</v>
@@ -18808,7 +18808,7 @@
         <v>27</v>
       </c>
       <c r="D864">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E864" t="s">
         <v>28</v>
@@ -18825,7 +18825,7 @@
         <v>27</v>
       </c>
       <c r="D865">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E865" t="s">
         <v>28</v>
@@ -18842,7 +18842,7 @@
         <v>27</v>
       </c>
       <c r="D866">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E866" t="s">
         <v>28</v>
@@ -18859,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="D867">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E867" t="s">
         <v>28</v>
@@ -18876,7 +18876,7 @@
         <v>27</v>
       </c>
       <c r="D868">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E868" t="s">
         <v>28</v>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
       <c r="D869">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E869" t="s">
         <v>28</v>
@@ -18910,7 +18910,7 @@
         <v>27</v>
       </c>
       <c r="D870">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E870" t="s">
         <v>28</v>
@@ -18927,7 +18927,7 @@
         <v>27</v>
       </c>
       <c r="D871">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E871" t="s">
         <v>28</v>
@@ -18944,7 +18944,7 @@
         <v>27</v>
       </c>
       <c r="D872">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E872" t="s">
         <v>28</v>
@@ -18961,7 +18961,7 @@
         <v>27</v>
       </c>
       <c r="D873">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E873" t="s">
         <v>28</v>
@@ -18978,7 +18978,7 @@
         <v>27</v>
       </c>
       <c r="D874">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E874" t="s">
         <v>28</v>
@@ -18995,7 +18995,7 @@
         <v>27</v>
       </c>
       <c r="D875">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E875" t="s">
         <v>28</v>
@@ -19012,7 +19012,7 @@
         <v>27</v>
       </c>
       <c r="D876">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E876" t="s">
         <v>28</v>
@@ -19029,7 +19029,7 @@
         <v>27</v>
       </c>
       <c r="D877">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E877" t="s">
         <v>28</v>
@@ -19046,7 +19046,7 @@
         <v>27</v>
       </c>
       <c r="D878">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E878" t="s">
         <v>28</v>
@@ -19063,7 +19063,7 @@
         <v>27</v>
       </c>
       <c r="D879">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E879" t="s">
         <v>28</v>
@@ -19080,7 +19080,7 @@
         <v>27</v>
       </c>
       <c r="D880">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E880" t="s">
         <v>28</v>
@@ -19097,7 +19097,7 @@
         <v>27</v>
       </c>
       <c r="D881">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E881" t="s">
         <v>28</v>
@@ -19114,7 +19114,7 @@
         <v>27</v>
       </c>
       <c r="D882">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E882" t="s">
         <v>28</v>
@@ -19131,7 +19131,7 @@
         <v>27</v>
       </c>
       <c r="D883">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E883" t="s">
         <v>28</v>
@@ -19148,7 +19148,7 @@
         <v>27</v>
       </c>
       <c r="D884">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E884" t="s">
         <v>28</v>
@@ -19165,7 +19165,7 @@
         <v>27</v>
       </c>
       <c r="D885">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E885" t="s">
         <v>28</v>
@@ -19182,7 +19182,7 @@
         <v>27</v>
       </c>
       <c r="D886">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E886" t="s">
         <v>28</v>
@@ -19199,7 +19199,7 @@
         <v>27</v>
       </c>
       <c r="D887">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E887" t="s">
         <v>28</v>
@@ -19216,7 +19216,7 @@
         <v>27</v>
       </c>
       <c r="D888">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E888" t="s">
         <v>28</v>
@@ -19233,7 +19233,7 @@
         <v>27</v>
       </c>
       <c r="D889">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E889" t="s">
         <v>28</v>
@@ -19250,7 +19250,7 @@
         <v>27</v>
       </c>
       <c r="D890">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E890" t="s">
         <v>28</v>
@@ -19267,7 +19267,7 @@
         <v>27</v>
       </c>
       <c r="D891">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E891" t="s">
         <v>28</v>
@@ -19284,7 +19284,7 @@
         <v>27</v>
       </c>
       <c r="D892">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E892" t="s">
         <v>28</v>
@@ -19301,7 +19301,7 @@
         <v>27</v>
       </c>
       <c r="D893">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E893" t="s">
         <v>28</v>
@@ -19318,7 +19318,7 @@
         <v>27</v>
       </c>
       <c r="D894">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E894" t="s">
         <v>28</v>
@@ -19335,7 +19335,7 @@
         <v>27</v>
       </c>
       <c r="D895">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E895" t="s">
         <v>28</v>
@@ -19352,7 +19352,7 @@
         <v>27</v>
       </c>
       <c r="D896">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E896" t="s">
         <v>28</v>
@@ -19369,7 +19369,7 @@
         <v>27</v>
       </c>
       <c r="D897">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E897" t="s">
         <v>28</v>
@@ -19386,7 +19386,7 @@
         <v>27</v>
       </c>
       <c r="D898">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E898" t="s">
         <v>28</v>
@@ -19403,7 +19403,7 @@
         <v>27</v>
       </c>
       <c r="D899">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E899" t="s">
         <v>28</v>
@@ -19420,7 +19420,7 @@
         <v>27</v>
       </c>
       <c r="D900">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E900" t="s">
         <v>28</v>
@@ -19437,7 +19437,7 @@
         <v>27</v>
       </c>
       <c r="D901">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E901" t="s">
         <v>28</v>
@@ -19471,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D903">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E903" t="s">
         <v>28</v>
@@ -19488,7 +19488,7 @@
         <v>27</v>
       </c>
       <c r="D904">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E904" t="s">
         <v>28</v>
@@ -19505,7 +19505,7 @@
         <v>27</v>
       </c>
       <c r="D905">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E905" t="s">
         <v>28</v>
@@ -19522,7 +19522,7 @@
         <v>27</v>
       </c>
       <c r="D906">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E906" t="s">
         <v>28</v>
@@ -19539,7 +19539,7 @@
         <v>27</v>
       </c>
       <c r="D907">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E907" t="s">
         <v>28</v>
@@ -19556,7 +19556,7 @@
         <v>27</v>
       </c>
       <c r="D908">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E908" t="s">
         <v>28</v>
@@ -19573,7 +19573,7 @@
         <v>27</v>
       </c>
       <c r="D909">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E909" t="s">
         <v>28</v>
@@ -19590,7 +19590,7 @@
         <v>27</v>
       </c>
       <c r="D910">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E910" t="s">
         <v>28</v>
@@ -19607,7 +19607,7 @@
         <v>27</v>
       </c>
       <c r="D911">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E911" t="s">
         <v>28</v>
@@ -19624,7 +19624,7 @@
         <v>27</v>
       </c>
       <c r="D912">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E912" t="s">
         <v>28</v>
@@ -19641,7 +19641,7 @@
         <v>27</v>
       </c>
       <c r="D913">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E913" t="s">
         <v>28</v>
@@ -19658,7 +19658,7 @@
         <v>27</v>
       </c>
       <c r="D914">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E914" t="s">
         <v>28</v>
@@ -19675,7 +19675,7 @@
         <v>27</v>
       </c>
       <c r="D915">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E915" t="s">
         <v>28</v>
@@ -19692,7 +19692,7 @@
         <v>27</v>
       </c>
       <c r="D916">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E916" t="s">
         <v>28</v>
@@ -19709,7 +19709,7 @@
         <v>27</v>
       </c>
       <c r="D917">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E917" t="s">
         <v>28</v>
@@ -19726,7 +19726,7 @@
         <v>27</v>
       </c>
       <c r="D918">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E918" t="s">
         <v>28</v>
@@ -19743,7 +19743,7 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E919" t="s">
         <v>28</v>
@@ -19760,7 +19760,7 @@
         <v>27</v>
       </c>
       <c r="D920">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E920" t="s">
         <v>28</v>
@@ -19777,7 +19777,7 @@
         <v>27</v>
       </c>
       <c r="D921">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E921" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>27</v>
       </c>
       <c r="D922">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E922" t="s">
         <v>28</v>
@@ -19811,7 +19811,7 @@
         <v>27</v>
       </c>
       <c r="D923">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E923" t="s">
         <v>28</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="D924">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E924" t="s">
         <v>28</v>
@@ -19845,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="D925">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E925" t="s">
         <v>28</v>
@@ -19862,7 +19862,7 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E926" t="s">
         <v>28</v>
@@ -19879,7 +19879,7 @@
         <v>27</v>
       </c>
       <c r="D927">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E927" t="s">
         <v>28</v>
@@ -19896,7 +19896,7 @@
         <v>27</v>
       </c>
       <c r="D928">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E928" t="s">
         <v>28</v>
@@ -19913,7 +19913,7 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E929" t="s">
         <v>28</v>
@@ -19930,7 +19930,7 @@
         <v>27</v>
       </c>
       <c r="D930">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E930" t="s">
         <v>28</v>
@@ -19947,7 +19947,7 @@
         <v>27</v>
       </c>
       <c r="D931">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E931" t="s">
         <v>28</v>
@@ -19964,7 +19964,7 @@
         <v>27</v>
       </c>
       <c r="D932">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E932" t="s">
         <v>28</v>
@@ -19981,7 +19981,7 @@
         <v>27</v>
       </c>
       <c r="D933">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E933" t="s">
         <v>28</v>
@@ -19998,7 +19998,7 @@
         <v>27</v>
       </c>
       <c r="D934">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E934" t="s">
         <v>28</v>
@@ -20015,7 +20015,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E935" t="s">
         <v>28</v>
@@ -20032,7 +20032,7 @@
         <v>27</v>
       </c>
       <c r="D936">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E936" t="s">
         <v>28</v>
@@ -20049,7 +20049,7 @@
         <v>27</v>
       </c>
       <c r="D937">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E937" t="s">
         <v>28</v>
@@ -20066,7 +20066,7 @@
         <v>27</v>
       </c>
       <c r="D938">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E938" t="s">
         <v>28</v>
@@ -20083,7 +20083,7 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E939" t="s">
         <v>28</v>
@@ -20100,7 +20100,7 @@
         <v>27</v>
       </c>
       <c r="D940">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E940" t="s">
         <v>28</v>
@@ -20117,7 +20117,7 @@
         <v>27</v>
       </c>
       <c r="D941">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E941" t="s">
         <v>28</v>
@@ -20134,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D942">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E942" t="s">
         <v>28</v>
@@ -20151,7 +20151,7 @@
         <v>27</v>
       </c>
       <c r="D943">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E943" t="s">
         <v>28</v>
@@ -20168,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="D944">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E944" t="s">
         <v>28</v>
@@ -20185,7 +20185,7 @@
         <v>27</v>
       </c>
       <c r="D945">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E945" t="s">
         <v>28</v>
@@ -20202,7 +20202,7 @@
         <v>27</v>
       </c>
       <c r="D946">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E946" t="s">
         <v>28</v>
@@ -20219,7 +20219,7 @@
         <v>27</v>
       </c>
       <c r="D947">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E947" t="s">
         <v>28</v>
@@ -20236,7 +20236,7 @@
         <v>27</v>
       </c>
       <c r="D948">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E948" t="s">
         <v>28</v>
@@ -20253,7 +20253,7 @@
         <v>27</v>
       </c>
       <c r="D949">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E949" t="s">
         <v>28</v>
@@ -20270,7 +20270,7 @@
         <v>27</v>
       </c>
       <c r="D950">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E950" t="s">
         <v>28</v>
@@ -20287,7 +20287,7 @@
         <v>27</v>
       </c>
       <c r="D951">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E951" t="s">
         <v>28</v>
@@ -20304,7 +20304,7 @@
         <v>27</v>
       </c>
       <c r="D952">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E952" t="s">
         <v>28</v>
@@ -20321,7 +20321,7 @@
         <v>27</v>
       </c>
       <c r="D953">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E953" t="s">
         <v>28</v>
@@ -20338,7 +20338,7 @@
         <v>27</v>
       </c>
       <c r="D954">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E954" t="s">
         <v>28</v>
@@ -20355,7 +20355,7 @@
         <v>27</v>
       </c>
       <c r="D955">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E955" t="s">
         <v>28</v>
@@ -20372,7 +20372,7 @@
         <v>27</v>
       </c>
       <c r="D956">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E956" t="s">
         <v>28</v>
@@ -20389,7 +20389,7 @@
         <v>27</v>
       </c>
       <c r="D957">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E957" t="s">
         <v>28</v>
@@ -20406,7 +20406,7 @@
         <v>27</v>
       </c>
       <c r="D958">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E958" t="s">
         <v>28</v>
@@ -20423,7 +20423,7 @@
         <v>27</v>
       </c>
       <c r="D959">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E959" t="s">
         <v>28</v>
@@ -20440,7 +20440,7 @@
         <v>27</v>
       </c>
       <c r="D960">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E960" t="s">
         <v>28</v>
@@ -20457,7 +20457,7 @@
         <v>27</v>
       </c>
       <c r="D961">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E961" t="s">
         <v>28</v>
@@ -20474,7 +20474,7 @@
         <v>27</v>
       </c>
       <c r="D962">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E962" t="s">
         <v>28</v>
@@ -20491,7 +20491,7 @@
         <v>27</v>
       </c>
       <c r="D963">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E963" t="s">
         <v>28</v>
@@ -20508,7 +20508,7 @@
         <v>27</v>
       </c>
       <c r="D964">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E964" t="s">
         <v>28</v>
@@ -20525,7 +20525,7 @@
         <v>27</v>
       </c>
       <c r="D965">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E965" t="s">
         <v>28</v>
@@ -20542,7 +20542,7 @@
         <v>27</v>
       </c>
       <c r="D966">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E966" t="s">
         <v>28</v>
@@ -20559,7 +20559,7 @@
         <v>27</v>
       </c>
       <c r="D967">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E967" t="s">
         <v>28</v>
@@ -20576,7 +20576,7 @@
         <v>27</v>
       </c>
       <c r="D968">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E968" t="s">
         <v>28</v>
@@ -20593,7 +20593,7 @@
         <v>27</v>
       </c>
       <c r="D969">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E969" t="s">
         <v>28</v>
@@ -20610,7 +20610,7 @@
         <v>27</v>
       </c>
       <c r="D970">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E970" t="s">
         <v>28</v>
@@ -20627,7 +20627,7 @@
         <v>27</v>
       </c>
       <c r="D971">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E971" t="s">
         <v>28</v>
@@ -20661,7 +20661,7 @@
         <v>27</v>
       </c>
       <c r="D973">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E973" t="s">
         <v>28</v>
@@ -20678,7 +20678,7 @@
         <v>27</v>
       </c>
       <c r="D974">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E974" t="s">
         <v>28</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="D975">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E975" t="s">
         <v>28</v>
@@ -20712,7 +20712,7 @@
         <v>27</v>
       </c>
       <c r="D976">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E976" t="s">
         <v>28</v>
@@ -20729,7 +20729,7 @@
         <v>27</v>
       </c>
       <c r="D977">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E977" t="s">
         <v>28</v>
@@ -20746,7 +20746,7 @@
         <v>27</v>
       </c>
       <c r="D978">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E978" t="s">
         <v>28</v>
@@ -20763,7 +20763,7 @@
         <v>27</v>
       </c>
       <c r="D979">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E979" t="s">
         <v>28</v>
@@ -20780,7 +20780,7 @@
         <v>27</v>
       </c>
       <c r="D980">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E980" t="s">
         <v>28</v>
@@ -20797,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="D981">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E981" t="s">
         <v>28</v>
@@ -20814,7 +20814,7 @@
         <v>27</v>
       </c>
       <c r="D982">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E982" t="s">
         <v>28</v>
@@ -20831,7 +20831,7 @@
         <v>27</v>
       </c>
       <c r="D983">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E983" t="s">
         <v>28</v>
@@ -20848,7 +20848,7 @@
         <v>27</v>
       </c>
       <c r="D984">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E984" t="s">
         <v>28</v>
@@ -20865,7 +20865,7 @@
         <v>27</v>
       </c>
       <c r="D985">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E985" t="s">
         <v>28</v>
@@ -20882,7 +20882,7 @@
         <v>27</v>
       </c>
       <c r="D986">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E986" t="s">
         <v>28</v>
@@ -20899,7 +20899,7 @@
         <v>27</v>
       </c>
       <c r="D987">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E987" t="s">
         <v>28</v>
@@ -20916,7 +20916,7 @@
         <v>27</v>
       </c>
       <c r="D988">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E988" t="s">
         <v>28</v>
@@ -20933,7 +20933,7 @@
         <v>27</v>
       </c>
       <c r="D989">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E989" t="s">
         <v>28</v>
@@ -20950,7 +20950,7 @@
         <v>27</v>
       </c>
       <c r="D990">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E990" t="s">
         <v>28</v>
@@ -20967,7 +20967,7 @@
         <v>27</v>
       </c>
       <c r="D991">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E991" t="s">
         <v>28</v>
@@ -21001,7 +21001,7 @@
         <v>27</v>
       </c>
       <c r="D993">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E993" t="s">
         <v>28</v>
@@ -21018,7 +21018,7 @@
         <v>27</v>
       </c>
       <c r="D994">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E994" t="s">
         <v>28</v>
@@ -21035,7 +21035,7 @@
         <v>27</v>
       </c>
       <c r="D995">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E995" t="s">
         <v>28</v>
@@ -21052,7 +21052,7 @@
         <v>27</v>
       </c>
       <c r="D996">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E996" t="s">
         <v>28</v>
@@ -21069,7 +21069,7 @@
         <v>27</v>
       </c>
       <c r="D997">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E997" t="s">
         <v>28</v>
@@ -21086,7 +21086,7 @@
         <v>27</v>
       </c>
       <c r="D998">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E998" t="s">
         <v>28</v>
@@ -21103,7 +21103,7 @@
         <v>27</v>
       </c>
       <c r="D999">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E999" t="s">
         <v>28</v>
@@ -21120,7 +21120,7 @@
         <v>27</v>
       </c>
       <c r="D1000">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1000" t="s">
         <v>28</v>
@@ -21137,7 +21137,7 @@
         <v>27</v>
       </c>
       <c r="D1001">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1001" t="s">
         <v>28</v>
@@ -21154,7 +21154,7 @@
         <v>27</v>
       </c>
       <c r="D1002">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E1002" t="s">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>27</v>
       </c>
       <c r="D1003">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1003" t="s">
         <v>28</v>
@@ -21188,7 +21188,7 @@
         <v>27</v>
       </c>
       <c r="D1004">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1004" t="s">
         <v>28</v>
@@ -21205,7 +21205,7 @@
         <v>27</v>
       </c>
       <c r="D1005">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1005" t="s">
         <v>28</v>
@@ -21222,7 +21222,7 @@
         <v>27</v>
       </c>
       <c r="D1006">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E1006" t="s">
         <v>28</v>
@@ -21239,7 +21239,7 @@
         <v>27</v>
       </c>
       <c r="D1007">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1007" t="s">
         <v>28</v>
@@ -21256,7 +21256,7 @@
         <v>27</v>
       </c>
       <c r="D1008">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1008" t="s">
         <v>28</v>
@@ -21273,7 +21273,7 @@
         <v>27</v>
       </c>
       <c r="D1009">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1009" t="s">
         <v>28</v>
@@ -21290,7 +21290,7 @@
         <v>27</v>
       </c>
       <c r="D1010">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E1010" t="s">
         <v>28</v>
@@ -21307,7 +21307,7 @@
         <v>27</v>
       </c>
       <c r="D1011">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1011" t="s">
         <v>28</v>
@@ -21324,7 +21324,7 @@
         <v>27</v>
       </c>
       <c r="D1012">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1012" t="s">
         <v>28</v>
@@ -21341,7 +21341,7 @@
         <v>27</v>
       </c>
       <c r="D1013">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E1013" t="s">
         <v>28</v>
@@ -21358,7 +21358,7 @@
         <v>27</v>
       </c>
       <c r="D1014">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E1014" t="s">
         <v>28</v>
@@ -21375,7 +21375,7 @@
         <v>27</v>
       </c>
       <c r="D1015">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E1015" t="s">
         <v>28</v>
@@ -21392,7 +21392,7 @@
         <v>27</v>
       </c>
       <c r="D1016">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E1016" t="s">
         <v>28</v>
@@ -21409,7 +21409,7 @@
         <v>27</v>
       </c>
       <c r="D1017">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E1017" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>27</v>
       </c>
       <c r="D1018">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1018" t="s">
         <v>28</v>
@@ -21443,7 +21443,7 @@
         <v>27</v>
       </c>
       <c r="D1019">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E1019" t="s">
         <v>28</v>
@@ -21460,7 +21460,7 @@
         <v>27</v>
       </c>
       <c r="D1020">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1020" t="s">
         <v>28</v>
@@ -21477,7 +21477,7 @@
         <v>27</v>
       </c>
       <c r="D1021">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E1021" t="s">
         <v>28</v>
@@ -21494,7 +21494,7 @@
         <v>27</v>
       </c>
       <c r="D1022">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1022" t="s">
         <v>28</v>
@@ -21511,7 +21511,7 @@
         <v>27</v>
       </c>
       <c r="D1023">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1023" t="s">
         <v>28</v>
@@ -21528,7 +21528,7 @@
         <v>27</v>
       </c>
       <c r="D1024">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E1024" t="s">
         <v>28</v>
@@ -21545,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E1025" t="s">
         <v>28</v>
@@ -21562,7 +21562,7 @@
         <v>27</v>
       </c>
       <c r="D1026">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E1026" t="s">
         <v>28</v>
@@ -21579,7 +21579,7 @@
         <v>27</v>
       </c>
       <c r="D1027">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1027" t="s">
         <v>28</v>
@@ -21596,7 +21596,7 @@
         <v>27</v>
       </c>
       <c r="D1028">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E1028" t="s">
         <v>28</v>
@@ -21613,7 +21613,7 @@
         <v>27</v>
       </c>
       <c r="D1029">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E1029" t="s">
         <v>28</v>
@@ -21630,7 +21630,7 @@
         <v>27</v>
       </c>
       <c r="D1030">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1030" t="s">
         <v>28</v>
@@ -21647,7 +21647,7 @@
         <v>27</v>
       </c>
       <c r="D1031">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1031" t="s">
         <v>28</v>
@@ -21664,7 +21664,7 @@
         <v>27</v>
       </c>
       <c r="D1032">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1032" t="s">
         <v>28</v>
@@ -21681,7 +21681,7 @@
         <v>27</v>
       </c>
       <c r="D1033">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1033" t="s">
         <v>28</v>
@@ -21698,7 +21698,7 @@
         <v>27</v>
       </c>
       <c r="D1034">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1034" t="s">
         <v>28</v>
@@ -21715,7 +21715,7 @@
         <v>27</v>
       </c>
       <c r="D1035">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E1035" t="s">
         <v>28</v>
@@ -21732,7 +21732,7 @@
         <v>27</v>
       </c>
       <c r="D1036">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E1036" t="s">
         <v>28</v>
@@ -21749,7 +21749,7 @@
         <v>27</v>
       </c>
       <c r="D1037">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1037" t="s">
         <v>28</v>
@@ -21766,7 +21766,7 @@
         <v>27</v>
       </c>
       <c r="D1038">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1038" t="s">
         <v>28</v>
@@ -21783,7 +21783,7 @@
         <v>27</v>
       </c>
       <c r="D1039">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1039" t="s">
         <v>28</v>
@@ -21800,7 +21800,7 @@
         <v>27</v>
       </c>
       <c r="D1040">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E1040" t="s">
         <v>28</v>
@@ -21817,7 +21817,7 @@
         <v>27</v>
       </c>
       <c r="D1041">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1041" t="s">
         <v>28</v>
@@ -21834,7 +21834,7 @@
         <v>27</v>
       </c>
       <c r="D1042">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E1042" t="s">
         <v>28</v>
@@ -21851,7 +21851,7 @@
         <v>27</v>
       </c>
       <c r="D1043">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1043" t="s">
         <v>28</v>
@@ -21868,7 +21868,7 @@
         <v>27</v>
       </c>
       <c r="D1044">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1044" t="s">
         <v>28</v>
@@ -21885,7 +21885,7 @@
         <v>27</v>
       </c>
       <c r="D1045">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E1045" t="s">
         <v>28</v>
@@ -21902,7 +21902,7 @@
         <v>27</v>
       </c>
       <c r="D1046">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1046" t="s">
         <v>28</v>
@@ -21919,7 +21919,7 @@
         <v>27</v>
       </c>
       <c r="D1047">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1047" t="s">
         <v>28</v>
@@ -21936,7 +21936,7 @@
         <v>27</v>
       </c>
       <c r="D1048">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E1048" t="s">
         <v>28</v>
@@ -21953,7 +21953,7 @@
         <v>27</v>
       </c>
       <c r="D1049">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1049" t="s">
         <v>28</v>
@@ -21970,7 +21970,7 @@
         <v>27</v>
       </c>
       <c r="D1050">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E1050" t="s">
         <v>28</v>
@@ -21987,7 +21987,7 @@
         <v>27</v>
       </c>
       <c r="D1051">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E1051" t="s">
         <v>28</v>
@@ -22004,7 +22004,7 @@
         <v>27</v>
       </c>
       <c r="D1052">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E1052" t="s">
         <v>28</v>
@@ -22021,7 +22021,7 @@
         <v>27</v>
       </c>
       <c r="D1053">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1053" t="s">
         <v>28</v>
@@ -22038,7 +22038,7 @@
         <v>27</v>
       </c>
       <c r="D1054">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1054" t="s">
         <v>28</v>
@@ -22055,7 +22055,7 @@
         <v>27</v>
       </c>
       <c r="D1055">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E1055" t="s">
         <v>28</v>
@@ -22072,7 +22072,7 @@
         <v>27</v>
       </c>
       <c r="D1056">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E1056" t="s">
         <v>28</v>
@@ -22089,7 +22089,7 @@
         <v>27</v>
       </c>
       <c r="D1057">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E1057" t="s">
         <v>28</v>
@@ -22106,7 +22106,7 @@
         <v>27</v>
       </c>
       <c r="D1058">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1058" t="s">
         <v>28</v>
@@ -22123,7 +22123,7 @@
         <v>27</v>
       </c>
       <c r="D1059">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E1059" t="s">
         <v>28</v>
@@ -22140,7 +22140,7 @@
         <v>27</v>
       </c>
       <c r="D1060">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1060" t="s">
         <v>28</v>
@@ -22174,7 +22174,7 @@
         <v>27</v>
       </c>
       <c r="D1062">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1062" t="s">
         <v>28</v>
@@ -22191,7 +22191,7 @@
         <v>27</v>
       </c>
       <c r="D1063">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E1063" t="s">
         <v>28</v>
@@ -22208,7 +22208,7 @@
         <v>27</v>
       </c>
       <c r="D1064">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E1064" t="s">
         <v>28</v>
@@ -22225,7 +22225,7 @@
         <v>27</v>
       </c>
       <c r="D1065">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E1065" t="s">
         <v>28</v>
@@ -22242,7 +22242,7 @@
         <v>27</v>
       </c>
       <c r="D1066">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E1066" t="s">
         <v>28</v>
@@ -22259,7 +22259,7 @@
         <v>27</v>
       </c>
       <c r="D1067">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1067" t="s">
         <v>28</v>
@@ -22293,7 +22293,7 @@
         <v>27</v>
       </c>
       <c r="D1069">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E1069" t="s">
         <v>28</v>
@@ -22310,7 +22310,7 @@
         <v>27</v>
       </c>
       <c r="D1070">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E1070" t="s">
         <v>28</v>
@@ -22327,7 +22327,7 @@
         <v>27</v>
       </c>
       <c r="D1071">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E1071" t="s">
         <v>28</v>
@@ -22344,7 +22344,7 @@
         <v>27</v>
       </c>
       <c r="D1072">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1072" t="s">
         <v>28</v>
@@ -22361,7 +22361,7 @@
         <v>27</v>
       </c>
       <c r="D1073">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1073" t="s">
         <v>28</v>
@@ -22395,7 +22395,7 @@
         <v>27</v>
       </c>
       <c r="D1075">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E1075" t="s">
         <v>28</v>
@@ -22412,7 +22412,7 @@
         <v>27</v>
       </c>
       <c r="D1076">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1076" t="s">
         <v>28</v>
@@ -22429,7 +22429,7 @@
         <v>27</v>
       </c>
       <c r="D1077">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1077" t="s">
         <v>28</v>
@@ -22463,7 +22463,7 @@
         <v>27</v>
       </c>
       <c r="D1079">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E1079" t="s">
         <v>28</v>
@@ -22480,7 +22480,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E1080" t="s">
         <v>28</v>
@@ -22497,7 +22497,7 @@
         <v>27</v>
       </c>
       <c r="D1081">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E1081" t="s">
         <v>28</v>
@@ -22514,7 +22514,7 @@
         <v>27</v>
       </c>
       <c r="D1082">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E1082" t="s">
         <v>28</v>
@@ -22531,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="D1083">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1083" t="s">
         <v>28</v>
@@ -22548,7 +22548,7 @@
         <v>27</v>
       </c>
       <c r="D1084">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E1084" t="s">
         <v>28</v>
@@ -22565,7 +22565,7 @@
         <v>27</v>
       </c>
       <c r="D1085">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E1085" t="s">
         <v>28</v>
@@ -22582,7 +22582,7 @@
         <v>27</v>
       </c>
       <c r="D1086">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1086" t="s">
         <v>28</v>
@@ -22599,7 +22599,7 @@
         <v>27</v>
       </c>
       <c r="D1087">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E1087" t="s">
         <v>28</v>
@@ -22616,7 +22616,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E1088" t="s">
         <v>28</v>
@@ -22633,7 +22633,7 @@
         <v>27</v>
       </c>
       <c r="D1089">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1089" t="s">
         <v>28</v>
@@ -22650,7 +22650,7 @@
         <v>27</v>
       </c>
       <c r="D1090">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1090" t="s">
         <v>28</v>
@@ -22667,7 +22667,7 @@
         <v>27</v>
       </c>
       <c r="D1091">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1091" t="s">
         <v>28</v>
@@ -22684,7 +22684,7 @@
         <v>27</v>
       </c>
       <c r="D1092">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E1092" t="s">
         <v>28</v>
@@ -22701,7 +22701,7 @@
         <v>27</v>
       </c>
       <c r="D1093">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E1093" t="s">
         <v>28</v>
@@ -22718,7 +22718,7 @@
         <v>27</v>
       </c>
       <c r="D1094">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1094" t="s">
         <v>28</v>
@@ -22735,7 +22735,7 @@
         <v>27</v>
       </c>
       <c r="D1095">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1095" t="s">
         <v>28</v>
@@ -22752,7 +22752,7 @@
         <v>27</v>
       </c>
       <c r="D1096">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1096" t="s">
         <v>28</v>
@@ -22769,7 +22769,7 @@
         <v>27</v>
       </c>
       <c r="D1097">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1097" t="s">
         <v>28</v>
@@ -22786,7 +22786,7 @@
         <v>27</v>
       </c>
       <c r="D1098">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E1098" t="s">
         <v>28</v>
@@ -22803,7 +22803,7 @@
         <v>27</v>
       </c>
       <c r="D1099">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E1099" t="s">
         <v>28</v>
@@ -22820,7 +22820,7 @@
         <v>27</v>
       </c>
       <c r="D1100">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E1100" t="s">
         <v>28</v>
@@ -22837,7 +22837,7 @@
         <v>27</v>
       </c>
       <c r="D1101">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1101" t="s">
         <v>28</v>
@@ -22854,7 +22854,7 @@
         <v>27</v>
       </c>
       <c r="D1102">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E1102" t="s">
         <v>28</v>
@@ -22871,7 +22871,7 @@
         <v>27</v>
       </c>
       <c r="D1103">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E1103" t="s">
         <v>28</v>
@@ -22888,7 +22888,7 @@
         <v>27</v>
       </c>
       <c r="D1104">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1104" t="s">
         <v>28</v>
@@ -22905,7 +22905,7 @@
         <v>27</v>
       </c>
       <c r="D1105">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1105" t="s">
         <v>28</v>
@@ -22922,7 +22922,7 @@
         <v>27</v>
       </c>
       <c r="D1106">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E1106" t="s">
         <v>28</v>
@@ -22939,7 +22939,7 @@
         <v>27</v>
       </c>
       <c r="D1107">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1107" t="s">
         <v>28</v>
@@ -22956,7 +22956,7 @@
         <v>27</v>
       </c>
       <c r="D1108">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E1108" t="s">
         <v>28</v>
@@ -22973,7 +22973,7 @@
         <v>27</v>
       </c>
       <c r="D1109">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E1109" t="s">
         <v>28</v>
@@ -22990,7 +22990,7 @@
         <v>27</v>
       </c>
       <c r="D1110">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1110" t="s">
         <v>28</v>
@@ -23007,7 +23007,7 @@
         <v>27</v>
       </c>
       <c r="D1111">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E1111" t="s">
         <v>28</v>
@@ -23024,7 +23024,7 @@
         <v>27</v>
       </c>
       <c r="D1112">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E1112" t="s">
         <v>28</v>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1286</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1245</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1265</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1286</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1277</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1312</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1269</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1330</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1264</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1329</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1293</v>
+        <v>1346</v>
       </c>
     </row>
   </sheetData>
@@ -4154,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -4188,7 +4188,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -4205,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -4222,7 +4222,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -4256,7 +4256,7 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -4273,7 +4273,7 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4307,7 +4307,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4341,7 +4341,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -4358,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4409,7 +4409,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -4443,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -4460,7 +4460,7 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
@@ -4494,7 +4494,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -4511,7 +4511,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -4528,7 +4528,7 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -4545,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
         <v>28</v>
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -4579,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -4596,7 +4596,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -4613,7 +4613,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E29" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
         <v>28</v>
@@ -4647,7 +4647,7 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4681,7 +4681,7 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4698,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -4715,7 +4715,7 @@
         <v>27</v>
       </c>
       <c r="D35">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E35" t="s">
         <v>28</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -4749,7 +4749,7 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" t="s">
         <v>28</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="D38">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
         <v>28</v>
@@ -4783,7 +4783,7 @@
         <v>27</v>
       </c>
       <c r="D39">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E39" t="s">
         <v>28</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
@@ -4817,7 +4817,7 @@
         <v>27</v>
       </c>
       <c r="D41">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4834,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4851,7 +4851,7 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4885,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
         <v>27</v>
       </c>
       <c r="D46">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -4919,7 +4919,7 @@
         <v>27</v>
       </c>
       <c r="D47">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="D48">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4953,7 +4953,7 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
@@ -4970,7 +4970,7 @@
         <v>27</v>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -5004,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5038,7 +5038,7 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E54" t="s">
         <v>28</v>
@@ -5055,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="D55">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -5072,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
         <v>28</v>
@@ -5089,7 +5089,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E57" t="s">
         <v>28</v>
@@ -5106,7 +5106,7 @@
         <v>27</v>
       </c>
       <c r="D58">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -5123,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E59" t="s">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         <v>27</v>
       </c>
       <c r="D60">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E60" t="s">
         <v>28</v>
@@ -5157,7 +5157,7 @@
         <v>27</v>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -5174,7 +5174,7 @@
         <v>27</v>
       </c>
       <c r="D62">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="D64">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
@@ -5225,7 +5225,7 @@
         <v>27</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -5242,7 +5242,7 @@
         <v>27</v>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="D67">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
@@ -5293,7 +5293,7 @@
         <v>27</v>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -5310,7 +5310,7 @@
         <v>27</v>
       </c>
       <c r="D70">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="D71">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -5344,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="D72">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
@@ -5361,7 +5361,7 @@
         <v>27</v>
       </c>
       <c r="D73">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -5378,7 +5378,7 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
@@ -5395,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="D76">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
@@ -5429,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="D77">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -5446,7 +5446,7 @@
         <v>27</v>
       </c>
       <c r="D78">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
@@ -5463,7 +5463,7 @@
         <v>27</v>
       </c>
       <c r="D79">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
@@ -5480,7 +5480,7 @@
         <v>27</v>
       </c>
       <c r="D80">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
@@ -5497,7 +5497,7 @@
         <v>27</v>
       </c>
       <c r="D81">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -5514,7 +5514,7 @@
         <v>27</v>
       </c>
       <c r="D82">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
@@ -5531,7 +5531,7 @@
         <v>27</v>
       </c>
       <c r="D83">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
@@ -5548,7 +5548,7 @@
         <v>27</v>
       </c>
       <c r="D84">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
@@ -5565,7 +5565,7 @@
         <v>27</v>
       </c>
       <c r="D85">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -5582,7 +5582,7 @@
         <v>27</v>
       </c>
       <c r="D86">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
@@ -5599,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="D87">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
@@ -5616,7 +5616,7 @@
         <v>27</v>
       </c>
       <c r="D88">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -5633,7 +5633,7 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="D90">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -5684,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="D92">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
@@ -5718,7 +5718,7 @@
         <v>27</v>
       </c>
       <c r="D94">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E94" t="s">
         <v>28</v>
@@ -5735,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D95">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -5752,7 +5752,7 @@
         <v>27</v>
       </c>
       <c r="D96">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
         <v>28</v>
@@ -5769,7 +5769,7 @@
         <v>27</v>
       </c>
       <c r="D97">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E97" t="s">
         <v>28</v>
@@ -5786,7 +5786,7 @@
         <v>27</v>
       </c>
       <c r="D98">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="D99">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E99" t="s">
         <v>28</v>
@@ -5820,7 +5820,7 @@
         <v>27</v>
       </c>
       <c r="D100">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E100" t="s">
         <v>28</v>
@@ -5837,7 +5837,7 @@
         <v>27</v>
       </c>
       <c r="D101">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E101" t="s">
         <v>28</v>
@@ -5854,7 +5854,7 @@
         <v>27</v>
       </c>
       <c r="D102">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E102" t="s">
         <v>28</v>
@@ -5871,7 +5871,7 @@
         <v>27</v>
       </c>
       <c r="D103">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E103" t="s">
         <v>28</v>
@@ -5888,7 +5888,7 @@
         <v>27</v>
       </c>
       <c r="D104">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E104" t="s">
         <v>28</v>
@@ -5905,7 +5905,7 @@
         <v>27</v>
       </c>
       <c r="D105">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E105" t="s">
         <v>28</v>
@@ -5922,7 +5922,7 @@
         <v>27</v>
       </c>
       <c r="D106">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>27</v>
       </c>
       <c r="D107">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E107" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="D108">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5973,7 +5973,7 @@
         <v>27</v>
       </c>
       <c r="D109">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E109" t="s">
         <v>28</v>
@@ -5990,7 +5990,7 @@
         <v>27</v>
       </c>
       <c r="D110">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E110" t="s">
         <v>28</v>
@@ -6007,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="D111">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="D112">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
@@ -6058,7 +6058,7 @@
         <v>27</v>
       </c>
       <c r="D114">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>27</v>
       </c>
       <c r="D115">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -6092,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="D116">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E116" t="s">
         <v>28</v>
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="D117">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E117" t="s">
         <v>28</v>
@@ -6126,7 +6126,7 @@
         <v>27</v>
       </c>
       <c r="D118">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E118" t="s">
         <v>28</v>
@@ -6143,7 +6143,7 @@
         <v>27</v>
       </c>
       <c r="D119">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E119" t="s">
         <v>28</v>
@@ -6177,7 +6177,7 @@
         <v>27</v>
       </c>
       <c r="D121">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E121" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="D122">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E122" t="s">
         <v>28</v>
@@ -6211,7 +6211,7 @@
         <v>27</v>
       </c>
       <c r="D123">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E123" t="s">
         <v>28</v>
@@ -6228,7 +6228,7 @@
         <v>27</v>
       </c>
       <c r="D124">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E124" t="s">
         <v>28</v>
@@ -6245,7 +6245,7 @@
         <v>27</v>
       </c>
       <c r="D125">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
@@ -6262,7 +6262,7 @@
         <v>27</v>
       </c>
       <c r="D126">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -6296,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="D128">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E128" t="s">
         <v>28</v>
@@ -6313,7 +6313,7 @@
         <v>27</v>
       </c>
       <c r="D129">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
@@ -6330,7 +6330,7 @@
         <v>27</v>
       </c>
       <c r="D130">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E130" t="s">
         <v>28</v>
@@ -6347,7 +6347,7 @@
         <v>27</v>
       </c>
       <c r="D131">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E131" t="s">
         <v>28</v>
@@ -6381,7 +6381,7 @@
         <v>27</v>
       </c>
       <c r="D133">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E133" t="s">
         <v>28</v>
@@ -6398,7 +6398,7 @@
         <v>27</v>
       </c>
       <c r="D134">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E134" t="s">
         <v>28</v>
@@ -6415,7 +6415,7 @@
         <v>27</v>
       </c>
       <c r="D135">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E135" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="D136">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E136" t="s">
         <v>28</v>
@@ -6449,7 +6449,7 @@
         <v>27</v>
       </c>
       <c r="D137">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E137" t="s">
         <v>28</v>
@@ -6466,7 +6466,7 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E138" t="s">
         <v>28</v>
@@ -6500,7 +6500,7 @@
         <v>27</v>
       </c>
       <c r="D140">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E140" t="s">
         <v>28</v>
@@ -6517,7 +6517,7 @@
         <v>27</v>
       </c>
       <c r="D141">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E141" t="s">
         <v>28</v>
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="D142">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E142" t="s">
         <v>28</v>
@@ -6551,7 +6551,7 @@
         <v>27</v>
       </c>
       <c r="D143">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E143" t="s">
         <v>28</v>
@@ -6568,7 +6568,7 @@
         <v>27</v>
       </c>
       <c r="D144">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E144" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="D145">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E145" t="s">
         <v>28</v>
@@ -6619,7 +6619,7 @@
         <v>27</v>
       </c>
       <c r="D147">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E147" t="s">
         <v>28</v>
@@ -6636,7 +6636,7 @@
         <v>27</v>
       </c>
       <c r="D148">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E148" t="s">
         <v>28</v>
@@ -6653,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="D149">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6687,7 +6687,7 @@
         <v>27</v>
       </c>
       <c r="D151">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>27</v>
       </c>
       <c r="D152">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E152" t="s">
         <v>28</v>
@@ -6721,7 +6721,7 @@
         <v>27</v>
       </c>
       <c r="D153">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E153" t="s">
         <v>28</v>
@@ -6738,7 +6738,7 @@
         <v>27</v>
       </c>
       <c r="D154">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E154" t="s">
         <v>28</v>
@@ -6755,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -6789,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="D157">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E157" t="s">
         <v>28</v>
@@ -6806,7 +6806,7 @@
         <v>27</v>
       </c>
       <c r="D158">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E158" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="D159">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E159" t="s">
         <v>28</v>
@@ -6840,7 +6840,7 @@
         <v>27</v>
       </c>
       <c r="D160">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E160" t="s">
         <v>28</v>
@@ -6857,7 +6857,7 @@
         <v>27</v>
       </c>
       <c r="D161">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
@@ -6891,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="D163">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E163" t="s">
         <v>28</v>
@@ -6908,7 +6908,7 @@
         <v>27</v>
       </c>
       <c r="D164">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E164" t="s">
         <v>28</v>
@@ -6925,7 +6925,7 @@
         <v>27</v>
       </c>
       <c r="D165">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E165" t="s">
         <v>28</v>
@@ -6942,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="D166">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E166" t="s">
         <v>28</v>
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="D167">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E167" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="D168">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E168" t="s">
         <v>28</v>
@@ -6993,7 +6993,7 @@
         <v>27</v>
       </c>
       <c r="D169">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E169" t="s">
         <v>28</v>
@@ -7027,7 +7027,7 @@
         <v>27</v>
       </c>
       <c r="D171">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E171" t="s">
         <v>28</v>
@@ -7044,7 +7044,7 @@
         <v>27</v>
       </c>
       <c r="D172">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E172" t="s">
         <v>28</v>
@@ -7061,7 +7061,7 @@
         <v>27</v>
       </c>
       <c r="D173">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E173" t="s">
         <v>28</v>
@@ -7095,7 +7095,7 @@
         <v>27</v>
       </c>
       <c r="D175">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E175" t="s">
         <v>28</v>
@@ -7112,7 +7112,7 @@
         <v>27</v>
       </c>
       <c r="D176">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E176" t="s">
         <v>28</v>
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="D178">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E178" t="s">
         <v>28</v>
@@ -7163,7 +7163,7 @@
         <v>27</v>
       </c>
       <c r="D179">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E179" t="s">
         <v>28</v>
@@ -7180,7 +7180,7 @@
         <v>27</v>
       </c>
       <c r="D180">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -7197,7 +7197,7 @@
         <v>27</v>
       </c>
       <c r="D181">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E181" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="D182">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E182" t="s">
         <v>28</v>
@@ -7231,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="D183">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
@@ -7248,7 +7248,7 @@
         <v>27</v>
       </c>
       <c r="D184">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E184" t="s">
         <v>28</v>
@@ -7265,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="D185">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E185" t="s">
         <v>28</v>
@@ -7282,7 +7282,7 @@
         <v>27</v>
       </c>
       <c r="D186">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E186" t="s">
         <v>28</v>
@@ -7299,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="D187">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E187" t="s">
         <v>28</v>
@@ -7316,7 +7316,7 @@
         <v>27</v>
       </c>
       <c r="D188">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -7333,7 +7333,7 @@
         <v>27</v>
       </c>
       <c r="D189">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E189" t="s">
         <v>28</v>
@@ -7350,7 +7350,7 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E190" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="D191">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
@@ -7384,7 +7384,7 @@
         <v>27</v>
       </c>
       <c r="D192">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E192" t="s">
         <v>28</v>
@@ -7401,7 +7401,7 @@
         <v>27</v>
       </c>
       <c r="D193">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E193" t="s">
         <v>28</v>
@@ -7418,7 +7418,7 @@
         <v>27</v>
       </c>
       <c r="D194">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E194" t="s">
         <v>28</v>
@@ -7452,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="D196">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E196" t="s">
         <v>28</v>
@@ -7469,7 +7469,7 @@
         <v>27</v>
       </c>
       <c r="D197">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E197" t="s">
         <v>28</v>
@@ -7503,7 +7503,7 @@
         <v>27</v>
       </c>
       <c r="D199">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E199" t="s">
         <v>28</v>
@@ -7520,7 +7520,7 @@
         <v>27</v>
       </c>
       <c r="D200">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E200" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>27</v>
       </c>
       <c r="D201">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E201" t="s">
         <v>28</v>
@@ -7554,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="D202">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E202" t="s">
         <v>28</v>
@@ -7571,7 +7571,7 @@
         <v>27</v>
       </c>
       <c r="D203">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
@@ -7588,7 +7588,7 @@
         <v>27</v>
       </c>
       <c r="D204">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E204" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="D205">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -7622,7 +7622,7 @@
         <v>27</v>
       </c>
       <c r="D206">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E206" t="s">
         <v>28</v>
@@ -7639,7 +7639,7 @@
         <v>27</v>
       </c>
       <c r="D207">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E207" t="s">
         <v>28</v>
@@ -7656,7 +7656,7 @@
         <v>27</v>
       </c>
       <c r="D208">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E208" t="s">
         <v>28</v>
@@ -7673,7 +7673,7 @@
         <v>27</v>
       </c>
       <c r="D209">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E209" t="s">
         <v>28</v>
@@ -7690,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="D210">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E210" t="s">
         <v>28</v>
@@ -7707,7 +7707,7 @@
         <v>27</v>
       </c>
       <c r="D211">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E211" t="s">
         <v>28</v>
@@ -7724,7 +7724,7 @@
         <v>27</v>
       </c>
       <c r="D212">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E212" t="s">
         <v>28</v>
@@ -7741,7 +7741,7 @@
         <v>27</v>
       </c>
       <c r="D213">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E213" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="D214">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E214" t="s">
         <v>28</v>
@@ -7775,7 +7775,7 @@
         <v>27</v>
       </c>
       <c r="D215">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E215" t="s">
         <v>28</v>
@@ -7792,7 +7792,7 @@
         <v>27</v>
       </c>
       <c r="D216">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E216" t="s">
         <v>28</v>
@@ -7809,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="D217">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E217" t="s">
         <v>28</v>
@@ -7826,7 +7826,7 @@
         <v>27</v>
       </c>
       <c r="D218">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E218" t="s">
         <v>28</v>
@@ -7843,7 +7843,7 @@
         <v>27</v>
       </c>
       <c r="D219">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E219" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="D220">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E220" t="s">
         <v>28</v>
@@ -7877,7 +7877,7 @@
         <v>27</v>
       </c>
       <c r="D221">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E221" t="s">
         <v>28</v>
@@ -7894,7 +7894,7 @@
         <v>27</v>
       </c>
       <c r="D222">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E222" t="s">
         <v>28</v>
@@ -7911,7 +7911,7 @@
         <v>27</v>
       </c>
       <c r="D223">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E223" t="s">
         <v>28</v>
@@ -7928,7 +7928,7 @@
         <v>27</v>
       </c>
       <c r="D224">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E224" t="s">
         <v>28</v>
@@ -7945,7 +7945,7 @@
         <v>27</v>
       </c>
       <c r="D225">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E225" t="s">
         <v>28</v>
@@ -7962,7 +7962,7 @@
         <v>27</v>
       </c>
       <c r="D226">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E226" t="s">
         <v>28</v>
@@ -7979,7 +7979,7 @@
         <v>27</v>
       </c>
       <c r="D227">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E227" t="s">
         <v>28</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="D228">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E228" t="s">
         <v>28</v>
@@ -8013,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="D229">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E229" t="s">
         <v>28</v>
@@ -8030,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="D230">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E230" t="s">
         <v>28</v>
@@ -8047,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="D231">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E231" t="s">
         <v>28</v>
@@ -8064,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="D232">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E232" t="s">
         <v>28</v>
@@ -8081,7 +8081,7 @@
         <v>27</v>
       </c>
       <c r="D233">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E233" t="s">
         <v>28</v>
@@ -8098,7 +8098,7 @@
         <v>27</v>
       </c>
       <c r="D234">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E234" t="s">
         <v>28</v>
@@ -8115,7 +8115,7 @@
         <v>27</v>
       </c>
       <c r="D235">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E235" t="s">
         <v>28</v>
@@ -8132,7 +8132,7 @@
         <v>27</v>
       </c>
       <c r="D236">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E236" t="s">
         <v>28</v>
@@ -8166,7 +8166,7 @@
         <v>27</v>
       </c>
       <c r="D238">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E238" t="s">
         <v>28</v>
@@ -8183,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="D239">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E239" t="s">
         <v>28</v>
@@ -8200,7 +8200,7 @@
         <v>27</v>
       </c>
       <c r="D240">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E240" t="s">
         <v>28</v>
@@ -8217,7 +8217,7 @@
         <v>27</v>
       </c>
       <c r="D241">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E241" t="s">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>27</v>
       </c>
       <c r="D242">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E242" t="s">
         <v>28</v>
@@ -8251,7 +8251,7 @@
         <v>27</v>
       </c>
       <c r="D243">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E243" t="s">
         <v>28</v>
@@ -8268,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="D244">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E244" t="s">
         <v>28</v>
@@ -8285,7 +8285,7 @@
         <v>27</v>
       </c>
       <c r="D245">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E245" t="s">
         <v>28</v>
@@ -8302,7 +8302,7 @@
         <v>27</v>
       </c>
       <c r="D246">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E246" t="s">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="D247">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E247" t="s">
         <v>28</v>
@@ -8336,7 +8336,7 @@
         <v>27</v>
       </c>
       <c r="D248">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E248" t="s">
         <v>28</v>
@@ -8353,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="D249">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E249" t="s">
         <v>28</v>
@@ -8370,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="D250">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E250" t="s">
         <v>28</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="D251">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E251" t="s">
         <v>28</v>
@@ -8404,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="D252">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E252" t="s">
         <v>28</v>
@@ -8421,7 +8421,7 @@
         <v>27</v>
       </c>
       <c r="D253">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E253" t="s">
         <v>28</v>
@@ -8438,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D254">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E254" t="s">
         <v>28</v>
@@ -8455,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="D255">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E255" t="s">
         <v>28</v>
@@ -8472,7 +8472,7 @@
         <v>27</v>
       </c>
       <c r="D256">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E256" t="s">
         <v>28</v>
@@ -8489,7 +8489,7 @@
         <v>27</v>
       </c>
       <c r="D257">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E257" t="s">
         <v>28</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="D258">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E258" t="s">
         <v>28</v>
@@ -8523,7 +8523,7 @@
         <v>27</v>
       </c>
       <c r="D259">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E259" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="D260">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E260" t="s">
         <v>28</v>
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="D261">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E261" t="s">
         <v>28</v>
@@ -8574,7 +8574,7 @@
         <v>27</v>
       </c>
       <c r="D262">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E262" t="s">
         <v>28</v>
@@ -8591,7 +8591,7 @@
         <v>27</v>
       </c>
       <c r="D263">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E263" t="s">
         <v>28</v>
@@ -8608,7 +8608,7 @@
         <v>27</v>
       </c>
       <c r="D264">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E264" t="s">
         <v>28</v>
@@ -8625,7 +8625,7 @@
         <v>27</v>
       </c>
       <c r="D265">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E265" t="s">
         <v>28</v>
@@ -8642,7 +8642,7 @@
         <v>27</v>
       </c>
       <c r="D266">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E266" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="D267">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E267" t="s">
         <v>28</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="D268">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E268" t="s">
         <v>28</v>
@@ -8693,7 +8693,7 @@
         <v>27</v>
       </c>
       <c r="D269">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E269" t="s">
         <v>28</v>
@@ -8710,7 +8710,7 @@
         <v>27</v>
       </c>
       <c r="D270">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E270" t="s">
         <v>28</v>
@@ -8727,7 +8727,7 @@
         <v>27</v>
       </c>
       <c r="D271">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E271" t="s">
         <v>28</v>
@@ -8744,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="D272">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E272" t="s">
         <v>28</v>
@@ -8761,7 +8761,7 @@
         <v>27</v>
       </c>
       <c r="D273">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E273" t="s">
         <v>28</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="D274">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E274" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>27</v>
       </c>
       <c r="D275">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E275" t="s">
         <v>28</v>
@@ -8812,7 +8812,7 @@
         <v>27</v>
       </c>
       <c r="D276">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E276" t="s">
         <v>28</v>
@@ -8829,7 +8829,7 @@
         <v>27</v>
       </c>
       <c r="D277">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E277" t="s">
         <v>28</v>
@@ -8846,7 +8846,7 @@
         <v>27</v>
       </c>
       <c r="D278">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E278" t="s">
         <v>28</v>
@@ -8863,7 +8863,7 @@
         <v>27</v>
       </c>
       <c r="D279">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E279" t="s">
         <v>28</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E280" t="s">
         <v>28</v>
@@ -8897,7 +8897,7 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E281" t="s">
         <v>28</v>
@@ -8914,7 +8914,7 @@
         <v>27</v>
       </c>
       <c r="D282">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E282" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="D283">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E283" t="s">
         <v>28</v>
@@ -8948,7 +8948,7 @@
         <v>27</v>
       </c>
       <c r="D284">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E284" t="s">
         <v>28</v>
@@ -8965,7 +8965,7 @@
         <v>27</v>
       </c>
       <c r="D285">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E285" t="s">
         <v>28</v>
@@ -8982,7 +8982,7 @@
         <v>27</v>
       </c>
       <c r="D286">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E286" t="s">
         <v>28</v>
@@ -8999,7 +8999,7 @@
         <v>27</v>
       </c>
       <c r="D287">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E287" t="s">
         <v>28</v>
@@ -9016,7 +9016,7 @@
         <v>27</v>
       </c>
       <c r="D288">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E288" t="s">
         <v>28</v>
@@ -9033,7 +9033,7 @@
         <v>27</v>
       </c>
       <c r="D289">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E289" t="s">
         <v>28</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="D290">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E290" t="s">
         <v>28</v>
@@ -9067,7 +9067,7 @@
         <v>27</v>
       </c>
       <c r="D291">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E291" t="s">
         <v>28</v>
@@ -9084,7 +9084,7 @@
         <v>27</v>
       </c>
       <c r="D292">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E292" t="s">
         <v>28</v>
@@ -9101,7 +9101,7 @@
         <v>27</v>
       </c>
       <c r="D293">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E293" t="s">
         <v>28</v>
@@ -9118,7 +9118,7 @@
         <v>27</v>
       </c>
       <c r="D294">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E294" t="s">
         <v>28</v>
@@ -9135,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="D295">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E295" t="s">
         <v>28</v>
@@ -9152,7 +9152,7 @@
         <v>27</v>
       </c>
       <c r="D296">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E296" t="s">
         <v>28</v>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="D298">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E298" t="s">
         <v>28</v>
@@ -9203,7 +9203,7 @@
         <v>27</v>
       </c>
       <c r="D299">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E299" t="s">
         <v>28</v>
@@ -9220,7 +9220,7 @@
         <v>27</v>
       </c>
       <c r="D300">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E300" t="s">
         <v>28</v>
@@ -9237,7 +9237,7 @@
         <v>27</v>
       </c>
       <c r="D301">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E301" t="s">
         <v>28</v>
@@ -9254,7 +9254,7 @@
         <v>27</v>
       </c>
       <c r="D302">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E302" t="s">
         <v>28</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="D304">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E304" t="s">
         <v>28</v>
@@ -9305,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="D305">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E305" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="D306">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E306" t="s">
         <v>28</v>
@@ -9339,7 +9339,7 @@
         <v>27</v>
       </c>
       <c r="D307">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E307" t="s">
         <v>28</v>
@@ -9356,7 +9356,7 @@
         <v>27</v>
       </c>
       <c r="D308">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E308" t="s">
         <v>28</v>
@@ -9373,7 +9373,7 @@
         <v>27</v>
       </c>
       <c r="D309">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E309" t="s">
         <v>28</v>
@@ -9390,7 +9390,7 @@
         <v>27</v>
       </c>
       <c r="D310">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E310" t="s">
         <v>28</v>
@@ -9424,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="D312">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E312" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="D313">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E313" t="s">
         <v>28</v>
@@ -9458,7 +9458,7 @@
         <v>27</v>
       </c>
       <c r="D314">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E314" t="s">
         <v>28</v>
@@ -9475,7 +9475,7 @@
         <v>27</v>
       </c>
       <c r="D315">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E315" t="s">
         <v>28</v>
@@ -9492,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="D316">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E316" t="s">
         <v>28</v>
@@ -9509,7 +9509,7 @@
         <v>27</v>
       </c>
       <c r="D317">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E317" t="s">
         <v>28</v>
@@ -9526,7 +9526,7 @@
         <v>27</v>
       </c>
       <c r="D318">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E318" t="s">
         <v>28</v>
@@ -9543,7 +9543,7 @@
         <v>27</v>
       </c>
       <c r="D319">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E319" t="s">
         <v>28</v>
@@ -9560,7 +9560,7 @@
         <v>27</v>
       </c>
       <c r="D320">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E320" t="s">
         <v>28</v>
@@ -9577,7 +9577,7 @@
         <v>27</v>
       </c>
       <c r="D321">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E321" t="s">
         <v>28</v>
@@ -9594,7 +9594,7 @@
         <v>27</v>
       </c>
       <c r="D322">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E322" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
         <v>27</v>
       </c>
       <c r="D323">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E323" t="s">
         <v>28</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="D324">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E324" t="s">
         <v>28</v>
@@ -9645,7 +9645,7 @@
         <v>27</v>
       </c>
       <c r="D325">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E325" t="s">
         <v>28</v>
@@ -9662,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="D326">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E326" t="s">
         <v>28</v>
@@ -9679,7 +9679,7 @@
         <v>27</v>
       </c>
       <c r="D327">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E327" t="s">
         <v>28</v>
@@ -9696,7 +9696,7 @@
         <v>27</v>
       </c>
       <c r="D328">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E328" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="D329">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E329" t="s">
         <v>28</v>
@@ -9730,7 +9730,7 @@
         <v>27</v>
       </c>
       <c r="D330">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E330" t="s">
         <v>28</v>
@@ -9747,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="D331">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E331" t="s">
         <v>28</v>
@@ -9764,7 +9764,7 @@
         <v>27</v>
       </c>
       <c r="D332">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E332" t="s">
         <v>28</v>
@@ -9781,7 +9781,7 @@
         <v>27</v>
       </c>
       <c r="D333">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E333" t="s">
         <v>28</v>
@@ -9798,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="D334">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E334" t="s">
         <v>28</v>
@@ -9815,7 +9815,7 @@
         <v>27</v>
       </c>
       <c r="D335">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E335" t="s">
         <v>28</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="D336">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E336" t="s">
         <v>28</v>
@@ -9849,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="D337">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E337" t="s">
         <v>28</v>
@@ -9866,7 +9866,7 @@
         <v>27</v>
       </c>
       <c r="D338">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E338" t="s">
         <v>28</v>
@@ -9883,7 +9883,7 @@
         <v>27</v>
       </c>
       <c r="D339">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E339" t="s">
         <v>28</v>
@@ -9900,7 +9900,7 @@
         <v>27</v>
       </c>
       <c r="D340">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E340" t="s">
         <v>28</v>
@@ -9917,7 +9917,7 @@
         <v>27</v>
       </c>
       <c r="D341">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E341" t="s">
         <v>28</v>
@@ -9934,7 +9934,7 @@
         <v>27</v>
       </c>
       <c r="D342">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E342" t="s">
         <v>28</v>
@@ -9951,7 +9951,7 @@
         <v>27</v>
       </c>
       <c r="D343">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E343" t="s">
         <v>28</v>
@@ -9968,7 +9968,7 @@
         <v>27</v>
       </c>
       <c r="D344">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E344" t="s">
         <v>28</v>
@@ -9985,7 +9985,7 @@
         <v>27</v>
       </c>
       <c r="D345">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E345" t="s">
         <v>28</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D346">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E346" t="s">
         <v>28</v>
@@ -10019,7 +10019,7 @@
         <v>27</v>
       </c>
       <c r="D347">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E347" t="s">
         <v>28</v>
@@ -10053,7 +10053,7 @@
         <v>27</v>
       </c>
       <c r="D349">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E349" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="D350">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E350" t="s">
         <v>28</v>
@@ -10087,7 +10087,7 @@
         <v>27</v>
       </c>
       <c r="D351">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E351" t="s">
         <v>28</v>
@@ -10104,7 +10104,7 @@
         <v>27</v>
       </c>
       <c r="D352">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E352" t="s">
         <v>28</v>
@@ -10121,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D353">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E353" t="s">
         <v>28</v>
@@ -10138,7 +10138,7 @@
         <v>27</v>
       </c>
       <c r="D354">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E354" t="s">
         <v>28</v>
@@ -10155,7 +10155,7 @@
         <v>27</v>
       </c>
       <c r="D355">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E355" t="s">
         <v>28</v>
@@ -10172,7 +10172,7 @@
         <v>27</v>
       </c>
       <c r="D356">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E356" t="s">
         <v>28</v>
@@ -10189,7 +10189,7 @@
         <v>27</v>
       </c>
       <c r="D357">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E357" t="s">
         <v>28</v>
@@ -10206,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="D358">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E358" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="D359">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E359" t="s">
         <v>28</v>
@@ -10240,7 +10240,7 @@
         <v>27</v>
       </c>
       <c r="D360">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E360" t="s">
         <v>28</v>
@@ -10257,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="D361">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E361" t="s">
         <v>28</v>
@@ -10274,7 +10274,7 @@
         <v>27</v>
       </c>
       <c r="D362">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E362" t="s">
         <v>28</v>
@@ -10291,7 +10291,7 @@
         <v>27</v>
       </c>
       <c r="D363">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E363" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="D364">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E364" t="s">
         <v>28</v>
@@ -10325,7 +10325,7 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E365" t="s">
         <v>28</v>
@@ -10342,7 +10342,7 @@
         <v>27</v>
       </c>
       <c r="D366">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E366" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
         <v>27</v>
       </c>
       <c r="D367">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E367" t="s">
         <v>28</v>
@@ -10376,7 +10376,7 @@
         <v>27</v>
       </c>
       <c r="D368">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E368" t="s">
         <v>28</v>
@@ -10393,7 +10393,7 @@
         <v>27</v>
       </c>
       <c r="D369">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E369" t="s">
         <v>28</v>
@@ -10410,7 +10410,7 @@
         <v>27</v>
       </c>
       <c r="D370">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E370" t="s">
         <v>28</v>
@@ -10427,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="D371">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E371" t="s">
         <v>28</v>
@@ -10444,7 +10444,7 @@
         <v>27</v>
       </c>
       <c r="D372">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E372" t="s">
         <v>28</v>
@@ -10461,7 +10461,7 @@
         <v>27</v>
       </c>
       <c r="D373">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E373" t="s">
         <v>28</v>
@@ -10478,7 +10478,7 @@
         <v>27</v>
       </c>
       <c r="D374">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E374" t="s">
         <v>28</v>
@@ -10495,7 +10495,7 @@
         <v>27</v>
       </c>
       <c r="D375">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E375" t="s">
         <v>28</v>
@@ -10512,7 +10512,7 @@
         <v>27</v>
       </c>
       <c r="D376">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E376" t="s">
         <v>28</v>
@@ -10529,7 +10529,7 @@
         <v>27</v>
       </c>
       <c r="D377">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E377" t="s">
         <v>28</v>
@@ -10546,7 +10546,7 @@
         <v>27</v>
       </c>
       <c r="D378">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E378" t="s">
         <v>28</v>
@@ -10563,7 +10563,7 @@
         <v>27</v>
       </c>
       <c r="D379">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E379" t="s">
         <v>28</v>
@@ -10580,7 +10580,7 @@
         <v>27</v>
       </c>
       <c r="D380">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E380" t="s">
         <v>28</v>
@@ -10597,7 +10597,7 @@
         <v>27</v>
       </c>
       <c r="D381">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E381" t="s">
         <v>28</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="D382">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E382" t="s">
         <v>28</v>
@@ -10631,7 +10631,7 @@
         <v>27</v>
       </c>
       <c r="D383">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E383" t="s">
         <v>28</v>
@@ -10648,7 +10648,7 @@
         <v>27</v>
       </c>
       <c r="D384">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E384" t="s">
         <v>28</v>
@@ -10665,7 +10665,7 @@
         <v>27</v>
       </c>
       <c r="D385">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E385" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="D387">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E387" t="s">
         <v>28</v>
@@ -10716,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="D388">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E388" t="s">
         <v>28</v>
@@ -10733,7 +10733,7 @@
         <v>27</v>
       </c>
       <c r="D389">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E389" t="s">
         <v>28</v>
@@ -10750,7 +10750,7 @@
         <v>27</v>
       </c>
       <c r="D390">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E390" t="s">
         <v>28</v>
@@ -10767,7 +10767,7 @@
         <v>27</v>
       </c>
       <c r="D391">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E391" t="s">
         <v>28</v>
@@ -10784,7 +10784,7 @@
         <v>27</v>
       </c>
       <c r="D392">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E392" t="s">
         <v>28</v>
@@ -10801,7 +10801,7 @@
         <v>27</v>
       </c>
       <c r="D393">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E393" t="s">
         <v>28</v>
@@ -10818,7 +10818,7 @@
         <v>27</v>
       </c>
       <c r="D394">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E394" t="s">
         <v>28</v>
@@ -10835,7 +10835,7 @@
         <v>27</v>
       </c>
       <c r="D395">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E395" t="s">
         <v>28</v>
@@ -10852,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="D396">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E396" t="s">
         <v>28</v>
@@ -10869,7 +10869,7 @@
         <v>27</v>
       </c>
       <c r="D397">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E397" t="s">
         <v>28</v>
@@ -10903,7 +10903,7 @@
         <v>27</v>
       </c>
       <c r="D399">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E399" t="s">
         <v>28</v>
@@ -10920,7 +10920,7 @@
         <v>27</v>
       </c>
       <c r="D400">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E400" t="s">
         <v>28</v>
@@ -10937,7 +10937,7 @@
         <v>27</v>
       </c>
       <c r="D401">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E401" t="s">
         <v>28</v>
@@ -10954,7 +10954,7 @@
         <v>27</v>
       </c>
       <c r="D402">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E402" t="s">
         <v>28</v>
@@ -10971,7 +10971,7 @@
         <v>27</v>
       </c>
       <c r="D403">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E403" t="s">
         <v>28</v>
@@ -10988,7 +10988,7 @@
         <v>27</v>
       </c>
       <c r="D404">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E404" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="D405">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E405" t="s">
         <v>28</v>
@@ -11022,7 +11022,7 @@
         <v>27</v>
       </c>
       <c r="D406">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E406" t="s">
         <v>28</v>
@@ -11056,7 +11056,7 @@
         <v>27</v>
       </c>
       <c r="D408">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E408" t="s">
         <v>28</v>
@@ -11073,7 +11073,7 @@
         <v>27</v>
       </c>
       <c r="D409">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E409" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="D410">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E410" t="s">
         <v>28</v>
@@ -11107,7 +11107,7 @@
         <v>27</v>
       </c>
       <c r="D411">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E411" t="s">
         <v>28</v>
@@ -11124,7 +11124,7 @@
         <v>27</v>
       </c>
       <c r="D412">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E412" t="s">
         <v>28</v>
@@ -11141,7 +11141,7 @@
         <v>27</v>
       </c>
       <c r="D413">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E413" t="s">
         <v>28</v>
@@ -11158,7 +11158,7 @@
         <v>27</v>
       </c>
       <c r="D414">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E414" t="s">
         <v>28</v>
@@ -11175,7 +11175,7 @@
         <v>27</v>
       </c>
       <c r="D415">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E415" t="s">
         <v>28</v>
@@ -11192,7 +11192,7 @@
         <v>27</v>
       </c>
       <c r="D416">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E416" t="s">
         <v>28</v>
@@ -11209,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="D417">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E417" t="s">
         <v>28</v>
@@ -11226,7 +11226,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E418" t="s">
         <v>28</v>
@@ -11243,7 +11243,7 @@
         <v>27</v>
       </c>
       <c r="D419">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E419" t="s">
         <v>28</v>
@@ -11260,7 +11260,7 @@
         <v>27</v>
       </c>
       <c r="D420">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E420" t="s">
         <v>28</v>
@@ -11277,7 +11277,7 @@
         <v>27</v>
       </c>
       <c r="D421">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E421" t="s">
         <v>28</v>
@@ -11294,7 +11294,7 @@
         <v>27</v>
       </c>
       <c r="D422">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E422" t="s">
         <v>28</v>
@@ -11311,7 +11311,7 @@
         <v>27</v>
       </c>
       <c r="D423">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E423" t="s">
         <v>28</v>
@@ -11328,7 +11328,7 @@
         <v>27</v>
       </c>
       <c r="D424">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E424" t="s">
         <v>28</v>
@@ -11345,7 +11345,7 @@
         <v>27</v>
       </c>
       <c r="D425">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E425" t="s">
         <v>28</v>
@@ -11362,7 +11362,7 @@
         <v>27</v>
       </c>
       <c r="D426">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E426" t="s">
         <v>28</v>
@@ -11379,7 +11379,7 @@
         <v>27</v>
       </c>
       <c r="D427">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E427" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="D428">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E428" t="s">
         <v>28</v>
@@ -11413,7 +11413,7 @@
         <v>27</v>
       </c>
       <c r="D429">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E429" t="s">
         <v>28</v>
@@ -11430,7 +11430,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E430" t="s">
         <v>28</v>
@@ -11447,7 +11447,7 @@
         <v>27</v>
       </c>
       <c r="D431">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E431" t="s">
         <v>28</v>
@@ -11464,7 +11464,7 @@
         <v>27</v>
       </c>
       <c r="D432">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E432" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="D433">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E433" t="s">
         <v>28</v>
@@ -11498,7 +11498,7 @@
         <v>27</v>
       </c>
       <c r="D434">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E434" t="s">
         <v>28</v>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="D435">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E435" t="s">
         <v>28</v>
@@ -11532,7 +11532,7 @@
         <v>27</v>
       </c>
       <c r="D436">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E436" t="s">
         <v>28</v>
@@ -11549,7 +11549,7 @@
         <v>27</v>
       </c>
       <c r="D437">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E437" t="s">
         <v>28</v>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
       <c r="D438">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E438" t="s">
         <v>28</v>
@@ -11583,7 +11583,7 @@
         <v>27</v>
       </c>
       <c r="D439">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E439" t="s">
         <v>28</v>
@@ -11600,7 +11600,7 @@
         <v>27</v>
       </c>
       <c r="D440">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E440" t="s">
         <v>28</v>
@@ -11634,7 +11634,7 @@
         <v>27</v>
       </c>
       <c r="D442">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E442" t="s">
         <v>28</v>
@@ -11651,7 +11651,7 @@
         <v>27</v>
       </c>
       <c r="D443">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E443" t="s">
         <v>28</v>
@@ -11668,7 +11668,7 @@
         <v>27</v>
       </c>
       <c r="D444">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E444" t="s">
         <v>28</v>
@@ -11685,7 +11685,7 @@
         <v>27</v>
       </c>
       <c r="D445">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E445" t="s">
         <v>28</v>
@@ -11702,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D446">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E446" t="s">
         <v>28</v>
@@ -11719,7 +11719,7 @@
         <v>27</v>
       </c>
       <c r="D447">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E447" t="s">
         <v>28</v>
@@ -11736,7 +11736,7 @@
         <v>27</v>
       </c>
       <c r="D448">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E448" t="s">
         <v>28</v>
@@ -11753,7 +11753,7 @@
         <v>27</v>
       </c>
       <c r="D449">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E449" t="s">
         <v>28</v>
@@ -11770,7 +11770,7 @@
         <v>27</v>
       </c>
       <c r="D450">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E450" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="D451">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E451" t="s">
         <v>28</v>
@@ -11804,7 +11804,7 @@
         <v>27</v>
       </c>
       <c r="D452">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E452" t="s">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>27</v>
       </c>
       <c r="D453">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E453" t="s">
         <v>28</v>
@@ -11838,7 +11838,7 @@
         <v>27</v>
       </c>
       <c r="D454">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E454" t="s">
         <v>28</v>
@@ -11855,7 +11855,7 @@
         <v>27</v>
       </c>
       <c r="D455">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E455" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="D456">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E456" t="s">
         <v>28</v>
@@ -11889,7 +11889,7 @@
         <v>27</v>
       </c>
       <c r="D457">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E457" t="s">
         <v>28</v>
@@ -11906,7 +11906,7 @@
         <v>27</v>
       </c>
       <c r="D458">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E458" t="s">
         <v>28</v>
@@ -11923,7 +11923,7 @@
         <v>27</v>
       </c>
       <c r="D459">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E459" t="s">
         <v>28</v>
@@ -11940,7 +11940,7 @@
         <v>27</v>
       </c>
       <c r="D460">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E460" t="s">
         <v>28</v>
@@ -11957,7 +11957,7 @@
         <v>27</v>
       </c>
       <c r="D461">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E461" t="s">
         <v>28</v>
@@ -11974,7 +11974,7 @@
         <v>27</v>
       </c>
       <c r="D462">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E462" t="s">
         <v>28</v>
@@ -11991,7 +11991,7 @@
         <v>27</v>
       </c>
       <c r="D463">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E463" t="s">
         <v>28</v>
@@ -12008,7 +12008,7 @@
         <v>27</v>
       </c>
       <c r="D464">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E464" t="s">
         <v>28</v>
@@ -12025,7 +12025,7 @@
         <v>27</v>
       </c>
       <c r="D465">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E465" t="s">
         <v>28</v>
@@ -12042,7 +12042,7 @@
         <v>27</v>
       </c>
       <c r="D466">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E466" t="s">
         <v>28</v>
@@ -12059,7 +12059,7 @@
         <v>27</v>
       </c>
       <c r="D467">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E467" t="s">
         <v>28</v>
@@ -12076,7 +12076,7 @@
         <v>27</v>
       </c>
       <c r="D468">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E468" t="s">
         <v>28</v>
@@ -12093,7 +12093,7 @@
         <v>27</v>
       </c>
       <c r="D469">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E469" t="s">
         <v>28</v>
@@ -12110,7 +12110,7 @@
         <v>27</v>
       </c>
       <c r="D470">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E470" t="s">
         <v>28</v>
@@ -12127,7 +12127,7 @@
         <v>27</v>
       </c>
       <c r="D471">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E471" t="s">
         <v>28</v>
@@ -12144,7 +12144,7 @@
         <v>27</v>
       </c>
       <c r="D472">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E472" t="s">
         <v>28</v>
@@ -12161,7 +12161,7 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E473" t="s">
         <v>28</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="D474">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E474" t="s">
         <v>28</v>
@@ -12195,7 +12195,7 @@
         <v>27</v>
       </c>
       <c r="D475">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E475" t="s">
         <v>28</v>
@@ -12212,7 +12212,7 @@
         <v>27</v>
       </c>
       <c r="D476">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E476" t="s">
         <v>28</v>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
       <c r="D477">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E477" t="s">
         <v>28</v>
@@ -12246,7 +12246,7 @@
         <v>27</v>
       </c>
       <c r="D478">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E478" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="D479">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E479" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="D480">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E480" t="s">
         <v>28</v>
@@ -12297,7 +12297,7 @@
         <v>27</v>
       </c>
       <c r="D481">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E481" t="s">
         <v>28</v>
@@ -12314,7 +12314,7 @@
         <v>27</v>
       </c>
       <c r="D482">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E482" t="s">
         <v>28</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="D483">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E483" t="s">
         <v>28</v>
@@ -12348,7 +12348,7 @@
         <v>27</v>
       </c>
       <c r="D484">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E484" t="s">
         <v>28</v>
@@ -12365,7 +12365,7 @@
         <v>27</v>
       </c>
       <c r="D485">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E485" t="s">
         <v>28</v>
@@ -12382,7 +12382,7 @@
         <v>27</v>
       </c>
       <c r="D486">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E486" t="s">
         <v>28</v>
@@ -12399,7 +12399,7 @@
         <v>27</v>
       </c>
       <c r="D487">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E487" t="s">
         <v>28</v>
@@ -12416,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="D488">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E488" t="s">
         <v>28</v>
@@ -12433,7 +12433,7 @@
         <v>27</v>
       </c>
       <c r="D489">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E489" t="s">
         <v>28</v>
@@ -12450,7 +12450,7 @@
         <v>27</v>
       </c>
       <c r="D490">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E490" t="s">
         <v>28</v>
@@ -12467,7 +12467,7 @@
         <v>27</v>
       </c>
       <c r="D491">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E491" t="s">
         <v>28</v>
@@ -12484,7 +12484,7 @@
         <v>27</v>
       </c>
       <c r="D492">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E492" t="s">
         <v>28</v>
@@ -12501,7 +12501,7 @@
         <v>27</v>
       </c>
       <c r="D493">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E493" t="s">
         <v>28</v>
@@ -12518,7 +12518,7 @@
         <v>27</v>
       </c>
       <c r="D494">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E494" t="s">
         <v>28</v>
@@ -12535,7 +12535,7 @@
         <v>27</v>
       </c>
       <c r="D495">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E495" t="s">
         <v>28</v>
@@ -12552,7 +12552,7 @@
         <v>27</v>
       </c>
       <c r="D496">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E496" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="D497">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E497" t="s">
         <v>28</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D499">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E499" t="s">
         <v>28</v>
@@ -12620,7 +12620,7 @@
         <v>27</v>
       </c>
       <c r="D500">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E500" t="s">
         <v>28</v>
@@ -12637,7 +12637,7 @@
         <v>27</v>
       </c>
       <c r="D501">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E501" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="D502">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E502" t="s">
         <v>28</v>
@@ -12671,7 +12671,7 @@
         <v>27</v>
       </c>
       <c r="D503">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E503" t="s">
         <v>28</v>
@@ -12688,7 +12688,7 @@
         <v>27</v>
       </c>
       <c r="D504">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E504" t="s">
         <v>28</v>
@@ -12705,7 +12705,7 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E505" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="D506">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E506" t="s">
         <v>28</v>
@@ -12739,7 +12739,7 @@
         <v>27</v>
       </c>
       <c r="D507">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E507" t="s">
         <v>28</v>
@@ -12756,7 +12756,7 @@
         <v>27</v>
       </c>
       <c r="D508">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E508" t="s">
         <v>28</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="D509">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E509" t="s">
         <v>28</v>
@@ -12790,7 +12790,7 @@
         <v>27</v>
       </c>
       <c r="D510">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E510" t="s">
         <v>28</v>
@@ -12807,7 +12807,7 @@
         <v>27</v>
       </c>
       <c r="D511">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E511" t="s">
         <v>28</v>
@@ -12824,7 +12824,7 @@
         <v>27</v>
       </c>
       <c r="D512">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E512" t="s">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27</v>
       </c>
       <c r="D513">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E513" t="s">
         <v>28</v>
@@ -12858,7 +12858,7 @@
         <v>27</v>
       </c>
       <c r="D514">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E514" t="s">
         <v>28</v>
@@ -12875,7 +12875,7 @@
         <v>27</v>
       </c>
       <c r="D515">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E515" t="s">
         <v>28</v>
@@ -12892,7 +12892,7 @@
         <v>27</v>
       </c>
       <c r="D516">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E516" t="s">
         <v>28</v>
@@ -12909,7 +12909,7 @@
         <v>27</v>
       </c>
       <c r="D517">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E517" t="s">
         <v>28</v>
@@ -12926,7 +12926,7 @@
         <v>27</v>
       </c>
       <c r="D518">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E518" t="s">
         <v>28</v>
@@ -12943,7 +12943,7 @@
         <v>27</v>
       </c>
       <c r="D519">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E519" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="D520">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E520" t="s">
         <v>28</v>
@@ -12977,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="D521">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E521" t="s">
         <v>28</v>
@@ -12994,7 +12994,7 @@
         <v>27</v>
       </c>
       <c r="D522">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E522" t="s">
         <v>28</v>
@@ -13011,7 +13011,7 @@
         <v>27</v>
       </c>
       <c r="D523">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E523" t="s">
         <v>28</v>
@@ -13028,7 +13028,7 @@
         <v>27</v>
       </c>
       <c r="D524">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E524" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="D525">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E525" t="s">
         <v>28</v>
@@ -13062,7 +13062,7 @@
         <v>27</v>
       </c>
       <c r="D526">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E526" t="s">
         <v>28</v>
@@ -13079,7 +13079,7 @@
         <v>27</v>
       </c>
       <c r="D527">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E527" t="s">
         <v>28</v>
@@ -13096,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="D528">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E528" t="s">
         <v>28</v>
@@ -13130,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -13147,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="D531">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
@@ -13164,7 +13164,7 @@
         <v>27</v>
       </c>
       <c r="D532">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E532" t="s">
         <v>28</v>
@@ -13181,7 +13181,7 @@
         <v>27</v>
       </c>
       <c r="D533">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E533" t="s">
         <v>28</v>
@@ -13198,7 +13198,7 @@
         <v>27</v>
       </c>
       <c r="D534">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E534" t="s">
         <v>28</v>
@@ -13215,7 +13215,7 @@
         <v>27</v>
       </c>
       <c r="D535">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E535" t="s">
         <v>28</v>
@@ -13232,7 +13232,7 @@
         <v>27</v>
       </c>
       <c r="D536">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E536" t="s">
         <v>28</v>
@@ -13249,7 +13249,7 @@
         <v>27</v>
       </c>
       <c r="D537">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E537" t="s">
         <v>28</v>
@@ -13266,7 +13266,7 @@
         <v>27</v>
       </c>
       <c r="D538">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E538" t="s">
         <v>28</v>
@@ -13317,7 +13317,7 @@
         <v>27</v>
       </c>
       <c r="D541">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E541" t="s">
         <v>28</v>
@@ -13334,7 +13334,7 @@
         <v>27</v>
       </c>
       <c r="D542">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E542" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="D543">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E543" t="s">
         <v>28</v>
@@ -13368,7 +13368,7 @@
         <v>27</v>
       </c>
       <c r="D544">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E544" t="s">
         <v>28</v>
@@ -13385,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="D545">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
@@ -13402,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="D546">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
@@ -13419,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="D547">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E547" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="D548">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E548" t="s">
         <v>28</v>
@@ -13453,7 +13453,7 @@
         <v>27</v>
       </c>
       <c r="D549">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E549" t="s">
         <v>28</v>
@@ -13470,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="D550">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E550" t="s">
         <v>28</v>
@@ -13487,7 +13487,7 @@
         <v>27</v>
       </c>
       <c r="D551">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E551" t="s">
         <v>28</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="D552">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -13521,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="D553">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E553" t="s">
         <v>28</v>
@@ -13538,7 +13538,7 @@
         <v>27</v>
       </c>
       <c r="D554">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E554" t="s">
         <v>28</v>
@@ -13555,7 +13555,7 @@
         <v>27</v>
       </c>
       <c r="D555">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E555" t="s">
         <v>28</v>
@@ -13572,7 +13572,7 @@
         <v>27</v>
       </c>
       <c r="D556">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E556" t="s">
         <v>28</v>
@@ -13589,7 +13589,7 @@
         <v>27</v>
       </c>
       <c r="D557">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E557" t="s">
         <v>28</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="D558">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E558" t="s">
         <v>28</v>
@@ -13623,7 +13623,7 @@
         <v>27</v>
       </c>
       <c r="D559">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -13640,7 +13640,7 @@
         <v>27</v>
       </c>
       <c r="D560">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
@@ -13657,7 +13657,7 @@
         <v>27</v>
       </c>
       <c r="D561">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E561" t="s">
         <v>28</v>
@@ -13674,7 +13674,7 @@
         <v>27</v>
       </c>
       <c r="D562">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E562" t="s">
         <v>28</v>
@@ -13691,7 +13691,7 @@
         <v>27</v>
       </c>
       <c r="D563">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E563" t="s">
         <v>28</v>
@@ -13708,7 +13708,7 @@
         <v>27</v>
       </c>
       <c r="D564">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E564" t="s">
         <v>28</v>
@@ -13725,7 +13725,7 @@
         <v>27</v>
       </c>
       <c r="D565">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E565" t="s">
         <v>28</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="D566">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E566" t="s">
         <v>28</v>
@@ -13759,7 +13759,7 @@
         <v>27</v>
       </c>
       <c r="D567">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E567" t="s">
         <v>28</v>
@@ -13776,7 +13776,7 @@
         <v>27</v>
       </c>
       <c r="D568">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E568" t="s">
         <v>28</v>
@@ -13793,7 +13793,7 @@
         <v>27</v>
       </c>
       <c r="D569">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="D571">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E571" t="s">
         <v>28</v>
@@ -13844,7 +13844,7 @@
         <v>27</v>
       </c>
       <c r="D572">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E572" t="s">
         <v>28</v>
@@ -13861,7 +13861,7 @@
         <v>27</v>
       </c>
       <c r="D573">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E573" t="s">
         <v>28</v>
@@ -13878,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="D574">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E574" t="s">
         <v>28</v>
@@ -13895,7 +13895,7 @@
         <v>27</v>
       </c>
       <c r="D575">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E575" t="s">
         <v>28</v>
@@ -13912,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="D576">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E576" t="s">
         <v>28</v>
@@ -13929,7 +13929,7 @@
         <v>27</v>
       </c>
       <c r="D577">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E577" t="s">
         <v>28</v>
@@ -13946,7 +13946,7 @@
         <v>27</v>
       </c>
       <c r="D578">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E578" t="s">
         <v>28</v>
@@ -13963,7 +13963,7 @@
         <v>27</v>
       </c>
       <c r="D579">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E579" t="s">
         <v>28</v>
@@ -13980,7 +13980,7 @@
         <v>27</v>
       </c>
       <c r="D580">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E580" t="s">
         <v>28</v>
@@ -13997,7 +13997,7 @@
         <v>27</v>
       </c>
       <c r="D581">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E581" t="s">
         <v>28</v>
@@ -14031,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="D583">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E583" t="s">
         <v>28</v>
@@ -14048,7 +14048,7 @@
         <v>27</v>
       </c>
       <c r="D584">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E584" t="s">
         <v>28</v>
@@ -14065,7 +14065,7 @@
         <v>27</v>
       </c>
       <c r="D585">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E585" t="s">
         <v>28</v>
@@ -14082,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="D586">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E586" t="s">
         <v>28</v>
@@ -14099,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="D587">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E587" t="s">
         <v>28</v>
@@ -14116,7 +14116,7 @@
         <v>27</v>
       </c>
       <c r="D588">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E588" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="D589">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
@@ -14150,7 +14150,7 @@
         <v>27</v>
       </c>
       <c r="D590">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
@@ -14167,7 +14167,7 @@
         <v>27</v>
       </c>
       <c r="D591">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E591" t="s">
         <v>28</v>
@@ -14184,7 +14184,7 @@
         <v>27</v>
       </c>
       <c r="D592">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E592" t="s">
         <v>28</v>
@@ -14201,7 +14201,7 @@
         <v>27</v>
       </c>
       <c r="D593">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E593" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="D594">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E594" t="s">
         <v>28</v>
@@ -14235,7 +14235,7 @@
         <v>27</v>
       </c>
       <c r="D595">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E595" t="s">
         <v>28</v>
@@ -14252,7 +14252,7 @@
         <v>27</v>
       </c>
       <c r="D596">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
@@ -14269,7 +14269,7 @@
         <v>27</v>
       </c>
       <c r="D597">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
@@ -14286,7 +14286,7 @@
         <v>27</v>
       </c>
       <c r="D598">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
@@ -14303,7 +14303,7 @@
         <v>27</v>
       </c>
       <c r="D599">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="D600">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
@@ -14337,7 +14337,7 @@
         <v>27</v>
       </c>
       <c r="D601">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
@@ -14354,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="D602">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
@@ -14371,7 +14371,7 @@
         <v>27</v>
       </c>
       <c r="D603">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
@@ -14388,7 +14388,7 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
@@ -14405,7 +14405,7 @@
         <v>27</v>
       </c>
       <c r="D605">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E605" t="s">
         <v>28</v>
@@ -14422,7 +14422,7 @@
         <v>27</v>
       </c>
       <c r="D606">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E606" t="s">
         <v>28</v>
@@ -14439,7 +14439,7 @@
         <v>27</v>
       </c>
       <c r="D607">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E607" t="s">
         <v>28</v>
@@ -14456,7 +14456,7 @@
         <v>27</v>
       </c>
       <c r="D608">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
@@ -14473,7 +14473,7 @@
         <v>27</v>
       </c>
       <c r="D609">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E609" t="s">
         <v>28</v>
@@ -14490,7 +14490,7 @@
         <v>27</v>
       </c>
       <c r="D610">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E610" t="s">
         <v>28</v>
@@ -14507,7 +14507,7 @@
         <v>27</v>
       </c>
       <c r="D611">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E611" t="s">
         <v>28</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="D612">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E612" t="s">
         <v>28</v>
@@ -14541,7 +14541,7 @@
         <v>27</v>
       </c>
       <c r="D613">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E613" t="s">
         <v>28</v>
@@ -14575,7 +14575,7 @@
         <v>27</v>
       </c>
       <c r="D615">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E615" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="D617">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E617" t="s">
         <v>28</v>
@@ -14626,7 +14626,7 @@
         <v>27</v>
       </c>
       <c r="D618">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E618" t="s">
         <v>28</v>
@@ -14643,7 +14643,7 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E619" t="s">
         <v>28</v>
@@ -14660,7 +14660,7 @@
         <v>27</v>
       </c>
       <c r="D620">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E620" t="s">
         <v>28</v>
@@ -14694,7 +14694,7 @@
         <v>27</v>
       </c>
       <c r="D622">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E622" t="s">
         <v>28</v>
@@ -14711,7 +14711,7 @@
         <v>27</v>
       </c>
       <c r="D623">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E623" t="s">
         <v>28</v>
@@ -14728,7 +14728,7 @@
         <v>27</v>
       </c>
       <c r="D624">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E624" t="s">
         <v>28</v>
@@ -14745,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="D625">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E625" t="s">
         <v>28</v>
@@ -14762,7 +14762,7 @@
         <v>27</v>
       </c>
       <c r="D626">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E626" t="s">
         <v>28</v>
@@ -14779,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="D627">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E627" t="s">
         <v>28</v>
@@ -14796,7 +14796,7 @@
         <v>27</v>
       </c>
       <c r="D628">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E628" t="s">
         <v>28</v>
@@ -14813,7 +14813,7 @@
         <v>27</v>
       </c>
       <c r="D629">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E629" t="s">
         <v>28</v>
@@ -14830,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="D630">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E630" t="s">
         <v>28</v>
@@ -14847,7 +14847,7 @@
         <v>27</v>
       </c>
       <c r="D631">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E631" t="s">
         <v>28</v>
@@ -14864,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D632">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E632" t="s">
         <v>28</v>
@@ -14881,7 +14881,7 @@
         <v>27</v>
       </c>
       <c r="D633">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E633" t="s">
         <v>28</v>
@@ -14898,7 +14898,7 @@
         <v>27</v>
       </c>
       <c r="D634">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E634" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="D635">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E635" t="s">
         <v>28</v>
@@ -14932,7 +14932,7 @@
         <v>27</v>
       </c>
       <c r="D636">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E636" t="s">
         <v>28</v>
@@ -14949,7 +14949,7 @@
         <v>27</v>
       </c>
       <c r="D637">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E637" t="s">
         <v>28</v>
@@ -14966,7 +14966,7 @@
         <v>27</v>
       </c>
       <c r="D638">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E638" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E640" t="s">
         <v>28</v>
@@ -15017,7 +15017,7 @@
         <v>27</v>
       </c>
       <c r="D641">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E641" t="s">
         <v>28</v>
@@ -15034,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="D642">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E642" t="s">
         <v>28</v>
@@ -15051,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="D643">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E643" t="s">
         <v>28</v>
@@ -15068,7 +15068,7 @@
         <v>27</v>
       </c>
       <c r="D644">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E644" t="s">
         <v>28</v>
@@ -15085,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="D645">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E645" t="s">
         <v>28</v>
@@ -15102,7 +15102,7 @@
         <v>27</v>
       </c>
       <c r="D646">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E646" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>27</v>
       </c>
       <c r="D647">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E647" t="s">
         <v>28</v>
@@ -15136,7 +15136,7 @@
         <v>27</v>
       </c>
       <c r="D648">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E648" t="s">
         <v>28</v>
@@ -15153,7 +15153,7 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E649" t="s">
         <v>28</v>
@@ -15170,7 +15170,7 @@
         <v>27</v>
       </c>
       <c r="D650">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E650" t="s">
         <v>28</v>
@@ -15187,7 +15187,7 @@
         <v>27</v>
       </c>
       <c r="D651">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E651" t="s">
         <v>28</v>
@@ -15221,7 +15221,7 @@
         <v>27</v>
       </c>
       <c r="D653">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E653" t="s">
         <v>28</v>
@@ -15238,7 +15238,7 @@
         <v>27</v>
       </c>
       <c r="D654">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E654" t="s">
         <v>28</v>
@@ -15255,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="D655">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E655" t="s">
         <v>28</v>
@@ -15272,7 +15272,7 @@
         <v>27</v>
       </c>
       <c r="D656">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
@@ -15289,7 +15289,7 @@
         <v>27</v>
       </c>
       <c r="D657">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E657" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
@@ -15323,7 +15323,7 @@
         <v>27</v>
       </c>
       <c r="D659">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E659" t="s">
         <v>28</v>
@@ -15340,7 +15340,7 @@
         <v>27</v>
       </c>
       <c r="D660">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E660" t="s">
         <v>28</v>
@@ -15374,7 +15374,7 @@
         <v>27</v>
       </c>
       <c r="D662">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E662" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="D663">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E663" t="s">
         <v>28</v>
@@ -15408,7 +15408,7 @@
         <v>27</v>
       </c>
       <c r="D664">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E664" t="s">
         <v>28</v>
@@ -15425,7 +15425,7 @@
         <v>27</v>
       </c>
       <c r="D665">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E665" t="s">
         <v>28</v>
@@ -15442,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="D666">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E666" t="s">
         <v>28</v>
@@ -15459,7 +15459,7 @@
         <v>27</v>
       </c>
       <c r="D667">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E667" t="s">
         <v>28</v>
@@ -15476,7 +15476,7 @@
         <v>27</v>
       </c>
       <c r="D668">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E668" t="s">
         <v>28</v>
@@ -15493,7 +15493,7 @@
         <v>27</v>
       </c>
       <c r="D669">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E669" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>27</v>
       </c>
       <c r="D670">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E670" t="s">
         <v>28</v>
@@ -15527,7 +15527,7 @@
         <v>27</v>
       </c>
       <c r="D671">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E671" t="s">
         <v>28</v>
@@ -15544,7 +15544,7 @@
         <v>27</v>
       </c>
       <c r="D672">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E672" t="s">
         <v>28</v>
@@ -15561,7 +15561,7 @@
         <v>27</v>
       </c>
       <c r="D673">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E673" t="s">
         <v>28</v>
@@ -15578,7 +15578,7 @@
         <v>27</v>
       </c>
       <c r="D674">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E674" t="s">
         <v>28</v>
@@ -15595,7 +15595,7 @@
         <v>27</v>
       </c>
       <c r="D675">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E675" t="s">
         <v>28</v>
@@ -15612,7 +15612,7 @@
         <v>27</v>
       </c>
       <c r="D676">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E676" t="s">
         <v>28</v>
@@ -15629,7 +15629,7 @@
         <v>27</v>
       </c>
       <c r="D677">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E677" t="s">
         <v>28</v>
@@ -15646,7 +15646,7 @@
         <v>27</v>
       </c>
       <c r="D678">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E678" t="s">
         <v>28</v>
@@ -15663,7 +15663,7 @@
         <v>27</v>
       </c>
       <c r="D679">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E679" t="s">
         <v>28</v>
@@ -15680,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="D680">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E680" t="s">
         <v>28</v>
@@ -15697,7 +15697,7 @@
         <v>27</v>
       </c>
       <c r="D681">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E681" t="s">
         <v>28</v>
@@ -15714,7 +15714,7 @@
         <v>27</v>
       </c>
       <c r="D682">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E682" t="s">
         <v>28</v>
@@ -15731,7 +15731,7 @@
         <v>27</v>
       </c>
       <c r="D683">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E683" t="s">
         <v>28</v>
@@ -15748,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="D684">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E684" t="s">
         <v>28</v>
@@ -15765,7 +15765,7 @@
         <v>27</v>
       </c>
       <c r="D685">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E685" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="D686">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E686" t="s">
         <v>28</v>
@@ -15799,7 +15799,7 @@
         <v>27</v>
       </c>
       <c r="D687">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E687" t="s">
         <v>28</v>
@@ -15816,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="D688">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E688" t="s">
         <v>28</v>
@@ -15833,7 +15833,7 @@
         <v>27</v>
       </c>
       <c r="D689">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E689" t="s">
         <v>28</v>
@@ -15850,7 +15850,7 @@
         <v>27</v>
       </c>
       <c r="D690">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E690" t="s">
         <v>28</v>
@@ -15867,7 +15867,7 @@
         <v>27</v>
       </c>
       <c r="D691">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E691" t="s">
         <v>28</v>
@@ -15884,7 +15884,7 @@
         <v>27</v>
       </c>
       <c r="D692">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E692" t="s">
         <v>28</v>
@@ -15901,7 +15901,7 @@
         <v>27</v>
       </c>
       <c r="D693">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E693" t="s">
         <v>28</v>
@@ -15918,7 +15918,7 @@
         <v>27</v>
       </c>
       <c r="D694">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E694" t="s">
         <v>28</v>
@@ -15935,7 +15935,7 @@
         <v>27</v>
       </c>
       <c r="D695">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E695" t="s">
         <v>28</v>
@@ -15952,7 +15952,7 @@
         <v>27</v>
       </c>
       <c r="D696">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E696" t="s">
         <v>28</v>
@@ -15969,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="D697">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E697" t="s">
         <v>28</v>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
       <c r="D698">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E698" t="s">
         <v>28</v>
@@ -16003,7 +16003,7 @@
         <v>27</v>
       </c>
       <c r="D699">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E699" t="s">
         <v>28</v>
@@ -16020,7 +16020,7 @@
         <v>27</v>
       </c>
       <c r="D700">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E700" t="s">
         <v>28</v>
@@ -16054,7 +16054,7 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E702" t="s">
         <v>28</v>
@@ -16071,7 +16071,7 @@
         <v>27</v>
       </c>
       <c r="D703">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E703" t="s">
         <v>28</v>
@@ -16088,7 +16088,7 @@
         <v>27</v>
       </c>
       <c r="D704">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E704" t="s">
         <v>28</v>
@@ -16105,7 +16105,7 @@
         <v>27</v>
       </c>
       <c r="D705">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E705" t="s">
         <v>28</v>
@@ -16122,7 +16122,7 @@
         <v>27</v>
       </c>
       <c r="D706">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E706" t="s">
         <v>28</v>
@@ -16139,7 +16139,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E707" t="s">
         <v>28</v>
@@ -16156,7 +16156,7 @@
         <v>27</v>
       </c>
       <c r="D708">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E708" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="D709">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E709" t="s">
         <v>28</v>
@@ -16207,7 +16207,7 @@
         <v>27</v>
       </c>
       <c r="D711">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E711" t="s">
         <v>28</v>
@@ -16224,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="D712">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E712" t="s">
         <v>28</v>
@@ -16241,7 +16241,7 @@
         <v>27</v>
       </c>
       <c r="D713">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E713" t="s">
         <v>28</v>
@@ -16258,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="D714">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E714" t="s">
         <v>28</v>
@@ -16275,7 +16275,7 @@
         <v>27</v>
       </c>
       <c r="D715">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E715" t="s">
         <v>28</v>
@@ -16292,7 +16292,7 @@
         <v>27</v>
       </c>
       <c r="D716">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E716" t="s">
         <v>28</v>
@@ -16309,7 +16309,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E717" t="s">
         <v>28</v>
@@ -16326,7 +16326,7 @@
         <v>27</v>
       </c>
       <c r="D718">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E718" t="s">
         <v>28</v>
@@ -16360,7 +16360,7 @@
         <v>27</v>
       </c>
       <c r="D720">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E720" t="s">
         <v>28</v>
@@ -16377,7 +16377,7 @@
         <v>27</v>
       </c>
       <c r="D721">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E721" t="s">
         <v>28</v>
@@ -16394,7 +16394,7 @@
         <v>27</v>
       </c>
       <c r="D722">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E722" t="s">
         <v>28</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="D723">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E723" t="s">
         <v>28</v>
@@ -16428,7 +16428,7 @@
         <v>27</v>
       </c>
       <c r="D724">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E724" t="s">
         <v>28</v>
@@ -16445,7 +16445,7 @@
         <v>27</v>
       </c>
       <c r="D725">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E725" t="s">
         <v>28</v>
@@ -16462,7 +16462,7 @@
         <v>27</v>
       </c>
       <c r="D726">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E726" t="s">
         <v>28</v>
@@ -16479,7 +16479,7 @@
         <v>27</v>
       </c>
       <c r="D727">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E727" t="s">
         <v>28</v>
@@ -16496,7 +16496,7 @@
         <v>27</v>
       </c>
       <c r="D728">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E728" t="s">
         <v>28</v>
@@ -16530,7 +16530,7 @@
         <v>27</v>
       </c>
       <c r="D730">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E730" t="s">
         <v>28</v>
@@ -16547,7 +16547,7 @@
         <v>27</v>
       </c>
       <c r="D731">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E731" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="D732">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E732" t="s">
         <v>28</v>
@@ -16598,7 +16598,7 @@
         <v>27</v>
       </c>
       <c r="D734">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E734" t="s">
         <v>28</v>
@@ -16615,7 +16615,7 @@
         <v>27</v>
       </c>
       <c r="D735">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E735" t="s">
         <v>28</v>
@@ -16632,7 +16632,7 @@
         <v>27</v>
       </c>
       <c r="D736">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E736" t="s">
         <v>28</v>
@@ -16649,7 +16649,7 @@
         <v>27</v>
       </c>
       <c r="D737">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E737" t="s">
         <v>28</v>
@@ -16666,7 +16666,7 @@
         <v>27</v>
       </c>
       <c r="D738">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E738" t="s">
         <v>28</v>
@@ -16683,7 +16683,7 @@
         <v>27</v>
       </c>
       <c r="D739">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E739" t="s">
         <v>28</v>
@@ -16717,7 +16717,7 @@
         <v>27</v>
       </c>
       <c r="D741">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E741" t="s">
         <v>28</v>
@@ -16734,7 +16734,7 @@
         <v>27</v>
       </c>
       <c r="D742">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E742" t="s">
         <v>28</v>
@@ -16751,7 +16751,7 @@
         <v>27</v>
       </c>
       <c r="D743">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E743" t="s">
         <v>28</v>
@@ -16768,7 +16768,7 @@
         <v>27</v>
       </c>
       <c r="D744">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E744" t="s">
         <v>28</v>
@@ -16785,7 +16785,7 @@
         <v>27</v>
       </c>
       <c r="D745">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E745" t="s">
         <v>28</v>
@@ -16802,7 +16802,7 @@
         <v>27</v>
       </c>
       <c r="D746">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E746" t="s">
         <v>28</v>
@@ -16819,7 +16819,7 @@
         <v>27</v>
       </c>
       <c r="D747">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E747" t="s">
         <v>28</v>
@@ -16836,7 +16836,7 @@
         <v>27</v>
       </c>
       <c r="D748">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E748" t="s">
         <v>28</v>
@@ -16853,7 +16853,7 @@
         <v>27</v>
       </c>
       <c r="D749">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E749" t="s">
         <v>28</v>
@@ -16870,7 +16870,7 @@
         <v>27</v>
       </c>
       <c r="D750">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E750" t="s">
         <v>28</v>
@@ -16887,7 +16887,7 @@
         <v>27</v>
       </c>
       <c r="D751">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E751" t="s">
         <v>28</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="D752">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E752" t="s">
         <v>28</v>
@@ -16921,7 +16921,7 @@
         <v>27</v>
       </c>
       <c r="D753">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E753" t="s">
         <v>28</v>
@@ -16938,7 +16938,7 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E754" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="D755">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E755" t="s">
         <v>28</v>
@@ -16972,7 +16972,7 @@
         <v>27</v>
       </c>
       <c r="D756">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E756" t="s">
         <v>28</v>
@@ -16989,7 +16989,7 @@
         <v>27</v>
       </c>
       <c r="D757">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E757" t="s">
         <v>28</v>
@@ -17006,7 +17006,7 @@
         <v>27</v>
       </c>
       <c r="D758">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E758" t="s">
         <v>28</v>
@@ -17023,7 +17023,7 @@
         <v>27</v>
       </c>
       <c r="D759">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E759" t="s">
         <v>28</v>
@@ -17040,7 +17040,7 @@
         <v>27</v>
       </c>
       <c r="D760">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E760" t="s">
         <v>28</v>
@@ -17057,7 +17057,7 @@
         <v>27</v>
       </c>
       <c r="D761">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E761" t="s">
         <v>28</v>
@@ -17074,7 +17074,7 @@
         <v>27</v>
       </c>
       <c r="D762">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E762" t="s">
         <v>28</v>
@@ -17091,7 +17091,7 @@
         <v>27</v>
       </c>
       <c r="D763">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E763" t="s">
         <v>28</v>
@@ -17108,7 +17108,7 @@
         <v>27</v>
       </c>
       <c r="D764">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E764" t="s">
         <v>28</v>
@@ -17125,7 +17125,7 @@
         <v>27</v>
       </c>
       <c r="D765">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E765" t="s">
         <v>28</v>
@@ -17142,7 +17142,7 @@
         <v>27</v>
       </c>
       <c r="D766">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E766" t="s">
         <v>28</v>
@@ -17159,7 +17159,7 @@
         <v>27</v>
       </c>
       <c r="D767">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E767" t="s">
         <v>28</v>
@@ -17176,7 +17176,7 @@
         <v>27</v>
       </c>
       <c r="D768">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E768" t="s">
         <v>28</v>
@@ -17210,7 +17210,7 @@
         <v>27</v>
       </c>
       <c r="D770">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E770" t="s">
         <v>28</v>
@@ -17227,7 +17227,7 @@
         <v>27</v>
       </c>
       <c r="D771">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E771" t="s">
         <v>28</v>
@@ -17244,7 +17244,7 @@
         <v>27</v>
       </c>
       <c r="D772">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E772" t="s">
         <v>28</v>
@@ -17261,7 +17261,7 @@
         <v>27</v>
       </c>
       <c r="D773">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E773" t="s">
         <v>28</v>
@@ -17278,7 +17278,7 @@
         <v>27</v>
       </c>
       <c r="D774">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E774" t="s">
         <v>28</v>
@@ -17312,7 +17312,7 @@
         <v>27</v>
       </c>
       <c r="D776">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E776" t="s">
         <v>28</v>
@@ -17329,7 +17329,7 @@
         <v>27</v>
       </c>
       <c r="D777">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E777" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="D778">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E778" t="s">
         <v>28</v>
@@ -17363,7 +17363,7 @@
         <v>27</v>
       </c>
       <c r="D779">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E779" t="s">
         <v>28</v>
@@ -17380,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="D780">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E780" t="s">
         <v>28</v>
@@ -17397,7 +17397,7 @@
         <v>27</v>
       </c>
       <c r="D781">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E781" t="s">
         <v>28</v>
@@ -17414,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="D782">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E782" t="s">
         <v>28</v>
@@ -17431,7 +17431,7 @@
         <v>27</v>
       </c>
       <c r="D783">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E783" t="s">
         <v>28</v>
@@ -17448,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D784">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E784" t="s">
         <v>28</v>
@@ -17465,7 +17465,7 @@
         <v>27</v>
       </c>
       <c r="D785">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E785" t="s">
         <v>28</v>
@@ -17482,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="D786">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E786" t="s">
         <v>28</v>
@@ -17499,7 +17499,7 @@
         <v>27</v>
       </c>
       <c r="D787">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E787" t="s">
         <v>28</v>
@@ -17516,7 +17516,7 @@
         <v>27</v>
       </c>
       <c r="D788">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E788" t="s">
         <v>28</v>
@@ -17533,7 +17533,7 @@
         <v>27</v>
       </c>
       <c r="D789">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E789" t="s">
         <v>28</v>
@@ -17550,7 +17550,7 @@
         <v>27</v>
       </c>
       <c r="D790">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E790" t="s">
         <v>28</v>
@@ -17567,7 +17567,7 @@
         <v>27</v>
       </c>
       <c r="D791">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E791" t="s">
         <v>28</v>
@@ -17584,7 +17584,7 @@
         <v>27</v>
       </c>
       <c r="D792">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E792" t="s">
         <v>28</v>
@@ -17601,7 +17601,7 @@
         <v>27</v>
       </c>
       <c r="D793">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E793" t="s">
         <v>28</v>
@@ -17618,7 +17618,7 @@
         <v>27</v>
       </c>
       <c r="D794">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E794" t="s">
         <v>28</v>
@@ -17635,7 +17635,7 @@
         <v>27</v>
       </c>
       <c r="D795">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E795" t="s">
         <v>28</v>
@@ -17652,7 +17652,7 @@
         <v>27</v>
       </c>
       <c r="D796">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E796" t="s">
         <v>28</v>
@@ -17669,7 +17669,7 @@
         <v>27</v>
       </c>
       <c r="D797">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E797" t="s">
         <v>28</v>
@@ -17686,7 +17686,7 @@
         <v>27</v>
       </c>
       <c r="D798">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E798" t="s">
         <v>28</v>
@@ -17703,7 +17703,7 @@
         <v>27</v>
       </c>
       <c r="D799">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E799" t="s">
         <v>28</v>
@@ -17720,7 +17720,7 @@
         <v>27</v>
       </c>
       <c r="D800">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E800" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="D801">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E801" t="s">
         <v>28</v>
@@ -17754,7 +17754,7 @@
         <v>27</v>
       </c>
       <c r="D802">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E802" t="s">
         <v>28</v>
@@ -17771,7 +17771,7 @@
         <v>27</v>
       </c>
       <c r="D803">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E803" t="s">
         <v>28</v>
@@ -17788,7 +17788,7 @@
         <v>27</v>
       </c>
       <c r="D804">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E804" t="s">
         <v>28</v>
@@ -17805,7 +17805,7 @@
         <v>27</v>
       </c>
       <c r="D805">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E805" t="s">
         <v>28</v>
@@ -17822,7 +17822,7 @@
         <v>27</v>
       </c>
       <c r="D806">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E806" t="s">
         <v>28</v>
@@ -17839,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="D807">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E807" t="s">
         <v>28</v>
@@ -17856,7 +17856,7 @@
         <v>27</v>
       </c>
       <c r="D808">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E808" t="s">
         <v>28</v>
@@ -17873,7 +17873,7 @@
         <v>27</v>
       </c>
       <c r="D809">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E809" t="s">
         <v>28</v>
@@ -17890,7 +17890,7 @@
         <v>27</v>
       </c>
       <c r="D810">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E810" t="s">
         <v>28</v>
@@ -17907,7 +17907,7 @@
         <v>27</v>
       </c>
       <c r="D811">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E811" t="s">
         <v>28</v>
@@ -17924,7 +17924,7 @@
         <v>27</v>
       </c>
       <c r="D812">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E812" t="s">
         <v>28</v>
@@ -17941,7 +17941,7 @@
         <v>27</v>
       </c>
       <c r="D813">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E813" t="s">
         <v>28</v>
@@ -17958,7 +17958,7 @@
         <v>27</v>
       </c>
       <c r="D814">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E814" t="s">
         <v>28</v>
@@ -17975,7 +17975,7 @@
         <v>27</v>
       </c>
       <c r="D815">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E815" t="s">
         <v>28</v>
@@ -17992,7 +17992,7 @@
         <v>27</v>
       </c>
       <c r="D816">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E816" t="s">
         <v>28</v>
@@ -18009,7 +18009,7 @@
         <v>27</v>
       </c>
       <c r="D817">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E817" t="s">
         <v>28</v>
@@ -18026,7 +18026,7 @@
         <v>27</v>
       </c>
       <c r="D818">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E818" t="s">
         <v>28</v>
@@ -18043,7 +18043,7 @@
         <v>27</v>
       </c>
       <c r="D819">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E819" t="s">
         <v>28</v>
@@ -18060,7 +18060,7 @@
         <v>27</v>
       </c>
       <c r="D820">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E820" t="s">
         <v>28</v>
@@ -18077,7 +18077,7 @@
         <v>27</v>
       </c>
       <c r="D821">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E821" t="s">
         <v>28</v>
@@ -18111,7 +18111,7 @@
         <v>27</v>
       </c>
       <c r="D823">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E823" t="s">
         <v>28</v>
@@ -18128,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="D824">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E824" t="s">
         <v>28</v>
@@ -18145,7 +18145,7 @@
         <v>27</v>
       </c>
       <c r="D825">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E825" t="s">
         <v>28</v>
@@ -18162,7 +18162,7 @@
         <v>27</v>
       </c>
       <c r="D826">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E826" t="s">
         <v>28</v>
@@ -18179,7 +18179,7 @@
         <v>27</v>
       </c>
       <c r="D827">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E827" t="s">
         <v>28</v>
@@ -18196,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="D828">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E828" t="s">
         <v>28</v>
@@ -18213,7 +18213,7 @@
         <v>27</v>
       </c>
       <c r="D829">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E829" t="s">
         <v>28</v>
@@ -18230,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="D830">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E830" t="s">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E831" t="s">
         <v>28</v>
@@ -18264,7 +18264,7 @@
         <v>27</v>
       </c>
       <c r="D832">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E832" t="s">
         <v>28</v>
@@ -18281,7 +18281,7 @@
         <v>27</v>
       </c>
       <c r="D833">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E833" t="s">
         <v>28</v>
@@ -18315,7 +18315,7 @@
         <v>27</v>
       </c>
       <c r="D835">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E835" t="s">
         <v>28</v>
@@ -18332,7 +18332,7 @@
         <v>27</v>
       </c>
       <c r="D836">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E836" t="s">
         <v>28</v>
@@ -18349,7 +18349,7 @@
         <v>27</v>
       </c>
       <c r="D837">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E837" t="s">
         <v>28</v>
@@ -18366,7 +18366,7 @@
         <v>27</v>
       </c>
       <c r="D838">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E838" t="s">
         <v>28</v>
@@ -18383,7 +18383,7 @@
         <v>27</v>
       </c>
       <c r="D839">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E839" t="s">
         <v>28</v>
@@ -18400,7 +18400,7 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E840" t="s">
         <v>28</v>
@@ -18417,7 +18417,7 @@
         <v>27</v>
       </c>
       <c r="D841">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E841" t="s">
         <v>28</v>
@@ -18434,7 +18434,7 @@
         <v>27</v>
       </c>
       <c r="D842">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E842" t="s">
         <v>28</v>
@@ -18451,7 +18451,7 @@
         <v>27</v>
       </c>
       <c r="D843">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E843" t="s">
         <v>28</v>
@@ -18468,7 +18468,7 @@
         <v>27</v>
       </c>
       <c r="D844">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E844" t="s">
         <v>28</v>
@@ -18502,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="D846">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E846" t="s">
         <v>28</v>
@@ -18519,7 +18519,7 @@
         <v>27</v>
       </c>
       <c r="D847">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E847" t="s">
         <v>28</v>
@@ -18536,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="D848">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E848" t="s">
         <v>28</v>
@@ -18553,7 +18553,7 @@
         <v>27</v>
       </c>
       <c r="D849">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E849" t="s">
         <v>28</v>
@@ -18621,7 +18621,7 @@
         <v>27</v>
       </c>
       <c r="D853">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E853" t="s">
         <v>28</v>
@@ -18638,7 +18638,7 @@
         <v>27</v>
       </c>
       <c r="D854">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E854" t="s">
         <v>28</v>
@@ -18655,7 +18655,7 @@
         <v>27</v>
       </c>
       <c r="D855">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E855" t="s">
         <v>28</v>
@@ -18672,7 +18672,7 @@
         <v>27</v>
       </c>
       <c r="D856">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E856" t="s">
         <v>28</v>
@@ -18689,7 +18689,7 @@
         <v>27</v>
       </c>
       <c r="D857">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E857" t="s">
         <v>28</v>
@@ -18706,7 +18706,7 @@
         <v>27</v>
       </c>
       <c r="D858">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E858" t="s">
         <v>28</v>
@@ -18723,7 +18723,7 @@
         <v>27</v>
       </c>
       <c r="D859">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E859" t="s">
         <v>28</v>
@@ -18740,7 +18740,7 @@
         <v>27</v>
       </c>
       <c r="D860">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E860" t="s">
         <v>28</v>
@@ -18757,7 +18757,7 @@
         <v>27</v>
       </c>
       <c r="D861">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E861" t="s">
         <v>28</v>
@@ -18774,7 +18774,7 @@
         <v>27</v>
       </c>
       <c r="D862">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E862" t="s">
         <v>28</v>
@@ -18791,7 +18791,7 @@
         <v>27</v>
       </c>
       <c r="D863">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E863" t="s">
         <v>28</v>
@@ -18808,7 +18808,7 @@
         <v>27</v>
       </c>
       <c r="D864">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E864" t="s">
         <v>28</v>
@@ -18825,7 +18825,7 @@
         <v>27</v>
       </c>
       <c r="D865">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E865" t="s">
         <v>28</v>
@@ -18842,7 +18842,7 @@
         <v>27</v>
       </c>
       <c r="D866">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E866" t="s">
         <v>28</v>
@@ -18859,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="D867">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E867" t="s">
         <v>28</v>
@@ -18876,7 +18876,7 @@
         <v>27</v>
       </c>
       <c r="D868">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E868" t="s">
         <v>28</v>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
       <c r="D869">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E869" t="s">
         <v>28</v>
@@ -18910,7 +18910,7 @@
         <v>27</v>
       </c>
       <c r="D870">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E870" t="s">
         <v>28</v>
@@ -18927,7 +18927,7 @@
         <v>27</v>
       </c>
       <c r="D871">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E871" t="s">
         <v>28</v>
@@ -18944,7 +18944,7 @@
         <v>27</v>
       </c>
       <c r="D872">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E872" t="s">
         <v>28</v>
@@ -18961,7 +18961,7 @@
         <v>27</v>
       </c>
       <c r="D873">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E873" t="s">
         <v>28</v>
@@ -18978,7 +18978,7 @@
         <v>27</v>
       </c>
       <c r="D874">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E874" t="s">
         <v>28</v>
@@ -18995,7 +18995,7 @@
         <v>27</v>
       </c>
       <c r="D875">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E875" t="s">
         <v>28</v>
@@ -19012,7 +19012,7 @@
         <v>27</v>
       </c>
       <c r="D876">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E876" t="s">
         <v>28</v>
@@ -19029,7 +19029,7 @@
         <v>27</v>
       </c>
       <c r="D877">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E877" t="s">
         <v>28</v>
@@ -19046,7 +19046,7 @@
         <v>27</v>
       </c>
       <c r="D878">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E878" t="s">
         <v>28</v>
@@ -19063,7 +19063,7 @@
         <v>27</v>
       </c>
       <c r="D879">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E879" t="s">
         <v>28</v>
@@ -19080,7 +19080,7 @@
         <v>27</v>
       </c>
       <c r="D880">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E880" t="s">
         <v>28</v>
@@ -19097,7 +19097,7 @@
         <v>27</v>
       </c>
       <c r="D881">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E881" t="s">
         <v>28</v>
@@ -19114,7 +19114,7 @@
         <v>27</v>
       </c>
       <c r="D882">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E882" t="s">
         <v>28</v>
@@ -19131,7 +19131,7 @@
         <v>27</v>
       </c>
       <c r="D883">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E883" t="s">
         <v>28</v>
@@ -19148,7 +19148,7 @@
         <v>27</v>
       </c>
       <c r="D884">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E884" t="s">
         <v>28</v>
@@ -19165,7 +19165,7 @@
         <v>27</v>
       </c>
       <c r="D885">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E885" t="s">
         <v>28</v>
@@ -19182,7 +19182,7 @@
         <v>27</v>
       </c>
       <c r="D886">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E886" t="s">
         <v>28</v>
@@ -19199,7 +19199,7 @@
         <v>27</v>
       </c>
       <c r="D887">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E887" t="s">
         <v>28</v>
@@ -19216,7 +19216,7 @@
         <v>27</v>
       </c>
       <c r="D888">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E888" t="s">
         <v>28</v>
@@ -19233,7 +19233,7 @@
         <v>27</v>
       </c>
       <c r="D889">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E889" t="s">
         <v>28</v>
@@ -19250,7 +19250,7 @@
         <v>27</v>
       </c>
       <c r="D890">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E890" t="s">
         <v>28</v>
@@ -19267,7 +19267,7 @@
         <v>27</v>
       </c>
       <c r="D891">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E891" t="s">
         <v>28</v>
@@ -19284,7 +19284,7 @@
         <v>27</v>
       </c>
       <c r="D892">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E892" t="s">
         <v>28</v>
@@ -19301,7 +19301,7 @@
         <v>27</v>
       </c>
       <c r="D893">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E893" t="s">
         <v>28</v>
@@ -19318,7 +19318,7 @@
         <v>27</v>
       </c>
       <c r="D894">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E894" t="s">
         <v>28</v>
@@ -19335,7 +19335,7 @@
         <v>27</v>
       </c>
       <c r="D895">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E895" t="s">
         <v>28</v>
@@ -19352,7 +19352,7 @@
         <v>27</v>
       </c>
       <c r="D896">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E896" t="s">
         <v>28</v>
@@ -19369,7 +19369,7 @@
         <v>27</v>
       </c>
       <c r="D897">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E897" t="s">
         <v>28</v>
@@ -19386,7 +19386,7 @@
         <v>27</v>
       </c>
       <c r="D898">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E898" t="s">
         <v>28</v>
@@ -19403,7 +19403,7 @@
         <v>27</v>
       </c>
       <c r="D899">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E899" t="s">
         <v>28</v>
@@ -19420,7 +19420,7 @@
         <v>27</v>
       </c>
       <c r="D900">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E900" t="s">
         <v>28</v>
@@ -19437,7 +19437,7 @@
         <v>27</v>
       </c>
       <c r="D901">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E901" t="s">
         <v>28</v>
@@ -19454,7 +19454,7 @@
         <v>27</v>
       </c>
       <c r="D902">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E902" t="s">
         <v>28</v>
@@ -19471,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D903">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E903" t="s">
         <v>28</v>
@@ -19488,7 +19488,7 @@
         <v>27</v>
       </c>
       <c r="D904">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E904" t="s">
         <v>28</v>
@@ -19505,7 +19505,7 @@
         <v>27</v>
       </c>
       <c r="D905">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E905" t="s">
         <v>28</v>
@@ -19522,7 +19522,7 @@
         <v>27</v>
       </c>
       <c r="D906">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E906" t="s">
         <v>28</v>
@@ -19539,7 +19539,7 @@
         <v>27</v>
       </c>
       <c r="D907">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E907" t="s">
         <v>28</v>
@@ -19556,7 +19556,7 @@
         <v>27</v>
       </c>
       <c r="D908">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E908" t="s">
         <v>28</v>
@@ -19573,7 +19573,7 @@
         <v>27</v>
       </c>
       <c r="D909">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E909" t="s">
         <v>28</v>
@@ -19590,7 +19590,7 @@
         <v>27</v>
       </c>
       <c r="D910">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E910" t="s">
         <v>28</v>
@@ -19607,7 +19607,7 @@
         <v>27</v>
       </c>
       <c r="D911">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E911" t="s">
         <v>28</v>
@@ -19624,7 +19624,7 @@
         <v>27</v>
       </c>
       <c r="D912">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E912" t="s">
         <v>28</v>
@@ -19641,7 +19641,7 @@
         <v>27</v>
       </c>
       <c r="D913">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E913" t="s">
         <v>28</v>
@@ -19658,7 +19658,7 @@
         <v>27</v>
       </c>
       <c r="D914">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E914" t="s">
         <v>28</v>
@@ -19675,7 +19675,7 @@
         <v>27</v>
       </c>
       <c r="D915">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E915" t="s">
         <v>28</v>
@@ -19692,7 +19692,7 @@
         <v>27</v>
       </c>
       <c r="D916">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E916" t="s">
         <v>28</v>
@@ -19709,7 +19709,7 @@
         <v>27</v>
       </c>
       <c r="D917">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E917" t="s">
         <v>28</v>
@@ -19726,7 +19726,7 @@
         <v>27</v>
       </c>
       <c r="D918">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E918" t="s">
         <v>28</v>
@@ -19743,7 +19743,7 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E919" t="s">
         <v>28</v>
@@ -19760,7 +19760,7 @@
         <v>27</v>
       </c>
       <c r="D920">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E920" t="s">
         <v>28</v>
@@ -19777,7 +19777,7 @@
         <v>27</v>
       </c>
       <c r="D921">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E921" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>27</v>
       </c>
       <c r="D922">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E922" t="s">
         <v>28</v>
@@ -19811,7 +19811,7 @@
         <v>27</v>
       </c>
       <c r="D923">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E923" t="s">
         <v>28</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="D924">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E924" t="s">
         <v>28</v>
@@ -19845,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="D925">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E925" t="s">
         <v>28</v>
@@ -19862,7 +19862,7 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E926" t="s">
         <v>28</v>
@@ -19879,7 +19879,7 @@
         <v>27</v>
       </c>
       <c r="D927">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E927" t="s">
         <v>28</v>
@@ -19896,7 +19896,7 @@
         <v>27</v>
       </c>
       <c r="D928">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E928" t="s">
         <v>28</v>
@@ -19913,7 +19913,7 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E929" t="s">
         <v>28</v>
@@ -19930,7 +19930,7 @@
         <v>27</v>
       </c>
       <c r="D930">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E930" t="s">
         <v>28</v>
@@ -19947,7 +19947,7 @@
         <v>27</v>
       </c>
       <c r="D931">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E931" t="s">
         <v>28</v>
@@ -19981,7 +19981,7 @@
         <v>27</v>
       </c>
       <c r="D933">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E933" t="s">
         <v>28</v>
@@ -19998,7 +19998,7 @@
         <v>27</v>
       </c>
       <c r="D934">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E934" t="s">
         <v>28</v>
@@ -20015,7 +20015,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E935" t="s">
         <v>28</v>
@@ -20032,7 +20032,7 @@
         <v>27</v>
       </c>
       <c r="D936">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E936" t="s">
         <v>28</v>
@@ -20049,7 +20049,7 @@
         <v>27</v>
       </c>
       <c r="D937">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E937" t="s">
         <v>28</v>
@@ -20066,7 +20066,7 @@
         <v>27</v>
       </c>
       <c r="D938">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E938" t="s">
         <v>28</v>
@@ -20083,7 +20083,7 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E939" t="s">
         <v>28</v>
@@ -20100,7 +20100,7 @@
         <v>27</v>
       </c>
       <c r="D940">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E940" t="s">
         <v>28</v>
@@ -20117,7 +20117,7 @@
         <v>27</v>
       </c>
       <c r="D941">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E941" t="s">
         <v>28</v>
@@ -20134,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D942">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E942" t="s">
         <v>28</v>
@@ -20151,7 +20151,7 @@
         <v>27</v>
       </c>
       <c r="D943">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E943" t="s">
         <v>28</v>
@@ -20168,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="D944">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E944" t="s">
         <v>28</v>
@@ -20185,7 +20185,7 @@
         <v>27</v>
       </c>
       <c r="D945">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E945" t="s">
         <v>28</v>
@@ -20202,7 +20202,7 @@
         <v>27</v>
       </c>
       <c r="D946">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E946" t="s">
         <v>28</v>
@@ -20219,7 +20219,7 @@
         <v>27</v>
       </c>
       <c r="D947">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E947" t="s">
         <v>28</v>
@@ -20236,7 +20236,7 @@
         <v>27</v>
       </c>
       <c r="D948">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E948" t="s">
         <v>28</v>
@@ -20253,7 +20253,7 @@
         <v>27</v>
       </c>
       <c r="D949">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E949" t="s">
         <v>28</v>
@@ -20270,7 +20270,7 @@
         <v>27</v>
       </c>
       <c r="D950">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E950" t="s">
         <v>28</v>
@@ -20287,7 +20287,7 @@
         <v>27</v>
       </c>
       <c r="D951">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E951" t="s">
         <v>28</v>
@@ -20304,7 +20304,7 @@
         <v>27</v>
       </c>
       <c r="D952">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E952" t="s">
         <v>28</v>
@@ -20321,7 +20321,7 @@
         <v>27</v>
       </c>
       <c r="D953">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E953" t="s">
         <v>28</v>
@@ -20338,7 +20338,7 @@
         <v>27</v>
       </c>
       <c r="D954">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E954" t="s">
         <v>28</v>
@@ -20355,7 +20355,7 @@
         <v>27</v>
       </c>
       <c r="D955">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E955" t="s">
         <v>28</v>
@@ -20372,7 +20372,7 @@
         <v>27</v>
       </c>
       <c r="D956">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E956" t="s">
         <v>28</v>
@@ -20389,7 +20389,7 @@
         <v>27</v>
       </c>
       <c r="D957">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E957" t="s">
         <v>28</v>
@@ -20406,7 +20406,7 @@
         <v>27</v>
       </c>
       <c r="D958">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E958" t="s">
         <v>28</v>
@@ -20423,7 +20423,7 @@
         <v>27</v>
       </c>
       <c r="D959">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E959" t="s">
         <v>28</v>
@@ -20440,7 +20440,7 @@
         <v>27</v>
       </c>
       <c r="D960">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E960" t="s">
         <v>28</v>
@@ -20474,7 +20474,7 @@
         <v>27</v>
       </c>
       <c r="D962">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E962" t="s">
         <v>28</v>
@@ -20491,7 +20491,7 @@
         <v>27</v>
       </c>
       <c r="D963">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E963" t="s">
         <v>28</v>
@@ -20525,7 +20525,7 @@
         <v>27</v>
       </c>
       <c r="D965">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E965" t="s">
         <v>28</v>
@@ -20542,7 +20542,7 @@
         <v>27</v>
       </c>
       <c r="D966">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E966" t="s">
         <v>28</v>
@@ -20559,7 +20559,7 @@
         <v>27</v>
       </c>
       <c r="D967">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E967" t="s">
         <v>28</v>
@@ -20576,7 +20576,7 @@
         <v>27</v>
       </c>
       <c r="D968">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E968" t="s">
         <v>28</v>
@@ -20593,7 +20593,7 @@
         <v>27</v>
       </c>
       <c r="D969">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E969" t="s">
         <v>28</v>
@@ -20610,7 +20610,7 @@
         <v>27</v>
       </c>
       <c r="D970">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E970" t="s">
         <v>28</v>
@@ -20627,7 +20627,7 @@
         <v>27</v>
       </c>
       <c r="D971">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E971" t="s">
         <v>28</v>
@@ -20644,7 +20644,7 @@
         <v>27</v>
       </c>
       <c r="D972">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E972" t="s">
         <v>28</v>
@@ -20661,7 +20661,7 @@
         <v>27</v>
       </c>
       <c r="D973">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E973" t="s">
         <v>28</v>
@@ -20678,7 +20678,7 @@
         <v>27</v>
       </c>
       <c r="D974">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E974" t="s">
         <v>28</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="D975">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E975" t="s">
         <v>28</v>
@@ -20712,7 +20712,7 @@
         <v>27</v>
       </c>
       <c r="D976">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E976" t="s">
         <v>28</v>
@@ -20729,7 +20729,7 @@
         <v>27</v>
       </c>
       <c r="D977">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E977" t="s">
         <v>28</v>
@@ -20746,7 +20746,7 @@
         <v>27</v>
       </c>
       <c r="D978">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E978" t="s">
         <v>28</v>
@@ -20763,7 +20763,7 @@
         <v>27</v>
       </c>
       <c r="D979">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E979" t="s">
         <v>28</v>
@@ -20780,7 +20780,7 @@
         <v>27</v>
       </c>
       <c r="D980">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E980" t="s">
         <v>28</v>
@@ -20797,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="D981">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E981" t="s">
         <v>28</v>
@@ -20814,7 +20814,7 @@
         <v>27</v>
       </c>
       <c r="D982">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E982" t="s">
         <v>28</v>
@@ -20831,7 +20831,7 @@
         <v>27</v>
       </c>
       <c r="D983">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E983" t="s">
         <v>28</v>
@@ -20848,7 +20848,7 @@
         <v>27</v>
       </c>
       <c r="D984">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E984" t="s">
         <v>28</v>
@@ -20882,7 +20882,7 @@
         <v>27</v>
       </c>
       <c r="D986">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E986" t="s">
         <v>28</v>
@@ -20899,7 +20899,7 @@
         <v>27</v>
       </c>
       <c r="D987">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E987" t="s">
         <v>28</v>
@@ -20916,7 +20916,7 @@
         <v>27</v>
       </c>
       <c r="D988">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E988" t="s">
         <v>28</v>
@@ -20933,7 +20933,7 @@
         <v>27</v>
       </c>
       <c r="D989">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E989" t="s">
         <v>28</v>
@@ -20950,7 +20950,7 @@
         <v>27</v>
       </c>
       <c r="D990">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E990" t="s">
         <v>28</v>
@@ -20967,7 +20967,7 @@
         <v>27</v>
       </c>
       <c r="D991">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E991" t="s">
         <v>28</v>
@@ -20984,7 +20984,7 @@
         <v>27</v>
       </c>
       <c r="D992">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E992" t="s">
         <v>28</v>
@@ -21001,7 +21001,7 @@
         <v>27</v>
       </c>
       <c r="D993">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E993" t="s">
         <v>28</v>
@@ -21018,7 +21018,7 @@
         <v>27</v>
       </c>
       <c r="D994">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E994" t="s">
         <v>28</v>
@@ -21035,7 +21035,7 @@
         <v>27</v>
       </c>
       <c r="D995">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E995" t="s">
         <v>28</v>
@@ -21052,7 +21052,7 @@
         <v>27</v>
       </c>
       <c r="D996">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E996" t="s">
         <v>28</v>
@@ -21069,7 +21069,7 @@
         <v>27</v>
       </c>
       <c r="D997">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E997" t="s">
         <v>28</v>
@@ -21086,7 +21086,7 @@
         <v>27</v>
       </c>
       <c r="D998">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E998" t="s">
         <v>28</v>
@@ -21120,7 +21120,7 @@
         <v>27</v>
       </c>
       <c r="D1000">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1000" t="s">
         <v>28</v>
@@ -21137,7 +21137,7 @@
         <v>27</v>
       </c>
       <c r="D1001">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1001" t="s">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>27</v>
       </c>
       <c r="D1003">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1003" t="s">
         <v>28</v>
@@ -21188,7 +21188,7 @@
         <v>27</v>
       </c>
       <c r="D1004">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E1004" t="s">
         <v>28</v>
@@ -21205,7 +21205,7 @@
         <v>27</v>
       </c>
       <c r="D1005">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1005" t="s">
         <v>28</v>
@@ -21222,7 +21222,7 @@
         <v>27</v>
       </c>
       <c r="D1006">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1006" t="s">
         <v>28</v>
@@ -21239,7 +21239,7 @@
         <v>27</v>
       </c>
       <c r="D1007">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1007" t="s">
         <v>28</v>
@@ -21256,7 +21256,7 @@
         <v>27</v>
       </c>
       <c r="D1008">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1008" t="s">
         <v>28</v>
@@ -21273,7 +21273,7 @@
         <v>27</v>
       </c>
       <c r="D1009">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E1009" t="s">
         <v>28</v>
@@ -21290,7 +21290,7 @@
         <v>27</v>
       </c>
       <c r="D1010">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1010" t="s">
         <v>28</v>
@@ -21307,7 +21307,7 @@
         <v>27</v>
       </c>
       <c r="D1011">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E1011" t="s">
         <v>28</v>
@@ -21324,7 +21324,7 @@
         <v>27</v>
       </c>
       <c r="D1012">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E1012" t="s">
         <v>28</v>
@@ -21341,7 +21341,7 @@
         <v>27</v>
       </c>
       <c r="D1013">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1013" t="s">
         <v>28</v>
@@ -21358,7 +21358,7 @@
         <v>27</v>
       </c>
       <c r="D1014">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E1014" t="s">
         <v>28</v>
@@ -21375,7 +21375,7 @@
         <v>27</v>
       </c>
       <c r="D1015">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E1015" t="s">
         <v>28</v>
@@ -21392,7 +21392,7 @@
         <v>27</v>
       </c>
       <c r="D1016">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E1016" t="s">
         <v>28</v>
@@ -21409,7 +21409,7 @@
         <v>27</v>
       </c>
       <c r="D1017">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E1017" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>27</v>
       </c>
       <c r="D1018">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1018" t="s">
         <v>28</v>
@@ -21460,7 +21460,7 @@
         <v>27</v>
       </c>
       <c r="D1020">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1020" t="s">
         <v>28</v>
@@ -21477,7 +21477,7 @@
         <v>27</v>
       </c>
       <c r="D1021">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E1021" t="s">
         <v>28</v>
@@ -21494,7 +21494,7 @@
         <v>27</v>
       </c>
       <c r="D1022">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1022" t="s">
         <v>28</v>
@@ -21511,7 +21511,7 @@
         <v>27</v>
       </c>
       <c r="D1023">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E1023" t="s">
         <v>28</v>
@@ -21528,7 +21528,7 @@
         <v>27</v>
       </c>
       <c r="D1024">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1024" t="s">
         <v>28</v>
@@ -21545,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1025" t="s">
         <v>28</v>
@@ -21562,7 +21562,7 @@
         <v>27</v>
       </c>
       <c r="D1026">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E1026" t="s">
         <v>28</v>
@@ -21579,7 +21579,7 @@
         <v>27</v>
       </c>
       <c r="D1027">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E1027" t="s">
         <v>28</v>
@@ -21596,7 +21596,7 @@
         <v>27</v>
       </c>
       <c r="D1028">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E1028" t="s">
         <v>28</v>
@@ -21630,7 +21630,7 @@
         <v>27</v>
       </c>
       <c r="D1030">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E1030" t="s">
         <v>28</v>
@@ -21647,7 +21647,7 @@
         <v>27</v>
       </c>
       <c r="D1031">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1031" t="s">
         <v>28</v>
@@ -21664,7 +21664,7 @@
         <v>27</v>
       </c>
       <c r="D1032">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1032" t="s">
         <v>28</v>
@@ -21681,7 +21681,7 @@
         <v>27</v>
       </c>
       <c r="D1033">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1033" t="s">
         <v>28</v>
@@ -21698,7 +21698,7 @@
         <v>27</v>
       </c>
       <c r="D1034">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E1034" t="s">
         <v>28</v>
@@ -21715,7 +21715,7 @@
         <v>27</v>
       </c>
       <c r="D1035">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E1035" t="s">
         <v>28</v>
@@ -21732,7 +21732,7 @@
         <v>27</v>
       </c>
       <c r="D1036">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E1036" t="s">
         <v>28</v>
@@ -21749,7 +21749,7 @@
         <v>27</v>
       </c>
       <c r="D1037">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1037" t="s">
         <v>28</v>
@@ -21766,7 +21766,7 @@
         <v>27</v>
       </c>
       <c r="D1038">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1038" t="s">
         <v>28</v>
@@ -21783,7 +21783,7 @@
         <v>27</v>
       </c>
       <c r="D1039">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E1039" t="s">
         <v>28</v>
@@ -21800,7 +21800,7 @@
         <v>27</v>
       </c>
       <c r="D1040">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1040" t="s">
         <v>28</v>
@@ -21817,7 +21817,7 @@
         <v>27</v>
       </c>
       <c r="D1041">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E1041" t="s">
         <v>28</v>
@@ -21834,7 +21834,7 @@
         <v>27</v>
       </c>
       <c r="D1042">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E1042" t="s">
         <v>28</v>
@@ -21851,7 +21851,7 @@
         <v>27</v>
       </c>
       <c r="D1043">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1043" t="s">
         <v>28</v>
@@ -21868,7 +21868,7 @@
         <v>27</v>
       </c>
       <c r="D1044">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1044" t="s">
         <v>28</v>
@@ -21885,7 +21885,7 @@
         <v>27</v>
       </c>
       <c r="D1045">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E1045" t="s">
         <v>28</v>
@@ -21902,7 +21902,7 @@
         <v>27</v>
       </c>
       <c r="D1046">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E1046" t="s">
         <v>28</v>
@@ -21919,7 +21919,7 @@
         <v>27</v>
       </c>
       <c r="D1047">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E1047" t="s">
         <v>28</v>
@@ -21936,7 +21936,7 @@
         <v>27</v>
       </c>
       <c r="D1048">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E1048" t="s">
         <v>28</v>
@@ -21953,7 +21953,7 @@
         <v>27</v>
       </c>
       <c r="D1049">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1049" t="s">
         <v>28</v>
@@ -21970,7 +21970,7 @@
         <v>27</v>
       </c>
       <c r="D1050">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1050" t="s">
         <v>28</v>
@@ -21987,7 +21987,7 @@
         <v>27</v>
       </c>
       <c r="D1051">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E1051" t="s">
         <v>28</v>
@@ -22004,7 +22004,7 @@
         <v>27</v>
       </c>
       <c r="D1052">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E1052" t="s">
         <v>28</v>
@@ -22021,7 +22021,7 @@
         <v>27</v>
       </c>
       <c r="D1053">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E1053" t="s">
         <v>28</v>
@@ -22038,7 +22038,7 @@
         <v>27</v>
       </c>
       <c r="D1054">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E1054" t="s">
         <v>28</v>
@@ -22055,7 +22055,7 @@
         <v>27</v>
       </c>
       <c r="D1055">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1055" t="s">
         <v>28</v>
@@ -22072,7 +22072,7 @@
         <v>27</v>
       </c>
       <c r="D1056">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E1056" t="s">
         <v>28</v>
@@ -22089,7 +22089,7 @@
         <v>27</v>
       </c>
       <c r="D1057">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E1057" t="s">
         <v>28</v>
@@ -22106,7 +22106,7 @@
         <v>27</v>
       </c>
       <c r="D1058">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E1058" t="s">
         <v>28</v>
@@ -22123,7 +22123,7 @@
         <v>27</v>
       </c>
       <c r="D1059">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E1059" t="s">
         <v>28</v>
@@ -22140,7 +22140,7 @@
         <v>27</v>
       </c>
       <c r="D1060">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E1060" t="s">
         <v>28</v>
@@ -22157,7 +22157,7 @@
         <v>27</v>
       </c>
       <c r="D1061">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E1061" t="s">
         <v>28</v>
@@ -22174,7 +22174,7 @@
         <v>27</v>
       </c>
       <c r="D1062">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1062" t="s">
         <v>28</v>
@@ -22191,7 +22191,7 @@
         <v>27</v>
       </c>
       <c r="D1063">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1063" t="s">
         <v>28</v>
@@ -22225,7 +22225,7 @@
         <v>27</v>
       </c>
       <c r="D1065">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E1065" t="s">
         <v>28</v>
@@ -22242,7 +22242,7 @@
         <v>27</v>
       </c>
       <c r="D1066">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1066" t="s">
         <v>28</v>
@@ -22259,7 +22259,7 @@
         <v>27</v>
       </c>
       <c r="D1067">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1067" t="s">
         <v>28</v>
@@ -22276,7 +22276,7 @@
         <v>27</v>
       </c>
       <c r="D1068">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1068" t="s">
         <v>28</v>
@@ -22293,7 +22293,7 @@
         <v>27</v>
       </c>
       <c r="D1069">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1069" t="s">
         <v>28</v>
@@ -22310,7 +22310,7 @@
         <v>27</v>
       </c>
       <c r="D1070">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E1070" t="s">
         <v>28</v>
@@ -22327,7 +22327,7 @@
         <v>27</v>
       </c>
       <c r="D1071">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E1071" t="s">
         <v>28</v>
@@ -22344,7 +22344,7 @@
         <v>27</v>
       </c>
       <c r="D1072">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E1072" t="s">
         <v>28</v>
@@ -22361,7 +22361,7 @@
         <v>27</v>
       </c>
       <c r="D1073">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E1073" t="s">
         <v>28</v>
@@ -22378,7 +22378,7 @@
         <v>27</v>
       </c>
       <c r="D1074">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E1074" t="s">
         <v>28</v>
@@ -22395,7 +22395,7 @@
         <v>27</v>
       </c>
       <c r="D1075">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1075" t="s">
         <v>28</v>
@@ -22412,7 +22412,7 @@
         <v>27</v>
       </c>
       <c r="D1076">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1076" t="s">
         <v>28</v>
@@ -22429,7 +22429,7 @@
         <v>27</v>
       </c>
       <c r="D1077">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1077" t="s">
         <v>28</v>
@@ -22446,7 +22446,7 @@
         <v>27</v>
       </c>
       <c r="D1078">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1078" t="s">
         <v>28</v>
@@ -22463,7 +22463,7 @@
         <v>27</v>
       </c>
       <c r="D1079">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1079" t="s">
         <v>28</v>
@@ -22480,7 +22480,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E1080" t="s">
         <v>28</v>
@@ -22497,7 +22497,7 @@
         <v>27</v>
       </c>
       <c r="D1081">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E1081" t="s">
         <v>28</v>
@@ -22514,7 +22514,7 @@
         <v>27</v>
       </c>
       <c r="D1082">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E1082" t="s">
         <v>28</v>
@@ -22531,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="D1083">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1083" t="s">
         <v>28</v>
@@ -22548,7 +22548,7 @@
         <v>27</v>
       </c>
       <c r="D1084">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1084" t="s">
         <v>28</v>
@@ -22565,7 +22565,7 @@
         <v>27</v>
       </c>
       <c r="D1085">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E1085" t="s">
         <v>28</v>
@@ -22582,7 +22582,7 @@
         <v>27</v>
       </c>
       <c r="D1086">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1086" t="s">
         <v>28</v>
@@ -22599,7 +22599,7 @@
         <v>27</v>
       </c>
       <c r="D1087">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1087" t="s">
         <v>28</v>
@@ -22616,7 +22616,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1088" t="s">
         <v>28</v>
@@ -22633,7 +22633,7 @@
         <v>27</v>
       </c>
       <c r="D1089">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1089" t="s">
         <v>28</v>
@@ -22650,7 +22650,7 @@
         <v>27</v>
       </c>
       <c r="D1090">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1090" t="s">
         <v>28</v>
@@ -22667,7 +22667,7 @@
         <v>27</v>
       </c>
       <c r="D1091">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1091" t="s">
         <v>28</v>
@@ -22684,7 +22684,7 @@
         <v>27</v>
       </c>
       <c r="D1092">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E1092" t="s">
         <v>28</v>
@@ -22701,7 +22701,7 @@
         <v>27</v>
       </c>
       <c r="D1093">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1093" t="s">
         <v>28</v>
@@ -22718,7 +22718,7 @@
         <v>27</v>
       </c>
       <c r="D1094">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1094" t="s">
         <v>28</v>
@@ -22735,7 +22735,7 @@
         <v>27</v>
       </c>
       <c r="D1095">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E1095" t="s">
         <v>28</v>
@@ -22752,7 +22752,7 @@
         <v>27</v>
       </c>
       <c r="D1096">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1096" t="s">
         <v>28</v>
@@ -22786,7 +22786,7 @@
         <v>27</v>
       </c>
       <c r="D1098">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1098" t="s">
         <v>28</v>
@@ -22803,7 +22803,7 @@
         <v>27</v>
       </c>
       <c r="D1099">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1099" t="s">
         <v>28</v>
@@ -22820,7 +22820,7 @@
         <v>27</v>
       </c>
       <c r="D1100">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1100" t="s">
         <v>28</v>
@@ -22837,7 +22837,7 @@
         <v>27</v>
       </c>
       <c r="D1101">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E1101" t="s">
         <v>28</v>
@@ -22854,7 +22854,7 @@
         <v>27</v>
       </c>
       <c r="D1102">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E1102" t="s">
         <v>28</v>
@@ -22871,7 +22871,7 @@
         <v>27</v>
       </c>
       <c r="D1103">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1103" t="s">
         <v>28</v>
@@ -22888,7 +22888,7 @@
         <v>27</v>
       </c>
       <c r="D1104">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1104" t="s">
         <v>28</v>
@@ -22905,7 +22905,7 @@
         <v>27</v>
       </c>
       <c r="D1105">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1105" t="s">
         <v>28</v>
@@ -22922,7 +22922,7 @@
         <v>27</v>
       </c>
       <c r="D1106">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1106" t="s">
         <v>28</v>
@@ -22939,7 +22939,7 @@
         <v>27</v>
       </c>
       <c r="D1107">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1107" t="s">
         <v>28</v>
@@ -22956,7 +22956,7 @@
         <v>27</v>
       </c>
       <c r="D1108">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1108" t="s">
         <v>28</v>
@@ -22973,7 +22973,7 @@
         <v>27</v>
       </c>
       <c r="D1109">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E1109" t="s">
         <v>28</v>
@@ -22990,7 +22990,7 @@
         <v>27</v>
       </c>
       <c r="D1110">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1110" t="s">
         <v>28</v>
@@ -23007,7 +23007,7 @@
         <v>27</v>
       </c>
       <c r="D1111">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1111" t="s">
         <v>28</v>
@@ -23024,7 +23024,7 @@
         <v>27</v>
       </c>
       <c r="D1112">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1112" t="s">
         <v>28</v>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1296</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1341</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1326</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1207</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1410</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1304</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1258</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1196</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1212</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1319</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1346</v>
+        <v>1296</v>
       </c>
     </row>
   </sheetData>
@@ -4154,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -4188,7 +4188,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -4205,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -4222,7 +4222,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -4256,7 +4256,7 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -4273,7 +4273,7 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4307,7 +4307,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4341,7 +4341,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -4358,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4409,7 +4409,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -4426,7 +4426,7 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -4443,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -4460,7 +4460,7 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
@@ -4494,7 +4494,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -4545,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
         <v>28</v>
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -4579,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -4596,7 +4596,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -4613,7 +4613,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4681,7 +4681,7 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4698,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -4715,7 +4715,7 @@
         <v>27</v>
       </c>
       <c r="D35">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E35" t="s">
         <v>28</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -4749,7 +4749,7 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
         <v>28</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="D38">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E38" t="s">
         <v>28</v>
@@ -4783,7 +4783,7 @@
         <v>27</v>
       </c>
       <c r="D39">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
         <v>28</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
@@ -4817,7 +4817,7 @@
         <v>27</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4834,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4851,7 +4851,7 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
@@ -4885,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="D45">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
         <v>27</v>
       </c>
       <c r="D46">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -4919,7 +4919,7 @@
         <v>27</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="D48">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4953,7 +4953,7 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
@@ -4970,7 +4970,7 @@
         <v>27</v>
       </c>
       <c r="D50">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -4987,7 +4987,7 @@
         <v>27</v>
       </c>
       <c r="D51">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
@@ -5004,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5038,7 +5038,7 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E54" t="s">
         <v>28</v>
@@ -5055,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="D55">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -5072,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>28</v>
@@ -5089,7 +5089,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E57" t="s">
         <v>28</v>
@@ -5106,7 +5106,7 @@
         <v>27</v>
       </c>
       <c r="D58">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -5123,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E59" t="s">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         <v>27</v>
       </c>
       <c r="D60">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E60" t="s">
         <v>28</v>
@@ -5157,7 +5157,7 @@
         <v>27</v>
       </c>
       <c r="D61">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -5174,7 +5174,7 @@
         <v>27</v>
       </c>
       <c r="D62">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="D64">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
@@ -5225,7 +5225,7 @@
         <v>27</v>
       </c>
       <c r="D65">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -5242,7 +5242,7 @@
         <v>27</v>
       </c>
       <c r="D66">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="D67">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
@@ -5310,7 +5310,7 @@
         <v>27</v>
       </c>
       <c r="D70">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="D71">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -5344,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="D72">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
@@ -5361,7 +5361,7 @@
         <v>27</v>
       </c>
       <c r="D73">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -5378,7 +5378,7 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
@@ -5395,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="D75">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="D76">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
@@ -5429,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="D77">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -5446,7 +5446,7 @@
         <v>27</v>
       </c>
       <c r="D78">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
@@ -5463,7 +5463,7 @@
         <v>27</v>
       </c>
       <c r="D79">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
@@ -5497,7 +5497,7 @@
         <v>27</v>
       </c>
       <c r="D81">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -5514,7 +5514,7 @@
         <v>27</v>
       </c>
       <c r="D82">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
@@ -5531,7 +5531,7 @@
         <v>27</v>
       </c>
       <c r="D83">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
@@ -5548,7 +5548,7 @@
         <v>27</v>
       </c>
       <c r="D84">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
@@ -5565,7 +5565,7 @@
         <v>27</v>
       </c>
       <c r="D85">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -5582,7 +5582,7 @@
         <v>27</v>
       </c>
       <c r="D86">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
@@ -5599,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="D87">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
@@ -5616,7 +5616,7 @@
         <v>27</v>
       </c>
       <c r="D88">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -5633,7 +5633,7 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="D90">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -5667,7 +5667,7 @@
         <v>27</v>
       </c>
       <c r="D91">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E91" t="s">
         <v>28</v>
@@ -5684,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
@@ -5701,7 +5701,7 @@
         <v>27</v>
       </c>
       <c r="D93">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E93" t="s">
         <v>28</v>
@@ -5718,7 +5718,7 @@
         <v>27</v>
       </c>
       <c r="D94">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E94" t="s">
         <v>28</v>
@@ -5735,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D95">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -5752,7 +5752,7 @@
         <v>27</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E96" t="s">
         <v>28</v>
@@ -5769,7 +5769,7 @@
         <v>27</v>
       </c>
       <c r="D97">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E97" t="s">
         <v>28</v>
@@ -5786,7 +5786,7 @@
         <v>27</v>
       </c>
       <c r="D98">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="D99">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E99" t="s">
         <v>28</v>
@@ -5820,7 +5820,7 @@
         <v>27</v>
       </c>
       <c r="D100">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E100" t="s">
         <v>28</v>
@@ -5837,7 +5837,7 @@
         <v>27</v>
       </c>
       <c r="D101">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E101" t="s">
         <v>28</v>
@@ -5854,7 +5854,7 @@
         <v>27</v>
       </c>
       <c r="D102">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E102" t="s">
         <v>28</v>
@@ -5871,7 +5871,7 @@
         <v>27</v>
       </c>
       <c r="D103">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E103" t="s">
         <v>28</v>
@@ -5888,7 +5888,7 @@
         <v>27</v>
       </c>
       <c r="D104">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E104" t="s">
         <v>28</v>
@@ -5905,7 +5905,7 @@
         <v>27</v>
       </c>
       <c r="D105">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E105" t="s">
         <v>28</v>
@@ -5922,7 +5922,7 @@
         <v>27</v>
       </c>
       <c r="D106">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>27</v>
       </c>
       <c r="D107">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E107" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="D108">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5973,7 +5973,7 @@
         <v>27</v>
       </c>
       <c r="D109">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E109" t="s">
         <v>28</v>
@@ -5990,7 +5990,7 @@
         <v>27</v>
       </c>
       <c r="D110">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E110" t="s">
         <v>28</v>
@@ -6007,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="D111">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="D112">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
@@ -6058,7 +6058,7 @@
         <v>27</v>
       </c>
       <c r="D114">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>27</v>
       </c>
       <c r="D115">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -6092,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="D116">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E116" t="s">
         <v>28</v>
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="D117">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E117" t="s">
         <v>28</v>
@@ -6160,7 +6160,7 @@
         <v>27</v>
       </c>
       <c r="D120">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E120" t="s">
         <v>28</v>
@@ -6177,7 +6177,7 @@
         <v>27</v>
       </c>
       <c r="D121">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E121" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="D122">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E122" t="s">
         <v>28</v>
@@ -6211,7 +6211,7 @@
         <v>27</v>
       </c>
       <c r="D123">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E123" t="s">
         <v>28</v>
@@ -6228,7 +6228,7 @@
         <v>27</v>
       </c>
       <c r="D124">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E124" t="s">
         <v>28</v>
@@ -6245,7 +6245,7 @@
         <v>27</v>
       </c>
       <c r="D125">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
@@ -6262,7 +6262,7 @@
         <v>27</v>
       </c>
       <c r="D126">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -6279,7 +6279,7 @@
         <v>27</v>
       </c>
       <c r="D127">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E127" t="s">
         <v>28</v>
@@ -6296,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="D128">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E128" t="s">
         <v>28</v>
@@ -6313,7 +6313,7 @@
         <v>27</v>
       </c>
       <c r="D129">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
@@ -6330,7 +6330,7 @@
         <v>27</v>
       </c>
       <c r="D130">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E130" t="s">
         <v>28</v>
@@ -6347,7 +6347,7 @@
         <v>27</v>
       </c>
       <c r="D131">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E131" t="s">
         <v>28</v>
@@ -6398,7 +6398,7 @@
         <v>27</v>
       </c>
       <c r="D134">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E134" t="s">
         <v>28</v>
@@ -6415,7 +6415,7 @@
         <v>27</v>
       </c>
       <c r="D135">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E135" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="D136">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E136" t="s">
         <v>28</v>
@@ -6466,7 +6466,7 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E138" t="s">
         <v>28</v>
@@ -6483,7 +6483,7 @@
         <v>27</v>
       </c>
       <c r="D139">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E139" t="s">
         <v>28</v>
@@ -6500,7 +6500,7 @@
         <v>27</v>
       </c>
       <c r="D140">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E140" t="s">
         <v>28</v>
@@ -6517,7 +6517,7 @@
         <v>27</v>
       </c>
       <c r="D141">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E141" t="s">
         <v>28</v>
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="D142">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E142" t="s">
         <v>28</v>
@@ -6551,7 +6551,7 @@
         <v>27</v>
       </c>
       <c r="D143">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E143" t="s">
         <v>28</v>
@@ -6568,7 +6568,7 @@
         <v>27</v>
       </c>
       <c r="D144">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E144" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="D145">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E145" t="s">
         <v>28</v>
@@ -6602,7 +6602,7 @@
         <v>27</v>
       </c>
       <c r="D146">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E146" t="s">
         <v>28</v>
@@ -6619,7 +6619,7 @@
         <v>27</v>
       </c>
       <c r="D147">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E147" t="s">
         <v>28</v>
@@ -6636,7 +6636,7 @@
         <v>27</v>
       </c>
       <c r="D148">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E148" t="s">
         <v>28</v>
@@ -6653,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="D149">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6670,7 +6670,7 @@
         <v>27</v>
       </c>
       <c r="D150">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E150" t="s">
         <v>28</v>
@@ -6687,7 +6687,7 @@
         <v>27</v>
       </c>
       <c r="D151">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>27</v>
       </c>
       <c r="D152">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E152" t="s">
         <v>28</v>
@@ -6721,7 +6721,7 @@
         <v>27</v>
       </c>
       <c r="D153">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E153" t="s">
         <v>28</v>
@@ -6738,7 +6738,7 @@
         <v>27</v>
       </c>
       <c r="D154">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E154" t="s">
         <v>28</v>
@@ -6755,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -6772,7 +6772,7 @@
         <v>27</v>
       </c>
       <c r="D156">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E156" t="s">
         <v>28</v>
@@ -6789,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="D157">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E157" t="s">
         <v>28</v>
@@ -6806,7 +6806,7 @@
         <v>27</v>
       </c>
       <c r="D158">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E158" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="D159">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E159" t="s">
         <v>28</v>
@@ -6840,7 +6840,7 @@
         <v>27</v>
       </c>
       <c r="D160">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E160" t="s">
         <v>28</v>
@@ -6857,7 +6857,7 @@
         <v>27</v>
       </c>
       <c r="D161">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
@@ -6891,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="D163">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E163" t="s">
         <v>28</v>
@@ -6908,7 +6908,7 @@
         <v>27</v>
       </c>
       <c r="D164">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E164" t="s">
         <v>28</v>
@@ -6925,7 +6925,7 @@
         <v>27</v>
       </c>
       <c r="D165">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E165" t="s">
         <v>28</v>
@@ -6942,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="D166">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E166" t="s">
         <v>28</v>
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="D167">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E167" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="D168">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E168" t="s">
         <v>28</v>
@@ -6993,7 +6993,7 @@
         <v>27</v>
       </c>
       <c r="D169">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E169" t="s">
         <v>28</v>
@@ -7010,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="D170">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E170" t="s">
         <v>28</v>
@@ -7027,7 +7027,7 @@
         <v>27</v>
       </c>
       <c r="D171">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E171" t="s">
         <v>28</v>
@@ -7044,7 +7044,7 @@
         <v>27</v>
       </c>
       <c r="D172">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E172" t="s">
         <v>28</v>
@@ -7061,7 +7061,7 @@
         <v>27</v>
       </c>
       <c r="D173">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E173" t="s">
         <v>28</v>
@@ -7078,7 +7078,7 @@
         <v>27</v>
       </c>
       <c r="D174">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E174" t="s">
         <v>28</v>
@@ -7095,7 +7095,7 @@
         <v>27</v>
       </c>
       <c r="D175">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E175" t="s">
         <v>28</v>
@@ -7112,7 +7112,7 @@
         <v>27</v>
       </c>
       <c r="D176">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E176" t="s">
         <v>28</v>
@@ -7129,7 +7129,7 @@
         <v>27</v>
       </c>
       <c r="D177">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E177" t="s">
         <v>28</v>
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="D178">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E178" t="s">
         <v>28</v>
@@ -7163,7 +7163,7 @@
         <v>27</v>
       </c>
       <c r="D179">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E179" t="s">
         <v>28</v>
@@ -7180,7 +7180,7 @@
         <v>27</v>
       </c>
       <c r="D180">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -7197,7 +7197,7 @@
         <v>27</v>
       </c>
       <c r="D181">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E181" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="D182">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E182" t="s">
         <v>28</v>
@@ -7231,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="D183">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
@@ -7248,7 +7248,7 @@
         <v>27</v>
       </c>
       <c r="D184">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E184" t="s">
         <v>28</v>
@@ -7265,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="D185">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E185" t="s">
         <v>28</v>
@@ -7282,7 +7282,7 @@
         <v>27</v>
       </c>
       <c r="D186">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E186" t="s">
         <v>28</v>
@@ -7299,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="D187">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E187" t="s">
         <v>28</v>
@@ -7316,7 +7316,7 @@
         <v>27</v>
       </c>
       <c r="D188">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -7333,7 +7333,7 @@
         <v>27</v>
       </c>
       <c r="D189">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E189" t="s">
         <v>28</v>
@@ -7350,7 +7350,7 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E190" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="D191">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
@@ -7384,7 +7384,7 @@
         <v>27</v>
       </c>
       <c r="D192">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E192" t="s">
         <v>28</v>
@@ -7401,7 +7401,7 @@
         <v>27</v>
       </c>
       <c r="D193">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E193" t="s">
         <v>28</v>
@@ -7418,7 +7418,7 @@
         <v>27</v>
       </c>
       <c r="D194">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E194" t="s">
         <v>28</v>
@@ -7435,7 +7435,7 @@
         <v>27</v>
       </c>
       <c r="D195">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E195" t="s">
         <v>28</v>
@@ -7452,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="D196">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E196" t="s">
         <v>28</v>
@@ -7469,7 +7469,7 @@
         <v>27</v>
       </c>
       <c r="D197">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E197" t="s">
         <v>28</v>
@@ -7486,7 +7486,7 @@
         <v>27</v>
       </c>
       <c r="D198">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E198" t="s">
         <v>28</v>
@@ -7503,7 +7503,7 @@
         <v>27</v>
       </c>
       <c r="D199">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E199" t="s">
         <v>28</v>
@@ -7520,7 +7520,7 @@
         <v>27</v>
       </c>
       <c r="D200">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E200" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>27</v>
       </c>
       <c r="D201">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E201" t="s">
         <v>28</v>
@@ -7554,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="D202">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E202" t="s">
         <v>28</v>
@@ -7571,7 +7571,7 @@
         <v>27</v>
       </c>
       <c r="D203">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
@@ -7588,7 +7588,7 @@
         <v>27</v>
       </c>
       <c r="D204">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E204" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="D205">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -7622,7 +7622,7 @@
         <v>27</v>
       </c>
       <c r="D206">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E206" t="s">
         <v>28</v>
@@ -7639,7 +7639,7 @@
         <v>27</v>
       </c>
       <c r="D207">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E207" t="s">
         <v>28</v>
@@ -7656,7 +7656,7 @@
         <v>27</v>
       </c>
       <c r="D208">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E208" t="s">
         <v>28</v>
@@ -7673,7 +7673,7 @@
         <v>27</v>
       </c>
       <c r="D209">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E209" t="s">
         <v>28</v>
@@ -7690,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="D210">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E210" t="s">
         <v>28</v>
@@ -7707,7 +7707,7 @@
         <v>27</v>
       </c>
       <c r="D211">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E211" t="s">
         <v>28</v>
@@ -7741,7 +7741,7 @@
         <v>27</v>
       </c>
       <c r="D213">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E213" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="D214">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E214" t="s">
         <v>28</v>
@@ -7775,7 +7775,7 @@
         <v>27</v>
       </c>
       <c r="D215">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E215" t="s">
         <v>28</v>
@@ -7792,7 +7792,7 @@
         <v>27</v>
       </c>
       <c r="D216">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E216" t="s">
         <v>28</v>
@@ -7809,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="D217">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E217" t="s">
         <v>28</v>
@@ -7826,7 +7826,7 @@
         <v>27</v>
       </c>
       <c r="D218">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E218" t="s">
         <v>28</v>
@@ -7843,7 +7843,7 @@
         <v>27</v>
       </c>
       <c r="D219">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E219" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="D220">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E220" t="s">
         <v>28</v>
@@ -7877,7 +7877,7 @@
         <v>27</v>
       </c>
       <c r="D221">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E221" t="s">
         <v>28</v>
@@ -7911,7 +7911,7 @@
         <v>27</v>
       </c>
       <c r="D223">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E223" t="s">
         <v>28</v>
@@ -7928,7 +7928,7 @@
         <v>27</v>
       </c>
       <c r="D224">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E224" t="s">
         <v>28</v>
@@ -7945,7 +7945,7 @@
         <v>27</v>
       </c>
       <c r="D225">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E225" t="s">
         <v>28</v>
@@ -7962,7 +7962,7 @@
         <v>27</v>
       </c>
       <c r="D226">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E226" t="s">
         <v>28</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="D228">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E228" t="s">
         <v>28</v>
@@ -8013,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="D229">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E229" t="s">
         <v>28</v>
@@ -8030,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="D230">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E230" t="s">
         <v>28</v>
@@ -8047,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="D231">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E231" t="s">
         <v>28</v>
@@ -8064,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="D232">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E232" t="s">
         <v>28</v>
@@ -8081,7 +8081,7 @@
         <v>27</v>
       </c>
       <c r="D233">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E233" t="s">
         <v>28</v>
@@ -8098,7 +8098,7 @@
         <v>27</v>
       </c>
       <c r="D234">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E234" t="s">
         <v>28</v>
@@ -8132,7 +8132,7 @@
         <v>27</v>
       </c>
       <c r="D236">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E236" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="D237">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E237" t="s">
         <v>28</v>
@@ -8166,7 +8166,7 @@
         <v>27</v>
       </c>
       <c r="D238">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E238" t="s">
         <v>28</v>
@@ -8183,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="D239">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E239" t="s">
         <v>28</v>
@@ -8200,7 +8200,7 @@
         <v>27</v>
       </c>
       <c r="D240">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E240" t="s">
         <v>28</v>
@@ -8217,7 +8217,7 @@
         <v>27</v>
       </c>
       <c r="D241">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E241" t="s">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>27</v>
       </c>
       <c r="D242">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E242" t="s">
         <v>28</v>
@@ -8251,7 +8251,7 @@
         <v>27</v>
       </c>
       <c r="D243">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E243" t="s">
         <v>28</v>
@@ -8268,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="D244">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E244" t="s">
         <v>28</v>
@@ -8285,7 +8285,7 @@
         <v>27</v>
       </c>
       <c r="D245">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E245" t="s">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="D247">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E247" t="s">
         <v>28</v>
@@ -8336,7 +8336,7 @@
         <v>27</v>
       </c>
       <c r="D248">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E248" t="s">
         <v>28</v>
@@ -8353,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="D249">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E249" t="s">
         <v>28</v>
@@ -8370,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="D250">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E250" t="s">
         <v>28</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="D251">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E251" t="s">
         <v>28</v>
@@ -8404,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="D252">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E252" t="s">
         <v>28</v>
@@ -8421,7 +8421,7 @@
         <v>27</v>
       </c>
       <c r="D253">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E253" t="s">
         <v>28</v>
@@ -8438,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D254">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E254" t="s">
         <v>28</v>
@@ -8455,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="D255">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E255" t="s">
         <v>28</v>
@@ -8472,7 +8472,7 @@
         <v>27</v>
       </c>
       <c r="D256">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E256" t="s">
         <v>28</v>
@@ -8489,7 +8489,7 @@
         <v>27</v>
       </c>
       <c r="D257">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E257" t="s">
         <v>28</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="D258">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E258" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="D260">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E260" t="s">
         <v>28</v>
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="D261">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E261" t="s">
         <v>28</v>
@@ -8574,7 +8574,7 @@
         <v>27</v>
       </c>
       <c r="D262">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E262" t="s">
         <v>28</v>
@@ -8591,7 +8591,7 @@
         <v>27</v>
       </c>
       <c r="D263">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E263" t="s">
         <v>28</v>
@@ -8625,7 +8625,7 @@
         <v>27</v>
       </c>
       <c r="D265">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E265" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="D267">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E267" t="s">
         <v>28</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="D268">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E268" t="s">
         <v>28</v>
@@ -8693,7 +8693,7 @@
         <v>27</v>
       </c>
       <c r="D269">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E269" t="s">
         <v>28</v>
@@ -8710,7 +8710,7 @@
         <v>27</v>
       </c>
       <c r="D270">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E270" t="s">
         <v>28</v>
@@ -8727,7 +8727,7 @@
         <v>27</v>
       </c>
       <c r="D271">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E271" t="s">
         <v>28</v>
@@ -8761,7 +8761,7 @@
         <v>27</v>
       </c>
       <c r="D273">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E273" t="s">
         <v>28</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="D274">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E274" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>27</v>
       </c>
       <c r="D275">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E275" t="s">
         <v>28</v>
@@ -8812,7 +8812,7 @@
         <v>27</v>
       </c>
       <c r="D276">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E276" t="s">
         <v>28</v>
@@ -8829,7 +8829,7 @@
         <v>27</v>
       </c>
       <c r="D277">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E277" t="s">
         <v>28</v>
@@ -8846,7 +8846,7 @@
         <v>27</v>
       </c>
       <c r="D278">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E278" t="s">
         <v>28</v>
@@ -8863,7 +8863,7 @@
         <v>27</v>
       </c>
       <c r="D279">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E279" t="s">
         <v>28</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E280" t="s">
         <v>28</v>
@@ -8897,7 +8897,7 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E281" t="s">
         <v>28</v>
@@ -8914,7 +8914,7 @@
         <v>27</v>
       </c>
       <c r="D282">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E282" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="D283">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E283" t="s">
         <v>28</v>
@@ -8948,7 +8948,7 @@
         <v>27</v>
       </c>
       <c r="D284">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E284" t="s">
         <v>28</v>
@@ -8965,7 +8965,7 @@
         <v>27</v>
       </c>
       <c r="D285">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E285" t="s">
         <v>28</v>
@@ -8982,7 +8982,7 @@
         <v>27</v>
       </c>
       <c r="D286">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E286" t="s">
         <v>28</v>
@@ -8999,7 +8999,7 @@
         <v>27</v>
       </c>
       <c r="D287">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E287" t="s">
         <v>28</v>
@@ -9016,7 +9016,7 @@
         <v>27</v>
       </c>
       <c r="D288">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E288" t="s">
         <v>28</v>
@@ -9033,7 +9033,7 @@
         <v>27</v>
       </c>
       <c r="D289">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E289" t="s">
         <v>28</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="D290">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E290" t="s">
         <v>28</v>
@@ -9084,7 +9084,7 @@
         <v>27</v>
       </c>
       <c r="D292">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E292" t="s">
         <v>28</v>
@@ -9101,7 +9101,7 @@
         <v>27</v>
       </c>
       <c r="D293">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E293" t="s">
         <v>28</v>
@@ -9118,7 +9118,7 @@
         <v>27</v>
       </c>
       <c r="D294">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E294" t="s">
         <v>28</v>
@@ -9135,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="D295">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E295" t="s">
         <v>28</v>
@@ -9152,7 +9152,7 @@
         <v>27</v>
       </c>
       <c r="D296">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E296" t="s">
         <v>28</v>
@@ -9169,7 +9169,7 @@
         <v>27</v>
       </c>
       <c r="D297">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E297" t="s">
         <v>28</v>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="D298">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E298" t="s">
         <v>28</v>
@@ -9203,7 +9203,7 @@
         <v>27</v>
       </c>
       <c r="D299">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E299" t="s">
         <v>28</v>
@@ -9237,7 +9237,7 @@
         <v>27</v>
       </c>
       <c r="D301">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E301" t="s">
         <v>28</v>
@@ -9254,7 +9254,7 @@
         <v>27</v>
       </c>
       <c r="D302">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E302" t="s">
         <v>28</v>
@@ -9271,7 +9271,7 @@
         <v>27</v>
       </c>
       <c r="D303">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E303" t="s">
         <v>28</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="D304">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E304" t="s">
         <v>28</v>
@@ -9305,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="D305">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E305" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="D306">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E306" t="s">
         <v>28</v>
@@ -9339,7 +9339,7 @@
         <v>27</v>
       </c>
       <c r="D307">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E307" t="s">
         <v>28</v>
@@ -9356,7 +9356,7 @@
         <v>27</v>
       </c>
       <c r="D308">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E308" t="s">
         <v>28</v>
@@ -9373,7 +9373,7 @@
         <v>27</v>
       </c>
       <c r="D309">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E309" t="s">
         <v>28</v>
@@ -9390,7 +9390,7 @@
         <v>27</v>
       </c>
       <c r="D310">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E310" t="s">
         <v>28</v>
@@ -9407,7 +9407,7 @@
         <v>27</v>
       </c>
       <c r="D311">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E311" t="s">
         <v>28</v>
@@ -9424,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="D312">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E312" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="D313">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E313" t="s">
         <v>28</v>
@@ -9458,7 +9458,7 @@
         <v>27</v>
       </c>
       <c r="D314">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E314" t="s">
         <v>28</v>
@@ -9475,7 +9475,7 @@
         <v>27</v>
       </c>
       <c r="D315">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E315" t="s">
         <v>28</v>
@@ -9492,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="D316">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E316" t="s">
         <v>28</v>
@@ -9509,7 +9509,7 @@
         <v>27</v>
       </c>
       <c r="D317">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E317" t="s">
         <v>28</v>
@@ -9526,7 +9526,7 @@
         <v>27</v>
       </c>
       <c r="D318">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E318" t="s">
         <v>28</v>
@@ -9543,7 +9543,7 @@
         <v>27</v>
       </c>
       <c r="D319">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E319" t="s">
         <v>28</v>
@@ -9560,7 +9560,7 @@
         <v>27</v>
       </c>
       <c r="D320">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E320" t="s">
         <v>28</v>
@@ -9577,7 +9577,7 @@
         <v>27</v>
       </c>
       <c r="D321">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E321" t="s">
         <v>28</v>
@@ -9594,7 +9594,7 @@
         <v>27</v>
       </c>
       <c r="D322">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E322" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
         <v>27</v>
       </c>
       <c r="D323">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E323" t="s">
         <v>28</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="D324">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E324" t="s">
         <v>28</v>
@@ -9645,7 +9645,7 @@
         <v>27</v>
       </c>
       <c r="D325">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E325" t="s">
         <v>28</v>
@@ -9662,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="D326">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E326" t="s">
         <v>28</v>
@@ -9679,7 +9679,7 @@
         <v>27</v>
       </c>
       <c r="D327">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E327" t="s">
         <v>28</v>
@@ -9696,7 +9696,7 @@
         <v>27</v>
       </c>
       <c r="D328">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E328" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="D329">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E329" t="s">
         <v>28</v>
@@ -9730,7 +9730,7 @@
         <v>27</v>
       </c>
       <c r="D330">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E330" t="s">
         <v>28</v>
@@ -9747,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="D331">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E331" t="s">
         <v>28</v>
@@ -9764,7 +9764,7 @@
         <v>27</v>
       </c>
       <c r="D332">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E332" t="s">
         <v>28</v>
@@ -9781,7 +9781,7 @@
         <v>27</v>
       </c>
       <c r="D333">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E333" t="s">
         <v>28</v>
@@ -9798,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="D334">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E334" t="s">
         <v>28</v>
@@ -9815,7 +9815,7 @@
         <v>27</v>
       </c>
       <c r="D335">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E335" t="s">
         <v>28</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="D336">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E336" t="s">
         <v>28</v>
@@ -9849,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="D337">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E337" t="s">
         <v>28</v>
@@ -9866,7 +9866,7 @@
         <v>27</v>
       </c>
       <c r="D338">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E338" t="s">
         <v>28</v>
@@ -9883,7 +9883,7 @@
         <v>27</v>
       </c>
       <c r="D339">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E339" t="s">
         <v>28</v>
@@ -9900,7 +9900,7 @@
         <v>27</v>
       </c>
       <c r="D340">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E340" t="s">
         <v>28</v>
@@ -9917,7 +9917,7 @@
         <v>27</v>
       </c>
       <c r="D341">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E341" t="s">
         <v>28</v>
@@ -9934,7 +9934,7 @@
         <v>27</v>
       </c>
       <c r="D342">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E342" t="s">
         <v>28</v>
@@ -9951,7 +9951,7 @@
         <v>27</v>
       </c>
       <c r="D343">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E343" t="s">
         <v>28</v>
@@ -9968,7 +9968,7 @@
         <v>27</v>
       </c>
       <c r="D344">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E344" t="s">
         <v>28</v>
@@ -9985,7 +9985,7 @@
         <v>27</v>
       </c>
       <c r="D345">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E345" t="s">
         <v>28</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D346">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E346" t="s">
         <v>28</v>
@@ -10019,7 +10019,7 @@
         <v>27</v>
       </c>
       <c r="D347">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E347" t="s">
         <v>28</v>
@@ -10036,7 +10036,7 @@
         <v>27</v>
       </c>
       <c r="D348">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E348" t="s">
         <v>28</v>
@@ -10053,7 +10053,7 @@
         <v>27</v>
       </c>
       <c r="D349">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E349" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="D350">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E350" t="s">
         <v>28</v>
@@ -10087,7 +10087,7 @@
         <v>27</v>
       </c>
       <c r="D351">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E351" t="s">
         <v>28</v>
@@ -10104,7 +10104,7 @@
         <v>27</v>
       </c>
       <c r="D352">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E352" t="s">
         <v>28</v>
@@ -10121,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D353">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E353" t="s">
         <v>28</v>
@@ -10138,7 +10138,7 @@
         <v>27</v>
       </c>
       <c r="D354">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E354" t="s">
         <v>28</v>
@@ -10155,7 +10155,7 @@
         <v>27</v>
       </c>
       <c r="D355">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E355" t="s">
         <v>28</v>
@@ -10172,7 +10172,7 @@
         <v>27</v>
       </c>
       <c r="D356">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E356" t="s">
         <v>28</v>
@@ -10189,7 +10189,7 @@
         <v>27</v>
       </c>
       <c r="D357">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E357" t="s">
         <v>28</v>
@@ -10206,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="D358">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E358" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="D359">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E359" t="s">
         <v>28</v>
@@ -10240,7 +10240,7 @@
         <v>27</v>
       </c>
       <c r="D360">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E360" t="s">
         <v>28</v>
@@ -10257,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="D361">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E361" t="s">
         <v>28</v>
@@ -10274,7 +10274,7 @@
         <v>27</v>
       </c>
       <c r="D362">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E362" t="s">
         <v>28</v>
@@ -10291,7 +10291,7 @@
         <v>27</v>
       </c>
       <c r="D363">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E363" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="D364">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E364" t="s">
         <v>28</v>
@@ -10325,7 +10325,7 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E365" t="s">
         <v>28</v>
@@ -10342,7 +10342,7 @@
         <v>27</v>
       </c>
       <c r="D366">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E366" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
         <v>27</v>
       </c>
       <c r="D367">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E367" t="s">
         <v>28</v>
@@ -10376,7 +10376,7 @@
         <v>27</v>
       </c>
       <c r="D368">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E368" t="s">
         <v>28</v>
@@ -10393,7 +10393,7 @@
         <v>27</v>
       </c>
       <c r="D369">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E369" t="s">
         <v>28</v>
@@ -10410,7 +10410,7 @@
         <v>27</v>
       </c>
       <c r="D370">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E370" t="s">
         <v>28</v>
@@ -10427,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="D371">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E371" t="s">
         <v>28</v>
@@ -10444,7 +10444,7 @@
         <v>27</v>
       </c>
       <c r="D372">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E372" t="s">
         <v>28</v>
@@ -10478,7 +10478,7 @@
         <v>27</v>
       </c>
       <c r="D374">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E374" t="s">
         <v>28</v>
@@ -10495,7 +10495,7 @@
         <v>27</v>
       </c>
       <c r="D375">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E375" t="s">
         <v>28</v>
@@ -10512,7 +10512,7 @@
         <v>27</v>
       </c>
       <c r="D376">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E376" t="s">
         <v>28</v>
@@ -10529,7 +10529,7 @@
         <v>27</v>
       </c>
       <c r="D377">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E377" t="s">
         <v>28</v>
@@ -10546,7 +10546,7 @@
         <v>27</v>
       </c>
       <c r="D378">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E378" t="s">
         <v>28</v>
@@ -10563,7 +10563,7 @@
         <v>27</v>
       </c>
       <c r="D379">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E379" t="s">
         <v>28</v>
@@ -10580,7 +10580,7 @@
         <v>27</v>
       </c>
       <c r="D380">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E380" t="s">
         <v>28</v>
@@ -10597,7 +10597,7 @@
         <v>27</v>
       </c>
       <c r="D381">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E381" t="s">
         <v>28</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="D382">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E382" t="s">
         <v>28</v>
@@ -10631,7 +10631,7 @@
         <v>27</v>
       </c>
       <c r="D383">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E383" t="s">
         <v>28</v>
@@ -10648,7 +10648,7 @@
         <v>27</v>
       </c>
       <c r="D384">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E384" t="s">
         <v>28</v>
@@ -10665,7 +10665,7 @@
         <v>27</v>
       </c>
       <c r="D385">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E385" t="s">
         <v>28</v>
@@ -10682,7 +10682,7 @@
         <v>27</v>
       </c>
       <c r="D386">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E386" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="D387">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E387" t="s">
         <v>28</v>
@@ -10716,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="D388">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E388" t="s">
         <v>28</v>
@@ -10733,7 +10733,7 @@
         <v>27</v>
       </c>
       <c r="D389">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E389" t="s">
         <v>28</v>
@@ -10750,7 +10750,7 @@
         <v>27</v>
       </c>
       <c r="D390">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E390" t="s">
         <v>28</v>
@@ -10767,7 +10767,7 @@
         <v>27</v>
       </c>
       <c r="D391">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E391" t="s">
         <v>28</v>
@@ -10784,7 +10784,7 @@
         <v>27</v>
       </c>
       <c r="D392">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E392" t="s">
         <v>28</v>
@@ -10801,7 +10801,7 @@
         <v>27</v>
       </c>
       <c r="D393">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E393" t="s">
         <v>28</v>
@@ -10818,7 +10818,7 @@
         <v>27</v>
       </c>
       <c r="D394">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E394" t="s">
         <v>28</v>
@@ -10835,7 +10835,7 @@
         <v>27</v>
       </c>
       <c r="D395">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E395" t="s">
         <v>28</v>
@@ -10852,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="D396">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E396" t="s">
         <v>28</v>
@@ -10869,7 +10869,7 @@
         <v>27</v>
       </c>
       <c r="D397">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E397" t="s">
         <v>28</v>
@@ -10886,7 +10886,7 @@
         <v>27</v>
       </c>
       <c r="D398">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E398" t="s">
         <v>28</v>
@@ -10903,7 +10903,7 @@
         <v>27</v>
       </c>
       <c r="D399">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E399" t="s">
         <v>28</v>
@@ -10920,7 +10920,7 @@
         <v>27</v>
       </c>
       <c r="D400">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E400" t="s">
         <v>28</v>
@@ -10937,7 +10937,7 @@
         <v>27</v>
       </c>
       <c r="D401">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E401" t="s">
         <v>28</v>
@@ -10954,7 +10954,7 @@
         <v>27</v>
       </c>
       <c r="D402">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E402" t="s">
         <v>28</v>
@@ -10971,7 +10971,7 @@
         <v>27</v>
       </c>
       <c r="D403">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E403" t="s">
         <v>28</v>
@@ -10988,7 +10988,7 @@
         <v>27</v>
       </c>
       <c r="D404">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E404" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="D405">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E405" t="s">
         <v>28</v>
@@ -11022,7 +11022,7 @@
         <v>27</v>
       </c>
       <c r="D406">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E406" t="s">
         <v>28</v>
@@ -11039,7 +11039,7 @@
         <v>27</v>
       </c>
       <c r="D407">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E407" t="s">
         <v>28</v>
@@ -11056,7 +11056,7 @@
         <v>27</v>
       </c>
       <c r="D408">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E408" t="s">
         <v>28</v>
@@ -11073,7 +11073,7 @@
         <v>27</v>
       </c>
       <c r="D409">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E409" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="D410">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E410" t="s">
         <v>28</v>
@@ -11107,7 +11107,7 @@
         <v>27</v>
       </c>
       <c r="D411">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E411" t="s">
         <v>28</v>
@@ -11124,7 +11124,7 @@
         <v>27</v>
       </c>
       <c r="D412">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E412" t="s">
         <v>28</v>
@@ -11141,7 +11141,7 @@
         <v>27</v>
       </c>
       <c r="D413">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E413" t="s">
         <v>28</v>
@@ -11158,7 +11158,7 @@
         <v>27</v>
       </c>
       <c r="D414">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E414" t="s">
         <v>28</v>
@@ -11175,7 +11175,7 @@
         <v>27</v>
       </c>
       <c r="D415">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E415" t="s">
         <v>28</v>
@@ -11192,7 +11192,7 @@
         <v>27</v>
       </c>
       <c r="D416">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E416" t="s">
         <v>28</v>
@@ -11209,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="D417">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E417" t="s">
         <v>28</v>
@@ -11226,7 +11226,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E418" t="s">
         <v>28</v>
@@ -11243,7 +11243,7 @@
         <v>27</v>
       </c>
       <c r="D419">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E419" t="s">
         <v>28</v>
@@ -11260,7 +11260,7 @@
         <v>27</v>
       </c>
       <c r="D420">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E420" t="s">
         <v>28</v>
@@ -11277,7 +11277,7 @@
         <v>27</v>
       </c>
       <c r="D421">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E421" t="s">
         <v>28</v>
@@ -11294,7 +11294,7 @@
         <v>27</v>
       </c>
       <c r="D422">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E422" t="s">
         <v>28</v>
@@ -11311,7 +11311,7 @@
         <v>27</v>
       </c>
       <c r="D423">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E423" t="s">
         <v>28</v>
@@ -11328,7 +11328,7 @@
         <v>27</v>
       </c>
       <c r="D424">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E424" t="s">
         <v>28</v>
@@ -11345,7 +11345,7 @@
         <v>27</v>
       </c>
       <c r="D425">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E425" t="s">
         <v>28</v>
@@ -11362,7 +11362,7 @@
         <v>27</v>
       </c>
       <c r="D426">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E426" t="s">
         <v>28</v>
@@ -11379,7 +11379,7 @@
         <v>27</v>
       </c>
       <c r="D427">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E427" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="D428">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E428" t="s">
         <v>28</v>
@@ -11430,7 +11430,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E430" t="s">
         <v>28</v>
@@ -11447,7 +11447,7 @@
         <v>27</v>
       </c>
       <c r="D431">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E431" t="s">
         <v>28</v>
@@ -11464,7 +11464,7 @@
         <v>27</v>
       </c>
       <c r="D432">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E432" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="D433">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E433" t="s">
         <v>28</v>
@@ -11498,7 +11498,7 @@
         <v>27</v>
       </c>
       <c r="D434">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E434" t="s">
         <v>28</v>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="D435">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E435" t="s">
         <v>28</v>
@@ -11532,7 +11532,7 @@
         <v>27</v>
       </c>
       <c r="D436">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E436" t="s">
         <v>28</v>
@@ -11549,7 +11549,7 @@
         <v>27</v>
       </c>
       <c r="D437">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E437" t="s">
         <v>28</v>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
       <c r="D438">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E438" t="s">
         <v>28</v>
@@ -11583,7 +11583,7 @@
         <v>27</v>
       </c>
       <c r="D439">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E439" t="s">
         <v>28</v>
@@ -11600,7 +11600,7 @@
         <v>27</v>
       </c>
       <c r="D440">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E440" t="s">
         <v>28</v>
@@ -11617,7 +11617,7 @@
         <v>27</v>
       </c>
       <c r="D441">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E441" t="s">
         <v>28</v>
@@ -11651,7 +11651,7 @@
         <v>27</v>
       </c>
       <c r="D443">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E443" t="s">
         <v>28</v>
@@ -11668,7 +11668,7 @@
         <v>27</v>
       </c>
       <c r="D444">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E444" t="s">
         <v>28</v>
@@ -11685,7 +11685,7 @@
         <v>27</v>
       </c>
       <c r="D445">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E445" t="s">
         <v>28</v>
@@ -11702,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D446">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E446" t="s">
         <v>28</v>
@@ -11719,7 +11719,7 @@
         <v>27</v>
       </c>
       <c r="D447">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E447" t="s">
         <v>28</v>
@@ -11736,7 +11736,7 @@
         <v>27</v>
       </c>
       <c r="D448">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E448" t="s">
         <v>28</v>
@@ -11753,7 +11753,7 @@
         <v>27</v>
       </c>
       <c r="D449">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E449" t="s">
         <v>28</v>
@@ -11770,7 +11770,7 @@
         <v>27</v>
       </c>
       <c r="D450">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E450" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="D451">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E451" t="s">
         <v>28</v>
@@ -11804,7 +11804,7 @@
         <v>27</v>
       </c>
       <c r="D452">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E452" t="s">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>27</v>
       </c>
       <c r="D453">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E453" t="s">
         <v>28</v>
@@ -11838,7 +11838,7 @@
         <v>27</v>
       </c>
       <c r="D454">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E454" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="D456">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E456" t="s">
         <v>28</v>
@@ -11906,7 +11906,7 @@
         <v>27</v>
       </c>
       <c r="D458">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E458" t="s">
         <v>28</v>
@@ -11923,7 +11923,7 @@
         <v>27</v>
       </c>
       <c r="D459">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E459" t="s">
         <v>28</v>
@@ -11940,7 +11940,7 @@
         <v>27</v>
       </c>
       <c r="D460">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E460" t="s">
         <v>28</v>
@@ -11957,7 +11957,7 @@
         <v>27</v>
       </c>
       <c r="D461">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E461" t="s">
         <v>28</v>
@@ -11974,7 +11974,7 @@
         <v>27</v>
       </c>
       <c r="D462">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E462" t="s">
         <v>28</v>
@@ -11991,7 +11991,7 @@
         <v>27</v>
       </c>
       <c r="D463">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E463" t="s">
         <v>28</v>
@@ -12008,7 +12008,7 @@
         <v>27</v>
       </c>
       <c r="D464">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E464" t="s">
         <v>28</v>
@@ -12025,7 +12025,7 @@
         <v>27</v>
       </c>
       <c r="D465">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E465" t="s">
         <v>28</v>
@@ -12042,7 +12042,7 @@
         <v>27</v>
       </c>
       <c r="D466">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E466" t="s">
         <v>28</v>
@@ -12059,7 +12059,7 @@
         <v>27</v>
       </c>
       <c r="D467">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E467" t="s">
         <v>28</v>
@@ -12076,7 +12076,7 @@
         <v>27</v>
       </c>
       <c r="D468">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E468" t="s">
         <v>28</v>
@@ -12093,7 +12093,7 @@
         <v>27</v>
       </c>
       <c r="D469">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E469" t="s">
         <v>28</v>
@@ -12110,7 +12110,7 @@
         <v>27</v>
       </c>
       <c r="D470">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E470" t="s">
         <v>28</v>
@@ -12127,7 +12127,7 @@
         <v>27</v>
       </c>
       <c r="D471">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E471" t="s">
         <v>28</v>
@@ -12144,7 +12144,7 @@
         <v>27</v>
       </c>
       <c r="D472">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E472" t="s">
         <v>28</v>
@@ -12161,7 +12161,7 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E473" t="s">
         <v>28</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="D474">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E474" t="s">
         <v>28</v>
@@ -12195,7 +12195,7 @@
         <v>27</v>
       </c>
       <c r="D475">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E475" t="s">
         <v>28</v>
@@ -12212,7 +12212,7 @@
         <v>27</v>
       </c>
       <c r="D476">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E476" t="s">
         <v>28</v>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
       <c r="D477">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E477" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="D479">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E479" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="D480">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="E480" t="s">
         <v>28</v>
@@ -12314,7 +12314,7 @@
         <v>27</v>
       </c>
       <c r="D482">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E482" t="s">
         <v>28</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="D483">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E483" t="s">
         <v>28</v>
@@ -12348,7 +12348,7 @@
         <v>27</v>
       </c>
       <c r="D484">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E484" t="s">
         <v>28</v>
@@ -12365,7 +12365,7 @@
         <v>27</v>
       </c>
       <c r="D485">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E485" t="s">
         <v>28</v>
@@ -12382,7 +12382,7 @@
         <v>27</v>
       </c>
       <c r="D486">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E486" t="s">
         <v>28</v>
@@ -12399,7 +12399,7 @@
         <v>27</v>
       </c>
       <c r="D487">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E487" t="s">
         <v>28</v>
@@ -12416,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="D488">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E488" t="s">
         <v>28</v>
@@ -12450,7 +12450,7 @@
         <v>27</v>
       </c>
       <c r="D490">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E490" t="s">
         <v>28</v>
@@ -12467,7 +12467,7 @@
         <v>27</v>
       </c>
       <c r="D491">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E491" t="s">
         <v>28</v>
@@ -12484,7 +12484,7 @@
         <v>27</v>
       </c>
       <c r="D492">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E492" t="s">
         <v>28</v>
@@ -12501,7 +12501,7 @@
         <v>27</v>
       </c>
       <c r="D493">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E493" t="s">
         <v>28</v>
@@ -12535,7 +12535,7 @@
         <v>27</v>
       </c>
       <c r="D495">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E495" t="s">
         <v>28</v>
@@ -12552,7 +12552,7 @@
         <v>27</v>
       </c>
       <c r="D496">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E496" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="D497">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E497" t="s">
         <v>28</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D499">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E499" t="s">
         <v>28</v>
@@ -12620,7 +12620,7 @@
         <v>27</v>
       </c>
       <c r="D500">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E500" t="s">
         <v>28</v>
@@ -12637,7 +12637,7 @@
         <v>27</v>
       </c>
       <c r="D501">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E501" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="D502">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E502" t="s">
         <v>28</v>
@@ -12671,7 +12671,7 @@
         <v>27</v>
       </c>
       <c r="D503">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E503" t="s">
         <v>28</v>
@@ -12688,7 +12688,7 @@
         <v>27</v>
       </c>
       <c r="D504">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E504" t="s">
         <v>28</v>
@@ -12705,7 +12705,7 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E505" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="D506">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E506" t="s">
         <v>28</v>
@@ -12739,7 +12739,7 @@
         <v>27</v>
       </c>
       <c r="D507">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E507" t="s">
         <v>28</v>
@@ -12756,7 +12756,7 @@
         <v>27</v>
       </c>
       <c r="D508">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E508" t="s">
         <v>28</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="D509">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E509" t="s">
         <v>28</v>
@@ -12790,7 +12790,7 @@
         <v>27</v>
       </c>
       <c r="D510">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E510" t="s">
         <v>28</v>
@@ -12807,7 +12807,7 @@
         <v>27</v>
       </c>
       <c r="D511">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E511" t="s">
         <v>28</v>
@@ -12824,7 +12824,7 @@
         <v>27</v>
       </c>
       <c r="D512">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E512" t="s">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27</v>
       </c>
       <c r="D513">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E513" t="s">
         <v>28</v>
@@ -12858,7 +12858,7 @@
         <v>27</v>
       </c>
       <c r="D514">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E514" t="s">
         <v>28</v>
@@ -12875,7 +12875,7 @@
         <v>27</v>
       </c>
       <c r="D515">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E515" t="s">
         <v>28</v>
@@ -12892,7 +12892,7 @@
         <v>27</v>
       </c>
       <c r="D516">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E516" t="s">
         <v>28</v>
@@ -12909,7 +12909,7 @@
         <v>27</v>
       </c>
       <c r="D517">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E517" t="s">
         <v>28</v>
@@ -12926,7 +12926,7 @@
         <v>27</v>
       </c>
       <c r="D518">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E518" t="s">
         <v>28</v>
@@ -12943,7 +12943,7 @@
         <v>27</v>
       </c>
       <c r="D519">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E519" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="D520">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E520" t="s">
         <v>28</v>
@@ -12977,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="D521">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E521" t="s">
         <v>28</v>
@@ -12994,7 +12994,7 @@
         <v>27</v>
       </c>
       <c r="D522">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E522" t="s">
         <v>28</v>
@@ -13011,7 +13011,7 @@
         <v>27</v>
       </c>
       <c r="D523">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E523" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="D525">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E525" t="s">
         <v>28</v>
@@ -13062,7 +13062,7 @@
         <v>27</v>
       </c>
       <c r="D526">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E526" t="s">
         <v>28</v>
@@ -13079,7 +13079,7 @@
         <v>27</v>
       </c>
       <c r="D527">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E527" t="s">
         <v>28</v>
@@ -13096,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="D528">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E528" t="s">
         <v>28</v>
@@ -13113,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="D529">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
@@ -13130,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -13147,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="D531">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
@@ -13164,7 +13164,7 @@
         <v>27</v>
       </c>
       <c r="D532">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E532" t="s">
         <v>28</v>
@@ -13181,7 +13181,7 @@
         <v>27</v>
       </c>
       <c r="D533">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E533" t="s">
         <v>28</v>
@@ -13198,7 +13198,7 @@
         <v>27</v>
       </c>
       <c r="D534">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E534" t="s">
         <v>28</v>
@@ -13215,7 +13215,7 @@
         <v>27</v>
       </c>
       <c r="D535">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E535" t="s">
         <v>28</v>
@@ -13232,7 +13232,7 @@
         <v>27</v>
       </c>
       <c r="D536">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E536" t="s">
         <v>28</v>
@@ -13249,7 +13249,7 @@
         <v>27</v>
       </c>
       <c r="D537">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E537" t="s">
         <v>28</v>
@@ -13266,7 +13266,7 @@
         <v>27</v>
       </c>
       <c r="D538">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E538" t="s">
         <v>28</v>
@@ -13283,7 +13283,7 @@
         <v>27</v>
       </c>
       <c r="D539">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E539" t="s">
         <v>28</v>
@@ -13300,7 +13300,7 @@
         <v>27</v>
       </c>
       <c r="D540">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E540" t="s">
         <v>28</v>
@@ -13317,7 +13317,7 @@
         <v>27</v>
       </c>
       <c r="D541">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E541" t="s">
         <v>28</v>
@@ -13334,7 +13334,7 @@
         <v>27</v>
       </c>
       <c r="D542">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E542" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="D543">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E543" t="s">
         <v>28</v>
@@ -13385,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="D545">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
@@ -13402,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="D546">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
@@ -13419,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="D547">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E547" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="D548">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E548" t="s">
         <v>28</v>
@@ -13453,7 +13453,7 @@
         <v>27</v>
       </c>
       <c r="D549">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E549" t="s">
         <v>28</v>
@@ -13470,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="D550">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E550" t="s">
         <v>28</v>
@@ -13487,7 +13487,7 @@
         <v>27</v>
       </c>
       <c r="D551">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E551" t="s">
         <v>28</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="D552">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -13521,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="D553">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E553" t="s">
         <v>28</v>
@@ -13538,7 +13538,7 @@
         <v>27</v>
       </c>
       <c r="D554">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E554" t="s">
         <v>28</v>
@@ -13555,7 +13555,7 @@
         <v>27</v>
       </c>
       <c r="D555">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E555" t="s">
         <v>28</v>
@@ -13572,7 +13572,7 @@
         <v>27</v>
       </c>
       <c r="D556">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E556" t="s">
         <v>28</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="D558">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E558" t="s">
         <v>28</v>
@@ -13623,7 +13623,7 @@
         <v>27</v>
       </c>
       <c r="D559">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -13640,7 +13640,7 @@
         <v>27</v>
       </c>
       <c r="D560">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
@@ -13657,7 +13657,7 @@
         <v>27</v>
       </c>
       <c r="D561">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E561" t="s">
         <v>28</v>
@@ -13674,7 +13674,7 @@
         <v>27</v>
       </c>
       <c r="D562">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E562" t="s">
         <v>28</v>
@@ -13691,7 +13691,7 @@
         <v>27</v>
       </c>
       <c r="D563">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E563" t="s">
         <v>28</v>
@@ -13725,7 +13725,7 @@
         <v>27</v>
       </c>
       <c r="D565">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E565" t="s">
         <v>28</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="D566">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E566" t="s">
         <v>28</v>
@@ -13759,7 +13759,7 @@
         <v>27</v>
       </c>
       <c r="D567">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E567" t="s">
         <v>28</v>
@@ -13776,7 +13776,7 @@
         <v>27</v>
       </c>
       <c r="D568">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E568" t="s">
         <v>28</v>
@@ -13793,7 +13793,7 @@
         <v>27</v>
       </c>
       <c r="D569">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
@@ -13844,7 +13844,7 @@
         <v>27</v>
       </c>
       <c r="D572">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E572" t="s">
         <v>28</v>
@@ -13861,7 +13861,7 @@
         <v>27</v>
       </c>
       <c r="D573">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E573" t="s">
         <v>28</v>
@@ -13878,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="D574">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E574" t="s">
         <v>28</v>
@@ -13912,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="D576">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E576" t="s">
         <v>28</v>
@@ -13929,7 +13929,7 @@
         <v>27</v>
       </c>
       <c r="D577">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E577" t="s">
         <v>28</v>
@@ -13946,7 +13946,7 @@
         <v>27</v>
       </c>
       <c r="D578">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E578" t="s">
         <v>28</v>
@@ -13963,7 +13963,7 @@
         <v>27</v>
       </c>
       <c r="D579">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E579" t="s">
         <v>28</v>
@@ -13980,7 +13980,7 @@
         <v>27</v>
       </c>
       <c r="D580">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E580" t="s">
         <v>28</v>
@@ -13997,7 +13997,7 @@
         <v>27</v>
       </c>
       <c r="D581">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E581" t="s">
         <v>28</v>
@@ -14014,7 +14014,7 @@
         <v>27</v>
       </c>
       <c r="D582">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E582" t="s">
         <v>28</v>
@@ -14031,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="D583">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E583" t="s">
         <v>28</v>
@@ -14048,7 +14048,7 @@
         <v>27</v>
       </c>
       <c r="D584">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E584" t="s">
         <v>28</v>
@@ -14065,7 +14065,7 @@
         <v>27</v>
       </c>
       <c r="D585">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E585" t="s">
         <v>28</v>
@@ -14082,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="D586">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E586" t="s">
         <v>28</v>
@@ -14099,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="D587">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E587" t="s">
         <v>28</v>
@@ -14116,7 +14116,7 @@
         <v>27</v>
       </c>
       <c r="D588">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E588" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="D589">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
@@ -14150,7 +14150,7 @@
         <v>27</v>
       </c>
       <c r="D590">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
@@ -14184,7 +14184,7 @@
         <v>27</v>
       </c>
       <c r="D592">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E592" t="s">
         <v>28</v>
@@ -14201,7 +14201,7 @@
         <v>27</v>
       </c>
       <c r="D593">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E593" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="D594">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E594" t="s">
         <v>28</v>
@@ -14235,7 +14235,7 @@
         <v>27</v>
       </c>
       <c r="D595">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E595" t="s">
         <v>28</v>
@@ -14252,7 +14252,7 @@
         <v>27</v>
       </c>
       <c r="D596">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
@@ -14269,7 +14269,7 @@
         <v>27</v>
       </c>
       <c r="D597">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
@@ -14286,7 +14286,7 @@
         <v>27</v>
       </c>
       <c r="D598">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
@@ -14303,7 +14303,7 @@
         <v>27</v>
       </c>
       <c r="D599">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="D600">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
@@ -14337,7 +14337,7 @@
         <v>27</v>
       </c>
       <c r="D601">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
@@ -14354,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="D602">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
@@ -14371,7 +14371,7 @@
         <v>27</v>
       </c>
       <c r="D603">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
@@ -14388,7 +14388,7 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
@@ -14405,7 +14405,7 @@
         <v>27</v>
       </c>
       <c r="D605">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E605" t="s">
         <v>28</v>
@@ -14422,7 +14422,7 @@
         <v>27</v>
       </c>
       <c r="D606">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E606" t="s">
         <v>28</v>
@@ -14439,7 +14439,7 @@
         <v>27</v>
       </c>
       <c r="D607">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E607" t="s">
         <v>28</v>
@@ -14456,7 +14456,7 @@
         <v>27</v>
       </c>
       <c r="D608">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
@@ -14473,7 +14473,7 @@
         <v>27</v>
       </c>
       <c r="D609">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E609" t="s">
         <v>28</v>
@@ -14490,7 +14490,7 @@
         <v>27</v>
       </c>
       <c r="D610">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E610" t="s">
         <v>28</v>
@@ -14507,7 +14507,7 @@
         <v>27</v>
       </c>
       <c r="D611">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E611" t="s">
         <v>28</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="D612">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E612" t="s">
         <v>28</v>
@@ -14541,7 +14541,7 @@
         <v>27</v>
       </c>
       <c r="D613">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E613" t="s">
         <v>28</v>
@@ -14558,7 +14558,7 @@
         <v>27</v>
       </c>
       <c r="D614">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E614" t="s">
         <v>28</v>
@@ -14575,7 +14575,7 @@
         <v>27</v>
       </c>
       <c r="D615">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E615" t="s">
         <v>28</v>
@@ -14592,7 +14592,7 @@
         <v>27</v>
       </c>
       <c r="D616">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E616" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="D617">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E617" t="s">
         <v>28</v>
@@ -14626,7 +14626,7 @@
         <v>27</v>
       </c>
       <c r="D618">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E618" t="s">
         <v>28</v>
@@ -14643,7 +14643,7 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E619" t="s">
         <v>28</v>
@@ -14660,7 +14660,7 @@
         <v>27</v>
       </c>
       <c r="D620">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E620" t="s">
         <v>28</v>
@@ -14677,7 +14677,7 @@
         <v>27</v>
       </c>
       <c r="D621">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E621" t="s">
         <v>28</v>
@@ -14711,7 +14711,7 @@
         <v>27</v>
       </c>
       <c r="D623">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E623" t="s">
         <v>28</v>
@@ -14728,7 +14728,7 @@
         <v>27</v>
       </c>
       <c r="D624">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E624" t="s">
         <v>28</v>
@@ -14745,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="D625">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E625" t="s">
         <v>28</v>
@@ -14762,7 +14762,7 @@
         <v>27</v>
       </c>
       <c r="D626">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E626" t="s">
         <v>28</v>
@@ -14779,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="D627">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E627" t="s">
         <v>28</v>
@@ -14796,7 +14796,7 @@
         <v>27</v>
       </c>
       <c r="D628">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E628" t="s">
         <v>28</v>
@@ -14813,7 +14813,7 @@
         <v>27</v>
       </c>
       <c r="D629">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E629" t="s">
         <v>28</v>
@@ -14830,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="D630">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E630" t="s">
         <v>28</v>
@@ -14847,7 +14847,7 @@
         <v>27</v>
       </c>
       <c r="D631">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E631" t="s">
         <v>28</v>
@@ -14864,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D632">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E632" t="s">
         <v>28</v>
@@ -14881,7 +14881,7 @@
         <v>27</v>
       </c>
       <c r="D633">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E633" t="s">
         <v>28</v>
@@ -14898,7 +14898,7 @@
         <v>27</v>
       </c>
       <c r="D634">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E634" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="D635">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E635" t="s">
         <v>28</v>
@@ -14932,7 +14932,7 @@
         <v>27</v>
       </c>
       <c r="D636">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E636" t="s">
         <v>28</v>
@@ -14949,7 +14949,7 @@
         <v>27</v>
       </c>
       <c r="D637">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E637" t="s">
         <v>28</v>
@@ -14966,7 +14966,7 @@
         <v>27</v>
       </c>
       <c r="D638">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E638" t="s">
         <v>28</v>
@@ -14983,7 +14983,7 @@
         <v>27</v>
       </c>
       <c r="D639">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E639" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E640" t="s">
         <v>28</v>
@@ -15017,7 +15017,7 @@
         <v>27</v>
       </c>
       <c r="D641">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E641" t="s">
         <v>28</v>
@@ -15051,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="D643">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E643" t="s">
         <v>28</v>
@@ -15068,7 +15068,7 @@
         <v>27</v>
       </c>
       <c r="D644">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E644" t="s">
         <v>28</v>
@@ -15085,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="D645">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E645" t="s">
         <v>28</v>
@@ -15102,7 +15102,7 @@
         <v>27</v>
       </c>
       <c r="D646">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E646" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>27</v>
       </c>
       <c r="D647">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E647" t="s">
         <v>28</v>
@@ -15153,7 +15153,7 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E649" t="s">
         <v>28</v>
@@ -15170,7 +15170,7 @@
         <v>27</v>
       </c>
       <c r="D650">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E650" t="s">
         <v>28</v>
@@ -15187,7 +15187,7 @@
         <v>27</v>
       </c>
       <c r="D651">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E651" t="s">
         <v>28</v>
@@ -15204,7 +15204,7 @@
         <v>27</v>
       </c>
       <c r="D652">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E652" t="s">
         <v>28</v>
@@ -15221,7 +15221,7 @@
         <v>27</v>
       </c>
       <c r="D653">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E653" t="s">
         <v>28</v>
@@ -15238,7 +15238,7 @@
         <v>27</v>
       </c>
       <c r="D654">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E654" t="s">
         <v>28</v>
@@ -15255,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="D655">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E655" t="s">
         <v>28</v>
@@ -15272,7 +15272,7 @@
         <v>27</v>
       </c>
       <c r="D656">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
@@ -15289,7 +15289,7 @@
         <v>27</v>
       </c>
       <c r="D657">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E657" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
@@ -15323,7 +15323,7 @@
         <v>27</v>
       </c>
       <c r="D659">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E659" t="s">
         <v>28</v>
@@ -15340,7 +15340,7 @@
         <v>27</v>
       </c>
       <c r="D660">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E660" t="s">
         <v>28</v>
@@ -15357,7 +15357,7 @@
         <v>27</v>
       </c>
       <c r="D661">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E661" t="s">
         <v>28</v>
@@ -15374,7 +15374,7 @@
         <v>27</v>
       </c>
       <c r="D662">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E662" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="D663">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E663" t="s">
         <v>28</v>
@@ -15408,7 +15408,7 @@
         <v>27</v>
       </c>
       <c r="D664">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E664" t="s">
         <v>28</v>
@@ -15425,7 +15425,7 @@
         <v>27</v>
       </c>
       <c r="D665">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E665" t="s">
         <v>28</v>
@@ -15442,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="D666">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E666" t="s">
         <v>28</v>
@@ -15459,7 +15459,7 @@
         <v>27</v>
       </c>
       <c r="D667">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E667" t="s">
         <v>28</v>
@@ -15476,7 +15476,7 @@
         <v>27</v>
       </c>
       <c r="D668">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E668" t="s">
         <v>28</v>
@@ -15493,7 +15493,7 @@
         <v>27</v>
       </c>
       <c r="D669">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E669" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>27</v>
       </c>
       <c r="D670">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E670" t="s">
         <v>28</v>
@@ -15527,7 +15527,7 @@
         <v>27</v>
       </c>
       <c r="D671">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E671" t="s">
         <v>28</v>
@@ -15544,7 +15544,7 @@
         <v>27</v>
       </c>
       <c r="D672">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E672" t="s">
         <v>28</v>
@@ -15561,7 +15561,7 @@
         <v>27</v>
       </c>
       <c r="D673">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E673" t="s">
         <v>28</v>
@@ -15578,7 +15578,7 @@
         <v>27</v>
       </c>
       <c r="D674">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E674" t="s">
         <v>28</v>
@@ -15595,7 +15595,7 @@
         <v>27</v>
       </c>
       <c r="D675">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E675" t="s">
         <v>28</v>
@@ -15629,7 +15629,7 @@
         <v>27</v>
       </c>
       <c r="D677">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E677" t="s">
         <v>28</v>
@@ -15646,7 +15646,7 @@
         <v>27</v>
       </c>
       <c r="D678">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E678" t="s">
         <v>28</v>
@@ -15680,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="D680">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E680" t="s">
         <v>28</v>
@@ -15697,7 +15697,7 @@
         <v>27</v>
       </c>
       <c r="D681">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E681" t="s">
         <v>28</v>
@@ -15714,7 +15714,7 @@
         <v>27</v>
       </c>
       <c r="D682">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E682" t="s">
         <v>28</v>
@@ -15731,7 +15731,7 @@
         <v>27</v>
       </c>
       <c r="D683">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E683" t="s">
         <v>28</v>
@@ -15748,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="D684">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E684" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="D686">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E686" t="s">
         <v>28</v>
@@ -15799,7 +15799,7 @@
         <v>27</v>
       </c>
       <c r="D687">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E687" t="s">
         <v>28</v>
@@ -15816,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="D688">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E688" t="s">
         <v>28</v>
@@ -15850,7 +15850,7 @@
         <v>27</v>
       </c>
       <c r="D690">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E690" t="s">
         <v>28</v>
@@ -15867,7 +15867,7 @@
         <v>27</v>
       </c>
       <c r="D691">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E691" t="s">
         <v>28</v>
@@ -15884,7 +15884,7 @@
         <v>27</v>
       </c>
       <c r="D692">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E692" t="s">
         <v>28</v>
@@ -15901,7 +15901,7 @@
         <v>27</v>
       </c>
       <c r="D693">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E693" t="s">
         <v>28</v>
@@ -15918,7 +15918,7 @@
         <v>27</v>
       </c>
       <c r="D694">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E694" t="s">
         <v>28</v>
@@ -15935,7 +15935,7 @@
         <v>27</v>
       </c>
       <c r="D695">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E695" t="s">
         <v>28</v>
@@ -15952,7 +15952,7 @@
         <v>27</v>
       </c>
       <c r="D696">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E696" t="s">
         <v>28</v>
@@ -15969,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="D697">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E697" t="s">
         <v>28</v>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
       <c r="D698">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E698" t="s">
         <v>28</v>
@@ -16003,7 +16003,7 @@
         <v>27</v>
       </c>
       <c r="D699">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E699" t="s">
         <v>28</v>
@@ -16020,7 +16020,7 @@
         <v>27</v>
       </c>
       <c r="D700">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E700" t="s">
         <v>28</v>
@@ -16037,7 +16037,7 @@
         <v>27</v>
       </c>
       <c r="D701">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E701" t="s">
         <v>28</v>
@@ -16054,7 +16054,7 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E702" t="s">
         <v>28</v>
@@ -16071,7 +16071,7 @@
         <v>27</v>
       </c>
       <c r="D703">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E703" t="s">
         <v>28</v>
@@ -16088,7 +16088,7 @@
         <v>27</v>
       </c>
       <c r="D704">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E704" t="s">
         <v>28</v>
@@ -16105,7 +16105,7 @@
         <v>27</v>
       </c>
       <c r="D705">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E705" t="s">
         <v>28</v>
@@ -16122,7 +16122,7 @@
         <v>27</v>
       </c>
       <c r="D706">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E706" t="s">
         <v>28</v>
@@ -16139,7 +16139,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E707" t="s">
         <v>28</v>
@@ -16156,7 +16156,7 @@
         <v>27</v>
       </c>
       <c r="D708">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E708" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="D709">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E709" t="s">
         <v>28</v>
@@ -16190,7 +16190,7 @@
         <v>27</v>
       </c>
       <c r="D710">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E710" t="s">
         <v>28</v>
@@ -16207,7 +16207,7 @@
         <v>27</v>
       </c>
       <c r="D711">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E711" t="s">
         <v>28</v>
@@ -16224,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="D712">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E712" t="s">
         <v>28</v>
@@ -16241,7 +16241,7 @@
         <v>27</v>
       </c>
       <c r="D713">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E713" t="s">
         <v>28</v>
@@ -16258,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="D714">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E714" t="s">
         <v>28</v>
@@ -16275,7 +16275,7 @@
         <v>27</v>
       </c>
       <c r="D715">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E715" t="s">
         <v>28</v>
@@ -16292,7 +16292,7 @@
         <v>27</v>
       </c>
       <c r="D716">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E716" t="s">
         <v>28</v>
@@ -16309,7 +16309,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E717" t="s">
         <v>28</v>
@@ -16326,7 +16326,7 @@
         <v>27</v>
       </c>
       <c r="D718">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E718" t="s">
         <v>28</v>
@@ -16343,7 +16343,7 @@
         <v>27</v>
       </c>
       <c r="D719">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E719" t="s">
         <v>28</v>
@@ -16360,7 +16360,7 @@
         <v>27</v>
       </c>
       <c r="D720">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E720" t="s">
         <v>28</v>
@@ -16377,7 +16377,7 @@
         <v>27</v>
       </c>
       <c r="D721">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E721" t="s">
         <v>28</v>
@@ -16394,7 +16394,7 @@
         <v>27</v>
       </c>
       <c r="D722">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E722" t="s">
         <v>28</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="D723">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E723" t="s">
         <v>28</v>
@@ -16445,7 +16445,7 @@
         <v>27</v>
       </c>
       <c r="D725">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E725" t="s">
         <v>28</v>
@@ -16462,7 +16462,7 @@
         <v>27</v>
       </c>
       <c r="D726">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E726" t="s">
         <v>28</v>
@@ -16479,7 +16479,7 @@
         <v>27</v>
       </c>
       <c r="D727">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E727" t="s">
         <v>28</v>
@@ -16496,7 +16496,7 @@
         <v>27</v>
       </c>
       <c r="D728">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E728" t="s">
         <v>28</v>
@@ -16513,7 +16513,7 @@
         <v>27</v>
       </c>
       <c r="D729">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E729" t="s">
         <v>28</v>
@@ -16530,7 +16530,7 @@
         <v>27</v>
       </c>
       <c r="D730">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E730" t="s">
         <v>28</v>
@@ -16547,7 +16547,7 @@
         <v>27</v>
       </c>
       <c r="D731">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E731" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="D732">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E732" t="s">
         <v>28</v>
@@ -16581,7 +16581,7 @@
         <v>27</v>
       </c>
       <c r="D733">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E733" t="s">
         <v>28</v>
@@ -16615,7 +16615,7 @@
         <v>27</v>
       </c>
       <c r="D735">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E735" t="s">
         <v>28</v>
@@ -16632,7 +16632,7 @@
         <v>27</v>
       </c>
       <c r="D736">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E736" t="s">
         <v>28</v>
@@ -16649,7 +16649,7 @@
         <v>27</v>
       </c>
       <c r="D737">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E737" t="s">
         <v>28</v>
@@ -16683,7 +16683,7 @@
         <v>27</v>
       </c>
       <c r="D739">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E739" t="s">
         <v>28</v>
@@ -16700,7 +16700,7 @@
         <v>27</v>
       </c>
       <c r="D740">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E740" t="s">
         <v>28</v>
@@ -16717,7 +16717,7 @@
         <v>27</v>
       </c>
       <c r="D741">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E741" t="s">
         <v>28</v>
@@ -16734,7 +16734,7 @@
         <v>27</v>
       </c>
       <c r="D742">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E742" t="s">
         <v>28</v>
@@ -16751,7 +16751,7 @@
         <v>27</v>
       </c>
       <c r="D743">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E743" t="s">
         <v>28</v>
@@ -16768,7 +16768,7 @@
         <v>27</v>
       </c>
       <c r="D744">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E744" t="s">
         <v>28</v>
@@ -16785,7 +16785,7 @@
         <v>27</v>
       </c>
       <c r="D745">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E745" t="s">
         <v>28</v>
@@ -16802,7 +16802,7 @@
         <v>27</v>
       </c>
       <c r="D746">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E746" t="s">
         <v>28</v>
@@ -16819,7 +16819,7 @@
         <v>27</v>
       </c>
       <c r="D747">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E747" t="s">
         <v>28</v>
@@ -16836,7 +16836,7 @@
         <v>27</v>
       </c>
       <c r="D748">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E748" t="s">
         <v>28</v>
@@ -16853,7 +16853,7 @@
         <v>27</v>
       </c>
       <c r="D749">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E749" t="s">
         <v>28</v>
@@ -16870,7 +16870,7 @@
         <v>27</v>
       </c>
       <c r="D750">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E750" t="s">
         <v>28</v>
@@ -16887,7 +16887,7 @@
         <v>27</v>
       </c>
       <c r="D751">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E751" t="s">
         <v>28</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="D752">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E752" t="s">
         <v>28</v>
@@ -16921,7 +16921,7 @@
         <v>27</v>
       </c>
       <c r="D753">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E753" t="s">
         <v>28</v>
@@ -16938,7 +16938,7 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E754" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="D755">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E755" t="s">
         <v>28</v>
@@ -16972,7 +16972,7 @@
         <v>27</v>
       </c>
       <c r="D756">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E756" t="s">
         <v>28</v>
@@ -16989,7 +16989,7 @@
         <v>27</v>
       </c>
       <c r="D757">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E757" t="s">
         <v>28</v>
@@ -17006,7 +17006,7 @@
         <v>27</v>
       </c>
       <c r="D758">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E758" t="s">
         <v>28</v>
@@ -17023,7 +17023,7 @@
         <v>27</v>
       </c>
       <c r="D759">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E759" t="s">
         <v>28</v>
@@ -17040,7 +17040,7 @@
         <v>27</v>
       </c>
       <c r="D760">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E760" t="s">
         <v>28</v>
@@ -17057,7 +17057,7 @@
         <v>27</v>
       </c>
       <c r="D761">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E761" t="s">
         <v>28</v>
@@ -17074,7 +17074,7 @@
         <v>27</v>
       </c>
       <c r="D762">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E762" t="s">
         <v>28</v>
@@ -17091,7 +17091,7 @@
         <v>27</v>
       </c>
       <c r="D763">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E763" t="s">
         <v>28</v>
@@ -17108,7 +17108,7 @@
         <v>27</v>
       </c>
       <c r="D764">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E764" t="s">
         <v>28</v>
@@ -17125,7 +17125,7 @@
         <v>27</v>
       </c>
       <c r="D765">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E765" t="s">
         <v>28</v>
@@ -17142,7 +17142,7 @@
         <v>27</v>
       </c>
       <c r="D766">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E766" t="s">
         <v>28</v>
@@ -17159,7 +17159,7 @@
         <v>27</v>
       </c>
       <c r="D767">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E767" t="s">
         <v>28</v>
@@ -17176,7 +17176,7 @@
         <v>27</v>
       </c>
       <c r="D768">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E768" t="s">
         <v>28</v>
@@ -17193,7 +17193,7 @@
         <v>27</v>
       </c>
       <c r="D769">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E769" t="s">
         <v>28</v>
@@ -17210,7 +17210,7 @@
         <v>27</v>
       </c>
       <c r="D770">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E770" t="s">
         <v>28</v>
@@ -17227,7 +17227,7 @@
         <v>27</v>
       </c>
       <c r="D771">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E771" t="s">
         <v>28</v>
@@ -17244,7 +17244,7 @@
         <v>27</v>
       </c>
       <c r="D772">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E772" t="s">
         <v>28</v>
@@ -17261,7 +17261,7 @@
         <v>27</v>
       </c>
       <c r="D773">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E773" t="s">
         <v>28</v>
@@ -17278,7 +17278,7 @@
         <v>27</v>
       </c>
       <c r="D774">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E774" t="s">
         <v>28</v>
@@ -17295,7 +17295,7 @@
         <v>27</v>
       </c>
       <c r="D775">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E775" t="s">
         <v>28</v>
@@ -17312,7 +17312,7 @@
         <v>27</v>
       </c>
       <c r="D776">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E776" t="s">
         <v>28</v>
@@ -17329,7 +17329,7 @@
         <v>27</v>
       </c>
       <c r="D777">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E777" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="D778">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E778" t="s">
         <v>28</v>
@@ -17363,7 +17363,7 @@
         <v>27</v>
       </c>
       <c r="D779">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E779" t="s">
         <v>28</v>
@@ -17380,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="D780">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E780" t="s">
         <v>28</v>
@@ -17397,7 +17397,7 @@
         <v>27</v>
       </c>
       <c r="D781">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E781" t="s">
         <v>28</v>
@@ -17414,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="D782">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E782" t="s">
         <v>28</v>
@@ -17431,7 +17431,7 @@
         <v>27</v>
       </c>
       <c r="D783">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E783" t="s">
         <v>28</v>
@@ -17448,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D784">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E784" t="s">
         <v>28</v>
@@ -17465,7 +17465,7 @@
         <v>27</v>
       </c>
       <c r="D785">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E785" t="s">
         <v>28</v>
@@ -17482,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="D786">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E786" t="s">
         <v>28</v>
@@ -17499,7 +17499,7 @@
         <v>27</v>
       </c>
       <c r="D787">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E787" t="s">
         <v>28</v>
@@ -17516,7 +17516,7 @@
         <v>27</v>
       </c>
       <c r="D788">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E788" t="s">
         <v>28</v>
@@ -17533,7 +17533,7 @@
         <v>27</v>
       </c>
       <c r="D789">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E789" t="s">
         <v>28</v>
@@ -17550,7 +17550,7 @@
         <v>27</v>
       </c>
       <c r="D790">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E790" t="s">
         <v>28</v>
@@ -17567,7 +17567,7 @@
         <v>27</v>
       </c>
       <c r="D791">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E791" t="s">
         <v>28</v>
@@ -17584,7 +17584,7 @@
         <v>27</v>
       </c>
       <c r="D792">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E792" t="s">
         <v>28</v>
@@ -17601,7 +17601,7 @@
         <v>27</v>
       </c>
       <c r="D793">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E793" t="s">
         <v>28</v>
@@ -17618,7 +17618,7 @@
         <v>27</v>
       </c>
       <c r="D794">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E794" t="s">
         <v>28</v>
@@ -17635,7 +17635,7 @@
         <v>27</v>
       </c>
       <c r="D795">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E795" t="s">
         <v>28</v>
@@ -17652,7 +17652,7 @@
         <v>27</v>
       </c>
       <c r="D796">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E796" t="s">
         <v>28</v>
@@ -17669,7 +17669,7 @@
         <v>27</v>
       </c>
       <c r="D797">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E797" t="s">
         <v>28</v>
@@ -17686,7 +17686,7 @@
         <v>27</v>
       </c>
       <c r="D798">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E798" t="s">
         <v>28</v>
@@ -17703,7 +17703,7 @@
         <v>27</v>
       </c>
       <c r="D799">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E799" t="s">
         <v>28</v>
@@ -17720,7 +17720,7 @@
         <v>27</v>
       </c>
       <c r="D800">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E800" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="D801">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E801" t="s">
         <v>28</v>
@@ -17754,7 +17754,7 @@
         <v>27</v>
       </c>
       <c r="D802">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E802" t="s">
         <v>28</v>
@@ -17771,7 +17771,7 @@
         <v>27</v>
       </c>
       <c r="D803">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E803" t="s">
         <v>28</v>
@@ -17788,7 +17788,7 @@
         <v>27</v>
       </c>
       <c r="D804">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E804" t="s">
         <v>28</v>
@@ -17805,7 +17805,7 @@
         <v>27</v>
       </c>
       <c r="D805">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E805" t="s">
         <v>28</v>
@@ -17822,7 +17822,7 @@
         <v>27</v>
       </c>
       <c r="D806">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E806" t="s">
         <v>28</v>
@@ -17839,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="D807">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E807" t="s">
         <v>28</v>
@@ -17856,7 +17856,7 @@
         <v>27</v>
       </c>
       <c r="D808">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E808" t="s">
         <v>28</v>
@@ -17873,7 +17873,7 @@
         <v>27</v>
       </c>
       <c r="D809">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E809" t="s">
         <v>28</v>
@@ -17890,7 +17890,7 @@
         <v>27</v>
       </c>
       <c r="D810">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E810" t="s">
         <v>28</v>
@@ -17907,7 +17907,7 @@
         <v>27</v>
       </c>
       <c r="D811">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E811" t="s">
         <v>28</v>
@@ -17924,7 +17924,7 @@
         <v>27</v>
       </c>
       <c r="D812">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E812" t="s">
         <v>28</v>
@@ -17941,7 +17941,7 @@
         <v>27</v>
       </c>
       <c r="D813">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E813" t="s">
         <v>28</v>
@@ -17958,7 +17958,7 @@
         <v>27</v>
       </c>
       <c r="D814">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E814" t="s">
         <v>28</v>
@@ -17975,7 +17975,7 @@
         <v>27</v>
       </c>
       <c r="D815">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E815" t="s">
         <v>28</v>
@@ -17992,7 +17992,7 @@
         <v>27</v>
       </c>
       <c r="D816">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E816" t="s">
         <v>28</v>
@@ -18009,7 +18009,7 @@
         <v>27</v>
       </c>
       <c r="D817">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E817" t="s">
         <v>28</v>
@@ -18026,7 +18026,7 @@
         <v>27</v>
       </c>
       <c r="D818">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E818" t="s">
         <v>28</v>
@@ -18043,7 +18043,7 @@
         <v>27</v>
       </c>
       <c r="D819">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E819" t="s">
         <v>28</v>
@@ -18060,7 +18060,7 @@
         <v>27</v>
       </c>
       <c r="D820">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E820" t="s">
         <v>28</v>
@@ -18077,7 +18077,7 @@
         <v>27</v>
       </c>
       <c r="D821">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E821" t="s">
         <v>28</v>
@@ -18094,7 +18094,7 @@
         <v>27</v>
       </c>
       <c r="D822">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E822" t="s">
         <v>28</v>
@@ -18111,7 +18111,7 @@
         <v>27</v>
       </c>
       <c r="D823">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E823" t="s">
         <v>28</v>
@@ -18128,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="D824">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E824" t="s">
         <v>28</v>
@@ -18145,7 +18145,7 @@
         <v>27</v>
       </c>
       <c r="D825">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E825" t="s">
         <v>28</v>
@@ -18162,7 +18162,7 @@
         <v>27</v>
       </c>
       <c r="D826">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E826" t="s">
         <v>28</v>
@@ -18179,7 +18179,7 @@
         <v>27</v>
       </c>
       <c r="D827">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E827" t="s">
         <v>28</v>
@@ -18196,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="D828">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E828" t="s">
         <v>28</v>
@@ -18213,7 +18213,7 @@
         <v>27</v>
       </c>
       <c r="D829">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E829" t="s">
         <v>28</v>
@@ -18230,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="D830">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E830" t="s">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E831" t="s">
         <v>28</v>
@@ -18264,7 +18264,7 @@
         <v>27</v>
       </c>
       <c r="D832">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E832" t="s">
         <v>28</v>
@@ -18281,7 +18281,7 @@
         <v>27</v>
       </c>
       <c r="D833">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E833" t="s">
         <v>28</v>
@@ -18298,7 +18298,7 @@
         <v>27</v>
       </c>
       <c r="D834">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E834" t="s">
         <v>28</v>
@@ -18315,7 +18315,7 @@
         <v>27</v>
       </c>
       <c r="D835">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E835" t="s">
         <v>28</v>
@@ -18332,7 +18332,7 @@
         <v>27</v>
       </c>
       <c r="D836">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E836" t="s">
         <v>28</v>
@@ -18366,7 +18366,7 @@
         <v>27</v>
       </c>
       <c r="D838">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E838" t="s">
         <v>28</v>
@@ -18383,7 +18383,7 @@
         <v>27</v>
       </c>
       <c r="D839">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E839" t="s">
         <v>28</v>
@@ -18400,7 +18400,7 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E840" t="s">
         <v>28</v>
@@ -18417,7 +18417,7 @@
         <v>27</v>
       </c>
       <c r="D841">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E841" t="s">
         <v>28</v>
@@ -18434,7 +18434,7 @@
         <v>27</v>
       </c>
       <c r="D842">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E842" t="s">
         <v>28</v>
@@ -18451,7 +18451,7 @@
         <v>27</v>
       </c>
       <c r="D843">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E843" t="s">
         <v>28</v>
@@ -18468,7 +18468,7 @@
         <v>27</v>
       </c>
       <c r="D844">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E844" t="s">
         <v>28</v>
@@ -18485,7 +18485,7 @@
         <v>27</v>
       </c>
       <c r="D845">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E845" t="s">
         <v>28</v>
@@ -18502,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="D846">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E846" t="s">
         <v>28</v>
@@ -18519,7 +18519,7 @@
         <v>27</v>
       </c>
       <c r="D847">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E847" t="s">
         <v>28</v>
@@ -18536,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="D848">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E848" t="s">
         <v>28</v>
@@ -18553,7 +18553,7 @@
         <v>27</v>
       </c>
       <c r="D849">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E849" t="s">
         <v>28</v>
@@ -18570,7 +18570,7 @@
         <v>27</v>
       </c>
       <c r="D850">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E850" t="s">
         <v>28</v>
@@ -18587,7 +18587,7 @@
         <v>27</v>
       </c>
       <c r="D851">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E851" t="s">
         <v>28</v>
@@ -18604,7 +18604,7 @@
         <v>27</v>
       </c>
       <c r="D852">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E852" t="s">
         <v>28</v>
@@ -18621,7 +18621,7 @@
         <v>27</v>
       </c>
       <c r="D853">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E853" t="s">
         <v>28</v>
@@ -18638,7 +18638,7 @@
         <v>27</v>
       </c>
       <c r="D854">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E854" t="s">
         <v>28</v>
@@ -18655,7 +18655,7 @@
         <v>27</v>
       </c>
       <c r="D855">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E855" t="s">
         <v>28</v>
@@ -18672,7 +18672,7 @@
         <v>27</v>
       </c>
       <c r="D856">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E856" t="s">
         <v>28</v>
@@ -18689,7 +18689,7 @@
         <v>27</v>
       </c>
       <c r="D857">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E857" t="s">
         <v>28</v>
@@ -18706,7 +18706,7 @@
         <v>27</v>
       </c>
       <c r="D858">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E858" t="s">
         <v>28</v>
@@ -18723,7 +18723,7 @@
         <v>27</v>
       </c>
       <c r="D859">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E859" t="s">
         <v>28</v>
@@ -18740,7 +18740,7 @@
         <v>27</v>
       </c>
       <c r="D860">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E860" t="s">
         <v>28</v>
@@ -18757,7 +18757,7 @@
         <v>27</v>
       </c>
       <c r="D861">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E861" t="s">
         <v>28</v>
@@ -18774,7 +18774,7 @@
         <v>27</v>
       </c>
       <c r="D862">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E862" t="s">
         <v>28</v>
@@ -18791,7 +18791,7 @@
         <v>27</v>
       </c>
       <c r="D863">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E863" t="s">
         <v>28</v>
@@ -18808,7 +18808,7 @@
         <v>27</v>
       </c>
       <c r="D864">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E864" t="s">
         <v>28</v>
@@ -18825,7 +18825,7 @@
         <v>27</v>
       </c>
       <c r="D865">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E865" t="s">
         <v>28</v>
@@ -18842,7 +18842,7 @@
         <v>27</v>
       </c>
       <c r="D866">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E866" t="s">
         <v>28</v>
@@ -18859,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="D867">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E867" t="s">
         <v>28</v>
@@ -18876,7 +18876,7 @@
         <v>27</v>
       </c>
       <c r="D868">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E868" t="s">
         <v>28</v>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
       <c r="D869">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E869" t="s">
         <v>28</v>
@@ -18910,7 +18910,7 @@
         <v>27</v>
       </c>
       <c r="D870">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E870" t="s">
         <v>28</v>
@@ -18927,7 +18927,7 @@
         <v>27</v>
       </c>
       <c r="D871">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E871" t="s">
         <v>28</v>
@@ -18944,7 +18944,7 @@
         <v>27</v>
       </c>
       <c r="D872">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E872" t="s">
         <v>28</v>
@@ -18961,7 +18961,7 @@
         <v>27</v>
       </c>
       <c r="D873">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E873" t="s">
         <v>28</v>
@@ -18978,7 +18978,7 @@
         <v>27</v>
       </c>
       <c r="D874">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E874" t="s">
         <v>28</v>
@@ -18995,7 +18995,7 @@
         <v>27</v>
       </c>
       <c r="D875">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E875" t="s">
         <v>28</v>
@@ -19012,7 +19012,7 @@
         <v>27</v>
       </c>
       <c r="D876">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E876" t="s">
         <v>28</v>
@@ -19029,7 +19029,7 @@
         <v>27</v>
       </c>
       <c r="D877">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E877" t="s">
         <v>28</v>
@@ -19046,7 +19046,7 @@
         <v>27</v>
       </c>
       <c r="D878">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E878" t="s">
         <v>28</v>
@@ -19063,7 +19063,7 @@
         <v>27</v>
       </c>
       <c r="D879">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E879" t="s">
         <v>28</v>
@@ -19080,7 +19080,7 @@
         <v>27</v>
       </c>
       <c r="D880">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E880" t="s">
         <v>28</v>
@@ -19097,7 +19097,7 @@
         <v>27</v>
       </c>
       <c r="D881">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E881" t="s">
         <v>28</v>
@@ -19114,7 +19114,7 @@
         <v>27</v>
       </c>
       <c r="D882">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E882" t="s">
         <v>28</v>
@@ -19148,7 +19148,7 @@
         <v>27</v>
       </c>
       <c r="D884">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E884" t="s">
         <v>28</v>
@@ -19165,7 +19165,7 @@
         <v>27</v>
       </c>
       <c r="D885">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E885" t="s">
         <v>28</v>
@@ -19182,7 +19182,7 @@
         <v>27</v>
       </c>
       <c r="D886">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E886" t="s">
         <v>28</v>
@@ -19199,7 +19199,7 @@
         <v>27</v>
       </c>
       <c r="D887">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E887" t="s">
         <v>28</v>
@@ -19216,7 +19216,7 @@
         <v>27</v>
       </c>
       <c r="D888">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E888" t="s">
         <v>28</v>
@@ -19233,7 +19233,7 @@
         <v>27</v>
       </c>
       <c r="D889">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E889" t="s">
         <v>28</v>
@@ -19250,7 +19250,7 @@
         <v>27</v>
       </c>
       <c r="D890">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E890" t="s">
         <v>28</v>
@@ -19267,7 +19267,7 @@
         <v>27</v>
       </c>
       <c r="D891">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E891" t="s">
         <v>28</v>
@@ -19284,7 +19284,7 @@
         <v>27</v>
       </c>
       <c r="D892">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E892" t="s">
         <v>28</v>
@@ -19301,7 +19301,7 @@
         <v>27</v>
       </c>
       <c r="D893">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E893" t="s">
         <v>28</v>
@@ -19318,7 +19318,7 @@
         <v>27</v>
       </c>
       <c r="D894">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E894" t="s">
         <v>28</v>
@@ -19352,7 +19352,7 @@
         <v>27</v>
       </c>
       <c r="D896">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E896" t="s">
         <v>28</v>
@@ -19369,7 +19369,7 @@
         <v>27</v>
       </c>
       <c r="D897">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E897" t="s">
         <v>28</v>
@@ -19386,7 +19386,7 @@
         <v>27</v>
       </c>
       <c r="D898">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E898" t="s">
         <v>28</v>
@@ -19403,7 +19403,7 @@
         <v>27</v>
       </c>
       <c r="D899">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E899" t="s">
         <v>28</v>
@@ -19420,7 +19420,7 @@
         <v>27</v>
       </c>
       <c r="D900">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E900" t="s">
         <v>28</v>
@@ -19437,7 +19437,7 @@
         <v>27</v>
       </c>
       <c r="D901">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E901" t="s">
         <v>28</v>
@@ -19454,7 +19454,7 @@
         <v>27</v>
       </c>
       <c r="D902">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E902" t="s">
         <v>28</v>
@@ -19471,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D903">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E903" t="s">
         <v>28</v>
@@ -19488,7 +19488,7 @@
         <v>27</v>
       </c>
       <c r="D904">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E904" t="s">
         <v>28</v>
@@ -19505,7 +19505,7 @@
         <v>27</v>
       </c>
       <c r="D905">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E905" t="s">
         <v>28</v>
@@ -19522,7 +19522,7 @@
         <v>27</v>
       </c>
       <c r="D906">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E906" t="s">
         <v>28</v>
@@ -19539,7 +19539,7 @@
         <v>27</v>
       </c>
       <c r="D907">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E907" t="s">
         <v>28</v>
@@ -19556,7 +19556,7 @@
         <v>27</v>
       </c>
       <c r="D908">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E908" t="s">
         <v>28</v>
@@ -19573,7 +19573,7 @@
         <v>27</v>
       </c>
       <c r="D909">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E909" t="s">
         <v>28</v>
@@ -19590,7 +19590,7 @@
         <v>27</v>
       </c>
       <c r="D910">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E910" t="s">
         <v>28</v>
@@ -19607,7 +19607,7 @@
         <v>27</v>
       </c>
       <c r="D911">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E911" t="s">
         <v>28</v>
@@ -19624,7 +19624,7 @@
         <v>27</v>
       </c>
       <c r="D912">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E912" t="s">
         <v>28</v>
@@ -19641,7 +19641,7 @@
         <v>27</v>
       </c>
       <c r="D913">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E913" t="s">
         <v>28</v>
@@ -19658,7 +19658,7 @@
         <v>27</v>
       </c>
       <c r="D914">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E914" t="s">
         <v>28</v>
@@ -19675,7 +19675,7 @@
         <v>27</v>
       </c>
       <c r="D915">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E915" t="s">
         <v>28</v>
@@ -19692,7 +19692,7 @@
         <v>27</v>
       </c>
       <c r="D916">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E916" t="s">
         <v>28</v>
@@ -19709,7 +19709,7 @@
         <v>27</v>
       </c>
       <c r="D917">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E917" t="s">
         <v>28</v>
@@ -19726,7 +19726,7 @@
         <v>27</v>
       </c>
       <c r="D918">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E918" t="s">
         <v>28</v>
@@ -19743,7 +19743,7 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E919" t="s">
         <v>28</v>
@@ -19760,7 +19760,7 @@
         <v>27</v>
       </c>
       <c r="D920">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E920" t="s">
         <v>28</v>
@@ -19777,7 +19777,7 @@
         <v>27</v>
       </c>
       <c r="D921">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E921" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>27</v>
       </c>
       <c r="D922">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E922" t="s">
         <v>28</v>
@@ -19811,7 +19811,7 @@
         <v>27</v>
       </c>
       <c r="D923">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E923" t="s">
         <v>28</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="D924">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E924" t="s">
         <v>28</v>
@@ -19845,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="D925">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E925" t="s">
         <v>28</v>
@@ -19862,7 +19862,7 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E926" t="s">
         <v>28</v>
@@ -19879,7 +19879,7 @@
         <v>27</v>
       </c>
       <c r="D927">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E927" t="s">
         <v>28</v>
@@ -19896,7 +19896,7 @@
         <v>27</v>
       </c>
       <c r="D928">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E928" t="s">
         <v>28</v>
@@ -19913,7 +19913,7 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E929" t="s">
         <v>28</v>
@@ -19930,7 +19930,7 @@
         <v>27</v>
       </c>
       <c r="D930">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E930" t="s">
         <v>28</v>
@@ -19947,7 +19947,7 @@
         <v>27</v>
       </c>
       <c r="D931">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E931" t="s">
         <v>28</v>
@@ -19964,7 +19964,7 @@
         <v>27</v>
       </c>
       <c r="D932">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E932" t="s">
         <v>28</v>
@@ -19981,7 +19981,7 @@
         <v>27</v>
       </c>
       <c r="D933">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E933" t="s">
         <v>28</v>
@@ -19998,7 +19998,7 @@
         <v>27</v>
       </c>
       <c r="D934">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E934" t="s">
         <v>28</v>
@@ -20015,7 +20015,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E935" t="s">
         <v>28</v>
@@ -20032,7 +20032,7 @@
         <v>27</v>
       </c>
       <c r="D936">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E936" t="s">
         <v>28</v>
@@ -20049,7 +20049,7 @@
         <v>27</v>
       </c>
       <c r="D937">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E937" t="s">
         <v>28</v>
@@ -20066,7 +20066,7 @@
         <v>27</v>
       </c>
       <c r="D938">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E938" t="s">
         <v>28</v>
@@ -20083,7 +20083,7 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E939" t="s">
         <v>28</v>
@@ -20100,7 +20100,7 @@
         <v>27</v>
       </c>
       <c r="D940">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E940" t="s">
         <v>28</v>
@@ -20117,7 +20117,7 @@
         <v>27</v>
       </c>
       <c r="D941">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E941" t="s">
         <v>28</v>
@@ -20134,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D942">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E942" t="s">
         <v>28</v>
@@ -20151,7 +20151,7 @@
         <v>27</v>
       </c>
       <c r="D943">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E943" t="s">
         <v>28</v>
@@ -20168,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="D944">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E944" t="s">
         <v>28</v>
@@ -20185,7 +20185,7 @@
         <v>27</v>
       </c>
       <c r="D945">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E945" t="s">
         <v>28</v>
@@ -20202,7 +20202,7 @@
         <v>27</v>
       </c>
       <c r="D946">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E946" t="s">
         <v>28</v>
@@ -20219,7 +20219,7 @@
         <v>27</v>
       </c>
       <c r="D947">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E947" t="s">
         <v>28</v>
@@ -20236,7 +20236,7 @@
         <v>27</v>
       </c>
       <c r="D948">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E948" t="s">
         <v>28</v>
@@ -20253,7 +20253,7 @@
         <v>27</v>
       </c>
       <c r="D949">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E949" t="s">
         <v>28</v>
@@ -20270,7 +20270,7 @@
         <v>27</v>
       </c>
       <c r="D950">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E950" t="s">
         <v>28</v>
@@ -20287,7 +20287,7 @@
         <v>27</v>
       </c>
       <c r="D951">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E951" t="s">
         <v>28</v>
@@ -20304,7 +20304,7 @@
         <v>27</v>
       </c>
       <c r="D952">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E952" t="s">
         <v>28</v>
@@ -20321,7 +20321,7 @@
         <v>27</v>
       </c>
       <c r="D953">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E953" t="s">
         <v>28</v>
@@ -20338,7 +20338,7 @@
         <v>27</v>
       </c>
       <c r="D954">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E954" t="s">
         <v>28</v>
@@ -20355,7 +20355,7 @@
         <v>27</v>
       </c>
       <c r="D955">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E955" t="s">
         <v>28</v>
@@ -20389,7 +20389,7 @@
         <v>27</v>
       </c>
       <c r="D957">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E957" t="s">
         <v>28</v>
@@ -20406,7 +20406,7 @@
         <v>27</v>
       </c>
       <c r="D958">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E958" t="s">
         <v>28</v>
@@ -20423,7 +20423,7 @@
         <v>27</v>
       </c>
       <c r="D959">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E959" t="s">
         <v>28</v>
@@ -20440,7 +20440,7 @@
         <v>27</v>
       </c>
       <c r="D960">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E960" t="s">
         <v>28</v>
@@ -20457,7 +20457,7 @@
         <v>27</v>
       </c>
       <c r="D961">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E961" t="s">
         <v>28</v>
@@ -20491,7 +20491,7 @@
         <v>27</v>
       </c>
       <c r="D963">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E963" t="s">
         <v>28</v>
@@ -20508,7 +20508,7 @@
         <v>27</v>
       </c>
       <c r="D964">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E964" t="s">
         <v>28</v>
@@ -20525,7 +20525,7 @@
         <v>27</v>
       </c>
       <c r="D965">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E965" t="s">
         <v>28</v>
@@ -20542,7 +20542,7 @@
         <v>27</v>
       </c>
       <c r="D966">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E966" t="s">
         <v>28</v>
@@ -20559,7 +20559,7 @@
         <v>27</v>
       </c>
       <c r="D967">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E967" t="s">
         <v>28</v>
@@ -20576,7 +20576,7 @@
         <v>27</v>
       </c>
       <c r="D968">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E968" t="s">
         <v>28</v>
@@ -20593,7 +20593,7 @@
         <v>27</v>
       </c>
       <c r="D969">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E969" t="s">
         <v>28</v>
@@ -20610,7 +20610,7 @@
         <v>27</v>
       </c>
       <c r="D970">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E970" t="s">
         <v>28</v>
@@ -20627,7 +20627,7 @@
         <v>27</v>
       </c>
       <c r="D971">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E971" t="s">
         <v>28</v>
@@ -20644,7 +20644,7 @@
         <v>27</v>
       </c>
       <c r="D972">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E972" t="s">
         <v>28</v>
@@ -20661,7 +20661,7 @@
         <v>27</v>
       </c>
       <c r="D973">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E973" t="s">
         <v>28</v>
@@ -20678,7 +20678,7 @@
         <v>27</v>
       </c>
       <c r="D974">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E974" t="s">
         <v>28</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="D975">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E975" t="s">
         <v>28</v>
@@ -20712,7 +20712,7 @@
         <v>27</v>
       </c>
       <c r="D976">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E976" t="s">
         <v>28</v>
@@ -20729,7 +20729,7 @@
         <v>27</v>
       </c>
       <c r="D977">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E977" t="s">
         <v>28</v>
@@ -20746,7 +20746,7 @@
         <v>27</v>
       </c>
       <c r="D978">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E978" t="s">
         <v>28</v>
@@ -20763,7 +20763,7 @@
         <v>27</v>
       </c>
       <c r="D979">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E979" t="s">
         <v>28</v>
@@ -20797,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="D981">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E981" t="s">
         <v>28</v>
@@ -20814,7 +20814,7 @@
         <v>27</v>
       </c>
       <c r="D982">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E982" t="s">
         <v>28</v>
@@ -20831,7 +20831,7 @@
         <v>27</v>
       </c>
       <c r="D983">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E983" t="s">
         <v>28</v>
@@ -20848,7 +20848,7 @@
         <v>27</v>
       </c>
       <c r="D984">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E984" t="s">
         <v>28</v>
@@ -20865,7 +20865,7 @@
         <v>27</v>
       </c>
       <c r="D985">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E985" t="s">
         <v>28</v>
@@ -20882,7 +20882,7 @@
         <v>27</v>
       </c>
       <c r="D986">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E986" t="s">
         <v>28</v>
@@ -20899,7 +20899,7 @@
         <v>27</v>
       </c>
       <c r="D987">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E987" t="s">
         <v>28</v>
@@ -20916,7 +20916,7 @@
         <v>27</v>
       </c>
       <c r="D988">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E988" t="s">
         <v>28</v>
@@ -20933,7 +20933,7 @@
         <v>27</v>
       </c>
       <c r="D989">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E989" t="s">
         <v>28</v>
@@ -20950,7 +20950,7 @@
         <v>27</v>
       </c>
       <c r="D990">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E990" t="s">
         <v>28</v>
@@ -20967,7 +20967,7 @@
         <v>27</v>
       </c>
       <c r="D991">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E991" t="s">
         <v>28</v>
@@ -20984,7 +20984,7 @@
         <v>27</v>
       </c>
       <c r="D992">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E992" t="s">
         <v>28</v>
@@ -21001,7 +21001,7 @@
         <v>27</v>
       </c>
       <c r="D993">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E993" t="s">
         <v>28</v>
@@ -21018,7 +21018,7 @@
         <v>27</v>
       </c>
       <c r="D994">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E994" t="s">
         <v>28</v>
@@ -21035,7 +21035,7 @@
         <v>27</v>
       </c>
       <c r="D995">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E995" t="s">
         <v>28</v>
@@ -21052,7 +21052,7 @@
         <v>27</v>
       </c>
       <c r="D996">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E996" t="s">
         <v>28</v>
@@ -21069,7 +21069,7 @@
         <v>27</v>
       </c>
       <c r="D997">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E997" t="s">
         <v>28</v>
@@ -21086,7 +21086,7 @@
         <v>27</v>
       </c>
       <c r="D998">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E998" t="s">
         <v>28</v>
@@ -21103,7 +21103,7 @@
         <v>27</v>
       </c>
       <c r="D999">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E999" t="s">
         <v>28</v>
@@ -21120,7 +21120,7 @@
         <v>27</v>
       </c>
       <c r="D1000">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1000" t="s">
         <v>28</v>
@@ -21137,7 +21137,7 @@
         <v>27</v>
       </c>
       <c r="D1001">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1001" t="s">
         <v>28</v>
@@ -21154,7 +21154,7 @@
         <v>27</v>
       </c>
       <c r="D1002">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1002" t="s">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>27</v>
       </c>
       <c r="D1003">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E1003" t="s">
         <v>28</v>
@@ -21188,7 +21188,7 @@
         <v>27</v>
       </c>
       <c r="D1004">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E1004" t="s">
         <v>28</v>
@@ -21205,7 +21205,7 @@
         <v>27</v>
       </c>
       <c r="D1005">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E1005" t="s">
         <v>28</v>
@@ -21222,7 +21222,7 @@
         <v>27</v>
       </c>
       <c r="D1006">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1006" t="s">
         <v>28</v>
@@ -21239,7 +21239,7 @@
         <v>27</v>
       </c>
       <c r="D1007">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1007" t="s">
         <v>28</v>
@@ -21256,7 +21256,7 @@
         <v>27</v>
       </c>
       <c r="D1008">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E1008" t="s">
         <v>28</v>
@@ -21273,7 +21273,7 @@
         <v>27</v>
       </c>
       <c r="D1009">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1009" t="s">
         <v>28</v>
@@ -21290,7 +21290,7 @@
         <v>27</v>
       </c>
       <c r="D1010">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1010" t="s">
         <v>28</v>
@@ -21307,7 +21307,7 @@
         <v>27</v>
       </c>
       <c r="D1011">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1011" t="s">
         <v>28</v>
@@ -21324,7 +21324,7 @@
         <v>27</v>
       </c>
       <c r="D1012">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E1012" t="s">
         <v>28</v>
@@ -21341,7 +21341,7 @@
         <v>27</v>
       </c>
       <c r="D1013">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1013" t="s">
         <v>28</v>
@@ -21358,7 +21358,7 @@
         <v>27</v>
       </c>
       <c r="D1014">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E1014" t="s">
         <v>28</v>
@@ -21375,7 +21375,7 @@
         <v>27</v>
       </c>
       <c r="D1015">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E1015" t="s">
         <v>28</v>
@@ -21392,7 +21392,7 @@
         <v>27</v>
       </c>
       <c r="D1016">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E1016" t="s">
         <v>28</v>
@@ -21409,7 +21409,7 @@
         <v>27</v>
       </c>
       <c r="D1017">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E1017" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>27</v>
       </c>
       <c r="D1018">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1018" t="s">
         <v>28</v>
@@ -21443,7 +21443,7 @@
         <v>27</v>
       </c>
       <c r="D1019">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E1019" t="s">
         <v>28</v>
@@ -21460,7 +21460,7 @@
         <v>27</v>
       </c>
       <c r="D1020">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1020" t="s">
         <v>28</v>
@@ -21477,7 +21477,7 @@
         <v>27</v>
       </c>
       <c r="D1021">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1021" t="s">
         <v>28</v>
@@ -21494,7 +21494,7 @@
         <v>27</v>
       </c>
       <c r="D1022">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1022" t="s">
         <v>28</v>
@@ -21511,7 +21511,7 @@
         <v>27</v>
       </c>
       <c r="D1023">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E1023" t="s">
         <v>28</v>
@@ -21528,7 +21528,7 @@
         <v>27</v>
       </c>
       <c r="D1024">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E1024" t="s">
         <v>28</v>
@@ -21545,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E1025" t="s">
         <v>28</v>
@@ -21562,7 +21562,7 @@
         <v>27</v>
       </c>
       <c r="D1026">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1026" t="s">
         <v>28</v>
@@ -21579,7 +21579,7 @@
         <v>27</v>
       </c>
       <c r="D1027">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E1027" t="s">
         <v>28</v>
@@ -21596,7 +21596,7 @@
         <v>27</v>
       </c>
       <c r="D1028">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1028" t="s">
         <v>28</v>
@@ -21613,7 +21613,7 @@
         <v>27</v>
       </c>
       <c r="D1029">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E1029" t="s">
         <v>28</v>
@@ -21630,7 +21630,7 @@
         <v>27</v>
       </c>
       <c r="D1030">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1030" t="s">
         <v>28</v>
@@ -21647,7 +21647,7 @@
         <v>27</v>
       </c>
       <c r="D1031">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E1031" t="s">
         <v>28</v>
@@ -21664,7 +21664,7 @@
         <v>27</v>
       </c>
       <c r="D1032">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E1032" t="s">
         <v>28</v>
@@ -21681,7 +21681,7 @@
         <v>27</v>
       </c>
       <c r="D1033">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1033" t="s">
         <v>28</v>
@@ -21698,7 +21698,7 @@
         <v>27</v>
       </c>
       <c r="D1034">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E1034" t="s">
         <v>28</v>
@@ -21715,7 +21715,7 @@
         <v>27</v>
       </c>
       <c r="D1035">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1035" t="s">
         <v>28</v>
@@ -21732,7 +21732,7 @@
         <v>27</v>
       </c>
       <c r="D1036">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1036" t="s">
         <v>28</v>
@@ -21749,7 +21749,7 @@
         <v>27</v>
       </c>
       <c r="D1037">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1037" t="s">
         <v>28</v>
@@ -21766,7 +21766,7 @@
         <v>27</v>
       </c>
       <c r="D1038">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E1038" t="s">
         <v>28</v>
@@ -21800,7 +21800,7 @@
         <v>27</v>
       </c>
       <c r="D1040">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E1040" t="s">
         <v>28</v>
@@ -21817,7 +21817,7 @@
         <v>27</v>
       </c>
       <c r="D1041">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E1041" t="s">
         <v>28</v>
@@ -21834,7 +21834,7 @@
         <v>27</v>
       </c>
       <c r="D1042">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E1042" t="s">
         <v>28</v>
@@ -21868,7 +21868,7 @@
         <v>27</v>
       </c>
       <c r="D1044">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E1044" t="s">
         <v>28</v>
@@ -21885,7 +21885,7 @@
         <v>27</v>
       </c>
       <c r="D1045">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1045" t="s">
         <v>28</v>
@@ -21902,7 +21902,7 @@
         <v>27</v>
       </c>
       <c r="D1046">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1046" t="s">
         <v>28</v>
@@ -21919,7 +21919,7 @@
         <v>27</v>
       </c>
       <c r="D1047">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1047" t="s">
         <v>28</v>
@@ -21936,7 +21936,7 @@
         <v>27</v>
       </c>
       <c r="D1048">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1048" t="s">
         <v>28</v>
@@ -21953,7 +21953,7 @@
         <v>27</v>
       </c>
       <c r="D1049">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E1049" t="s">
         <v>28</v>
@@ -21970,7 +21970,7 @@
         <v>27</v>
       </c>
       <c r="D1050">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E1050" t="s">
         <v>28</v>
@@ -21987,7 +21987,7 @@
         <v>27</v>
       </c>
       <c r="D1051">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E1051" t="s">
         <v>28</v>
@@ -22004,7 +22004,7 @@
         <v>27</v>
       </c>
       <c r="D1052">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E1052" t="s">
         <v>28</v>
@@ -22021,7 +22021,7 @@
         <v>27</v>
       </c>
       <c r="D1053">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1053" t="s">
         <v>28</v>
@@ -22038,7 +22038,7 @@
         <v>27</v>
       </c>
       <c r="D1054">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1054" t="s">
         <v>28</v>
@@ -22055,7 +22055,7 @@
         <v>27</v>
       </c>
       <c r="D1055">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1055" t="s">
         <v>28</v>
@@ -22072,7 +22072,7 @@
         <v>27</v>
       </c>
       <c r="D1056">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1056" t="s">
         <v>28</v>
@@ -22089,7 +22089,7 @@
         <v>27</v>
       </c>
       <c r="D1057">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1057" t="s">
         <v>28</v>
@@ -22106,7 +22106,7 @@
         <v>27</v>
       </c>
       <c r="D1058">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1058" t="s">
         <v>28</v>
@@ -22123,7 +22123,7 @@
         <v>27</v>
       </c>
       <c r="D1059">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E1059" t="s">
         <v>28</v>
@@ -22140,7 +22140,7 @@
         <v>27</v>
       </c>
       <c r="D1060">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1060" t="s">
         <v>28</v>
@@ -22157,7 +22157,7 @@
         <v>27</v>
       </c>
       <c r="D1061">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E1061" t="s">
         <v>28</v>
@@ -22174,7 +22174,7 @@
         <v>27</v>
       </c>
       <c r="D1062">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1062" t="s">
         <v>28</v>
@@ -22191,7 +22191,7 @@
         <v>27</v>
       </c>
       <c r="D1063">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E1063" t="s">
         <v>28</v>
@@ -22208,7 +22208,7 @@
         <v>27</v>
       </c>
       <c r="D1064">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1064" t="s">
         <v>28</v>
@@ -22225,7 +22225,7 @@
         <v>27</v>
       </c>
       <c r="D1065">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E1065" t="s">
         <v>28</v>
@@ -22242,7 +22242,7 @@
         <v>27</v>
       </c>
       <c r="D1066">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E1066" t="s">
         <v>28</v>
@@ -22259,7 +22259,7 @@
         <v>27</v>
       </c>
       <c r="D1067">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1067" t="s">
         <v>28</v>
@@ -22276,7 +22276,7 @@
         <v>27</v>
       </c>
       <c r="D1068">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E1068" t="s">
         <v>28</v>
@@ -22293,7 +22293,7 @@
         <v>27</v>
       </c>
       <c r="D1069">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1069" t="s">
         <v>28</v>
@@ -22310,7 +22310,7 @@
         <v>27</v>
       </c>
       <c r="D1070">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E1070" t="s">
         <v>28</v>
@@ -22344,7 +22344,7 @@
         <v>27</v>
       </c>
       <c r="D1072">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1072" t="s">
         <v>28</v>
@@ -22361,7 +22361,7 @@
         <v>27</v>
       </c>
       <c r="D1073">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1073" t="s">
         <v>28</v>
@@ -22378,7 +22378,7 @@
         <v>27</v>
       </c>
       <c r="D1074">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E1074" t="s">
         <v>28</v>
@@ -22395,7 +22395,7 @@
         <v>27</v>
       </c>
       <c r="D1075">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1075" t="s">
         <v>28</v>
@@ -22412,7 +22412,7 @@
         <v>27</v>
       </c>
       <c r="D1076">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E1076" t="s">
         <v>28</v>
@@ -22429,7 +22429,7 @@
         <v>27</v>
       </c>
       <c r="D1077">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E1077" t="s">
         <v>28</v>
@@ -22446,7 +22446,7 @@
         <v>27</v>
       </c>
       <c r="D1078">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E1078" t="s">
         <v>28</v>
@@ -22463,7 +22463,7 @@
         <v>27</v>
       </c>
       <c r="D1079">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1079" t="s">
         <v>28</v>
@@ -22480,7 +22480,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1080" t="s">
         <v>28</v>
@@ -22497,7 +22497,7 @@
         <v>27</v>
       </c>
       <c r="D1081">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1081" t="s">
         <v>28</v>
@@ -22514,7 +22514,7 @@
         <v>27</v>
       </c>
       <c r="D1082">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1082" t="s">
         <v>28</v>
@@ -22531,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="D1083">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1083" t="s">
         <v>28</v>
@@ -22548,7 +22548,7 @@
         <v>27</v>
       </c>
       <c r="D1084">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E1084" t="s">
         <v>28</v>
@@ -22565,7 +22565,7 @@
         <v>27</v>
       </c>
       <c r="D1085">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E1085" t="s">
         <v>28</v>
@@ -22582,7 +22582,7 @@
         <v>27</v>
       </c>
       <c r="D1086">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1086" t="s">
         <v>28</v>
@@ -22599,7 +22599,7 @@
         <v>27</v>
       </c>
       <c r="D1087">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1087" t="s">
         <v>28</v>
@@ -22616,7 +22616,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1088" t="s">
         <v>28</v>
@@ -22633,7 +22633,7 @@
         <v>27</v>
       </c>
       <c r="D1089">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1089" t="s">
         <v>28</v>
@@ -22650,7 +22650,7 @@
         <v>27</v>
       </c>
       <c r="D1090">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1090" t="s">
         <v>28</v>
@@ -22667,7 +22667,7 @@
         <v>27</v>
       </c>
       <c r="D1091">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1091" t="s">
         <v>28</v>
@@ -22684,7 +22684,7 @@
         <v>27</v>
       </c>
       <c r="D1092">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1092" t="s">
         <v>28</v>
@@ -22701,7 +22701,7 @@
         <v>27</v>
       </c>
       <c r="D1093">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1093" t="s">
         <v>28</v>
@@ -22718,7 +22718,7 @@
         <v>27</v>
       </c>
       <c r="D1094">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1094" t="s">
         <v>28</v>
@@ -22735,7 +22735,7 @@
         <v>27</v>
       </c>
       <c r="D1095">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1095" t="s">
         <v>28</v>
@@ -22769,7 +22769,7 @@
         <v>27</v>
       </c>
       <c r="D1097">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1097" t="s">
         <v>28</v>
@@ -22786,7 +22786,7 @@
         <v>27</v>
       </c>
       <c r="D1098">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1098" t="s">
         <v>28</v>
@@ -22803,7 +22803,7 @@
         <v>27</v>
       </c>
       <c r="D1099">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1099" t="s">
         <v>28</v>
@@ -22820,7 +22820,7 @@
         <v>27</v>
       </c>
       <c r="D1100">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1100" t="s">
         <v>28</v>
@@ -22837,7 +22837,7 @@
         <v>27</v>
       </c>
       <c r="D1101">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1101" t="s">
         <v>28</v>
@@ -22854,7 +22854,7 @@
         <v>27</v>
       </c>
       <c r="D1102">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E1102" t="s">
         <v>28</v>
@@ -22871,7 +22871,7 @@
         <v>27</v>
       </c>
       <c r="D1103">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E1103" t="s">
         <v>28</v>
@@ -22888,7 +22888,7 @@
         <v>27</v>
       </c>
       <c r="D1104">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1104" t="s">
         <v>28</v>
@@ -22905,7 +22905,7 @@
         <v>27</v>
       </c>
       <c r="D1105">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E1105" t="s">
         <v>28</v>
@@ -22922,7 +22922,7 @@
         <v>27</v>
       </c>
       <c r="D1106">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E1106" t="s">
         <v>28</v>
@@ -22939,7 +22939,7 @@
         <v>27</v>
       </c>
       <c r="D1107">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E1107" t="s">
         <v>28</v>
@@ -22956,7 +22956,7 @@
         <v>27</v>
       </c>
       <c r="D1108">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1108" t="s">
         <v>28</v>
@@ -22973,7 +22973,7 @@
         <v>27</v>
       </c>
       <c r="D1109">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E1109" t="s">
         <v>28</v>
@@ -22990,7 +22990,7 @@
         <v>27</v>
       </c>
       <c r="D1110">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E1110" t="s">
         <v>28</v>
@@ -23007,7 +23007,7 @@
         <v>27</v>
       </c>
       <c r="D1111">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E1111" t="s">
         <v>28</v>
@@ -23024,7 +23024,7 @@
         <v>27</v>
       </c>
       <c r="D1112">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1112" t="s">
         <v>28</v>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1385</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1311</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1403</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1274</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1318</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1259</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1290</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1264</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1260</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1175</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1296</v>
+        <v>1242</v>
       </c>
     </row>
   </sheetData>
@@ -4154,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -4188,7 +4188,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -4205,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -4222,7 +4222,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -4256,7 +4256,7 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -4273,7 +4273,7 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4307,7 +4307,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4341,7 +4341,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -4358,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4409,7 +4409,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -4443,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -4460,7 +4460,7 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
@@ -4494,7 +4494,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -4511,7 +4511,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -4528,7 +4528,7 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -4545,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
         <v>28</v>
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -4579,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -4596,7 +4596,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -4613,7 +4613,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E30" t="s">
         <v>28</v>
@@ -4647,7 +4647,7 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4681,7 +4681,7 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4698,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -4715,7 +4715,7 @@
         <v>27</v>
       </c>
       <c r="D35">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E35" t="s">
         <v>28</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -4749,7 +4749,7 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E37" t="s">
         <v>28</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="D38">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
         <v>28</v>
@@ -4783,7 +4783,7 @@
         <v>27</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E39" t="s">
         <v>28</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
@@ -4817,7 +4817,7 @@
         <v>27</v>
       </c>
       <c r="D41">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4834,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4851,7 +4851,7 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
@@ -4885,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
         <v>27</v>
       </c>
       <c r="D46">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -4919,7 +4919,7 @@
         <v>27</v>
       </c>
       <c r="D47">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="D48">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4953,7 +4953,7 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
@@ -4970,7 +4970,7 @@
         <v>27</v>
       </c>
       <c r="D50">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E50" t="s">
         <v>28</v>
@@ -4987,7 +4987,7 @@
         <v>27</v>
       </c>
       <c r="D51">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
@@ -5004,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5038,7 +5038,7 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E54" t="s">
         <v>28</v>
@@ -5055,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="D55">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -5072,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E56" t="s">
         <v>28</v>
@@ -5089,7 +5089,7 @@
         <v>27</v>
       </c>
       <c r="D57">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E57" t="s">
         <v>28</v>
@@ -5106,7 +5106,7 @@
         <v>27</v>
       </c>
       <c r="D58">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -5123,7 +5123,7 @@
         <v>27</v>
       </c>
       <c r="D59">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E59" t="s">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         <v>27</v>
       </c>
       <c r="D60">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E60" t="s">
         <v>28</v>
@@ -5157,7 +5157,7 @@
         <v>27</v>
       </c>
       <c r="D61">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -5174,7 +5174,7 @@
         <v>27</v>
       </c>
       <c r="D62">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
@@ -5191,7 +5191,7 @@
         <v>27</v>
       </c>
       <c r="D63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="D64">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
@@ -5225,7 +5225,7 @@
         <v>27</v>
       </c>
       <c r="D65">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -5242,7 +5242,7 @@
         <v>27</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="D67">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
@@ -5293,7 +5293,7 @@
         <v>27</v>
       </c>
       <c r="D69">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -5310,7 +5310,7 @@
         <v>27</v>
       </c>
       <c r="D70">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="D71">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -5344,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="D72">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
@@ -5361,7 +5361,7 @@
         <v>27</v>
       </c>
       <c r="D73">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -5378,7 +5378,7 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
@@ -5395,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="D75">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="D76">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
@@ -5429,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="D77">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -5446,7 +5446,7 @@
         <v>27</v>
       </c>
       <c r="D78">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
@@ -5463,7 +5463,7 @@
         <v>27</v>
       </c>
       <c r="D79">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
@@ -5480,7 +5480,7 @@
         <v>27</v>
       </c>
       <c r="D80">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
@@ -5497,7 +5497,7 @@
         <v>27</v>
       </c>
       <c r="D81">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E81" t="s">
         <v>28</v>
@@ -5514,7 +5514,7 @@
         <v>27</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
@@ -5531,7 +5531,7 @@
         <v>27</v>
       </c>
       <c r="D83">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
@@ -5548,7 +5548,7 @@
         <v>27</v>
       </c>
       <c r="D84">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
@@ -5565,7 +5565,7 @@
         <v>27</v>
       </c>
       <c r="D85">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -5582,7 +5582,7 @@
         <v>27</v>
       </c>
       <c r="D86">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
@@ -5599,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
@@ -5616,7 +5616,7 @@
         <v>27</v>
       </c>
       <c r="D88">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -5633,7 +5633,7 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="D90">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -5667,7 +5667,7 @@
         <v>27</v>
       </c>
       <c r="D91">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E91" t="s">
         <v>28</v>
@@ -5684,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="D92">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
@@ -5701,7 +5701,7 @@
         <v>27</v>
       </c>
       <c r="D93">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E93" t="s">
         <v>28</v>
@@ -5718,7 +5718,7 @@
         <v>27</v>
       </c>
       <c r="D94">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E94" t="s">
         <v>28</v>
@@ -5735,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -5752,7 +5752,7 @@
         <v>27</v>
       </c>
       <c r="D96">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E96" t="s">
         <v>28</v>
@@ -5769,7 +5769,7 @@
         <v>27</v>
       </c>
       <c r="D97">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E97" t="s">
         <v>28</v>
@@ -5786,7 +5786,7 @@
         <v>27</v>
       </c>
       <c r="D98">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="D99">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E99" t="s">
         <v>28</v>
@@ -5820,7 +5820,7 @@
         <v>27</v>
       </c>
       <c r="D100">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E100" t="s">
         <v>28</v>
@@ -5837,7 +5837,7 @@
         <v>27</v>
       </c>
       <c r="D101">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E101" t="s">
         <v>28</v>
@@ -5854,7 +5854,7 @@
         <v>27</v>
       </c>
       <c r="D102">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E102" t="s">
         <v>28</v>
@@ -5871,7 +5871,7 @@
         <v>27</v>
       </c>
       <c r="D103">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E103" t="s">
         <v>28</v>
@@ -5888,7 +5888,7 @@
         <v>27</v>
       </c>
       <c r="D104">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E104" t="s">
         <v>28</v>
@@ -5922,7 +5922,7 @@
         <v>27</v>
       </c>
       <c r="D106">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>27</v>
       </c>
       <c r="D107">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E107" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="D108">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5973,7 +5973,7 @@
         <v>27</v>
       </c>
       <c r="D109">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E109" t="s">
         <v>28</v>
@@ -5990,7 +5990,7 @@
         <v>27</v>
       </c>
       <c r="D110">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E110" t="s">
         <v>28</v>
@@ -6007,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="D111">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="D112">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="D113">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E113" t="s">
         <v>28</v>
@@ -6058,7 +6058,7 @@
         <v>27</v>
       </c>
       <c r="D114">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>27</v>
       </c>
       <c r="D115">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -6092,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="D116">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E116" t="s">
         <v>28</v>
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="D117">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E117" t="s">
         <v>28</v>
@@ -6126,7 +6126,7 @@
         <v>27</v>
       </c>
       <c r="D118">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E118" t="s">
         <v>28</v>
@@ -6160,7 +6160,7 @@
         <v>27</v>
       </c>
       <c r="D120">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E120" t="s">
         <v>28</v>
@@ -6177,7 +6177,7 @@
         <v>27</v>
       </c>
       <c r="D121">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E121" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="D122">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E122" t="s">
         <v>28</v>
@@ -6211,7 +6211,7 @@
         <v>27</v>
       </c>
       <c r="D123">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E123" t="s">
         <v>28</v>
@@ -6228,7 +6228,7 @@
         <v>27</v>
       </c>
       <c r="D124">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E124" t="s">
         <v>28</v>
@@ -6245,7 +6245,7 @@
         <v>27</v>
       </c>
       <c r="D125">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
@@ -6262,7 +6262,7 @@
         <v>27</v>
       </c>
       <c r="D126">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -6296,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="D128">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E128" t="s">
         <v>28</v>
@@ -6313,7 +6313,7 @@
         <v>27</v>
       </c>
       <c r="D129">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
@@ -6347,7 +6347,7 @@
         <v>27</v>
       </c>
       <c r="D131">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E131" t="s">
         <v>28</v>
@@ -6364,7 +6364,7 @@
         <v>27</v>
       </c>
       <c r="D132">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E132" t="s">
         <v>28</v>
@@ -6381,7 +6381,7 @@
         <v>27</v>
       </c>
       <c r="D133">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E133" t="s">
         <v>28</v>
@@ -6398,7 +6398,7 @@
         <v>27</v>
       </c>
       <c r="D134">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E134" t="s">
         <v>28</v>
@@ -6415,7 +6415,7 @@
         <v>27</v>
       </c>
       <c r="D135">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E135" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="D136">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E136" t="s">
         <v>28</v>
@@ -6449,7 +6449,7 @@
         <v>27</v>
       </c>
       <c r="D137">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E137" t="s">
         <v>28</v>
@@ -6466,7 +6466,7 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E138" t="s">
         <v>28</v>
@@ -6483,7 +6483,7 @@
         <v>27</v>
       </c>
       <c r="D139">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E139" t="s">
         <v>28</v>
@@ -6500,7 +6500,7 @@
         <v>27</v>
       </c>
       <c r="D140">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E140" t="s">
         <v>28</v>
@@ -6517,7 +6517,7 @@
         <v>27</v>
       </c>
       <c r="D141">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E141" t="s">
         <v>28</v>
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="D142">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E142" t="s">
         <v>28</v>
@@ -6551,7 +6551,7 @@
         <v>27</v>
       </c>
       <c r="D143">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E143" t="s">
         <v>28</v>
@@ -6568,7 +6568,7 @@
         <v>27</v>
       </c>
       <c r="D144">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E144" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="D145">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E145" t="s">
         <v>28</v>
@@ -6602,7 +6602,7 @@
         <v>27</v>
       </c>
       <c r="D146">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E146" t="s">
         <v>28</v>
@@ -6619,7 +6619,7 @@
         <v>27</v>
       </c>
       <c r="D147">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E147" t="s">
         <v>28</v>
@@ -6636,7 +6636,7 @@
         <v>27</v>
       </c>
       <c r="D148">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E148" t="s">
         <v>28</v>
@@ -6653,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="D149">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6687,7 +6687,7 @@
         <v>27</v>
       </c>
       <c r="D151">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>27</v>
       </c>
       <c r="D152">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E152" t="s">
         <v>28</v>
@@ -6721,7 +6721,7 @@
         <v>27</v>
       </c>
       <c r="D153">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E153" t="s">
         <v>28</v>
@@ -6738,7 +6738,7 @@
         <v>27</v>
       </c>
       <c r="D154">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E154" t="s">
         <v>28</v>
@@ -6755,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -6789,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="D157">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E157" t="s">
         <v>28</v>
@@ -6806,7 +6806,7 @@
         <v>27</v>
       </c>
       <c r="D158">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E158" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="D159">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E159" t="s">
         <v>28</v>
@@ -6840,7 +6840,7 @@
         <v>27</v>
       </c>
       <c r="D160">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E160" t="s">
         <v>28</v>
@@ -6857,7 +6857,7 @@
         <v>27</v>
       </c>
       <c r="D161">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
@@ -6891,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="D163">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E163" t="s">
         <v>28</v>
@@ -6908,7 +6908,7 @@
         <v>27</v>
       </c>
       <c r="D164">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E164" t="s">
         <v>28</v>
@@ -6925,7 +6925,7 @@
         <v>27</v>
       </c>
       <c r="D165">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E165" t="s">
         <v>28</v>
@@ -6942,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="D166">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E166" t="s">
         <v>28</v>
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="D167">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E167" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="D168">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E168" t="s">
         <v>28</v>
@@ -6993,7 +6993,7 @@
         <v>27</v>
       </c>
       <c r="D169">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E169" t="s">
         <v>28</v>
@@ -7010,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="D170">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E170" t="s">
         <v>28</v>
@@ -7027,7 +7027,7 @@
         <v>27</v>
       </c>
       <c r="D171">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E171" t="s">
         <v>28</v>
@@ -7044,7 +7044,7 @@
         <v>27</v>
       </c>
       <c r="D172">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E172" t="s">
         <v>28</v>
@@ -7078,7 +7078,7 @@
         <v>27</v>
       </c>
       <c r="D174">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E174" t="s">
         <v>28</v>
@@ -7095,7 +7095,7 @@
         <v>27</v>
       </c>
       <c r="D175">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E175" t="s">
         <v>28</v>
@@ -7112,7 +7112,7 @@
         <v>27</v>
       </c>
       <c r="D176">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E176" t="s">
         <v>28</v>
@@ -7129,7 +7129,7 @@
         <v>27</v>
       </c>
       <c r="D177">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E177" t="s">
         <v>28</v>
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="D178">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E178" t="s">
         <v>28</v>
@@ -7163,7 +7163,7 @@
         <v>27</v>
       </c>
       <c r="D179">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E179" t="s">
         <v>28</v>
@@ -7180,7 +7180,7 @@
         <v>27</v>
       </c>
       <c r="D180">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -7197,7 +7197,7 @@
         <v>27</v>
       </c>
       <c r="D181">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E181" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="D182">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E182" t="s">
         <v>28</v>
@@ -7231,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="D183">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
@@ -7248,7 +7248,7 @@
         <v>27</v>
       </c>
       <c r="D184">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E184" t="s">
         <v>28</v>
@@ -7265,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="D185">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E185" t="s">
         <v>28</v>
@@ -7282,7 +7282,7 @@
         <v>27</v>
       </c>
       <c r="D186">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E186" t="s">
         <v>28</v>
@@ -7299,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="D187">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E187" t="s">
         <v>28</v>
@@ -7316,7 +7316,7 @@
         <v>27</v>
       </c>
       <c r="D188">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -7333,7 +7333,7 @@
         <v>27</v>
       </c>
       <c r="D189">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E189" t="s">
         <v>28</v>
@@ -7350,7 +7350,7 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E190" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="D191">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
@@ -7384,7 +7384,7 @@
         <v>27</v>
       </c>
       <c r="D192">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E192" t="s">
         <v>28</v>
@@ -7401,7 +7401,7 @@
         <v>27</v>
       </c>
       <c r="D193">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E193" t="s">
         <v>28</v>
@@ -7418,7 +7418,7 @@
         <v>27</v>
       </c>
       <c r="D194">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E194" t="s">
         <v>28</v>
@@ -7435,7 +7435,7 @@
         <v>27</v>
       </c>
       <c r="D195">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E195" t="s">
         <v>28</v>
@@ -7452,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="D196">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E196" t="s">
         <v>28</v>
@@ -7469,7 +7469,7 @@
         <v>27</v>
       </c>
       <c r="D197">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E197" t="s">
         <v>28</v>
@@ -7486,7 +7486,7 @@
         <v>27</v>
       </c>
       <c r="D198">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E198" t="s">
         <v>28</v>
@@ -7503,7 +7503,7 @@
         <v>27</v>
       </c>
       <c r="D199">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E199" t="s">
         <v>28</v>
@@ -7520,7 +7520,7 @@
         <v>27</v>
       </c>
       <c r="D200">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E200" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>27</v>
       </c>
       <c r="D201">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E201" t="s">
         <v>28</v>
@@ -7554,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="D202">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E202" t="s">
         <v>28</v>
@@ -7571,7 +7571,7 @@
         <v>27</v>
       </c>
       <c r="D203">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
@@ -7588,7 +7588,7 @@
         <v>27</v>
       </c>
       <c r="D204">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E204" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="D205">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -7622,7 +7622,7 @@
         <v>27</v>
       </c>
       <c r="D206">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E206" t="s">
         <v>28</v>
@@ -7639,7 +7639,7 @@
         <v>27</v>
       </c>
       <c r="D207">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E207" t="s">
         <v>28</v>
@@ -7656,7 +7656,7 @@
         <v>27</v>
       </c>
       <c r="D208">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E208" t="s">
         <v>28</v>
@@ -7673,7 +7673,7 @@
         <v>27</v>
       </c>
       <c r="D209">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E209" t="s">
         <v>28</v>
@@ -7690,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="D210">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E210" t="s">
         <v>28</v>
@@ -7741,7 +7741,7 @@
         <v>27</v>
       </c>
       <c r="D213">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E213" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="D214">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E214" t="s">
         <v>28</v>
@@ -7775,7 +7775,7 @@
         <v>27</v>
       </c>
       <c r="D215">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E215" t="s">
         <v>28</v>
@@ -7809,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="D217">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E217" t="s">
         <v>28</v>
@@ -7826,7 +7826,7 @@
         <v>27</v>
       </c>
       <c r="D218">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E218" t="s">
         <v>28</v>
@@ -7843,7 +7843,7 @@
         <v>27</v>
       </c>
       <c r="D219">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E219" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="D220">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E220" t="s">
         <v>28</v>
@@ -7877,7 +7877,7 @@
         <v>27</v>
       </c>
       <c r="D221">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E221" t="s">
         <v>28</v>
@@ -7894,7 +7894,7 @@
         <v>27</v>
       </c>
       <c r="D222">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E222" t="s">
         <v>28</v>
@@ -7911,7 +7911,7 @@
         <v>27</v>
       </c>
       <c r="D223">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E223" t="s">
         <v>28</v>
@@ -7928,7 +7928,7 @@
         <v>27</v>
       </c>
       <c r="D224">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E224" t="s">
         <v>28</v>
@@ -7945,7 +7945,7 @@
         <v>27</v>
       </c>
       <c r="D225">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E225" t="s">
         <v>28</v>
@@ -7962,7 +7962,7 @@
         <v>27</v>
       </c>
       <c r="D226">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E226" t="s">
         <v>28</v>
@@ -7979,7 +7979,7 @@
         <v>27</v>
       </c>
       <c r="D227">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E227" t="s">
         <v>28</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="D228">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E228" t="s">
         <v>28</v>
@@ -8013,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="D229">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E229" t="s">
         <v>28</v>
@@ -8030,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="D230">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E230" t="s">
         <v>28</v>
@@ -8047,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="D231">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E231" t="s">
         <v>28</v>
@@ -8064,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="D232">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E232" t="s">
         <v>28</v>
@@ -8081,7 +8081,7 @@
         <v>27</v>
       </c>
       <c r="D233">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E233" t="s">
         <v>28</v>
@@ -8098,7 +8098,7 @@
         <v>27</v>
       </c>
       <c r="D234">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E234" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="D237">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E237" t="s">
         <v>28</v>
@@ -8166,7 +8166,7 @@
         <v>27</v>
       </c>
       <c r="D238">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E238" t="s">
         <v>28</v>
@@ -8183,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="D239">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E239" t="s">
         <v>28</v>
@@ -8200,7 +8200,7 @@
         <v>27</v>
       </c>
       <c r="D240">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E240" t="s">
         <v>28</v>
@@ -8217,7 +8217,7 @@
         <v>27</v>
       </c>
       <c r="D241">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E241" t="s">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>27</v>
       </c>
       <c r="D242">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E242" t="s">
         <v>28</v>
@@ -8251,7 +8251,7 @@
         <v>27</v>
       </c>
       <c r="D243">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E243" t="s">
         <v>28</v>
@@ -8268,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="D244">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E244" t="s">
         <v>28</v>
@@ -8285,7 +8285,7 @@
         <v>27</v>
       </c>
       <c r="D245">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E245" t="s">
         <v>28</v>
@@ -8302,7 +8302,7 @@
         <v>27</v>
       </c>
       <c r="D246">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E246" t="s">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="D247">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E247" t="s">
         <v>28</v>
@@ -8336,7 +8336,7 @@
         <v>27</v>
       </c>
       <c r="D248">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E248" t="s">
         <v>28</v>
@@ -8353,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="D249">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E249" t="s">
         <v>28</v>
@@ -8370,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="D250">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E250" t="s">
         <v>28</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="D251">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E251" t="s">
         <v>28</v>
@@ -8404,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="D252">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E252" t="s">
         <v>28</v>
@@ -8421,7 +8421,7 @@
         <v>27</v>
       </c>
       <c r="D253">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E253" t="s">
         <v>28</v>
@@ -8438,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D254">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E254" t="s">
         <v>28</v>
@@ -8455,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="D255">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E255" t="s">
         <v>28</v>
@@ -8472,7 +8472,7 @@
         <v>27</v>
       </c>
       <c r="D256">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E256" t="s">
         <v>28</v>
@@ -8489,7 +8489,7 @@
         <v>27</v>
       </c>
       <c r="D257">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E257" t="s">
         <v>28</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="D258">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E258" t="s">
         <v>28</v>
@@ -8523,7 +8523,7 @@
         <v>27</v>
       </c>
       <c r="D259">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E259" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="D260">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E260" t="s">
         <v>28</v>
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="D261">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E261" t="s">
         <v>28</v>
@@ -8574,7 +8574,7 @@
         <v>27</v>
       </c>
       <c r="D262">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E262" t="s">
         <v>28</v>
@@ -8591,7 +8591,7 @@
         <v>27</v>
       </c>
       <c r="D263">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E263" t="s">
         <v>28</v>
@@ -8608,7 +8608,7 @@
         <v>27</v>
       </c>
       <c r="D264">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E264" t="s">
         <v>28</v>
@@ -8642,7 +8642,7 @@
         <v>27</v>
       </c>
       <c r="D266">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E266" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="D267">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E267" t="s">
         <v>28</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="D268">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E268" t="s">
         <v>28</v>
@@ -8693,7 +8693,7 @@
         <v>27</v>
       </c>
       <c r="D269">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E269" t="s">
         <v>28</v>
@@ -8710,7 +8710,7 @@
         <v>27</v>
       </c>
       <c r="D270">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E270" t="s">
         <v>28</v>
@@ -8727,7 +8727,7 @@
         <v>27</v>
       </c>
       <c r="D271">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E271" t="s">
         <v>28</v>
@@ -8744,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="D272">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E272" t="s">
         <v>28</v>
@@ -8761,7 +8761,7 @@
         <v>27</v>
       </c>
       <c r="D273">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E273" t="s">
         <v>28</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="D274">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E274" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>27</v>
       </c>
       <c r="D275">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E275" t="s">
         <v>28</v>
@@ -8812,7 +8812,7 @@
         <v>27</v>
       </c>
       <c r="D276">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E276" t="s">
         <v>28</v>
@@ -8829,7 +8829,7 @@
         <v>27</v>
       </c>
       <c r="D277">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E277" t="s">
         <v>28</v>
@@ -8846,7 +8846,7 @@
         <v>27</v>
       </c>
       <c r="D278">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E278" t="s">
         <v>28</v>
@@ -8863,7 +8863,7 @@
         <v>27</v>
       </c>
       <c r="D279">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E279" t="s">
         <v>28</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E280" t="s">
         <v>28</v>
@@ -8897,7 +8897,7 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E281" t="s">
         <v>28</v>
@@ -8914,7 +8914,7 @@
         <v>27</v>
       </c>
       <c r="D282">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E282" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="D283">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E283" t="s">
         <v>28</v>
@@ -8948,7 +8948,7 @@
         <v>27</v>
       </c>
       <c r="D284">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E284" t="s">
         <v>28</v>
@@ -8965,7 +8965,7 @@
         <v>27</v>
       </c>
       <c r="D285">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E285" t="s">
         <v>28</v>
@@ -8982,7 +8982,7 @@
         <v>27</v>
       </c>
       <c r="D286">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E286" t="s">
         <v>28</v>
@@ -8999,7 +8999,7 @@
         <v>27</v>
       </c>
       <c r="D287">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E287" t="s">
         <v>28</v>
@@ -9016,7 +9016,7 @@
         <v>27</v>
       </c>
       <c r="D288">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E288" t="s">
         <v>28</v>
@@ -9033,7 +9033,7 @@
         <v>27</v>
       </c>
       <c r="D289">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E289" t="s">
         <v>28</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="D290">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E290" t="s">
         <v>28</v>
@@ -9067,7 +9067,7 @@
         <v>27</v>
       </c>
       <c r="D291">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E291" t="s">
         <v>28</v>
@@ -9084,7 +9084,7 @@
         <v>27</v>
       </c>
       <c r="D292">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E292" t="s">
         <v>28</v>
@@ -9101,7 +9101,7 @@
         <v>27</v>
       </c>
       <c r="D293">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E293" t="s">
         <v>28</v>
@@ -9118,7 +9118,7 @@
         <v>27</v>
       </c>
       <c r="D294">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E294" t="s">
         <v>28</v>
@@ -9135,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="D295">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E295" t="s">
         <v>28</v>
@@ -9152,7 +9152,7 @@
         <v>27</v>
       </c>
       <c r="D296">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E296" t="s">
         <v>28</v>
@@ -9169,7 +9169,7 @@
         <v>27</v>
       </c>
       <c r="D297">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E297" t="s">
         <v>28</v>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="D298">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E298" t="s">
         <v>28</v>
@@ -9203,7 +9203,7 @@
         <v>27</v>
       </c>
       <c r="D299">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E299" t="s">
         <v>28</v>
@@ -9220,7 +9220,7 @@
         <v>27</v>
       </c>
       <c r="D300">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E300" t="s">
         <v>28</v>
@@ -9237,7 +9237,7 @@
         <v>27</v>
       </c>
       <c r="D301">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E301" t="s">
         <v>28</v>
@@ -9254,7 +9254,7 @@
         <v>27</v>
       </c>
       <c r="D302">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E302" t="s">
         <v>28</v>
@@ -9271,7 +9271,7 @@
         <v>27</v>
       </c>
       <c r="D303">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E303" t="s">
         <v>28</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="D304">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E304" t="s">
         <v>28</v>
@@ -9305,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="D305">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E305" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="D306">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E306" t="s">
         <v>28</v>
@@ -9339,7 +9339,7 @@
         <v>27</v>
       </c>
       <c r="D307">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E307" t="s">
         <v>28</v>
@@ -9356,7 +9356,7 @@
         <v>27</v>
       </c>
       <c r="D308">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E308" t="s">
         <v>28</v>
@@ -9373,7 +9373,7 @@
         <v>27</v>
       </c>
       <c r="D309">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E309" t="s">
         <v>28</v>
@@ -9390,7 +9390,7 @@
         <v>27</v>
       </c>
       <c r="D310">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E310" t="s">
         <v>28</v>
@@ -9407,7 +9407,7 @@
         <v>27</v>
       </c>
       <c r="D311">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E311" t="s">
         <v>28</v>
@@ -9424,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="D312">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E312" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="D313">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E313" t="s">
         <v>28</v>
@@ -9458,7 +9458,7 @@
         <v>27</v>
       </c>
       <c r="D314">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E314" t="s">
         <v>28</v>
@@ -9475,7 +9475,7 @@
         <v>27</v>
       </c>
       <c r="D315">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E315" t="s">
         <v>28</v>
@@ -9492,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="D316">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E316" t="s">
         <v>28</v>
@@ -9509,7 +9509,7 @@
         <v>27</v>
       </c>
       <c r="D317">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E317" t="s">
         <v>28</v>
@@ -9526,7 +9526,7 @@
         <v>27</v>
       </c>
       <c r="D318">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E318" t="s">
         <v>28</v>
@@ -9543,7 +9543,7 @@
         <v>27</v>
       </c>
       <c r="D319">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E319" t="s">
         <v>28</v>
@@ -9560,7 +9560,7 @@
         <v>27</v>
       </c>
       <c r="D320">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E320" t="s">
         <v>28</v>
@@ -9577,7 +9577,7 @@
         <v>27</v>
       </c>
       <c r="D321">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E321" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
         <v>27</v>
       </c>
       <c r="D323">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E323" t="s">
         <v>28</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="D324">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E324" t="s">
         <v>28</v>
@@ -9645,7 +9645,7 @@
         <v>27</v>
       </c>
       <c r="D325">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E325" t="s">
         <v>28</v>
@@ -9662,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="D326">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E326" t="s">
         <v>28</v>
@@ -9679,7 +9679,7 @@
         <v>27</v>
       </c>
       <c r="D327">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E327" t="s">
         <v>28</v>
@@ -9696,7 +9696,7 @@
         <v>27</v>
       </c>
       <c r="D328">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E328" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="D329">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E329" t="s">
         <v>28</v>
@@ -9730,7 +9730,7 @@
         <v>27</v>
       </c>
       <c r="D330">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E330" t="s">
         <v>28</v>
@@ -9747,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="D331">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E331" t="s">
         <v>28</v>
@@ -9764,7 +9764,7 @@
         <v>27</v>
       </c>
       <c r="D332">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E332" t="s">
         <v>28</v>
@@ -9781,7 +9781,7 @@
         <v>27</v>
       </c>
       <c r="D333">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E333" t="s">
         <v>28</v>
@@ -9798,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="D334">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E334" t="s">
         <v>28</v>
@@ -9815,7 +9815,7 @@
         <v>27</v>
       </c>
       <c r="D335">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E335" t="s">
         <v>28</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="D336">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E336" t="s">
         <v>28</v>
@@ -9849,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="D337">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E337" t="s">
         <v>28</v>
@@ -9866,7 +9866,7 @@
         <v>27</v>
       </c>
       <c r="D338">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E338" t="s">
         <v>28</v>
@@ -9883,7 +9883,7 @@
         <v>27</v>
       </c>
       <c r="D339">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E339" t="s">
         <v>28</v>
@@ -9900,7 +9900,7 @@
         <v>27</v>
       </c>
       <c r="D340">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E340" t="s">
         <v>28</v>
@@ -9934,7 +9934,7 @@
         <v>27</v>
       </c>
       <c r="D342">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E342" t="s">
         <v>28</v>
@@ -9951,7 +9951,7 @@
         <v>27</v>
       </c>
       <c r="D343">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E343" t="s">
         <v>28</v>
@@ -9968,7 +9968,7 @@
         <v>27</v>
       </c>
       <c r="D344">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E344" t="s">
         <v>28</v>
@@ -9985,7 +9985,7 @@
         <v>27</v>
       </c>
       <c r="D345">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E345" t="s">
         <v>28</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D346">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E346" t="s">
         <v>28</v>
@@ -10019,7 +10019,7 @@
         <v>27</v>
       </c>
       <c r="D347">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E347" t="s">
         <v>28</v>
@@ -10036,7 +10036,7 @@
         <v>27</v>
       </c>
       <c r="D348">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E348" t="s">
         <v>28</v>
@@ -10053,7 +10053,7 @@
         <v>27</v>
       </c>
       <c r="D349">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E349" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="D350">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E350" t="s">
         <v>28</v>
@@ -10087,7 +10087,7 @@
         <v>27</v>
       </c>
       <c r="D351">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E351" t="s">
         <v>28</v>
@@ -10104,7 +10104,7 @@
         <v>27</v>
       </c>
       <c r="D352">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E352" t="s">
         <v>28</v>
@@ -10121,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D353">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E353" t="s">
         <v>28</v>
@@ -10138,7 +10138,7 @@
         <v>27</v>
       </c>
       <c r="D354">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E354" t="s">
         <v>28</v>
@@ -10155,7 +10155,7 @@
         <v>27</v>
       </c>
       <c r="D355">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E355" t="s">
         <v>28</v>
@@ -10172,7 +10172,7 @@
         <v>27</v>
       </c>
       <c r="D356">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E356" t="s">
         <v>28</v>
@@ -10189,7 +10189,7 @@
         <v>27</v>
       </c>
       <c r="D357">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E357" t="s">
         <v>28</v>
@@ -10206,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="D358">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E358" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="D359">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E359" t="s">
         <v>28</v>
@@ -10240,7 +10240,7 @@
         <v>27</v>
       </c>
       <c r="D360">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E360" t="s">
         <v>28</v>
@@ -10257,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="D361">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E361" t="s">
         <v>28</v>
@@ -10274,7 +10274,7 @@
         <v>27</v>
       </c>
       <c r="D362">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E362" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="D364">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E364" t="s">
         <v>28</v>
@@ -10325,7 +10325,7 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E365" t="s">
         <v>28</v>
@@ -10342,7 +10342,7 @@
         <v>27</v>
       </c>
       <c r="D366">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E366" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
         <v>27</v>
       </c>
       <c r="D367">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E367" t="s">
         <v>28</v>
@@ -10376,7 +10376,7 @@
         <v>27</v>
       </c>
       <c r="D368">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E368" t="s">
         <v>28</v>
@@ -10427,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="D371">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E371" t="s">
         <v>28</v>
@@ -10444,7 +10444,7 @@
         <v>27</v>
       </c>
       <c r="D372">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E372" t="s">
         <v>28</v>
@@ -10461,7 +10461,7 @@
         <v>27</v>
       </c>
       <c r="D373">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E373" t="s">
         <v>28</v>
@@ -10478,7 +10478,7 @@
         <v>27</v>
       </c>
       <c r="D374">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E374" t="s">
         <v>28</v>
@@ -10495,7 +10495,7 @@
         <v>27</v>
       </c>
       <c r="D375">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E375" t="s">
         <v>28</v>
@@ -10529,7 +10529,7 @@
         <v>27</v>
       </c>
       <c r="D377">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E377" t="s">
         <v>28</v>
@@ -10546,7 +10546,7 @@
         <v>27</v>
       </c>
       <c r="D378">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E378" t="s">
         <v>28</v>
@@ -10563,7 +10563,7 @@
         <v>27</v>
       </c>
       <c r="D379">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E379" t="s">
         <v>28</v>
@@ -10580,7 +10580,7 @@
         <v>27</v>
       </c>
       <c r="D380">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E380" t="s">
         <v>28</v>
@@ -10597,7 +10597,7 @@
         <v>27</v>
       </c>
       <c r="D381">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E381" t="s">
         <v>28</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="D382">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E382" t="s">
         <v>28</v>
@@ -10631,7 +10631,7 @@
         <v>27</v>
       </c>
       <c r="D383">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E383" t="s">
         <v>28</v>
@@ -10648,7 +10648,7 @@
         <v>27</v>
       </c>
       <c r="D384">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E384" t="s">
         <v>28</v>
@@ -10665,7 +10665,7 @@
         <v>27</v>
       </c>
       <c r="D385">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E385" t="s">
         <v>28</v>
@@ -10682,7 +10682,7 @@
         <v>27</v>
       </c>
       <c r="D386">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E386" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="D387">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E387" t="s">
         <v>28</v>
@@ -10716,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="D388">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E388" t="s">
         <v>28</v>
@@ -10733,7 +10733,7 @@
         <v>27</v>
       </c>
       <c r="D389">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E389" t="s">
         <v>28</v>
@@ -10750,7 +10750,7 @@
         <v>27</v>
       </c>
       <c r="D390">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E390" t="s">
         <v>28</v>
@@ -10767,7 +10767,7 @@
         <v>27</v>
       </c>
       <c r="D391">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E391" t="s">
         <v>28</v>
@@ -10784,7 +10784,7 @@
         <v>27</v>
       </c>
       <c r="D392">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E392" t="s">
         <v>28</v>
@@ -10818,7 +10818,7 @@
         <v>27</v>
       </c>
       <c r="D394">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E394" t="s">
         <v>28</v>
@@ -10852,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="D396">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E396" t="s">
         <v>28</v>
@@ -10869,7 +10869,7 @@
         <v>27</v>
       </c>
       <c r="D397">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E397" t="s">
         <v>28</v>
@@ -10886,7 +10886,7 @@
         <v>27</v>
       </c>
       <c r="D398">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E398" t="s">
         <v>28</v>
@@ -10903,7 +10903,7 @@
         <v>27</v>
       </c>
       <c r="D399">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E399" t="s">
         <v>28</v>
@@ -10920,7 +10920,7 @@
         <v>27</v>
       </c>
       <c r="D400">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E400" t="s">
         <v>28</v>
@@ -10937,7 +10937,7 @@
         <v>27</v>
       </c>
       <c r="D401">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E401" t="s">
         <v>28</v>
@@ -10954,7 +10954,7 @@
         <v>27</v>
       </c>
       <c r="D402">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E402" t="s">
         <v>28</v>
@@ -10971,7 +10971,7 @@
         <v>27</v>
       </c>
       <c r="D403">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E403" t="s">
         <v>28</v>
@@ -10988,7 +10988,7 @@
         <v>27</v>
       </c>
       <c r="D404">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E404" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="D405">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E405" t="s">
         <v>28</v>
@@ -11022,7 +11022,7 @@
         <v>27</v>
       </c>
       <c r="D406">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E406" t="s">
         <v>28</v>
@@ -11039,7 +11039,7 @@
         <v>27</v>
       </c>
       <c r="D407">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E407" t="s">
         <v>28</v>
@@ -11056,7 +11056,7 @@
         <v>27</v>
       </c>
       <c r="D408">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E408" t="s">
         <v>28</v>
@@ -11073,7 +11073,7 @@
         <v>27</v>
       </c>
       <c r="D409">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E409" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="D410">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E410" t="s">
         <v>28</v>
@@ -11107,7 +11107,7 @@
         <v>27</v>
       </c>
       <c r="D411">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E411" t="s">
         <v>28</v>
@@ -11124,7 +11124,7 @@
         <v>27</v>
       </c>
       <c r="D412">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E412" t="s">
         <v>28</v>
@@ -11141,7 +11141,7 @@
         <v>27</v>
       </c>
       <c r="D413">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E413" t="s">
         <v>28</v>
@@ -11158,7 +11158,7 @@
         <v>27</v>
       </c>
       <c r="D414">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E414" t="s">
         <v>28</v>
@@ -11175,7 +11175,7 @@
         <v>27</v>
       </c>
       <c r="D415">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E415" t="s">
         <v>28</v>
@@ -11192,7 +11192,7 @@
         <v>27</v>
       </c>
       <c r="D416">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E416" t="s">
         <v>28</v>
@@ -11209,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="D417">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E417" t="s">
         <v>28</v>
@@ -11226,7 +11226,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E418" t="s">
         <v>28</v>
@@ -11260,7 +11260,7 @@
         <v>27</v>
       </c>
       <c r="D420">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E420" t="s">
         <v>28</v>
@@ -11277,7 +11277,7 @@
         <v>27</v>
       </c>
       <c r="D421">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E421" t="s">
         <v>28</v>
@@ -11311,7 +11311,7 @@
         <v>27</v>
       </c>
       <c r="D423">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E423" t="s">
         <v>28</v>
@@ -11328,7 +11328,7 @@
         <v>27</v>
       </c>
       <c r="D424">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E424" t="s">
         <v>28</v>
@@ -11345,7 +11345,7 @@
         <v>27</v>
       </c>
       <c r="D425">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E425" t="s">
         <v>28</v>
@@ -11362,7 +11362,7 @@
         <v>27</v>
       </c>
       <c r="D426">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E426" t="s">
         <v>28</v>
@@ -11379,7 +11379,7 @@
         <v>27</v>
       </c>
       <c r="D427">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E427" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="D428">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E428" t="s">
         <v>28</v>
@@ -11413,7 +11413,7 @@
         <v>27</v>
       </c>
       <c r="D429">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E429" t="s">
         <v>28</v>
@@ -11430,7 +11430,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E430" t="s">
         <v>28</v>
@@ -11447,7 +11447,7 @@
         <v>27</v>
       </c>
       <c r="D431">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E431" t="s">
         <v>28</v>
@@ -11464,7 +11464,7 @@
         <v>27</v>
       </c>
       <c r="D432">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E432" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="D433">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E433" t="s">
         <v>28</v>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="D435">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E435" t="s">
         <v>28</v>
@@ -11532,7 +11532,7 @@
         <v>27</v>
       </c>
       <c r="D436">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E436" t="s">
         <v>28</v>
@@ -11549,7 +11549,7 @@
         <v>27</v>
       </c>
       <c r="D437">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E437" t="s">
         <v>28</v>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
       <c r="D438">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E438" t="s">
         <v>28</v>
@@ -11583,7 +11583,7 @@
         <v>27</v>
       </c>
       <c r="D439">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E439" t="s">
         <v>28</v>
@@ -11600,7 +11600,7 @@
         <v>27</v>
       </c>
       <c r="D440">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E440" t="s">
         <v>28</v>
@@ -11617,7 +11617,7 @@
         <v>27</v>
       </c>
       <c r="D441">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E441" t="s">
         <v>28</v>
@@ -11634,7 +11634,7 @@
         <v>27</v>
       </c>
       <c r="D442">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E442" t="s">
         <v>28</v>
@@ -11651,7 +11651,7 @@
         <v>27</v>
       </c>
       <c r="D443">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E443" t="s">
         <v>28</v>
@@ -11668,7 +11668,7 @@
         <v>27</v>
       </c>
       <c r="D444">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E444" t="s">
         <v>28</v>
@@ -11685,7 +11685,7 @@
         <v>27</v>
       </c>
       <c r="D445">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E445" t="s">
         <v>28</v>
@@ -11702,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D446">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E446" t="s">
         <v>28</v>
@@ -11719,7 +11719,7 @@
         <v>27</v>
       </c>
       <c r="D447">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E447" t="s">
         <v>28</v>
@@ -11736,7 +11736,7 @@
         <v>27</v>
       </c>
       <c r="D448">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E448" t="s">
         <v>28</v>
@@ -11753,7 +11753,7 @@
         <v>27</v>
       </c>
       <c r="D449">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E449" t="s">
         <v>28</v>
@@ -11770,7 +11770,7 @@
         <v>27</v>
       </c>
       <c r="D450">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E450" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="D451">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E451" t="s">
         <v>28</v>
@@ -11804,7 +11804,7 @@
         <v>27</v>
       </c>
       <c r="D452">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E452" t="s">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>27</v>
       </c>
       <c r="D453">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E453" t="s">
         <v>28</v>
@@ -11838,7 +11838,7 @@
         <v>27</v>
       </c>
       <c r="D454">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E454" t="s">
         <v>28</v>
@@ -11855,7 +11855,7 @@
         <v>27</v>
       </c>
       <c r="D455">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E455" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="D456">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E456" t="s">
         <v>28</v>
@@ -11906,7 +11906,7 @@
         <v>27</v>
       </c>
       <c r="D458">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E458" t="s">
         <v>28</v>
@@ -11923,7 +11923,7 @@
         <v>27</v>
       </c>
       <c r="D459">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E459" t="s">
         <v>28</v>
@@ -11940,7 +11940,7 @@
         <v>27</v>
       </c>
       <c r="D460">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E460" t="s">
         <v>28</v>
@@ -11957,7 +11957,7 @@
         <v>27</v>
       </c>
       <c r="D461">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E461" t="s">
         <v>28</v>
@@ -11974,7 +11974,7 @@
         <v>27</v>
       </c>
       <c r="D462">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E462" t="s">
         <v>28</v>
@@ -11991,7 +11991,7 @@
         <v>27</v>
       </c>
       <c r="D463">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E463" t="s">
         <v>28</v>
@@ -12008,7 +12008,7 @@
         <v>27</v>
       </c>
       <c r="D464">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E464" t="s">
         <v>28</v>
@@ -12025,7 +12025,7 @@
         <v>27</v>
       </c>
       <c r="D465">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E465" t="s">
         <v>28</v>
@@ -12042,7 +12042,7 @@
         <v>27</v>
       </c>
       <c r="D466">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E466" t="s">
         <v>28</v>
@@ -12076,7 +12076,7 @@
         <v>27</v>
       </c>
       <c r="D468">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E468" t="s">
         <v>28</v>
@@ -12093,7 +12093,7 @@
         <v>27</v>
       </c>
       <c r="D469">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E469" t="s">
         <v>28</v>
@@ -12110,7 +12110,7 @@
         <v>27</v>
       </c>
       <c r="D470">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E470" t="s">
         <v>28</v>
@@ -12127,7 +12127,7 @@
         <v>27</v>
       </c>
       <c r="D471">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E471" t="s">
         <v>28</v>
@@ -12144,7 +12144,7 @@
         <v>27</v>
       </c>
       <c r="D472">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E472" t="s">
         <v>28</v>
@@ -12161,7 +12161,7 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E473" t="s">
         <v>28</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="D474">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E474" t="s">
         <v>28</v>
@@ -12195,7 +12195,7 @@
         <v>27</v>
       </c>
       <c r="D475">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E475" t="s">
         <v>28</v>
@@ -12212,7 +12212,7 @@
         <v>27</v>
       </c>
       <c r="D476">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E476" t="s">
         <v>28</v>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
       <c r="D477">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E477" t="s">
         <v>28</v>
@@ -12246,7 +12246,7 @@
         <v>27</v>
       </c>
       <c r="D478">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E478" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="D479">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E479" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="D480">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E480" t="s">
         <v>28</v>
@@ -12297,7 +12297,7 @@
         <v>27</v>
       </c>
       <c r="D481">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E481" t="s">
         <v>28</v>
@@ -12314,7 +12314,7 @@
         <v>27</v>
       </c>
       <c r="D482">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E482" t="s">
         <v>28</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="D483">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E483" t="s">
         <v>28</v>
@@ -12348,7 +12348,7 @@
         <v>27</v>
       </c>
       <c r="D484">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E484" t="s">
         <v>28</v>
@@ -12365,7 +12365,7 @@
         <v>27</v>
       </c>
       <c r="D485">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E485" t="s">
         <v>28</v>
@@ -12382,7 +12382,7 @@
         <v>27</v>
       </c>
       <c r="D486">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E486" t="s">
         <v>28</v>
@@ -12399,7 +12399,7 @@
         <v>27</v>
       </c>
       <c r="D487">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E487" t="s">
         <v>28</v>
@@ -12416,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="D488">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E488" t="s">
         <v>28</v>
@@ -12433,7 +12433,7 @@
         <v>27</v>
       </c>
       <c r="D489">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E489" t="s">
         <v>28</v>
@@ -12450,7 +12450,7 @@
         <v>27</v>
       </c>
       <c r="D490">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E490" t="s">
         <v>28</v>
@@ -12467,7 +12467,7 @@
         <v>27</v>
       </c>
       <c r="D491">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E491" t="s">
         <v>28</v>
@@ -12484,7 +12484,7 @@
         <v>27</v>
       </c>
       <c r="D492">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E492" t="s">
         <v>28</v>
@@ -12518,7 +12518,7 @@
         <v>27</v>
       </c>
       <c r="D494">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E494" t="s">
         <v>28</v>
@@ -12535,7 +12535,7 @@
         <v>27</v>
       </c>
       <c r="D495">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E495" t="s">
         <v>28</v>
@@ -12552,7 +12552,7 @@
         <v>27</v>
       </c>
       <c r="D496">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E496" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="D497">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E497" t="s">
         <v>28</v>
@@ -12586,7 +12586,7 @@
         <v>27</v>
       </c>
       <c r="D498">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E498" t="s">
         <v>28</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D499">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E499" t="s">
         <v>28</v>
@@ -12620,7 +12620,7 @@
         <v>27</v>
       </c>
       <c r="D500">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E500" t="s">
         <v>28</v>
@@ -12637,7 +12637,7 @@
         <v>27</v>
       </c>
       <c r="D501">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E501" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="D502">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E502" t="s">
         <v>28</v>
@@ -12671,7 +12671,7 @@
         <v>27</v>
       </c>
       <c r="D503">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E503" t="s">
         <v>28</v>
@@ -12688,7 +12688,7 @@
         <v>27</v>
       </c>
       <c r="D504">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E504" t="s">
         <v>28</v>
@@ -12705,7 +12705,7 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E505" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="D506">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E506" t="s">
         <v>28</v>
@@ -12739,7 +12739,7 @@
         <v>27</v>
       </c>
       <c r="D507">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E507" t="s">
         <v>28</v>
@@ -12756,7 +12756,7 @@
         <v>27</v>
       </c>
       <c r="D508">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E508" t="s">
         <v>28</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="D509">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E509" t="s">
         <v>28</v>
@@ -12790,7 +12790,7 @@
         <v>27</v>
       </c>
       <c r="D510">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E510" t="s">
         <v>28</v>
@@ -12807,7 +12807,7 @@
         <v>27</v>
       </c>
       <c r="D511">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E511" t="s">
         <v>28</v>
@@ -12824,7 +12824,7 @@
         <v>27</v>
       </c>
       <c r="D512">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E512" t="s">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27</v>
       </c>
       <c r="D513">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E513" t="s">
         <v>28</v>
@@ -12858,7 +12858,7 @@
         <v>27</v>
       </c>
       <c r="D514">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E514" t="s">
         <v>28</v>
@@ -12875,7 +12875,7 @@
         <v>27</v>
       </c>
       <c r="D515">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E515" t="s">
         <v>28</v>
@@ -12892,7 +12892,7 @@
         <v>27</v>
       </c>
       <c r="D516">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E516" t="s">
         <v>28</v>
@@ -12909,7 +12909,7 @@
         <v>27</v>
       </c>
       <c r="D517">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E517" t="s">
         <v>28</v>
@@ -12926,7 +12926,7 @@
         <v>27</v>
       </c>
       <c r="D518">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E518" t="s">
         <v>28</v>
@@ -12943,7 +12943,7 @@
         <v>27</v>
       </c>
       <c r="D519">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E519" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="D520">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E520" t="s">
         <v>28</v>
@@ -12977,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="D521">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E521" t="s">
         <v>28</v>
@@ -12994,7 +12994,7 @@
         <v>27</v>
       </c>
       <c r="D522">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E522" t="s">
         <v>28</v>
@@ -13011,7 +13011,7 @@
         <v>27</v>
       </c>
       <c r="D523">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E523" t="s">
         <v>28</v>
@@ -13028,7 +13028,7 @@
         <v>27</v>
       </c>
       <c r="D524">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E524" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="D525">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E525" t="s">
         <v>28</v>
@@ -13062,7 +13062,7 @@
         <v>27</v>
       </c>
       <c r="D526">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E526" t="s">
         <v>28</v>
@@ -13079,7 +13079,7 @@
         <v>27</v>
       </c>
       <c r="D527">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E527" t="s">
         <v>28</v>
@@ -13113,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="D529">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
@@ -13130,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -13147,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="D531">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
@@ -13164,7 +13164,7 @@
         <v>27</v>
       </c>
       <c r="D532">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E532" t="s">
         <v>28</v>
@@ -13181,7 +13181,7 @@
         <v>27</v>
       </c>
       <c r="D533">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E533" t="s">
         <v>28</v>
@@ -13198,7 +13198,7 @@
         <v>27</v>
       </c>
       <c r="D534">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E534" t="s">
         <v>28</v>
@@ -13215,7 +13215,7 @@
         <v>27</v>
       </c>
       <c r="D535">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E535" t="s">
         <v>28</v>
@@ -13232,7 +13232,7 @@
         <v>27</v>
       </c>
       <c r="D536">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E536" t="s">
         <v>28</v>
@@ -13249,7 +13249,7 @@
         <v>27</v>
       </c>
       <c r="D537">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E537" t="s">
         <v>28</v>
@@ -13266,7 +13266,7 @@
         <v>27</v>
       </c>
       <c r="D538">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E538" t="s">
         <v>28</v>
@@ -13283,7 +13283,7 @@
         <v>27</v>
       </c>
       <c r="D539">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E539" t="s">
         <v>28</v>
@@ -13300,7 +13300,7 @@
         <v>27</v>
       </c>
       <c r="D540">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E540" t="s">
         <v>28</v>
@@ -13317,7 +13317,7 @@
         <v>27</v>
       </c>
       <c r="D541">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E541" t="s">
         <v>28</v>
@@ -13334,7 +13334,7 @@
         <v>27</v>
       </c>
       <c r="D542">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E542" t="s">
         <v>28</v>
@@ -13368,7 +13368,7 @@
         <v>27</v>
       </c>
       <c r="D544">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E544" t="s">
         <v>28</v>
@@ -13385,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="D545">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
@@ -13402,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="D546">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
@@ -13419,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="D547">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E547" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="D548">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E548" t="s">
         <v>28</v>
@@ -13453,7 +13453,7 @@
         <v>27</v>
       </c>
       <c r="D549">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E549" t="s">
         <v>28</v>
@@ -13470,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="D550">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E550" t="s">
         <v>28</v>
@@ -13487,7 +13487,7 @@
         <v>27</v>
       </c>
       <c r="D551">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E551" t="s">
         <v>28</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="D552">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -13521,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="D553">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E553" t="s">
         <v>28</v>
@@ -13538,7 +13538,7 @@
         <v>27</v>
       </c>
       <c r="D554">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E554" t="s">
         <v>28</v>
@@ -13555,7 +13555,7 @@
         <v>27</v>
       </c>
       <c r="D555">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E555" t="s">
         <v>28</v>
@@ -13572,7 +13572,7 @@
         <v>27</v>
       </c>
       <c r="D556">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E556" t="s">
         <v>28</v>
@@ -13589,7 +13589,7 @@
         <v>27</v>
       </c>
       <c r="D557">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E557" t="s">
         <v>28</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="D558">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E558" t="s">
         <v>28</v>
@@ -13623,7 +13623,7 @@
         <v>27</v>
       </c>
       <c r="D559">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -13640,7 +13640,7 @@
         <v>27</v>
       </c>
       <c r="D560">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
@@ -13657,7 +13657,7 @@
         <v>27</v>
       </c>
       <c r="D561">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E561" t="s">
         <v>28</v>
@@ -13674,7 +13674,7 @@
         <v>27</v>
       </c>
       <c r="D562">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E562" t="s">
         <v>28</v>
@@ -13691,7 +13691,7 @@
         <v>27</v>
       </c>
       <c r="D563">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E563" t="s">
         <v>28</v>
@@ -13708,7 +13708,7 @@
         <v>27</v>
       </c>
       <c r="D564">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E564" t="s">
         <v>28</v>
@@ -13725,7 +13725,7 @@
         <v>27</v>
       </c>
       <c r="D565">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E565" t="s">
         <v>28</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="D566">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E566" t="s">
         <v>28</v>
@@ -13759,7 +13759,7 @@
         <v>27</v>
       </c>
       <c r="D567">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E567" t="s">
         <v>28</v>
@@ -13776,7 +13776,7 @@
         <v>27</v>
       </c>
       <c r="D568">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E568" t="s">
         <v>28</v>
@@ -13793,7 +13793,7 @@
         <v>27</v>
       </c>
       <c r="D569">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
@@ -13810,7 +13810,7 @@
         <v>27</v>
       </c>
       <c r="D570">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E570" t="s">
         <v>28</v>
@@ -13844,7 +13844,7 @@
         <v>27</v>
       </c>
       <c r="D572">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E572" t="s">
         <v>28</v>
@@ -13861,7 +13861,7 @@
         <v>27</v>
       </c>
       <c r="D573">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E573" t="s">
         <v>28</v>
@@ -13878,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="D574">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E574" t="s">
         <v>28</v>
@@ -13895,7 +13895,7 @@
         <v>27</v>
       </c>
       <c r="D575">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E575" t="s">
         <v>28</v>
@@ -13912,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="D576">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E576" t="s">
         <v>28</v>
@@ -13929,7 +13929,7 @@
         <v>27</v>
       </c>
       <c r="D577">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E577" t="s">
         <v>28</v>
@@ -13946,7 +13946,7 @@
         <v>27</v>
       </c>
       <c r="D578">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E578" t="s">
         <v>28</v>
@@ -13963,7 +13963,7 @@
         <v>27</v>
       </c>
       <c r="D579">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E579" t="s">
         <v>28</v>
@@ -13997,7 +13997,7 @@
         <v>27</v>
       </c>
       <c r="D581">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E581" t="s">
         <v>28</v>
@@ -14014,7 +14014,7 @@
         <v>27</v>
       </c>
       <c r="D582">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E582" t="s">
         <v>28</v>
@@ -14031,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="D583">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E583" t="s">
         <v>28</v>
@@ -14048,7 +14048,7 @@
         <v>27</v>
       </c>
       <c r="D584">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E584" t="s">
         <v>28</v>
@@ -14065,7 +14065,7 @@
         <v>27</v>
       </c>
       <c r="D585">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E585" t="s">
         <v>28</v>
@@ -14082,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="D586">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E586" t="s">
         <v>28</v>
@@ -14099,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="D587">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E587" t="s">
         <v>28</v>
@@ -14116,7 +14116,7 @@
         <v>27</v>
       </c>
       <c r="D588">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E588" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="D589">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
@@ -14150,7 +14150,7 @@
         <v>27</v>
       </c>
       <c r="D590">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
@@ -14167,7 +14167,7 @@
         <v>27</v>
       </c>
       <c r="D591">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E591" t="s">
         <v>28</v>
@@ -14184,7 +14184,7 @@
         <v>27</v>
       </c>
       <c r="D592">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E592" t="s">
         <v>28</v>
@@ -14201,7 +14201,7 @@
         <v>27</v>
       </c>
       <c r="D593">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E593" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="D594">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E594" t="s">
         <v>28</v>
@@ -14235,7 +14235,7 @@
         <v>27</v>
       </c>
       <c r="D595">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E595" t="s">
         <v>28</v>
@@ -14252,7 +14252,7 @@
         <v>27</v>
       </c>
       <c r="D596">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
@@ -14269,7 +14269,7 @@
         <v>27</v>
       </c>
       <c r="D597">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
@@ -14286,7 +14286,7 @@
         <v>27</v>
       </c>
       <c r="D598">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
@@ -14303,7 +14303,7 @@
         <v>27</v>
       </c>
       <c r="D599">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="D600">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
@@ -14337,7 +14337,7 @@
         <v>27</v>
       </c>
       <c r="D601">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
@@ -14354,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="D602">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
@@ -14371,7 +14371,7 @@
         <v>27</v>
       </c>
       <c r="D603">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
@@ -14388,7 +14388,7 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
@@ -14405,7 +14405,7 @@
         <v>27</v>
       </c>
       <c r="D605">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E605" t="s">
         <v>28</v>
@@ -14439,7 +14439,7 @@
         <v>27</v>
       </c>
       <c r="D607">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E607" t="s">
         <v>28</v>
@@ -14456,7 +14456,7 @@
         <v>27</v>
       </c>
       <c r="D608">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
@@ -14473,7 +14473,7 @@
         <v>27</v>
       </c>
       <c r="D609">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E609" t="s">
         <v>28</v>
@@ -14490,7 +14490,7 @@
         <v>27</v>
       </c>
       <c r="D610">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E610" t="s">
         <v>28</v>
@@ -14507,7 +14507,7 @@
         <v>27</v>
       </c>
       <c r="D611">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E611" t="s">
         <v>28</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="D612">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E612" t="s">
         <v>28</v>
@@ -14541,7 +14541,7 @@
         <v>27</v>
       </c>
       <c r="D613">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E613" t="s">
         <v>28</v>
@@ -14558,7 +14558,7 @@
         <v>27</v>
       </c>
       <c r="D614">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E614" t="s">
         <v>28</v>
@@ -14575,7 +14575,7 @@
         <v>27</v>
       </c>
       <c r="D615">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E615" t="s">
         <v>28</v>
@@ -14592,7 +14592,7 @@
         <v>27</v>
       </c>
       <c r="D616">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E616" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="D617">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E617" t="s">
         <v>28</v>
@@ -14643,7 +14643,7 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E619" t="s">
         <v>28</v>
@@ -14660,7 +14660,7 @@
         <v>27</v>
       </c>
       <c r="D620">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E620" t="s">
         <v>28</v>
@@ -14677,7 +14677,7 @@
         <v>27</v>
       </c>
       <c r="D621">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E621" t="s">
         <v>28</v>
@@ -14694,7 +14694,7 @@
         <v>27</v>
       </c>
       <c r="D622">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E622" t="s">
         <v>28</v>
@@ -14711,7 +14711,7 @@
         <v>27</v>
       </c>
       <c r="D623">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E623" t="s">
         <v>28</v>
@@ -14728,7 +14728,7 @@
         <v>27</v>
       </c>
       <c r="D624">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E624" t="s">
         <v>28</v>
@@ -14745,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="D625">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E625" t="s">
         <v>28</v>
@@ -14762,7 +14762,7 @@
         <v>27</v>
       </c>
       <c r="D626">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E626" t="s">
         <v>28</v>
@@ -14779,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="D627">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E627" t="s">
         <v>28</v>
@@ -14796,7 +14796,7 @@
         <v>27</v>
       </c>
       <c r="D628">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E628" t="s">
         <v>28</v>
@@ -14813,7 +14813,7 @@
         <v>27</v>
       </c>
       <c r="D629">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E629" t="s">
         <v>28</v>
@@ -14830,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="D630">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E630" t="s">
         <v>28</v>
@@ -14864,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D632">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E632" t="s">
         <v>28</v>
@@ -14881,7 +14881,7 @@
         <v>27</v>
       </c>
       <c r="D633">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E633" t="s">
         <v>28</v>
@@ -14932,7 +14932,7 @@
         <v>27</v>
       </c>
       <c r="D636">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E636" t="s">
         <v>28</v>
@@ -14983,7 +14983,7 @@
         <v>27</v>
       </c>
       <c r="D639">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E639" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E640" t="s">
         <v>28</v>
@@ -15017,7 +15017,7 @@
         <v>27</v>
       </c>
       <c r="D641">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E641" t="s">
         <v>28</v>
@@ -15034,7 +15034,7 @@
         <v>27</v>
       </c>
       <c r="D642">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E642" t="s">
         <v>28</v>
@@ -15051,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="D643">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E643" t="s">
         <v>28</v>
@@ -15068,7 +15068,7 @@
         <v>27</v>
       </c>
       <c r="D644">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E644" t="s">
         <v>28</v>
@@ -15085,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="D645">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E645" t="s">
         <v>28</v>
@@ -15102,7 +15102,7 @@
         <v>27</v>
       </c>
       <c r="D646">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E646" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>27</v>
       </c>
       <c r="D647">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E647" t="s">
         <v>28</v>
@@ -15136,7 +15136,7 @@
         <v>27</v>
       </c>
       <c r="D648">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E648" t="s">
         <v>28</v>
@@ -15153,7 +15153,7 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E649" t="s">
         <v>28</v>
@@ -15170,7 +15170,7 @@
         <v>27</v>
       </c>
       <c r="D650">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E650" t="s">
         <v>28</v>
@@ -15187,7 +15187,7 @@
         <v>27</v>
       </c>
       <c r="D651">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E651" t="s">
         <v>28</v>
@@ -15204,7 +15204,7 @@
         <v>27</v>
       </c>
       <c r="D652">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E652" t="s">
         <v>28</v>
@@ -15221,7 +15221,7 @@
         <v>27</v>
       </c>
       <c r="D653">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E653" t="s">
         <v>28</v>
@@ -15238,7 +15238,7 @@
         <v>27</v>
       </c>
       <c r="D654">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E654" t="s">
         <v>28</v>
@@ -15255,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="D655">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E655" t="s">
         <v>28</v>
@@ -15272,7 +15272,7 @@
         <v>27</v>
       </c>
       <c r="D656">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
@@ -15289,7 +15289,7 @@
         <v>27</v>
       </c>
       <c r="D657">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E657" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
@@ -15323,7 +15323,7 @@
         <v>27</v>
       </c>
       <c r="D659">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E659" t="s">
         <v>28</v>
@@ -15340,7 +15340,7 @@
         <v>27</v>
       </c>
       <c r="D660">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E660" t="s">
         <v>28</v>
@@ -15357,7 +15357,7 @@
         <v>27</v>
       </c>
       <c r="D661">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E661" t="s">
         <v>28</v>
@@ -15374,7 +15374,7 @@
         <v>27</v>
       </c>
       <c r="D662">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E662" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="D663">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E663" t="s">
         <v>28</v>
@@ -15408,7 +15408,7 @@
         <v>27</v>
       </c>
       <c r="D664">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E664" t="s">
         <v>28</v>
@@ -15425,7 +15425,7 @@
         <v>27</v>
       </c>
       <c r="D665">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E665" t="s">
         <v>28</v>
@@ -15442,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="D666">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E666" t="s">
         <v>28</v>
@@ -15459,7 +15459,7 @@
         <v>27</v>
       </c>
       <c r="D667">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E667" t="s">
         <v>28</v>
@@ -15476,7 +15476,7 @@
         <v>27</v>
       </c>
       <c r="D668">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E668" t="s">
         <v>28</v>
@@ -15493,7 +15493,7 @@
         <v>27</v>
       </c>
       <c r="D669">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E669" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>27</v>
       </c>
       <c r="D670">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E670" t="s">
         <v>28</v>
@@ -15527,7 +15527,7 @@
         <v>27</v>
       </c>
       <c r="D671">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E671" t="s">
         <v>28</v>
@@ -15544,7 +15544,7 @@
         <v>27</v>
       </c>
       <c r="D672">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E672" t="s">
         <v>28</v>
@@ -15561,7 +15561,7 @@
         <v>27</v>
       </c>
       <c r="D673">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E673" t="s">
         <v>28</v>
@@ -15578,7 +15578,7 @@
         <v>27</v>
       </c>
       <c r="D674">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E674" t="s">
         <v>28</v>
@@ -15595,7 +15595,7 @@
         <v>27</v>
       </c>
       <c r="D675">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E675" t="s">
         <v>28</v>
@@ -15612,7 +15612,7 @@
         <v>27</v>
       </c>
       <c r="D676">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E676" t="s">
         <v>28</v>
@@ -15629,7 +15629,7 @@
         <v>27</v>
       </c>
       <c r="D677">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E677" t="s">
         <v>28</v>
@@ -15663,7 +15663,7 @@
         <v>27</v>
       </c>
       <c r="D679">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E679" t="s">
         <v>28</v>
@@ -15680,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="D680">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E680" t="s">
         <v>28</v>
@@ -15697,7 +15697,7 @@
         <v>27</v>
       </c>
       <c r="D681">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E681" t="s">
         <v>28</v>
@@ -15714,7 +15714,7 @@
         <v>27</v>
       </c>
       <c r="D682">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E682" t="s">
         <v>28</v>
@@ -15731,7 +15731,7 @@
         <v>27</v>
       </c>
       <c r="D683">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E683" t="s">
         <v>28</v>
@@ -15748,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="D684">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E684" t="s">
         <v>28</v>
@@ -15765,7 +15765,7 @@
         <v>27</v>
       </c>
       <c r="D685">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E685" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="D686">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E686" t="s">
         <v>28</v>
@@ -15799,7 +15799,7 @@
         <v>27</v>
       </c>
       <c r="D687">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E687" t="s">
         <v>28</v>
@@ -15816,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="D688">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E688" t="s">
         <v>28</v>
@@ -15833,7 +15833,7 @@
         <v>27</v>
       </c>
       <c r="D689">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E689" t="s">
         <v>28</v>
@@ -15850,7 +15850,7 @@
         <v>27</v>
       </c>
       <c r="D690">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E690" t="s">
         <v>28</v>
@@ -15867,7 +15867,7 @@
         <v>27</v>
       </c>
       <c r="D691">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E691" t="s">
         <v>28</v>
@@ -15884,7 +15884,7 @@
         <v>27</v>
       </c>
       <c r="D692">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E692" t="s">
         <v>28</v>
@@ -15901,7 +15901,7 @@
         <v>27</v>
       </c>
       <c r="D693">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E693" t="s">
         <v>28</v>
@@ -15918,7 +15918,7 @@
         <v>27</v>
       </c>
       <c r="D694">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E694" t="s">
         <v>28</v>
@@ -15935,7 +15935,7 @@
         <v>27</v>
       </c>
       <c r="D695">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E695" t="s">
         <v>28</v>
@@ -15952,7 +15952,7 @@
         <v>27</v>
       </c>
       <c r="D696">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E696" t="s">
         <v>28</v>
@@ -15969,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="D697">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E697" t="s">
         <v>28</v>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
       <c r="D698">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E698" t="s">
         <v>28</v>
@@ -16003,7 +16003,7 @@
         <v>27</v>
       </c>
       <c r="D699">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E699" t="s">
         <v>28</v>
@@ -16020,7 +16020,7 @@
         <v>27</v>
       </c>
       <c r="D700">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E700" t="s">
         <v>28</v>
@@ -16037,7 +16037,7 @@
         <v>27</v>
       </c>
       <c r="D701">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E701" t="s">
         <v>28</v>
@@ -16054,7 +16054,7 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E702" t="s">
         <v>28</v>
@@ -16071,7 +16071,7 @@
         <v>27</v>
       </c>
       <c r="D703">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E703" t="s">
         <v>28</v>
@@ -16088,7 +16088,7 @@
         <v>27</v>
       </c>
       <c r="D704">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E704" t="s">
         <v>28</v>
@@ -16105,7 +16105,7 @@
         <v>27</v>
       </c>
       <c r="D705">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E705" t="s">
         <v>28</v>
@@ -16122,7 +16122,7 @@
         <v>27</v>
       </c>
       <c r="D706">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E706" t="s">
         <v>28</v>
@@ -16139,7 +16139,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E707" t="s">
         <v>28</v>
@@ -16156,7 +16156,7 @@
         <v>27</v>
       </c>
       <c r="D708">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E708" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="D709">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E709" t="s">
         <v>28</v>
@@ -16190,7 +16190,7 @@
         <v>27</v>
       </c>
       <c r="D710">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E710" t="s">
         <v>28</v>
@@ -16207,7 +16207,7 @@
         <v>27</v>
       </c>
       <c r="D711">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E711" t="s">
         <v>28</v>
@@ -16224,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="D712">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E712" t="s">
         <v>28</v>
@@ -16241,7 +16241,7 @@
         <v>27</v>
       </c>
       <c r="D713">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E713" t="s">
         <v>28</v>
@@ -16258,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="D714">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E714" t="s">
         <v>28</v>
@@ -16275,7 +16275,7 @@
         <v>27</v>
       </c>
       <c r="D715">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E715" t="s">
         <v>28</v>
@@ -16309,7 +16309,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E717" t="s">
         <v>28</v>
@@ -16326,7 +16326,7 @@
         <v>27</v>
       </c>
       <c r="D718">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E718" t="s">
         <v>28</v>
@@ -16343,7 +16343,7 @@
         <v>27</v>
       </c>
       <c r="D719">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E719" t="s">
         <v>28</v>
@@ -16360,7 +16360,7 @@
         <v>27</v>
       </c>
       <c r="D720">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E720" t="s">
         <v>28</v>
@@ -16377,7 +16377,7 @@
         <v>27</v>
       </c>
       <c r="D721">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E721" t="s">
         <v>28</v>
@@ -16394,7 +16394,7 @@
         <v>27</v>
       </c>
       <c r="D722">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E722" t="s">
         <v>28</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="D723">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E723" t="s">
         <v>28</v>
@@ -16428,7 +16428,7 @@
         <v>27</v>
       </c>
       <c r="D724">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E724" t="s">
         <v>28</v>
@@ -16445,7 +16445,7 @@
         <v>27</v>
       </c>
       <c r="D725">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E725" t="s">
         <v>28</v>
@@ -16462,7 +16462,7 @@
         <v>27</v>
       </c>
       <c r="D726">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E726" t="s">
         <v>28</v>
@@ -16479,7 +16479,7 @@
         <v>27</v>
       </c>
       <c r="D727">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E727" t="s">
         <v>28</v>
@@ -16496,7 +16496,7 @@
         <v>27</v>
       </c>
       <c r="D728">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E728" t="s">
         <v>28</v>
@@ -16513,7 +16513,7 @@
         <v>27</v>
       </c>
       <c r="D729">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E729" t="s">
         <v>28</v>
@@ -16530,7 +16530,7 @@
         <v>27</v>
       </c>
       <c r="D730">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E730" t="s">
         <v>28</v>
@@ -16547,7 +16547,7 @@
         <v>27</v>
       </c>
       <c r="D731">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E731" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="D732">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E732" t="s">
         <v>28</v>
@@ -16581,7 +16581,7 @@
         <v>27</v>
       </c>
       <c r="D733">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E733" t="s">
         <v>28</v>
@@ -16598,7 +16598,7 @@
         <v>27</v>
       </c>
       <c r="D734">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E734" t="s">
         <v>28</v>
@@ -16615,7 +16615,7 @@
         <v>27</v>
       </c>
       <c r="D735">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E735" t="s">
         <v>28</v>
@@ -16632,7 +16632,7 @@
         <v>27</v>
       </c>
       <c r="D736">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E736" t="s">
         <v>28</v>
@@ -16649,7 +16649,7 @@
         <v>27</v>
       </c>
       <c r="D737">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E737" t="s">
         <v>28</v>
@@ -16666,7 +16666,7 @@
         <v>27</v>
       </c>
       <c r="D738">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E738" t="s">
         <v>28</v>
@@ -16683,7 +16683,7 @@
         <v>27</v>
       </c>
       <c r="D739">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E739" t="s">
         <v>28</v>
@@ -16700,7 +16700,7 @@
         <v>27</v>
       </c>
       <c r="D740">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E740" t="s">
         <v>28</v>
@@ -16717,7 +16717,7 @@
         <v>27</v>
       </c>
       <c r="D741">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E741" t="s">
         <v>28</v>
@@ -16734,7 +16734,7 @@
         <v>27</v>
       </c>
       <c r="D742">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E742" t="s">
         <v>28</v>
@@ -16751,7 +16751,7 @@
         <v>27</v>
       </c>
       <c r="D743">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E743" t="s">
         <v>28</v>
@@ -16768,7 +16768,7 @@
         <v>27</v>
       </c>
       <c r="D744">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E744" t="s">
         <v>28</v>
@@ -16802,7 +16802,7 @@
         <v>27</v>
       </c>
       <c r="D746">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E746" t="s">
         <v>28</v>
@@ -16819,7 +16819,7 @@
         <v>27</v>
       </c>
       <c r="D747">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E747" t="s">
         <v>28</v>
@@ -16836,7 +16836,7 @@
         <v>27</v>
       </c>
       <c r="D748">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E748" t="s">
         <v>28</v>
@@ -16853,7 +16853,7 @@
         <v>27</v>
       </c>
       <c r="D749">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E749" t="s">
         <v>28</v>
@@ -16870,7 +16870,7 @@
         <v>27</v>
       </c>
       <c r="D750">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E750" t="s">
         <v>28</v>
@@ -16887,7 +16887,7 @@
         <v>27</v>
       </c>
       <c r="D751">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E751" t="s">
         <v>28</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="D752">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E752" t="s">
         <v>28</v>
@@ -16921,7 +16921,7 @@
         <v>27</v>
       </c>
       <c r="D753">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E753" t="s">
         <v>28</v>
@@ -16938,7 +16938,7 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E754" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="D755">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E755" t="s">
         <v>28</v>
@@ -16972,7 +16972,7 @@
         <v>27</v>
       </c>
       <c r="D756">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E756" t="s">
         <v>28</v>
@@ -16989,7 +16989,7 @@
         <v>27</v>
       </c>
       <c r="D757">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E757" t="s">
         <v>28</v>
@@ -17006,7 +17006,7 @@
         <v>27</v>
       </c>
       <c r="D758">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E758" t="s">
         <v>28</v>
@@ -17023,7 +17023,7 @@
         <v>27</v>
       </c>
       <c r="D759">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E759" t="s">
         <v>28</v>
@@ -17040,7 +17040,7 @@
         <v>27</v>
       </c>
       <c r="D760">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E760" t="s">
         <v>28</v>
@@ -17057,7 +17057,7 @@
         <v>27</v>
       </c>
       <c r="D761">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E761" t="s">
         <v>28</v>
@@ -17074,7 +17074,7 @@
         <v>27</v>
       </c>
       <c r="D762">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E762" t="s">
         <v>28</v>
@@ -17091,7 +17091,7 @@
         <v>27</v>
       </c>
       <c r="D763">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E763" t="s">
         <v>28</v>
@@ -17108,7 +17108,7 @@
         <v>27</v>
       </c>
       <c r="D764">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E764" t="s">
         <v>28</v>
@@ -17125,7 +17125,7 @@
         <v>27</v>
       </c>
       <c r="D765">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E765" t="s">
         <v>28</v>
@@ -17142,7 +17142,7 @@
         <v>27</v>
       </c>
       <c r="D766">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E766" t="s">
         <v>28</v>
@@ -17159,7 +17159,7 @@
         <v>27</v>
       </c>
       <c r="D767">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E767" t="s">
         <v>28</v>
@@ -17176,7 +17176,7 @@
         <v>27</v>
       </c>
       <c r="D768">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E768" t="s">
         <v>28</v>
@@ -17193,7 +17193,7 @@
         <v>27</v>
       </c>
       <c r="D769">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E769" t="s">
         <v>28</v>
@@ -17210,7 +17210,7 @@
         <v>27</v>
       </c>
       <c r="D770">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E770" t="s">
         <v>28</v>
@@ -17227,7 +17227,7 @@
         <v>27</v>
       </c>
       <c r="D771">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E771" t="s">
         <v>28</v>
@@ -17244,7 +17244,7 @@
         <v>27</v>
       </c>
       <c r="D772">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E772" t="s">
         <v>28</v>
@@ -17261,7 +17261,7 @@
         <v>27</v>
       </c>
       <c r="D773">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E773" t="s">
         <v>28</v>
@@ -17278,7 +17278,7 @@
         <v>27</v>
       </c>
       <c r="D774">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E774" t="s">
         <v>28</v>
@@ -17295,7 +17295,7 @@
         <v>27</v>
       </c>
       <c r="D775">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E775" t="s">
         <v>28</v>
@@ -17312,7 +17312,7 @@
         <v>27</v>
       </c>
       <c r="D776">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E776" t="s">
         <v>28</v>
@@ -17329,7 +17329,7 @@
         <v>27</v>
       </c>
       <c r="D777">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E777" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="D778">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E778" t="s">
         <v>28</v>
@@ -17363,7 +17363,7 @@
         <v>27</v>
       </c>
       <c r="D779">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E779" t="s">
         <v>28</v>
@@ -17380,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="D780">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E780" t="s">
         <v>28</v>
@@ -17397,7 +17397,7 @@
         <v>27</v>
       </c>
       <c r="D781">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E781" t="s">
         <v>28</v>
@@ -17414,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="D782">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E782" t="s">
         <v>28</v>
@@ -17431,7 +17431,7 @@
         <v>27</v>
       </c>
       <c r="D783">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E783" t="s">
         <v>28</v>
@@ -17448,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D784">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E784" t="s">
         <v>28</v>
@@ -17465,7 +17465,7 @@
         <v>27</v>
       </c>
       <c r="D785">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E785" t="s">
         <v>28</v>
@@ -17482,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="D786">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E786" t="s">
         <v>28</v>
@@ -17499,7 +17499,7 @@
         <v>27</v>
       </c>
       <c r="D787">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E787" t="s">
         <v>28</v>
@@ -17516,7 +17516,7 @@
         <v>27</v>
       </c>
       <c r="D788">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E788" t="s">
         <v>28</v>
@@ -17533,7 +17533,7 @@
         <v>27</v>
       </c>
       <c r="D789">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E789" t="s">
         <v>28</v>
@@ -17550,7 +17550,7 @@
         <v>27</v>
       </c>
       <c r="D790">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E790" t="s">
         <v>28</v>
@@ -17567,7 +17567,7 @@
         <v>27</v>
       </c>
       <c r="D791">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E791" t="s">
         <v>28</v>
@@ -17584,7 +17584,7 @@
         <v>27</v>
       </c>
       <c r="D792">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E792" t="s">
         <v>28</v>
@@ -17601,7 +17601,7 @@
         <v>27</v>
       </c>
       <c r="D793">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E793" t="s">
         <v>28</v>
@@ -17618,7 +17618,7 @@
         <v>27</v>
       </c>
       <c r="D794">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E794" t="s">
         <v>28</v>
@@ -17635,7 +17635,7 @@
         <v>27</v>
       </c>
       <c r="D795">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E795" t="s">
         <v>28</v>
@@ -17669,7 +17669,7 @@
         <v>27</v>
       </c>
       <c r="D797">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E797" t="s">
         <v>28</v>
@@ -17686,7 +17686,7 @@
         <v>27</v>
       </c>
       <c r="D798">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E798" t="s">
         <v>28</v>
@@ -17703,7 +17703,7 @@
         <v>27</v>
       </c>
       <c r="D799">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E799" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="D801">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E801" t="s">
         <v>28</v>
@@ -17754,7 +17754,7 @@
         <v>27</v>
       </c>
       <c r="D802">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E802" t="s">
         <v>28</v>
@@ -17771,7 +17771,7 @@
         <v>27</v>
       </c>
       <c r="D803">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E803" t="s">
         <v>28</v>
@@ -17805,7 +17805,7 @@
         <v>27</v>
       </c>
       <c r="D805">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E805" t="s">
         <v>28</v>
@@ -17822,7 +17822,7 @@
         <v>27</v>
       </c>
       <c r="D806">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E806" t="s">
         <v>28</v>
@@ -17839,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="D807">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E807" t="s">
         <v>28</v>
@@ -17856,7 +17856,7 @@
         <v>27</v>
       </c>
       <c r="D808">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E808" t="s">
         <v>28</v>
@@ -17873,7 +17873,7 @@
         <v>27</v>
       </c>
       <c r="D809">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E809" t="s">
         <v>28</v>
@@ -17890,7 +17890,7 @@
         <v>27</v>
       </c>
       <c r="D810">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E810" t="s">
         <v>28</v>
@@ -17907,7 +17907,7 @@
         <v>27</v>
       </c>
       <c r="D811">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E811" t="s">
         <v>28</v>
@@ -17924,7 +17924,7 @@
         <v>27</v>
       </c>
       <c r="D812">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E812" t="s">
         <v>28</v>
@@ -17941,7 +17941,7 @@
         <v>27</v>
       </c>
       <c r="D813">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E813" t="s">
         <v>28</v>
@@ -17958,7 +17958,7 @@
         <v>27</v>
       </c>
       <c r="D814">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E814" t="s">
         <v>28</v>
@@ -17975,7 +17975,7 @@
         <v>27</v>
       </c>
       <c r="D815">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E815" t="s">
         <v>28</v>
@@ -17992,7 +17992,7 @@
         <v>27</v>
       </c>
       <c r="D816">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E816" t="s">
         <v>28</v>
@@ -18009,7 +18009,7 @@
         <v>27</v>
       </c>
       <c r="D817">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E817" t="s">
         <v>28</v>
@@ -18026,7 +18026,7 @@
         <v>27</v>
       </c>
       <c r="D818">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E818" t="s">
         <v>28</v>
@@ -18043,7 +18043,7 @@
         <v>27</v>
       </c>
       <c r="D819">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E819" t="s">
         <v>28</v>
@@ -18060,7 +18060,7 @@
         <v>27</v>
       </c>
       <c r="D820">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E820" t="s">
         <v>28</v>
@@ -18077,7 +18077,7 @@
         <v>27</v>
       </c>
       <c r="D821">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E821" t="s">
         <v>28</v>
@@ -18094,7 +18094,7 @@
         <v>27</v>
       </c>
       <c r="D822">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E822" t="s">
         <v>28</v>
@@ -18111,7 +18111,7 @@
         <v>27</v>
       </c>
       <c r="D823">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E823" t="s">
         <v>28</v>
@@ -18128,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="D824">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E824" t="s">
         <v>28</v>
@@ -18145,7 +18145,7 @@
         <v>27</v>
       </c>
       <c r="D825">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E825" t="s">
         <v>28</v>
@@ -18162,7 +18162,7 @@
         <v>27</v>
       </c>
       <c r="D826">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E826" t="s">
         <v>28</v>
@@ -18179,7 +18179,7 @@
         <v>27</v>
       </c>
       <c r="D827">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E827" t="s">
         <v>28</v>
@@ -18196,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="D828">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E828" t="s">
         <v>28</v>
@@ -18213,7 +18213,7 @@
         <v>27</v>
       </c>
       <c r="D829">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E829" t="s">
         <v>28</v>
@@ -18230,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="D830">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E830" t="s">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E831" t="s">
         <v>28</v>
@@ -18264,7 +18264,7 @@
         <v>27</v>
       </c>
       <c r="D832">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E832" t="s">
         <v>28</v>
@@ -18281,7 +18281,7 @@
         <v>27</v>
       </c>
       <c r="D833">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E833" t="s">
         <v>28</v>
@@ -18298,7 +18298,7 @@
         <v>27</v>
       </c>
       <c r="D834">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E834" t="s">
         <v>28</v>
@@ -18315,7 +18315,7 @@
         <v>27</v>
       </c>
       <c r="D835">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E835" t="s">
         <v>28</v>
@@ -18349,7 +18349,7 @@
         <v>27</v>
       </c>
       <c r="D837">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E837" t="s">
         <v>28</v>
@@ -18366,7 +18366,7 @@
         <v>27</v>
       </c>
       <c r="D838">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E838" t="s">
         <v>28</v>
@@ -18383,7 +18383,7 @@
         <v>27</v>
       </c>
       <c r="D839">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E839" t="s">
         <v>28</v>
@@ -18400,7 +18400,7 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E840" t="s">
         <v>28</v>
@@ -18417,7 +18417,7 @@
         <v>27</v>
       </c>
       <c r="D841">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E841" t="s">
         <v>28</v>
@@ -18434,7 +18434,7 @@
         <v>27</v>
       </c>
       <c r="D842">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E842" t="s">
         <v>28</v>
@@ -18451,7 +18451,7 @@
         <v>27</v>
       </c>
       <c r="D843">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E843" t="s">
         <v>28</v>
@@ -18468,7 +18468,7 @@
         <v>27</v>
       </c>
       <c r="D844">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E844" t="s">
         <v>28</v>
@@ -18485,7 +18485,7 @@
         <v>27</v>
       </c>
       <c r="D845">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E845" t="s">
         <v>28</v>
@@ -18502,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="D846">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E846" t="s">
         <v>28</v>
@@ -18519,7 +18519,7 @@
         <v>27</v>
       </c>
       <c r="D847">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E847" t="s">
         <v>28</v>
@@ -18536,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="D848">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E848" t="s">
         <v>28</v>
@@ -18553,7 +18553,7 @@
         <v>27</v>
       </c>
       <c r="D849">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E849" t="s">
         <v>28</v>
@@ -18570,7 +18570,7 @@
         <v>27</v>
       </c>
       <c r="D850">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E850" t="s">
         <v>28</v>
@@ -18587,7 +18587,7 @@
         <v>27</v>
       </c>
       <c r="D851">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E851" t="s">
         <v>28</v>
@@ -18604,7 +18604,7 @@
         <v>27</v>
       </c>
       <c r="D852">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E852" t="s">
         <v>28</v>
@@ -18621,7 +18621,7 @@
         <v>27</v>
       </c>
       <c r="D853">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E853" t="s">
         <v>28</v>
@@ -18638,7 +18638,7 @@
         <v>27</v>
       </c>
       <c r="D854">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E854" t="s">
         <v>28</v>
@@ -18655,7 +18655,7 @@
         <v>27</v>
       </c>
       <c r="D855">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E855" t="s">
         <v>28</v>
@@ -18672,7 +18672,7 @@
         <v>27</v>
       </c>
       <c r="D856">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E856" t="s">
         <v>28</v>
@@ -18689,7 +18689,7 @@
         <v>27</v>
       </c>
       <c r="D857">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E857" t="s">
         <v>28</v>
@@ -18723,7 +18723,7 @@
         <v>27</v>
       </c>
       <c r="D859">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E859" t="s">
         <v>28</v>
@@ -18740,7 +18740,7 @@
         <v>27</v>
       </c>
       <c r="D860">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E860" t="s">
         <v>28</v>
@@ -18757,7 +18757,7 @@
         <v>27</v>
       </c>
       <c r="D861">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E861" t="s">
         <v>28</v>
@@ -18774,7 +18774,7 @@
         <v>27</v>
       </c>
       <c r="D862">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E862" t="s">
         <v>28</v>
@@ -18791,7 +18791,7 @@
         <v>27</v>
       </c>
       <c r="D863">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E863" t="s">
         <v>28</v>
@@ -18808,7 +18808,7 @@
         <v>27</v>
       </c>
       <c r="D864">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E864" t="s">
         <v>28</v>
@@ -18825,7 +18825,7 @@
         <v>27</v>
       </c>
       <c r="D865">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E865" t="s">
         <v>28</v>
@@ -18842,7 +18842,7 @@
         <v>27</v>
       </c>
       <c r="D866">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E866" t="s">
         <v>28</v>
@@ -18859,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="D867">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E867" t="s">
         <v>28</v>
@@ -18876,7 +18876,7 @@
         <v>27</v>
       </c>
       <c r="D868">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E868" t="s">
         <v>28</v>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
       <c r="D869">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E869" t="s">
         <v>28</v>
@@ -18910,7 +18910,7 @@
         <v>27</v>
       </c>
       <c r="D870">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E870" t="s">
         <v>28</v>
@@ -18927,7 +18927,7 @@
         <v>27</v>
       </c>
       <c r="D871">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E871" t="s">
         <v>28</v>
@@ -18944,7 +18944,7 @@
         <v>27</v>
       </c>
       <c r="D872">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E872" t="s">
         <v>28</v>
@@ -18961,7 +18961,7 @@
         <v>27</v>
       </c>
       <c r="D873">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E873" t="s">
         <v>28</v>
@@ -18995,7 +18995,7 @@
         <v>27</v>
       </c>
       <c r="D875">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E875" t="s">
         <v>28</v>
@@ -19012,7 +19012,7 @@
         <v>27</v>
       </c>
       <c r="D876">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E876" t="s">
         <v>28</v>
@@ -19029,7 +19029,7 @@
         <v>27</v>
       </c>
       <c r="D877">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E877" t="s">
         <v>28</v>
@@ -19046,7 +19046,7 @@
         <v>27</v>
       </c>
       <c r="D878">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E878" t="s">
         <v>28</v>
@@ -19063,7 +19063,7 @@
         <v>27</v>
       </c>
       <c r="D879">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E879" t="s">
         <v>28</v>
@@ -19080,7 +19080,7 @@
         <v>27</v>
       </c>
       <c r="D880">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E880" t="s">
         <v>28</v>
@@ -19097,7 +19097,7 @@
         <v>27</v>
       </c>
       <c r="D881">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E881" t="s">
         <v>28</v>
@@ -19114,7 +19114,7 @@
         <v>27</v>
       </c>
       <c r="D882">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E882" t="s">
         <v>28</v>
@@ -19131,7 +19131,7 @@
         <v>27</v>
       </c>
       <c r="D883">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E883" t="s">
         <v>28</v>
@@ -19148,7 +19148,7 @@
         <v>27</v>
       </c>
       <c r="D884">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E884" t="s">
         <v>28</v>
@@ -19165,7 +19165,7 @@
         <v>27</v>
       </c>
       <c r="D885">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E885" t="s">
         <v>28</v>
@@ -19182,7 +19182,7 @@
         <v>27</v>
       </c>
       <c r="D886">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E886" t="s">
         <v>28</v>
@@ -19199,7 +19199,7 @@
         <v>27</v>
       </c>
       <c r="D887">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E887" t="s">
         <v>28</v>
@@ -19216,7 +19216,7 @@
         <v>27</v>
       </c>
       <c r="D888">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E888" t="s">
         <v>28</v>
@@ -19233,7 +19233,7 @@
         <v>27</v>
       </c>
       <c r="D889">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E889" t="s">
         <v>28</v>
@@ -19250,7 +19250,7 @@
         <v>27</v>
       </c>
       <c r="D890">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E890" t="s">
         <v>28</v>
@@ -19267,7 +19267,7 @@
         <v>27</v>
       </c>
       <c r="D891">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E891" t="s">
         <v>28</v>
@@ -19301,7 +19301,7 @@
         <v>27</v>
       </c>
       <c r="D893">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E893" t="s">
         <v>28</v>
@@ -19318,7 +19318,7 @@
         <v>27</v>
       </c>
       <c r="D894">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E894" t="s">
         <v>28</v>
@@ -19335,7 +19335,7 @@
         <v>27</v>
       </c>
       <c r="D895">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E895" t="s">
         <v>28</v>
@@ -19352,7 +19352,7 @@
         <v>27</v>
       </c>
       <c r="D896">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E896" t="s">
         <v>28</v>
@@ -19369,7 +19369,7 @@
         <v>27</v>
       </c>
       <c r="D897">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E897" t="s">
         <v>28</v>
@@ -19386,7 +19386,7 @@
         <v>27</v>
       </c>
       <c r="D898">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E898" t="s">
         <v>28</v>
@@ -19403,7 +19403,7 @@
         <v>27</v>
       </c>
       <c r="D899">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E899" t="s">
         <v>28</v>
@@ -19420,7 +19420,7 @@
         <v>27</v>
       </c>
       <c r="D900">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E900" t="s">
         <v>28</v>
@@ -19437,7 +19437,7 @@
         <v>27</v>
       </c>
       <c r="D901">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E901" t="s">
         <v>28</v>
@@ -19454,7 +19454,7 @@
         <v>27</v>
       </c>
       <c r="D902">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E902" t="s">
         <v>28</v>
@@ -19471,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D903">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E903" t="s">
         <v>28</v>
@@ -19488,7 +19488,7 @@
         <v>27</v>
       </c>
       <c r="D904">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E904" t="s">
         <v>28</v>
@@ -19505,7 +19505,7 @@
         <v>27</v>
       </c>
       <c r="D905">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E905" t="s">
         <v>28</v>
@@ -19522,7 +19522,7 @@
         <v>27</v>
       </c>
       <c r="D906">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E906" t="s">
         <v>28</v>
@@ -19539,7 +19539,7 @@
         <v>27</v>
       </c>
       <c r="D907">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E907" t="s">
         <v>28</v>
@@ -19556,7 +19556,7 @@
         <v>27</v>
       </c>
       <c r="D908">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E908" t="s">
         <v>28</v>
@@ -19573,7 +19573,7 @@
         <v>27</v>
       </c>
       <c r="D909">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E909" t="s">
         <v>28</v>
@@ -19590,7 +19590,7 @@
         <v>27</v>
       </c>
       <c r="D910">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E910" t="s">
         <v>28</v>
@@ -19607,7 +19607,7 @@
         <v>27</v>
       </c>
       <c r="D911">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E911" t="s">
         <v>28</v>
@@ -19624,7 +19624,7 @@
         <v>27</v>
       </c>
       <c r="D912">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E912" t="s">
         <v>28</v>
@@ -19641,7 +19641,7 @@
         <v>27</v>
       </c>
       <c r="D913">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E913" t="s">
         <v>28</v>
@@ -19658,7 +19658,7 @@
         <v>27</v>
       </c>
       <c r="D914">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E914" t="s">
         <v>28</v>
@@ -19675,7 +19675,7 @@
         <v>27</v>
       </c>
       <c r="D915">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E915" t="s">
         <v>28</v>
@@ -19692,7 +19692,7 @@
         <v>27</v>
       </c>
       <c r="D916">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E916" t="s">
         <v>28</v>
@@ -19709,7 +19709,7 @@
         <v>27</v>
       </c>
       <c r="D917">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E917" t="s">
         <v>28</v>
@@ -19726,7 +19726,7 @@
         <v>27</v>
       </c>
       <c r="D918">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E918" t="s">
         <v>28</v>
@@ -19743,7 +19743,7 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E919" t="s">
         <v>28</v>
@@ -19760,7 +19760,7 @@
         <v>27</v>
       </c>
       <c r="D920">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E920" t="s">
         <v>28</v>
@@ -19777,7 +19777,7 @@
         <v>27</v>
       </c>
       <c r="D921">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E921" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>27</v>
       </c>
       <c r="D922">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E922" t="s">
         <v>28</v>
@@ -19811,7 +19811,7 @@
         <v>27</v>
       </c>
       <c r="D923">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E923" t="s">
         <v>28</v>
@@ -19828,7 +19828,7 @@
         <v>27</v>
       </c>
       <c r="D924">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E924" t="s">
         <v>28</v>
@@ -19845,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="D925">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E925" t="s">
         <v>28</v>
@@ -19862,7 +19862,7 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E926" t="s">
         <v>28</v>
@@ -19879,7 +19879,7 @@
         <v>27</v>
       </c>
       <c r="D927">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E927" t="s">
         <v>28</v>
@@ -19896,7 +19896,7 @@
         <v>27</v>
       </c>
       <c r="D928">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E928" t="s">
         <v>28</v>
@@ -19913,7 +19913,7 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E929" t="s">
         <v>28</v>
@@ -19930,7 +19930,7 @@
         <v>27</v>
       </c>
       <c r="D930">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E930" t="s">
         <v>28</v>
@@ -19947,7 +19947,7 @@
         <v>27</v>
       </c>
       <c r="D931">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E931" t="s">
         <v>28</v>
@@ -19964,7 +19964,7 @@
         <v>27</v>
       </c>
       <c r="D932">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E932" t="s">
         <v>28</v>
@@ -19981,7 +19981,7 @@
         <v>27</v>
       </c>
       <c r="D933">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E933" t="s">
         <v>28</v>
@@ -19998,7 +19998,7 @@
         <v>27</v>
       </c>
       <c r="D934">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E934" t="s">
         <v>28</v>
@@ -20015,7 +20015,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E935" t="s">
         <v>28</v>
@@ -20032,7 +20032,7 @@
         <v>27</v>
       </c>
       <c r="D936">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E936" t="s">
         <v>28</v>
@@ -20049,7 +20049,7 @@
         <v>27</v>
       </c>
       <c r="D937">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E937" t="s">
         <v>28</v>
@@ -20066,7 +20066,7 @@
         <v>27</v>
       </c>
       <c r="D938">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E938" t="s">
         <v>28</v>
@@ -20083,7 +20083,7 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E939" t="s">
         <v>28</v>
@@ -20100,7 +20100,7 @@
         <v>27</v>
       </c>
       <c r="D940">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E940" t="s">
         <v>28</v>
@@ -20117,7 +20117,7 @@
         <v>27</v>
       </c>
       <c r="D941">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E941" t="s">
         <v>28</v>
@@ -20134,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D942">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E942" t="s">
         <v>28</v>
@@ -20151,7 +20151,7 @@
         <v>27</v>
       </c>
       <c r="D943">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E943" t="s">
         <v>28</v>
@@ -20168,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="D944">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E944" t="s">
         <v>28</v>
@@ -20185,7 +20185,7 @@
         <v>27</v>
       </c>
       <c r="D945">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E945" t="s">
         <v>28</v>
@@ -20202,7 +20202,7 @@
         <v>27</v>
       </c>
       <c r="D946">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E946" t="s">
         <v>28</v>
@@ -20219,7 +20219,7 @@
         <v>27</v>
       </c>
       <c r="D947">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E947" t="s">
         <v>28</v>
@@ -20236,7 +20236,7 @@
         <v>27</v>
       </c>
       <c r="D948">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E948" t="s">
         <v>28</v>
@@ -20253,7 +20253,7 @@
         <v>27</v>
       </c>
       <c r="D949">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E949" t="s">
         <v>28</v>
@@ -20270,7 +20270,7 @@
         <v>27</v>
       </c>
       <c r="D950">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E950" t="s">
         <v>28</v>
@@ -20287,7 +20287,7 @@
         <v>27</v>
       </c>
       <c r="D951">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E951" t="s">
         <v>28</v>
@@ -20304,7 +20304,7 @@
         <v>27</v>
       </c>
       <c r="D952">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E952" t="s">
         <v>28</v>
@@ -20321,7 +20321,7 @@
         <v>27</v>
       </c>
       <c r="D953">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E953" t="s">
         <v>28</v>
@@ -20338,7 +20338,7 @@
         <v>27</v>
       </c>
       <c r="D954">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E954" t="s">
         <v>28</v>
@@ -20355,7 +20355,7 @@
         <v>27</v>
       </c>
       <c r="D955">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E955" t="s">
         <v>28</v>
@@ -20372,7 +20372,7 @@
         <v>27</v>
       </c>
       <c r="D956">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E956" t="s">
         <v>28</v>
@@ -20423,7 +20423,7 @@
         <v>27</v>
       </c>
       <c r="D959">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E959" t="s">
         <v>28</v>
@@ -20440,7 +20440,7 @@
         <v>27</v>
       </c>
       <c r="D960">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E960" t="s">
         <v>28</v>
@@ -20457,7 +20457,7 @@
         <v>27</v>
       </c>
       <c r="D961">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E961" t="s">
         <v>28</v>
@@ -20474,7 +20474,7 @@
         <v>27</v>
       </c>
       <c r="D962">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E962" t="s">
         <v>28</v>
@@ -20491,7 +20491,7 @@
         <v>27</v>
       </c>
       <c r="D963">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E963" t="s">
         <v>28</v>
@@ -20508,7 +20508,7 @@
         <v>27</v>
       </c>
       <c r="D964">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E964" t="s">
         <v>28</v>
@@ -20525,7 +20525,7 @@
         <v>27</v>
       </c>
       <c r="D965">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E965" t="s">
         <v>28</v>
@@ -20542,7 +20542,7 @@
         <v>27</v>
       </c>
       <c r="D966">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E966" t="s">
         <v>28</v>
@@ -20559,7 +20559,7 @@
         <v>27</v>
       </c>
       <c r="D967">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E967" t="s">
         <v>28</v>
@@ -20593,7 +20593,7 @@
         <v>27</v>
       </c>
       <c r="D969">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E969" t="s">
         <v>28</v>
@@ -20610,7 +20610,7 @@
         <v>27</v>
       </c>
       <c r="D970">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E970" t="s">
         <v>28</v>
@@ -20627,7 +20627,7 @@
         <v>27</v>
       </c>
       <c r="D971">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E971" t="s">
         <v>28</v>
@@ -20644,7 +20644,7 @@
         <v>27</v>
       </c>
       <c r="D972">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E972" t="s">
         <v>28</v>
@@ -20661,7 +20661,7 @@
         <v>27</v>
       </c>
       <c r="D973">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E973" t="s">
         <v>28</v>
@@ -20678,7 +20678,7 @@
         <v>27</v>
       </c>
       <c r="D974">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E974" t="s">
         <v>28</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="D975">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E975" t="s">
         <v>28</v>
@@ -20712,7 +20712,7 @@
         <v>27</v>
       </c>
       <c r="D976">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E976" t="s">
         <v>28</v>
@@ -20729,7 +20729,7 @@
         <v>27</v>
       </c>
       <c r="D977">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E977" t="s">
         <v>28</v>
@@ -20746,7 +20746,7 @@
         <v>27</v>
       </c>
       <c r="D978">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E978" t="s">
         <v>28</v>
@@ -20763,7 +20763,7 @@
         <v>27</v>
       </c>
       <c r="D979">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E979" t="s">
         <v>28</v>
@@ -20780,7 +20780,7 @@
         <v>27</v>
       </c>
       <c r="D980">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E980" t="s">
         <v>28</v>
@@ -20797,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="D981">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E981" t="s">
         <v>28</v>
@@ -20814,7 +20814,7 @@
         <v>27</v>
       </c>
       <c r="D982">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E982" t="s">
         <v>28</v>
@@ -20831,7 +20831,7 @@
         <v>27</v>
       </c>
       <c r="D983">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E983" t="s">
         <v>28</v>
@@ -20848,7 +20848,7 @@
         <v>27</v>
       </c>
       <c r="D984">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E984" t="s">
         <v>28</v>
@@ -20865,7 +20865,7 @@
         <v>27</v>
       </c>
       <c r="D985">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E985" t="s">
         <v>28</v>
@@ -20882,7 +20882,7 @@
         <v>27</v>
       </c>
       <c r="D986">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E986" t="s">
         <v>28</v>
@@ -20899,7 +20899,7 @@
         <v>27</v>
       </c>
       <c r="D987">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E987" t="s">
         <v>28</v>
@@ -20916,7 +20916,7 @@
         <v>27</v>
       </c>
       <c r="D988">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E988" t="s">
         <v>28</v>
@@ -20933,7 +20933,7 @@
         <v>27</v>
       </c>
       <c r="D989">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E989" t="s">
         <v>28</v>
@@ -20950,7 +20950,7 @@
         <v>27</v>
       </c>
       <c r="D990">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E990" t="s">
         <v>28</v>
@@ -20967,7 +20967,7 @@
         <v>27</v>
       </c>
       <c r="D991">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E991" t="s">
         <v>28</v>
@@ -20984,7 +20984,7 @@
         <v>27</v>
       </c>
       <c r="D992">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E992" t="s">
         <v>28</v>
@@ -21001,7 +21001,7 @@
         <v>27</v>
       </c>
       <c r="D993">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E993" t="s">
         <v>28</v>
@@ -21018,7 +21018,7 @@
         <v>27</v>
       </c>
       <c r="D994">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E994" t="s">
         <v>28</v>
@@ -21035,7 +21035,7 @@
         <v>27</v>
       </c>
       <c r="D995">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E995" t="s">
         <v>28</v>
@@ -21052,7 +21052,7 @@
         <v>27</v>
       </c>
       <c r="D996">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E996" t="s">
         <v>28</v>
@@ -21069,7 +21069,7 @@
         <v>27</v>
       </c>
       <c r="D997">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E997" t="s">
         <v>28</v>
@@ -21086,7 +21086,7 @@
         <v>27</v>
       </c>
       <c r="D998">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E998" t="s">
         <v>28</v>
@@ -21103,7 +21103,7 @@
         <v>27</v>
       </c>
       <c r="D999">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E999" t="s">
         <v>28</v>
@@ -21120,7 +21120,7 @@
         <v>27</v>
       </c>
       <c r="D1000">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1000" t="s">
         <v>28</v>
@@ -21137,7 +21137,7 @@
         <v>27</v>
       </c>
       <c r="D1001">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E1001" t="s">
         <v>28</v>
@@ -21154,7 +21154,7 @@
         <v>27</v>
       </c>
       <c r="D1002">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1002" t="s">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>27</v>
       </c>
       <c r="D1003">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E1003" t="s">
         <v>28</v>
@@ -21188,7 +21188,7 @@
         <v>27</v>
       </c>
       <c r="D1004">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E1004" t="s">
         <v>28</v>
@@ -21205,7 +21205,7 @@
         <v>27</v>
       </c>
       <c r="D1005">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E1005" t="s">
         <v>28</v>
@@ -21222,7 +21222,7 @@
         <v>27</v>
       </c>
       <c r="D1006">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1006" t="s">
         <v>28</v>
@@ -21239,7 +21239,7 @@
         <v>27</v>
       </c>
       <c r="D1007">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E1007" t="s">
         <v>28</v>
@@ -21256,7 +21256,7 @@
         <v>27</v>
       </c>
       <c r="D1008">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1008" t="s">
         <v>28</v>
@@ -21290,7 +21290,7 @@
         <v>27</v>
       </c>
       <c r="D1010">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1010" t="s">
         <v>28</v>
@@ -21307,7 +21307,7 @@
         <v>27</v>
       </c>
       <c r="D1011">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1011" t="s">
         <v>28</v>
@@ -21324,7 +21324,7 @@
         <v>27</v>
       </c>
       <c r="D1012">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1012" t="s">
         <v>28</v>
@@ -21341,7 +21341,7 @@
         <v>27</v>
       </c>
       <c r="D1013">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1013" t="s">
         <v>28</v>
@@ -21358,7 +21358,7 @@
         <v>27</v>
       </c>
       <c r="D1014">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1014" t="s">
         <v>28</v>
@@ -21375,7 +21375,7 @@
         <v>27</v>
       </c>
       <c r="D1015">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E1015" t="s">
         <v>28</v>
@@ -21392,7 +21392,7 @@
         <v>27</v>
       </c>
       <c r="D1016">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1016" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>27</v>
       </c>
       <c r="D1018">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1018" t="s">
         <v>28</v>
@@ -21443,7 +21443,7 @@
         <v>27</v>
       </c>
       <c r="D1019">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E1019" t="s">
         <v>28</v>
@@ -21460,7 +21460,7 @@
         <v>27</v>
       </c>
       <c r="D1020">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1020" t="s">
         <v>28</v>
@@ -21477,7 +21477,7 @@
         <v>27</v>
       </c>
       <c r="D1021">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1021" t="s">
         <v>28</v>
@@ -21494,7 +21494,7 @@
         <v>27</v>
       </c>
       <c r="D1022">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1022" t="s">
         <v>28</v>
@@ -21511,7 +21511,7 @@
         <v>27</v>
       </c>
       <c r="D1023">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E1023" t="s">
         <v>28</v>
@@ -21528,7 +21528,7 @@
         <v>27</v>
       </c>
       <c r="D1024">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E1024" t="s">
         <v>28</v>
@@ -21545,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1025" t="s">
         <v>28</v>
@@ -21562,7 +21562,7 @@
         <v>27</v>
       </c>
       <c r="D1026">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E1026" t="s">
         <v>28</v>
@@ -21579,7 +21579,7 @@
         <v>27</v>
       </c>
       <c r="D1027">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1027" t="s">
         <v>28</v>
@@ -21596,7 +21596,7 @@
         <v>27</v>
       </c>
       <c r="D1028">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E1028" t="s">
         <v>28</v>
@@ -21613,7 +21613,7 @@
         <v>27</v>
       </c>
       <c r="D1029">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E1029" t="s">
         <v>28</v>
@@ -21630,7 +21630,7 @@
         <v>27</v>
       </c>
       <c r="D1030">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1030" t="s">
         <v>28</v>
@@ -21647,7 +21647,7 @@
         <v>27</v>
       </c>
       <c r="D1031">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E1031" t="s">
         <v>28</v>
@@ -21664,7 +21664,7 @@
         <v>27</v>
       </c>
       <c r="D1032">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1032" t="s">
         <v>28</v>
@@ -21681,7 +21681,7 @@
         <v>27</v>
       </c>
       <c r="D1033">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1033" t="s">
         <v>28</v>
@@ -21698,7 +21698,7 @@
         <v>27</v>
       </c>
       <c r="D1034">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E1034" t="s">
         <v>28</v>
@@ -21715,7 +21715,7 @@
         <v>27</v>
       </c>
       <c r="D1035">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1035" t="s">
         <v>28</v>
@@ -21732,7 +21732,7 @@
         <v>27</v>
       </c>
       <c r="D1036">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1036" t="s">
         <v>28</v>
@@ -21749,7 +21749,7 @@
         <v>27</v>
       </c>
       <c r="D1037">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1037" t="s">
         <v>28</v>
@@ -21766,7 +21766,7 @@
         <v>27</v>
       </c>
       <c r="D1038">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E1038" t="s">
         <v>28</v>
@@ -21783,7 +21783,7 @@
         <v>27</v>
       </c>
       <c r="D1039">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E1039" t="s">
         <v>28</v>
@@ -21800,7 +21800,7 @@
         <v>27</v>
       </c>
       <c r="D1040">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E1040" t="s">
         <v>28</v>
@@ -21817,7 +21817,7 @@
         <v>27</v>
       </c>
       <c r="D1041">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1041" t="s">
         <v>28</v>
@@ -21834,7 +21834,7 @@
         <v>27</v>
       </c>
       <c r="D1042">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E1042" t="s">
         <v>28</v>
@@ -21851,7 +21851,7 @@
         <v>27</v>
       </c>
       <c r="D1043">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E1043" t="s">
         <v>28</v>
@@ -21885,7 +21885,7 @@
         <v>27</v>
       </c>
       <c r="D1045">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E1045" t="s">
         <v>28</v>
@@ -21902,7 +21902,7 @@
         <v>27</v>
       </c>
       <c r="D1046">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E1046" t="s">
         <v>28</v>
@@ -21919,7 +21919,7 @@
         <v>27</v>
       </c>
       <c r="D1047">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E1047" t="s">
         <v>28</v>
@@ -21936,7 +21936,7 @@
         <v>27</v>
       </c>
       <c r="D1048">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1048" t="s">
         <v>28</v>
@@ -21987,7 +21987,7 @@
         <v>27</v>
       </c>
       <c r="D1051">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1051" t="s">
         <v>28</v>
@@ -22004,7 +22004,7 @@
         <v>27</v>
       </c>
       <c r="D1052">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1052" t="s">
         <v>28</v>
@@ -22021,7 +22021,7 @@
         <v>27</v>
       </c>
       <c r="D1053">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E1053" t="s">
         <v>28</v>
@@ -22038,7 +22038,7 @@
         <v>27</v>
       </c>
       <c r="D1054">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1054" t="s">
         <v>28</v>
@@ -22055,7 +22055,7 @@
         <v>27</v>
       </c>
       <c r="D1055">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E1055" t="s">
         <v>28</v>
@@ -22072,7 +22072,7 @@
         <v>27</v>
       </c>
       <c r="D1056">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1056" t="s">
         <v>28</v>
@@ -22089,7 +22089,7 @@
         <v>27</v>
       </c>
       <c r="D1057">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1057" t="s">
         <v>28</v>
@@ -22106,7 +22106,7 @@
         <v>27</v>
       </c>
       <c r="D1058">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E1058" t="s">
         <v>28</v>
@@ -22140,7 +22140,7 @@
         <v>27</v>
       </c>
       <c r="D1060">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E1060" t="s">
         <v>28</v>
@@ -22157,7 +22157,7 @@
         <v>27</v>
       </c>
       <c r="D1061">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1061" t="s">
         <v>28</v>
@@ -22174,7 +22174,7 @@
         <v>27</v>
       </c>
       <c r="D1062">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E1062" t="s">
         <v>28</v>
@@ -22191,7 +22191,7 @@
         <v>27</v>
       </c>
       <c r="D1063">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E1063" t="s">
         <v>28</v>
@@ -22208,7 +22208,7 @@
         <v>27</v>
       </c>
       <c r="D1064">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1064" t="s">
         <v>28</v>
@@ -22259,7 +22259,7 @@
         <v>27</v>
       </c>
       <c r="D1067">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1067" t="s">
         <v>28</v>
@@ -22276,7 +22276,7 @@
         <v>27</v>
       </c>
       <c r="D1068">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E1068" t="s">
         <v>28</v>
@@ -22293,7 +22293,7 @@
         <v>27</v>
       </c>
       <c r="D1069">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1069" t="s">
         <v>28</v>
@@ -22310,7 +22310,7 @@
         <v>27</v>
       </c>
       <c r="D1070">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E1070" t="s">
         <v>28</v>
@@ -22327,7 +22327,7 @@
         <v>27</v>
       </c>
       <c r="D1071">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1071" t="s">
         <v>28</v>
@@ -22344,7 +22344,7 @@
         <v>27</v>
       </c>
       <c r="D1072">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E1072" t="s">
         <v>28</v>
@@ -22361,7 +22361,7 @@
         <v>27</v>
       </c>
       <c r="D1073">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1073" t="s">
         <v>28</v>
@@ -22378,7 +22378,7 @@
         <v>27</v>
       </c>
       <c r="D1074">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1074" t="s">
         <v>28</v>
@@ -22395,7 +22395,7 @@
         <v>27</v>
       </c>
       <c r="D1075">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1075" t="s">
         <v>28</v>
@@ -22412,7 +22412,7 @@
         <v>27</v>
       </c>
       <c r="D1076">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1076" t="s">
         <v>28</v>
@@ -22446,7 +22446,7 @@
         <v>27</v>
       </c>
       <c r="D1078">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E1078" t="s">
         <v>28</v>
@@ -22463,7 +22463,7 @@
         <v>27</v>
       </c>
       <c r="D1079">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1079" t="s">
         <v>28</v>
@@ -22480,7 +22480,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1080" t="s">
         <v>28</v>
@@ -22497,7 +22497,7 @@
         <v>27</v>
       </c>
       <c r="D1081">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E1081" t="s">
         <v>28</v>
@@ -22531,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="D1083">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1083" t="s">
         <v>28</v>
@@ -22548,7 +22548,7 @@
         <v>27</v>
       </c>
       <c r="D1084">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1084" t="s">
         <v>28</v>
@@ -22565,7 +22565,7 @@
         <v>27</v>
       </c>
       <c r="D1085">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1085" t="s">
         <v>28</v>
@@ -22582,7 +22582,7 @@
         <v>27</v>
       </c>
       <c r="D1086">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E1086" t="s">
         <v>28</v>
@@ -22599,7 +22599,7 @@
         <v>27</v>
       </c>
       <c r="D1087">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1087" t="s">
         <v>28</v>
@@ -22616,7 +22616,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1088" t="s">
         <v>28</v>
@@ -22633,7 +22633,7 @@
         <v>27</v>
       </c>
       <c r="D1089">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1089" t="s">
         <v>28</v>
@@ -22650,7 +22650,7 @@
         <v>27</v>
       </c>
       <c r="D1090">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1090" t="s">
         <v>28</v>
@@ -22667,7 +22667,7 @@
         <v>27</v>
       </c>
       <c r="D1091">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1091" t="s">
         <v>28</v>
@@ -22684,7 +22684,7 @@
         <v>27</v>
       </c>
       <c r="D1092">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E1092" t="s">
         <v>28</v>
@@ -22701,7 +22701,7 @@
         <v>27</v>
       </c>
       <c r="D1093">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E1093" t="s">
         <v>28</v>
@@ -22718,7 +22718,7 @@
         <v>27</v>
       </c>
       <c r="D1094">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E1094" t="s">
         <v>28</v>
@@ -22735,7 +22735,7 @@
         <v>27</v>
       </c>
       <c r="D1095">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E1095" t="s">
         <v>28</v>
@@ -22752,7 +22752,7 @@
         <v>27</v>
       </c>
       <c r="D1096">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E1096" t="s">
         <v>28</v>
@@ -22769,7 +22769,7 @@
         <v>27</v>
       </c>
       <c r="D1097">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1097" t="s">
         <v>28</v>
@@ -22786,7 +22786,7 @@
         <v>27</v>
       </c>
       <c r="D1098">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E1098" t="s">
         <v>28</v>
@@ -22803,7 +22803,7 @@
         <v>27</v>
       </c>
       <c r="D1099">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1099" t="s">
         <v>28</v>
@@ -22820,7 +22820,7 @@
         <v>27</v>
       </c>
       <c r="D1100">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1100" t="s">
         <v>28</v>
@@ -22837,7 +22837,7 @@
         <v>27</v>
       </c>
       <c r="D1101">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1101" t="s">
         <v>28</v>
@@ -22854,7 +22854,7 @@
         <v>27</v>
       </c>
       <c r="D1102">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E1102" t="s">
         <v>28</v>
@@ -22871,7 +22871,7 @@
         <v>27</v>
       </c>
       <c r="D1103">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E1103" t="s">
         <v>28</v>
@@ -22888,7 +22888,7 @@
         <v>27</v>
       </c>
       <c r="D1104">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1104" t="s">
         <v>28</v>
@@ -22905,7 +22905,7 @@
         <v>27</v>
       </c>
       <c r="D1105">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1105" t="s">
         <v>28</v>
@@ -22922,7 +22922,7 @@
         <v>27</v>
       </c>
       <c r="D1106">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1106" t="s">
         <v>28</v>
@@ -22939,7 +22939,7 @@
         <v>27</v>
       </c>
       <c r="D1107">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1107" t="s">
         <v>28</v>
@@ -22956,7 +22956,7 @@
         <v>27</v>
       </c>
       <c r="D1108">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E1108" t="s">
         <v>28</v>
@@ -22973,7 +22973,7 @@
         <v>27</v>
       </c>
       <c r="D1109">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E1109" t="s">
         <v>28</v>
@@ -22990,7 +22990,7 @@
         <v>27</v>
       </c>
       <c r="D1110">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1110" t="s">
         <v>28</v>
@@ -23007,7 +23007,7 @@
         <v>27</v>
       </c>
       <c r="D1111">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E1111" t="s">
         <v>28</v>
@@ -23024,7 +23024,7 @@
         <v>27</v>
       </c>
       <c r="D1112">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1112" t="s">
         <v>28</v>

--- a/android-reports/latest/appium-report.xlsx
+++ b/android-reports/latest/appium-report.xlsx
@@ -3905,7 +3905,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>1293</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>1219</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,7 +3965,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>1309</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>1313</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>1300</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4025,7 +4025,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>1373</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4045,7 +4045,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>1260</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>1283</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4085,7 +4085,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>1302</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4105,7 +4105,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>1242</v>
+        <v>1310</v>
       </c>
     </row>
   </sheetData>
@@ -4154,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>28</v>
@@ -4171,7 +4171,7 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
         <v>28</v>
@@ -4188,7 +4188,7 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
@@ -4205,7 +4205,7 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
@@ -4222,7 +4222,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -4256,7 +4256,7 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
@@ -4290,7 +4290,7 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
@@ -4307,7 +4307,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
@@ -4341,7 +4341,7 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -4358,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -4375,7 +4375,7 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
         <v>28</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
         <v>28</v>
@@ -4409,7 +4409,7 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
         <v>28</v>
@@ -4426,7 +4426,7 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
         <v>28</v>
@@ -4443,7 +4443,7 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="s">
         <v>28</v>
@@ -4460,7 +4460,7 @@
         <v>27</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
         <v>28</v>
@@ -4477,7 +4477,7 @@
         <v>27</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
         <v>28</v>
@@ -4494,7 +4494,7 @@
         <v>27</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -4511,7 +4511,7 @@
         <v>27</v>
       </c>
       <c r="D23">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E23" t="s">
         <v>28</v>
@@ -4528,7 +4528,7 @@
         <v>27</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s">
         <v>28</v>
@@ -4545,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
         <v>28</v>
@@ -4562,7 +4562,7 @@
         <v>27</v>
       </c>
       <c r="D26">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s">
         <v>28</v>
@@ -4579,7 +4579,7 @@
         <v>27</v>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E27" t="s">
         <v>28</v>
@@ -4596,7 +4596,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E28" t="s">
         <v>28</v>
@@ -4613,7 +4613,7 @@
         <v>27</v>
       </c>
       <c r="D29">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E30" t="s">
         <v>28</v>
@@ -4647,7 +4647,7 @@
         <v>27</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31" t="s">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>27</v>
       </c>
       <c r="D32">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E32" t="s">
         <v>28</v>
@@ -4681,7 +4681,7 @@
         <v>27</v>
       </c>
       <c r="D33">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
         <v>28</v>
@@ -4698,7 +4698,7 @@
         <v>27</v>
       </c>
       <c r="D34">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E34" t="s">
         <v>28</v>
@@ -4715,7 +4715,7 @@
         <v>27</v>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35" t="s">
         <v>28</v>
@@ -4732,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D36">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
         <v>28</v>
@@ -4749,7 +4749,7 @@
         <v>27</v>
       </c>
       <c r="D37">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
         <v>28</v>
@@ -4783,7 +4783,7 @@
         <v>27</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E39" t="s">
         <v>28</v>
@@ -4800,7 +4800,7 @@
         <v>27</v>
       </c>
       <c r="D40">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E40" t="s">
         <v>28</v>
@@ -4817,7 +4817,7 @@
         <v>27</v>
       </c>
       <c r="D41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
         <v>28</v>
@@ -4834,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E42" t="s">
         <v>28</v>
@@ -4851,7 +4851,7 @@
         <v>27</v>
       </c>
       <c r="D43">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
         <v>28</v>
@@ -4868,7 +4868,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
         <v>28</v>
@@ -4885,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="D45">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E45" t="s">
         <v>28</v>
@@ -4902,7 +4902,7 @@
         <v>27</v>
       </c>
       <c r="D46">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
         <v>28</v>
@@ -4919,7 +4919,7 @@
         <v>27</v>
       </c>
       <c r="D47">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
@@ -4936,7 +4936,7 @@
         <v>27</v>
       </c>
       <c r="D48">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
         <v>28</v>
@@ -4953,7 +4953,7 @@
         <v>27</v>
       </c>
       <c r="D49">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
@@ -4987,7 +4987,7 @@
         <v>27</v>
       </c>
       <c r="D51">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E51" t="s">
         <v>28</v>
@@ -5004,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="D52">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E52" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="D53">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E53" t="s">
         <v>28</v>
@@ -5038,7 +5038,7 @@
         <v>27</v>
       </c>
       <c r="D54">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E54" t="s">
         <v>28</v>
@@ -5055,7 +5055,7 @@
         <v>27</v>
       </c>
       <c r="D55">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
         <v>28</v>
@@ -5072,7 +5072,7 @@
         <v>27</v>
       </c>
       <c r="D56">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
         <v>28</v>
@@ -5106,7 +5106,7 @@
         <v>27</v>
       </c>
       <c r="D58">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E58" t="s">
         <v>28</v>
@@ -5140,7 +5140,7 @@
         <v>27</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E60" t="s">
         <v>28</v>
@@ -5157,7 +5157,7 @@
         <v>27</v>
       </c>
       <c r="D61">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -5174,7 +5174,7 @@
         <v>27</v>
       </c>
       <c r="D62">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E62" t="s">
         <v>28</v>
@@ -5191,7 +5191,7 @@
         <v>27</v>
       </c>
       <c r="D63">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="D64">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E64" t="s">
         <v>28</v>
@@ -5225,7 +5225,7 @@
         <v>27</v>
       </c>
       <c r="D65">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E65" t="s">
         <v>28</v>
@@ -5242,7 +5242,7 @@
         <v>27</v>
       </c>
       <c r="D66">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E66" t="s">
         <v>28</v>
@@ -5259,7 +5259,7 @@
         <v>27</v>
       </c>
       <c r="D67">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
@@ -5276,7 +5276,7 @@
         <v>27</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
@@ -5293,7 +5293,7 @@
         <v>27</v>
       </c>
       <c r="D69">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E69" t="s">
         <v>28</v>
@@ -5310,7 +5310,7 @@
         <v>27</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E70" t="s">
         <v>28</v>
@@ -5327,7 +5327,7 @@
         <v>27</v>
       </c>
       <c r="D71">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E71" t="s">
         <v>28</v>
@@ -5344,7 +5344,7 @@
         <v>27</v>
       </c>
       <c r="D72">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E72" t="s">
         <v>28</v>
@@ -5361,7 +5361,7 @@
         <v>27</v>
       </c>
       <c r="D73">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
@@ -5378,7 +5378,7 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
@@ -5395,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="D76">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E76" t="s">
         <v>28</v>
@@ -5429,7 +5429,7 @@
         <v>27</v>
       </c>
       <c r="D77">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E77" t="s">
         <v>28</v>
@@ -5446,7 +5446,7 @@
         <v>27</v>
       </c>
       <c r="D78">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
         <v>28</v>
@@ -5463,7 +5463,7 @@
         <v>27</v>
       </c>
       <c r="D79">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E79" t="s">
         <v>28</v>
@@ -5480,7 +5480,7 @@
         <v>27</v>
       </c>
       <c r="D80">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E80" t="s">
         <v>28</v>
@@ -5514,7 +5514,7 @@
         <v>27</v>
       </c>
       <c r="D82">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E82" t="s">
         <v>28</v>
@@ -5531,7 +5531,7 @@
         <v>27</v>
       </c>
       <c r="D83">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E83" t="s">
         <v>28</v>
@@ -5548,7 +5548,7 @@
         <v>27</v>
       </c>
       <c r="D84">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E84" t="s">
         <v>28</v>
@@ -5565,7 +5565,7 @@
         <v>27</v>
       </c>
       <c r="D85">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E85" t="s">
         <v>28</v>
@@ -5582,7 +5582,7 @@
         <v>27</v>
       </c>
       <c r="D86">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E86" t="s">
         <v>28</v>
@@ -5599,7 +5599,7 @@
         <v>27</v>
       </c>
       <c r="D87">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E87" t="s">
         <v>28</v>
@@ -5616,7 +5616,7 @@
         <v>27</v>
       </c>
       <c r="D88">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E88" t="s">
         <v>28</v>
@@ -5633,7 +5633,7 @@
         <v>27</v>
       </c>
       <c r="D89">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E89" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="D90">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E90" t="s">
         <v>28</v>
@@ -5684,7 +5684,7 @@
         <v>27</v>
       </c>
       <c r="D92">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E92" t="s">
         <v>28</v>
@@ -5701,7 +5701,7 @@
         <v>27</v>
       </c>
       <c r="D93">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E93" t="s">
         <v>28</v>
@@ -5718,7 +5718,7 @@
         <v>27</v>
       </c>
       <c r="D94">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E94" t="s">
         <v>28</v>
@@ -5735,7 +5735,7 @@
         <v>27</v>
       </c>
       <c r="D95">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E95" t="s">
         <v>28</v>
@@ -5752,7 +5752,7 @@
         <v>27</v>
       </c>
       <c r="D96">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E96" t="s">
         <v>28</v>
@@ -5769,7 +5769,7 @@
         <v>27</v>
       </c>
       <c r="D97">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
         <v>28</v>
@@ -5786,7 +5786,7 @@
         <v>27</v>
       </c>
       <c r="D98">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E98" t="s">
         <v>28</v>
@@ -5820,7 +5820,7 @@
         <v>27</v>
       </c>
       <c r="D100">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E100" t="s">
         <v>28</v>
@@ -5837,7 +5837,7 @@
         <v>27</v>
       </c>
       <c r="D101">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E101" t="s">
         <v>28</v>
@@ -5854,7 +5854,7 @@
         <v>27</v>
       </c>
       <c r="D102">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E102" t="s">
         <v>28</v>
@@ -5871,7 +5871,7 @@
         <v>27</v>
       </c>
       <c r="D103">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E103" t="s">
         <v>28</v>
@@ -5888,7 +5888,7 @@
         <v>27</v>
       </c>
       <c r="D104">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E104" t="s">
         <v>28</v>
@@ -5905,7 +5905,7 @@
         <v>27</v>
       </c>
       <c r="D105">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E105" t="s">
         <v>28</v>
@@ -5922,7 +5922,7 @@
         <v>27</v>
       </c>
       <c r="D106">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E106" t="s">
         <v>28</v>
@@ -5939,7 +5939,7 @@
         <v>27</v>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E107" t="s">
         <v>28</v>
@@ -5956,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="D108">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E108" t="s">
         <v>28</v>
@@ -5973,7 +5973,7 @@
         <v>27</v>
       </c>
       <c r="D109">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E109" t="s">
         <v>28</v>
@@ -5990,7 +5990,7 @@
         <v>27</v>
       </c>
       <c r="D110">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E110" t="s">
         <v>28</v>
@@ -6007,7 +6007,7 @@
         <v>27</v>
       </c>
       <c r="D111">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E111" t="s">
         <v>28</v>
@@ -6024,7 +6024,7 @@
         <v>27</v>
       </c>
       <c r="D112">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E112" t="s">
         <v>28</v>
@@ -6041,7 +6041,7 @@
         <v>27</v>
       </c>
       <c r="D113">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E113" t="s">
         <v>28</v>
@@ -6058,7 +6058,7 @@
         <v>27</v>
       </c>
       <c r="D114">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E114" t="s">
         <v>28</v>
@@ -6075,7 +6075,7 @@
         <v>27</v>
       </c>
       <c r="D115">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -6109,7 +6109,7 @@
         <v>27</v>
       </c>
       <c r="D117">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E117" t="s">
         <v>28</v>
@@ -6126,7 +6126,7 @@
         <v>27</v>
       </c>
       <c r="D118">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E118" t="s">
         <v>28</v>
@@ -6160,7 +6160,7 @@
         <v>27</v>
       </c>
       <c r="D120">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E120" t="s">
         <v>28</v>
@@ -6177,7 +6177,7 @@
         <v>27</v>
       </c>
       <c r="D121">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E121" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="D122">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E122" t="s">
         <v>28</v>
@@ -6211,7 +6211,7 @@
         <v>27</v>
       </c>
       <c r="D123">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E123" t="s">
         <v>28</v>
@@ -6228,7 +6228,7 @@
         <v>27</v>
       </c>
       <c r="D124">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E124" t="s">
         <v>28</v>
@@ -6245,7 +6245,7 @@
         <v>27</v>
       </c>
       <c r="D125">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E125" t="s">
         <v>28</v>
@@ -6262,7 +6262,7 @@
         <v>27</v>
       </c>
       <c r="D126">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E126" t="s">
         <v>28</v>
@@ -6279,7 +6279,7 @@
         <v>27</v>
       </c>
       <c r="D127">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E127" t="s">
         <v>28</v>
@@ -6296,7 +6296,7 @@
         <v>27</v>
       </c>
       <c r="D128">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E128" t="s">
         <v>28</v>
@@ -6313,7 +6313,7 @@
         <v>27</v>
       </c>
       <c r="D129">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E129" t="s">
         <v>28</v>
@@ -6330,7 +6330,7 @@
         <v>27</v>
       </c>
       <c r="D130">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E130" t="s">
         <v>28</v>
@@ -6347,7 +6347,7 @@
         <v>27</v>
       </c>
       <c r="D131">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E131" t="s">
         <v>28</v>
@@ -6364,7 +6364,7 @@
         <v>27</v>
       </c>
       <c r="D132">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E132" t="s">
         <v>28</v>
@@ -6381,7 +6381,7 @@
         <v>27</v>
       </c>
       <c r="D133">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E133" t="s">
         <v>28</v>
@@ -6398,7 +6398,7 @@
         <v>27</v>
       </c>
       <c r="D134">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E134" t="s">
         <v>28</v>
@@ -6415,7 +6415,7 @@
         <v>27</v>
       </c>
       <c r="D135">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E135" t="s">
         <v>28</v>
@@ -6432,7 +6432,7 @@
         <v>27</v>
       </c>
       <c r="D136">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E136" t="s">
         <v>28</v>
@@ -6449,7 +6449,7 @@
         <v>27</v>
       </c>
       <c r="D137">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E137" t="s">
         <v>28</v>
@@ -6466,7 +6466,7 @@
         <v>27</v>
       </c>
       <c r="D138">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E138" t="s">
         <v>28</v>
@@ -6483,7 +6483,7 @@
         <v>27</v>
       </c>
       <c r="D139">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E139" t="s">
         <v>28</v>
@@ -6500,7 +6500,7 @@
         <v>27</v>
       </c>
       <c r="D140">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E140" t="s">
         <v>28</v>
@@ -6517,7 +6517,7 @@
         <v>27</v>
       </c>
       <c r="D141">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E141" t="s">
         <v>28</v>
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="D142">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E142" t="s">
         <v>28</v>
@@ -6551,7 +6551,7 @@
         <v>27</v>
       </c>
       <c r="D143">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E143" t="s">
         <v>28</v>
@@ -6568,7 +6568,7 @@
         <v>27</v>
       </c>
       <c r="D144">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E144" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="D145">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E145" t="s">
         <v>28</v>
@@ -6602,7 +6602,7 @@
         <v>27</v>
       </c>
       <c r="D146">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E146" t="s">
         <v>28</v>
@@ -6619,7 +6619,7 @@
         <v>27</v>
       </c>
       <c r="D147">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E147" t="s">
         <v>28</v>
@@ -6653,7 +6653,7 @@
         <v>27</v>
       </c>
       <c r="D149">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E149" t="s">
         <v>28</v>
@@ -6670,7 +6670,7 @@
         <v>27</v>
       </c>
       <c r="D150">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E150" t="s">
         <v>28</v>
@@ -6687,7 +6687,7 @@
         <v>27</v>
       </c>
       <c r="D151">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E151" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>27</v>
       </c>
       <c r="D152">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E152" t="s">
         <v>28</v>
@@ -6755,7 +6755,7 @@
         <v>27</v>
       </c>
       <c r="D155">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E155" t="s">
         <v>28</v>
@@ -6772,7 +6772,7 @@
         <v>27</v>
       </c>
       <c r="D156">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E156" t="s">
         <v>28</v>
@@ -6789,7 +6789,7 @@
         <v>27</v>
       </c>
       <c r="D157">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E157" t="s">
         <v>28</v>
@@ -6806,7 +6806,7 @@
         <v>27</v>
       </c>
       <c r="D158">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E158" t="s">
         <v>28</v>
@@ -6823,7 +6823,7 @@
         <v>27</v>
       </c>
       <c r="D159">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E159" t="s">
         <v>28</v>
@@ -6840,7 +6840,7 @@
         <v>27</v>
       </c>
       <c r="D160">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E160" t="s">
         <v>28</v>
@@ -6857,7 +6857,7 @@
         <v>27</v>
       </c>
       <c r="D161">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E161" t="s">
         <v>28</v>
@@ -6874,7 +6874,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E162" t="s">
         <v>28</v>
@@ -6891,7 +6891,7 @@
         <v>27</v>
       </c>
       <c r="D163">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E163" t="s">
         <v>28</v>
@@ -6908,7 +6908,7 @@
         <v>27</v>
       </c>
       <c r="D164">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E164" t="s">
         <v>28</v>
@@ -6925,7 +6925,7 @@
         <v>27</v>
       </c>
       <c r="D165">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E165" t="s">
         <v>28</v>
@@ -6942,7 +6942,7 @@
         <v>27</v>
       </c>
       <c r="D166">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E166" t="s">
         <v>28</v>
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="D167">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E167" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="D168">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E168" t="s">
         <v>28</v>
@@ -6993,7 +6993,7 @@
         <v>27</v>
       </c>
       <c r="D169">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E169" t="s">
         <v>28</v>
@@ -7010,7 +7010,7 @@
         <v>27</v>
       </c>
       <c r="D170">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E170" t="s">
         <v>28</v>
@@ -7027,7 +7027,7 @@
         <v>27</v>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E171" t="s">
         <v>28</v>
@@ -7044,7 +7044,7 @@
         <v>27</v>
       </c>
       <c r="D172">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E172" t="s">
         <v>28</v>
@@ -7061,7 +7061,7 @@
         <v>27</v>
       </c>
       <c r="D173">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E173" t="s">
         <v>28</v>
@@ -7078,7 +7078,7 @@
         <v>27</v>
       </c>
       <c r="D174">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E174" t="s">
         <v>28</v>
@@ -7095,7 +7095,7 @@
         <v>27</v>
       </c>
       <c r="D175">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E175" t="s">
         <v>28</v>
@@ -7112,7 +7112,7 @@
         <v>27</v>
       </c>
       <c r="D176">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E176" t="s">
         <v>28</v>
@@ -7129,7 +7129,7 @@
         <v>27</v>
       </c>
       <c r="D177">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E177" t="s">
         <v>28</v>
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="D178">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E178" t="s">
         <v>28</v>
@@ -7163,7 +7163,7 @@
         <v>27</v>
       </c>
       <c r="D179">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E179" t="s">
         <v>28</v>
@@ -7180,7 +7180,7 @@
         <v>27</v>
       </c>
       <c r="D180">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E180" t="s">
         <v>28</v>
@@ -7197,7 +7197,7 @@
         <v>27</v>
       </c>
       <c r="D181">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E181" t="s">
         <v>28</v>
@@ -7214,7 +7214,7 @@
         <v>27</v>
       </c>
       <c r="D182">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E182" t="s">
         <v>28</v>
@@ -7231,7 +7231,7 @@
         <v>27</v>
       </c>
       <c r="D183">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E183" t="s">
         <v>28</v>
@@ -7248,7 +7248,7 @@
         <v>27</v>
       </c>
       <c r="D184">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E184" t="s">
         <v>28</v>
@@ -7265,7 +7265,7 @@
         <v>27</v>
       </c>
       <c r="D185">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E185" t="s">
         <v>28</v>
@@ -7282,7 +7282,7 @@
         <v>27</v>
       </c>
       <c r="D186">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E186" t="s">
         <v>28</v>
@@ -7299,7 +7299,7 @@
         <v>27</v>
       </c>
       <c r="D187">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E187" t="s">
         <v>28</v>
@@ -7316,7 +7316,7 @@
         <v>27</v>
       </c>
       <c r="D188">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E188" t="s">
         <v>28</v>
@@ -7333,7 +7333,7 @@
         <v>27</v>
       </c>
       <c r="D189">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E189" t="s">
         <v>28</v>
@@ -7350,7 +7350,7 @@
         <v>27</v>
       </c>
       <c r="D190">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E190" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="D191">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E191" t="s">
         <v>28</v>
@@ -7384,7 +7384,7 @@
         <v>27</v>
       </c>
       <c r="D192">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E192" t="s">
         <v>28</v>
@@ -7401,7 +7401,7 @@
         <v>27</v>
       </c>
       <c r="D193">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E193" t="s">
         <v>28</v>
@@ -7418,7 +7418,7 @@
         <v>27</v>
       </c>
       <c r="D194">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E194" t="s">
         <v>28</v>
@@ -7435,7 +7435,7 @@
         <v>27</v>
       </c>
       <c r="D195">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E195" t="s">
         <v>28</v>
@@ -7452,7 +7452,7 @@
         <v>27</v>
       </c>
       <c r="D196">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E196" t="s">
         <v>28</v>
@@ -7469,7 +7469,7 @@
         <v>27</v>
       </c>
       <c r="D197">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E197" t="s">
         <v>28</v>
@@ -7503,7 +7503,7 @@
         <v>27</v>
       </c>
       <c r="D199">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E199" t="s">
         <v>28</v>
@@ -7520,7 +7520,7 @@
         <v>27</v>
       </c>
       <c r="D200">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E200" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>27</v>
       </c>
       <c r="D201">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E201" t="s">
         <v>28</v>
@@ -7554,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="D202">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E202" t="s">
         <v>28</v>
@@ -7571,7 +7571,7 @@
         <v>27</v>
       </c>
       <c r="D203">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E203" t="s">
         <v>28</v>
@@ -7588,7 +7588,7 @@
         <v>27</v>
       </c>
       <c r="D204">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E204" t="s">
         <v>28</v>
@@ -7605,7 +7605,7 @@
         <v>27</v>
       </c>
       <c r="D205">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E205" t="s">
         <v>28</v>
@@ -7622,7 +7622,7 @@
         <v>27</v>
       </c>
       <c r="D206">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E206" t="s">
         <v>28</v>
@@ -7639,7 +7639,7 @@
         <v>27</v>
       </c>
       <c r="D207">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E207" t="s">
         <v>28</v>
@@ -7656,7 +7656,7 @@
         <v>27</v>
       </c>
       <c r="D208">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E208" t="s">
         <v>28</v>
@@ -7673,7 +7673,7 @@
         <v>27</v>
       </c>
       <c r="D209">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E209" t="s">
         <v>28</v>
@@ -7690,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="D210">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E210" t="s">
         <v>28</v>
@@ -7707,7 +7707,7 @@
         <v>27</v>
       </c>
       <c r="D211">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E211" t="s">
         <v>28</v>
@@ -7724,7 +7724,7 @@
         <v>27</v>
       </c>
       <c r="D212">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E212" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="D214">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E214" t="s">
         <v>28</v>
@@ -7775,7 +7775,7 @@
         <v>27</v>
       </c>
       <c r="D215">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E215" t="s">
         <v>28</v>
@@ -7792,7 +7792,7 @@
         <v>27</v>
       </c>
       <c r="D216">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E216" t="s">
         <v>28</v>
@@ -7809,7 +7809,7 @@
         <v>27</v>
       </c>
       <c r="D217">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E217" t="s">
         <v>28</v>
@@ -7826,7 +7826,7 @@
         <v>27</v>
       </c>
       <c r="D218">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E218" t="s">
         <v>28</v>
@@ -7843,7 +7843,7 @@
         <v>27</v>
       </c>
       <c r="D219">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E219" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="D220">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E220" t="s">
         <v>28</v>
@@ -7877,7 +7877,7 @@
         <v>27</v>
       </c>
       <c r="D221">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E221" t="s">
         <v>28</v>
@@ -7911,7 +7911,7 @@
         <v>27</v>
       </c>
       <c r="D223">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E223" t="s">
         <v>28</v>
@@ -7928,7 +7928,7 @@
         <v>27</v>
       </c>
       <c r="D224">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E224" t="s">
         <v>28</v>
@@ -7945,7 +7945,7 @@
         <v>27</v>
       </c>
       <c r="D225">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E225" t="s">
         <v>28</v>
@@ -7962,7 +7962,7 @@
         <v>27</v>
       </c>
       <c r="D226">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E226" t="s">
         <v>28</v>
@@ -7979,7 +7979,7 @@
         <v>27</v>
       </c>
       <c r="D227">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E227" t="s">
         <v>28</v>
@@ -7996,7 +7996,7 @@
         <v>27</v>
       </c>
       <c r="D228">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E228" t="s">
         <v>28</v>
@@ -8013,7 +8013,7 @@
         <v>27</v>
       </c>
       <c r="D229">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E229" t="s">
         <v>28</v>
@@ -8030,7 +8030,7 @@
         <v>27</v>
       </c>
       <c r="D230">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E230" t="s">
         <v>28</v>
@@ -8047,7 +8047,7 @@
         <v>27</v>
       </c>
       <c r="D231">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E231" t="s">
         <v>28</v>
@@ -8064,7 +8064,7 @@
         <v>27</v>
       </c>
       <c r="D232">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E232" t="s">
         <v>28</v>
@@ -8081,7 +8081,7 @@
         <v>27</v>
       </c>
       <c r="D233">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E233" t="s">
         <v>28</v>
@@ -8098,7 +8098,7 @@
         <v>27</v>
       </c>
       <c r="D234">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E234" t="s">
         <v>28</v>
@@ -8115,7 +8115,7 @@
         <v>27</v>
       </c>
       <c r="D235">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E235" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="D237">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E237" t="s">
         <v>28</v>
@@ -8166,7 +8166,7 @@
         <v>27</v>
       </c>
       <c r="D238">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E238" t="s">
         <v>28</v>
@@ -8183,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="D239">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E239" t="s">
         <v>28</v>
@@ -8200,7 +8200,7 @@
         <v>27</v>
       </c>
       <c r="D240">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E240" t="s">
         <v>28</v>
@@ -8217,7 +8217,7 @@
         <v>27</v>
       </c>
       <c r="D241">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E241" t="s">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>27</v>
       </c>
       <c r="D242">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E242" t="s">
         <v>28</v>
@@ -8251,7 +8251,7 @@
         <v>27</v>
       </c>
       <c r="D243">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E243" t="s">
         <v>28</v>
@@ -8268,7 +8268,7 @@
         <v>27</v>
       </c>
       <c r="D244">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E244" t="s">
         <v>28</v>
@@ -8285,7 +8285,7 @@
         <v>27</v>
       </c>
       <c r="D245">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E245" t="s">
         <v>28</v>
@@ -8302,7 +8302,7 @@
         <v>27</v>
       </c>
       <c r="D246">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E246" t="s">
         <v>28</v>
@@ -8319,7 +8319,7 @@
         <v>27</v>
       </c>
       <c r="D247">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E247" t="s">
         <v>28</v>
@@ -8336,7 +8336,7 @@
         <v>27</v>
       </c>
       <c r="D248">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E248" t="s">
         <v>28</v>
@@ -8353,7 +8353,7 @@
         <v>27</v>
       </c>
       <c r="D249">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E249" t="s">
         <v>28</v>
@@ -8370,7 +8370,7 @@
         <v>27</v>
       </c>
       <c r="D250">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E250" t="s">
         <v>28</v>
@@ -8387,7 +8387,7 @@
         <v>27</v>
       </c>
       <c r="D251">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E251" t="s">
         <v>28</v>
@@ -8404,7 +8404,7 @@
         <v>27</v>
       </c>
       <c r="D252">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E252" t="s">
         <v>28</v>
@@ -8421,7 +8421,7 @@
         <v>27</v>
       </c>
       <c r="D253">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E253" t="s">
         <v>28</v>
@@ -8438,7 +8438,7 @@
         <v>27</v>
       </c>
       <c r="D254">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E254" t="s">
         <v>28</v>
@@ -8455,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="D255">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E255" t="s">
         <v>28</v>
@@ -8472,7 +8472,7 @@
         <v>27</v>
       </c>
       <c r="D256">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E256" t="s">
         <v>28</v>
@@ -8489,7 +8489,7 @@
         <v>27</v>
       </c>
       <c r="D257">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E257" t="s">
         <v>28</v>
@@ -8506,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="D258">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E258" t="s">
         <v>28</v>
@@ -8523,7 +8523,7 @@
         <v>27</v>
       </c>
       <c r="D259">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E259" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="D260">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E260" t="s">
         <v>28</v>
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="D261">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E261" t="s">
         <v>28</v>
@@ -8574,7 +8574,7 @@
         <v>27</v>
       </c>
       <c r="D262">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E262" t="s">
         <v>28</v>
@@ -8591,7 +8591,7 @@
         <v>27</v>
       </c>
       <c r="D263">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E263" t="s">
         <v>28</v>
@@ -8608,7 +8608,7 @@
         <v>27</v>
       </c>
       <c r="D264">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E264" t="s">
         <v>28</v>
@@ -8625,7 +8625,7 @@
         <v>27</v>
       </c>
       <c r="D265">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E265" t="s">
         <v>28</v>
@@ -8642,7 +8642,7 @@
         <v>27</v>
       </c>
       <c r="D266">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E266" t="s">
         <v>28</v>
@@ -8659,7 +8659,7 @@
         <v>27</v>
       </c>
       <c r="D267">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E267" t="s">
         <v>28</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="D268">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E268" t="s">
         <v>28</v>
@@ -8693,7 +8693,7 @@
         <v>27</v>
       </c>
       <c r="D269">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E269" t="s">
         <v>28</v>
@@ -8710,7 +8710,7 @@
         <v>27</v>
       </c>
       <c r="D270">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E270" t="s">
         <v>28</v>
@@ -8727,7 +8727,7 @@
         <v>27</v>
       </c>
       <c r="D271">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E271" t="s">
         <v>28</v>
@@ -8744,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="D272">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E272" t="s">
         <v>28</v>
@@ -8761,7 +8761,7 @@
         <v>27</v>
       </c>
       <c r="D273">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E273" t="s">
         <v>28</v>
@@ -8778,7 +8778,7 @@
         <v>27</v>
       </c>
       <c r="D274">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E274" t="s">
         <v>28</v>
@@ -8795,7 +8795,7 @@
         <v>27</v>
       </c>
       <c r="D275">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E275" t="s">
         <v>28</v>
@@ -8812,7 +8812,7 @@
         <v>27</v>
       </c>
       <c r="D276">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E276" t="s">
         <v>28</v>
@@ -8829,7 +8829,7 @@
         <v>27</v>
       </c>
       <c r="D277">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E277" t="s">
         <v>28</v>
@@ -8846,7 +8846,7 @@
         <v>27</v>
       </c>
       <c r="D278">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E278" t="s">
         <v>28</v>
@@ -8863,7 +8863,7 @@
         <v>27</v>
       </c>
       <c r="D279">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E279" t="s">
         <v>28</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="D280">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E280" t="s">
         <v>28</v>
@@ -8897,7 +8897,7 @@
         <v>27</v>
       </c>
       <c r="D281">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E281" t="s">
         <v>28</v>
@@ -8914,7 +8914,7 @@
         <v>27</v>
       </c>
       <c r="D282">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E282" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="D283">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E283" t="s">
         <v>28</v>
@@ -8948,7 +8948,7 @@
         <v>27</v>
       </c>
       <c r="D284">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E284" t="s">
         <v>28</v>
@@ -8965,7 +8965,7 @@
         <v>27</v>
       </c>
       <c r="D285">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E285" t="s">
         <v>28</v>
@@ -8982,7 +8982,7 @@
         <v>27</v>
       </c>
       <c r="D286">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E286" t="s">
         <v>28</v>
@@ -8999,7 +8999,7 @@
         <v>27</v>
       </c>
       <c r="D287">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E287" t="s">
         <v>28</v>
@@ -9016,7 +9016,7 @@
         <v>27</v>
       </c>
       <c r="D288">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E288" t="s">
         <v>28</v>
@@ -9033,7 +9033,7 @@
         <v>27</v>
       </c>
       <c r="D289">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E289" t="s">
         <v>28</v>
@@ -9050,7 +9050,7 @@
         <v>27</v>
       </c>
       <c r="D290">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E290" t="s">
         <v>28</v>
@@ -9067,7 +9067,7 @@
         <v>27</v>
       </c>
       <c r="D291">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E291" t="s">
         <v>28</v>
@@ -9084,7 +9084,7 @@
         <v>27</v>
       </c>
       <c r="D292">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E292" t="s">
         <v>28</v>
@@ -9101,7 +9101,7 @@
         <v>27</v>
       </c>
       <c r="D293">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E293" t="s">
         <v>28</v>
@@ -9118,7 +9118,7 @@
         <v>27</v>
       </c>
       <c r="D294">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E294" t="s">
         <v>28</v>
@@ -9135,7 +9135,7 @@
         <v>27</v>
       </c>
       <c r="D295">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E295" t="s">
         <v>28</v>
@@ -9152,7 +9152,7 @@
         <v>27</v>
       </c>
       <c r="D296">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E296" t="s">
         <v>28</v>
@@ -9169,7 +9169,7 @@
         <v>27</v>
       </c>
       <c r="D297">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E297" t="s">
         <v>28</v>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="D298">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E298" t="s">
         <v>28</v>
@@ -9203,7 +9203,7 @@
         <v>27</v>
       </c>
       <c r="D299">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E299" t="s">
         <v>28</v>
@@ -9237,7 +9237,7 @@
         <v>27</v>
       </c>
       <c r="D301">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E301" t="s">
         <v>28</v>
@@ -9254,7 +9254,7 @@
         <v>27</v>
       </c>
       <c r="D302">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E302" t="s">
         <v>28</v>
@@ -9271,7 +9271,7 @@
         <v>27</v>
       </c>
       <c r="D303">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E303" t="s">
         <v>28</v>
@@ -9288,7 +9288,7 @@
         <v>27</v>
       </c>
       <c r="D304">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E304" t="s">
         <v>28</v>
@@ -9305,7 +9305,7 @@
         <v>27</v>
       </c>
       <c r="D305">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E305" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="D306">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E306" t="s">
         <v>28</v>
@@ -9339,7 +9339,7 @@
         <v>27</v>
       </c>
       <c r="D307">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E307" t="s">
         <v>28</v>
@@ -9356,7 +9356,7 @@
         <v>27</v>
       </c>
       <c r="D308">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E308" t="s">
         <v>28</v>
@@ -9373,7 +9373,7 @@
         <v>27</v>
       </c>
       <c r="D309">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E309" t="s">
         <v>28</v>
@@ -9390,7 +9390,7 @@
         <v>27</v>
       </c>
       <c r="D310">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E310" t="s">
         <v>28</v>
@@ -9407,7 +9407,7 @@
         <v>27</v>
       </c>
       <c r="D311">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E311" t="s">
         <v>28</v>
@@ -9424,7 +9424,7 @@
         <v>27</v>
       </c>
       <c r="D312">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E312" t="s">
         <v>28</v>
@@ -9441,7 +9441,7 @@
         <v>27</v>
       </c>
       <c r="D313">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E313" t="s">
         <v>28</v>
@@ -9475,7 +9475,7 @@
         <v>27</v>
       </c>
       <c r="D315">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E315" t="s">
         <v>28</v>
@@ -9492,7 +9492,7 @@
         <v>27</v>
       </c>
       <c r="D316">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E316" t="s">
         <v>28</v>
@@ -9509,7 +9509,7 @@
         <v>27</v>
       </c>
       <c r="D317">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E317" t="s">
         <v>28</v>
@@ -9526,7 +9526,7 @@
         <v>27</v>
       </c>
       <c r="D318">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E318" t="s">
         <v>28</v>
@@ -9543,7 +9543,7 @@
         <v>27</v>
       </c>
       <c r="D319">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E319" t="s">
         <v>28</v>
@@ -9560,7 +9560,7 @@
         <v>27</v>
       </c>
       <c r="D320">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E320" t="s">
         <v>28</v>
@@ -9577,7 +9577,7 @@
         <v>27</v>
       </c>
       <c r="D321">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E321" t="s">
         <v>28</v>
@@ -9594,7 +9594,7 @@
         <v>27</v>
       </c>
       <c r="D322">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E322" t="s">
         <v>28</v>
@@ -9611,7 +9611,7 @@
         <v>27</v>
       </c>
       <c r="D323">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E323" t="s">
         <v>28</v>
@@ -9628,7 +9628,7 @@
         <v>27</v>
       </c>
       <c r="D324">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E324" t="s">
         <v>28</v>
@@ -9645,7 +9645,7 @@
         <v>27</v>
       </c>
       <c r="D325">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E325" t="s">
         <v>28</v>
@@ -9662,7 +9662,7 @@
         <v>27</v>
       </c>
       <c r="D326">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E326" t="s">
         <v>28</v>
@@ -9679,7 +9679,7 @@
         <v>27</v>
       </c>
       <c r="D327">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E327" t="s">
         <v>28</v>
@@ -9696,7 +9696,7 @@
         <v>27</v>
       </c>
       <c r="D328">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E328" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="D329">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E329" t="s">
         <v>28</v>
@@ -9730,7 +9730,7 @@
         <v>27</v>
       </c>
       <c r="D330">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E330" t="s">
         <v>28</v>
@@ -9747,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="D331">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E331" t="s">
         <v>28</v>
@@ -9764,7 +9764,7 @@
         <v>27</v>
       </c>
       <c r="D332">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E332" t="s">
         <v>28</v>
@@ -9781,7 +9781,7 @@
         <v>27</v>
       </c>
       <c r="D333">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E333" t="s">
         <v>28</v>
@@ -9798,7 +9798,7 @@
         <v>27</v>
       </c>
       <c r="D334">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E334" t="s">
         <v>28</v>
@@ -9815,7 +9815,7 @@
         <v>27</v>
       </c>
       <c r="D335">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E335" t="s">
         <v>28</v>
@@ -9832,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="D336">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E336" t="s">
         <v>28</v>
@@ -9849,7 +9849,7 @@
         <v>27</v>
       </c>
       <c r="D337">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E337" t="s">
         <v>28</v>
@@ -9866,7 +9866,7 @@
         <v>27</v>
       </c>
       <c r="D338">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E338" t="s">
         <v>28</v>
@@ -9900,7 +9900,7 @@
         <v>27</v>
       </c>
       <c r="D340">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E340" t="s">
         <v>28</v>
@@ -9917,7 +9917,7 @@
         <v>27</v>
       </c>
       <c r="D341">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E341" t="s">
         <v>28</v>
@@ -9934,7 +9934,7 @@
         <v>27</v>
       </c>
       <c r="D342">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E342" t="s">
         <v>28</v>
@@ -9951,7 +9951,7 @@
         <v>27</v>
       </c>
       <c r="D343">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E343" t="s">
         <v>28</v>
@@ -9985,7 +9985,7 @@
         <v>27</v>
       </c>
       <c r="D345">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E345" t="s">
         <v>28</v>
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="D346">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E346" t="s">
         <v>28</v>
@@ -10019,7 +10019,7 @@
         <v>27</v>
       </c>
       <c r="D347">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E347" t="s">
         <v>28</v>
@@ -10036,7 +10036,7 @@
         <v>27</v>
       </c>
       <c r="D348">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E348" t="s">
         <v>28</v>
@@ -10053,7 +10053,7 @@
         <v>27</v>
       </c>
       <c r="D349">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E349" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="D350">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E350" t="s">
         <v>28</v>
@@ -10087,7 +10087,7 @@
         <v>27</v>
       </c>
       <c r="D351">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E351" t="s">
         <v>28</v>
@@ -10104,7 +10104,7 @@
         <v>27</v>
       </c>
       <c r="D352">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E352" t="s">
         <v>28</v>
@@ -10121,7 +10121,7 @@
         <v>27</v>
       </c>
       <c r="D353">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E353" t="s">
         <v>28</v>
@@ -10138,7 +10138,7 @@
         <v>27</v>
       </c>
       <c r="D354">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E354" t="s">
         <v>28</v>
@@ -10155,7 +10155,7 @@
         <v>27</v>
       </c>
       <c r="D355">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E355" t="s">
         <v>28</v>
@@ -10172,7 +10172,7 @@
         <v>27</v>
       </c>
       <c r="D356">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E356" t="s">
         <v>28</v>
@@ -10189,7 +10189,7 @@
         <v>27</v>
       </c>
       <c r="D357">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E357" t="s">
         <v>28</v>
@@ -10206,7 +10206,7 @@
         <v>27</v>
       </c>
       <c r="D358">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E358" t="s">
         <v>28</v>
@@ -10223,7 +10223,7 @@
         <v>27</v>
       </c>
       <c r="D359">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E359" t="s">
         <v>28</v>
@@ -10240,7 +10240,7 @@
         <v>27</v>
       </c>
       <c r="D360">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E360" t="s">
         <v>28</v>
@@ -10257,7 +10257,7 @@
         <v>27</v>
       </c>
       <c r="D361">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E361" t="s">
         <v>28</v>
@@ -10274,7 +10274,7 @@
         <v>27</v>
       </c>
       <c r="D362">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E362" t="s">
         <v>28</v>
@@ -10291,7 +10291,7 @@
         <v>27</v>
       </c>
       <c r="D363">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E363" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="D364">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E364" t="s">
         <v>28</v>
@@ -10325,7 +10325,7 @@
         <v>27</v>
       </c>
       <c r="D365">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E365" t="s">
         <v>28</v>
@@ -10342,7 +10342,7 @@
         <v>27</v>
       </c>
       <c r="D366">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E366" t="s">
         <v>28</v>
@@ -10359,7 +10359,7 @@
         <v>27</v>
       </c>
       <c r="D367">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E367" t="s">
         <v>28</v>
@@ -10376,7 +10376,7 @@
         <v>27</v>
       </c>
       <c r="D368">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E368" t="s">
         <v>28</v>
@@ -10393,7 +10393,7 @@
         <v>27</v>
       </c>
       <c r="D369">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E369" t="s">
         <v>28</v>
@@ -10410,7 +10410,7 @@
         <v>27</v>
       </c>
       <c r="D370">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E370" t="s">
         <v>28</v>
@@ -10427,7 +10427,7 @@
         <v>27</v>
       </c>
       <c r="D371">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E371" t="s">
         <v>28</v>
@@ -10444,7 +10444,7 @@
         <v>27</v>
       </c>
       <c r="D372">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E372" t="s">
         <v>28</v>
@@ -10461,7 +10461,7 @@
         <v>27</v>
       </c>
       <c r="D373">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E373" t="s">
         <v>28</v>
@@ -10478,7 +10478,7 @@
         <v>27</v>
       </c>
       <c r="D374">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E374" t="s">
         <v>28</v>
@@ -10512,7 +10512,7 @@
         <v>27</v>
       </c>
       <c r="D376">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E376" t="s">
         <v>28</v>
@@ -10529,7 +10529,7 @@
         <v>27</v>
       </c>
       <c r="D377">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E377" t="s">
         <v>28</v>
@@ -10546,7 +10546,7 @@
         <v>27</v>
       </c>
       <c r="D378">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E378" t="s">
         <v>28</v>
@@ -10563,7 +10563,7 @@
         <v>27</v>
       </c>
       <c r="D379">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E379" t="s">
         <v>28</v>
@@ -10580,7 +10580,7 @@
         <v>27</v>
       </c>
       <c r="D380">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E380" t="s">
         <v>28</v>
@@ -10614,7 +10614,7 @@
         <v>27</v>
       </c>
       <c r="D382">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E382" t="s">
         <v>28</v>
@@ -10631,7 +10631,7 @@
         <v>27</v>
       </c>
       <c r="D383">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E383" t="s">
         <v>28</v>
@@ -10648,7 +10648,7 @@
         <v>27</v>
       </c>
       <c r="D384">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E384" t="s">
         <v>28</v>
@@ -10665,7 +10665,7 @@
         <v>27</v>
       </c>
       <c r="D385">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E385" t="s">
         <v>28</v>
@@ -10682,7 +10682,7 @@
         <v>27</v>
       </c>
       <c r="D386">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E386" t="s">
         <v>28</v>
@@ -10716,7 +10716,7 @@
         <v>27</v>
       </c>
       <c r="D388">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E388" t="s">
         <v>28</v>
@@ -10733,7 +10733,7 @@
         <v>27</v>
       </c>
       <c r="D389">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E389" t="s">
         <v>28</v>
@@ -10750,7 +10750,7 @@
         <v>27</v>
       </c>
       <c r="D390">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E390" t="s">
         <v>28</v>
@@ -10767,7 +10767,7 @@
         <v>27</v>
       </c>
       <c r="D391">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E391" t="s">
         <v>28</v>
@@ -10784,7 +10784,7 @@
         <v>27</v>
       </c>
       <c r="D392">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E392" t="s">
         <v>28</v>
@@ -10801,7 +10801,7 @@
         <v>27</v>
       </c>
       <c r="D393">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E393" t="s">
         <v>28</v>
@@ -10818,7 +10818,7 @@
         <v>27</v>
       </c>
       <c r="D394">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E394" t="s">
         <v>28</v>
@@ -10835,7 +10835,7 @@
         <v>27</v>
       </c>
       <c r="D395">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E395" t="s">
         <v>28</v>
@@ -10852,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="D396">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E396" t="s">
         <v>28</v>
@@ -10886,7 +10886,7 @@
         <v>27</v>
       </c>
       <c r="D398">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E398" t="s">
         <v>28</v>
@@ -10920,7 +10920,7 @@
         <v>27</v>
       </c>
       <c r="D400">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E400" t="s">
         <v>28</v>
@@ -10937,7 +10937,7 @@
         <v>27</v>
       </c>
       <c r="D401">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E401" t="s">
         <v>28</v>
@@ -10971,7 +10971,7 @@
         <v>27</v>
       </c>
       <c r="D403">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E403" t="s">
         <v>28</v>
@@ -10988,7 +10988,7 @@
         <v>27</v>
       </c>
       <c r="D404">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E404" t="s">
         <v>28</v>
@@ -11005,7 +11005,7 @@
         <v>27</v>
       </c>
       <c r="D405">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E405" t="s">
         <v>28</v>
@@ -11022,7 +11022,7 @@
         <v>27</v>
       </c>
       <c r="D406">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E406" t="s">
         <v>28</v>
@@ -11039,7 +11039,7 @@
         <v>27</v>
       </c>
       <c r="D407">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E407" t="s">
         <v>28</v>
@@ -11056,7 +11056,7 @@
         <v>27</v>
       </c>
       <c r="D408">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E408" t="s">
         <v>28</v>
@@ -11073,7 +11073,7 @@
         <v>27</v>
       </c>
       <c r="D409">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E409" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="D410">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E410" t="s">
         <v>28</v>
@@ -11107,7 +11107,7 @@
         <v>27</v>
       </c>
       <c r="D411">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E411" t="s">
         <v>28</v>
@@ -11124,7 +11124,7 @@
         <v>27</v>
       </c>
       <c r="D412">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E412" t="s">
         <v>28</v>
@@ -11141,7 +11141,7 @@
         <v>27</v>
       </c>
       <c r="D413">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E413" t="s">
         <v>28</v>
@@ -11158,7 +11158,7 @@
         <v>27</v>
       </c>
       <c r="D414">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E414" t="s">
         <v>28</v>
@@ -11175,7 +11175,7 @@
         <v>27</v>
       </c>
       <c r="D415">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E415" t="s">
         <v>28</v>
@@ -11192,7 +11192,7 @@
         <v>27</v>
       </c>
       <c r="D416">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E416" t="s">
         <v>28</v>
@@ -11209,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="D417">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E417" t="s">
         <v>28</v>
@@ -11226,7 +11226,7 @@
         <v>27</v>
       </c>
       <c r="D418">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E418" t="s">
         <v>28</v>
@@ -11243,7 +11243,7 @@
         <v>27</v>
       </c>
       <c r="D419">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E419" t="s">
         <v>28</v>
@@ -11260,7 +11260,7 @@
         <v>27</v>
       </c>
       <c r="D420">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E420" t="s">
         <v>28</v>
@@ -11277,7 +11277,7 @@
         <v>27</v>
       </c>
       <c r="D421">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E421" t="s">
         <v>28</v>
@@ -11294,7 +11294,7 @@
         <v>27</v>
       </c>
       <c r="D422">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E422" t="s">
         <v>28</v>
@@ -11328,7 +11328,7 @@
         <v>27</v>
       </c>
       <c r="D424">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E424" t="s">
         <v>28</v>
@@ -11345,7 +11345,7 @@
         <v>27</v>
       </c>
       <c r="D425">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E425" t="s">
         <v>28</v>
@@ -11362,7 +11362,7 @@
         <v>27</v>
       </c>
       <c r="D426">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E426" t="s">
         <v>28</v>
@@ -11379,7 +11379,7 @@
         <v>27</v>
       </c>
       <c r="D427">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E427" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="D428">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E428" t="s">
         <v>28</v>
@@ -11413,7 +11413,7 @@
         <v>27</v>
       </c>
       <c r="D429">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E429" t="s">
         <v>28</v>
@@ -11430,7 +11430,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E430" t="s">
         <v>28</v>
@@ -11447,7 +11447,7 @@
         <v>27</v>
       </c>
       <c r="D431">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E431" t="s">
         <v>28</v>
@@ -11464,7 +11464,7 @@
         <v>27</v>
       </c>
       <c r="D432">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E432" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="D433">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E433" t="s">
         <v>28</v>
@@ -11498,7 +11498,7 @@
         <v>27</v>
       </c>
       <c r="D434">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E434" t="s">
         <v>28</v>
@@ -11515,7 +11515,7 @@
         <v>27</v>
       </c>
       <c r="D435">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E435" t="s">
         <v>28</v>
@@ -11549,7 +11549,7 @@
         <v>27</v>
       </c>
       <c r="D437">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E437" t="s">
         <v>28</v>
@@ -11566,7 +11566,7 @@
         <v>27</v>
       </c>
       <c r="D438">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E438" t="s">
         <v>28</v>
@@ -11583,7 +11583,7 @@
         <v>27</v>
       </c>
       <c r="D439">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E439" t="s">
         <v>28</v>
@@ -11600,7 +11600,7 @@
         <v>27</v>
       </c>
       <c r="D440">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E440" t="s">
         <v>28</v>
@@ -11617,7 +11617,7 @@
         <v>27</v>
       </c>
       <c r="D441">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E441" t="s">
         <v>28</v>
@@ -11634,7 +11634,7 @@
         <v>27</v>
       </c>
       <c r="D442">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E442" t="s">
         <v>28</v>
@@ -11651,7 +11651,7 @@
         <v>27</v>
       </c>
       <c r="D443">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E443" t="s">
         <v>28</v>
@@ -11668,7 +11668,7 @@
         <v>27</v>
       </c>
       <c r="D444">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E444" t="s">
         <v>28</v>
@@ -11702,7 +11702,7 @@
         <v>27</v>
       </c>
       <c r="D446">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E446" t="s">
         <v>28</v>
@@ -11719,7 +11719,7 @@
         <v>27</v>
       </c>
       <c r="D447">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E447" t="s">
         <v>28</v>
@@ -11736,7 +11736,7 @@
         <v>27</v>
       </c>
       <c r="D448">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E448" t="s">
         <v>28</v>
@@ -11753,7 +11753,7 @@
         <v>27</v>
       </c>
       <c r="D449">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E449" t="s">
         <v>28</v>
@@ -11787,7 +11787,7 @@
         <v>27</v>
       </c>
       <c r="D451">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E451" t="s">
         <v>28</v>
@@ -11804,7 +11804,7 @@
         <v>27</v>
       </c>
       <c r="D452">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E452" t="s">
         <v>28</v>
@@ -11821,7 +11821,7 @@
         <v>27</v>
       </c>
       <c r="D453">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E453" t="s">
         <v>28</v>
@@ -11838,7 +11838,7 @@
         <v>27</v>
       </c>
       <c r="D454">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E454" t="s">
         <v>28</v>
@@ -11855,7 +11855,7 @@
         <v>27</v>
       </c>
       <c r="D455">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E455" t="s">
         <v>28</v>
@@ -11889,7 +11889,7 @@
         <v>27</v>
       </c>
       <c r="D457">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E457" t="s">
         <v>28</v>
@@ -11906,7 +11906,7 @@
         <v>27</v>
       </c>
       <c r="D458">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E458" t="s">
         <v>28</v>
@@ -11923,7 +11923,7 @@
         <v>27</v>
       </c>
       <c r="D459">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E459" t="s">
         <v>28</v>
@@ -11940,7 +11940,7 @@
         <v>27</v>
       </c>
       <c r="D460">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E460" t="s">
         <v>28</v>
@@ -11957,7 +11957,7 @@
         <v>27</v>
       </c>
       <c r="D461">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E461" t="s">
         <v>28</v>
@@ -11974,7 +11974,7 @@
         <v>27</v>
       </c>
       <c r="D462">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E462" t="s">
         <v>28</v>
@@ -11991,7 +11991,7 @@
         <v>27</v>
       </c>
       <c r="D463">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E463" t="s">
         <v>28</v>
@@ -12008,7 +12008,7 @@
         <v>27</v>
       </c>
       <c r="D464">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E464" t="s">
         <v>28</v>
@@ -12025,7 +12025,7 @@
         <v>27</v>
       </c>
       <c r="D465">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E465" t="s">
         <v>28</v>
@@ -12042,7 +12042,7 @@
         <v>27</v>
       </c>
       <c r="D466">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E466" t="s">
         <v>28</v>
@@ -12059,7 +12059,7 @@
         <v>27</v>
       </c>
       <c r="D467">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E467" t="s">
         <v>28</v>
@@ -12076,7 +12076,7 @@
         <v>27</v>
       </c>
       <c r="D468">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E468" t="s">
         <v>28</v>
@@ -12093,7 +12093,7 @@
         <v>27</v>
       </c>
       <c r="D469">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E469" t="s">
         <v>28</v>
@@ -12110,7 +12110,7 @@
         <v>27</v>
       </c>
       <c r="D470">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E470" t="s">
         <v>28</v>
@@ -12127,7 +12127,7 @@
         <v>27</v>
       </c>
       <c r="D471">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E471" t="s">
         <v>28</v>
@@ -12144,7 +12144,7 @@
         <v>27</v>
       </c>
       <c r="D472">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E472" t="s">
         <v>28</v>
@@ -12161,7 +12161,7 @@
         <v>27</v>
       </c>
       <c r="D473">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E473" t="s">
         <v>28</v>
@@ -12178,7 +12178,7 @@
         <v>27</v>
       </c>
       <c r="D474">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E474" t="s">
         <v>28</v>
@@ -12195,7 +12195,7 @@
         <v>27</v>
       </c>
       <c r="D475">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E475" t="s">
         <v>28</v>
@@ -12212,7 +12212,7 @@
         <v>27</v>
       </c>
       <c r="D476">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E476" t="s">
         <v>28</v>
@@ -12229,7 +12229,7 @@
         <v>27</v>
       </c>
       <c r="D477">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E477" t="s">
         <v>28</v>
@@ -12246,7 +12246,7 @@
         <v>27</v>
       </c>
       <c r="D478">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E478" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="D479">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E479" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="D480">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E480" t="s">
         <v>28</v>
@@ -12297,7 +12297,7 @@
         <v>27</v>
       </c>
       <c r="D481">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E481" t="s">
         <v>28</v>
@@ -12314,7 +12314,7 @@
         <v>27</v>
       </c>
       <c r="D482">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E482" t="s">
         <v>28</v>
@@ -12331,7 +12331,7 @@
         <v>27</v>
       </c>
       <c r="D483">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E483" t="s">
         <v>28</v>
@@ -12365,7 +12365,7 @@
         <v>27</v>
       </c>
       <c r="D485">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E485" t="s">
         <v>28</v>
@@ -12382,7 +12382,7 @@
         <v>27</v>
       </c>
       <c r="D486">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E486" t="s">
         <v>28</v>
@@ -12399,7 +12399,7 @@
         <v>27</v>
       </c>
       <c r="D487">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E487" t="s">
         <v>28</v>
@@ -12416,7 +12416,7 @@
         <v>27</v>
       </c>
       <c r="D488">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E488" t="s">
         <v>28</v>
@@ -12433,7 +12433,7 @@
         <v>27</v>
       </c>
       <c r="D489">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E489" t="s">
         <v>28</v>
@@ -12450,7 +12450,7 @@
         <v>27</v>
       </c>
       <c r="D490">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E490" t="s">
         <v>28</v>
@@ -12467,7 +12467,7 @@
         <v>27</v>
       </c>
       <c r="D491">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E491" t="s">
         <v>28</v>
@@ -12484,7 +12484,7 @@
         <v>27</v>
       </c>
       <c r="D492">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E492" t="s">
         <v>28</v>
@@ -12501,7 +12501,7 @@
         <v>27</v>
       </c>
       <c r="D493">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E493" t="s">
         <v>28</v>
@@ -12535,7 +12535,7 @@
         <v>27</v>
       </c>
       <c r="D495">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E495" t="s">
         <v>28</v>
@@ -12552,7 +12552,7 @@
         <v>27</v>
       </c>
       <c r="D496">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E496" t="s">
         <v>28</v>
@@ -12569,7 +12569,7 @@
         <v>27</v>
       </c>
       <c r="D497">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E497" t="s">
         <v>28</v>
@@ -12586,7 +12586,7 @@
         <v>27</v>
       </c>
       <c r="D498">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E498" t="s">
         <v>28</v>
@@ -12603,7 +12603,7 @@
         <v>27</v>
       </c>
       <c r="D499">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E499" t="s">
         <v>28</v>
@@ -12620,7 +12620,7 @@
         <v>27</v>
       </c>
       <c r="D500">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E500" t="s">
         <v>28</v>
@@ -12637,7 +12637,7 @@
         <v>27</v>
       </c>
       <c r="D501">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E501" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="D502">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E502" t="s">
         <v>28</v>
@@ -12671,7 +12671,7 @@
         <v>27</v>
       </c>
       <c r="D503">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E503" t="s">
         <v>28</v>
@@ -12688,7 +12688,7 @@
         <v>27</v>
       </c>
       <c r="D504">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E504" t="s">
         <v>28</v>
@@ -12705,7 +12705,7 @@
         <v>27</v>
       </c>
       <c r="D505">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E505" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="D506">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E506" t="s">
         <v>28</v>
@@ -12739,7 +12739,7 @@
         <v>27</v>
       </c>
       <c r="D507">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E507" t="s">
         <v>28</v>
@@ -12756,7 +12756,7 @@
         <v>27</v>
       </c>
       <c r="D508">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E508" t="s">
         <v>28</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="D509">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E509" t="s">
         <v>28</v>
@@ -12790,7 +12790,7 @@
         <v>27</v>
       </c>
       <c r="D510">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E510" t="s">
         <v>28</v>
@@ -12807,7 +12807,7 @@
         <v>27</v>
       </c>
       <c r="D511">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E511" t="s">
         <v>28</v>
@@ -12824,7 +12824,7 @@
         <v>27</v>
       </c>
       <c r="D512">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E512" t="s">
         <v>28</v>
@@ -12841,7 +12841,7 @@
         <v>27</v>
       </c>
       <c r="D513">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E513" t="s">
         <v>28</v>
@@ -12858,7 +12858,7 @@
         <v>27</v>
       </c>
       <c r="D514">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E514" t="s">
         <v>28</v>
@@ -12875,7 +12875,7 @@
         <v>27</v>
       </c>
       <c r="D515">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E515" t="s">
         <v>28</v>
@@ -12892,7 +12892,7 @@
         <v>27</v>
       </c>
       <c r="D516">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E516" t="s">
         <v>28</v>
@@ -12909,7 +12909,7 @@
         <v>27</v>
       </c>
       <c r="D517">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E517" t="s">
         <v>28</v>
@@ -12926,7 +12926,7 @@
         <v>27</v>
       </c>
       <c r="D518">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E518" t="s">
         <v>28</v>
@@ -12943,7 +12943,7 @@
         <v>27</v>
       </c>
       <c r="D519">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E519" t="s">
         <v>28</v>
@@ -12960,7 +12960,7 @@
         <v>27</v>
       </c>
       <c r="D520">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E520" t="s">
         <v>28</v>
@@ -12977,7 +12977,7 @@
         <v>27</v>
       </c>
       <c r="D521">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E521" t="s">
         <v>28</v>
@@ -12994,7 +12994,7 @@
         <v>27</v>
       </c>
       <c r="D522">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E522" t="s">
         <v>28</v>
@@ -13011,7 +13011,7 @@
         <v>27</v>
       </c>
       <c r="D523">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E523" t="s">
         <v>28</v>
@@ -13028,7 +13028,7 @@
         <v>27</v>
       </c>
       <c r="D524">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E524" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="D525">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E525" t="s">
         <v>28</v>
@@ -13062,7 +13062,7 @@
         <v>27</v>
       </c>
       <c r="D526">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E526" t="s">
         <v>28</v>
@@ -13079,7 +13079,7 @@
         <v>27</v>
       </c>
       <c r="D527">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E527" t="s">
         <v>28</v>
@@ -13096,7 +13096,7 @@
         <v>27</v>
       </c>
       <c r="D528">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E528" t="s">
         <v>28</v>
@@ -13113,7 +13113,7 @@
         <v>27</v>
       </c>
       <c r="D529">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E529" t="s">
         <v>28</v>
@@ -13130,7 +13130,7 @@
         <v>27</v>
       </c>
       <c r="D530">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E530" t="s">
         <v>28</v>
@@ -13147,7 +13147,7 @@
         <v>27</v>
       </c>
       <c r="D531">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E531" t="s">
         <v>28</v>
@@ -13164,7 +13164,7 @@
         <v>27</v>
       </c>
       <c r="D532">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E532" t="s">
         <v>28</v>
@@ -13181,7 +13181,7 @@
         <v>27</v>
       </c>
       <c r="D533">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E533" t="s">
         <v>28</v>
@@ -13198,7 +13198,7 @@
         <v>27</v>
       </c>
       <c r="D534">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E534" t="s">
         <v>28</v>
@@ -13215,7 +13215,7 @@
         <v>27</v>
       </c>
       <c r="D535">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E535" t="s">
         <v>28</v>
@@ -13232,7 +13232,7 @@
         <v>27</v>
       </c>
       <c r="D536">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E536" t="s">
         <v>28</v>
@@ -13249,7 +13249,7 @@
         <v>27</v>
       </c>
       <c r="D537">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E537" t="s">
         <v>28</v>
@@ -13266,7 +13266,7 @@
         <v>27</v>
       </c>
       <c r="D538">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E538" t="s">
         <v>28</v>
@@ -13283,7 +13283,7 @@
         <v>27</v>
       </c>
       <c r="D539">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E539" t="s">
         <v>28</v>
@@ -13300,7 +13300,7 @@
         <v>27</v>
       </c>
       <c r="D540">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E540" t="s">
         <v>28</v>
@@ -13317,7 +13317,7 @@
         <v>27</v>
       </c>
       <c r="D541">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E541" t="s">
         <v>28</v>
@@ -13334,7 +13334,7 @@
         <v>27</v>
       </c>
       <c r="D542">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E542" t="s">
         <v>28</v>
@@ -13351,7 +13351,7 @@
         <v>27</v>
       </c>
       <c r="D543">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E543" t="s">
         <v>28</v>
@@ -13368,7 +13368,7 @@
         <v>27</v>
       </c>
       <c r="D544">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E544" t="s">
         <v>28</v>
@@ -13385,7 +13385,7 @@
         <v>27</v>
       </c>
       <c r="D545">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E545" t="s">
         <v>28</v>
@@ -13402,7 +13402,7 @@
         <v>27</v>
       </c>
       <c r="D546">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E546" t="s">
         <v>28</v>
@@ -13419,7 +13419,7 @@
         <v>27</v>
       </c>
       <c r="D547">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E547" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="D548">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E548" t="s">
         <v>28</v>
@@ -13453,7 +13453,7 @@
         <v>27</v>
       </c>
       <c r="D549">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E549" t="s">
         <v>28</v>
@@ -13470,7 +13470,7 @@
         <v>27</v>
       </c>
       <c r="D550">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E550" t="s">
         <v>28</v>
@@ -13487,7 +13487,7 @@
         <v>27</v>
       </c>
       <c r="D551">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E551" t="s">
         <v>28</v>
@@ -13504,7 +13504,7 @@
         <v>27</v>
       </c>
       <c r="D552">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E552" t="s">
         <v>28</v>
@@ -13521,7 +13521,7 @@
         <v>27</v>
       </c>
       <c r="D553">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E553" t="s">
         <v>28</v>
@@ -13538,7 +13538,7 @@
         <v>27</v>
       </c>
       <c r="D554">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E554" t="s">
         <v>28</v>
@@ -13555,7 +13555,7 @@
         <v>27</v>
       </c>
       <c r="D555">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E555" t="s">
         <v>28</v>
@@ -13572,7 +13572,7 @@
         <v>27</v>
       </c>
       <c r="D556">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E556" t="s">
         <v>28</v>
@@ -13589,7 +13589,7 @@
         <v>27</v>
       </c>
       <c r="D557">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E557" t="s">
         <v>28</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="D558">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E558" t="s">
         <v>28</v>
@@ -13623,7 +13623,7 @@
         <v>27</v>
       </c>
       <c r="D559">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E559" t="s">
         <v>28</v>
@@ -13640,7 +13640,7 @@
         <v>27</v>
       </c>
       <c r="D560">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E560" t="s">
         <v>28</v>
@@ -13657,7 +13657,7 @@
         <v>27</v>
       </c>
       <c r="D561">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E561" t="s">
         <v>28</v>
@@ -13674,7 +13674,7 @@
         <v>27</v>
       </c>
       <c r="D562">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E562" t="s">
         <v>28</v>
@@ -13691,7 +13691,7 @@
         <v>27</v>
       </c>
       <c r="D563">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E563" t="s">
         <v>28</v>
@@ -13708,7 +13708,7 @@
         <v>27</v>
       </c>
       <c r="D564">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E564" t="s">
         <v>28</v>
@@ -13725,7 +13725,7 @@
         <v>27</v>
       </c>
       <c r="D565">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E565" t="s">
         <v>28</v>
@@ -13742,7 +13742,7 @@
         <v>27</v>
       </c>
       <c r="D566">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E566" t="s">
         <v>28</v>
@@ -13759,7 +13759,7 @@
         <v>27</v>
       </c>
       <c r="D567">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E567" t="s">
         <v>28</v>
@@ -13776,7 +13776,7 @@
         <v>27</v>
       </c>
       <c r="D568">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E568" t="s">
         <v>28</v>
@@ -13793,7 +13793,7 @@
         <v>27</v>
       </c>
       <c r="D569">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E569" t="s">
         <v>28</v>
@@ -13810,7 +13810,7 @@
         <v>27</v>
       </c>
       <c r="D570">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E570" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="D571">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E571" t="s">
         <v>28</v>
@@ -13844,7 +13844,7 @@
         <v>27</v>
       </c>
       <c r="D572">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E572" t="s">
         <v>28</v>
@@ -13861,7 +13861,7 @@
         <v>27</v>
       </c>
       <c r="D573">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E573" t="s">
         <v>28</v>
@@ -13878,7 +13878,7 @@
         <v>27</v>
       </c>
       <c r="D574">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E574" t="s">
         <v>28</v>
@@ -13895,7 +13895,7 @@
         <v>27</v>
       </c>
       <c r="D575">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E575" t="s">
         <v>28</v>
@@ -13912,7 +13912,7 @@
         <v>27</v>
       </c>
       <c r="D576">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E576" t="s">
         <v>28</v>
@@ -13929,7 +13929,7 @@
         <v>27</v>
       </c>
       <c r="D577">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E577" t="s">
         <v>28</v>
@@ -13946,7 +13946,7 @@
         <v>27</v>
       </c>
       <c r="D578">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E578" t="s">
         <v>28</v>
@@ -13980,7 +13980,7 @@
         <v>27</v>
       </c>
       <c r="D580">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E580" t="s">
         <v>28</v>
@@ -13997,7 +13997,7 @@
         <v>27</v>
       </c>
       <c r="D581">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E581" t="s">
         <v>28</v>
@@ -14014,7 +14014,7 @@
         <v>27</v>
       </c>
       <c r="D582">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E582" t="s">
         <v>28</v>
@@ -14031,7 +14031,7 @@
         <v>27</v>
       </c>
       <c r="D583">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E583" t="s">
         <v>28</v>
@@ -14048,7 +14048,7 @@
         <v>27</v>
       </c>
       <c r="D584">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E584" t="s">
         <v>28</v>
@@ -14065,7 +14065,7 @@
         <v>27</v>
       </c>
       <c r="D585">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E585" t="s">
         <v>28</v>
@@ -14082,7 +14082,7 @@
         <v>27</v>
       </c>
       <c r="D586">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E586" t="s">
         <v>28</v>
@@ -14099,7 +14099,7 @@
         <v>27</v>
       </c>
       <c r="D587">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E587" t="s">
         <v>28</v>
@@ -14116,7 +14116,7 @@
         <v>27</v>
       </c>
       <c r="D588">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E588" t="s">
         <v>28</v>
@@ -14133,7 +14133,7 @@
         <v>27</v>
       </c>
       <c r="D589">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E589" t="s">
         <v>28</v>
@@ -14150,7 +14150,7 @@
         <v>27</v>
       </c>
       <c r="D590">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E590" t="s">
         <v>28</v>
@@ -14167,7 +14167,7 @@
         <v>27</v>
       </c>
       <c r="D591">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E591" t="s">
         <v>28</v>
@@ -14184,7 +14184,7 @@
         <v>27</v>
       </c>
       <c r="D592">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E592" t="s">
         <v>28</v>
@@ -14201,7 +14201,7 @@
         <v>27</v>
       </c>
       <c r="D593">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E593" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="D594">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E594" t="s">
         <v>28</v>
@@ -14235,7 +14235,7 @@
         <v>27</v>
       </c>
       <c r="D595">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E595" t="s">
         <v>28</v>
@@ -14252,7 +14252,7 @@
         <v>27</v>
       </c>
       <c r="D596">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E596" t="s">
         <v>28</v>
@@ -14269,7 +14269,7 @@
         <v>27</v>
       </c>
       <c r="D597">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E597" t="s">
         <v>28</v>
@@ -14286,7 +14286,7 @@
         <v>27</v>
       </c>
       <c r="D598">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E598" t="s">
         <v>28</v>
@@ -14303,7 +14303,7 @@
         <v>27</v>
       </c>
       <c r="D599">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E599" t="s">
         <v>28</v>
@@ -14320,7 +14320,7 @@
         <v>27</v>
       </c>
       <c r="D600">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E600" t="s">
         <v>28</v>
@@ -14337,7 +14337,7 @@
         <v>27</v>
       </c>
       <c r="D601">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E601" t="s">
         <v>28</v>
@@ -14354,7 +14354,7 @@
         <v>27</v>
       </c>
       <c r="D602">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E602" t="s">
         <v>28</v>
@@ -14371,7 +14371,7 @@
         <v>27</v>
       </c>
       <c r="D603">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E603" t="s">
         <v>28</v>
@@ -14388,7 +14388,7 @@
         <v>27</v>
       </c>
       <c r="D604">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E604" t="s">
         <v>28</v>
@@ -14422,7 +14422,7 @@
         <v>27</v>
       </c>
       <c r="D606">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E606" t="s">
         <v>28</v>
@@ -14439,7 +14439,7 @@
         <v>27</v>
       </c>
       <c r="D607">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E607" t="s">
         <v>28</v>
@@ -14456,7 +14456,7 @@
         <v>27</v>
       </c>
       <c r="D608">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E608" t="s">
         <v>28</v>
@@ -14473,7 +14473,7 @@
         <v>27</v>
       </c>
       <c r="D609">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E609" t="s">
         <v>28</v>
@@ -14490,7 +14490,7 @@
         <v>27</v>
       </c>
       <c r="D610">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E610" t="s">
         <v>28</v>
@@ -14507,7 +14507,7 @@
         <v>27</v>
       </c>
       <c r="D611">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E611" t="s">
         <v>28</v>
@@ -14524,7 +14524,7 @@
         <v>27</v>
       </c>
       <c r="D612">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E612" t="s">
         <v>28</v>
@@ -14558,7 +14558,7 @@
         <v>27</v>
       </c>
       <c r="D614">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E614" t="s">
         <v>28</v>
@@ -14575,7 +14575,7 @@
         <v>27</v>
       </c>
       <c r="D615">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E615" t="s">
         <v>28</v>
@@ -14592,7 +14592,7 @@
         <v>27</v>
       </c>
       <c r="D616">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E616" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="D617">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E617" t="s">
         <v>28</v>
@@ -14626,7 +14626,7 @@
         <v>27</v>
       </c>
       <c r="D618">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E618" t="s">
         <v>28</v>
@@ -14643,7 +14643,7 @@
         <v>27</v>
       </c>
       <c r="D619">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E619" t="s">
         <v>28</v>
@@ -14660,7 +14660,7 @@
         <v>27</v>
       </c>
       <c r="D620">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E620" t="s">
         <v>28</v>
@@ -14677,7 +14677,7 @@
         <v>27</v>
       </c>
       <c r="D621">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E621" t="s">
         <v>28</v>
@@ -14694,7 +14694,7 @@
         <v>27</v>
       </c>
       <c r="D622">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E622" t="s">
         <v>28</v>
@@ -14711,7 +14711,7 @@
         <v>27</v>
       </c>
       <c r="D623">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E623" t="s">
         <v>28</v>
@@ -14728,7 +14728,7 @@
         <v>27</v>
       </c>
       <c r="D624">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E624" t="s">
         <v>28</v>
@@ -14745,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="D625">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E625" t="s">
         <v>28</v>
@@ -14779,7 +14779,7 @@
         <v>27</v>
       </c>
       <c r="D627">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E627" t="s">
         <v>28</v>
@@ -14796,7 +14796,7 @@
         <v>27</v>
       </c>
       <c r="D628">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E628" t="s">
         <v>28</v>
@@ -14813,7 +14813,7 @@
         <v>27</v>
       </c>
       <c r="D629">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E629" t="s">
         <v>28</v>
@@ -14830,7 +14830,7 @@
         <v>27</v>
       </c>
       <c r="D630">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E630" t="s">
         <v>28</v>
@@ -14847,7 +14847,7 @@
         <v>27</v>
       </c>
       <c r="D631">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E631" t="s">
         <v>28</v>
@@ -14864,7 +14864,7 @@
         <v>27</v>
       </c>
       <c r="D632">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E632" t="s">
         <v>28</v>
@@ -14881,7 +14881,7 @@
         <v>27</v>
       </c>
       <c r="D633">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E633" t="s">
         <v>28</v>
@@ -14898,7 +14898,7 @@
         <v>27</v>
       </c>
       <c r="D634">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E634" t="s">
         <v>28</v>
@@ -14915,7 +14915,7 @@
         <v>27</v>
       </c>
       <c r="D635">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E635" t="s">
         <v>28</v>
@@ -14932,7 +14932,7 @@
         <v>27</v>
       </c>
       <c r="D636">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E636" t="s">
         <v>28</v>
@@ -14949,7 +14949,7 @@
         <v>27</v>
       </c>
       <c r="D637">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E637" t="s">
         <v>28</v>
@@ -14966,7 +14966,7 @@
         <v>27</v>
       </c>
       <c r="D638">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E638" t="s">
         <v>28</v>
@@ -14983,7 +14983,7 @@
         <v>27</v>
       </c>
       <c r="D639">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E639" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="D640">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E640" t="s">
         <v>28</v>
@@ -15017,7 +15017,7 @@
         <v>27</v>
       </c>
       <c r="D641">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E641" t="s">
         <v>28</v>
@@ -15051,7 +15051,7 @@
         <v>27</v>
       </c>
       <c r="D643">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E643" t="s">
         <v>28</v>
@@ -15068,7 +15068,7 @@
         <v>27</v>
       </c>
       <c r="D644">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E644" t="s">
         <v>28</v>
@@ -15085,7 +15085,7 @@
         <v>27</v>
       </c>
       <c r="D645">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E645" t="s">
         <v>28</v>
@@ -15102,7 +15102,7 @@
         <v>27</v>
       </c>
       <c r="D646">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E646" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>27</v>
       </c>
       <c r="D647">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E647" t="s">
         <v>28</v>
@@ -15136,7 +15136,7 @@
         <v>27</v>
       </c>
       <c r="D648">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E648" t="s">
         <v>28</v>
@@ -15153,7 +15153,7 @@
         <v>27</v>
       </c>
       <c r="D649">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E649" t="s">
         <v>28</v>
@@ -15170,7 +15170,7 @@
         <v>27</v>
       </c>
       <c r="D650">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E650" t="s">
         <v>28</v>
@@ -15187,7 +15187,7 @@
         <v>27</v>
       </c>
       <c r="D651">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E651" t="s">
         <v>28</v>
@@ -15204,7 +15204,7 @@
         <v>27</v>
       </c>
       <c r="D652">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E652" t="s">
         <v>28</v>
@@ -15221,7 +15221,7 @@
         <v>27</v>
       </c>
       <c r="D653">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E653" t="s">
         <v>28</v>
@@ -15238,7 +15238,7 @@
         <v>27</v>
       </c>
       <c r="D654">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E654" t="s">
         <v>28</v>
@@ -15255,7 +15255,7 @@
         <v>27</v>
       </c>
       <c r="D655">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E655" t="s">
         <v>28</v>
@@ -15272,7 +15272,7 @@
         <v>27</v>
       </c>
       <c r="D656">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E656" t="s">
         <v>28</v>
@@ -15289,7 +15289,7 @@
         <v>27</v>
       </c>
       <c r="D657">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E657" t="s">
         <v>28</v>
@@ -15306,7 +15306,7 @@
         <v>27</v>
       </c>
       <c r="D658">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E658" t="s">
         <v>28</v>
@@ -15323,7 +15323,7 @@
         <v>27</v>
       </c>
       <c r="D659">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E659" t="s">
         <v>28</v>
@@ -15340,7 +15340,7 @@
         <v>27</v>
       </c>
       <c r="D660">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E660" t="s">
         <v>28</v>
@@ -15357,7 +15357,7 @@
         <v>27</v>
       </c>
       <c r="D661">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E661" t="s">
         <v>28</v>
@@ -15374,7 +15374,7 @@
         <v>27</v>
       </c>
       <c r="D662">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E662" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="D663">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E663" t="s">
         <v>28</v>
@@ -15425,7 +15425,7 @@
         <v>27</v>
       </c>
       <c r="D665">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E665" t="s">
         <v>28</v>
@@ -15442,7 +15442,7 @@
         <v>27</v>
       </c>
       <c r="D666">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E666" t="s">
         <v>28</v>
@@ -15459,7 +15459,7 @@
         <v>27</v>
       </c>
       <c r="D667">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E667" t="s">
         <v>28</v>
@@ -15476,7 +15476,7 @@
         <v>27</v>
       </c>
       <c r="D668">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E668" t="s">
         <v>28</v>
@@ -15493,7 +15493,7 @@
         <v>27</v>
       </c>
       <c r="D669">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E669" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>27</v>
       </c>
       <c r="D670">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E670" t="s">
         <v>28</v>
@@ -15527,7 +15527,7 @@
         <v>27</v>
       </c>
       <c r="D671">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E671" t="s">
         <v>28</v>
@@ -15544,7 +15544,7 @@
         <v>27</v>
       </c>
       <c r="D672">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E672" t="s">
         <v>28</v>
@@ -15578,7 +15578,7 @@
         <v>27</v>
       </c>
       <c r="D674">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E674" t="s">
         <v>28</v>
@@ -15595,7 +15595,7 @@
         <v>27</v>
       </c>
       <c r="D675">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E675" t="s">
         <v>28</v>
@@ -15612,7 +15612,7 @@
         <v>27</v>
       </c>
       <c r="D676">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E676" t="s">
         <v>28</v>
@@ -15629,7 +15629,7 @@
         <v>27</v>
       </c>
       <c r="D677">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E677" t="s">
         <v>28</v>
@@ -15663,7 +15663,7 @@
         <v>27</v>
       </c>
       <c r="D679">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E679" t="s">
         <v>28</v>
@@ -15680,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="D680">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E680" t="s">
         <v>28</v>
@@ -15697,7 +15697,7 @@
         <v>27</v>
       </c>
       <c r="D681">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E681" t="s">
         <v>28</v>
@@ -15714,7 +15714,7 @@
         <v>27</v>
       </c>
       <c r="D682">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E682" t="s">
         <v>28</v>
@@ -15731,7 +15731,7 @@
         <v>27</v>
       </c>
       <c r="D683">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E683" t="s">
         <v>28</v>
@@ -15748,7 +15748,7 @@
         <v>27</v>
       </c>
       <c r="D684">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E684" t="s">
         <v>28</v>
@@ -15765,7 +15765,7 @@
         <v>27</v>
       </c>
       <c r="D685">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E685" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="D686">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E686" t="s">
         <v>28</v>
@@ -15816,7 +15816,7 @@
         <v>27</v>
       </c>
       <c r="D688">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E688" t="s">
         <v>28</v>
@@ -15833,7 +15833,7 @@
         <v>27</v>
       </c>
       <c r="D689">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E689" t="s">
         <v>28</v>
@@ -15850,7 +15850,7 @@
         <v>27</v>
       </c>
       <c r="D690">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E690" t="s">
         <v>28</v>
@@ -15867,7 +15867,7 @@
         <v>27</v>
       </c>
       <c r="D691">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E691" t="s">
         <v>28</v>
@@ -15901,7 +15901,7 @@
         <v>27</v>
       </c>
       <c r="D693">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E693" t="s">
         <v>28</v>
@@ -15918,7 +15918,7 @@
         <v>27</v>
       </c>
       <c r="D694">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E694" t="s">
         <v>28</v>
@@ -15935,7 +15935,7 @@
         <v>27</v>
       </c>
       <c r="D695">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E695" t="s">
         <v>28</v>
@@ -15952,7 +15952,7 @@
         <v>27</v>
       </c>
       <c r="D696">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E696" t="s">
         <v>28</v>
@@ -15969,7 +15969,7 @@
         <v>27</v>
       </c>
       <c r="D697">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E697" t="s">
         <v>28</v>
@@ -15986,7 +15986,7 @@
         <v>27</v>
       </c>
       <c r="D698">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E698" t="s">
         <v>28</v>
@@ -16003,7 +16003,7 @@
         <v>27</v>
       </c>
       <c r="D699">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E699" t="s">
         <v>28</v>
@@ -16020,7 +16020,7 @@
         <v>27</v>
       </c>
       <c r="D700">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E700" t="s">
         <v>28</v>
@@ -16037,7 +16037,7 @@
         <v>27</v>
       </c>
       <c r="D701">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E701" t="s">
         <v>28</v>
@@ -16054,7 +16054,7 @@
         <v>27</v>
       </c>
       <c r="D702">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E702" t="s">
         <v>28</v>
@@ -16071,7 +16071,7 @@
         <v>27</v>
       </c>
       <c r="D703">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E703" t="s">
         <v>28</v>
@@ -16088,7 +16088,7 @@
         <v>27</v>
       </c>
       <c r="D704">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E704" t="s">
         <v>28</v>
@@ -16105,7 +16105,7 @@
         <v>27</v>
       </c>
       <c r="D705">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E705" t="s">
         <v>28</v>
@@ -16122,7 +16122,7 @@
         <v>27</v>
       </c>
       <c r="D706">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E706" t="s">
         <v>28</v>
@@ -16139,7 +16139,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E707" t="s">
         <v>28</v>
@@ -16156,7 +16156,7 @@
         <v>27</v>
       </c>
       <c r="D708">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E708" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="D709">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E709" t="s">
         <v>28</v>
@@ -16190,7 +16190,7 @@
         <v>27</v>
       </c>
       <c r="D710">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E710" t="s">
         <v>28</v>
@@ -16207,7 +16207,7 @@
         <v>27</v>
       </c>
       <c r="D711">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E711" t="s">
         <v>28</v>
@@ -16224,7 +16224,7 @@
         <v>27</v>
       </c>
       <c r="D712">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E712" t="s">
         <v>28</v>
@@ -16241,7 +16241,7 @@
         <v>27</v>
       </c>
       <c r="D713">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E713" t="s">
         <v>28</v>
@@ -16258,7 +16258,7 @@
         <v>27</v>
       </c>
       <c r="D714">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E714" t="s">
         <v>28</v>
@@ -16275,7 +16275,7 @@
         <v>27</v>
       </c>
       <c r="D715">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E715" t="s">
         <v>28</v>
@@ -16292,7 +16292,7 @@
         <v>27</v>
       </c>
       <c r="D716">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E716" t="s">
         <v>28</v>
@@ -16309,7 +16309,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E717" t="s">
         <v>28</v>
@@ -16326,7 +16326,7 @@
         <v>27</v>
       </c>
       <c r="D718">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E718" t="s">
         <v>28</v>
@@ -16343,7 +16343,7 @@
         <v>27</v>
       </c>
       <c r="D719">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E719" t="s">
         <v>28</v>
@@ -16360,7 +16360,7 @@
         <v>27</v>
       </c>
       <c r="D720">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E720" t="s">
         <v>28</v>
@@ -16377,7 +16377,7 @@
         <v>27</v>
       </c>
       <c r="D721">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E721" t="s">
         <v>28</v>
@@ -16394,7 +16394,7 @@
         <v>27</v>
       </c>
       <c r="D722">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E722" t="s">
         <v>28</v>
@@ -16411,7 +16411,7 @@
         <v>27</v>
       </c>
       <c r="D723">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E723" t="s">
         <v>28</v>
@@ -16428,7 +16428,7 @@
         <v>27</v>
       </c>
       <c r="D724">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E724" t="s">
         <v>28</v>
@@ -16445,7 +16445,7 @@
         <v>27</v>
       </c>
       <c r="D725">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E725" t="s">
         <v>28</v>
@@ -16462,7 +16462,7 @@
         <v>27</v>
       </c>
       <c r="D726">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E726" t="s">
         <v>28</v>
@@ -16479,7 +16479,7 @@
         <v>27</v>
       </c>
       <c r="D727">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E727" t="s">
         <v>28</v>
@@ -16496,7 +16496,7 @@
         <v>27</v>
       </c>
       <c r="D728">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E728" t="s">
         <v>28</v>
@@ -16530,7 +16530,7 @@
         <v>27</v>
       </c>
       <c r="D730">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E730" t="s">
         <v>28</v>
@@ -16547,7 +16547,7 @@
         <v>27</v>
       </c>
       <c r="D731">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E731" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="D732">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E732" t="s">
         <v>28</v>
@@ -16581,7 +16581,7 @@
         <v>27</v>
       </c>
       <c r="D733">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E733" t="s">
         <v>28</v>
@@ -16598,7 +16598,7 @@
         <v>27</v>
       </c>
       <c r="D734">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E734" t="s">
         <v>28</v>
@@ -16615,7 +16615,7 @@
         <v>27</v>
       </c>
       <c r="D735">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E735" t="s">
         <v>28</v>
@@ -16632,7 +16632,7 @@
         <v>27</v>
       </c>
       <c r="D736">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E736" t="s">
         <v>28</v>
@@ -16649,7 +16649,7 @@
         <v>27</v>
       </c>
       <c r="D737">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E737" t="s">
         <v>28</v>
@@ -16666,7 +16666,7 @@
         <v>27</v>
       </c>
       <c r="D738">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E738" t="s">
         <v>28</v>
@@ -16683,7 +16683,7 @@
         <v>27</v>
       </c>
       <c r="D739">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E739" t="s">
         <v>28</v>
@@ -16700,7 +16700,7 @@
         <v>27</v>
       </c>
       <c r="D740">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E740" t="s">
         <v>28</v>
@@ -16717,7 +16717,7 @@
         <v>27</v>
       </c>
       <c r="D741">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E741" t="s">
         <v>28</v>
@@ -16734,7 +16734,7 @@
         <v>27</v>
       </c>
       <c r="D742">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E742" t="s">
         <v>28</v>
@@ -16751,7 +16751,7 @@
         <v>27</v>
       </c>
       <c r="D743">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E743" t="s">
         <v>28</v>
@@ -16768,7 +16768,7 @@
         <v>27</v>
       </c>
       <c r="D744">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E744" t="s">
         <v>28</v>
@@ -16785,7 +16785,7 @@
         <v>27</v>
       </c>
       <c r="D745">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E745" t="s">
         <v>28</v>
@@ -16802,7 +16802,7 @@
         <v>27</v>
       </c>
       <c r="D746">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E746" t="s">
         <v>28</v>
@@ -16819,7 +16819,7 @@
         <v>27</v>
       </c>
       <c r="D747">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E747" t="s">
         <v>28</v>
@@ -16836,7 +16836,7 @@
         <v>27</v>
       </c>
       <c r="D748">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E748" t="s">
         <v>28</v>
@@ -16853,7 +16853,7 @@
         <v>27</v>
       </c>
       <c r="D749">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E749" t="s">
         <v>28</v>
@@ -16870,7 +16870,7 @@
         <v>27</v>
       </c>
       <c r="D750">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E750" t="s">
         <v>28</v>
@@ -16887,7 +16887,7 @@
         <v>27</v>
       </c>
       <c r="D751">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E751" t="s">
         <v>28</v>
@@ -16904,7 +16904,7 @@
         <v>27</v>
       </c>
       <c r="D752">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E752" t="s">
         <v>28</v>
@@ -16921,7 +16921,7 @@
         <v>27</v>
       </c>
       <c r="D753">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E753" t="s">
         <v>28</v>
@@ -16938,7 +16938,7 @@
         <v>27</v>
       </c>
       <c r="D754">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E754" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="D755">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E755" t="s">
         <v>28</v>
@@ -16972,7 +16972,7 @@
         <v>27</v>
       </c>
       <c r="D756">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E756" t="s">
         <v>28</v>
@@ -16989,7 +16989,7 @@
         <v>27</v>
       </c>
       <c r="D757">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E757" t="s">
         <v>28</v>
@@ -17006,7 +17006,7 @@
         <v>27</v>
       </c>
       <c r="D758">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E758" t="s">
         <v>28</v>
@@ -17023,7 +17023,7 @@
         <v>27</v>
       </c>
       <c r="D759">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E759" t="s">
         <v>28</v>
@@ -17040,7 +17040,7 @@
         <v>27</v>
       </c>
       <c r="D760">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E760" t="s">
         <v>28</v>
@@ -17057,7 +17057,7 @@
         <v>27</v>
       </c>
       <c r="D761">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E761" t="s">
         <v>28</v>
@@ -17074,7 +17074,7 @@
         <v>27</v>
       </c>
       <c r="D762">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E762" t="s">
         <v>28</v>
@@ -17091,7 +17091,7 @@
         <v>27</v>
       </c>
       <c r="D763">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E763" t="s">
         <v>28</v>
@@ -17108,7 +17108,7 @@
         <v>27</v>
       </c>
       <c r="D764">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E764" t="s">
         <v>28</v>
@@ -17125,7 +17125,7 @@
         <v>27</v>
       </c>
       <c r="D765">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E765" t="s">
         <v>28</v>
@@ -17142,7 +17142,7 @@
         <v>27</v>
       </c>
       <c r="D766">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E766" t="s">
         <v>28</v>
@@ -17159,7 +17159,7 @@
         <v>27</v>
       </c>
       <c r="D767">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E767" t="s">
         <v>28</v>
@@ -17193,7 +17193,7 @@
         <v>27</v>
       </c>
       <c r="D769">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E769" t="s">
         <v>28</v>
@@ -17210,7 +17210,7 @@
         <v>27</v>
       </c>
       <c r="D770">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E770" t="s">
         <v>28</v>
@@ -17227,7 +17227,7 @@
         <v>27</v>
       </c>
       <c r="D771">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E771" t="s">
         <v>28</v>
@@ -17244,7 +17244,7 @@
         <v>27</v>
       </c>
       <c r="D772">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E772" t="s">
         <v>28</v>
@@ -17261,7 +17261,7 @@
         <v>27</v>
       </c>
       <c r="D773">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E773" t="s">
         <v>28</v>
@@ -17278,7 +17278,7 @@
         <v>27</v>
       </c>
       <c r="D774">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E774" t="s">
         <v>28</v>
@@ -17295,7 +17295,7 @@
         <v>27</v>
       </c>
       <c r="D775">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E775" t="s">
         <v>28</v>
@@ -17312,7 +17312,7 @@
         <v>27</v>
       </c>
       <c r="D776">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E776" t="s">
         <v>28</v>
@@ -17329,7 +17329,7 @@
         <v>27</v>
       </c>
       <c r="D777">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E777" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="D778">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E778" t="s">
         <v>28</v>
@@ -17380,7 +17380,7 @@
         <v>27</v>
       </c>
       <c r="D780">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E780" t="s">
         <v>28</v>
@@ -17397,7 +17397,7 @@
         <v>27</v>
       </c>
       <c r="D781">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E781" t="s">
         <v>28</v>
@@ -17414,7 +17414,7 @@
         <v>27</v>
       </c>
       <c r="D782">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E782" t="s">
         <v>28</v>
@@ -17431,7 +17431,7 @@
         <v>27</v>
       </c>
       <c r="D783">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E783" t="s">
         <v>28</v>
@@ -17448,7 +17448,7 @@
         <v>27</v>
       </c>
       <c r="D784">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E784" t="s">
         <v>28</v>
@@ -17482,7 +17482,7 @@
         <v>27</v>
       </c>
       <c r="D786">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E786" t="s">
         <v>28</v>
@@ -17499,7 +17499,7 @@
         <v>27</v>
       </c>
       <c r="D787">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E787" t="s">
         <v>28</v>
@@ -17516,7 +17516,7 @@
         <v>27</v>
       </c>
       <c r="D788">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E788" t="s">
         <v>28</v>
@@ -17533,7 +17533,7 @@
         <v>27</v>
       </c>
       <c r="D789">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E789" t="s">
         <v>28</v>
@@ -17550,7 +17550,7 @@
         <v>27</v>
       </c>
       <c r="D790">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E790" t="s">
         <v>28</v>
@@ -17567,7 +17567,7 @@
         <v>27</v>
       </c>
       <c r="D791">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E791" t="s">
         <v>28</v>
@@ -17584,7 +17584,7 @@
         <v>27</v>
       </c>
       <c r="D792">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E792" t="s">
         <v>28</v>
@@ -17601,7 +17601,7 @@
         <v>27</v>
       </c>
       <c r="D793">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E793" t="s">
         <v>28</v>
@@ -17618,7 +17618,7 @@
         <v>27</v>
       </c>
       <c r="D794">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E794" t="s">
         <v>28</v>
@@ -17635,7 +17635,7 @@
         <v>27</v>
       </c>
       <c r="D795">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E795" t="s">
         <v>28</v>
@@ -17652,7 +17652,7 @@
         <v>27</v>
       </c>
       <c r="D796">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E796" t="s">
         <v>28</v>
@@ -17669,7 +17669,7 @@
         <v>27</v>
       </c>
       <c r="D797">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E797" t="s">
         <v>28</v>
@@ -17686,7 +17686,7 @@
         <v>27</v>
       </c>
       <c r="D798">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E798" t="s">
         <v>28</v>
@@ -17703,7 +17703,7 @@
         <v>27</v>
       </c>
       <c r="D799">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E799" t="s">
         <v>28</v>
@@ -17720,7 +17720,7 @@
         <v>27</v>
       </c>
       <c r="D800">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E800" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="D801">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E801" t="s">
         <v>28</v>
@@ -17754,7 +17754,7 @@
         <v>27</v>
       </c>
       <c r="D802">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E802" t="s">
         <v>28</v>
@@ -17771,7 +17771,7 @@
         <v>27</v>
       </c>
       <c r="D803">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E803" t="s">
         <v>28</v>
@@ -17788,7 +17788,7 @@
         <v>27</v>
       </c>
       <c r="D804">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E804" t="s">
         <v>28</v>
@@ -17805,7 +17805,7 @@
         <v>27</v>
       </c>
       <c r="D805">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E805" t="s">
         <v>28</v>
@@ -17822,7 +17822,7 @@
         <v>27</v>
       </c>
       <c r="D806">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E806" t="s">
         <v>28</v>
@@ -17839,7 +17839,7 @@
         <v>27</v>
       </c>
       <c r="D807">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E807" t="s">
         <v>28</v>
@@ -17856,7 +17856,7 @@
         <v>27</v>
       </c>
       <c r="D808">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E808" t="s">
         <v>28</v>
@@ -17890,7 +17890,7 @@
         <v>27</v>
       </c>
       <c r="D810">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E810" t="s">
         <v>28</v>
@@ -17907,7 +17907,7 @@
         <v>27</v>
       </c>
       <c r="D811">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E811" t="s">
         <v>28</v>
@@ -17924,7 +17924,7 @@
         <v>27</v>
       </c>
       <c r="D812">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E812" t="s">
         <v>28</v>
@@ -17941,7 +17941,7 @@
         <v>27</v>
       </c>
       <c r="D813">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E813" t="s">
         <v>28</v>
@@ -17975,7 +17975,7 @@
         <v>27</v>
       </c>
       <c r="D815">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E815" t="s">
         <v>28</v>
@@ -17992,7 +17992,7 @@
         <v>27</v>
       </c>
       <c r="D816">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E816" t="s">
         <v>28</v>
@@ -18009,7 +18009,7 @@
         <v>27</v>
       </c>
       <c r="D817">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E817" t="s">
         <v>28</v>
@@ -18026,7 +18026,7 @@
         <v>27</v>
       </c>
       <c r="D818">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E818" t="s">
         <v>28</v>
@@ -18060,7 +18060,7 @@
         <v>27</v>
       </c>
       <c r="D820">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E820" t="s">
         <v>28</v>
@@ -18077,7 +18077,7 @@
         <v>27</v>
       </c>
       <c r="D821">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E821" t="s">
         <v>28</v>
@@ -18094,7 +18094,7 @@
         <v>27</v>
       </c>
       <c r="D822">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E822" t="s">
         <v>28</v>
@@ -18111,7 +18111,7 @@
         <v>27</v>
       </c>
       <c r="D823">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E823" t="s">
         <v>28</v>
@@ -18128,7 +18128,7 @@
         <v>27</v>
       </c>
       <c r="D824">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E824" t="s">
         <v>28</v>
@@ -18145,7 +18145,7 @@
         <v>27</v>
       </c>
       <c r="D825">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E825" t="s">
         <v>28</v>
@@ -18162,7 +18162,7 @@
         <v>27</v>
       </c>
       <c r="D826">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E826" t="s">
         <v>28</v>
@@ -18196,7 +18196,7 @@
         <v>27</v>
       </c>
       <c r="D828">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E828" t="s">
         <v>28</v>
@@ -18213,7 +18213,7 @@
         <v>27</v>
       </c>
       <c r="D829">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E829" t="s">
         <v>28</v>
@@ -18230,7 +18230,7 @@
         <v>27</v>
       </c>
       <c r="D830">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E830" t="s">
         <v>28</v>
@@ -18247,7 +18247,7 @@
         <v>27</v>
       </c>
       <c r="D831">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E831" t="s">
         <v>28</v>
@@ -18264,7 +18264,7 @@
         <v>27</v>
       </c>
       <c r="D832">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E832" t="s">
         <v>28</v>
@@ -18281,7 +18281,7 @@
         <v>27</v>
       </c>
       <c r="D833">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E833" t="s">
         <v>28</v>
@@ -18298,7 +18298,7 @@
         <v>27</v>
       </c>
       <c r="D834">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E834" t="s">
         <v>28</v>
@@ -18332,7 +18332,7 @@
         <v>27</v>
       </c>
       <c r="D836">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E836" t="s">
         <v>28</v>
@@ -18349,7 +18349,7 @@
         <v>27</v>
       </c>
       <c r="D837">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E837" t="s">
         <v>28</v>
@@ -18366,7 +18366,7 @@
         <v>27</v>
       </c>
       <c r="D838">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E838" t="s">
         <v>28</v>
@@ -18383,7 +18383,7 @@
         <v>27</v>
       </c>
       <c r="D839">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E839" t="s">
         <v>28</v>
@@ -18400,7 +18400,7 @@
         <v>27</v>
       </c>
       <c r="D840">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E840" t="s">
         <v>28</v>
@@ -18417,7 +18417,7 @@
         <v>27</v>
       </c>
       <c r="D841">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E841" t="s">
         <v>28</v>
@@ -18434,7 +18434,7 @@
         <v>27</v>
       </c>
       <c r="D842">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E842" t="s">
         <v>28</v>
@@ -18451,7 +18451,7 @@
         <v>27</v>
       </c>
       <c r="D843">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E843" t="s">
         <v>28</v>
@@ -18468,7 +18468,7 @@
         <v>27</v>
       </c>
       <c r="D844">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E844" t="s">
         <v>28</v>
@@ -18485,7 +18485,7 @@
         <v>27</v>
       </c>
       <c r="D845">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E845" t="s">
         <v>28</v>
@@ -18502,7 +18502,7 @@
         <v>27</v>
       </c>
       <c r="D846">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E846" t="s">
         <v>28</v>
@@ -18519,7 +18519,7 @@
         <v>27</v>
       </c>
       <c r="D847">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E847" t="s">
         <v>28</v>
@@ -18536,7 +18536,7 @@
         <v>27</v>
       </c>
       <c r="D848">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E848" t="s">
         <v>28</v>
@@ -18553,7 +18553,7 @@
         <v>27</v>
       </c>
       <c r="D849">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E849" t="s">
         <v>28</v>
@@ -18570,7 +18570,7 @@
         <v>27</v>
       </c>
       <c r="D850">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E850" t="s">
         <v>28</v>
@@ -18587,7 +18587,7 @@
         <v>27</v>
       </c>
       <c r="D851">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E851" t="s">
         <v>28</v>
@@ -18604,7 +18604,7 @@
         <v>27</v>
       </c>
       <c r="D852">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E852" t="s">
         <v>28</v>
@@ -18621,7 +18621,7 @@
         <v>27</v>
       </c>
       <c r="D853">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E853" t="s">
         <v>28</v>
@@ -18638,7 +18638,7 @@
         <v>27</v>
       </c>
       <c r="D854">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E854" t="s">
         <v>28</v>
@@ -18655,7 +18655,7 @@
         <v>27</v>
       </c>
       <c r="D855">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E855" t="s">
         <v>28</v>
@@ -18672,7 +18672,7 @@
         <v>27</v>
       </c>
       <c r="D856">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E856" t="s">
         <v>28</v>
@@ -18689,7 +18689,7 @@
         <v>27</v>
       </c>
       <c r="D857">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E857" t="s">
         <v>28</v>
@@ -18706,7 +18706,7 @@
         <v>27</v>
       </c>
       <c r="D858">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E858" t="s">
         <v>28</v>
@@ -18723,7 +18723,7 @@
         <v>27</v>
       </c>
       <c r="D859">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E859" t="s">
         <v>28</v>
@@ -18740,7 +18740,7 @@
         <v>27</v>
       </c>
       <c r="D860">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E860" t="s">
         <v>28</v>
@@ -18757,7 +18757,7 @@
         <v>27</v>
       </c>
       <c r="D861">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E861" t="s">
         <v>28</v>
@@ -18774,7 +18774,7 @@
         <v>27</v>
       </c>
       <c r="D862">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E862" t="s">
         <v>28</v>
@@ -18791,7 +18791,7 @@
         <v>27</v>
       </c>
       <c r="D863">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E863" t="s">
         <v>28</v>
@@ -18808,7 +18808,7 @@
         <v>27</v>
       </c>
       <c r="D864">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E864" t="s">
         <v>28</v>
@@ -18825,7 +18825,7 @@
         <v>27</v>
       </c>
       <c r="D865">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E865" t="s">
         <v>28</v>
@@ -18842,7 +18842,7 @@
         <v>27</v>
       </c>
       <c r="D866">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E866" t="s">
         <v>28</v>
@@ -18859,7 +18859,7 @@
         <v>27</v>
       </c>
       <c r="D867">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E867" t="s">
         <v>28</v>
@@ -18876,7 +18876,7 @@
         <v>27</v>
       </c>
       <c r="D868">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E868" t="s">
         <v>28</v>
@@ -18893,7 +18893,7 @@
         <v>27</v>
       </c>
       <c r="D869">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E869" t="s">
         <v>28</v>
@@ -18910,7 +18910,7 @@
         <v>27</v>
       </c>
       <c r="D870">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E870" t="s">
         <v>28</v>
@@ -18927,7 +18927,7 @@
         <v>27</v>
       </c>
       <c r="D871">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E871" t="s">
         <v>28</v>
@@ -18944,7 +18944,7 @@
         <v>27</v>
       </c>
       <c r="D872">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E872" t="s">
         <v>28</v>
@@ -18961,7 +18961,7 @@
         <v>27</v>
       </c>
       <c r="D873">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E873" t="s">
         <v>28</v>
@@ -18978,7 +18978,7 @@
         <v>27</v>
       </c>
       <c r="D874">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E874" t="s">
         <v>28</v>
@@ -18995,7 +18995,7 @@
         <v>27</v>
       </c>
       <c r="D875">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E875" t="s">
         <v>28</v>
@@ -19012,7 +19012,7 @@
         <v>27</v>
       </c>
       <c r="D876">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E876" t="s">
         <v>28</v>
@@ -19029,7 +19029,7 @@
         <v>27</v>
       </c>
       <c r="D877">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E877" t="s">
         <v>28</v>
@@ -19046,7 +19046,7 @@
         <v>27</v>
       </c>
       <c r="D878">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E878" t="s">
         <v>28</v>
@@ -19063,7 +19063,7 @@
         <v>27</v>
       </c>
       <c r="D879">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E879" t="s">
         <v>28</v>
@@ -19080,7 +19080,7 @@
         <v>27</v>
       </c>
       <c r="D880">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E880" t="s">
         <v>28</v>
@@ -19097,7 +19097,7 @@
         <v>27</v>
       </c>
       <c r="D881">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E881" t="s">
         <v>28</v>
@@ -19114,7 +19114,7 @@
         <v>27</v>
       </c>
       <c r="D882">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E882" t="s">
         <v>28</v>
@@ -19131,7 +19131,7 @@
         <v>27</v>
       </c>
       <c r="D883">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E883" t="s">
         <v>28</v>
@@ -19148,7 +19148,7 @@
         <v>27</v>
       </c>
       <c r="D884">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E884" t="s">
         <v>28</v>
@@ -19165,7 +19165,7 @@
         <v>27</v>
       </c>
       <c r="D885">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E885" t="s">
         <v>28</v>
@@ -19199,7 +19199,7 @@
         <v>27</v>
       </c>
       <c r="D887">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E887" t="s">
         <v>28</v>
@@ -19216,7 +19216,7 @@
         <v>27</v>
       </c>
       <c r="D888">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E888" t="s">
         <v>28</v>
@@ -19233,7 +19233,7 @@
         <v>27</v>
       </c>
       <c r="D889">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E889" t="s">
         <v>28</v>
@@ -19250,7 +19250,7 @@
         <v>27</v>
       </c>
       <c r="D890">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E890" t="s">
         <v>28</v>
@@ -19284,7 +19284,7 @@
         <v>27</v>
       </c>
       <c r="D892">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E892" t="s">
         <v>28</v>
@@ -19301,7 +19301,7 @@
         <v>27</v>
       </c>
       <c r="D893">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E893" t="s">
         <v>28</v>
@@ -19318,7 +19318,7 @@
         <v>27</v>
       </c>
       <c r="D894">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E894" t="s">
         <v>28</v>
@@ -19335,7 +19335,7 @@
         <v>27</v>
       </c>
       <c r="D895">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E895" t="s">
         <v>28</v>
@@ -19386,7 +19386,7 @@
         <v>27</v>
       </c>
       <c r="D898">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E898" t="s">
         <v>28</v>
@@ -19403,7 +19403,7 @@
         <v>27</v>
       </c>
       <c r="D899">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E899" t="s">
         <v>28</v>
@@ -19420,7 +19420,7 @@
         <v>27</v>
       </c>
       <c r="D900">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E900" t="s">
         <v>28</v>
@@ -19437,7 +19437,7 @@
         <v>27</v>
       </c>
       <c r="D901">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E901" t="s">
         <v>28</v>
@@ -19454,7 +19454,7 @@
         <v>27</v>
       </c>
       <c r="D902">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E902" t="s">
         <v>28</v>
@@ -19471,7 +19471,7 @@
         <v>27</v>
       </c>
       <c r="D903">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E903" t="s">
         <v>28</v>
@@ -19488,7 +19488,7 @@
         <v>27</v>
       </c>
       <c r="D904">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E904" t="s">
         <v>28</v>
@@ -19505,7 +19505,7 @@
         <v>27</v>
       </c>
       <c r="D905">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E905" t="s">
         <v>28</v>
@@ -19539,7 +19539,7 @@
         <v>27</v>
       </c>
       <c r="D907">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E907" t="s">
         <v>28</v>
@@ -19556,7 +19556,7 @@
         <v>27</v>
       </c>
       <c r="D908">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E908" t="s">
         <v>28</v>
@@ -19573,7 +19573,7 @@
         <v>27</v>
       </c>
       <c r="D909">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E909" t="s">
         <v>28</v>
@@ -19590,7 +19590,7 @@
         <v>27</v>
       </c>
       <c r="D910">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E910" t="s">
         <v>28</v>
@@ -19607,7 +19607,7 @@
         <v>27</v>
       </c>
       <c r="D911">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E911" t="s">
         <v>28</v>
@@ -19624,7 +19624,7 @@
         <v>27</v>
       </c>
       <c r="D912">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E912" t="s">
         <v>28</v>
@@ -19641,7 +19641,7 @@
         <v>27</v>
       </c>
       <c r="D913">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E913" t="s">
         <v>28</v>
@@ -19658,7 +19658,7 @@
         <v>27</v>
       </c>
       <c r="D914">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E914" t="s">
         <v>28</v>
@@ -19675,7 +19675,7 @@
         <v>27</v>
       </c>
       <c r="D915">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E915" t="s">
         <v>28</v>
@@ -19692,7 +19692,7 @@
         <v>27</v>
       </c>
       <c r="D916">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E916" t="s">
         <v>28</v>
@@ -19709,7 +19709,7 @@
         <v>27</v>
       </c>
       <c r="D917">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E917" t="s">
         <v>28</v>
@@ -19726,7 +19726,7 @@
         <v>27</v>
       </c>
       <c r="D918">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E918" t="s">
         <v>28</v>
@@ -19743,7 +19743,7 @@
         <v>27</v>
       </c>
       <c r="D919">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E919" t="s">
         <v>28</v>
@@ -19760,7 +19760,7 @@
         <v>27</v>
       </c>
       <c r="D920">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E920" t="s">
         <v>28</v>
@@ -19777,7 +19777,7 @@
         <v>27</v>
       </c>
       <c r="D921">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E921" t="s">
         <v>28</v>
@@ -19794,7 +19794,7 @@
         <v>27</v>
       </c>
       <c r="D922">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E922" t="s">
         <v>28</v>
@@ -19811,7 +19811,7 @@
         <v>27</v>
       </c>
       <c r="D923">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E923" t="s">
         <v>28</v>
@@ -19845,7 +19845,7 @@
         <v>27</v>
       </c>
       <c r="D925">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E925" t="s">
         <v>28</v>
@@ -19862,7 +19862,7 @@
         <v>27</v>
       </c>
       <c r="D926">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E926" t="s">
         <v>28</v>
@@ -19879,7 +19879,7 @@
         <v>27</v>
       </c>
       <c r="D927">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E927" t="s">
         <v>28</v>
@@ -19896,7 +19896,7 @@
         <v>27</v>
       </c>
       <c r="D928">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E928" t="s">
         <v>28</v>
@@ -19913,7 +19913,7 @@
         <v>27</v>
       </c>
       <c r="D929">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E929" t="s">
         <v>28</v>
@@ -19930,7 +19930,7 @@
         <v>27</v>
       </c>
       <c r="D930">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E930" t="s">
         <v>28</v>
@@ -19947,7 +19947,7 @@
         <v>27</v>
       </c>
       <c r="D931">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E931" t="s">
         <v>28</v>
@@ -19964,7 +19964,7 @@
         <v>27</v>
       </c>
       <c r="D932">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E932" t="s">
         <v>28</v>
@@ -19981,7 +19981,7 @@
         <v>27</v>
       </c>
       <c r="D933">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E933" t="s">
         <v>28</v>
@@ -19998,7 +19998,7 @@
         <v>27</v>
       </c>
       <c r="D934">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E934" t="s">
         <v>28</v>
@@ -20015,7 +20015,7 @@
         <v>27</v>
       </c>
       <c r="D935">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E935" t="s">
         <v>28</v>
@@ -20032,7 +20032,7 @@
         <v>27</v>
       </c>
       <c r="D936">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E936" t="s">
         <v>28</v>
@@ -20049,7 +20049,7 @@
         <v>27</v>
       </c>
       <c r="D937">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E937" t="s">
         <v>28</v>
@@ -20066,7 +20066,7 @@
         <v>27</v>
       </c>
       <c r="D938">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E938" t="s">
         <v>28</v>
@@ -20083,7 +20083,7 @@
         <v>27</v>
       </c>
       <c r="D939">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E939" t="s">
         <v>28</v>
@@ -20100,7 +20100,7 @@
         <v>27</v>
       </c>
       <c r="D940">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E940" t="s">
         <v>28</v>
@@ -20117,7 +20117,7 @@
         <v>27</v>
       </c>
       <c r="D941">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E941" t="s">
         <v>28</v>
@@ -20134,7 +20134,7 @@
         <v>27</v>
       </c>
       <c r="D942">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E942" t="s">
         <v>28</v>
@@ -20151,7 +20151,7 @@
         <v>27</v>
       </c>
       <c r="D943">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E943" t="s">
         <v>28</v>
@@ -20168,7 +20168,7 @@
         <v>27</v>
       </c>
       <c r="D944">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E944" t="s">
         <v>28</v>
@@ -20185,7 +20185,7 @@
         <v>27</v>
       </c>
       <c r="D945">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E945" t="s">
         <v>28</v>
@@ -20202,7 +20202,7 @@
         <v>27</v>
       </c>
       <c r="D946">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E946" t="s">
         <v>28</v>
@@ -20219,7 +20219,7 @@
         <v>27</v>
       </c>
       <c r="D947">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E947" t="s">
         <v>28</v>
@@ -20236,7 +20236,7 @@
         <v>27</v>
       </c>
       <c r="D948">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E948" t="s">
         <v>28</v>
@@ -20253,7 +20253,7 @@
         <v>27</v>
       </c>
       <c r="D949">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E949" t="s">
         <v>28</v>
@@ -20270,7 +20270,7 @@
         <v>27</v>
       </c>
       <c r="D950">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E950" t="s">
         <v>28</v>
@@ -20287,7 +20287,7 @@
         <v>27</v>
       </c>
       <c r="D951">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E951" t="s">
         <v>28</v>
@@ -20304,7 +20304,7 @@
         <v>27</v>
       </c>
       <c r="D952">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E952" t="s">
         <v>28</v>
@@ -20338,7 +20338,7 @@
         <v>27</v>
       </c>
       <c r="D954">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E954" t="s">
         <v>28</v>
@@ -20355,7 +20355,7 @@
         <v>27</v>
       </c>
       <c r="D955">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E955" t="s">
         <v>28</v>
@@ -20372,7 +20372,7 @@
         <v>27</v>
       </c>
       <c r="D956">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E956" t="s">
         <v>28</v>
@@ -20389,7 +20389,7 @@
         <v>27</v>
       </c>
       <c r="D957">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E957" t="s">
         <v>28</v>
@@ -20406,7 +20406,7 @@
         <v>27</v>
       </c>
       <c r="D958">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E958" t="s">
         <v>28</v>
@@ -20423,7 +20423,7 @@
         <v>27</v>
       </c>
       <c r="D959">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E959" t="s">
         <v>28</v>
@@ -20440,7 +20440,7 @@
         <v>27</v>
       </c>
       <c r="D960">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E960" t="s">
         <v>28</v>
@@ -20457,7 +20457,7 @@
         <v>27</v>
       </c>
       <c r="D961">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E961" t="s">
         <v>28</v>
@@ -20474,7 +20474,7 @@
         <v>27</v>
       </c>
       <c r="D962">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E962" t="s">
         <v>28</v>
@@ -20491,7 +20491,7 @@
         <v>27</v>
       </c>
       <c r="D963">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E963" t="s">
         <v>28</v>
@@ -20508,7 +20508,7 @@
         <v>27</v>
       </c>
       <c r="D964">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E964" t="s">
         <v>28</v>
@@ -20525,7 +20525,7 @@
         <v>27</v>
       </c>
       <c r="D965">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E965" t="s">
         <v>28</v>
@@ -20542,7 +20542,7 @@
         <v>27</v>
       </c>
       <c r="D966">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E966" t="s">
         <v>28</v>
@@ -20576,7 +20576,7 @@
         <v>27</v>
       </c>
       <c r="D968">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E968" t="s">
         <v>28</v>
@@ -20593,7 +20593,7 @@
         <v>27</v>
       </c>
       <c r="D969">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E969" t="s">
         <v>28</v>
@@ -20610,7 +20610,7 @@
         <v>27</v>
       </c>
       <c r="D970">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E970" t="s">
         <v>28</v>
@@ -20627,7 +20627,7 @@
         <v>27</v>
       </c>
       <c r="D971">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E971" t="s">
         <v>28</v>
@@ -20644,7 +20644,7 @@
         <v>27</v>
       </c>
       <c r="D972">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E972" t="s">
         <v>28</v>
@@ -20661,7 +20661,7 @@
         <v>27</v>
       </c>
       <c r="D973">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E973" t="s">
         <v>28</v>
@@ -20678,7 +20678,7 @@
         <v>27</v>
       </c>
       <c r="D974">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E974" t="s">
         <v>28</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="D975">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E975" t="s">
         <v>28</v>
@@ -20712,7 +20712,7 @@
         <v>27</v>
       </c>
       <c r="D976">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E976" t="s">
         <v>28</v>
@@ -20729,7 +20729,7 @@
         <v>27</v>
       </c>
       <c r="D977">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E977" t="s">
         <v>28</v>
@@ -20746,7 +20746,7 @@
         <v>27</v>
       </c>
       <c r="D978">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E978" t="s">
         <v>28</v>
@@ -20763,7 +20763,7 @@
         <v>27</v>
       </c>
       <c r="D979">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E979" t="s">
         <v>28</v>
@@ -20780,7 +20780,7 @@
         <v>27</v>
       </c>
       <c r="D980">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E980" t="s">
         <v>28</v>
@@ -20797,7 +20797,7 @@
         <v>27</v>
       </c>
       <c r="D981">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E981" t="s">
         <v>28</v>
@@ -20814,7 +20814,7 @@
         <v>27</v>
       </c>
       <c r="D982">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E982" t="s">
         <v>28</v>
@@ -20831,7 +20831,7 @@
         <v>27</v>
       </c>
       <c r="D983">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E983" t="s">
         <v>28</v>
@@ -20848,7 +20848,7 @@
         <v>27</v>
       </c>
       <c r="D984">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E984" t="s">
         <v>28</v>
@@ -20865,7 +20865,7 @@
         <v>27</v>
       </c>
       <c r="D985">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E985" t="s">
         <v>28</v>
@@ -20882,7 +20882,7 @@
         <v>27</v>
       </c>
       <c r="D986">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E986" t="s">
         <v>28</v>
@@ -20899,7 +20899,7 @@
         <v>27</v>
       </c>
       <c r="D987">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E987" t="s">
         <v>28</v>
@@ -20916,7 +20916,7 @@
         <v>27</v>
       </c>
       <c r="D988">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E988" t="s">
         <v>28</v>
@@ -20933,7 +20933,7 @@
         <v>27</v>
       </c>
       <c r="D989">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E989" t="s">
         <v>28</v>
@@ -20950,7 +20950,7 @@
         <v>27</v>
       </c>
       <c r="D990">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E990" t="s">
         <v>28</v>
@@ -20967,7 +20967,7 @@
         <v>27</v>
       </c>
       <c r="D991">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E991" t="s">
         <v>28</v>
@@ -20984,7 +20984,7 @@
         <v>27</v>
       </c>
       <c r="D992">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E992" t="s">
         <v>28</v>
@@ -21001,7 +21001,7 @@
         <v>27</v>
       </c>
       <c r="D993">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E993" t="s">
         <v>28</v>
@@ -21018,7 +21018,7 @@
         <v>27</v>
       </c>
       <c r="D994">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E994" t="s">
         <v>28</v>
@@ -21035,7 +21035,7 @@
         <v>27</v>
       </c>
       <c r="D995">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E995" t="s">
         <v>28</v>
@@ -21052,7 +21052,7 @@
         <v>27</v>
       </c>
       <c r="D996">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E996" t="s">
         <v>28</v>
@@ -21069,7 +21069,7 @@
         <v>27</v>
       </c>
       <c r="D997">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E997" t="s">
         <v>28</v>
@@ -21086,7 +21086,7 @@
         <v>27</v>
       </c>
       <c r="D998">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E998" t="s">
         <v>28</v>
@@ -21103,7 +21103,7 @@
         <v>27</v>
       </c>
       <c r="D999">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E999" t="s">
         <v>28</v>
@@ -21120,7 +21120,7 @@
         <v>27</v>
       </c>
       <c r="D1000">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1000" t="s">
         <v>28</v>
@@ -21137,7 +21137,7 @@
         <v>27</v>
       </c>
       <c r="D1001">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E1001" t="s">
         <v>28</v>
@@ -21154,7 +21154,7 @@
         <v>27</v>
       </c>
       <c r="D1002">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E1002" t="s">
         <v>28</v>
@@ -21171,7 +21171,7 @@
         <v>27</v>
       </c>
       <c r="D1003">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1003" t="s">
         <v>28</v>
@@ -21188,7 +21188,7 @@
         <v>27</v>
       </c>
       <c r="D1004">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E1004" t="s">
         <v>28</v>
@@ -21205,7 +21205,7 @@
         <v>27</v>
       </c>
       <c r="D1005">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E1005" t="s">
         <v>28</v>
@@ -21222,7 +21222,7 @@
         <v>27</v>
       </c>
       <c r="D1006">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1006" t="s">
         <v>28</v>
@@ -21239,7 +21239,7 @@
         <v>27</v>
       </c>
       <c r="D1007">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E1007" t="s">
         <v>28</v>
@@ -21256,7 +21256,7 @@
         <v>27</v>
       </c>
       <c r="D1008">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E1008" t="s">
         <v>28</v>
@@ -21273,7 +21273,7 @@
         <v>27</v>
       </c>
       <c r="D1009">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1009" t="s">
         <v>28</v>
@@ -21290,7 +21290,7 @@
         <v>27</v>
       </c>
       <c r="D1010">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E1010" t="s">
         <v>28</v>
@@ -21307,7 +21307,7 @@
         <v>27</v>
       </c>
       <c r="D1011">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1011" t="s">
         <v>28</v>
@@ -21324,7 +21324,7 @@
         <v>27</v>
       </c>
       <c r="D1012">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E1012" t="s">
         <v>28</v>
@@ -21341,7 +21341,7 @@
         <v>27</v>
       </c>
       <c r="D1013">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E1013" t="s">
         <v>28</v>
@@ -21358,7 +21358,7 @@
         <v>27</v>
       </c>
       <c r="D1014">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1014" t="s">
         <v>28</v>
@@ -21375,7 +21375,7 @@
         <v>27</v>
       </c>
       <c r="D1015">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1015" t="s">
         <v>28</v>
@@ -21392,7 +21392,7 @@
         <v>27</v>
       </c>
       <c r="D1016">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E1016" t="s">
         <v>28</v>
@@ -21409,7 +21409,7 @@
         <v>27</v>
       </c>
       <c r="D1017">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E1017" t="s">
         <v>28</v>
@@ -21426,7 +21426,7 @@
         <v>27</v>
       </c>
       <c r="D1018">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E1018" t="s">
         <v>28</v>
@@ -21443,7 +21443,7 @@
         <v>27</v>
       </c>
       <c r="D1019">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1019" t="s">
         <v>28</v>
@@ -21460,7 +21460,7 @@
         <v>27</v>
       </c>
       <c r="D1020">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E1020" t="s">
         <v>28</v>
@@ -21477,7 +21477,7 @@
         <v>27</v>
       </c>
       <c r="D1021">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1021" t="s">
         <v>28</v>
@@ -21494,7 +21494,7 @@
         <v>27</v>
       </c>
       <c r="D1022">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E1022" t="s">
         <v>28</v>
@@ -21511,7 +21511,7 @@
         <v>27</v>
       </c>
       <c r="D1023">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1023" t="s">
         <v>28</v>
@@ -21528,7 +21528,7 @@
         <v>27</v>
       </c>
       <c r="D1024">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E1024" t="s">
         <v>28</v>
@@ -21545,7 +21545,7 @@
         <v>27</v>
       </c>
       <c r="D1025">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E1025" t="s">
         <v>28</v>
@@ -21562,7 +21562,7 @@
         <v>27</v>
       </c>
       <c r="D1026">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E1026" t="s">
         <v>28</v>
@@ -21579,7 +21579,7 @@
         <v>27</v>
       </c>
       <c r="D1027">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E1027" t="s">
         <v>28</v>
@@ -21596,7 +21596,7 @@
         <v>27</v>
       </c>
       <c r="D1028">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E1028" t="s">
         <v>28</v>
@@ -21613,7 +21613,7 @@
         <v>27</v>
       </c>
       <c r="D1029">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1029" t="s">
         <v>28</v>
@@ -21647,7 +21647,7 @@
         <v>27</v>
       </c>
       <c r="D1031">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1031" t="s">
         <v>28</v>
@@ -21664,7 +21664,7 @@
         <v>27</v>
       </c>
       <c r="D1032">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E1032" t="s">
         <v>28</v>
@@ -21681,7 +21681,7 @@
         <v>27</v>
       </c>
       <c r="D1033">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E1033" t="s">
         <v>28</v>
@@ -21698,7 +21698,7 @@
         <v>27</v>
       </c>
       <c r="D1034">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1034" t="s">
         <v>28</v>
@@ -21715,7 +21715,7 @@
         <v>27</v>
       </c>
       <c r="D1035">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E1035" t="s">
         <v>28</v>
@@ -21732,7 +21732,7 @@
         <v>27</v>
       </c>
       <c r="D1036">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E1036" t="s">
         <v>28</v>
@@ -21749,7 +21749,7 @@
         <v>27</v>
       </c>
       <c r="D1037">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1037" t="s">
         <v>28</v>
@@ -21766,7 +21766,7 @@
         <v>27</v>
       </c>
       <c r="D1038">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1038" t="s">
         <v>28</v>
@@ -21783,7 +21783,7 @@
         <v>27</v>
       </c>
       <c r="D1039">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1039" t="s">
         <v>28</v>
@@ -21817,7 +21817,7 @@
         <v>27</v>
       </c>
       <c r="D1041">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E1041" t="s">
         <v>28</v>
@@ -21834,7 +21834,7 @@
         <v>27</v>
       </c>
       <c r="D1042">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E1042" t="s">
         <v>28</v>
@@ -21851,7 +21851,7 @@
         <v>27</v>
       </c>
       <c r="D1043">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1043" t="s">
         <v>28</v>
@@ -21868,7 +21868,7 @@
         <v>27</v>
       </c>
       <c r="D1044">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1044" t="s">
         <v>28</v>
@@ -21885,7 +21885,7 @@
         <v>27</v>
       </c>
       <c r="D1045">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E1045" t="s">
         <v>28</v>
@@ -21902,7 +21902,7 @@
         <v>27</v>
       </c>
       <c r="D1046">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E1046" t="s">
         <v>28</v>
@@ -21919,7 +21919,7 @@
         <v>27</v>
       </c>
       <c r="D1047">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1047" t="s">
         <v>28</v>
@@ -21936,7 +21936,7 @@
         <v>27</v>
       </c>
       <c r="D1048">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1048" t="s">
         <v>28</v>
@@ -21953,7 +21953,7 @@
         <v>27</v>
       </c>
       <c r="D1049">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E1049" t="s">
         <v>28</v>
@@ -21970,7 +21970,7 @@
         <v>27</v>
       </c>
       <c r="D1050">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1050" t="s">
         <v>28</v>
@@ -22004,7 +22004,7 @@
         <v>27</v>
       </c>
       <c r="D1052">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1052" t="s">
         <v>28</v>
@@ -22021,7 +22021,7 @@
         <v>27</v>
       </c>
       <c r="D1053">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E1053" t="s">
         <v>28</v>
@@ -22038,7 +22038,7 @@
         <v>27</v>
       </c>
       <c r="D1054">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1054" t="s">
         <v>28</v>
@@ -22055,7 +22055,7 @@
         <v>27</v>
       </c>
       <c r="D1055">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E1055" t="s">
         <v>28</v>
@@ -22072,7 +22072,7 @@
         <v>27</v>
       </c>
       <c r="D1056">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E1056" t="s">
         <v>28</v>
@@ -22089,7 +22089,7 @@
         <v>27</v>
       </c>
       <c r="D1057">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1057" t="s">
         <v>28</v>
@@ -22106,7 +22106,7 @@
         <v>27</v>
       </c>
       <c r="D1058">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1058" t="s">
         <v>28</v>
@@ -22123,7 +22123,7 @@
         <v>27</v>
       </c>
       <c r="D1059">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1059" t="s">
         <v>28</v>
@@ -22140,7 +22140,7 @@
         <v>27</v>
       </c>
       <c r="D1060">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E1060" t="s">
         <v>28</v>
@@ -22157,7 +22157,7 @@
         <v>27</v>
       </c>
       <c r="D1061">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1061" t="s">
         <v>28</v>
@@ -22174,7 +22174,7 @@
         <v>27</v>
       </c>
       <c r="D1062">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E1062" t="s">
         <v>28</v>
@@ -22191,7 +22191,7 @@
         <v>27</v>
       </c>
       <c r="D1063">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E1063" t="s">
         <v>28</v>
@@ -22208,7 +22208,7 @@
         <v>27</v>
       </c>
       <c r="D1064">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1064" t="s">
         <v>28</v>
@@ -22225,7 +22225,7 @@
         <v>27</v>
       </c>
       <c r="D1065">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1065" t="s">
         <v>28</v>
@@ -22242,7 +22242,7 @@
         <v>27</v>
       </c>
       <c r="D1066">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E1066" t="s">
         <v>28</v>
@@ -22259,7 +22259,7 @@
         <v>27</v>
       </c>
       <c r="D1067">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E1067" t="s">
         <v>28</v>
@@ -22276,7 +22276,7 @@
         <v>27</v>
       </c>
       <c r="D1068">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1068" t="s">
         <v>28</v>
@@ -22293,7 +22293,7 @@
         <v>27</v>
       </c>
       <c r="D1069">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1069" t="s">
         <v>28</v>
@@ -22310,7 +22310,7 @@
         <v>27</v>
       </c>
       <c r="D1070">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E1070" t="s">
         <v>28</v>
@@ -22327,7 +22327,7 @@
         <v>27</v>
       </c>
       <c r="D1071">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E1071" t="s">
         <v>28</v>
@@ -22344,7 +22344,7 @@
         <v>27</v>
       </c>
       <c r="D1072">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1072" t="s">
         <v>28</v>
@@ -22361,7 +22361,7 @@
         <v>27</v>
       </c>
       <c r="D1073">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E1073" t="s">
         <v>28</v>
@@ -22378,7 +22378,7 @@
         <v>27</v>
       </c>
       <c r="D1074">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E1074" t="s">
         <v>28</v>
@@ -22395,7 +22395,7 @@
         <v>27</v>
       </c>
       <c r="D1075">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1075" t="s">
         <v>28</v>
@@ -22412,7 +22412,7 @@
         <v>27</v>
       </c>
       <c r="D1076">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E1076" t="s">
         <v>28</v>
@@ -22429,7 +22429,7 @@
         <v>27</v>
       </c>
       <c r="D1077">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E1077" t="s">
         <v>28</v>
@@ -22446,7 +22446,7 @@
         <v>27</v>
       </c>
       <c r="D1078">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E1078" t="s">
         <v>28</v>
@@ -22480,7 +22480,7 @@
         <v>27</v>
       </c>
       <c r="D1080">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1080" t="s">
         <v>28</v>
@@ -22497,7 +22497,7 @@
         <v>27</v>
       </c>
       <c r="D1081">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E1081" t="s">
         <v>28</v>
@@ -22514,7 +22514,7 @@
         <v>27</v>
       </c>
       <c r="D1082">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E1082" t="s">
         <v>28</v>
@@ -22531,7 +22531,7 @@
         <v>27</v>
       </c>
       <c r="D1083">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1083" t="s">
         <v>28</v>
@@ -22548,7 +22548,7 @@
         <v>27</v>
       </c>
       <c r="D1084">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E1084" t="s">
         <v>28</v>
@@ -22565,7 +22565,7 @@
         <v>27</v>
       </c>
       <c r="D1085">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1085" t="s">
         <v>28</v>
@@ -22582,7 +22582,7 @@
         <v>27</v>
       </c>
       <c r="D1086">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1086" t="s">
         <v>28</v>
@@ -22599,7 +22599,7 @@
         <v>27</v>
       </c>
       <c r="D1087">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E1087" t="s">
         <v>28</v>
@@ -22616,7 +22616,7 @@
         <v>27</v>
       </c>
       <c r="D1088">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1088" t="s">
         <v>28</v>
@@ -22633,7 +22633,7 @@
         <v>27</v>
       </c>
       <c r="D1089">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1089" t="s">
         <v>28</v>
@@ -22650,7 +22650,7 @@
         <v>27</v>
       </c>
       <c r="D1090">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1090" t="s">
         <v>28</v>
@@ -22667,7 +22667,7 @@
         <v>27</v>
       </c>
       <c r="D1091">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E1091" t="s">
         <v>28</v>
@@ -22684,7 +22684,7 @@
         <v>27</v>
       </c>
       <c r="D1092">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1092" t="s">
         <v>28</v>
@@ -22701,7 +22701,7 @@
         <v>27</v>
       </c>
       <c r="D1093">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E1093" t="s">
         <v>28</v>
@@ -22718,7 +22718,7 @@
         <v>27</v>
       </c>
       <c r="D1094">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E1094" t="s">
         <v>28</v>
@@ -22735,7 +22735,7 @@
         <v>27</v>
       </c>
       <c r="D1095">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1095" t="s">
         <v>28</v>
@@ -22752,7 +22752,7 @@
         <v>27</v>
       </c>
       <c r="D1096">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E1096" t="s">
         <v>28</v>
@@ -22786,7 +22786,7 @@
         <v>27</v>
       </c>
       <c r="D1098">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1098" t="s">
         <v>28</v>
@@ -22803,7 +22803,7 @@
         <v>27</v>
       </c>
       <c r="D1099">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1099" t="s">
         <v>28</v>
@@ -22820,7 +22820,7 @@
         <v>27</v>
       </c>
       <c r="D1100">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1100" t="s">
         <v>28</v>
@@ -22837,7 +22837,7 @@
         <v>27</v>
       </c>
       <c r="D1101">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1101" t="s">
         <v>28</v>
@@ -22854,7 +22854,7 @@
         <v>27</v>
       </c>
       <c r="D1102">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E1102" t="s">
         <v>28</v>
@@ -22871,7 +22871,7 @@
         <v>27</v>
       </c>
       <c r="D1103">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1103" t="s">
         <v>28</v>
@@ -22888,7 +22888,7 @@
         <v>27</v>
       </c>
       <c r="D1104">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E1104" t="s">
         <v>28</v>
@@ -22905,7 +22905,7 @@
         <v>27</v>
       </c>
       <c r="D1105">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1105" t="s">
         <v>28</v>
@@ -22922,7 +22922,7 @@
         <v>27</v>
       </c>
       <c r="D1106">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E1106" t="s">
         <v>28</v>
@@ -22939,7 +22939,7 @@
         <v>27</v>
       </c>
       <c r="D1107">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1107" t="s">
         <v>28</v>
@@ -22956,7 +22956,7 @@
         <v>27</v>
       </c>
       <c r="D1108">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1108" t="s">
         <v>28</v>
@@ -22973,7 +22973,7 @@
         <v>27</v>
       </c>
       <c r="D1109">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1109" t="s">
         <v>28</v>
@@ -22990,7 +22990,7 @@
         <v>27</v>
       </c>
       <c r="D1110">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1110" t="s">
         <v>28</v>
@@ -23007,7 +23007,7 @@
         <v>27</v>
       </c>
       <c r="D1111">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1111" t="s">
         <v>28</v>
@@ -23024,7 +23024,7 @@
         <v>27</v>
       </c>
       <c r="D1112">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1112" t="s">
         <v>28</v>
